--- a/artfynd/A 51041-2025 artfynd.xlsx
+++ b/artfynd/A 51041-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129795253</v>
+        <v>129795298</v>
       </c>
       <c r="B2" t="n">
         <v>79081</v>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>444185</v>
+        <v>444305</v>
       </c>
       <c r="R2" t="n">
-        <v>6787247</v>
+        <v>6787353</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -746,11 +746,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-11-22</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Gott om garnlav inom en radie av 50 m.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,7 +772,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129795291</v>
+        <v>129795253</v>
       </c>
       <c r="B3" t="n">
         <v>79081</v>
@@ -812,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>444412</v>
+        <v>444185</v>
       </c>
       <c r="R3" t="n">
-        <v>6787307</v>
+        <v>6787247</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -848,6 +843,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-11-22</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Gott om garnlav inom en radie av 50 m.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -874,7 +874,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129795298</v>
+        <v>129795244</v>
       </c>
       <c r="B4" t="n">
         <v>79081</v>
@@ -909,10 +909,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>444305</v>
+        <v>444105</v>
       </c>
       <c r="R4" t="n">
-        <v>6787353</v>
+        <v>6787246</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -971,7 +971,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129795285</v>
+        <v>129795283</v>
       </c>
       <c r="B5" t="n">
         <v>79081</v>
@@ -1000,16 +1000,19 @@
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>444405</v>
+        <v>444337</v>
       </c>
       <c r="R5" t="n">
-        <v>6787405</v>
+        <v>6787374</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1050,6 +1053,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1068,45 +1072,54 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129795244</v>
+        <v>129795197</v>
       </c>
       <c r="B6" t="n">
-        <v>79081</v>
+        <v>8450</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>444105</v>
+        <v>444406</v>
       </c>
       <c r="R6" t="n">
-        <v>6787246</v>
+        <v>6787392</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1147,6 +1160,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1165,45 +1179,54 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129795261</v>
+        <v>129795169</v>
       </c>
       <c r="B7" t="n">
-        <v>79081</v>
+        <v>8450</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>444193</v>
+        <v>444272</v>
       </c>
       <c r="R7" t="n">
-        <v>6787130</v>
+        <v>6787239</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1244,6 +1267,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1262,37 +1286,43 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129795283</v>
+        <v>129795190</v>
       </c>
       <c r="B8" t="n">
-        <v>79081</v>
+        <v>8450</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1300,10 +1330,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>444337</v>
+        <v>444510</v>
       </c>
       <c r="R8" t="n">
-        <v>6787374</v>
+        <v>6787276</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1363,54 +1393,45 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129795197</v>
+        <v>129795291</v>
       </c>
       <c r="B9" t="n">
-        <v>8450</v>
+        <v>79081</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>444406</v>
+        <v>444412</v>
       </c>
       <c r="R9" t="n">
-        <v>6787392</v>
+        <v>6787307</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1451,7 +1472,6 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1470,54 +1490,45 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129795169</v>
+        <v>129795285</v>
       </c>
       <c r="B10" t="n">
-        <v>8450</v>
+        <v>79081</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>444272</v>
+        <v>444405</v>
       </c>
       <c r="R10" t="n">
-        <v>6787239</v>
+        <v>6787405</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1558,7 +1569,6 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1577,54 +1587,45 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129795190</v>
+        <v>129795261</v>
       </c>
       <c r="B11" t="n">
-        <v>8450</v>
+        <v>79081</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>444510</v>
+        <v>444193</v>
       </c>
       <c r="R11" t="n">
-        <v>6787276</v>
+        <v>6787130</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1665,7 +1666,6 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -2094,41 +2094,40 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129795205</v>
+        <v>129795155</v>
       </c>
       <c r="B16" t="n">
-        <v>8450</v>
+        <v>57733</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N16" t="inlineStr"/>
@@ -2138,10 +2137,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>444343</v>
+        <v>444498</v>
       </c>
       <c r="R16" t="n">
-        <v>6787310</v>
+        <v>6787306</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2182,7 +2181,6 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2201,7 +2199,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129795155</v>
+        <v>129795153</v>
       </c>
       <c r="B17" t="n">
         <v>57733</v>
@@ -2234,7 +2232,7 @@
       <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N17" t="inlineStr"/>
@@ -2244,10 +2242,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>444498</v>
+        <v>444452</v>
       </c>
       <c r="R17" t="n">
-        <v>6787306</v>
+        <v>6787294</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2411,40 +2409,41 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129795153</v>
+        <v>129795174</v>
       </c>
       <c r="B19" t="n">
-        <v>57733</v>
+        <v>8450</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
       <c r="M19" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N19" t="inlineStr"/>
@@ -2454,10 +2453,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>444452</v>
+        <v>444166</v>
       </c>
       <c r="R19" t="n">
-        <v>6787294</v>
+        <v>6787161</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2498,6 +2497,7 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2516,7 +2516,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129795174</v>
+        <v>129795205</v>
       </c>
       <c r="B20" t="n">
         <v>8450</v>
@@ -2560,10 +2560,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>444166</v>
+        <v>444343</v>
       </c>
       <c r="R20" t="n">
-        <v>6787161</v>
+        <v>6787310</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2623,7 +2623,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129795273</v>
+        <v>129795310</v>
       </c>
       <c r="B21" t="n">
         <v>79081</v>
@@ -2652,16 +2652,19 @@
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>444548</v>
+        <v>444488</v>
       </c>
       <c r="R21" t="n">
-        <v>6787330</v>
+        <v>6787445</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2696,12 +2699,18 @@
           <t>2025-11-22</t>
         </is>
       </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Gott om garnlav inom en radie av 40m</t>
+        </is>
+      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -2720,7 +2729,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129795265</v>
+        <v>129795273</v>
       </c>
       <c r="B22" t="n">
         <v>79081</v>
@@ -2755,10 +2764,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>444278</v>
+        <v>444548</v>
       </c>
       <c r="R22" t="n">
-        <v>6787163</v>
+        <v>6787330</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2817,7 +2826,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129795310</v>
+        <v>129795265</v>
       </c>
       <c r="B23" t="n">
         <v>79081</v>
@@ -2846,19 +2855,16 @@
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>444488</v>
+        <v>444278</v>
       </c>
       <c r="R23" t="n">
-        <v>6787445</v>
+        <v>6787163</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2893,18 +2899,12 @@
           <t>2025-11-22</t>
         </is>
       </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Gott om garnlav inom en radie av 40m</t>
-        </is>
-      </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -3020,7 +3020,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129795198</v>
+        <v>129795200</v>
       </c>
       <c r="B25" t="n">
         <v>8450</v>
@@ -3064,10 +3064,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>444434</v>
+        <v>444429</v>
       </c>
       <c r="R25" t="n">
-        <v>6787384</v>
+        <v>6787341</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3127,7 +3127,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129795207</v>
+        <v>129795198</v>
       </c>
       <c r="B26" t="n">
         <v>8450</v>
@@ -3171,10 +3171,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>444221</v>
+        <v>444434</v>
       </c>
       <c r="R26" t="n">
-        <v>6787340</v>
+        <v>6787384</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3234,7 +3234,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129795200</v>
+        <v>129795207</v>
       </c>
       <c r="B27" t="n">
         <v>8450</v>
@@ -3278,10 +3278,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>444429</v>
+        <v>444221</v>
       </c>
       <c r="R27" t="n">
-        <v>6787341</v>
+        <v>6787340</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3448,41 +3448,40 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129795176</v>
+        <v>129795142</v>
       </c>
       <c r="B29" t="n">
-        <v>8450</v>
+        <v>57733</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr"/>
       <c r="M29" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N29" t="inlineStr"/>
@@ -3492,10 +3491,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>444215</v>
+        <v>444276</v>
       </c>
       <c r="R29" t="n">
-        <v>6787151</v>
+        <v>6787287</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3536,7 +3535,6 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -3555,10 +3553,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129795142</v>
+        <v>129795268</v>
       </c>
       <c r="B30" t="n">
-        <v>57733</v>
+        <v>79081</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3566,42 +3564,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>444276</v>
+        <v>444383</v>
       </c>
       <c r="R30" t="n">
-        <v>6787287</v>
+        <v>6787218</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3660,54 +3650,45 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129795189</v>
+        <v>129795256</v>
       </c>
       <c r="B31" t="n">
-        <v>8450</v>
+        <v>79081</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>444500</v>
+        <v>444226</v>
       </c>
       <c r="R31" t="n">
-        <v>6787274</v>
+        <v>6787196</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3748,7 +3729,6 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
-      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
@@ -3767,7 +3747,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129795187</v>
+        <v>129795176</v>
       </c>
       <c r="B32" t="n">
         <v>8450</v>
@@ -3801,7 +3781,7 @@
       <c r="L32" t="inlineStr"/>
       <c r="M32" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="N32" t="inlineStr"/>
@@ -3811,10 +3791,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>444487</v>
+        <v>444215</v>
       </c>
       <c r="R32" t="n">
-        <v>6787321</v>
+        <v>6787151</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3874,45 +3854,54 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129795268</v>
+        <v>129795189</v>
       </c>
       <c r="B33" t="n">
-        <v>79081</v>
+        <v>8450</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>444383</v>
+        <v>444500</v>
       </c>
       <c r="R33" t="n">
-        <v>6787218</v>
+        <v>6787274</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3953,6 +3942,7 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
+      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -3971,45 +3961,54 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129795256</v>
+        <v>129795187</v>
       </c>
       <c r="B34" t="n">
-        <v>79081</v>
+        <v>8450</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>444226</v>
+        <v>444487</v>
       </c>
       <c r="R34" t="n">
-        <v>6787196</v>
+        <v>6787321</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4050,6 +4049,7 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
+      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
@@ -4068,7 +4068,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129795270</v>
+        <v>129795296</v>
       </c>
       <c r="B35" t="n">
         <v>79081</v>
@@ -4097,16 +4097,19 @@
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>444416</v>
+        <v>444299</v>
       </c>
       <c r="R35" t="n">
-        <v>6787260</v>
+        <v>6787304</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4141,12 +4144,18 @@
           <t>2025-11-22</t>
         </is>
       </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 50 m.</t>
+        </is>
+      </c>
       <c r="AD35" t="b">
         <v>0</v>
       </c>
       <c r="AE35" t="b">
         <v>0</v>
       </c>
+      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
@@ -4165,7 +4174,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129795296</v>
+        <v>129795249</v>
       </c>
       <c r="B36" t="n">
         <v>79081</v>
@@ -4194,19 +4203,16 @@
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
-      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>444299</v>
+        <v>444267</v>
       </c>
       <c r="R36" t="n">
-        <v>6787304</v>
+        <v>6787295</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4241,18 +4247,12 @@
           <t>2025-11-22</t>
         </is>
       </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 50 m.</t>
-        </is>
-      </c>
       <c r="AD36" t="b">
         <v>0</v>
       </c>
       <c r="AE36" t="b">
         <v>0</v>
       </c>
-      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
@@ -4271,7 +4271,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129795269</v>
+        <v>129795270</v>
       </c>
       <c r="B37" t="n">
         <v>79081</v>
@@ -4306,10 +4306,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>444429</v>
+        <v>444416</v>
       </c>
       <c r="R37" t="n">
-        <v>6787240</v>
+        <v>6787260</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4368,7 +4368,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129795249</v>
+        <v>129795269</v>
       </c>
       <c r="B38" t="n">
         <v>79081</v>
@@ -4403,10 +4403,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>444267</v>
+        <v>444429</v>
       </c>
       <c r="R38" t="n">
-        <v>6787295</v>
+        <v>6787240</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4465,41 +4465,40 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129795202</v>
+        <v>129795165</v>
       </c>
       <c r="B39" t="n">
-        <v>8450</v>
+        <v>57733</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr"/>
       <c r="L39" t="inlineStr"/>
       <c r="M39" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N39" t="inlineStr"/>
@@ -4509,10 +4508,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>444413</v>
+        <v>444251</v>
       </c>
       <c r="R39" t="n">
-        <v>6787314</v>
+        <v>6787376</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4553,7 +4552,6 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
-      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -4572,10 +4570,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129795165</v>
+        <v>129795133</v>
       </c>
       <c r="B40" t="n">
-        <v>57733</v>
+        <v>57896</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4583,21 +4581,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4605,7 +4603,7 @@
       <c r="L40" t="inlineStr"/>
       <c r="M40" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N40" t="inlineStr"/>
@@ -4615,10 +4613,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>444251</v>
+        <v>444226</v>
       </c>
       <c r="R40" t="n">
-        <v>6787376</v>
+        <v>6787236</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4677,7 +4675,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129795193</v>
+        <v>129795202</v>
       </c>
       <c r="B41" t="n">
         <v>8450</v>
@@ -4721,10 +4719,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>444508</v>
+        <v>444413</v>
       </c>
       <c r="R41" t="n">
-        <v>6787352</v>
+        <v>6787314</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4784,40 +4782,41 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129795133</v>
+        <v>129795193</v>
       </c>
       <c r="B42" t="n">
-        <v>57896</v>
+        <v>8450</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>103021</v>
+        <v>106545</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr"/>
       <c r="K42" t="inlineStr"/>
       <c r="L42" t="inlineStr"/>
       <c r="M42" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N42" t="inlineStr"/>
@@ -4827,10 +4826,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>444226</v>
+        <v>444508</v>
       </c>
       <c r="R42" t="n">
-        <v>6787236</v>
+        <v>6787352</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4871,6 +4870,7 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
+      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
@@ -4889,10 +4889,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129795282</v>
+        <v>129795136</v>
       </c>
       <c r="B43" t="n">
-        <v>79081</v>
+        <v>91614</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4900,21 +4900,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4927,10 +4927,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>444374</v>
+        <v>444235</v>
       </c>
       <c r="R43" t="n">
-        <v>6787384</v>
+        <v>6787149</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4963,11 +4963,6 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-11-22</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 50 m.</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -4995,7 +4990,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129795293</v>
+        <v>129795282</v>
       </c>
       <c r="B44" t="n">
         <v>79081</v>
@@ -5024,16 +5019,19 @@
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
+      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>444365</v>
+        <v>444374</v>
       </c>
       <c r="R44" t="n">
-        <v>6787285</v>
+        <v>6787384</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5070,7 +5068,7 @@
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>Rikligt med garnlav inom en radie av 50m.</t>
+          <t>Rikligt med garnlav inom en radie av 50 m.</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5079,6 +5077,7 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
+      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
@@ -5097,10 +5096,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129795136</v>
+        <v>129795293</v>
       </c>
       <c r="B45" t="n">
-        <v>91614</v>
+        <v>79081</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5108,37 +5107,34 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="J45" t="inlineStr"/>
-      <c r="K45" t="inlineStr"/>
-      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>444235</v>
+        <v>444365</v>
       </c>
       <c r="R45" t="n">
-        <v>6787149</v>
+        <v>6787285</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5173,13 +5169,17 @@
           <t>2025-11-22</t>
         </is>
       </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 50m.</t>
+        </is>
+      </c>
       <c r="AD45" t="b">
         <v>0</v>
       </c>
       <c r="AE45" t="b">
         <v>0</v>
       </c>
-      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
@@ -5198,41 +5198,40 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129795170</v>
+        <v>129795158</v>
       </c>
       <c r="B46" t="n">
-        <v>8450</v>
+        <v>57733</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="J46" t="inlineStr"/>
       <c r="K46" t="inlineStr"/>
       <c r="L46" t="inlineStr"/>
       <c r="M46" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N46" t="inlineStr"/>
@@ -5242,10 +5241,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>444172</v>
+        <v>444501</v>
       </c>
       <c r="R46" t="n">
-        <v>6787202</v>
+        <v>6787402</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5286,7 +5285,6 @@
       <c r="AE46" t="b">
         <v>0</v>
       </c>
-      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
@@ -5305,40 +5303,41 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129795158</v>
+        <v>129795170</v>
       </c>
       <c r="B47" t="n">
-        <v>57733</v>
+        <v>8450</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr"/>
       <c r="K47" t="inlineStr"/>
       <c r="L47" t="inlineStr"/>
       <c r="M47" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N47" t="inlineStr"/>
@@ -5348,10 +5347,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>444501</v>
+        <v>444172</v>
       </c>
       <c r="R47" t="n">
-        <v>6787402</v>
+        <v>6787202</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5392,6 +5391,7 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
+      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
@@ -5410,7 +5410,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129795309</v>
+        <v>129795260</v>
       </c>
       <c r="B48" t="n">
         <v>79081</v>
@@ -5445,10 +5445,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>444095</v>
+        <v>444197</v>
       </c>
       <c r="R48" t="n">
-        <v>6787293</v>
+        <v>6787111</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5481,11 +5481,6 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-11-22</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>8.32</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5512,7 +5507,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129795260</v>
+        <v>129795250</v>
       </c>
       <c r="B49" t="n">
         <v>79081</v>
@@ -5547,10 +5542,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>444197</v>
+        <v>444295</v>
       </c>
       <c r="R49" t="n">
-        <v>6787111</v>
+        <v>6787287</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5609,10 +5604,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129795250</v>
+        <v>129795138</v>
       </c>
       <c r="B50" t="n">
-        <v>79081</v>
+        <v>91614</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5620,34 +5615,37 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
+      <c r="J50" t="inlineStr"/>
+      <c r="K50" t="inlineStr"/>
+      <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>444295</v>
+        <v>444250</v>
       </c>
       <c r="R50" t="n">
-        <v>6787287</v>
+        <v>6787196</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5688,6 +5686,7 @@
       <c r="AE50" t="b">
         <v>0</v>
       </c>
+      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>
@@ -5706,7 +5705,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129795246</v>
+        <v>129795309</v>
       </c>
       <c r="B51" t="n">
         <v>79081</v>
@@ -5741,10 +5740,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>444145</v>
+        <v>444095</v>
       </c>
       <c r="R51" t="n">
-        <v>6787239</v>
+        <v>6787293</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5781,7 +5780,7 @@
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>Rikligt med garnlav inom en radie av 40m.</t>
+          <t>8.32</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5808,10 +5807,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129795138</v>
+        <v>129795246</v>
       </c>
       <c r="B52" t="n">
-        <v>91614</v>
+        <v>79081</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5819,37 +5818,34 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="J52" t="inlineStr"/>
-      <c r="K52" t="inlineStr"/>
-      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>444250</v>
+        <v>444145</v>
       </c>
       <c r="R52" t="n">
-        <v>6787196</v>
+        <v>6787239</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5884,13 +5880,17 @@
           <t>2025-11-22</t>
         </is>
       </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 40m.</t>
+        </is>
+      </c>
       <c r="AD52" t="b">
         <v>0</v>
       </c>
       <c r="AE52" t="b">
         <v>0</v>
       </c>
-      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
@@ -5909,7 +5909,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129795277</v>
+        <v>129795279</v>
       </c>
       <c r="B53" t="n">
         <v>79081</v>
@@ -5944,10 +5944,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>444491</v>
+        <v>444463</v>
       </c>
       <c r="R53" t="n">
-        <v>6787412</v>
+        <v>6787459</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6006,54 +6006,45 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129795199</v>
+        <v>129795277</v>
       </c>
       <c r="B54" t="n">
-        <v>8450</v>
+        <v>79081</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
-      <c r="J54" t="inlineStr"/>
-      <c r="K54" t="inlineStr"/>
-      <c r="L54" t="inlineStr"/>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>444431</v>
+        <v>444491</v>
       </c>
       <c r="R54" t="n">
-        <v>6787350</v>
+        <v>6787412</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6094,7 +6085,6 @@
       <c r="AE54" t="b">
         <v>0</v>
       </c>
-      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
@@ -6113,45 +6103,53 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129795279</v>
+        <v>129795131</v>
       </c>
       <c r="B55" t="n">
-        <v>79081</v>
+        <v>56926</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
+      <c r="K55" t="inlineStr"/>
+      <c r="L55" t="inlineStr"/>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>444463</v>
+        <v>444250</v>
       </c>
       <c r="R55" t="n">
-        <v>6787459</v>
+        <v>6787212</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6210,41 +6208,40 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129795172</v>
+        <v>129795134</v>
       </c>
       <c r="B56" t="n">
-        <v>8450</v>
+        <v>57896</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>106545</v>
+        <v>103021</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
-      <c r="J56" t="inlineStr"/>
       <c r="K56" t="inlineStr"/>
       <c r="L56" t="inlineStr"/>
       <c r="M56" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N56" t="inlineStr"/>
@@ -6254,10 +6251,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>444225</v>
+        <v>444289</v>
       </c>
       <c r="R56" t="n">
-        <v>6787223</v>
+        <v>6787357</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6298,7 +6295,6 @@
       <c r="AE56" t="b">
         <v>0</v>
       </c>
-      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
       </c>
@@ -6317,10 +6313,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129795131</v>
+        <v>129795172</v>
       </c>
       <c r="B57" t="n">
-        <v>56926</v>
+        <v>8450</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6328,29 +6324,30 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>100138</v>
+        <v>106545</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
+      <c r="J57" t="inlineStr"/>
       <c r="K57" t="inlineStr"/>
       <c r="L57" t="inlineStr"/>
       <c r="M57" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N57" t="inlineStr"/>
@@ -6360,10 +6357,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>444250</v>
+        <v>444225</v>
       </c>
       <c r="R57" t="n">
-        <v>6787212</v>
+        <v>6787223</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6404,6 +6401,7 @@
       <c r="AE57" t="b">
         <v>0</v>
       </c>
+      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
@@ -6422,40 +6420,41 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129795147</v>
+        <v>129795199</v>
       </c>
       <c r="B58" t="n">
-        <v>57733</v>
+        <v>8450</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
+      <c r="J58" t="inlineStr"/>
       <c r="K58" t="inlineStr"/>
       <c r="L58" t="inlineStr"/>
       <c r="M58" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N58" t="inlineStr"/>
@@ -6465,10 +6464,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>444220</v>
+        <v>444431</v>
       </c>
       <c r="R58" t="n">
-        <v>6787221</v>
+        <v>6787350</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6509,6 +6508,7 @@
       <c r="AE58" t="b">
         <v>0</v>
       </c>
+      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
       </c>
@@ -6527,40 +6527,41 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129795161</v>
+        <v>129795184</v>
       </c>
       <c r="B59" t="n">
-        <v>57733</v>
+        <v>8450</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
+      <c r="J59" t="inlineStr"/>
       <c r="K59" t="inlineStr"/>
       <c r="L59" t="inlineStr"/>
       <c r="M59" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N59" t="inlineStr"/>
@@ -6570,10 +6571,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>444433</v>
+        <v>444452</v>
       </c>
       <c r="R59" t="n">
-        <v>6787338</v>
+        <v>6787305</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6614,6 +6615,7 @@
       <c r="AE59" t="b">
         <v>0</v>
       </c>
+      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
       </c>
@@ -6632,41 +6634,40 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129795184</v>
+        <v>129795161</v>
       </c>
       <c r="B60" t="n">
-        <v>8450</v>
+        <v>57733</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
-      <c r="J60" t="inlineStr"/>
       <c r="K60" t="inlineStr"/>
       <c r="L60" t="inlineStr"/>
       <c r="M60" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N60" t="inlineStr"/>
@@ -6676,10 +6677,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>444452</v>
+        <v>444433</v>
       </c>
       <c r="R60" t="n">
-        <v>6787305</v>
+        <v>6787338</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6720,7 +6721,6 @@
       <c r="AE60" t="b">
         <v>0</v>
       </c>
-      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
       </c>
@@ -6739,10 +6739,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129795134</v>
+        <v>129795147</v>
       </c>
       <c r="B61" t="n">
-        <v>57896</v>
+        <v>57733</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6750,21 +6750,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6772,7 +6772,7 @@
       <c r="L61" t="inlineStr"/>
       <c r="M61" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N61" t="inlineStr"/>
@@ -6782,10 +6782,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>444289</v>
+        <v>444220</v>
       </c>
       <c r="R61" t="n">
-        <v>6787357</v>
+        <v>6787221</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6951,45 +6951,54 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129795125</v>
+        <v>129795191</v>
       </c>
       <c r="B63" t="n">
-        <v>79700</v>
+        <v>8450</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
+      <c r="J63" t="inlineStr"/>
+      <c r="K63" t="inlineStr"/>
+      <c r="L63" t="inlineStr"/>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>444329</v>
+        <v>444520</v>
       </c>
       <c r="R63" t="n">
-        <v>6787371</v>
+        <v>6787287</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7030,6 +7039,7 @@
       <c r="AE63" t="b">
         <v>0</v>
       </c>
+      <c r="AF63" t="inlineStr"/>
       <c r="AG63" t="b">
         <v>0</v>
       </c>
@@ -7048,7 +7058,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129795191</v>
+        <v>129795177</v>
       </c>
       <c r="B64" t="n">
         <v>8450</v>
@@ -7082,7 +7092,7 @@
       <c r="L64" t="inlineStr"/>
       <c r="M64" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="N64" t="inlineStr"/>
@@ -7092,10 +7102,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>444520</v>
+        <v>444342</v>
       </c>
       <c r="R64" t="n">
-        <v>6787287</v>
+        <v>6787223</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7155,41 +7165,40 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129795177</v>
+        <v>129795162</v>
       </c>
       <c r="B65" t="n">
-        <v>8450</v>
+        <v>57733</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
-      <c r="J65" t="inlineStr"/>
       <c r="K65" t="inlineStr"/>
       <c r="L65" t="inlineStr"/>
       <c r="M65" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N65" t="inlineStr"/>
@@ -7199,10 +7208,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>444342</v>
+        <v>444428</v>
       </c>
       <c r="R65" t="n">
-        <v>6787223</v>
+        <v>6787329</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7243,7 +7252,6 @@
       <c r="AE65" t="b">
         <v>0</v>
       </c>
-      <c r="AF65" t="inlineStr"/>
       <c r="AG65" t="b">
         <v>0</v>
       </c>
@@ -7262,10 +7270,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129795162</v>
+        <v>129795125</v>
       </c>
       <c r="B66" t="n">
-        <v>57733</v>
+        <v>79700</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7273,42 +7281,34 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
-      <c r="K66" t="inlineStr"/>
-      <c r="L66" t="inlineStr"/>
-      <c r="M66" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>444428</v>
+        <v>444329</v>
       </c>
       <c r="R66" t="n">
-        <v>6787329</v>
+        <v>6787371</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7367,10 +7367,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129795257</v>
+        <v>129795150</v>
       </c>
       <c r="B67" t="n">
-        <v>79081</v>
+        <v>57733</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7378,34 +7378,42 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
+      <c r="K67" t="inlineStr"/>
+      <c r="L67" t="inlineStr"/>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>444168</v>
+        <v>444413</v>
       </c>
       <c r="R67" t="n">
-        <v>6787171</v>
+        <v>6787222</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7464,10 +7472,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129795150</v>
+        <v>129795257</v>
       </c>
       <c r="B68" t="n">
-        <v>57733</v>
+        <v>79081</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7475,42 +7483,34 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
-      <c r="K68" t="inlineStr"/>
-      <c r="L68" t="inlineStr"/>
-      <c r="M68" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>444413</v>
+        <v>444168</v>
       </c>
       <c r="R68" t="n">
-        <v>6787222</v>
+        <v>6787171</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7569,10 +7569,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129795280</v>
+        <v>129795166</v>
       </c>
       <c r="B69" t="n">
-        <v>79081</v>
+        <v>57733</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7580,34 +7580,42 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
+      <c r="K69" t="inlineStr"/>
+      <c r="L69" t="inlineStr"/>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>444451</v>
+        <v>444254</v>
       </c>
       <c r="R69" t="n">
-        <v>6787467</v>
+        <v>6787333</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7666,7 +7674,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129795272</v>
+        <v>129795280</v>
       </c>
       <c r="B70" t="n">
         <v>79081</v>
@@ -7701,10 +7709,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>444553</v>
+        <v>444451</v>
       </c>
       <c r="R70" t="n">
-        <v>6787299</v>
+        <v>6787467</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7763,10 +7771,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129795287</v>
+        <v>129795135</v>
       </c>
       <c r="B71" t="n">
-        <v>79081</v>
+        <v>91614</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7774,34 +7782,37 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
+      <c r="J71" t="inlineStr"/>
+      <c r="K71" t="inlineStr"/>
+      <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>444430</v>
+        <v>444158</v>
       </c>
       <c r="R71" t="n">
-        <v>6787384</v>
+        <v>6787148</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7842,6 +7853,7 @@
       <c r="AE71" t="b">
         <v>0</v>
       </c>
+      <c r="AF71" t="inlineStr"/>
       <c r="AG71" t="b">
         <v>0</v>
       </c>
@@ -7860,7 +7872,7 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129795284</v>
+        <v>129795243</v>
       </c>
       <c r="B72" t="n">
         <v>79081</v>
@@ -7895,10 +7907,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>444363</v>
+        <v>444159</v>
       </c>
       <c r="R72" t="n">
-        <v>6787411</v>
+        <v>6787297</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7957,7 +7969,7 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129795243</v>
+        <v>129795272</v>
       </c>
       <c r="B73" t="n">
         <v>79081</v>
@@ -7992,10 +8004,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>444159</v>
+        <v>444553</v>
       </c>
       <c r="R73" t="n">
-        <v>6787297</v>
+        <v>6787299</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8054,53 +8066,45 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129795208</v>
+        <v>129795287</v>
       </c>
       <c r="B74" t="n">
-        <v>58106</v>
+        <v>79081</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>103015</v>
+        <v>6425</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
-      <c r="K74" t="inlineStr"/>
-      <c r="L74" t="inlineStr"/>
-      <c r="M74" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>444434</v>
+        <v>444430</v>
       </c>
       <c r="R74" t="n">
-        <v>6787357</v>
+        <v>6787384</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8159,10 +8163,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129795135</v>
+        <v>129795284</v>
       </c>
       <c r="B75" t="n">
-        <v>91614</v>
+        <v>79081</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8170,37 +8174,34 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
-      <c r="J75" t="inlineStr"/>
-      <c r="K75" t="inlineStr"/>
-      <c r="N75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>444158</v>
+        <v>444363</v>
       </c>
       <c r="R75" t="n">
-        <v>6787148</v>
+        <v>6787411</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8241,7 +8242,6 @@
       <c r="AE75" t="b">
         <v>0</v>
       </c>
-      <c r="AF75" t="inlineStr"/>
       <c r="AG75" t="b">
         <v>0</v>
       </c>
@@ -8260,10 +8260,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129795182</v>
+        <v>129795208</v>
       </c>
       <c r="B76" t="n">
-        <v>8450</v>
+        <v>58106</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8271,30 +8271,29 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>106545</v>
+        <v>103015</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
-      <c r="J76" t="inlineStr"/>
       <c r="K76" t="inlineStr"/>
       <c r="L76" t="inlineStr"/>
       <c r="M76" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N76" t="inlineStr"/>
@@ -8304,10 +8303,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>444417</v>
+        <v>444434</v>
       </c>
       <c r="R76" t="n">
-        <v>6787266</v>
+        <v>6787357</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8348,7 +8347,6 @@
       <c r="AE76" t="b">
         <v>0</v>
       </c>
-      <c r="AF76" t="inlineStr"/>
       <c r="AG76" t="b">
         <v>0</v>
       </c>
@@ -8367,40 +8365,41 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129795166</v>
+        <v>129795182</v>
       </c>
       <c r="B77" t="n">
-        <v>57733</v>
+        <v>8450</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
+      <c r="J77" t="inlineStr"/>
       <c r="K77" t="inlineStr"/>
       <c r="L77" t="inlineStr"/>
       <c r="M77" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N77" t="inlineStr"/>
@@ -8410,10 +8409,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>444254</v>
+        <v>444417</v>
       </c>
       <c r="R77" t="n">
-        <v>6787333</v>
+        <v>6787266</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8454,6 +8453,7 @@
       <c r="AE77" t="b">
         <v>0</v>
       </c>
+      <c r="AF77" t="inlineStr"/>
       <c r="AG77" t="b">
         <v>0</v>
       </c>
@@ -8472,43 +8472,37 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129795194</v>
+        <v>129795300</v>
       </c>
       <c r="B78" t="n">
-        <v>8450</v>
+        <v>79081</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
       <c r="J78" t="inlineStr"/>
       <c r="K78" t="inlineStr"/>
-      <c r="L78" t="inlineStr"/>
-      <c r="M78" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
@@ -8516,10 +8510,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>444501</v>
+        <v>444264</v>
       </c>
       <c r="R78" t="n">
-        <v>6787363</v>
+        <v>6787349</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8552,6 +8546,11 @@
       <c r="AA78" t="inlineStr">
         <is>
           <t>2025-11-22</t>
+        </is>
+      </c>
+      <c r="AC78" t="inlineStr">
+        <is>
+          <t>Garnlav i de flesta träd inom en radie av 50 m.</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8579,7 +8578,7 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129795300</v>
+        <v>129795286</v>
       </c>
       <c r="B79" t="n">
         <v>79081</v>
@@ -8617,10 +8616,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>444264</v>
+        <v>444440</v>
       </c>
       <c r="R79" t="n">
-        <v>6787349</v>
+        <v>6787388</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8657,7 +8656,7 @@
       </c>
       <c r="AC79" t="inlineStr">
         <is>
-          <t>Garnlav i de flesta träd inom en radie av 50 m.</t>
+          <t>Gott om garnlav inom en radie av 50 m.</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -8685,7 +8684,7 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129795307</v>
+        <v>129795241</v>
       </c>
       <c r="B80" t="n">
         <v>79081</v>
@@ -8720,10 +8719,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>444134</v>
+        <v>444117</v>
       </c>
       <c r="R80" t="n">
-        <v>6787304</v>
+        <v>6787277</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8782,10 +8781,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129795286</v>
+        <v>129795126</v>
       </c>
       <c r="B81" t="n">
-        <v>79081</v>
+        <v>79700</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8793,37 +8792,34 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
-      <c r="J81" t="inlineStr"/>
-      <c r="K81" t="inlineStr"/>
-      <c r="N81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>444440</v>
+        <v>444358</v>
       </c>
       <c r="R81" t="n">
-        <v>6787388</v>
+        <v>6787400</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8858,18 +8854,12 @@
           <t>2025-11-22</t>
         </is>
       </c>
-      <c r="AC81" t="inlineStr">
-        <is>
-          <t>Gott om garnlav inom en radie av 50 m.</t>
-        </is>
-      </c>
       <c r="AD81" t="b">
         <v>0</v>
       </c>
       <c r="AE81" t="b">
         <v>0</v>
       </c>
-      <c r="AF81" t="inlineStr"/>
       <c r="AG81" t="b">
         <v>0</v>
       </c>
@@ -8888,7 +8878,7 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129795241</v>
+        <v>129795307</v>
       </c>
       <c r="B82" t="n">
         <v>79081</v>
@@ -8923,10 +8913,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>444117</v>
+        <v>444134</v>
       </c>
       <c r="R82" t="n">
-        <v>6787277</v>
+        <v>6787304</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8985,7 +8975,7 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129795126</v>
+        <v>129795127</v>
       </c>
       <c r="B83" t="n">
         <v>79700</v>
@@ -9020,10 +9010,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>444358</v>
+        <v>444432</v>
       </c>
       <c r="R83" t="n">
-        <v>6787400</v>
+        <v>6787388</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9189,45 +9179,54 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129795127</v>
+        <v>129795194</v>
       </c>
       <c r="B85" t="n">
-        <v>79700</v>
+        <v>8450</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
+      <c r="J85" t="inlineStr"/>
+      <c r="K85" t="inlineStr"/>
+      <c r="L85" t="inlineStr"/>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>444432</v>
+        <v>444501</v>
       </c>
       <c r="R85" t="n">
-        <v>6787388</v>
+        <v>6787363</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9268,6 +9267,7 @@
       <c r="AE85" t="b">
         <v>0</v>
       </c>
+      <c r="AF85" t="inlineStr"/>
       <c r="AG85" t="b">
         <v>0</v>
       </c>
@@ -9286,7 +9286,7 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129795308</v>
+        <v>129795242</v>
       </c>
       <c r="B86" t="n">
         <v>79081</v>
@@ -9321,7 +9321,7 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>444098</v>
+        <v>444125</v>
       </c>
       <c r="R86" t="n">
         <v>6787297</v>
@@ -9383,45 +9383,54 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129795242</v>
+        <v>129795181</v>
       </c>
       <c r="B87" t="n">
-        <v>79081</v>
+        <v>8450</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
+      <c r="J87" t="inlineStr"/>
+      <c r="K87" t="inlineStr"/>
+      <c r="L87" t="inlineStr"/>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>444125</v>
+        <v>444408</v>
       </c>
       <c r="R87" t="n">
-        <v>6787297</v>
+        <v>6787250</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9462,6 +9471,7 @@
       <c r="AE87" t="b">
         <v>0</v>
       </c>
+      <c r="AF87" t="inlineStr"/>
       <c r="AG87" t="b">
         <v>0</v>
       </c>
@@ -9480,7 +9490,7 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129795181</v>
+        <v>129795192</v>
       </c>
       <c r="B88" t="n">
         <v>8450</v>
@@ -9524,10 +9534,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>444408</v>
+        <v>444549</v>
       </c>
       <c r="R88" t="n">
-        <v>6787250</v>
+        <v>6787335</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9587,54 +9597,45 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>129795192</v>
+        <v>129795308</v>
       </c>
       <c r="B89" t="n">
-        <v>8450</v>
+        <v>79081</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
-      <c r="J89" t="inlineStr"/>
-      <c r="K89" t="inlineStr"/>
-      <c r="L89" t="inlineStr"/>
-      <c r="M89" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>444549</v>
+        <v>444098</v>
       </c>
       <c r="R89" t="n">
-        <v>6787335</v>
+        <v>6787297</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9675,7 +9676,6 @@
       <c r="AE89" t="b">
         <v>0</v>
       </c>
-      <c r="AF89" t="inlineStr"/>
       <c r="AG89" t="b">
         <v>0</v>
       </c>
@@ -9694,10 +9694,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>129795121</v>
+        <v>129795305</v>
       </c>
       <c r="B90" t="n">
-        <v>79700</v>
+        <v>79081</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9705,21 +9705,21 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9729,10 +9729,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>444254</v>
+        <v>444169</v>
       </c>
       <c r="R90" t="n">
-        <v>6787204</v>
+        <v>6787323</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9791,54 +9791,45 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>129795167</v>
+        <v>129795288</v>
       </c>
       <c r="B91" t="n">
-        <v>8450</v>
+        <v>79081</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
-      <c r="J91" t="inlineStr"/>
-      <c r="K91" t="inlineStr"/>
-      <c r="L91" t="inlineStr"/>
-      <c r="M91" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>444132</v>
+        <v>444420</v>
       </c>
       <c r="R91" t="n">
-        <v>6787237</v>
+        <v>6787366</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9879,7 +9870,6 @@
       <c r="AE91" t="b">
         <v>0</v>
       </c>
-      <c r="AF91" t="inlineStr"/>
       <c r="AG91" t="b">
         <v>0</v>
       </c>
@@ -9898,10 +9888,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>129795152</v>
+        <v>129795297</v>
       </c>
       <c r="B92" t="n">
-        <v>57733</v>
+        <v>79081</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9909,42 +9899,34 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
-      <c r="K92" t="inlineStr"/>
-      <c r="L92" t="inlineStr"/>
-      <c r="M92" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>444434</v>
+        <v>444297</v>
       </c>
       <c r="R92" t="n">
-        <v>6787304</v>
+        <v>6787333</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10003,10 +9985,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>129795123</v>
+        <v>129795262</v>
       </c>
       <c r="B93" t="n">
-        <v>79700</v>
+        <v>79081</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10014,21 +9996,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -10038,10 +10020,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>444530</v>
+        <v>444219</v>
       </c>
       <c r="R93" t="n">
-        <v>6787326</v>
+        <v>6787163</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10100,7 +10082,7 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>129795124</v>
+        <v>129795121</v>
       </c>
       <c r="B94" t="n">
         <v>79700</v>
@@ -10135,10 +10117,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>444393</v>
+        <v>444254</v>
       </c>
       <c r="R94" t="n">
-        <v>6787395</v>
+        <v>6787204</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10197,7 +10179,7 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>129795305</v>
+        <v>129795245</v>
       </c>
       <c r="B95" t="n">
         <v>79081</v>
@@ -10232,10 +10214,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>444169</v>
+        <v>444113</v>
       </c>
       <c r="R95" t="n">
-        <v>6787323</v>
+        <v>6787239</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10294,10 +10276,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>129795288</v>
+        <v>129795124</v>
       </c>
       <c r="B96" t="n">
-        <v>79081</v>
+        <v>79700</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10305,21 +10287,21 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10329,10 +10311,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>444420</v>
+        <v>444393</v>
       </c>
       <c r="R96" t="n">
-        <v>6787366</v>
+        <v>6787395</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10391,10 +10373,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>129795245</v>
+        <v>129795123</v>
       </c>
       <c r="B97" t="n">
-        <v>79081</v>
+        <v>79700</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10402,21 +10384,21 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -10426,10 +10408,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>444113</v>
+        <v>444530</v>
       </c>
       <c r="R97" t="n">
-        <v>6787239</v>
+        <v>6787326</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10488,7 +10470,7 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>129795297</v>
+        <v>129795252</v>
       </c>
       <c r="B98" t="n">
         <v>79081</v>
@@ -10523,10 +10505,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>444297</v>
+        <v>444249</v>
       </c>
       <c r="R98" t="n">
-        <v>6787333</v>
+        <v>6787249</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10559,6 +10541,11 @@
       <c r="AA98" t="inlineStr">
         <is>
           <t>2025-11-22</t>
+        </is>
+      </c>
+      <c r="AC98" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 40m.</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -10585,10 +10572,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>129795262</v>
+        <v>129795152</v>
       </c>
       <c r="B99" t="n">
-        <v>79081</v>
+        <v>57733</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10596,34 +10583,42 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
+      <c r="K99" t="inlineStr"/>
+      <c r="L99" t="inlineStr"/>
+      <c r="M99" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>444219</v>
+        <v>444434</v>
       </c>
       <c r="R99" t="n">
-        <v>6787163</v>
+        <v>6787304</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10682,45 +10677,54 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>129795252</v>
+        <v>129795167</v>
       </c>
       <c r="B100" t="n">
-        <v>79081</v>
+        <v>8450</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
+      <c r="J100" t="inlineStr"/>
+      <c r="K100" t="inlineStr"/>
+      <c r="L100" t="inlineStr"/>
+      <c r="M100" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>444249</v>
+        <v>444132</v>
       </c>
       <c r="R100" t="n">
-        <v>6787249</v>
+        <v>6787237</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10755,17 +10759,13 @@
           <t>2025-11-22</t>
         </is>
       </c>
-      <c r="AC100" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 40m.</t>
-        </is>
-      </c>
       <c r="AD100" t="b">
         <v>0</v>
       </c>
       <c r="AE100" t="b">
         <v>0</v>
       </c>
+      <c r="AF100" t="inlineStr"/>
       <c r="AG100" t="b">
         <v>0</v>
       </c>
@@ -10784,7 +10784,7 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>129795264</v>
+        <v>129795248</v>
       </c>
       <c r="B101" t="n">
         <v>79081</v>
@@ -10819,10 +10819,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>444252</v>
+        <v>444238</v>
       </c>
       <c r="R101" t="n">
-        <v>6787160</v>
+        <v>6787281</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10881,7 +10881,7 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>129795248</v>
+        <v>129795303</v>
       </c>
       <c r="B102" t="n">
         <v>79081</v>
@@ -10916,10 +10916,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>444238</v>
+        <v>444200</v>
       </c>
       <c r="R102" t="n">
-        <v>6787281</v>
+        <v>6787331</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -10978,7 +10978,7 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>129795303</v>
+        <v>129795264</v>
       </c>
       <c r="B103" t="n">
         <v>79081</v>
@@ -11013,10 +11013,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>444200</v>
+        <v>444252</v>
       </c>
       <c r="R103" t="n">
-        <v>6787331</v>
+        <v>6787160</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11172,7 +11172,7 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>129795196</v>
+        <v>129795185</v>
       </c>
       <c r="B105" t="n">
         <v>8450</v>
@@ -11216,10 +11216,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>444346</v>
+        <v>444458</v>
       </c>
       <c r="R105" t="n">
-        <v>6787369</v>
+        <v>6787304</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11279,7 +11279,7 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>129795185</v>
+        <v>129795186</v>
       </c>
       <c r="B106" t="n">
         <v>8450</v>
@@ -11323,10 +11323,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>444458</v>
+        <v>444473</v>
       </c>
       <c r="R106" t="n">
-        <v>6787304</v>
+        <v>6787334</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11386,7 +11386,7 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>129795186</v>
+        <v>129795196</v>
       </c>
       <c r="B107" t="n">
         <v>8450</v>
@@ -11430,10 +11430,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>444473</v>
+        <v>444346</v>
       </c>
       <c r="R107" t="n">
-        <v>6787334</v>
+        <v>6787369</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11804,41 +11804,40 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>129795203</v>
+        <v>129795149</v>
       </c>
       <c r="B111" t="n">
-        <v>8450</v>
+        <v>57733</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
-      <c r="J111" t="inlineStr"/>
       <c r="K111" t="inlineStr"/>
       <c r="L111" t="inlineStr"/>
       <c r="M111" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N111" t="inlineStr"/>
@@ -11848,10 +11847,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>444401</v>
+        <v>444223</v>
       </c>
       <c r="R111" t="n">
-        <v>6787298</v>
+        <v>6787221</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -11892,7 +11891,6 @@
       <c r="AE111" t="b">
         <v>0</v>
       </c>
-      <c r="AF111" t="inlineStr"/>
       <c r="AG111" t="b">
         <v>0</v>
       </c>
@@ -11911,41 +11909,40 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>129795201</v>
+        <v>129795145</v>
       </c>
       <c r="B112" t="n">
-        <v>8450</v>
+        <v>57733</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
-      <c r="J112" t="inlineStr"/>
       <c r="K112" t="inlineStr"/>
       <c r="L112" t="inlineStr"/>
       <c r="M112" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N112" t="inlineStr"/>
@@ -11955,10 +11952,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>444430</v>
+        <v>444228</v>
       </c>
       <c r="R112" t="n">
-        <v>6787332</v>
+        <v>6787226</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -11999,7 +11996,6 @@
       <c r="AE112" t="b">
         <v>0</v>
       </c>
-      <c r="AF112" t="inlineStr"/>
       <c r="AG112" t="b">
         <v>0</v>
       </c>
@@ -12018,7 +12014,7 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>129795145</v>
+        <v>129795151</v>
       </c>
       <c r="B113" t="n">
         <v>57733</v>
@@ -12061,10 +12057,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>444228</v>
+        <v>444425</v>
       </c>
       <c r="R113" t="n">
-        <v>6787226</v>
+        <v>6787278</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12123,40 +12119,41 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>129795149</v>
+        <v>129795203</v>
       </c>
       <c r="B114" t="n">
-        <v>57733</v>
+        <v>8450</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
+      <c r="J114" t="inlineStr"/>
       <c r="K114" t="inlineStr"/>
       <c r="L114" t="inlineStr"/>
       <c r="M114" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N114" t="inlineStr"/>
@@ -12166,10 +12163,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>444223</v>
+        <v>444401</v>
       </c>
       <c r="R114" t="n">
-        <v>6787221</v>
+        <v>6787298</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12210,6 +12207,7 @@
       <c r="AE114" t="b">
         <v>0</v>
       </c>
+      <c r="AF114" t="inlineStr"/>
       <c r="AG114" t="b">
         <v>0</v>
       </c>
@@ -12228,40 +12226,41 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>129795151</v>
+        <v>129795201</v>
       </c>
       <c r="B115" t="n">
-        <v>57733</v>
+        <v>8450</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
+      <c r="J115" t="inlineStr"/>
       <c r="K115" t="inlineStr"/>
       <c r="L115" t="inlineStr"/>
       <c r="M115" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N115" t="inlineStr"/>
@@ -12271,10 +12270,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>444425</v>
+        <v>444430</v>
       </c>
       <c r="R115" t="n">
-        <v>6787278</v>
+        <v>6787332</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12315,6 +12314,7 @@
       <c r="AE115" t="b">
         <v>0</v>
       </c>
+      <c r="AF115" t="inlineStr"/>
       <c r="AG115" t="b">
         <v>0</v>
       </c>
@@ -12333,45 +12333,54 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>129795289</v>
+        <v>129795171</v>
       </c>
       <c r="B116" t="n">
-        <v>79081</v>
+        <v>8450</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
+      <c r="J116" t="inlineStr"/>
+      <c r="K116" t="inlineStr"/>
+      <c r="L116" t="inlineStr"/>
+      <c r="M116" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N116" t="inlineStr"/>
       <c r="P116" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>444435</v>
+        <v>444185</v>
       </c>
       <c r="R116" t="n">
-        <v>6787341</v>
+        <v>6787226</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12412,6 +12421,7 @@
       <c r="AE116" t="b">
         <v>0</v>
       </c>
+      <c r="AF116" t="inlineStr"/>
       <c r="AG116" t="b">
         <v>0</v>
       </c>
@@ -12430,10 +12440,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>129795164</v>
+        <v>129795289</v>
       </c>
       <c r="B117" t="n">
-        <v>57733</v>
+        <v>79081</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -12441,42 +12451,34 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
-      <c r="K117" t="inlineStr"/>
-      <c r="L117" t="inlineStr"/>
-      <c r="M117" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N117" t="inlineStr"/>
       <c r="P117" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>444397</v>
+        <v>444435</v>
       </c>
       <c r="R117" t="n">
-        <v>6787300</v>
+        <v>6787341</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12535,32 +12537,32 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>129795132</v>
+        <v>129795164</v>
       </c>
       <c r="B118" t="n">
-        <v>56926</v>
+        <v>57733</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -12568,7 +12570,7 @@
       <c r="L118" t="inlineStr"/>
       <c r="M118" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N118" t="inlineStr"/>
@@ -12578,10 +12580,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>444315</v>
+        <v>444397</v>
       </c>
       <c r="R118" t="n">
-        <v>6787291</v>
+        <v>6787300</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12640,7 +12642,7 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>129795157</v>
+        <v>129795154</v>
       </c>
       <c r="B119" t="n">
         <v>57733</v>
@@ -12683,10 +12685,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>444525</v>
+        <v>444457</v>
       </c>
       <c r="R119" t="n">
-        <v>6787344</v>
+        <v>6787303</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -12745,41 +12747,40 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>129795171</v>
+        <v>129795157</v>
       </c>
       <c r="B120" t="n">
-        <v>8450</v>
+        <v>57733</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
-      <c r="J120" t="inlineStr"/>
       <c r="K120" t="inlineStr"/>
       <c r="L120" t="inlineStr"/>
       <c r="M120" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N120" t="inlineStr"/>
@@ -12789,10 +12790,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>444185</v>
+        <v>444525</v>
       </c>
       <c r="R120" t="n">
-        <v>6787226</v>
+        <v>6787344</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -12833,7 +12834,6 @@
       <c r="AE120" t="b">
         <v>0</v>
       </c>
-      <c r="AF120" t="inlineStr"/>
       <c r="AG120" t="b">
         <v>0</v>
       </c>
@@ -12852,32 +12852,32 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>129795154</v>
+        <v>129795132</v>
       </c>
       <c r="B121" t="n">
-        <v>57733</v>
+        <v>56926</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -12885,7 +12885,7 @@
       <c r="L121" t="inlineStr"/>
       <c r="M121" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="N121" t="inlineStr"/>
@@ -12895,10 +12895,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>444457</v>
+        <v>444315</v>
       </c>
       <c r="R121" t="n">
-        <v>6787303</v>
+        <v>6787291</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -12957,45 +12957,54 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>129795301</v>
+        <v>129795179</v>
       </c>
       <c r="B122" t="n">
-        <v>79081</v>
+        <v>8450</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
+      <c r="J122" t="inlineStr"/>
+      <c r="K122" t="inlineStr"/>
+      <c r="L122" t="inlineStr"/>
+      <c r="M122" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N122" t="inlineStr"/>
       <c r="P122" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>444250</v>
+        <v>444378</v>
       </c>
       <c r="R122" t="n">
-        <v>6787342</v>
+        <v>6787236</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -13036,6 +13045,7 @@
       <c r="AE122" t="b">
         <v>0</v>
       </c>
+      <c r="AF122" t="inlineStr"/>
       <c r="AG122" t="b">
         <v>0</v>
       </c>
@@ -13054,45 +13064,54 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>129795294</v>
+        <v>129795188</v>
       </c>
       <c r="B123" t="n">
-        <v>79081</v>
+        <v>8450</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
+      <c r="J123" t="inlineStr"/>
+      <c r="K123" t="inlineStr"/>
+      <c r="L123" t="inlineStr"/>
+      <c r="M123" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N123" t="inlineStr"/>
       <c r="P123" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>444323</v>
+        <v>444498</v>
       </c>
       <c r="R123" t="n">
-        <v>6787297</v>
+        <v>6787280</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13133,6 +13152,7 @@
       <c r="AE123" t="b">
         <v>0</v>
       </c>
+      <c r="AF123" t="inlineStr"/>
       <c r="AG123" t="b">
         <v>0</v>
       </c>
@@ -13151,54 +13171,45 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>129795179</v>
+        <v>129795301</v>
       </c>
       <c r="B124" t="n">
-        <v>8450</v>
+        <v>79081</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
-      <c r="J124" t="inlineStr"/>
-      <c r="K124" t="inlineStr"/>
-      <c r="L124" t="inlineStr"/>
-      <c r="M124" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N124" t="inlineStr"/>
       <c r="P124" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>444378</v>
+        <v>444250</v>
       </c>
       <c r="R124" t="n">
-        <v>6787236</v>
+        <v>6787342</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13239,7 +13250,6 @@
       <c r="AE124" t="b">
         <v>0</v>
       </c>
-      <c r="AF124" t="inlineStr"/>
       <c r="AG124" t="b">
         <v>0</v>
       </c>
@@ -13363,54 +13373,45 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>129795188</v>
+        <v>129795294</v>
       </c>
       <c r="B126" t="n">
-        <v>8450</v>
+        <v>79081</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
-      <c r="J126" t="inlineStr"/>
-      <c r="K126" t="inlineStr"/>
-      <c r="L126" t="inlineStr"/>
-      <c r="M126" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N126" t="inlineStr"/>
       <c r="P126" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>444498</v>
+        <v>444323</v>
       </c>
       <c r="R126" t="n">
-        <v>6787280</v>
+        <v>6787297</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -13451,7 +13452,6 @@
       <c r="AE126" t="b">
         <v>0</v>
       </c>
-      <c r="AF126" t="inlineStr"/>
       <c r="AG126" t="b">
         <v>0</v>
       </c>
@@ -13766,10 +13766,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>129795263</v>
+        <v>129795137</v>
       </c>
       <c r="B130" t="n">
-        <v>79081</v>
+        <v>91614</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -13777,34 +13777,37 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
+      <c r="J130" t="inlineStr"/>
+      <c r="K130" t="inlineStr"/>
+      <c r="N130" t="inlineStr"/>
       <c r="P130" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>444241</v>
+        <v>444203</v>
       </c>
       <c r="R130" t="n">
-        <v>6787149</v>
+        <v>6787221</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -13845,6 +13848,7 @@
       <c r="AE130" t="b">
         <v>0</v>
       </c>
+      <c r="AF130" t="inlineStr"/>
       <c r="AG130" t="b">
         <v>0</v>
       </c>
@@ -13968,7 +13972,7 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>129795168</v>
+        <v>129795175</v>
       </c>
       <c r="B132" t="n">
         <v>8450</v>
@@ -14012,10 +14016,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>444272</v>
+        <v>444182</v>
       </c>
       <c r="R132" t="n">
-        <v>6787286</v>
+        <v>6787101</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -14075,10 +14079,10 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>129795137</v>
+        <v>129795263</v>
       </c>
       <c r="B133" t="n">
-        <v>91614</v>
+        <v>79081</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -14086,37 +14090,34 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
-      <c r="J133" t="inlineStr"/>
-      <c r="K133" t="inlineStr"/>
-      <c r="N133" t="inlineStr"/>
       <c r="P133" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>444203</v>
+        <v>444241</v>
       </c>
       <c r="R133" t="n">
-        <v>6787221</v>
+        <v>6787149</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -14157,7 +14158,6 @@
       <c r="AE133" t="b">
         <v>0</v>
       </c>
-      <c r="AF133" t="inlineStr"/>
       <c r="AG133" t="b">
         <v>0</v>
       </c>
@@ -14176,7 +14176,7 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>129795175</v>
+        <v>129795168</v>
       </c>
       <c r="B134" t="n">
         <v>8450</v>
@@ -14220,10 +14220,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>444182</v>
+        <v>444272</v>
       </c>
       <c r="R134" t="n">
-        <v>6787101</v>
+        <v>6787286</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -14283,54 +14283,45 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>129795204</v>
+        <v>129795304</v>
       </c>
       <c r="B135" t="n">
-        <v>8450</v>
+        <v>79081</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
-      <c r="J135" t="inlineStr"/>
-      <c r="K135" t="inlineStr"/>
-      <c r="L135" t="inlineStr"/>
-      <c r="M135" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N135" t="inlineStr"/>
       <c r="P135" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>444380</v>
+        <v>444172</v>
       </c>
       <c r="R135" t="n">
-        <v>6787306</v>
+        <v>6787339</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -14371,7 +14362,6 @@
       <c r="AE135" t="b">
         <v>0</v>
       </c>
-      <c r="AF135" t="inlineStr"/>
       <c r="AG135" t="b">
         <v>0</v>
       </c>
@@ -14390,7 +14380,7 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>129795274</v>
+        <v>129795254</v>
       </c>
       <c r="B136" t="n">
         <v>79081</v>
@@ -14419,16 +14409,19 @@
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
+      <c r="J136" t="inlineStr"/>
+      <c r="K136" t="inlineStr"/>
+      <c r="N136" t="inlineStr"/>
       <c r="P136" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>444538</v>
+        <v>444199</v>
       </c>
       <c r="R136" t="n">
-        <v>6787325</v>
+        <v>6787221</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -14469,6 +14462,7 @@
       <c r="AE136" t="b">
         <v>0</v>
       </c>
+      <c r="AF136" t="inlineStr"/>
       <c r="AG136" t="b">
         <v>0</v>
       </c>
@@ -14487,45 +14481,54 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>129795304</v>
+        <v>129795204</v>
       </c>
       <c r="B137" t="n">
-        <v>79081</v>
+        <v>8450</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E137" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
+      <c r="J137" t="inlineStr"/>
+      <c r="K137" t="inlineStr"/>
+      <c r="L137" t="inlineStr"/>
+      <c r="M137" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N137" t="inlineStr"/>
       <c r="P137" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>444172</v>
+        <v>444380</v>
       </c>
       <c r="R137" t="n">
-        <v>6787339</v>
+        <v>6787306</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -14566,6 +14569,7 @@
       <c r="AE137" t="b">
         <v>0</v>
       </c>
+      <c r="AF137" t="inlineStr"/>
       <c r="AG137" t="b">
         <v>0</v>
       </c>
@@ -14584,7 +14588,7 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>129795254</v>
+        <v>129795274</v>
       </c>
       <c r="B138" t="n">
         <v>79081</v>
@@ -14613,19 +14617,16 @@
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
-      <c r="J138" t="inlineStr"/>
-      <c r="K138" t="inlineStr"/>
-      <c r="N138" t="inlineStr"/>
       <c r="P138" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>444199</v>
+        <v>444538</v>
       </c>
       <c r="R138" t="n">
-        <v>6787221</v>
+        <v>6787325</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -14666,7 +14667,6 @@
       <c r="AE138" t="b">
         <v>0</v>
       </c>
-      <c r="AF138" t="inlineStr"/>
       <c r="AG138" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 51041-2025 artfynd.xlsx
+++ b/artfynd/A 51041-2025 artfynd.xlsx
@@ -675,45 +675,54 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129795298</v>
+        <v>129795190</v>
       </c>
       <c r="B2" t="n">
-        <v>79081</v>
+        <v>8450</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>444305</v>
+        <v>444510</v>
       </c>
       <c r="R2" t="n">
-        <v>6787353</v>
+        <v>6787276</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -754,6 +763,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -772,45 +782,54 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129795253</v>
+        <v>129795197</v>
       </c>
       <c r="B3" t="n">
-        <v>79081</v>
+        <v>8450</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>444185</v>
+        <v>444406</v>
       </c>
       <c r="R3" t="n">
-        <v>6787247</v>
+        <v>6787392</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -845,17 +864,13 @@
           <t>2025-11-22</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Gott om garnlav inom en radie av 50 m.</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -874,45 +889,54 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129795244</v>
+        <v>129795169</v>
       </c>
       <c r="B4" t="n">
-        <v>79081</v>
+        <v>8450</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>444105</v>
+        <v>444272</v>
       </c>
       <c r="R4" t="n">
-        <v>6787246</v>
+        <v>6787239</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -953,6 +977,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -971,7 +996,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129795283</v>
+        <v>129795253</v>
       </c>
       <c r="B5" t="n">
         <v>79081</v>
@@ -1000,19 +1025,16 @@
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>444337</v>
+        <v>444185</v>
       </c>
       <c r="R5" t="n">
-        <v>6787374</v>
+        <v>6787247</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1047,13 +1069,17 @@
           <t>2025-11-22</t>
         </is>
       </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Gott om garnlav inom en radie av 50 m.</t>
+        </is>
+      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1072,54 +1098,45 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129795197</v>
+        <v>129795291</v>
       </c>
       <c r="B6" t="n">
-        <v>8450</v>
+        <v>79081</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>444406</v>
+        <v>444412</v>
       </c>
       <c r="R6" t="n">
-        <v>6787392</v>
+        <v>6787307</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1160,7 +1177,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1179,54 +1195,45 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129795169</v>
+        <v>129795244</v>
       </c>
       <c r="B7" t="n">
-        <v>8450</v>
+        <v>79081</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>444272</v>
+        <v>444105</v>
       </c>
       <c r="R7" t="n">
-        <v>6787239</v>
+        <v>6787246</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1267,7 +1274,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1286,54 +1292,45 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129795190</v>
+        <v>129795261</v>
       </c>
       <c r="B8" t="n">
-        <v>8450</v>
+        <v>79081</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>444510</v>
+        <v>444193</v>
       </c>
       <c r="R8" t="n">
-        <v>6787276</v>
+        <v>6787130</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1374,7 +1371,6 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1393,7 +1389,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129795291</v>
+        <v>129795298</v>
       </c>
       <c r="B9" t="n">
         <v>79081</v>
@@ -1428,10 +1424,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>444412</v>
+        <v>444305</v>
       </c>
       <c r="R9" t="n">
-        <v>6787307</v>
+        <v>6787353</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1587,7 +1583,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129795261</v>
+        <v>129795283</v>
       </c>
       <c r="B11" t="n">
         <v>79081</v>
@@ -1616,16 +1612,19 @@
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>444193</v>
+        <v>444337</v>
       </c>
       <c r="R11" t="n">
-        <v>6787130</v>
+        <v>6787374</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1666,6 +1665,7 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1684,10 +1684,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129795281</v>
+        <v>129795155</v>
       </c>
       <c r="B12" t="n">
-        <v>79081</v>
+        <v>57733</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1695,26 +1695,31 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1722,10 +1727,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>444408</v>
+        <v>444498</v>
       </c>
       <c r="R12" t="n">
-        <v>6787452</v>
+        <v>6787306</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1766,7 +1771,6 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1785,10 +1789,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129795271</v>
+        <v>129795163</v>
       </c>
       <c r="B13" t="n">
-        <v>79081</v>
+        <v>57733</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1796,26 +1800,31 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1823,10 +1832,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>444466</v>
+        <v>444415</v>
       </c>
       <c r="R13" t="n">
-        <v>6787306</v>
+        <v>6787316</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1861,18 +1870,12 @@
           <t>2025-11-22</t>
         </is>
       </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 50m.</t>
-        </is>
-      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -1891,10 +1894,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129795276</v>
+        <v>129795153</v>
       </c>
       <c r="B14" t="n">
-        <v>79081</v>
+        <v>57733</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1902,26 +1905,31 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -1929,10 +1937,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>444499</v>
+        <v>444452</v>
       </c>
       <c r="R14" t="n">
-        <v>6787367</v>
+        <v>6787294</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1967,18 +1975,12 @@
           <t>2025-11-22</t>
         </is>
       </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 50m.</t>
-        </is>
-      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -1997,45 +1999,54 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129795299</v>
+        <v>129795205</v>
       </c>
       <c r="B15" t="n">
-        <v>79081</v>
+        <v>8450</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>444265</v>
+        <v>444343</v>
       </c>
       <c r="R15" t="n">
-        <v>6787372</v>
+        <v>6787310</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2076,6 +2087,7 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2094,10 +2106,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129795155</v>
+        <v>129795281</v>
       </c>
       <c r="B16" t="n">
-        <v>57733</v>
+        <v>79081</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2105,31 +2117,26 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2137,10 +2144,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>444498</v>
+        <v>444408</v>
       </c>
       <c r="R16" t="n">
-        <v>6787306</v>
+        <v>6787452</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2181,6 +2188,7 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2199,10 +2207,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129795153</v>
+        <v>129795271</v>
       </c>
       <c r="B17" t="n">
-        <v>57733</v>
+        <v>79081</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2210,31 +2218,26 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2242,10 +2245,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>444452</v>
+        <v>444466</v>
       </c>
       <c r="R17" t="n">
-        <v>6787294</v>
+        <v>6787306</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2280,12 +2283,18 @@
           <t>2025-11-22</t>
         </is>
       </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 50m.</t>
+        </is>
+      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2304,10 +2313,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129795163</v>
+        <v>129795276</v>
       </c>
       <c r="B18" t="n">
-        <v>57733</v>
+        <v>79081</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2315,31 +2324,26 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2347,10 +2351,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>444415</v>
+        <v>444499</v>
       </c>
       <c r="R18" t="n">
-        <v>6787316</v>
+        <v>6787367</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2385,12 +2389,18 @@
           <t>2025-11-22</t>
         </is>
       </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 50m.</t>
+        </is>
+      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2409,54 +2419,45 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129795174</v>
+        <v>129795299</v>
       </c>
       <c r="B19" t="n">
-        <v>8450</v>
+        <v>79081</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>444166</v>
+        <v>444265</v>
       </c>
       <c r="R19" t="n">
-        <v>6787161</v>
+        <v>6787372</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2497,7 +2498,6 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2516,7 +2516,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129795205</v>
+        <v>129795174</v>
       </c>
       <c r="B20" t="n">
         <v>8450</v>
@@ -2560,10 +2560,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>444343</v>
+        <v>444166</v>
       </c>
       <c r="R20" t="n">
-        <v>6787310</v>
+        <v>6787161</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2623,7 +2623,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129795310</v>
+        <v>129795273</v>
       </c>
       <c r="B21" t="n">
         <v>79081</v>
@@ -2652,19 +2652,16 @@
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>444488</v>
+        <v>444548</v>
       </c>
       <c r="R21" t="n">
-        <v>6787445</v>
+        <v>6787330</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2699,18 +2696,12 @@
           <t>2025-11-22</t>
         </is>
       </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Gott om garnlav inom en radie av 40m</t>
-        </is>
-      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -2729,7 +2720,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129795273</v>
+        <v>129795265</v>
       </c>
       <c r="B22" t="n">
         <v>79081</v>
@@ -2764,10 +2755,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>444548</v>
+        <v>444278</v>
       </c>
       <c r="R22" t="n">
-        <v>6787330</v>
+        <v>6787163</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2826,7 +2817,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129795265</v>
+        <v>129795310</v>
       </c>
       <c r="B23" t="n">
         <v>79081</v>
@@ -2855,16 +2846,19 @@
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>444278</v>
+        <v>444488</v>
       </c>
       <c r="R23" t="n">
-        <v>6787163</v>
+        <v>6787445</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2899,12 +2893,18 @@
           <t>2025-11-22</t>
         </is>
       </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Gott om garnlav inom en radie av 40m</t>
+        </is>
+      </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -3020,7 +3020,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129795200</v>
+        <v>129795207</v>
       </c>
       <c r="B25" t="n">
         <v>8450</v>
@@ -3064,10 +3064,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>444429</v>
+        <v>444221</v>
       </c>
       <c r="R25" t="n">
-        <v>6787341</v>
+        <v>6787340</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3127,7 +3127,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129795198</v>
+        <v>129795206</v>
       </c>
       <c r="B26" t="n">
         <v>8450</v>
@@ -3171,10 +3171,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>444434</v>
+        <v>444247</v>
       </c>
       <c r="R26" t="n">
-        <v>6787384</v>
+        <v>6787328</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3234,7 +3234,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129795207</v>
+        <v>129795198</v>
       </c>
       <c r="B27" t="n">
         <v>8450</v>
@@ -3278,10 +3278,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>444221</v>
+        <v>444434</v>
       </c>
       <c r="R27" t="n">
-        <v>6787340</v>
+        <v>6787384</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3341,7 +3341,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129795206</v>
+        <v>129795200</v>
       </c>
       <c r="B28" t="n">
         <v>8450</v>
@@ -3385,10 +3385,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>444247</v>
+        <v>444429</v>
       </c>
       <c r="R28" t="n">
-        <v>6787328</v>
+        <v>6787341</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3448,10 +3448,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129795142</v>
+        <v>129795268</v>
       </c>
       <c r="B29" t="n">
-        <v>57733</v>
+        <v>79081</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3459,42 +3459,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>444276</v>
+        <v>444383</v>
       </c>
       <c r="R29" t="n">
-        <v>6787287</v>
+        <v>6787218</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3553,7 +3545,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129795268</v>
+        <v>129795256</v>
       </c>
       <c r="B30" t="n">
         <v>79081</v>
@@ -3588,10 +3580,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>444383</v>
+        <v>444226</v>
       </c>
       <c r="R30" t="n">
-        <v>6787218</v>
+        <v>6787196</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3650,10 +3642,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129795256</v>
+        <v>129795142</v>
       </c>
       <c r="B31" t="n">
-        <v>79081</v>
+        <v>57733</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3661,34 +3653,42 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>444226</v>
+        <v>444276</v>
       </c>
       <c r="R31" t="n">
-        <v>6787196</v>
+        <v>6787287</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3747,7 +3747,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129795176</v>
+        <v>129795187</v>
       </c>
       <c r="B32" t="n">
         <v>8450</v>
@@ -3781,7 +3781,7 @@
       <c r="L32" t="inlineStr"/>
       <c r="M32" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N32" t="inlineStr"/>
@@ -3791,10 +3791,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>444215</v>
+        <v>444487</v>
       </c>
       <c r="R32" t="n">
-        <v>6787151</v>
+        <v>6787321</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3961,7 +3961,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129795187</v>
+        <v>129795176</v>
       </c>
       <c r="B34" t="n">
         <v>8450</v>
@@ -3995,7 +3995,7 @@
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="N34" t="inlineStr"/>
@@ -4005,10 +4005,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>444487</v>
+        <v>444215</v>
       </c>
       <c r="R34" t="n">
-        <v>6787321</v>
+        <v>6787151</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4174,7 +4174,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129795249</v>
+        <v>129795269</v>
       </c>
       <c r="B36" t="n">
         <v>79081</v>
@@ -4209,10 +4209,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>444267</v>
+        <v>444429</v>
       </c>
       <c r="R36" t="n">
-        <v>6787295</v>
+        <v>6787240</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4271,7 +4271,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129795270</v>
+        <v>129795249</v>
       </c>
       <c r="B37" t="n">
         <v>79081</v>
@@ -4306,10 +4306,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>444416</v>
+        <v>444267</v>
       </c>
       <c r="R37" t="n">
-        <v>6787260</v>
+        <v>6787295</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4368,7 +4368,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129795269</v>
+        <v>129795270</v>
       </c>
       <c r="B38" t="n">
         <v>79081</v>
@@ -4403,10 +4403,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>444429</v>
+        <v>444416</v>
       </c>
       <c r="R38" t="n">
-        <v>6787240</v>
+        <v>6787260</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4465,40 +4465,41 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129795165</v>
+        <v>129795202</v>
       </c>
       <c r="B39" t="n">
-        <v>57733</v>
+        <v>8450</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr"/>
       <c r="L39" t="inlineStr"/>
       <c r="M39" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N39" t="inlineStr"/>
@@ -4508,10 +4509,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>444251</v>
+        <v>444413</v>
       </c>
       <c r="R39" t="n">
-        <v>6787376</v>
+        <v>6787314</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4552,6 +4553,7 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
+      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -4570,10 +4572,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129795133</v>
+        <v>129795165</v>
       </c>
       <c r="B40" t="n">
-        <v>57896</v>
+        <v>57733</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4581,21 +4583,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4603,7 +4605,7 @@
       <c r="L40" t="inlineStr"/>
       <c r="M40" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N40" t="inlineStr"/>
@@ -4613,10 +4615,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>444226</v>
+        <v>444251</v>
       </c>
       <c r="R40" t="n">
-        <v>6787236</v>
+        <v>6787376</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4675,41 +4677,40 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129795202</v>
+        <v>129795133</v>
       </c>
       <c r="B41" t="n">
-        <v>8450</v>
+        <v>57896</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>106545</v>
+        <v>103021</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr"/>
       <c r="K41" t="inlineStr"/>
       <c r="L41" t="inlineStr"/>
       <c r="M41" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N41" t="inlineStr"/>
@@ -4719,10 +4720,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>444413</v>
+        <v>444226</v>
       </c>
       <c r="R41" t="n">
-        <v>6787314</v>
+        <v>6787236</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4763,7 +4764,6 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
-      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
@@ -4889,37 +4889,43 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129795136</v>
+        <v>129795170</v>
       </c>
       <c r="B43" t="n">
-        <v>91614</v>
+        <v>8450</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>5442</v>
+        <v>106545</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="J43" t="inlineStr"/>
       <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
@@ -4927,10 +4933,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>444235</v>
+        <v>444172</v>
       </c>
       <c r="R43" t="n">
-        <v>6787149</v>
+        <v>6787202</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5198,10 +5204,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129795158</v>
+        <v>129795136</v>
       </c>
       <c r="B46" t="n">
-        <v>57733</v>
+        <v>91614</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5209,31 +5215,26 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100049</v>
+        <v>5442</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="J46" t="inlineStr"/>
       <c r="K46" t="inlineStr"/>
-      <c r="L46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
@@ -5241,10 +5242,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>444501</v>
+        <v>444235</v>
       </c>
       <c r="R46" t="n">
-        <v>6787402</v>
+        <v>6787149</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5285,6 +5286,7 @@
       <c r="AE46" t="b">
         <v>0</v>
       </c>
+      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
@@ -5303,41 +5305,40 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129795170</v>
+        <v>129795158</v>
       </c>
       <c r="B47" t="n">
-        <v>8450</v>
+        <v>57733</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="J47" t="inlineStr"/>
       <c r="K47" t="inlineStr"/>
       <c r="L47" t="inlineStr"/>
       <c r="M47" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N47" t="inlineStr"/>
@@ -5347,10 +5348,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>444172</v>
+        <v>444501</v>
       </c>
       <c r="R47" t="n">
-        <v>6787202</v>
+        <v>6787402</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5391,7 +5392,6 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
-      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
@@ -5410,7 +5410,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129795260</v>
+        <v>129795250</v>
       </c>
       <c r="B48" t="n">
         <v>79081</v>
@@ -5445,10 +5445,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>444197</v>
+        <v>444295</v>
       </c>
       <c r="R48" t="n">
-        <v>6787111</v>
+        <v>6787287</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5507,7 +5507,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129795250</v>
+        <v>129795309</v>
       </c>
       <c r="B49" t="n">
         <v>79081</v>
@@ -5542,10 +5542,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>444295</v>
+        <v>444095</v>
       </c>
       <c r="R49" t="n">
-        <v>6787287</v>
+        <v>6787293</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5578,6 +5578,11 @@
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-11-22</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>8.32</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5604,10 +5609,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129795138</v>
+        <v>129795260</v>
       </c>
       <c r="B50" t="n">
-        <v>91614</v>
+        <v>79081</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5615,37 +5620,34 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="J50" t="inlineStr"/>
-      <c r="K50" t="inlineStr"/>
-      <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>444250</v>
+        <v>444197</v>
       </c>
       <c r="R50" t="n">
-        <v>6787196</v>
+        <v>6787111</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5686,7 +5688,6 @@
       <c r="AE50" t="b">
         <v>0</v>
       </c>
-      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>
@@ -5705,7 +5706,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129795309</v>
+        <v>129795246</v>
       </c>
       <c r="B51" t="n">
         <v>79081</v>
@@ -5740,10 +5741,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>444095</v>
+        <v>444145</v>
       </c>
       <c r="R51" t="n">
-        <v>6787293</v>
+        <v>6787239</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5780,7 +5781,7 @@
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>8.32</t>
+          <t>Rikligt med garnlav inom en radie av 40m.</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5807,10 +5808,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129795246</v>
+        <v>129795138</v>
       </c>
       <c r="B52" t="n">
-        <v>79081</v>
+        <v>91614</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5818,34 +5819,37 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
+      <c r="J52" t="inlineStr"/>
+      <c r="K52" t="inlineStr"/>
+      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>444145</v>
+        <v>444250</v>
       </c>
       <c r="R52" t="n">
-        <v>6787239</v>
+        <v>6787196</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5880,17 +5884,13 @@
           <t>2025-11-22</t>
         </is>
       </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 40m.</t>
-        </is>
-      </c>
       <c r="AD52" t="b">
         <v>0</v>
       </c>
       <c r="AE52" t="b">
         <v>0</v>
       </c>
+      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
@@ -5909,10 +5909,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129795279</v>
+        <v>129795134</v>
       </c>
       <c r="B53" t="n">
-        <v>79081</v>
+        <v>57896</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5920,34 +5920,42 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
+      <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>444463</v>
+        <v>444289</v>
       </c>
       <c r="R53" t="n">
-        <v>6787459</v>
+        <v>6787357</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6103,53 +6111,45 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129795131</v>
+        <v>129795279</v>
       </c>
       <c r="B55" t="n">
-        <v>56926</v>
+        <v>79081</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
-      <c r="K55" t="inlineStr"/>
-      <c r="L55" t="inlineStr"/>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>444250</v>
+        <v>444463</v>
       </c>
       <c r="R55" t="n">
-        <v>6787212</v>
+        <v>6787459</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6208,10 +6208,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129795134</v>
+        <v>129795147</v>
       </c>
       <c r="B56" t="n">
-        <v>57896</v>
+        <v>57733</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6219,21 +6219,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6241,7 +6241,7 @@
       <c r="L56" t="inlineStr"/>
       <c r="M56" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N56" t="inlineStr"/>
@@ -6251,10 +6251,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>444289</v>
+        <v>444220</v>
       </c>
       <c r="R56" t="n">
-        <v>6787357</v>
+        <v>6787221</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6313,41 +6313,40 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129795172</v>
+        <v>129795161</v>
       </c>
       <c r="B57" t="n">
-        <v>8450</v>
+        <v>57733</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
-      <c r="J57" t="inlineStr"/>
       <c r="K57" t="inlineStr"/>
       <c r="L57" t="inlineStr"/>
       <c r="M57" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N57" t="inlineStr"/>
@@ -6357,10 +6356,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>444225</v>
+        <v>444433</v>
       </c>
       <c r="R57" t="n">
-        <v>6787223</v>
+        <v>6787338</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6401,7 +6400,6 @@
       <c r="AE57" t="b">
         <v>0</v>
       </c>
-      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
@@ -6420,10 +6418,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129795199</v>
+        <v>129795131</v>
       </c>
       <c r="B58" t="n">
-        <v>8450</v>
+        <v>56926</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6431,30 +6429,29 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>106545</v>
+        <v>100138</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
-      <c r="J58" t="inlineStr"/>
       <c r="K58" t="inlineStr"/>
       <c r="L58" t="inlineStr"/>
       <c r="M58" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="N58" t="inlineStr"/>
@@ -6464,10 +6461,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>444431</v>
+        <v>444250</v>
       </c>
       <c r="R58" t="n">
-        <v>6787350</v>
+        <v>6787212</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6508,7 +6505,6 @@
       <c r="AE58" t="b">
         <v>0</v>
       </c>
-      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
       </c>
@@ -6634,40 +6630,41 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129795161</v>
+        <v>129795199</v>
       </c>
       <c r="B60" t="n">
-        <v>57733</v>
+        <v>8450</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
+      <c r="J60" t="inlineStr"/>
       <c r="K60" t="inlineStr"/>
       <c r="L60" t="inlineStr"/>
       <c r="M60" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N60" t="inlineStr"/>
@@ -6677,10 +6674,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>444433</v>
+        <v>444431</v>
       </c>
       <c r="R60" t="n">
-        <v>6787338</v>
+        <v>6787350</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6721,6 +6718,7 @@
       <c r="AE60" t="b">
         <v>0</v>
       </c>
+      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
       </c>
@@ -6739,40 +6737,41 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129795147</v>
+        <v>129795172</v>
       </c>
       <c r="B61" t="n">
-        <v>57733</v>
+        <v>8450</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
+      <c r="J61" t="inlineStr"/>
       <c r="K61" t="inlineStr"/>
       <c r="L61" t="inlineStr"/>
       <c r="M61" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N61" t="inlineStr"/>
@@ -6782,10 +6781,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>444220</v>
+        <v>444225</v>
       </c>
       <c r="R61" t="n">
-        <v>6787221</v>
+        <v>6787223</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6826,6 +6825,7 @@
       <c r="AE61" t="b">
         <v>0</v>
       </c>
+      <c r="AF61" t="inlineStr"/>
       <c r="AG61" t="b">
         <v>0</v>
       </c>
@@ -6844,7 +6844,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129795195</v>
+        <v>129795191</v>
       </c>
       <c r="B62" t="n">
         <v>8450</v>
@@ -6888,10 +6888,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>444487</v>
+        <v>444520</v>
       </c>
       <c r="R62" t="n">
-        <v>6787441</v>
+        <v>6787287</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6951,7 +6951,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129795191</v>
+        <v>129795195</v>
       </c>
       <c r="B63" t="n">
         <v>8450</v>
@@ -6995,10 +6995,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>444520</v>
+        <v>444487</v>
       </c>
       <c r="R63" t="n">
-        <v>6787287</v>
+        <v>6787441</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7165,10 +7165,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129795162</v>
+        <v>129795125</v>
       </c>
       <c r="B65" t="n">
-        <v>57733</v>
+        <v>79700</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7176,42 +7176,34 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
-      <c r="K65" t="inlineStr"/>
-      <c r="L65" t="inlineStr"/>
-      <c r="M65" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>444428</v>
+        <v>444329</v>
       </c>
       <c r="R65" t="n">
-        <v>6787329</v>
+        <v>6787371</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7270,10 +7262,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129795125</v>
+        <v>129795162</v>
       </c>
       <c r="B66" t="n">
-        <v>79700</v>
+        <v>57733</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7281,34 +7273,42 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
+      <c r="K66" t="inlineStr"/>
+      <c r="L66" t="inlineStr"/>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>444329</v>
+        <v>444428</v>
       </c>
       <c r="R66" t="n">
-        <v>6787371</v>
+        <v>6787329</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7367,10 +7367,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129795150</v>
+        <v>129795257</v>
       </c>
       <c r="B67" t="n">
-        <v>57733</v>
+        <v>79081</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7378,42 +7378,34 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
-      <c r="K67" t="inlineStr"/>
-      <c r="L67" t="inlineStr"/>
-      <c r="M67" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>444413</v>
+        <v>444168</v>
       </c>
       <c r="R67" t="n">
-        <v>6787222</v>
+        <v>6787171</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7472,10 +7464,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129795257</v>
+        <v>129795150</v>
       </c>
       <c r="B68" t="n">
-        <v>79081</v>
+        <v>57733</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7483,34 +7475,42 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
+      <c r="K68" t="inlineStr"/>
+      <c r="L68" t="inlineStr"/>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>444168</v>
+        <v>444413</v>
       </c>
       <c r="R68" t="n">
-        <v>6787171</v>
+        <v>6787222</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7569,10 +7569,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129795166</v>
+        <v>129795280</v>
       </c>
       <c r="B69" t="n">
-        <v>57733</v>
+        <v>79081</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7580,42 +7580,34 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
-      <c r="K69" t="inlineStr"/>
-      <c r="L69" t="inlineStr"/>
-      <c r="M69" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>444254</v>
+        <v>444451</v>
       </c>
       <c r="R69" t="n">
-        <v>6787333</v>
+        <v>6787467</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7674,7 +7666,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129795280</v>
+        <v>129795272</v>
       </c>
       <c r="B70" t="n">
         <v>79081</v>
@@ -7709,10 +7701,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>444451</v>
+        <v>444553</v>
       </c>
       <c r="R70" t="n">
-        <v>6787467</v>
+        <v>6787299</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7771,10 +7763,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129795135</v>
+        <v>129795287</v>
       </c>
       <c r="B71" t="n">
-        <v>91614</v>
+        <v>79081</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7782,37 +7774,34 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
-      <c r="J71" t="inlineStr"/>
-      <c r="K71" t="inlineStr"/>
-      <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>444158</v>
+        <v>444430</v>
       </c>
       <c r="R71" t="n">
-        <v>6787148</v>
+        <v>6787384</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7853,7 +7842,6 @@
       <c r="AE71" t="b">
         <v>0</v>
       </c>
-      <c r="AF71" t="inlineStr"/>
       <c r="AG71" t="b">
         <v>0</v>
       </c>
@@ -7872,7 +7860,7 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129795243</v>
+        <v>129795284</v>
       </c>
       <c r="B72" t="n">
         <v>79081</v>
@@ -7907,10 +7895,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>444159</v>
+        <v>444363</v>
       </c>
       <c r="R72" t="n">
-        <v>6787297</v>
+        <v>6787411</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7969,7 +7957,7 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129795272</v>
+        <v>129795243</v>
       </c>
       <c r="B73" t="n">
         <v>79081</v>
@@ -8004,10 +7992,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>444553</v>
+        <v>444159</v>
       </c>
       <c r="R73" t="n">
-        <v>6787299</v>
+        <v>6787297</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8066,10 +8054,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129795287</v>
+        <v>129795135</v>
       </c>
       <c r="B74" t="n">
-        <v>79081</v>
+        <v>91614</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8077,34 +8065,37 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
+      <c r="J74" t="inlineStr"/>
+      <c r="K74" t="inlineStr"/>
+      <c r="N74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>444430</v>
+        <v>444158</v>
       </c>
       <c r="R74" t="n">
-        <v>6787384</v>
+        <v>6787148</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8145,6 +8136,7 @@
       <c r="AE74" t="b">
         <v>0</v>
       </c>
+      <c r="AF74" t="inlineStr"/>
       <c r="AG74" t="b">
         <v>0</v>
       </c>
@@ -8163,10 +8155,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129795284</v>
+        <v>129795166</v>
       </c>
       <c r="B75" t="n">
-        <v>79081</v>
+        <v>57733</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8174,34 +8166,42 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
+      <c r="K75" t="inlineStr"/>
+      <c r="L75" t="inlineStr"/>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>444363</v>
+        <v>444254</v>
       </c>
       <c r="R75" t="n">
-        <v>6787411</v>
+        <v>6787333</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8472,10 +8472,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129795300</v>
+        <v>129795126</v>
       </c>
       <c r="B78" t="n">
-        <v>79081</v>
+        <v>79700</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8483,37 +8483,34 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
-      <c r="J78" t="inlineStr"/>
-      <c r="K78" t="inlineStr"/>
-      <c r="N78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>444264</v>
+        <v>444358</v>
       </c>
       <c r="R78" t="n">
-        <v>6787349</v>
+        <v>6787400</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8548,18 +8545,12 @@
           <t>2025-11-22</t>
         </is>
       </c>
-      <c r="AC78" t="inlineStr">
-        <is>
-          <t>Garnlav i de flesta träd inom en radie av 50 m.</t>
-        </is>
-      </c>
       <c r="AD78" t="b">
         <v>0</v>
       </c>
       <c r="AE78" t="b">
         <v>0</v>
       </c>
-      <c r="AF78" t="inlineStr"/>
       <c r="AG78" t="b">
         <v>0</v>
       </c>
@@ -8578,7 +8569,7 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129795286</v>
+        <v>129795300</v>
       </c>
       <c r="B79" t="n">
         <v>79081</v>
@@ -8616,10 +8607,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>444440</v>
+        <v>444264</v>
       </c>
       <c r="R79" t="n">
-        <v>6787388</v>
+        <v>6787349</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8656,7 +8647,7 @@
       </c>
       <c r="AC79" t="inlineStr">
         <is>
-          <t>Gott om garnlav inom en radie av 50 m.</t>
+          <t>Garnlav i de flesta träd inom en radie av 50 m.</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -8684,7 +8675,7 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129795241</v>
+        <v>129795307</v>
       </c>
       <c r="B80" t="n">
         <v>79081</v>
@@ -8719,10 +8710,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>444117</v>
+        <v>444134</v>
       </c>
       <c r="R80" t="n">
-        <v>6787277</v>
+        <v>6787304</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8781,10 +8772,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129795126</v>
+        <v>129795286</v>
       </c>
       <c r="B81" t="n">
-        <v>79700</v>
+        <v>79081</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8792,34 +8783,37 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
+      <c r="J81" t="inlineStr"/>
+      <c r="K81" t="inlineStr"/>
+      <c r="N81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>444358</v>
+        <v>444440</v>
       </c>
       <c r="R81" t="n">
-        <v>6787400</v>
+        <v>6787388</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8854,12 +8848,18 @@
           <t>2025-11-22</t>
         </is>
       </c>
+      <c r="AC81" t="inlineStr">
+        <is>
+          <t>Gott om garnlav inom en radie av 50 m.</t>
+        </is>
+      </c>
       <c r="AD81" t="b">
         <v>0</v>
       </c>
       <c r="AE81" t="b">
         <v>0</v>
       </c>
+      <c r="AF81" t="inlineStr"/>
       <c r="AG81" t="b">
         <v>0</v>
       </c>
@@ -8878,7 +8878,7 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129795307</v>
+        <v>129795241</v>
       </c>
       <c r="B82" t="n">
         <v>79081</v>
@@ -8913,10 +8913,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>444134</v>
+        <v>444117</v>
       </c>
       <c r="R82" t="n">
-        <v>6787304</v>
+        <v>6787277</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9072,7 +9072,7 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129795173</v>
+        <v>129795194</v>
       </c>
       <c r="B84" t="n">
         <v>8450</v>
@@ -9116,10 +9116,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>444220</v>
+        <v>444501</v>
       </c>
       <c r="R84" t="n">
-        <v>6787210</v>
+        <v>6787363</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9179,7 +9179,7 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129795194</v>
+        <v>129795173</v>
       </c>
       <c r="B85" t="n">
         <v>8450</v>
@@ -9223,10 +9223,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>444501</v>
+        <v>444220</v>
       </c>
       <c r="R85" t="n">
-        <v>6787363</v>
+        <v>6787210</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9286,7 +9286,7 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129795242</v>
+        <v>129795308</v>
       </c>
       <c r="B86" t="n">
         <v>79081</v>
@@ -9321,7 +9321,7 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>444125</v>
+        <v>444098</v>
       </c>
       <c r="R86" t="n">
         <v>6787297</v>
@@ -9383,54 +9383,45 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129795181</v>
+        <v>129795242</v>
       </c>
       <c r="B87" t="n">
-        <v>8450</v>
+        <v>79081</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
-      <c r="J87" t="inlineStr"/>
-      <c r="K87" t="inlineStr"/>
-      <c r="L87" t="inlineStr"/>
-      <c r="M87" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>444408</v>
+        <v>444125</v>
       </c>
       <c r="R87" t="n">
-        <v>6787250</v>
+        <v>6787297</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9471,7 +9462,6 @@
       <c r="AE87" t="b">
         <v>0</v>
       </c>
-      <c r="AF87" t="inlineStr"/>
       <c r="AG87" t="b">
         <v>0</v>
       </c>
@@ -9490,7 +9480,7 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129795192</v>
+        <v>129795181</v>
       </c>
       <c r="B88" t="n">
         <v>8450</v>
@@ -9534,10 +9524,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>444549</v>
+        <v>444408</v>
       </c>
       <c r="R88" t="n">
-        <v>6787335</v>
+        <v>6787250</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9597,45 +9587,54 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>129795308</v>
+        <v>129795192</v>
       </c>
       <c r="B89" t="n">
-        <v>79081</v>
+        <v>8450</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
+      <c r="J89" t="inlineStr"/>
+      <c r="K89" t="inlineStr"/>
+      <c r="L89" t="inlineStr"/>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>444098</v>
+        <v>444549</v>
       </c>
       <c r="R89" t="n">
-        <v>6787297</v>
+        <v>6787335</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9676,6 +9675,7 @@
       <c r="AE89" t="b">
         <v>0</v>
       </c>
+      <c r="AF89" t="inlineStr"/>
       <c r="AG89" t="b">
         <v>0</v>
       </c>
@@ -9791,10 +9791,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>129795288</v>
+        <v>129795152</v>
       </c>
       <c r="B91" t="n">
-        <v>79081</v>
+        <v>57733</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9802,34 +9802,42 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
+      <c r="K91" t="inlineStr"/>
+      <c r="L91" t="inlineStr"/>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>444420</v>
+        <v>444434</v>
       </c>
       <c r="R91" t="n">
-        <v>6787366</v>
+        <v>6787304</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9888,7 +9896,7 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>129795297</v>
+        <v>129795288</v>
       </c>
       <c r="B92" t="n">
         <v>79081</v>
@@ -9923,10 +9931,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>444297</v>
+        <v>444420</v>
       </c>
       <c r="R92" t="n">
-        <v>6787333</v>
+        <v>6787366</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9985,7 +9993,7 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>129795262</v>
+        <v>129795245</v>
       </c>
       <c r="B93" t="n">
         <v>79081</v>
@@ -10020,10 +10028,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>444219</v>
+        <v>444113</v>
       </c>
       <c r="R93" t="n">
-        <v>6787163</v>
+        <v>6787239</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10082,10 +10090,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>129795121</v>
+        <v>129795297</v>
       </c>
       <c r="B94" t="n">
-        <v>79700</v>
+        <v>79081</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10093,21 +10101,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -10117,10 +10125,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>444254</v>
+        <v>444297</v>
       </c>
       <c r="R94" t="n">
-        <v>6787204</v>
+        <v>6787333</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10179,7 +10187,7 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>129795245</v>
+        <v>129795262</v>
       </c>
       <c r="B95" t="n">
         <v>79081</v>
@@ -10214,10 +10222,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>444113</v>
+        <v>444219</v>
       </c>
       <c r="R95" t="n">
-        <v>6787239</v>
+        <v>6787163</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10276,10 +10284,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>129795124</v>
+        <v>129795252</v>
       </c>
       <c r="B96" t="n">
-        <v>79700</v>
+        <v>79081</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10287,21 +10295,21 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10311,10 +10319,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>444393</v>
+        <v>444249</v>
       </c>
       <c r="R96" t="n">
-        <v>6787395</v>
+        <v>6787249</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10347,6 +10355,11 @@
       <c r="AA96" t="inlineStr">
         <is>
           <t>2025-11-22</t>
+        </is>
+      </c>
+      <c r="AC96" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 40m.</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10373,7 +10386,7 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>129795123</v>
+        <v>129795121</v>
       </c>
       <c r="B97" t="n">
         <v>79700</v>
@@ -10408,10 +10421,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>444530</v>
+        <v>444254</v>
       </c>
       <c r="R97" t="n">
-        <v>6787326</v>
+        <v>6787204</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10470,10 +10483,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>129795252</v>
+        <v>129795124</v>
       </c>
       <c r="B98" t="n">
-        <v>79081</v>
+        <v>79700</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10481,21 +10494,21 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10505,10 +10518,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>444249</v>
+        <v>444393</v>
       </c>
       <c r="R98" t="n">
-        <v>6787249</v>
+        <v>6787395</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10541,11 +10554,6 @@
       <c r="AA98" t="inlineStr">
         <is>
           <t>2025-11-22</t>
-        </is>
-      </c>
-      <c r="AC98" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 40m.</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -10572,10 +10580,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>129795152</v>
+        <v>129795123</v>
       </c>
       <c r="B99" t="n">
-        <v>57733</v>
+        <v>79700</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10583,42 +10591,34 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
-      <c r="K99" t="inlineStr"/>
-      <c r="L99" t="inlineStr"/>
-      <c r="M99" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>444434</v>
+        <v>444530</v>
       </c>
       <c r="R99" t="n">
-        <v>6787304</v>
+        <v>6787326</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10784,7 +10784,7 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>129795248</v>
+        <v>129795264</v>
       </c>
       <c r="B101" t="n">
         <v>79081</v>
@@ -10819,10 +10819,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>444238</v>
+        <v>444252</v>
       </c>
       <c r="R101" t="n">
-        <v>6787281</v>
+        <v>6787160</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10881,7 +10881,7 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>129795303</v>
+        <v>129795248</v>
       </c>
       <c r="B102" t="n">
         <v>79081</v>
@@ -10916,10 +10916,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>444200</v>
+        <v>444238</v>
       </c>
       <c r="R102" t="n">
-        <v>6787331</v>
+        <v>6787281</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -10978,7 +10978,7 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>129795264</v>
+        <v>129795303</v>
       </c>
       <c r="B103" t="n">
         <v>79081</v>
@@ -11013,10 +11013,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>444252</v>
+        <v>444200</v>
       </c>
       <c r="R103" t="n">
-        <v>6787160</v>
+        <v>6787331</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11279,7 +11279,7 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>129795186</v>
+        <v>129795180</v>
       </c>
       <c r="B106" t="n">
         <v>8450</v>
@@ -11323,10 +11323,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>444473</v>
+        <v>444409</v>
       </c>
       <c r="R106" t="n">
-        <v>6787334</v>
+        <v>6787219</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11386,7 +11386,7 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>129795196</v>
+        <v>129795186</v>
       </c>
       <c r="B107" t="n">
         <v>8450</v>
@@ -11430,10 +11430,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>444346</v>
+        <v>444473</v>
       </c>
       <c r="R107" t="n">
-        <v>6787369</v>
+        <v>6787334</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11493,7 +11493,7 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>129795178</v>
+        <v>129795196</v>
       </c>
       <c r="B108" t="n">
         <v>8450</v>
@@ -11537,10 +11537,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>444375</v>
+        <v>444346</v>
       </c>
       <c r="R108" t="n">
-        <v>6787207</v>
+        <v>6787369</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11600,7 +11600,7 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>129795180</v>
+        <v>129795178</v>
       </c>
       <c r="B109" t="n">
         <v>8450</v>
@@ -11644,10 +11644,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>444409</v>
+        <v>444375</v>
       </c>
       <c r="R109" t="n">
-        <v>6787219</v>
+        <v>6787207</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11707,45 +11707,54 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>129795259</v>
+        <v>129795201</v>
       </c>
       <c r="B110" t="n">
-        <v>79081</v>
+        <v>8450</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
+      <c r="J110" t="inlineStr"/>
+      <c r="K110" t="inlineStr"/>
+      <c r="L110" t="inlineStr"/>
+      <c r="M110" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N110" t="inlineStr"/>
       <c r="P110" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>444164</v>
+        <v>444430</v>
       </c>
       <c r="R110" t="n">
-        <v>6787121</v>
+        <v>6787332</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11786,6 +11795,7 @@
       <c r="AE110" t="b">
         <v>0</v>
       </c>
+      <c r="AF110" t="inlineStr"/>
       <c r="AG110" t="b">
         <v>0</v>
       </c>
@@ -11804,40 +11814,41 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>129795149</v>
+        <v>129795203</v>
       </c>
       <c r="B111" t="n">
-        <v>57733</v>
+        <v>8450</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
+      <c r="J111" t="inlineStr"/>
       <c r="K111" t="inlineStr"/>
       <c r="L111" t="inlineStr"/>
       <c r="M111" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N111" t="inlineStr"/>
@@ -11847,10 +11858,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>444223</v>
+        <v>444401</v>
       </c>
       <c r="R111" t="n">
-        <v>6787221</v>
+        <v>6787298</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -11891,6 +11902,7 @@
       <c r="AE111" t="b">
         <v>0</v>
       </c>
+      <c r="AF111" t="inlineStr"/>
       <c r="AG111" t="b">
         <v>0</v>
       </c>
@@ -11909,10 +11921,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>129795145</v>
+        <v>129795259</v>
       </c>
       <c r="B112" t="n">
-        <v>57733</v>
+        <v>79081</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -11920,42 +11932,34 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
-      <c r="K112" t="inlineStr"/>
-      <c r="L112" t="inlineStr"/>
-      <c r="M112" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N112" t="inlineStr"/>
       <c r="P112" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>444228</v>
+        <v>444164</v>
       </c>
       <c r="R112" t="n">
-        <v>6787226</v>
+        <v>6787121</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12014,7 +12018,7 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>129795151</v>
+        <v>129795149</v>
       </c>
       <c r="B113" t="n">
         <v>57733</v>
@@ -12047,7 +12051,7 @@
       <c r="L113" t="inlineStr"/>
       <c r="M113" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N113" t="inlineStr"/>
@@ -12057,10 +12061,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>444425</v>
+        <v>444223</v>
       </c>
       <c r="R113" t="n">
-        <v>6787278</v>
+        <v>6787221</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12119,41 +12123,40 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>129795203</v>
+        <v>129795145</v>
       </c>
       <c r="B114" t="n">
-        <v>8450</v>
+        <v>57733</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
-      <c r="J114" t="inlineStr"/>
       <c r="K114" t="inlineStr"/>
       <c r="L114" t="inlineStr"/>
       <c r="M114" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N114" t="inlineStr"/>
@@ -12163,10 +12166,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>444401</v>
+        <v>444228</v>
       </c>
       <c r="R114" t="n">
-        <v>6787298</v>
+        <v>6787226</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12207,7 +12210,6 @@
       <c r="AE114" t="b">
         <v>0</v>
       </c>
-      <c r="AF114" t="inlineStr"/>
       <c r="AG114" t="b">
         <v>0</v>
       </c>
@@ -12226,41 +12228,40 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>129795201</v>
+        <v>129795151</v>
       </c>
       <c r="B115" t="n">
-        <v>8450</v>
+        <v>57733</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
-      <c r="J115" t="inlineStr"/>
       <c r="K115" t="inlineStr"/>
       <c r="L115" t="inlineStr"/>
       <c r="M115" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N115" t="inlineStr"/>
@@ -12270,10 +12271,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>444430</v>
+        <v>444425</v>
       </c>
       <c r="R115" t="n">
-        <v>6787332</v>
+        <v>6787278</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12314,7 +12315,6 @@
       <c r="AE115" t="b">
         <v>0</v>
       </c>
-      <c r="AF115" t="inlineStr"/>
       <c r="AG115" t="b">
         <v>0</v>
       </c>
@@ -12333,54 +12333,45 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>129795171</v>
+        <v>129795289</v>
       </c>
       <c r="B116" t="n">
-        <v>8450</v>
+        <v>79081</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
-      <c r="J116" t="inlineStr"/>
-      <c r="K116" t="inlineStr"/>
-      <c r="L116" t="inlineStr"/>
-      <c r="M116" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N116" t="inlineStr"/>
       <c r="P116" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>444185</v>
+        <v>444435</v>
       </c>
       <c r="R116" t="n">
-        <v>6787226</v>
+        <v>6787341</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12421,7 +12412,6 @@
       <c r="AE116" t="b">
         <v>0</v>
       </c>
-      <c r="AF116" t="inlineStr"/>
       <c r="AG116" t="b">
         <v>0</v>
       </c>
@@ -12440,45 +12430,54 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>129795289</v>
+        <v>129795171</v>
       </c>
       <c r="B117" t="n">
-        <v>79081</v>
+        <v>8450</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
+      <c r="J117" t="inlineStr"/>
+      <c r="K117" t="inlineStr"/>
+      <c r="L117" t="inlineStr"/>
+      <c r="M117" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N117" t="inlineStr"/>
       <c r="P117" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>444435</v>
+        <v>444185</v>
       </c>
       <c r="R117" t="n">
-        <v>6787341</v>
+        <v>6787226</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12519,6 +12518,7 @@
       <c r="AE117" t="b">
         <v>0</v>
       </c>
+      <c r="AF117" t="inlineStr"/>
       <c r="AG117" t="b">
         <v>0</v>
       </c>
@@ -12957,7 +12957,7 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>129795179</v>
+        <v>129795188</v>
       </c>
       <c r="B122" t="n">
         <v>8450</v>
@@ -13001,10 +13001,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>444378</v>
+        <v>444498</v>
       </c>
       <c r="R122" t="n">
-        <v>6787236</v>
+        <v>6787280</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -13064,7 +13064,7 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>129795188</v>
+        <v>129795179</v>
       </c>
       <c r="B123" t="n">
         <v>8450</v>
@@ -13108,10 +13108,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>444498</v>
+        <v>444378</v>
       </c>
       <c r="R123" t="n">
-        <v>6787280</v>
+        <v>6787236</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13171,7 +13171,7 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>129795301</v>
+        <v>129795294</v>
       </c>
       <c r="B124" t="n">
         <v>79081</v>
@@ -13206,10 +13206,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>444250</v>
+        <v>444323</v>
       </c>
       <c r="R124" t="n">
-        <v>6787342</v>
+        <v>6787297</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13268,10 +13268,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>129795144</v>
+        <v>129795301</v>
       </c>
       <c r="B125" t="n">
-        <v>57733</v>
+        <v>79081</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -13279,42 +13279,34 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
-      <c r="K125" t="inlineStr"/>
-      <c r="L125" t="inlineStr"/>
-      <c r="M125" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N125" t="inlineStr"/>
       <c r="P125" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>444186</v>
+        <v>444250</v>
       </c>
       <c r="R125" t="n">
-        <v>6787223</v>
+        <v>6787342</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13373,10 +13365,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>129795294</v>
+        <v>129795144</v>
       </c>
       <c r="B126" t="n">
-        <v>79081</v>
+        <v>57733</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -13384,34 +13376,42 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
+      <c r="K126" t="inlineStr"/>
+      <c r="L126" t="inlineStr"/>
+      <c r="M126" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N126" t="inlineStr"/>
       <c r="P126" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>444323</v>
+        <v>444186</v>
       </c>
       <c r="R126" t="n">
-        <v>6787297</v>
+        <v>6787223</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -13470,7 +13470,7 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>129795258</v>
+        <v>129795267</v>
       </c>
       <c r="B127" t="n">
         <v>79081</v>
@@ -13505,10 +13505,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>444174</v>
+        <v>444353</v>
       </c>
       <c r="R127" t="n">
-        <v>6787136</v>
+        <v>6787215</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -13541,6 +13541,11 @@
       <c r="AA127" t="inlineStr">
         <is>
           <t>2025-11-22</t>
+        </is>
+      </c>
+      <c r="AC127" t="inlineStr">
+        <is>
+          <t>Gott om garnlav inom en radie av 40m.</t>
         </is>
       </c>
       <c r="AD127" t="b">
@@ -13567,7 +13572,7 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>129795275</v>
+        <v>129795263</v>
       </c>
       <c r="B128" t="n">
         <v>79081</v>
@@ -13602,10 +13607,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>444495</v>
+        <v>444241</v>
       </c>
       <c r="R128" t="n">
-        <v>6787340</v>
+        <v>6787149</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -13664,10 +13669,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>129795267</v>
+        <v>129795159</v>
       </c>
       <c r="B129" t="n">
-        <v>79081</v>
+        <v>57733</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -13675,34 +13680,42 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
+      <c r="K129" t="inlineStr"/>
+      <c r="L129" t="inlineStr"/>
+      <c r="M129" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N129" t="inlineStr"/>
       <c r="P129" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>444353</v>
+        <v>444436</v>
       </c>
       <c r="R129" t="n">
-        <v>6787215</v>
+        <v>6787463</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -13735,11 +13748,6 @@
       <c r="AA129" t="inlineStr">
         <is>
           <t>2025-11-22</t>
-        </is>
-      </c>
-      <c r="AC129" t="inlineStr">
-        <is>
-          <t>Gott om garnlav inom en radie av 40m.</t>
         </is>
       </c>
       <c r="AD129" t="b">
@@ -13766,10 +13774,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>129795137</v>
+        <v>129795258</v>
       </c>
       <c r="B130" t="n">
-        <v>91614</v>
+        <v>79081</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -13777,37 +13785,34 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
-      <c r="J130" t="inlineStr"/>
-      <c r="K130" t="inlineStr"/>
-      <c r="N130" t="inlineStr"/>
       <c r="P130" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>444203</v>
+        <v>444174</v>
       </c>
       <c r="R130" t="n">
-        <v>6787221</v>
+        <v>6787136</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -13848,7 +13853,6 @@
       <c r="AE130" t="b">
         <v>0</v>
       </c>
-      <c r="AF130" t="inlineStr"/>
       <c r="AG130" t="b">
         <v>0</v>
       </c>
@@ -13867,10 +13871,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>129795159</v>
+        <v>129795275</v>
       </c>
       <c r="B131" t="n">
-        <v>57733</v>
+        <v>79081</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -13878,42 +13882,34 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
-      <c r="K131" t="inlineStr"/>
-      <c r="L131" t="inlineStr"/>
-      <c r="M131" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N131" t="inlineStr"/>
       <c r="P131" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>444436</v>
+        <v>444495</v>
       </c>
       <c r="R131" t="n">
-        <v>6787463</v>
+        <v>6787340</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -13972,43 +13968,37 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>129795175</v>
+        <v>129795137</v>
       </c>
       <c r="B132" t="n">
-        <v>8450</v>
+        <v>91614</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>106545</v>
+        <v>5442</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
       <c r="J132" t="inlineStr"/>
       <c r="K132" t="inlineStr"/>
-      <c r="L132" t="inlineStr"/>
-      <c r="M132" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N132" t="inlineStr"/>
       <c r="P132" t="inlineStr">
         <is>
@@ -14016,10 +14006,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>444182</v>
+        <v>444203</v>
       </c>
       <c r="R132" t="n">
-        <v>6787101</v>
+        <v>6787221</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -14079,45 +14069,54 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>129795263</v>
+        <v>129795175</v>
       </c>
       <c r="B133" t="n">
-        <v>79081</v>
+        <v>8450</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
+      <c r="J133" t="inlineStr"/>
+      <c r="K133" t="inlineStr"/>
+      <c r="L133" t="inlineStr"/>
+      <c r="M133" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N133" t="inlineStr"/>
       <c r="P133" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>444241</v>
+        <v>444182</v>
       </c>
       <c r="R133" t="n">
-        <v>6787149</v>
+        <v>6787101</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -14158,6 +14157,7 @@
       <c r="AE133" t="b">
         <v>0</v>
       </c>
+      <c r="AF133" t="inlineStr"/>
       <c r="AG133" t="b">
         <v>0</v>
       </c>
@@ -14283,7 +14283,7 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>129795304</v>
+        <v>129795274</v>
       </c>
       <c r="B135" t="n">
         <v>79081</v>
@@ -14318,10 +14318,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>444172</v>
+        <v>444538</v>
       </c>
       <c r="R135" t="n">
-        <v>6787339</v>
+        <v>6787325</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -14380,7 +14380,7 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>129795254</v>
+        <v>129795304</v>
       </c>
       <c r="B136" t="n">
         <v>79081</v>
@@ -14409,19 +14409,16 @@
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
-      <c r="J136" t="inlineStr"/>
-      <c r="K136" t="inlineStr"/>
-      <c r="N136" t="inlineStr"/>
       <c r="P136" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>444199</v>
+        <v>444172</v>
       </c>
       <c r="R136" t="n">
-        <v>6787221</v>
+        <v>6787339</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -14462,7 +14459,6 @@
       <c r="AE136" t="b">
         <v>0</v>
       </c>
-      <c r="AF136" t="inlineStr"/>
       <c r="AG136" t="b">
         <v>0</v>
       </c>
@@ -14481,43 +14477,37 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>129795204</v>
+        <v>129795254</v>
       </c>
       <c r="B137" t="n">
-        <v>8450</v>
+        <v>79081</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E137" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
       <c r="J137" t="inlineStr"/>
       <c r="K137" t="inlineStr"/>
-      <c r="L137" t="inlineStr"/>
-      <c r="M137" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N137" t="inlineStr"/>
       <c r="P137" t="inlineStr">
         <is>
@@ -14525,10 +14515,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>444380</v>
+        <v>444199</v>
       </c>
       <c r="R137" t="n">
-        <v>6787306</v>
+        <v>6787221</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -14588,7 +14578,7 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>129795274</v>
+        <v>129795302</v>
       </c>
       <c r="B138" t="n">
         <v>79081</v>
@@ -14623,10 +14613,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>444538</v>
+        <v>444222</v>
       </c>
       <c r="R138" t="n">
-        <v>6787325</v>
+        <v>6787345</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -14685,7 +14675,7 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>129795302</v>
+        <v>129795251</v>
       </c>
       <c r="B139" t="n">
         <v>79081</v>
@@ -14714,16 +14704,19 @@
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
+      <c r="J139" t="inlineStr"/>
+      <c r="K139" t="inlineStr"/>
+      <c r="N139" t="inlineStr"/>
       <c r="P139" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>444222</v>
+        <v>444309</v>
       </c>
       <c r="R139" t="n">
-        <v>6787345</v>
+        <v>6787272</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -14764,6 +14757,7 @@
       <c r="AE139" t="b">
         <v>0</v>
       </c>
+      <c r="AF139" t="inlineStr"/>
       <c r="AG139" t="b">
         <v>0</v>
       </c>
@@ -14782,7 +14776,7 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>129795251</v>
+        <v>129795247</v>
       </c>
       <c r="B140" t="n">
         <v>79081</v>
@@ -14811,19 +14805,16 @@
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
-      <c r="J140" t="inlineStr"/>
-      <c r="K140" t="inlineStr"/>
-      <c r="N140" t="inlineStr"/>
       <c r="P140" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>444309</v>
+        <v>444225</v>
       </c>
       <c r="R140" t="n">
-        <v>6787272</v>
+        <v>6787275</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -14864,7 +14855,6 @@
       <c r="AE140" t="b">
         <v>0</v>
       </c>
-      <c r="AF140" t="inlineStr"/>
       <c r="AG140" t="b">
         <v>0</v>
       </c>
@@ -14883,45 +14873,54 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>129795266</v>
+        <v>129795204</v>
       </c>
       <c r="B141" t="n">
-        <v>79081</v>
+        <v>8450</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E141" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
+      <c r="J141" t="inlineStr"/>
+      <c r="K141" t="inlineStr"/>
+      <c r="L141" t="inlineStr"/>
+      <c r="M141" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N141" t="inlineStr"/>
       <c r="P141" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>444314</v>
+        <v>444380</v>
       </c>
       <c r="R141" t="n">
-        <v>6787212</v>
+        <v>6787306</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -14956,17 +14955,13 @@
           <t>2025-11-22</t>
         </is>
       </c>
-      <c r="AC141" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 40m</t>
-        </is>
-      </c>
       <c r="AD141" t="b">
         <v>0</v>
       </c>
       <c r="AE141" t="b">
         <v>0</v>
       </c>
+      <c r="AF141" t="inlineStr"/>
       <c r="AG141" t="b">
         <v>0</v>
       </c>
@@ -14985,7 +14980,7 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>129795247</v>
+        <v>129795266</v>
       </c>
       <c r="B142" t="n">
         <v>79081</v>
@@ -15020,10 +15015,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>444225</v>
+        <v>444314</v>
       </c>
       <c r="R142" t="n">
-        <v>6787275</v>
+        <v>6787212</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -15056,6 +15051,11 @@
       <c r="AA142" t="inlineStr">
         <is>
           <t>2025-11-22</t>
+        </is>
+      </c>
+      <c r="AC142" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 40m</t>
         </is>
       </c>
       <c r="AD142" t="b">

--- a/artfynd/A 51041-2025 artfynd.xlsx
+++ b/artfynd/A 51041-2025 artfynd.xlsx
@@ -675,54 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129795190</v>
+        <v>129795244</v>
       </c>
       <c r="B2" t="n">
-        <v>8450</v>
+        <v>79081</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>444510</v>
+        <v>444105</v>
       </c>
       <c r="R2" t="n">
-        <v>6787276</v>
+        <v>6787246</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -763,7 +754,6 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -782,54 +772,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129795197</v>
+        <v>129795261</v>
       </c>
       <c r="B3" t="n">
-        <v>8450</v>
+        <v>79081</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>444406</v>
+        <v>444193</v>
       </c>
       <c r="R3" t="n">
-        <v>6787392</v>
+        <v>6787130</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -870,7 +851,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -996,45 +976,54 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129795253</v>
+        <v>129795190</v>
       </c>
       <c r="B5" t="n">
-        <v>79081</v>
+        <v>8450</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>444185</v>
+        <v>444510</v>
       </c>
       <c r="R5" t="n">
-        <v>6787247</v>
+        <v>6787276</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1069,17 +1058,13 @@
           <t>2025-11-22</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Gott om garnlav inom en radie av 50 m.</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1098,45 +1083,54 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129795291</v>
+        <v>129795197</v>
       </c>
       <c r="B6" t="n">
-        <v>79081</v>
+        <v>8450</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>444412</v>
+        <v>444406</v>
       </c>
       <c r="R6" t="n">
-        <v>6787307</v>
+        <v>6787392</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1177,6 +1171,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1195,7 +1190,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129795244</v>
+        <v>129795253</v>
       </c>
       <c r="B7" t="n">
         <v>79081</v>
@@ -1230,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>444105</v>
+        <v>444185</v>
       </c>
       <c r="R7" t="n">
-        <v>6787246</v>
+        <v>6787247</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1266,6 +1261,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-11-22</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Gott om garnlav inom en radie av 50 m.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1292,7 +1292,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129795261</v>
+        <v>129795291</v>
       </c>
       <c r="B8" t="n">
         <v>79081</v>
@@ -1327,10 +1327,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>444193</v>
+        <v>444412</v>
       </c>
       <c r="R8" t="n">
-        <v>6787130</v>
+        <v>6787307</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1999,43 +1999,37 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129795205</v>
+        <v>129795281</v>
       </c>
       <c r="B15" t="n">
-        <v>8450</v>
+        <v>79081</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2043,10 +2037,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>444343</v>
+        <v>444408</v>
       </c>
       <c r="R15" t="n">
-        <v>6787310</v>
+        <v>6787452</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2106,7 +2100,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129795281</v>
+        <v>129795271</v>
       </c>
       <c r="B16" t="n">
         <v>79081</v>
@@ -2144,10 +2138,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>444408</v>
+        <v>444466</v>
       </c>
       <c r="R16" t="n">
-        <v>6787452</v>
+        <v>6787306</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2180,6 +2174,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-11-22</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 50m.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2207,7 +2206,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129795271</v>
+        <v>129795276</v>
       </c>
       <c r="B17" t="n">
         <v>79081</v>
@@ -2245,10 +2244,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>444466</v>
+        <v>444499</v>
       </c>
       <c r="R17" t="n">
-        <v>6787306</v>
+        <v>6787367</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2313,7 +2312,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129795276</v>
+        <v>129795299</v>
       </c>
       <c r="B18" t="n">
         <v>79081</v>
@@ -2342,19 +2341,16 @@
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>444499</v>
+        <v>444265</v>
       </c>
       <c r="R18" t="n">
-        <v>6787367</v>
+        <v>6787372</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2389,18 +2385,12 @@
           <t>2025-11-22</t>
         </is>
       </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 50m.</t>
-        </is>
-      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2419,45 +2409,54 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129795299</v>
+        <v>129795174</v>
       </c>
       <c r="B19" t="n">
-        <v>79081</v>
+        <v>8450</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>444265</v>
+        <v>444166</v>
       </c>
       <c r="R19" t="n">
-        <v>6787372</v>
+        <v>6787161</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2498,6 +2497,7 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2516,7 +2516,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129795174</v>
+        <v>129795205</v>
       </c>
       <c r="B20" t="n">
         <v>8450</v>
@@ -2560,10 +2560,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>444166</v>
+        <v>444343</v>
       </c>
       <c r="R20" t="n">
-        <v>6787161</v>
+        <v>6787310</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2623,45 +2623,54 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129795273</v>
+        <v>129795198</v>
       </c>
       <c r="B21" t="n">
-        <v>79081</v>
+        <v>8450</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>444548</v>
+        <v>444434</v>
       </c>
       <c r="R21" t="n">
-        <v>6787330</v>
+        <v>6787384</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2702,6 +2711,7 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -2720,45 +2730,54 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129795265</v>
+        <v>129795207</v>
       </c>
       <c r="B22" t="n">
-        <v>79081</v>
+        <v>8450</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>444278</v>
+        <v>444221</v>
       </c>
       <c r="R22" t="n">
-        <v>6787163</v>
+        <v>6787340</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2799,6 +2818,7 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -2817,37 +2837,43 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129795310</v>
+        <v>129795200</v>
       </c>
       <c r="B23" t="n">
-        <v>79081</v>
+        <v>8450</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -2855,10 +2881,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>444488</v>
+        <v>444429</v>
       </c>
       <c r="R23" t="n">
-        <v>6787445</v>
+        <v>6787341</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2891,11 +2917,6 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-11-22</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Gott om garnlav inom en radie av 40m</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2923,45 +2944,54 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129795278</v>
+        <v>129795206</v>
       </c>
       <c r="B24" t="n">
-        <v>79081</v>
+        <v>8450</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>444465</v>
+        <v>444247</v>
       </c>
       <c r="R24" t="n">
-        <v>6787451</v>
+        <v>6787328</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3002,6 +3032,7 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3020,54 +3051,45 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129795207</v>
+        <v>129795273</v>
       </c>
       <c r="B25" t="n">
-        <v>8450</v>
+        <v>79081</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>444221</v>
+        <v>444548</v>
       </c>
       <c r="R25" t="n">
-        <v>6787340</v>
+        <v>6787330</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3108,7 +3130,6 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3127,54 +3148,45 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129795206</v>
+        <v>129795265</v>
       </c>
       <c r="B26" t="n">
-        <v>8450</v>
+        <v>79081</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>444247</v>
+        <v>444278</v>
       </c>
       <c r="R26" t="n">
-        <v>6787328</v>
+        <v>6787163</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3215,7 +3227,6 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
-      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3234,43 +3245,37 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129795198</v>
+        <v>129795310</v>
       </c>
       <c r="B27" t="n">
-        <v>8450</v>
+        <v>79081</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -3278,10 +3283,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>444434</v>
+        <v>444488</v>
       </c>
       <c r="R27" t="n">
-        <v>6787384</v>
+        <v>6787445</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3314,6 +3319,11 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-11-22</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Gott om garnlav inom en radie av 40m</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3341,54 +3351,45 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129795200</v>
+        <v>129795278</v>
       </c>
       <c r="B28" t="n">
-        <v>8450</v>
+        <v>79081</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>444429</v>
+        <v>444465</v>
       </c>
       <c r="R28" t="n">
-        <v>6787341</v>
+        <v>6787451</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3429,7 +3430,6 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
-      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -3448,45 +3448,54 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129795268</v>
+        <v>129795187</v>
       </c>
       <c r="B29" t="n">
-        <v>79081</v>
+        <v>8450</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>444383</v>
+        <v>444487</v>
       </c>
       <c r="R29" t="n">
-        <v>6787218</v>
+        <v>6787321</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3527,6 +3536,7 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -3545,45 +3555,54 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129795256</v>
+        <v>129795189</v>
       </c>
       <c r="B30" t="n">
-        <v>79081</v>
+        <v>8450</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>444226</v>
+        <v>444500</v>
       </c>
       <c r="R30" t="n">
-        <v>6787196</v>
+        <v>6787274</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3624,6 +3643,7 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
+      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -3642,40 +3662,41 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129795142</v>
+        <v>129795176</v>
       </c>
       <c r="B31" t="n">
-        <v>57733</v>
+        <v>8450</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="N31" t="inlineStr"/>
@@ -3685,10 +3706,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>444276</v>
+        <v>444215</v>
       </c>
       <c r="R31" t="n">
-        <v>6787287</v>
+        <v>6787151</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3729,6 +3750,7 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
+      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
@@ -3747,41 +3769,40 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129795187</v>
+        <v>129795142</v>
       </c>
       <c r="B32" t="n">
-        <v>8450</v>
+        <v>57733</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr"/>
       <c r="M32" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N32" t="inlineStr"/>
@@ -3791,10 +3812,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>444487</v>
+        <v>444276</v>
       </c>
       <c r="R32" t="n">
-        <v>6787321</v>
+        <v>6787287</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3835,7 +3856,6 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
-      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
@@ -3854,54 +3874,45 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129795189</v>
+        <v>129795268</v>
       </c>
       <c r="B33" t="n">
-        <v>8450</v>
+        <v>79081</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>444500</v>
+        <v>444383</v>
       </c>
       <c r="R33" t="n">
-        <v>6787274</v>
+        <v>6787218</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3942,7 +3953,6 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
-      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -3961,54 +3971,45 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129795176</v>
+        <v>129795256</v>
       </c>
       <c r="B34" t="n">
-        <v>8450</v>
+        <v>79081</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>444215</v>
+        <v>444226</v>
       </c>
       <c r="R34" t="n">
-        <v>6787151</v>
+        <v>6787196</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4049,7 +4050,6 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
-      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
@@ -4068,10 +4068,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129795296</v>
+        <v>129795165</v>
       </c>
       <c r="B35" t="n">
-        <v>79081</v>
+        <v>57733</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4079,26 +4079,31 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
@@ -4106,10 +4111,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>444299</v>
+        <v>444251</v>
       </c>
       <c r="R35" t="n">
-        <v>6787304</v>
+        <v>6787376</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4144,18 +4149,12 @@
           <t>2025-11-22</t>
         </is>
       </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 50 m.</t>
-        </is>
-      </c>
       <c r="AD35" t="b">
         <v>0</v>
       </c>
       <c r="AE35" t="b">
         <v>0</v>
       </c>
-      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
@@ -4174,7 +4173,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129795269</v>
+        <v>129795270</v>
       </c>
       <c r="B36" t="n">
         <v>79081</v>
@@ -4209,10 +4208,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>444429</v>
+        <v>444416</v>
       </c>
       <c r="R36" t="n">
-        <v>6787240</v>
+        <v>6787260</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4271,7 +4270,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129795249</v>
+        <v>129795296</v>
       </c>
       <c r="B37" t="n">
         <v>79081</v>
@@ -4300,16 +4299,19 @@
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>444267</v>
+        <v>444299</v>
       </c>
       <c r="R37" t="n">
-        <v>6787295</v>
+        <v>6787304</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4344,12 +4346,18 @@
           <t>2025-11-22</t>
         </is>
       </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 50 m.</t>
+        </is>
+      </c>
       <c r="AD37" t="b">
         <v>0</v>
       </c>
       <c r="AE37" t="b">
         <v>0</v>
       </c>
+      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -4368,7 +4376,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129795270</v>
+        <v>129795269</v>
       </c>
       <c r="B38" t="n">
         <v>79081</v>
@@ -4403,10 +4411,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>444416</v>
+        <v>444429</v>
       </c>
       <c r="R38" t="n">
-        <v>6787260</v>
+        <v>6787240</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4465,54 +4473,45 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129795202</v>
+        <v>129795249</v>
       </c>
       <c r="B39" t="n">
-        <v>8450</v>
+        <v>79081</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>444413</v>
+        <v>444267</v>
       </c>
       <c r="R39" t="n">
-        <v>6787314</v>
+        <v>6787295</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4553,7 +4552,6 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
-      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -4572,10 +4570,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129795165</v>
+        <v>129795133</v>
       </c>
       <c r="B40" t="n">
-        <v>57733</v>
+        <v>57896</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4583,21 +4581,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4605,7 +4603,7 @@
       <c r="L40" t="inlineStr"/>
       <c r="M40" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N40" t="inlineStr"/>
@@ -4615,10 +4613,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>444251</v>
+        <v>444226</v>
       </c>
       <c r="R40" t="n">
-        <v>6787376</v>
+        <v>6787236</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4677,40 +4675,41 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129795133</v>
+        <v>129795193</v>
       </c>
       <c r="B41" t="n">
-        <v>57896</v>
+        <v>8450</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>103021</v>
+        <v>106545</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
       <c r="K41" t="inlineStr"/>
       <c r="L41" t="inlineStr"/>
       <c r="M41" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N41" t="inlineStr"/>
@@ -4720,10 +4719,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>444226</v>
+        <v>444508</v>
       </c>
       <c r="R41" t="n">
-        <v>6787236</v>
+        <v>6787352</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4764,6 +4763,7 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
+      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
@@ -4782,7 +4782,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129795193</v>
+        <v>129795202</v>
       </c>
       <c r="B42" t="n">
         <v>8450</v>
@@ -4826,10 +4826,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>444508</v>
+        <v>444413</v>
       </c>
       <c r="R42" t="n">
-        <v>6787352</v>
+        <v>6787314</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4889,43 +4889,37 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129795170</v>
+        <v>129795136</v>
       </c>
       <c r="B43" t="n">
-        <v>8450</v>
+        <v>91614</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>106545</v>
+        <v>5442</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="J43" t="inlineStr"/>
       <c r="K43" t="inlineStr"/>
-      <c r="L43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
@@ -4933,10 +4927,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>444172</v>
+        <v>444235</v>
       </c>
       <c r="R43" t="n">
-        <v>6787202</v>
+        <v>6787149</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4996,37 +4990,43 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129795282</v>
+        <v>129795170</v>
       </c>
       <c r="B44" t="n">
-        <v>79081</v>
+        <v>8450</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="J44" t="inlineStr"/>
       <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
@@ -5034,10 +5034,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>444374</v>
+        <v>444172</v>
       </c>
       <c r="R44" t="n">
-        <v>6787384</v>
+        <v>6787202</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5070,11 +5070,6 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-11-22</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 50 m.</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5102,10 +5097,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129795293</v>
+        <v>129795158</v>
       </c>
       <c r="B45" t="n">
-        <v>79081</v>
+        <v>57733</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5113,34 +5108,42 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>444365</v>
+        <v>444501</v>
       </c>
       <c r="R45" t="n">
-        <v>6787285</v>
+        <v>6787402</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5173,11 +5176,6 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-11-22</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 50m.</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5204,10 +5202,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129795136</v>
+        <v>129795282</v>
       </c>
       <c r="B46" t="n">
-        <v>91614</v>
+        <v>79081</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5215,21 +5213,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5242,10 +5240,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>444235</v>
+        <v>444374</v>
       </c>
       <c r="R46" t="n">
-        <v>6787149</v>
+        <v>6787384</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5278,6 +5276,11 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-11-22</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 50 m.</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5305,10 +5308,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129795158</v>
+        <v>129795293</v>
       </c>
       <c r="B47" t="n">
-        <v>57733</v>
+        <v>79081</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5316,42 +5319,34 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="K47" t="inlineStr"/>
-      <c r="L47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>444501</v>
+        <v>444365</v>
       </c>
       <c r="R47" t="n">
-        <v>6787402</v>
+        <v>6787285</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5384,6 +5379,11 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-11-22</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 50m.</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5410,10 +5410,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129795250</v>
+        <v>129795138</v>
       </c>
       <c r="B48" t="n">
-        <v>79081</v>
+        <v>91614</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5421,34 +5421,37 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="J48" t="inlineStr"/>
+      <c r="K48" t="inlineStr"/>
+      <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>444295</v>
+        <v>444250</v>
       </c>
       <c r="R48" t="n">
-        <v>6787287</v>
+        <v>6787196</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5489,6 +5492,7 @@
       <c r="AE48" t="b">
         <v>0</v>
       </c>
+      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
@@ -5706,7 +5710,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129795246</v>
+        <v>129795250</v>
       </c>
       <c r="B51" t="n">
         <v>79081</v>
@@ -5741,10 +5745,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>444145</v>
+        <v>444295</v>
       </c>
       <c r="R51" t="n">
-        <v>6787239</v>
+        <v>6787287</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5777,11 +5781,6 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-11-22</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 40m.</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5808,10 +5807,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129795138</v>
+        <v>129795246</v>
       </c>
       <c r="B52" t="n">
-        <v>91614</v>
+        <v>79081</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5819,37 +5818,34 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="J52" t="inlineStr"/>
-      <c r="K52" t="inlineStr"/>
-      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>444250</v>
+        <v>444145</v>
       </c>
       <c r="R52" t="n">
-        <v>6787196</v>
+        <v>6787239</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5884,13 +5880,17 @@
           <t>2025-11-22</t>
         </is>
       </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 40m.</t>
+        </is>
+      </c>
       <c r="AD52" t="b">
         <v>0</v>
       </c>
       <c r="AE52" t="b">
         <v>0</v>
       </c>
-      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
@@ -5909,10 +5909,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129795134</v>
+        <v>129795277</v>
       </c>
       <c r="B53" t="n">
-        <v>57896</v>
+        <v>79081</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5920,42 +5920,34 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="K53" t="inlineStr"/>
-      <c r="L53" t="inlineStr"/>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>444289</v>
+        <v>444491</v>
       </c>
       <c r="R53" t="n">
-        <v>6787357</v>
+        <v>6787412</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6014,7 +6006,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129795277</v>
+        <v>129795279</v>
       </c>
       <c r="B54" t="n">
         <v>79081</v>
@@ -6049,10 +6041,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>444491</v>
+        <v>444463</v>
       </c>
       <c r="R54" t="n">
-        <v>6787412</v>
+        <v>6787459</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6111,45 +6103,53 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129795279</v>
+        <v>129795131</v>
       </c>
       <c r="B55" t="n">
-        <v>79081</v>
+        <v>56926</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
+      <c r="K55" t="inlineStr"/>
+      <c r="L55" t="inlineStr"/>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>444463</v>
+        <v>444250</v>
       </c>
       <c r="R55" t="n">
-        <v>6787459</v>
+        <v>6787212</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6208,10 +6208,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129795147</v>
+        <v>129795134</v>
       </c>
       <c r="B56" t="n">
-        <v>57733</v>
+        <v>57896</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6219,21 +6219,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6241,7 +6241,7 @@
       <c r="L56" t="inlineStr"/>
       <c r="M56" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N56" t="inlineStr"/>
@@ -6251,10 +6251,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>444220</v>
+        <v>444289</v>
       </c>
       <c r="R56" t="n">
-        <v>6787221</v>
+        <v>6787357</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6313,40 +6313,41 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129795161</v>
+        <v>129795172</v>
       </c>
       <c r="B57" t="n">
-        <v>57733</v>
+        <v>8450</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
+      <c r="J57" t="inlineStr"/>
       <c r="K57" t="inlineStr"/>
       <c r="L57" t="inlineStr"/>
       <c r="M57" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N57" t="inlineStr"/>
@@ -6356,10 +6357,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>444433</v>
+        <v>444225</v>
       </c>
       <c r="R57" t="n">
-        <v>6787338</v>
+        <v>6787223</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6400,6 +6401,7 @@
       <c r="AE57" t="b">
         <v>0</v>
       </c>
+      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
@@ -6418,10 +6420,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129795131</v>
+        <v>129795199</v>
       </c>
       <c r="B58" t="n">
-        <v>56926</v>
+        <v>8450</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6429,29 +6431,30 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>100138</v>
+        <v>106545</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
+      <c r="J58" t="inlineStr"/>
       <c r="K58" t="inlineStr"/>
       <c r="L58" t="inlineStr"/>
       <c r="M58" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N58" t="inlineStr"/>
@@ -6461,10 +6464,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>444250</v>
+        <v>444431</v>
       </c>
       <c r="R58" t="n">
-        <v>6787212</v>
+        <v>6787350</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6505,6 +6508,7 @@
       <c r="AE58" t="b">
         <v>0</v>
       </c>
+      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
       </c>
@@ -6523,41 +6527,40 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129795184</v>
+        <v>129795161</v>
       </c>
       <c r="B59" t="n">
-        <v>8450</v>
+        <v>57733</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
-      <c r="J59" t="inlineStr"/>
       <c r="K59" t="inlineStr"/>
       <c r="L59" t="inlineStr"/>
       <c r="M59" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N59" t="inlineStr"/>
@@ -6567,10 +6570,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>444452</v>
+        <v>444433</v>
       </c>
       <c r="R59" t="n">
-        <v>6787305</v>
+        <v>6787338</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6611,7 +6614,6 @@
       <c r="AE59" t="b">
         <v>0</v>
       </c>
-      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
       </c>
@@ -6630,41 +6632,40 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129795199</v>
+        <v>129795147</v>
       </c>
       <c r="B60" t="n">
-        <v>8450</v>
+        <v>57733</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
-      <c r="J60" t="inlineStr"/>
       <c r="K60" t="inlineStr"/>
       <c r="L60" t="inlineStr"/>
       <c r="M60" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N60" t="inlineStr"/>
@@ -6674,10 +6675,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>444431</v>
+        <v>444220</v>
       </c>
       <c r="R60" t="n">
-        <v>6787350</v>
+        <v>6787221</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6718,7 +6719,6 @@
       <c r="AE60" t="b">
         <v>0</v>
       </c>
-      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
       </c>
@@ -6737,7 +6737,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129795172</v>
+        <v>129795184</v>
       </c>
       <c r="B61" t="n">
         <v>8450</v>
@@ -6781,10 +6781,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>444225</v>
+        <v>444452</v>
       </c>
       <c r="R61" t="n">
-        <v>6787223</v>
+        <v>6787305</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6844,54 +6844,45 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129795191</v>
+        <v>129795125</v>
       </c>
       <c r="B62" t="n">
-        <v>8450</v>
+        <v>79700</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
-      <c r="J62" t="inlineStr"/>
-      <c r="K62" t="inlineStr"/>
-      <c r="L62" t="inlineStr"/>
-      <c r="M62" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>444520</v>
+        <v>444329</v>
       </c>
       <c r="R62" t="n">
-        <v>6787287</v>
+        <v>6787371</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6932,7 +6923,6 @@
       <c r="AE62" t="b">
         <v>0</v>
       </c>
-      <c r="AF62" t="inlineStr"/>
       <c r="AG62" t="b">
         <v>0</v>
       </c>
@@ -6951,41 +6941,40 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129795195</v>
+        <v>129795162</v>
       </c>
       <c r="B63" t="n">
-        <v>8450</v>
+        <v>57733</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
-      <c r="J63" t="inlineStr"/>
       <c r="K63" t="inlineStr"/>
       <c r="L63" t="inlineStr"/>
       <c r="M63" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N63" t="inlineStr"/>
@@ -6995,10 +6984,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>444487</v>
+        <v>444428</v>
       </c>
       <c r="R63" t="n">
-        <v>6787441</v>
+        <v>6787329</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7039,7 +7028,6 @@
       <c r="AE63" t="b">
         <v>0</v>
       </c>
-      <c r="AF63" t="inlineStr"/>
       <c r="AG63" t="b">
         <v>0</v>
       </c>
@@ -7058,7 +7046,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129795177</v>
+        <v>129795191</v>
       </c>
       <c r="B64" t="n">
         <v>8450</v>
@@ -7092,7 +7080,7 @@
       <c r="L64" t="inlineStr"/>
       <c r="M64" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N64" t="inlineStr"/>
@@ -7102,10 +7090,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>444342</v>
+        <v>444520</v>
       </c>
       <c r="R64" t="n">
-        <v>6787223</v>
+        <v>6787287</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7165,45 +7153,54 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129795125</v>
+        <v>129795195</v>
       </c>
       <c r="B65" t="n">
-        <v>79700</v>
+        <v>8450</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
+      <c r="J65" t="inlineStr"/>
+      <c r="K65" t="inlineStr"/>
+      <c r="L65" t="inlineStr"/>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>444329</v>
+        <v>444487</v>
       </c>
       <c r="R65" t="n">
-        <v>6787371</v>
+        <v>6787441</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7244,6 +7241,7 @@
       <c r="AE65" t="b">
         <v>0</v>
       </c>
+      <c r="AF65" t="inlineStr"/>
       <c r="AG65" t="b">
         <v>0</v>
       </c>
@@ -7262,40 +7260,41 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129795162</v>
+        <v>129795177</v>
       </c>
       <c r="B66" t="n">
-        <v>57733</v>
+        <v>8450</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
+      <c r="J66" t="inlineStr"/>
       <c r="K66" t="inlineStr"/>
       <c r="L66" t="inlineStr"/>
       <c r="M66" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="N66" t="inlineStr"/>
@@ -7305,10 +7304,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>444428</v>
+        <v>444342</v>
       </c>
       <c r="R66" t="n">
-        <v>6787329</v>
+        <v>6787223</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7349,6 +7348,7 @@
       <c r="AE66" t="b">
         <v>0</v>
       </c>
+      <c r="AF66" t="inlineStr"/>
       <c r="AG66" t="b">
         <v>0</v>
       </c>
@@ -7367,10 +7367,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129795257</v>
+        <v>129795150</v>
       </c>
       <c r="B67" t="n">
-        <v>79081</v>
+        <v>57733</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7378,34 +7378,42 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
+      <c r="K67" t="inlineStr"/>
+      <c r="L67" t="inlineStr"/>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>444168</v>
+        <v>444413</v>
       </c>
       <c r="R67" t="n">
-        <v>6787171</v>
+        <v>6787222</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7464,10 +7472,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129795150</v>
+        <v>129795257</v>
       </c>
       <c r="B68" t="n">
-        <v>57733</v>
+        <v>79081</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7475,42 +7483,34 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
-      <c r="K68" t="inlineStr"/>
-      <c r="L68" t="inlineStr"/>
-      <c r="M68" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>444413</v>
+        <v>444168</v>
       </c>
       <c r="R68" t="n">
-        <v>6787222</v>
+        <v>6787171</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7569,45 +7569,54 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129795280</v>
+        <v>129795182</v>
       </c>
       <c r="B69" t="n">
-        <v>79081</v>
+        <v>8450</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
+      <c r="J69" t="inlineStr"/>
+      <c r="K69" t="inlineStr"/>
+      <c r="L69" t="inlineStr"/>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>444451</v>
+        <v>444417</v>
       </c>
       <c r="R69" t="n">
-        <v>6787467</v>
+        <v>6787266</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7648,6 +7657,7 @@
       <c r="AE69" t="b">
         <v>0</v>
       </c>
+      <c r="AF69" t="inlineStr"/>
       <c r="AG69" t="b">
         <v>0</v>
       </c>
@@ -7666,10 +7676,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129795272</v>
+        <v>129795135</v>
       </c>
       <c r="B70" t="n">
-        <v>79081</v>
+        <v>91614</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7677,34 +7687,37 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
+      <c r="J70" t="inlineStr"/>
+      <c r="K70" t="inlineStr"/>
+      <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>444553</v>
+        <v>444158</v>
       </c>
       <c r="R70" t="n">
-        <v>6787299</v>
+        <v>6787148</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7745,6 +7758,7 @@
       <c r="AE70" t="b">
         <v>0</v>
       </c>
+      <c r="AF70" t="inlineStr"/>
       <c r="AG70" t="b">
         <v>0</v>
       </c>
@@ -7763,10 +7777,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129795287</v>
+        <v>129795166</v>
       </c>
       <c r="B71" t="n">
-        <v>79081</v>
+        <v>57733</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7774,34 +7788,42 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
+      <c r="K71" t="inlineStr"/>
+      <c r="L71" t="inlineStr"/>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>444430</v>
+        <v>444254</v>
       </c>
       <c r="R71" t="n">
-        <v>6787384</v>
+        <v>6787333</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7860,7 +7882,7 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129795284</v>
+        <v>129795280</v>
       </c>
       <c r="B72" t="n">
         <v>79081</v>
@@ -7895,10 +7917,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>444363</v>
+        <v>444451</v>
       </c>
       <c r="R72" t="n">
-        <v>6787411</v>
+        <v>6787467</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7957,7 +7979,7 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129795243</v>
+        <v>129795272</v>
       </c>
       <c r="B73" t="n">
         <v>79081</v>
@@ -7992,10 +8014,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>444159</v>
+        <v>444553</v>
       </c>
       <c r="R73" t="n">
-        <v>6787297</v>
+        <v>6787299</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8054,10 +8076,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129795135</v>
+        <v>129795287</v>
       </c>
       <c r="B74" t="n">
-        <v>91614</v>
+        <v>79081</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8065,37 +8087,34 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
-      <c r="J74" t="inlineStr"/>
-      <c r="K74" t="inlineStr"/>
-      <c r="N74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>444158</v>
+        <v>444430</v>
       </c>
       <c r="R74" t="n">
-        <v>6787148</v>
+        <v>6787384</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8136,7 +8155,6 @@
       <c r="AE74" t="b">
         <v>0</v>
       </c>
-      <c r="AF74" t="inlineStr"/>
       <c r="AG74" t="b">
         <v>0</v>
       </c>
@@ -8155,10 +8173,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129795166</v>
+        <v>129795284</v>
       </c>
       <c r="B75" t="n">
-        <v>57733</v>
+        <v>79081</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8166,42 +8184,34 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
-      <c r="K75" t="inlineStr"/>
-      <c r="L75" t="inlineStr"/>
-      <c r="M75" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>444254</v>
+        <v>444363</v>
       </c>
       <c r="R75" t="n">
-        <v>6787333</v>
+        <v>6787411</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8260,53 +8270,45 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129795208</v>
+        <v>129795243</v>
       </c>
       <c r="B76" t="n">
-        <v>58106</v>
+        <v>79081</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>103015</v>
+        <v>6425</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
-      <c r="K76" t="inlineStr"/>
-      <c r="L76" t="inlineStr"/>
-      <c r="M76" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>444434</v>
+        <v>444159</v>
       </c>
       <c r="R76" t="n">
-        <v>6787357</v>
+        <v>6787297</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8365,10 +8367,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129795182</v>
+        <v>129795208</v>
       </c>
       <c r="B77" t="n">
-        <v>8450</v>
+        <v>58106</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8376,30 +8378,29 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>106545</v>
+        <v>103015</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
-      <c r="J77" t="inlineStr"/>
       <c r="K77" t="inlineStr"/>
       <c r="L77" t="inlineStr"/>
       <c r="M77" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N77" t="inlineStr"/>
@@ -8409,10 +8410,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>444417</v>
+        <v>444434</v>
       </c>
       <c r="R77" t="n">
-        <v>6787266</v>
+        <v>6787357</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8453,7 +8454,6 @@
       <c r="AE77" t="b">
         <v>0</v>
       </c>
-      <c r="AF77" t="inlineStr"/>
       <c r="AG77" t="b">
         <v>0</v>
       </c>
@@ -9694,10 +9694,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>129795305</v>
+        <v>129795152</v>
       </c>
       <c r="B90" t="n">
-        <v>79081</v>
+        <v>57733</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9705,34 +9705,42 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
+      <c r="K90" t="inlineStr"/>
+      <c r="L90" t="inlineStr"/>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>444169</v>
+        <v>444434</v>
       </c>
       <c r="R90" t="n">
-        <v>6787323</v>
+        <v>6787304</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9791,10 +9799,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>129795152</v>
+        <v>129795305</v>
       </c>
       <c r="B91" t="n">
-        <v>57733</v>
+        <v>79081</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9802,42 +9810,34 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
-      <c r="K91" t="inlineStr"/>
-      <c r="L91" t="inlineStr"/>
-      <c r="M91" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>444434</v>
+        <v>444169</v>
       </c>
       <c r="R91" t="n">
-        <v>6787304</v>
+        <v>6787323</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9896,10 +9896,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>129795288</v>
+        <v>129795121</v>
       </c>
       <c r="B92" t="n">
-        <v>79081</v>
+        <v>79700</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9907,21 +9907,21 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -9931,10 +9931,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>444420</v>
+        <v>444254</v>
       </c>
       <c r="R92" t="n">
-        <v>6787366</v>
+        <v>6787204</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9993,7 +9993,7 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>129795245</v>
+        <v>129795288</v>
       </c>
       <c r="B93" t="n">
         <v>79081</v>
@@ -10028,10 +10028,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>444113</v>
+        <v>444420</v>
       </c>
       <c r="R93" t="n">
-        <v>6787239</v>
+        <v>6787366</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10090,7 +10090,7 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>129795297</v>
+        <v>129795245</v>
       </c>
       <c r="B94" t="n">
         <v>79081</v>
@@ -10125,10 +10125,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>444297</v>
+        <v>444113</v>
       </c>
       <c r="R94" t="n">
-        <v>6787333</v>
+        <v>6787239</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10187,10 +10187,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>129795262</v>
+        <v>129795124</v>
       </c>
       <c r="B95" t="n">
-        <v>79081</v>
+        <v>79700</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10198,21 +10198,21 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10222,10 +10222,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>444219</v>
+        <v>444393</v>
       </c>
       <c r="R95" t="n">
-        <v>6787163</v>
+        <v>6787395</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10284,10 +10284,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>129795252</v>
+        <v>129795123</v>
       </c>
       <c r="B96" t="n">
-        <v>79081</v>
+        <v>79700</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10295,21 +10295,21 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10319,10 +10319,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>444249</v>
+        <v>444530</v>
       </c>
       <c r="R96" t="n">
-        <v>6787249</v>
+        <v>6787326</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10355,11 +10355,6 @@
       <c r="AA96" t="inlineStr">
         <is>
           <t>2025-11-22</t>
-        </is>
-      </c>
-      <c r="AC96" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 40m.</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10386,10 +10381,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>129795121</v>
+        <v>129795297</v>
       </c>
       <c r="B97" t="n">
-        <v>79700</v>
+        <v>79081</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10397,21 +10392,21 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -10421,10 +10416,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>444254</v>
+        <v>444297</v>
       </c>
       <c r="R97" t="n">
-        <v>6787204</v>
+        <v>6787333</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10483,10 +10478,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>129795124</v>
+        <v>129795262</v>
       </c>
       <c r="B98" t="n">
-        <v>79700</v>
+        <v>79081</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10494,21 +10489,21 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10518,10 +10513,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>444393</v>
+        <v>444219</v>
       </c>
       <c r="R98" t="n">
-        <v>6787395</v>
+        <v>6787163</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10580,10 +10575,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>129795123</v>
+        <v>129795252</v>
       </c>
       <c r="B99" t="n">
-        <v>79700</v>
+        <v>79081</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10591,21 +10586,21 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -10615,10 +10610,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>444530</v>
+        <v>444249</v>
       </c>
       <c r="R99" t="n">
-        <v>6787326</v>
+        <v>6787249</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10651,6 +10646,11 @@
       <c r="AA99" t="inlineStr">
         <is>
           <t>2025-11-22</t>
+        </is>
+      </c>
+      <c r="AC99" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 40m.</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -11386,7 +11386,7 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>129795186</v>
+        <v>129795178</v>
       </c>
       <c r="B107" t="n">
         <v>8450</v>
@@ -11430,10 +11430,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>444473</v>
+        <v>444375</v>
       </c>
       <c r="R107" t="n">
-        <v>6787334</v>
+        <v>6787207</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11493,7 +11493,7 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>129795196</v>
+        <v>129795186</v>
       </c>
       <c r="B108" t="n">
         <v>8450</v>
@@ -11537,10 +11537,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>444346</v>
+        <v>444473</v>
       </c>
       <c r="R108" t="n">
-        <v>6787369</v>
+        <v>6787334</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11600,7 +11600,7 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>129795178</v>
+        <v>129795196</v>
       </c>
       <c r="B109" t="n">
         <v>8450</v>
@@ -11644,10 +11644,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>444375</v>
+        <v>444346</v>
       </c>
       <c r="R109" t="n">
-        <v>6787207</v>
+        <v>6787369</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11707,41 +11707,40 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>129795201</v>
+        <v>129795149</v>
       </c>
       <c r="B110" t="n">
-        <v>8450</v>
+        <v>57733</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
-      <c r="J110" t="inlineStr"/>
       <c r="K110" t="inlineStr"/>
       <c r="L110" t="inlineStr"/>
       <c r="M110" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N110" t="inlineStr"/>
@@ -11751,10 +11750,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>444430</v>
+        <v>444223</v>
       </c>
       <c r="R110" t="n">
-        <v>6787332</v>
+        <v>6787221</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11795,7 +11794,6 @@
       <c r="AE110" t="b">
         <v>0</v>
       </c>
-      <c r="AF110" t="inlineStr"/>
       <c r="AG110" t="b">
         <v>0</v>
       </c>
@@ -11814,41 +11812,40 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>129795203</v>
+        <v>129795145</v>
       </c>
       <c r="B111" t="n">
-        <v>8450</v>
+        <v>57733</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
-      <c r="J111" t="inlineStr"/>
       <c r="K111" t="inlineStr"/>
       <c r="L111" t="inlineStr"/>
       <c r="M111" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N111" t="inlineStr"/>
@@ -11858,10 +11855,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>444401</v>
+        <v>444228</v>
       </c>
       <c r="R111" t="n">
-        <v>6787298</v>
+        <v>6787226</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -11902,7 +11899,6 @@
       <c r="AE111" t="b">
         <v>0</v>
       </c>
-      <c r="AF111" t="inlineStr"/>
       <c r="AG111" t="b">
         <v>0</v>
       </c>
@@ -11921,10 +11917,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>129795259</v>
+        <v>129795151</v>
       </c>
       <c r="B112" t="n">
-        <v>79081</v>
+        <v>57733</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -11932,34 +11928,42 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
+      <c r="K112" t="inlineStr"/>
+      <c r="L112" t="inlineStr"/>
+      <c r="M112" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N112" t="inlineStr"/>
       <c r="P112" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>444164</v>
+        <v>444425</v>
       </c>
       <c r="R112" t="n">
-        <v>6787121</v>
+        <v>6787278</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12018,40 +12022,41 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>129795149</v>
+        <v>129795203</v>
       </c>
       <c r="B113" t="n">
-        <v>57733</v>
+        <v>8450</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
+      <c r="J113" t="inlineStr"/>
       <c r="K113" t="inlineStr"/>
       <c r="L113" t="inlineStr"/>
       <c r="M113" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N113" t="inlineStr"/>
@@ -12061,10 +12066,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>444223</v>
+        <v>444401</v>
       </c>
       <c r="R113" t="n">
-        <v>6787221</v>
+        <v>6787298</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12105,6 +12110,7 @@
       <c r="AE113" t="b">
         <v>0</v>
       </c>
+      <c r="AF113" t="inlineStr"/>
       <c r="AG113" t="b">
         <v>0</v>
       </c>
@@ -12123,40 +12129,41 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>129795145</v>
+        <v>129795201</v>
       </c>
       <c r="B114" t="n">
-        <v>57733</v>
+        <v>8450</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
+      <c r="J114" t="inlineStr"/>
       <c r="K114" t="inlineStr"/>
       <c r="L114" t="inlineStr"/>
       <c r="M114" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N114" t="inlineStr"/>
@@ -12166,10 +12173,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>444228</v>
+        <v>444430</v>
       </c>
       <c r="R114" t="n">
-        <v>6787226</v>
+        <v>6787332</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12210,6 +12217,7 @@
       <c r="AE114" t="b">
         <v>0</v>
       </c>
+      <c r="AF114" t="inlineStr"/>
       <c r="AG114" t="b">
         <v>0</v>
       </c>
@@ -12228,10 +12236,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>129795151</v>
+        <v>129795259</v>
       </c>
       <c r="B115" t="n">
-        <v>57733</v>
+        <v>79081</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12239,42 +12247,34 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
-      <c r="K115" t="inlineStr"/>
-      <c r="L115" t="inlineStr"/>
-      <c r="M115" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N115" t="inlineStr"/>
       <c r="P115" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>444425</v>
+        <v>444164</v>
       </c>
       <c r="R115" t="n">
-        <v>6787278</v>
+        <v>6787121</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12333,10 +12333,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>129795289</v>
+        <v>129795164</v>
       </c>
       <c r="B116" t="n">
-        <v>79081</v>
+        <v>57733</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -12344,34 +12344,42 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
+      <c r="K116" t="inlineStr"/>
+      <c r="L116" t="inlineStr"/>
+      <c r="M116" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N116" t="inlineStr"/>
       <c r="P116" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>444435</v>
+        <v>444397</v>
       </c>
       <c r="R116" t="n">
-        <v>6787341</v>
+        <v>6787300</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12430,41 +12438,40 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>129795171</v>
+        <v>129795154</v>
       </c>
       <c r="B117" t="n">
-        <v>8450</v>
+        <v>57733</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
-      <c r="J117" t="inlineStr"/>
       <c r="K117" t="inlineStr"/>
       <c r="L117" t="inlineStr"/>
       <c r="M117" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N117" t="inlineStr"/>
@@ -12474,10 +12481,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>444185</v>
+        <v>444457</v>
       </c>
       <c r="R117" t="n">
-        <v>6787226</v>
+        <v>6787303</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12518,7 +12525,6 @@
       <c r="AE117" t="b">
         <v>0</v>
       </c>
-      <c r="AF117" t="inlineStr"/>
       <c r="AG117" t="b">
         <v>0</v>
       </c>
@@ -12537,7 +12543,7 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>129795164</v>
+        <v>129795157</v>
       </c>
       <c r="B118" t="n">
         <v>57733</v>
@@ -12580,10 +12586,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>444397</v>
+        <v>444525</v>
       </c>
       <c r="R118" t="n">
-        <v>6787300</v>
+        <v>6787344</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12642,10 +12648,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>129795154</v>
+        <v>129795289</v>
       </c>
       <c r="B119" t="n">
-        <v>57733</v>
+        <v>79081</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -12653,42 +12659,34 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
-      <c r="K119" t="inlineStr"/>
-      <c r="L119" t="inlineStr"/>
-      <c r="M119" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N119" t="inlineStr"/>
       <c r="P119" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>444457</v>
+        <v>444435</v>
       </c>
       <c r="R119" t="n">
-        <v>6787303</v>
+        <v>6787341</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -12747,32 +12745,32 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>129795157</v>
+        <v>129795132</v>
       </c>
       <c r="B120" t="n">
-        <v>57733</v>
+        <v>56926</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -12780,7 +12778,7 @@
       <c r="L120" t="inlineStr"/>
       <c r="M120" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="N120" t="inlineStr"/>
@@ -12790,10 +12788,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>444525</v>
+        <v>444315</v>
       </c>
       <c r="R120" t="n">
-        <v>6787344</v>
+        <v>6787291</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -12852,10 +12850,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>129795132</v>
+        <v>129795171</v>
       </c>
       <c r="B121" t="n">
-        <v>56926</v>
+        <v>8450</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -12863,29 +12861,30 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>100138</v>
+        <v>106545</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
+      <c r="J121" t="inlineStr"/>
       <c r="K121" t="inlineStr"/>
       <c r="L121" t="inlineStr"/>
       <c r="M121" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N121" t="inlineStr"/>
@@ -12895,10 +12894,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>444315</v>
+        <v>444185</v>
       </c>
       <c r="R121" t="n">
-        <v>6787291</v>
+        <v>6787226</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -12939,6 +12938,7 @@
       <c r="AE121" t="b">
         <v>0</v>
       </c>
+      <c r="AF121" t="inlineStr"/>
       <c r="AG121" t="b">
         <v>0</v>
       </c>
@@ -13171,10 +13171,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>129795294</v>
+        <v>129795144</v>
       </c>
       <c r="B124" t="n">
-        <v>79081</v>
+        <v>57733</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -13182,34 +13182,42 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
+      <c r="K124" t="inlineStr"/>
+      <c r="L124" t="inlineStr"/>
+      <c r="M124" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N124" t="inlineStr"/>
       <c r="P124" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>444323</v>
+        <v>444186</v>
       </c>
       <c r="R124" t="n">
-        <v>6787297</v>
+        <v>6787223</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13365,10 +13373,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>129795144</v>
+        <v>129795294</v>
       </c>
       <c r="B126" t="n">
-        <v>57733</v>
+        <v>79081</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -13376,42 +13384,34 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
-      <c r="K126" t="inlineStr"/>
-      <c r="L126" t="inlineStr"/>
-      <c r="M126" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N126" t="inlineStr"/>
       <c r="P126" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>444186</v>
+        <v>444323</v>
       </c>
       <c r="R126" t="n">
-        <v>6787223</v>
+        <v>6787297</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -13470,45 +13470,54 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>129795267</v>
+        <v>129795175</v>
       </c>
       <c r="B127" t="n">
-        <v>79081</v>
+        <v>8450</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
+      <c r="J127" t="inlineStr"/>
+      <c r="K127" t="inlineStr"/>
+      <c r="L127" t="inlineStr"/>
+      <c r="M127" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N127" t="inlineStr"/>
       <c r="P127" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>444353</v>
+        <v>444182</v>
       </c>
       <c r="R127" t="n">
-        <v>6787215</v>
+        <v>6787101</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -13543,17 +13552,13 @@
           <t>2025-11-22</t>
         </is>
       </c>
-      <c r="AC127" t="inlineStr">
-        <is>
-          <t>Gott om garnlav inom en radie av 40m.</t>
-        </is>
-      </c>
       <c r="AD127" t="b">
         <v>0</v>
       </c>
       <c r="AE127" t="b">
         <v>0</v>
       </c>
+      <c r="AF127" t="inlineStr"/>
       <c r="AG127" t="b">
         <v>0</v>
       </c>
@@ -13572,45 +13577,54 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>129795263</v>
+        <v>129795168</v>
       </c>
       <c r="B128" t="n">
-        <v>79081</v>
+        <v>8450</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
+      <c r="J128" t="inlineStr"/>
+      <c r="K128" t="inlineStr"/>
+      <c r="L128" t="inlineStr"/>
+      <c r="M128" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N128" t="inlineStr"/>
       <c r="P128" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>444241</v>
+        <v>444272</v>
       </c>
       <c r="R128" t="n">
-        <v>6787149</v>
+        <v>6787286</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -13651,6 +13665,7 @@
       <c r="AE128" t="b">
         <v>0</v>
       </c>
+      <c r="AF128" t="inlineStr"/>
       <c r="AG128" t="b">
         <v>0</v>
       </c>
@@ -13669,10 +13684,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>129795159</v>
+        <v>129795137</v>
       </c>
       <c r="B129" t="n">
-        <v>57733</v>
+        <v>91614</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -13680,31 +13695,26 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>100049</v>
+        <v>5442</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
+      <c r="J129" t="inlineStr"/>
       <c r="K129" t="inlineStr"/>
-      <c r="L129" t="inlineStr"/>
-      <c r="M129" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N129" t="inlineStr"/>
       <c r="P129" t="inlineStr">
         <is>
@@ -13712,10 +13722,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>444436</v>
+        <v>444203</v>
       </c>
       <c r="R129" t="n">
-        <v>6787463</v>
+        <v>6787221</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -13756,6 +13766,7 @@
       <c r="AE129" t="b">
         <v>0</v>
       </c>
+      <c r="AF129" t="inlineStr"/>
       <c r="AG129" t="b">
         <v>0</v>
       </c>
@@ -13774,10 +13785,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>129795258</v>
+        <v>129795159</v>
       </c>
       <c r="B130" t="n">
-        <v>79081</v>
+        <v>57733</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -13785,34 +13796,42 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
+      <c r="K130" t="inlineStr"/>
+      <c r="L130" t="inlineStr"/>
+      <c r="M130" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N130" t="inlineStr"/>
       <c r="P130" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>444174</v>
+        <v>444436</v>
       </c>
       <c r="R130" t="n">
-        <v>6787136</v>
+        <v>6787463</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -13871,7 +13890,7 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>129795275</v>
+        <v>129795258</v>
       </c>
       <c r="B131" t="n">
         <v>79081</v>
@@ -13906,10 +13925,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>444495</v>
+        <v>444174</v>
       </c>
       <c r="R131" t="n">
-        <v>6787340</v>
+        <v>6787136</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -13968,10 +13987,10 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>129795137</v>
+        <v>129795275</v>
       </c>
       <c r="B132" t="n">
-        <v>91614</v>
+        <v>79081</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -13979,37 +13998,34 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
-      <c r="J132" t="inlineStr"/>
-      <c r="K132" t="inlineStr"/>
-      <c r="N132" t="inlineStr"/>
       <c r="P132" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>444203</v>
+        <v>444495</v>
       </c>
       <c r="R132" t="n">
-        <v>6787221</v>
+        <v>6787340</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -14050,7 +14066,6 @@
       <c r="AE132" t="b">
         <v>0</v>
       </c>
-      <c r="AF132" t="inlineStr"/>
       <c r="AG132" t="b">
         <v>0</v>
       </c>
@@ -14069,54 +14084,45 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>129795175</v>
+        <v>129795267</v>
       </c>
       <c r="B133" t="n">
-        <v>8450</v>
+        <v>79081</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
-      <c r="J133" t="inlineStr"/>
-      <c r="K133" t="inlineStr"/>
-      <c r="L133" t="inlineStr"/>
-      <c r="M133" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N133" t="inlineStr"/>
       <c r="P133" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>444182</v>
+        <v>444353</v>
       </c>
       <c r="R133" t="n">
-        <v>6787101</v>
+        <v>6787215</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -14151,13 +14157,17 @@
           <t>2025-11-22</t>
         </is>
       </c>
+      <c r="AC133" t="inlineStr">
+        <is>
+          <t>Gott om garnlav inom en radie av 40m.</t>
+        </is>
+      </c>
       <c r="AD133" t="b">
         <v>0</v>
       </c>
       <c r="AE133" t="b">
         <v>0</v>
       </c>
-      <c r="AF133" t="inlineStr"/>
       <c r="AG133" t="b">
         <v>0</v>
       </c>
@@ -14176,54 +14186,45 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>129795168</v>
+        <v>129795263</v>
       </c>
       <c r="B134" t="n">
-        <v>8450</v>
+        <v>79081</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
-      <c r="J134" t="inlineStr"/>
-      <c r="K134" t="inlineStr"/>
-      <c r="L134" t="inlineStr"/>
-      <c r="M134" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N134" t="inlineStr"/>
       <c r="P134" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>444272</v>
+        <v>444241</v>
       </c>
       <c r="R134" t="n">
-        <v>6787286</v>
+        <v>6787149</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -14264,7 +14265,6 @@
       <c r="AE134" t="b">
         <v>0</v>
       </c>
-      <c r="AF134" t="inlineStr"/>
       <c r="AG134" t="b">
         <v>0</v>
       </c>
@@ -14283,10 +14283,10 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>129795274</v>
+        <v>129795139</v>
       </c>
       <c r="B135" t="n">
-        <v>79081</v>
+        <v>91614</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -14294,34 +14294,37 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
+      <c r="J135" t="inlineStr"/>
+      <c r="K135" t="inlineStr"/>
+      <c r="N135" t="inlineStr"/>
       <c r="P135" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>444538</v>
+        <v>444342</v>
       </c>
       <c r="R135" t="n">
-        <v>6787325</v>
+        <v>6787240</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -14362,6 +14365,7 @@
       <c r="AE135" t="b">
         <v>0</v>
       </c>
+      <c r="AF135" t="inlineStr"/>
       <c r="AG135" t="b">
         <v>0</v>
       </c>
@@ -14380,7 +14384,7 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>129795304</v>
+        <v>129795274</v>
       </c>
       <c r="B136" t="n">
         <v>79081</v>
@@ -14415,10 +14419,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>444172</v>
+        <v>444538</v>
       </c>
       <c r="R136" t="n">
-        <v>6787339</v>
+        <v>6787325</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -14477,7 +14481,7 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>129795254</v>
+        <v>129795304</v>
       </c>
       <c r="B137" t="n">
         <v>79081</v>
@@ -14506,19 +14510,16 @@
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
-      <c r="J137" t="inlineStr"/>
-      <c r="K137" t="inlineStr"/>
-      <c r="N137" t="inlineStr"/>
       <c r="P137" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>444199</v>
+        <v>444172</v>
       </c>
       <c r="R137" t="n">
-        <v>6787221</v>
+        <v>6787339</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -14559,7 +14560,6 @@
       <c r="AE137" t="b">
         <v>0</v>
       </c>
-      <c r="AF137" t="inlineStr"/>
       <c r="AG137" t="b">
         <v>0</v>
       </c>
@@ -14578,7 +14578,7 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>129795302</v>
+        <v>129795254</v>
       </c>
       <c r="B138" t="n">
         <v>79081</v>
@@ -14607,16 +14607,19 @@
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
+      <c r="J138" t="inlineStr"/>
+      <c r="K138" t="inlineStr"/>
+      <c r="N138" t="inlineStr"/>
       <c r="P138" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>444222</v>
+        <v>444199</v>
       </c>
       <c r="R138" t="n">
-        <v>6787345</v>
+        <v>6787221</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -14657,6 +14660,7 @@
       <c r="AE138" t="b">
         <v>0</v>
       </c>
+      <c r="AF138" t="inlineStr"/>
       <c r="AG138" t="b">
         <v>0</v>
       </c>
@@ -14675,7 +14679,7 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>129795251</v>
+        <v>129795302</v>
       </c>
       <c r="B139" t="n">
         <v>79081</v>
@@ -14704,19 +14708,16 @@
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
-      <c r="J139" t="inlineStr"/>
-      <c r="K139" t="inlineStr"/>
-      <c r="N139" t="inlineStr"/>
       <c r="P139" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>444309</v>
+        <v>444222</v>
       </c>
       <c r="R139" t="n">
-        <v>6787272</v>
+        <v>6787345</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -14757,7 +14758,6 @@
       <c r="AE139" t="b">
         <v>0</v>
       </c>
-      <c r="AF139" t="inlineStr"/>
       <c r="AG139" t="b">
         <v>0</v>
       </c>
@@ -14776,7 +14776,7 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>129795247</v>
+        <v>129795251</v>
       </c>
       <c r="B140" t="n">
         <v>79081</v>
@@ -14805,16 +14805,19 @@
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
+      <c r="J140" t="inlineStr"/>
+      <c r="K140" t="inlineStr"/>
+      <c r="N140" t="inlineStr"/>
       <c r="P140" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>444225</v>
+        <v>444309</v>
       </c>
       <c r="R140" t="n">
-        <v>6787275</v>
+        <v>6787272</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -14855,6 +14858,7 @@
       <c r="AE140" t="b">
         <v>0</v>
       </c>
+      <c r="AF140" t="inlineStr"/>
       <c r="AG140" t="b">
         <v>0</v>
       </c>
@@ -14873,54 +14877,45 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>129795204</v>
+        <v>129795266</v>
       </c>
       <c r="B141" t="n">
-        <v>8450</v>
+        <v>79081</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E141" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
-      <c r="J141" t="inlineStr"/>
-      <c r="K141" t="inlineStr"/>
-      <c r="L141" t="inlineStr"/>
-      <c r="M141" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N141" t="inlineStr"/>
       <c r="P141" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>444380</v>
+        <v>444314</v>
       </c>
       <c r="R141" t="n">
-        <v>6787306</v>
+        <v>6787212</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -14955,13 +14950,17 @@
           <t>2025-11-22</t>
         </is>
       </c>
+      <c r="AC141" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 40m</t>
+        </is>
+      </c>
       <c r="AD141" t="b">
         <v>0</v>
       </c>
       <c r="AE141" t="b">
         <v>0</v>
       </c>
-      <c r="AF141" t="inlineStr"/>
       <c r="AG141" t="b">
         <v>0</v>
       </c>
@@ -14980,7 +14979,7 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>129795266</v>
+        <v>129795247</v>
       </c>
       <c r="B142" t="n">
         <v>79081</v>
@@ -15015,10 +15014,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>444314</v>
+        <v>444225</v>
       </c>
       <c r="R142" t="n">
-        <v>6787212</v>
+        <v>6787275</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -15051,11 +15050,6 @@
       <c r="AA142" t="inlineStr">
         <is>
           <t>2025-11-22</t>
-        </is>
-      </c>
-      <c r="AC142" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 40m</t>
         </is>
       </c>
       <c r="AD142" t="b">
@@ -15082,37 +15076,43 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>129795139</v>
+        <v>129795204</v>
       </c>
       <c r="B143" t="n">
-        <v>91614</v>
+        <v>8450</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E143" t="n">
-        <v>5442</v>
+        <v>106545</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
       <c r="J143" t="inlineStr"/>
       <c r="K143" t="inlineStr"/>
+      <c r="L143" t="inlineStr"/>
+      <c r="M143" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N143" t="inlineStr"/>
       <c r="P143" t="inlineStr">
         <is>
@@ -15120,10 +15120,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>444342</v>
+        <v>444380</v>
       </c>
       <c r="R143" t="n">
-        <v>6787240</v>
+        <v>6787306</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>

--- a/artfynd/A 51041-2025 artfynd.xlsx
+++ b/artfynd/A 51041-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129795244</v>
+        <v>129795283</v>
       </c>
       <c r="B2" t="n">
         <v>79081</v>
@@ -704,16 +704,19 @@
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>444105</v>
+        <v>444337</v>
       </c>
       <c r="R2" t="n">
-        <v>6787246</v>
+        <v>6787374</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -754,6 +757,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -869,54 +873,45 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129795169</v>
+        <v>129795253</v>
       </c>
       <c r="B4" t="n">
-        <v>8450</v>
+        <v>79081</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>444272</v>
+        <v>444185</v>
       </c>
       <c r="R4" t="n">
-        <v>6787239</v>
+        <v>6787247</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -951,13 +946,17 @@
           <t>2025-11-22</t>
         </is>
       </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Gott om garnlav inom en radie av 50 m.</t>
+        </is>
+      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -976,54 +975,45 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129795190</v>
+        <v>129795285</v>
       </c>
       <c r="B5" t="n">
-        <v>8450</v>
+        <v>79081</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>444510</v>
+        <v>444405</v>
       </c>
       <c r="R5" t="n">
-        <v>6787276</v>
+        <v>6787405</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1064,7 +1054,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1083,54 +1072,45 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129795197</v>
+        <v>129795244</v>
       </c>
       <c r="B6" t="n">
-        <v>8450</v>
+        <v>79081</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>444406</v>
+        <v>444105</v>
       </c>
       <c r="R6" t="n">
-        <v>6787392</v>
+        <v>6787246</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1171,7 +1151,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1190,7 +1169,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129795253</v>
+        <v>129795291</v>
       </c>
       <c r="B7" t="n">
         <v>79081</v>
@@ -1225,10 +1204,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>444185</v>
+        <v>444412</v>
       </c>
       <c r="R7" t="n">
-        <v>6787247</v>
+        <v>6787307</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1261,11 +1240,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-11-22</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Gott om garnlav inom en radie av 50 m.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1292,7 +1266,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129795291</v>
+        <v>129795298</v>
       </c>
       <c r="B8" t="n">
         <v>79081</v>
@@ -1327,10 +1301,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>444412</v>
+        <v>444305</v>
       </c>
       <c r="R8" t="n">
-        <v>6787307</v>
+        <v>6787353</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1389,45 +1363,54 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129795298</v>
+        <v>129795169</v>
       </c>
       <c r="B9" t="n">
-        <v>79081</v>
+        <v>8450</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>444305</v>
+        <v>444272</v>
       </c>
       <c r="R9" t="n">
-        <v>6787353</v>
+        <v>6787239</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1468,6 +1451,7 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1486,45 +1470,54 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129795285</v>
+        <v>129795190</v>
       </c>
       <c r="B10" t="n">
-        <v>79081</v>
+        <v>8450</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>444405</v>
+        <v>444510</v>
       </c>
       <c r="R10" t="n">
-        <v>6787405</v>
+        <v>6787276</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1565,6 +1558,7 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1583,37 +1577,43 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129795283</v>
+        <v>129795197</v>
       </c>
       <c r="B11" t="n">
-        <v>79081</v>
+        <v>8450</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1621,10 +1621,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>444337</v>
+        <v>444406</v>
       </c>
       <c r="R11" t="n">
-        <v>6787374</v>
+        <v>6787392</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1684,7 +1684,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129795155</v>
+        <v>129795163</v>
       </c>
       <c r="B12" t="n">
         <v>57733</v>
@@ -1727,10 +1727,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>444498</v>
+        <v>444415</v>
       </c>
       <c r="R12" t="n">
-        <v>6787306</v>
+        <v>6787316</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1789,10 +1789,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129795163</v>
+        <v>129795276</v>
       </c>
       <c r="B13" t="n">
-        <v>57733</v>
+        <v>79081</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1800,31 +1800,26 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1832,10 +1827,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>444415</v>
+        <v>444499</v>
       </c>
       <c r="R13" t="n">
-        <v>6787316</v>
+        <v>6787367</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1870,12 +1865,18 @@
           <t>2025-11-22</t>
         </is>
       </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 50m.</t>
+        </is>
+      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -1894,10 +1895,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129795153</v>
+        <v>129795271</v>
       </c>
       <c r="B14" t="n">
-        <v>57733</v>
+        <v>79081</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1905,31 +1906,26 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -1937,10 +1933,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>444452</v>
+        <v>444466</v>
       </c>
       <c r="R14" t="n">
-        <v>6787294</v>
+        <v>6787306</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1975,12 +1971,18 @@
           <t>2025-11-22</t>
         </is>
       </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 50m.</t>
+        </is>
+      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2100,7 +2102,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129795271</v>
+        <v>129795299</v>
       </c>
       <c r="B16" t="n">
         <v>79081</v>
@@ -2129,19 +2131,16 @@
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>444466</v>
+        <v>444265</v>
       </c>
       <c r="R16" t="n">
-        <v>6787306</v>
+        <v>6787372</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2176,18 +2175,12 @@
           <t>2025-11-22</t>
         </is>
       </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 50m.</t>
-        </is>
-      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2206,10 +2199,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129795276</v>
+        <v>129795155</v>
       </c>
       <c r="B17" t="n">
-        <v>79081</v>
+        <v>57733</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2217,26 +2210,31 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2244,10 +2242,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>444499</v>
+        <v>444498</v>
       </c>
       <c r="R17" t="n">
-        <v>6787367</v>
+        <v>6787306</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2282,18 +2280,12 @@
           <t>2025-11-22</t>
         </is>
       </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 50m.</t>
-        </is>
-      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2312,10 +2304,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129795299</v>
+        <v>129795153</v>
       </c>
       <c r="B18" t="n">
-        <v>79081</v>
+        <v>57733</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2323,34 +2315,42 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>444265</v>
+        <v>444452</v>
       </c>
       <c r="R18" t="n">
-        <v>6787372</v>
+        <v>6787294</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2623,54 +2623,45 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129795198</v>
+        <v>129795265</v>
       </c>
       <c r="B21" t="n">
-        <v>8450</v>
+        <v>79081</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>444434</v>
+        <v>444278</v>
       </c>
       <c r="R21" t="n">
-        <v>6787384</v>
+        <v>6787163</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2711,7 +2702,6 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -2730,54 +2720,45 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129795207</v>
+        <v>129795278</v>
       </c>
       <c r="B22" t="n">
-        <v>8450</v>
+        <v>79081</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>444221</v>
+        <v>444465</v>
       </c>
       <c r="R22" t="n">
-        <v>6787340</v>
+        <v>6787451</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2818,7 +2799,6 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -2837,43 +2817,37 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129795200</v>
+        <v>129795310</v>
       </c>
       <c r="B23" t="n">
-        <v>8450</v>
+        <v>79081</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -2881,10 +2855,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>444429</v>
+        <v>444488</v>
       </c>
       <c r="R23" t="n">
-        <v>6787341</v>
+        <v>6787445</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2917,6 +2891,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-11-22</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Gott om garnlav inom en radie av 40m</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2944,54 +2923,45 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129795206</v>
+        <v>129795273</v>
       </c>
       <c r="B24" t="n">
-        <v>8450</v>
+        <v>79081</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>444247</v>
+        <v>444548</v>
       </c>
       <c r="R24" t="n">
-        <v>6787328</v>
+        <v>6787330</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3032,7 +3002,6 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3051,45 +3020,54 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129795273</v>
+        <v>129795198</v>
       </c>
       <c r="B25" t="n">
-        <v>79081</v>
+        <v>8450</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>444548</v>
+        <v>444434</v>
       </c>
       <c r="R25" t="n">
-        <v>6787330</v>
+        <v>6787384</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3130,6 +3108,7 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3148,45 +3127,54 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129795265</v>
+        <v>129795207</v>
       </c>
       <c r="B26" t="n">
-        <v>79081</v>
+        <v>8450</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>444278</v>
+        <v>444221</v>
       </c>
       <c r="R26" t="n">
-        <v>6787163</v>
+        <v>6787340</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3227,6 +3215,7 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3245,37 +3234,43 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129795310</v>
+        <v>129795200</v>
       </c>
       <c r="B27" t="n">
-        <v>79081</v>
+        <v>8450</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -3283,10 +3278,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>444488</v>
+        <v>444429</v>
       </c>
       <c r="R27" t="n">
-        <v>6787445</v>
+        <v>6787341</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3319,11 +3314,6 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-11-22</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Gott om garnlav inom en radie av 40m</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3351,45 +3341,54 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129795278</v>
+        <v>129795206</v>
       </c>
       <c r="B28" t="n">
-        <v>79081</v>
+        <v>8450</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>444465</v>
+        <v>444247</v>
       </c>
       <c r="R28" t="n">
-        <v>6787451</v>
+        <v>6787328</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3430,6 +3429,7 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
+      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -3448,41 +3448,40 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129795187</v>
+        <v>129795142</v>
       </c>
       <c r="B29" t="n">
-        <v>8450</v>
+        <v>57733</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr"/>
       <c r="M29" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N29" t="inlineStr"/>
@@ -3492,10 +3491,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>444487</v>
+        <v>444276</v>
       </c>
       <c r="R29" t="n">
-        <v>6787321</v>
+        <v>6787287</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3536,7 +3535,6 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -3555,54 +3553,45 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129795189</v>
+        <v>129795268</v>
       </c>
       <c r="B30" t="n">
-        <v>8450</v>
+        <v>79081</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>444500</v>
+        <v>444383</v>
       </c>
       <c r="R30" t="n">
-        <v>6787274</v>
+        <v>6787218</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3643,7 +3632,6 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
-      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -3662,54 +3650,45 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129795176</v>
+        <v>129795256</v>
       </c>
       <c r="B31" t="n">
-        <v>8450</v>
+        <v>79081</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>444215</v>
+        <v>444226</v>
       </c>
       <c r="R31" t="n">
-        <v>6787151</v>
+        <v>6787196</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3750,7 +3729,6 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
-      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
@@ -3769,40 +3747,41 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129795142</v>
+        <v>129795187</v>
       </c>
       <c r="B32" t="n">
-        <v>57733</v>
+        <v>8450</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr"/>
       <c r="M32" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N32" t="inlineStr"/>
@@ -3812,10 +3791,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>444276</v>
+        <v>444487</v>
       </c>
       <c r="R32" t="n">
-        <v>6787287</v>
+        <v>6787321</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3856,6 +3835,7 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
+      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
@@ -3874,45 +3854,54 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129795268</v>
+        <v>129795189</v>
       </c>
       <c r="B33" t="n">
-        <v>79081</v>
+        <v>8450</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>444383</v>
+        <v>444500</v>
       </c>
       <c r="R33" t="n">
-        <v>6787218</v>
+        <v>6787274</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3953,6 +3942,7 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
+      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -3971,45 +3961,54 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129795256</v>
+        <v>129795176</v>
       </c>
       <c r="B34" t="n">
-        <v>79081</v>
+        <v>8450</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>444226</v>
+        <v>444215</v>
       </c>
       <c r="R34" t="n">
-        <v>6787196</v>
+        <v>6787151</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4050,6 +4049,7 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
+      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
@@ -4173,7 +4173,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129795270</v>
+        <v>129795269</v>
       </c>
       <c r="B36" t="n">
         <v>79081</v>
@@ -4208,10 +4208,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>444416</v>
+        <v>444429</v>
       </c>
       <c r="R36" t="n">
-        <v>6787260</v>
+        <v>6787240</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4270,7 +4270,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129795296</v>
+        <v>129795249</v>
       </c>
       <c r="B37" t="n">
         <v>79081</v>
@@ -4299,19 +4299,16 @@
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
-      <c r="K37" t="inlineStr"/>
-      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>444299</v>
+        <v>444267</v>
       </c>
       <c r="R37" t="n">
-        <v>6787304</v>
+        <v>6787295</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4346,18 +4343,12 @@
           <t>2025-11-22</t>
         </is>
       </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 50 m.</t>
-        </is>
-      </c>
       <c r="AD37" t="b">
         <v>0</v>
       </c>
       <c r="AE37" t="b">
         <v>0</v>
       </c>
-      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -4376,7 +4367,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129795269</v>
+        <v>129795296</v>
       </c>
       <c r="B38" t="n">
         <v>79081</v>
@@ -4405,16 +4396,19 @@
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>444429</v>
+        <v>444299</v>
       </c>
       <c r="R38" t="n">
-        <v>6787240</v>
+        <v>6787304</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4449,12 +4443,18 @@
           <t>2025-11-22</t>
         </is>
       </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 50 m.</t>
+        </is>
+      </c>
       <c r="AD38" t="b">
         <v>0</v>
       </c>
       <c r="AE38" t="b">
         <v>0</v>
       </c>
+      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -4473,7 +4473,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129795249</v>
+        <v>129795270</v>
       </c>
       <c r="B39" t="n">
         <v>79081</v>
@@ -4508,10 +4508,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>444267</v>
+        <v>444416</v>
       </c>
       <c r="R39" t="n">
-        <v>6787295</v>
+        <v>6787260</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4889,10 +4889,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129795136</v>
+        <v>129795158</v>
       </c>
       <c r="B43" t="n">
-        <v>91614</v>
+        <v>57733</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4900,26 +4900,31 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>5442</v>
+        <v>100049</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="J43" t="inlineStr"/>
       <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
@@ -4927,10 +4932,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>444235</v>
+        <v>444501</v>
       </c>
       <c r="R43" t="n">
-        <v>6787149</v>
+        <v>6787402</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4971,7 +4976,6 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
-      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
@@ -4990,54 +4994,45 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129795170</v>
+        <v>129795293</v>
       </c>
       <c r="B44" t="n">
-        <v>8450</v>
+        <v>79081</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="J44" t="inlineStr"/>
-      <c r="K44" t="inlineStr"/>
-      <c r="L44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>444172</v>
+        <v>444365</v>
       </c>
       <c r="R44" t="n">
-        <v>6787202</v>
+        <v>6787285</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5072,13 +5067,17 @@
           <t>2025-11-22</t>
         </is>
       </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 50m.</t>
+        </is>
+      </c>
       <c r="AD44" t="b">
         <v>0</v>
       </c>
       <c r="AE44" t="b">
         <v>0</v>
       </c>
-      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
@@ -5097,10 +5096,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129795158</v>
+        <v>129795282</v>
       </c>
       <c r="B45" t="n">
-        <v>57733</v>
+        <v>79081</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5108,31 +5107,26 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="J45" t="inlineStr"/>
       <c r="K45" t="inlineStr"/>
-      <c r="L45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
@@ -5140,10 +5134,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>444501</v>
+        <v>444374</v>
       </c>
       <c r="R45" t="n">
-        <v>6787402</v>
+        <v>6787384</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5178,12 +5172,18 @@
           <t>2025-11-22</t>
         </is>
       </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 50 m.</t>
+        </is>
+      </c>
       <c r="AD45" t="b">
         <v>0</v>
       </c>
       <c r="AE45" t="b">
         <v>0</v>
       </c>
+      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
@@ -5202,37 +5202,43 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129795282</v>
+        <v>129795170</v>
       </c>
       <c r="B46" t="n">
-        <v>79081</v>
+        <v>8450</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="J46" t="inlineStr"/>
       <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
@@ -5240,10 +5246,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>444374</v>
+        <v>444172</v>
       </c>
       <c r="R46" t="n">
-        <v>6787384</v>
+        <v>6787202</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5276,11 +5282,6 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-11-22</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 50 m.</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5308,10 +5309,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129795293</v>
+        <v>129795136</v>
       </c>
       <c r="B47" t="n">
-        <v>79081</v>
+        <v>91618</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5319,34 +5320,37 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr"/>
+      <c r="K47" t="inlineStr"/>
+      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>444365</v>
+        <v>444235</v>
       </c>
       <c r="R47" t="n">
-        <v>6787285</v>
+        <v>6787149</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5381,17 +5385,13 @@
           <t>2025-11-22</t>
         </is>
       </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 50m.</t>
-        </is>
-      </c>
       <c r="AD47" t="b">
         <v>0</v>
       </c>
       <c r="AE47" t="b">
         <v>0</v>
       </c>
+      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
@@ -5413,7 +5413,7 @@
         <v>129795138</v>
       </c>
       <c r="B48" t="n">
-        <v>91614</v>
+        <v>91618</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5511,7 +5511,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129795309</v>
+        <v>129795246</v>
       </c>
       <c r="B49" t="n">
         <v>79081</v>
@@ -5546,10 +5546,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>444095</v>
+        <v>444145</v>
       </c>
       <c r="R49" t="n">
-        <v>6787293</v>
+        <v>6787239</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5586,7 +5586,7 @@
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>8.32</t>
+          <t>Rikligt med garnlav inom en radie av 40m.</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5710,7 +5710,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129795250</v>
+        <v>129795309</v>
       </c>
       <c r="B51" t="n">
         <v>79081</v>
@@ -5745,10 +5745,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>444295</v>
+        <v>444095</v>
       </c>
       <c r="R51" t="n">
-        <v>6787287</v>
+        <v>6787293</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5781,6 +5781,11 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-11-22</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>8.32</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5807,7 +5812,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129795246</v>
+        <v>129795250</v>
       </c>
       <c r="B52" t="n">
         <v>79081</v>
@@ -5842,10 +5847,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>444145</v>
+        <v>444295</v>
       </c>
       <c r="R52" t="n">
-        <v>6787239</v>
+        <v>6787287</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5878,11 +5883,6 @@
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-11-22</t>
-        </is>
-      </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 40m.</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -5909,10 +5909,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129795277</v>
+        <v>129795147</v>
       </c>
       <c r="B53" t="n">
-        <v>79081</v>
+        <v>57733</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5920,34 +5920,42 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
+      <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>444491</v>
+        <v>444220</v>
       </c>
       <c r="R53" t="n">
-        <v>6787412</v>
+        <v>6787221</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6006,45 +6014,53 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129795279</v>
+        <v>129795131</v>
       </c>
       <c r="B54" t="n">
-        <v>79081</v>
+        <v>56926</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
+      <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr"/>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>444463</v>
+        <v>444250</v>
       </c>
       <c r="R54" t="n">
-        <v>6787459</v>
+        <v>6787212</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6103,32 +6119,32 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129795131</v>
+        <v>129795161</v>
       </c>
       <c r="B55" t="n">
-        <v>56926</v>
+        <v>57733</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6136,7 +6152,7 @@
       <c r="L55" t="inlineStr"/>
       <c r="M55" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N55" t="inlineStr"/>
@@ -6146,10 +6162,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>444250</v>
+        <v>444433</v>
       </c>
       <c r="R55" t="n">
-        <v>6787212</v>
+        <v>6787338</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6208,10 +6224,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129795134</v>
+        <v>129795279</v>
       </c>
       <c r="B56" t="n">
-        <v>57896</v>
+        <v>79081</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6219,42 +6235,34 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
-      <c r="K56" t="inlineStr"/>
-      <c r="L56" t="inlineStr"/>
-      <c r="M56" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>444289</v>
+        <v>444463</v>
       </c>
       <c r="R56" t="n">
-        <v>6787357</v>
+        <v>6787459</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6313,54 +6321,45 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129795172</v>
+        <v>129795277</v>
       </c>
       <c r="B57" t="n">
-        <v>8450</v>
+        <v>79081</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
-      <c r="J57" t="inlineStr"/>
-      <c r="K57" t="inlineStr"/>
-      <c r="L57" t="inlineStr"/>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>444225</v>
+        <v>444491</v>
       </c>
       <c r="R57" t="n">
-        <v>6787223</v>
+        <v>6787412</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6401,7 +6400,6 @@
       <c r="AE57" t="b">
         <v>0</v>
       </c>
-      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
@@ -6420,7 +6418,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129795199</v>
+        <v>129795184</v>
       </c>
       <c r="B58" t="n">
         <v>8450</v>
@@ -6464,10 +6462,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>444431</v>
+        <v>444452</v>
       </c>
       <c r="R58" t="n">
-        <v>6787350</v>
+        <v>6787305</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6527,40 +6525,41 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129795161</v>
+        <v>129795172</v>
       </c>
       <c r="B59" t="n">
-        <v>57733</v>
+        <v>8450</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
+      <c r="J59" t="inlineStr"/>
       <c r="K59" t="inlineStr"/>
       <c r="L59" t="inlineStr"/>
       <c r="M59" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N59" t="inlineStr"/>
@@ -6570,10 +6569,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>444433</v>
+        <v>444225</v>
       </c>
       <c r="R59" t="n">
-        <v>6787338</v>
+        <v>6787223</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6614,6 +6613,7 @@
       <c r="AE59" t="b">
         <v>0</v>
       </c>
+      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
       </c>
@@ -6632,40 +6632,41 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129795147</v>
+        <v>129795199</v>
       </c>
       <c r="B60" t="n">
-        <v>57733</v>
+        <v>8450</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
+      <c r="J60" t="inlineStr"/>
       <c r="K60" t="inlineStr"/>
       <c r="L60" t="inlineStr"/>
       <c r="M60" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N60" t="inlineStr"/>
@@ -6675,10 +6676,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>444220</v>
+        <v>444431</v>
       </c>
       <c r="R60" t="n">
-        <v>6787221</v>
+        <v>6787350</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6719,6 +6720,7 @@
       <c r="AE60" t="b">
         <v>0</v>
       </c>
+      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
       </c>
@@ -6737,41 +6739,40 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129795184</v>
+        <v>129795134</v>
       </c>
       <c r="B61" t="n">
-        <v>8450</v>
+        <v>57896</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>106545</v>
+        <v>103021</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
-      <c r="J61" t="inlineStr"/>
       <c r="K61" t="inlineStr"/>
       <c r="L61" t="inlineStr"/>
       <c r="M61" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N61" t="inlineStr"/>
@@ -6781,10 +6782,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>444452</v>
+        <v>444289</v>
       </c>
       <c r="R61" t="n">
-        <v>6787305</v>
+        <v>6787357</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6825,7 +6826,6 @@
       <c r="AE61" t="b">
         <v>0</v>
       </c>
-      <c r="AF61" t="inlineStr"/>
       <c r="AG61" t="b">
         <v>0</v>
       </c>
@@ -7676,37 +7676,42 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129795135</v>
+        <v>129795208</v>
       </c>
       <c r="B70" t="n">
-        <v>91614</v>
+        <v>58106</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>5442</v>
+        <v>103015</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
-      <c r="J70" t="inlineStr"/>
       <c r="K70" t="inlineStr"/>
+      <c r="L70" t="inlineStr"/>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
@@ -7714,10 +7719,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>444158</v>
+        <v>444434</v>
       </c>
       <c r="R70" t="n">
-        <v>6787148</v>
+        <v>6787357</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7758,7 +7763,6 @@
       <c r="AE70" t="b">
         <v>0</v>
       </c>
-      <c r="AF70" t="inlineStr"/>
       <c r="AG70" t="b">
         <v>0</v>
       </c>
@@ -7777,10 +7781,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129795166</v>
+        <v>129795135</v>
       </c>
       <c r="B71" t="n">
-        <v>57733</v>
+        <v>91618</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7788,31 +7792,26 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>100049</v>
+        <v>5442</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
+      <c r="J71" t="inlineStr"/>
       <c r="K71" t="inlineStr"/>
-      <c r="L71" t="inlineStr"/>
-      <c r="M71" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
@@ -7820,10 +7819,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>444254</v>
+        <v>444158</v>
       </c>
       <c r="R71" t="n">
-        <v>6787333</v>
+        <v>6787148</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7864,6 +7863,7 @@
       <c r="AE71" t="b">
         <v>0</v>
       </c>
+      <c r="AF71" t="inlineStr"/>
       <c r="AG71" t="b">
         <v>0</v>
       </c>
@@ -7882,10 +7882,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129795280</v>
+        <v>129795166</v>
       </c>
       <c r="B72" t="n">
-        <v>79081</v>
+        <v>57733</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7893,34 +7893,42 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
+      <c r="K72" t="inlineStr"/>
+      <c r="L72" t="inlineStr"/>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>444451</v>
+        <v>444254</v>
       </c>
       <c r="R72" t="n">
-        <v>6787467</v>
+        <v>6787333</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7979,7 +7987,7 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129795272</v>
+        <v>129795243</v>
       </c>
       <c r="B73" t="n">
         <v>79081</v>
@@ -8014,10 +8022,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>444553</v>
+        <v>444159</v>
       </c>
       <c r="R73" t="n">
-        <v>6787299</v>
+        <v>6787297</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8173,7 +8181,7 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129795284</v>
+        <v>129795272</v>
       </c>
       <c r="B75" t="n">
         <v>79081</v>
@@ -8208,10 +8216,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>444363</v>
+        <v>444553</v>
       </c>
       <c r="R75" t="n">
-        <v>6787411</v>
+        <v>6787299</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8270,7 +8278,7 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129795243</v>
+        <v>129795280</v>
       </c>
       <c r="B76" t="n">
         <v>79081</v>
@@ -8305,10 +8313,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>444159</v>
+        <v>444451</v>
       </c>
       <c r="R76" t="n">
-        <v>6787297</v>
+        <v>6787467</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8367,53 +8375,45 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129795208</v>
+        <v>129795284</v>
       </c>
       <c r="B77" t="n">
-        <v>58106</v>
+        <v>79081</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>103015</v>
+        <v>6425</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
-      <c r="K77" t="inlineStr"/>
-      <c r="L77" t="inlineStr"/>
-      <c r="M77" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>444434</v>
+        <v>444363</v>
       </c>
       <c r="R77" t="n">
-        <v>6787357</v>
+        <v>6787411</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8569,10 +8569,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129795300</v>
+        <v>129795127</v>
       </c>
       <c r="B79" t="n">
-        <v>79081</v>
+        <v>79700</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8580,37 +8580,34 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
-      <c r="J79" t="inlineStr"/>
-      <c r="K79" t="inlineStr"/>
-      <c r="N79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>444264</v>
+        <v>444432</v>
       </c>
       <c r="R79" t="n">
-        <v>6787349</v>
+        <v>6787388</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8645,18 +8642,12 @@
           <t>2025-11-22</t>
         </is>
       </c>
-      <c r="AC79" t="inlineStr">
-        <is>
-          <t>Garnlav i de flesta träd inom en radie av 50 m.</t>
-        </is>
-      </c>
       <c r="AD79" t="b">
         <v>0</v>
       </c>
       <c r="AE79" t="b">
         <v>0</v>
       </c>
-      <c r="AF79" t="inlineStr"/>
       <c r="AG79" t="b">
         <v>0</v>
       </c>
@@ -8878,7 +8869,7 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129795241</v>
+        <v>129795300</v>
       </c>
       <c r="B82" t="n">
         <v>79081</v>
@@ -8907,16 +8898,19 @@
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
+      <c r="J82" t="inlineStr"/>
+      <c r="K82" t="inlineStr"/>
+      <c r="N82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>444117</v>
+        <v>444264</v>
       </c>
       <c r="R82" t="n">
-        <v>6787277</v>
+        <v>6787349</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8951,12 +8945,18 @@
           <t>2025-11-22</t>
         </is>
       </c>
+      <c r="AC82" t="inlineStr">
+        <is>
+          <t>Garnlav i de flesta träd inom en radie av 50 m.</t>
+        </is>
+      </c>
       <c r="AD82" t="b">
         <v>0</v>
       </c>
       <c r="AE82" t="b">
         <v>0</v>
       </c>
+      <c r="AF82" t="inlineStr"/>
       <c r="AG82" t="b">
         <v>0</v>
       </c>
@@ -8975,10 +8975,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129795127</v>
+        <v>129795241</v>
       </c>
       <c r="B83" t="n">
-        <v>79700</v>
+        <v>79081</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8986,21 +8986,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9010,10 +9010,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>444432</v>
+        <v>444117</v>
       </c>
       <c r="R83" t="n">
-        <v>6787388</v>
+        <v>6787277</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9286,7 +9286,7 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129795308</v>
+        <v>129795242</v>
       </c>
       <c r="B86" t="n">
         <v>79081</v>
@@ -9321,7 +9321,7 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>444098</v>
+        <v>444125</v>
       </c>
       <c r="R86" t="n">
         <v>6787297</v>
@@ -9383,7 +9383,7 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129795242</v>
+        <v>129795308</v>
       </c>
       <c r="B87" t="n">
         <v>79081</v>
@@ -9418,7 +9418,7 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>444125</v>
+        <v>444098</v>
       </c>
       <c r="R87" t="n">
         <v>6787297</v>
@@ -9694,10 +9694,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>129795152</v>
+        <v>129795121</v>
       </c>
       <c r="B90" t="n">
-        <v>57733</v>
+        <v>79700</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9705,42 +9705,34 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
-      <c r="K90" t="inlineStr"/>
-      <c r="L90" t="inlineStr"/>
-      <c r="M90" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>444434</v>
+        <v>444254</v>
       </c>
       <c r="R90" t="n">
-        <v>6787304</v>
+        <v>6787204</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9799,10 +9791,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>129795305</v>
+        <v>129795124</v>
       </c>
       <c r="B91" t="n">
-        <v>79081</v>
+        <v>79700</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9810,21 +9802,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -9834,10 +9826,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>444169</v>
+        <v>444393</v>
       </c>
       <c r="R91" t="n">
-        <v>6787323</v>
+        <v>6787395</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9896,7 +9888,7 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>129795121</v>
+        <v>129795123</v>
       </c>
       <c r="B92" t="n">
         <v>79700</v>
@@ -9931,10 +9923,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>444254</v>
+        <v>444530</v>
       </c>
       <c r="R92" t="n">
-        <v>6787204</v>
+        <v>6787326</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9993,10 +9985,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>129795288</v>
+        <v>129795152</v>
       </c>
       <c r="B93" t="n">
-        <v>79081</v>
+        <v>57733</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10004,34 +9996,42 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
+      <c r="K93" t="inlineStr"/>
+      <c r="L93" t="inlineStr"/>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>444420</v>
+        <v>444434</v>
       </c>
       <c r="R93" t="n">
-        <v>6787366</v>
+        <v>6787304</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10090,7 +10090,7 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>129795245</v>
+        <v>129795297</v>
       </c>
       <c r="B94" t="n">
         <v>79081</v>
@@ -10125,10 +10125,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>444113</v>
+        <v>444297</v>
       </c>
       <c r="R94" t="n">
-        <v>6787239</v>
+        <v>6787333</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10187,10 +10187,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>129795124</v>
+        <v>129795252</v>
       </c>
       <c r="B95" t="n">
-        <v>79700</v>
+        <v>79081</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10198,21 +10198,21 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10222,10 +10222,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>444393</v>
+        <v>444249</v>
       </c>
       <c r="R95" t="n">
-        <v>6787395</v>
+        <v>6787249</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10258,6 +10258,11 @@
       <c r="AA95" t="inlineStr">
         <is>
           <t>2025-11-22</t>
+        </is>
+      </c>
+      <c r="AC95" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 40m.</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10284,10 +10289,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>129795123</v>
+        <v>129795245</v>
       </c>
       <c r="B96" t="n">
-        <v>79700</v>
+        <v>79081</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10295,21 +10300,21 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10319,10 +10324,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>444530</v>
+        <v>444113</v>
       </c>
       <c r="R96" t="n">
-        <v>6787326</v>
+        <v>6787239</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10381,7 +10386,7 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>129795297</v>
+        <v>129795288</v>
       </c>
       <c r="B97" t="n">
         <v>79081</v>
@@ -10416,10 +10421,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>444297</v>
+        <v>444420</v>
       </c>
       <c r="R97" t="n">
-        <v>6787333</v>
+        <v>6787366</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10478,7 +10483,7 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>129795262</v>
+        <v>129795305</v>
       </c>
       <c r="B98" t="n">
         <v>79081</v>
@@ -10513,10 +10518,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>444219</v>
+        <v>444169</v>
       </c>
       <c r="R98" t="n">
-        <v>6787163</v>
+        <v>6787323</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10575,7 +10580,7 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>129795252</v>
+        <v>129795262</v>
       </c>
       <c r="B99" t="n">
         <v>79081</v>
@@ -10610,10 +10615,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>444249</v>
+        <v>444219</v>
       </c>
       <c r="R99" t="n">
-        <v>6787249</v>
+        <v>6787163</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10646,11 +10651,6 @@
       <c r="AA99" t="inlineStr">
         <is>
           <t>2025-11-22</t>
-        </is>
-      </c>
-      <c r="AC99" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 40m.</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -10784,45 +10784,54 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>129795264</v>
+        <v>129795185</v>
       </c>
       <c r="B101" t="n">
-        <v>79081</v>
+        <v>8450</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
+      <c r="J101" t="inlineStr"/>
+      <c r="K101" t="inlineStr"/>
+      <c r="L101" t="inlineStr"/>
+      <c r="M101" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>444252</v>
+        <v>444458</v>
       </c>
       <c r="R101" t="n">
-        <v>6787160</v>
+        <v>6787304</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10863,6 +10872,7 @@
       <c r="AE101" t="b">
         <v>0</v>
       </c>
+      <c r="AF101" t="inlineStr"/>
       <c r="AG101" t="b">
         <v>0</v>
       </c>
@@ -10881,45 +10891,54 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>129795248</v>
+        <v>129795180</v>
       </c>
       <c r="B102" t="n">
-        <v>79081</v>
+        <v>8450</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
+      <c r="J102" t="inlineStr"/>
+      <c r="K102" t="inlineStr"/>
+      <c r="L102" t="inlineStr"/>
+      <c r="M102" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>444238</v>
+        <v>444409</v>
       </c>
       <c r="R102" t="n">
-        <v>6787281</v>
+        <v>6787219</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -10960,6 +10979,7 @@
       <c r="AE102" t="b">
         <v>0</v>
       </c>
+      <c r="AF102" t="inlineStr"/>
       <c r="AG102" t="b">
         <v>0</v>
       </c>
@@ -10978,45 +10998,54 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>129795303</v>
+        <v>129795178</v>
       </c>
       <c r="B103" t="n">
-        <v>79081</v>
+        <v>8450</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
+      <c r="J103" t="inlineStr"/>
+      <c r="K103" t="inlineStr"/>
+      <c r="L103" t="inlineStr"/>
+      <c r="M103" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N103" t="inlineStr"/>
       <c r="P103" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>444200</v>
+        <v>444375</v>
       </c>
       <c r="R103" t="n">
-        <v>6787331</v>
+        <v>6787207</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11057,6 +11086,7 @@
       <c r="AE103" t="b">
         <v>0</v>
       </c>
+      <c r="AF103" t="inlineStr"/>
       <c r="AG103" t="b">
         <v>0</v>
       </c>
@@ -11075,45 +11105,54 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>129795306</v>
+        <v>129795186</v>
       </c>
       <c r="B104" t="n">
-        <v>79081</v>
+        <v>8450</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
+      <c r="J104" t="inlineStr"/>
+      <c r="K104" t="inlineStr"/>
+      <c r="L104" t="inlineStr"/>
+      <c r="M104" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>444152</v>
+        <v>444473</v>
       </c>
       <c r="R104" t="n">
-        <v>6787313</v>
+        <v>6787334</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11154,6 +11193,7 @@
       <c r="AE104" t="b">
         <v>0</v>
       </c>
+      <c r="AF104" t="inlineStr"/>
       <c r="AG104" t="b">
         <v>0</v>
       </c>
@@ -11172,7 +11212,7 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>129795185</v>
+        <v>129795196</v>
       </c>
       <c r="B105" t="n">
         <v>8450</v>
@@ -11216,10 +11256,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>444458</v>
+        <v>444346</v>
       </c>
       <c r="R105" t="n">
-        <v>6787304</v>
+        <v>6787369</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11279,54 +11319,45 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>129795180</v>
+        <v>129795303</v>
       </c>
       <c r="B106" t="n">
-        <v>8450</v>
+        <v>79081</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
-      <c r="J106" t="inlineStr"/>
-      <c r="K106" t="inlineStr"/>
-      <c r="L106" t="inlineStr"/>
-      <c r="M106" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>444409</v>
+        <v>444200</v>
       </c>
       <c r="R106" t="n">
-        <v>6787219</v>
+        <v>6787331</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11367,7 +11398,6 @@
       <c r="AE106" t="b">
         <v>0</v>
       </c>
-      <c r="AF106" t="inlineStr"/>
       <c r="AG106" t="b">
         <v>0</v>
       </c>
@@ -11386,54 +11416,45 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>129795178</v>
+        <v>129795264</v>
       </c>
       <c r="B107" t="n">
-        <v>8450</v>
+        <v>79081</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
-      <c r="J107" t="inlineStr"/>
-      <c r="K107" t="inlineStr"/>
-      <c r="L107" t="inlineStr"/>
-      <c r="M107" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>444375</v>
+        <v>444252</v>
       </c>
       <c r="R107" t="n">
-        <v>6787207</v>
+        <v>6787160</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11474,7 +11495,6 @@
       <c r="AE107" t="b">
         <v>0</v>
       </c>
-      <c r="AF107" t="inlineStr"/>
       <c r="AG107" t="b">
         <v>0</v>
       </c>
@@ -11493,54 +11513,45 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>129795186</v>
+        <v>129795248</v>
       </c>
       <c r="B108" t="n">
-        <v>8450</v>
+        <v>79081</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
-      <c r="J108" t="inlineStr"/>
-      <c r="K108" t="inlineStr"/>
-      <c r="L108" t="inlineStr"/>
-      <c r="M108" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>444473</v>
+        <v>444238</v>
       </c>
       <c r="R108" t="n">
-        <v>6787334</v>
+        <v>6787281</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11581,7 +11592,6 @@
       <c r="AE108" t="b">
         <v>0</v>
       </c>
-      <c r="AF108" t="inlineStr"/>
       <c r="AG108" t="b">
         <v>0</v>
       </c>
@@ -11600,54 +11610,45 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>129795196</v>
+        <v>129795306</v>
       </c>
       <c r="B109" t="n">
-        <v>8450</v>
+        <v>79081</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
-      <c r="J109" t="inlineStr"/>
-      <c r="K109" t="inlineStr"/>
-      <c r="L109" t="inlineStr"/>
-      <c r="M109" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>444346</v>
+        <v>444152</v>
       </c>
       <c r="R109" t="n">
-        <v>6787369</v>
+        <v>6787313</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11688,7 +11689,6 @@
       <c r="AE109" t="b">
         <v>0</v>
       </c>
-      <c r="AF109" t="inlineStr"/>
       <c r="AG109" t="b">
         <v>0</v>
       </c>
@@ -11707,7 +11707,7 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>129795149</v>
+        <v>129795145</v>
       </c>
       <c r="B110" t="n">
         <v>57733</v>
@@ -11740,7 +11740,7 @@
       <c r="L110" t="inlineStr"/>
       <c r="M110" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N110" t="inlineStr"/>
@@ -11750,10 +11750,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>444223</v>
+        <v>444228</v>
       </c>
       <c r="R110" t="n">
-        <v>6787221</v>
+        <v>6787226</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11812,7 +11812,7 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>129795145</v>
+        <v>129795149</v>
       </c>
       <c r="B111" t="n">
         <v>57733</v>
@@ -11845,7 +11845,7 @@
       <c r="L111" t="inlineStr"/>
       <c r="M111" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N111" t="inlineStr"/>
@@ -11855,10 +11855,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>444228</v>
+        <v>444223</v>
       </c>
       <c r="R111" t="n">
-        <v>6787226</v>
+        <v>6787221</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -12022,54 +12022,45 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>129795203</v>
+        <v>129795259</v>
       </c>
       <c r="B113" t="n">
-        <v>8450</v>
+        <v>79081</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
-      <c r="J113" t="inlineStr"/>
-      <c r="K113" t="inlineStr"/>
-      <c r="L113" t="inlineStr"/>
-      <c r="M113" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N113" t="inlineStr"/>
       <c r="P113" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>444401</v>
+        <v>444164</v>
       </c>
       <c r="R113" t="n">
-        <v>6787298</v>
+        <v>6787121</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12110,7 +12101,6 @@
       <c r="AE113" t="b">
         <v>0</v>
       </c>
-      <c r="AF113" t="inlineStr"/>
       <c r="AG113" t="b">
         <v>0</v>
       </c>
@@ -12129,7 +12119,7 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>129795201</v>
+        <v>129795203</v>
       </c>
       <c r="B114" t="n">
         <v>8450</v>
@@ -12173,10 +12163,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>444430</v>
+        <v>444401</v>
       </c>
       <c r="R114" t="n">
-        <v>6787332</v>
+        <v>6787298</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12236,45 +12226,54 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>129795259</v>
+        <v>129795201</v>
       </c>
       <c r="B115" t="n">
-        <v>79081</v>
+        <v>8450</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
+      <c r="J115" t="inlineStr"/>
+      <c r="K115" t="inlineStr"/>
+      <c r="L115" t="inlineStr"/>
+      <c r="M115" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N115" t="inlineStr"/>
       <c r="P115" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>444164</v>
+        <v>444430</v>
       </c>
       <c r="R115" t="n">
-        <v>6787121</v>
+        <v>6787332</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12315,6 +12314,7 @@
       <c r="AE115" t="b">
         <v>0</v>
       </c>
+      <c r="AF115" t="inlineStr"/>
       <c r="AG115" t="b">
         <v>0</v>
       </c>
@@ -12333,7 +12333,7 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>129795164</v>
+        <v>129795157</v>
       </c>
       <c r="B116" t="n">
         <v>57733</v>
@@ -12376,10 +12376,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>444397</v>
+        <v>444525</v>
       </c>
       <c r="R116" t="n">
-        <v>6787300</v>
+        <v>6787344</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12438,32 +12438,32 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>129795154</v>
+        <v>129795132</v>
       </c>
       <c r="B117" t="n">
-        <v>57733</v>
+        <v>56926</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -12471,7 +12471,7 @@
       <c r="L117" t="inlineStr"/>
       <c r="M117" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="N117" t="inlineStr"/>
@@ -12481,10 +12481,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>444457</v>
+        <v>444315</v>
       </c>
       <c r="R117" t="n">
-        <v>6787303</v>
+        <v>6787291</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12543,40 +12543,41 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>129795157</v>
+        <v>129795171</v>
       </c>
       <c r="B118" t="n">
-        <v>57733</v>
+        <v>8450</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
+      <c r="J118" t="inlineStr"/>
       <c r="K118" t="inlineStr"/>
       <c r="L118" t="inlineStr"/>
       <c r="M118" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N118" t="inlineStr"/>
@@ -12586,10 +12587,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>444525</v>
+        <v>444185</v>
       </c>
       <c r="R118" t="n">
-        <v>6787344</v>
+        <v>6787226</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12630,6 +12631,7 @@
       <c r="AE118" t="b">
         <v>0</v>
       </c>
+      <c r="AF118" t="inlineStr"/>
       <c r="AG118" t="b">
         <v>0</v>
       </c>
@@ -12648,10 +12650,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>129795289</v>
+        <v>129795164</v>
       </c>
       <c r="B119" t="n">
-        <v>79081</v>
+        <v>57733</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -12659,34 +12661,42 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
+      <c r="K119" t="inlineStr"/>
+      <c r="L119" t="inlineStr"/>
+      <c r="M119" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N119" t="inlineStr"/>
       <c r="P119" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>444435</v>
+        <v>444397</v>
       </c>
       <c r="R119" t="n">
-        <v>6787341</v>
+        <v>6787300</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -12745,32 +12755,32 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>129795132</v>
+        <v>129795154</v>
       </c>
       <c r="B120" t="n">
-        <v>56926</v>
+        <v>57733</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -12778,7 +12788,7 @@
       <c r="L120" t="inlineStr"/>
       <c r="M120" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N120" t="inlineStr"/>
@@ -12788,10 +12798,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>444315</v>
+        <v>444457</v>
       </c>
       <c r="R120" t="n">
-        <v>6787291</v>
+        <v>6787303</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -12850,54 +12860,45 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>129795171</v>
+        <v>129795289</v>
       </c>
       <c r="B121" t="n">
-        <v>8450</v>
+        <v>79081</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
-      <c r="J121" t="inlineStr"/>
-      <c r="K121" t="inlineStr"/>
-      <c r="L121" t="inlineStr"/>
-      <c r="M121" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N121" t="inlineStr"/>
       <c r="P121" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>444185</v>
+        <v>444435</v>
       </c>
       <c r="R121" t="n">
-        <v>6787226</v>
+        <v>6787341</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -12938,7 +12939,6 @@
       <c r="AE121" t="b">
         <v>0</v>
       </c>
-      <c r="AF121" t="inlineStr"/>
       <c r="AG121" t="b">
         <v>0</v>
       </c>
@@ -12957,41 +12957,40 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>129795188</v>
+        <v>129795144</v>
       </c>
       <c r="B122" t="n">
-        <v>8450</v>
+        <v>57733</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
-      <c r="J122" t="inlineStr"/>
       <c r="K122" t="inlineStr"/>
       <c r="L122" t="inlineStr"/>
       <c r="M122" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N122" t="inlineStr"/>
@@ -13001,10 +13000,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>444498</v>
+        <v>444186</v>
       </c>
       <c r="R122" t="n">
-        <v>6787280</v>
+        <v>6787223</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -13045,7 +13044,6 @@
       <c r="AE122" t="b">
         <v>0</v>
       </c>
-      <c r="AF122" t="inlineStr"/>
       <c r="AG122" t="b">
         <v>0</v>
       </c>
@@ -13064,7 +13062,7 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>129795179</v>
+        <v>129795188</v>
       </c>
       <c r="B123" t="n">
         <v>8450</v>
@@ -13108,10 +13106,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>444378</v>
+        <v>444498</v>
       </c>
       <c r="R123" t="n">
-        <v>6787236</v>
+        <v>6787280</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13171,40 +13169,41 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>129795144</v>
+        <v>129795179</v>
       </c>
       <c r="B124" t="n">
-        <v>57733</v>
+        <v>8450</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
+      <c r="J124" t="inlineStr"/>
       <c r="K124" t="inlineStr"/>
       <c r="L124" t="inlineStr"/>
       <c r="M124" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N124" t="inlineStr"/>
@@ -13214,10 +13213,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>444186</v>
+        <v>444378</v>
       </c>
       <c r="R124" t="n">
-        <v>6787223</v>
+        <v>6787236</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13258,6 +13257,7 @@
       <c r="AE124" t="b">
         <v>0</v>
       </c>
+      <c r="AF124" t="inlineStr"/>
       <c r="AG124" t="b">
         <v>0</v>
       </c>
@@ -13470,54 +13470,45 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>129795175</v>
+        <v>129795275</v>
       </c>
       <c r="B127" t="n">
-        <v>8450</v>
+        <v>79081</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
-      <c r="J127" t="inlineStr"/>
-      <c r="K127" t="inlineStr"/>
-      <c r="L127" t="inlineStr"/>
-      <c r="M127" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N127" t="inlineStr"/>
       <c r="P127" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>444182</v>
+        <v>444495</v>
       </c>
       <c r="R127" t="n">
-        <v>6787101</v>
+        <v>6787340</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -13558,7 +13549,6 @@
       <c r="AE127" t="b">
         <v>0</v>
       </c>
-      <c r="AF127" t="inlineStr"/>
       <c r="AG127" t="b">
         <v>0</v>
       </c>
@@ -13577,54 +13567,45 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>129795168</v>
+        <v>129795263</v>
       </c>
       <c r="B128" t="n">
-        <v>8450</v>
+        <v>79081</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
-      <c r="J128" t="inlineStr"/>
-      <c r="K128" t="inlineStr"/>
-      <c r="L128" t="inlineStr"/>
-      <c r="M128" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N128" t="inlineStr"/>
       <c r="P128" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>444272</v>
+        <v>444241</v>
       </c>
       <c r="R128" t="n">
-        <v>6787286</v>
+        <v>6787149</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -13665,7 +13646,6 @@
       <c r="AE128" t="b">
         <v>0</v>
       </c>
-      <c r="AF128" t="inlineStr"/>
       <c r="AG128" t="b">
         <v>0</v>
       </c>
@@ -13684,10 +13664,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>129795137</v>
+        <v>129795267</v>
       </c>
       <c r="B129" t="n">
-        <v>91614</v>
+        <v>79081</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -13695,37 +13675,34 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
-      <c r="J129" t="inlineStr"/>
-      <c r="K129" t="inlineStr"/>
-      <c r="N129" t="inlineStr"/>
       <c r="P129" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>444203</v>
+        <v>444353</v>
       </c>
       <c r="R129" t="n">
-        <v>6787221</v>
+        <v>6787215</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -13760,13 +13737,17 @@
           <t>2025-11-22</t>
         </is>
       </c>
+      <c r="AC129" t="inlineStr">
+        <is>
+          <t>Gott om garnlav inom en radie av 40m.</t>
+        </is>
+      </c>
       <c r="AD129" t="b">
         <v>0</v>
       </c>
       <c r="AE129" t="b">
         <v>0</v>
       </c>
-      <c r="AF129" t="inlineStr"/>
       <c r="AG129" t="b">
         <v>0</v>
       </c>
@@ -13785,10 +13766,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>129795159</v>
+        <v>129795258</v>
       </c>
       <c r="B130" t="n">
-        <v>57733</v>
+        <v>79081</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -13796,42 +13777,34 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
-      <c r="K130" t="inlineStr"/>
-      <c r="L130" t="inlineStr"/>
-      <c r="M130" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N130" t="inlineStr"/>
       <c r="P130" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>444436</v>
+        <v>444174</v>
       </c>
       <c r="R130" t="n">
-        <v>6787463</v>
+        <v>6787136</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -13890,10 +13863,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>129795258</v>
+        <v>129795159</v>
       </c>
       <c r="B131" t="n">
-        <v>79081</v>
+        <v>57733</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -13901,34 +13874,42 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
+      <c r="K131" t="inlineStr"/>
+      <c r="L131" t="inlineStr"/>
+      <c r="M131" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N131" t="inlineStr"/>
       <c r="P131" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>444174</v>
+        <v>444436</v>
       </c>
       <c r="R131" t="n">
-        <v>6787136</v>
+        <v>6787463</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -13987,45 +13968,54 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>129795275</v>
+        <v>129795175</v>
       </c>
       <c r="B132" t="n">
-        <v>79081</v>
+        <v>8450</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
+      <c r="J132" t="inlineStr"/>
+      <c r="K132" t="inlineStr"/>
+      <c r="L132" t="inlineStr"/>
+      <c r="M132" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N132" t="inlineStr"/>
       <c r="P132" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>444495</v>
+        <v>444182</v>
       </c>
       <c r="R132" t="n">
-        <v>6787340</v>
+        <v>6787101</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -14066,6 +14056,7 @@
       <c r="AE132" t="b">
         <v>0</v>
       </c>
+      <c r="AF132" t="inlineStr"/>
       <c r="AG132" t="b">
         <v>0</v>
       </c>
@@ -14084,45 +14075,54 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>129795267</v>
+        <v>129795168</v>
       </c>
       <c r="B133" t="n">
-        <v>79081</v>
+        <v>8450</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
+      <c r="J133" t="inlineStr"/>
+      <c r="K133" t="inlineStr"/>
+      <c r="L133" t="inlineStr"/>
+      <c r="M133" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N133" t="inlineStr"/>
       <c r="P133" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>444353</v>
+        <v>444272</v>
       </c>
       <c r="R133" t="n">
-        <v>6787215</v>
+        <v>6787286</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -14157,17 +14157,13 @@
           <t>2025-11-22</t>
         </is>
       </c>
-      <c r="AC133" t="inlineStr">
-        <is>
-          <t>Gott om garnlav inom en radie av 40m.</t>
-        </is>
-      </c>
       <c r="AD133" t="b">
         <v>0</v>
       </c>
       <c r="AE133" t="b">
         <v>0</v>
       </c>
+      <c r="AF133" t="inlineStr"/>
       <c r="AG133" t="b">
         <v>0</v>
       </c>
@@ -14186,10 +14182,10 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>129795263</v>
+        <v>129795137</v>
       </c>
       <c r="B134" t="n">
-        <v>79081</v>
+        <v>91618</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -14197,34 +14193,37 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
+      <c r="J134" t="inlineStr"/>
+      <c r="K134" t="inlineStr"/>
+      <c r="N134" t="inlineStr"/>
       <c r="P134" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>444241</v>
+        <v>444203</v>
       </c>
       <c r="R134" t="n">
-        <v>6787149</v>
+        <v>6787221</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -14265,6 +14264,7 @@
       <c r="AE134" t="b">
         <v>0</v>
       </c>
+      <c r="AF134" t="inlineStr"/>
       <c r="AG134" t="b">
         <v>0</v>
       </c>
@@ -14283,10 +14283,10 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>129795139</v>
+        <v>129795254</v>
       </c>
       <c r="B135" t="n">
-        <v>91614</v>
+        <v>79081</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -14294,21 +14294,21 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
@@ -14321,10 +14321,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>444342</v>
+        <v>444199</v>
       </c>
       <c r="R135" t="n">
-        <v>6787240</v>
+        <v>6787221</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -14384,7 +14384,7 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>129795274</v>
+        <v>129795266</v>
       </c>
       <c r="B136" t="n">
         <v>79081</v>
@@ -14419,10 +14419,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>444538</v>
+        <v>444314</v>
       </c>
       <c r="R136" t="n">
-        <v>6787325</v>
+        <v>6787212</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -14455,6 +14455,11 @@
       <c r="AA136" t="inlineStr">
         <is>
           <t>2025-11-22</t>
+        </is>
+      </c>
+      <c r="AC136" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 40m</t>
         </is>
       </c>
       <c r="AD136" t="b">
@@ -14481,7 +14486,7 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>129795304</v>
+        <v>129795302</v>
       </c>
       <c r="B137" t="n">
         <v>79081</v>
@@ -14516,10 +14521,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>444172</v>
+        <v>444222</v>
       </c>
       <c r="R137" t="n">
-        <v>6787339</v>
+        <v>6787345</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -14578,37 +14583,43 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>129795254</v>
+        <v>129795204</v>
       </c>
       <c r="B138" t="n">
-        <v>79081</v>
+        <v>8450</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E138" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
       <c r="J138" t="inlineStr"/>
       <c r="K138" t="inlineStr"/>
+      <c r="L138" t="inlineStr"/>
+      <c r="M138" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N138" t="inlineStr"/>
       <c r="P138" t="inlineStr">
         <is>
@@ -14616,10 +14627,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>444199</v>
+        <v>444380</v>
       </c>
       <c r="R138" t="n">
-        <v>6787221</v>
+        <v>6787306</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -14679,10 +14690,10 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>129795302</v>
+        <v>129795139</v>
       </c>
       <c r="B139" t="n">
-        <v>79081</v>
+        <v>91618</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -14690,34 +14701,37 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
+      <c r="J139" t="inlineStr"/>
+      <c r="K139" t="inlineStr"/>
+      <c r="N139" t="inlineStr"/>
       <c r="P139" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>444222</v>
+        <v>444342</v>
       </c>
       <c r="R139" t="n">
-        <v>6787345</v>
+        <v>6787240</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -14758,6 +14772,7 @@
       <c r="AE139" t="b">
         <v>0</v>
       </c>
+      <c r="AF139" t="inlineStr"/>
       <c r="AG139" t="b">
         <v>0</v>
       </c>
@@ -14776,7 +14791,7 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>129795251</v>
+        <v>129795274</v>
       </c>
       <c r="B140" t="n">
         <v>79081</v>
@@ -14805,19 +14820,16 @@
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
-      <c r="J140" t="inlineStr"/>
-      <c r="K140" t="inlineStr"/>
-      <c r="N140" t="inlineStr"/>
       <c r="P140" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>444309</v>
+        <v>444538</v>
       </c>
       <c r="R140" t="n">
-        <v>6787272</v>
+        <v>6787325</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -14858,7 +14870,6 @@
       <c r="AE140" t="b">
         <v>0</v>
       </c>
-      <c r="AF140" t="inlineStr"/>
       <c r="AG140" t="b">
         <v>0</v>
       </c>
@@ -14877,7 +14888,7 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>129795266</v>
+        <v>129795247</v>
       </c>
       <c r="B141" t="n">
         <v>79081</v>
@@ -14912,10 +14923,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>444314</v>
+        <v>444225</v>
       </c>
       <c r="R141" t="n">
-        <v>6787212</v>
+        <v>6787275</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -14948,11 +14959,6 @@
       <c r="AA141" t="inlineStr">
         <is>
           <t>2025-11-22</t>
-        </is>
-      </c>
-      <c r="AC141" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 40m</t>
         </is>
       </c>
       <c r="AD141" t="b">
@@ -14979,7 +14985,7 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>129795247</v>
+        <v>129795304</v>
       </c>
       <c r="B142" t="n">
         <v>79081</v>
@@ -15014,10 +15020,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>444225</v>
+        <v>444172</v>
       </c>
       <c r="R142" t="n">
-        <v>6787275</v>
+        <v>6787339</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -15076,43 +15082,37 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>129795204</v>
+        <v>129795251</v>
       </c>
       <c r="B143" t="n">
-        <v>8450</v>
+        <v>79081</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E143" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
       <c r="J143" t="inlineStr"/>
       <c r="K143" t="inlineStr"/>
-      <c r="L143" t="inlineStr"/>
-      <c r="M143" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N143" t="inlineStr"/>
       <c r="P143" t="inlineStr">
         <is>
@@ -15120,10 +15120,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>444380</v>
+        <v>444309</v>
       </c>
       <c r="R143" t="n">
-        <v>6787306</v>
+        <v>6787272</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>

--- a/artfynd/A 51041-2025 artfynd.xlsx
+++ b/artfynd/A 51041-2025 artfynd.xlsx
@@ -675,37 +675,43 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129795283</v>
+        <v>129795169</v>
       </c>
       <c r="B2" t="n">
-        <v>79081</v>
+        <v>8450</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -713,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>444337</v>
+        <v>444272</v>
       </c>
       <c r="R2" t="n">
-        <v>6787374</v>
+        <v>6787239</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -776,45 +782,54 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129795261</v>
+        <v>129795190</v>
       </c>
       <c r="B3" t="n">
-        <v>79081</v>
+        <v>8450</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>444193</v>
+        <v>444510</v>
       </c>
       <c r="R3" t="n">
-        <v>6787130</v>
+        <v>6787276</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -855,6 +870,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -873,45 +889,54 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129795253</v>
+        <v>129795197</v>
       </c>
       <c r="B4" t="n">
-        <v>79081</v>
+        <v>8450</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>444185</v>
+        <v>444406</v>
       </c>
       <c r="R4" t="n">
-        <v>6787247</v>
+        <v>6787392</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -946,17 +971,13 @@
           <t>2025-11-22</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Gott om garnlav inom en radie av 50 m.</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -975,7 +996,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129795285</v>
+        <v>129795283</v>
       </c>
       <c r="B5" t="n">
         <v>79081</v>
@@ -1004,16 +1025,19 @@
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>444405</v>
+        <v>444337</v>
       </c>
       <c r="R5" t="n">
-        <v>6787405</v>
+        <v>6787374</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1054,6 +1078,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1072,7 +1097,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129795244</v>
+        <v>129795261</v>
       </c>
       <c r="B6" t="n">
         <v>79081</v>
@@ -1107,10 +1132,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>444105</v>
+        <v>444193</v>
       </c>
       <c r="R6" t="n">
-        <v>6787246</v>
+        <v>6787130</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1169,7 +1194,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129795291</v>
+        <v>129795253</v>
       </c>
       <c r="B7" t="n">
         <v>79081</v>
@@ -1204,10 +1229,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>444412</v>
+        <v>444185</v>
       </c>
       <c r="R7" t="n">
-        <v>6787307</v>
+        <v>6787247</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1240,6 +1265,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-11-22</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Gott om garnlav inom en radie av 50 m.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1266,7 +1296,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129795298</v>
+        <v>129795285</v>
       </c>
       <c r="B8" t="n">
         <v>79081</v>
@@ -1301,10 +1331,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>444305</v>
+        <v>444405</v>
       </c>
       <c r="R8" t="n">
-        <v>6787353</v>
+        <v>6787405</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1363,54 +1393,45 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129795169</v>
+        <v>129795244</v>
       </c>
       <c r="B9" t="n">
-        <v>8450</v>
+        <v>79081</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>444272</v>
+        <v>444105</v>
       </c>
       <c r="R9" t="n">
-        <v>6787239</v>
+        <v>6787246</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1451,7 +1472,6 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1470,54 +1490,45 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129795190</v>
+        <v>129795291</v>
       </c>
       <c r="B10" t="n">
-        <v>8450</v>
+        <v>79081</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>444510</v>
+        <v>444412</v>
       </c>
       <c r="R10" t="n">
-        <v>6787276</v>
+        <v>6787307</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1558,7 +1569,6 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1577,54 +1587,45 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129795197</v>
+        <v>129795298</v>
       </c>
       <c r="B11" t="n">
-        <v>8450</v>
+        <v>79081</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>444406</v>
+        <v>444305</v>
       </c>
       <c r="R11" t="n">
-        <v>6787392</v>
+        <v>6787353</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1665,7 +1666,6 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1684,7 +1684,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129795163</v>
+        <v>129795155</v>
       </c>
       <c r="B12" t="n">
         <v>57733</v>
@@ -1727,10 +1727,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>444415</v>
+        <v>444498</v>
       </c>
       <c r="R12" t="n">
-        <v>6787316</v>
+        <v>6787306</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1789,10 +1789,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129795276</v>
+        <v>129795163</v>
       </c>
       <c r="B13" t="n">
-        <v>79081</v>
+        <v>57733</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1800,26 +1800,31 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1827,10 +1832,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>444499</v>
+        <v>444415</v>
       </c>
       <c r="R13" t="n">
-        <v>6787367</v>
+        <v>6787316</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1865,18 +1870,12 @@
           <t>2025-11-22</t>
         </is>
       </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 50m.</t>
-        </is>
-      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -1895,10 +1894,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129795271</v>
+        <v>129795153</v>
       </c>
       <c r="B14" t="n">
-        <v>79081</v>
+        <v>57733</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1906,26 +1905,31 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -1933,10 +1937,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>444466</v>
+        <v>444452</v>
       </c>
       <c r="R14" t="n">
-        <v>6787306</v>
+        <v>6787294</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1971,18 +1975,12 @@
           <t>2025-11-22</t>
         </is>
       </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 50m.</t>
-        </is>
-      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2001,7 +1999,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129795281</v>
+        <v>129795276</v>
       </c>
       <c r="B15" t="n">
         <v>79081</v>
@@ -2039,10 +2037,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>444408</v>
+        <v>444499</v>
       </c>
       <c r="R15" t="n">
-        <v>6787452</v>
+        <v>6787367</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2075,6 +2073,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-11-22</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 50m.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2102,7 +2105,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129795299</v>
+        <v>129795271</v>
       </c>
       <c r="B16" t="n">
         <v>79081</v>
@@ -2131,16 +2134,19 @@
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>444265</v>
+        <v>444466</v>
       </c>
       <c r="R16" t="n">
-        <v>6787372</v>
+        <v>6787306</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2175,12 +2181,18 @@
           <t>2025-11-22</t>
         </is>
       </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 50m.</t>
+        </is>
+      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2199,10 +2211,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129795155</v>
+        <v>129795281</v>
       </c>
       <c r="B17" t="n">
-        <v>57733</v>
+        <v>79081</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2210,31 +2222,26 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2242,10 +2249,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>444498</v>
+        <v>444408</v>
       </c>
       <c r="R17" t="n">
-        <v>6787306</v>
+        <v>6787452</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2286,6 +2293,7 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2304,10 +2312,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129795153</v>
+        <v>129795299</v>
       </c>
       <c r="B18" t="n">
-        <v>57733</v>
+        <v>79081</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2315,42 +2323,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>444452</v>
+        <v>444265</v>
       </c>
       <c r="R18" t="n">
-        <v>6787294</v>
+        <v>6787372</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2623,45 +2623,54 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129795265</v>
+        <v>129795206</v>
       </c>
       <c r="B21" t="n">
-        <v>79081</v>
+        <v>8450</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>444278</v>
+        <v>444247</v>
       </c>
       <c r="R21" t="n">
-        <v>6787163</v>
+        <v>6787328</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2702,6 +2711,7 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -2720,7 +2730,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129795278</v>
+        <v>129795265</v>
       </c>
       <c r="B22" t="n">
         <v>79081</v>
@@ -2755,10 +2765,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>444465</v>
+        <v>444278</v>
       </c>
       <c r="R22" t="n">
-        <v>6787451</v>
+        <v>6787163</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2817,7 +2827,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129795310</v>
+        <v>129795278</v>
       </c>
       <c r="B23" t="n">
         <v>79081</v>
@@ -2846,19 +2856,16 @@
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>444488</v>
+        <v>444465</v>
       </c>
       <c r="R23" t="n">
-        <v>6787445</v>
+        <v>6787451</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2893,18 +2900,12 @@
           <t>2025-11-22</t>
         </is>
       </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Gott om garnlav inom en radie av 40m</t>
-        </is>
-      </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -2923,7 +2924,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129795273</v>
+        <v>129795310</v>
       </c>
       <c r="B24" t="n">
         <v>79081</v>
@@ -2952,16 +2953,19 @@
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>444548</v>
+        <v>444488</v>
       </c>
       <c r="R24" t="n">
-        <v>6787330</v>
+        <v>6787445</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2996,12 +3000,18 @@
           <t>2025-11-22</t>
         </is>
       </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Gott om garnlav inom en radie av 40m</t>
+        </is>
+      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3020,54 +3030,45 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129795198</v>
+        <v>129795273</v>
       </c>
       <c r="B25" t="n">
-        <v>8450</v>
+        <v>79081</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>444434</v>
+        <v>444548</v>
       </c>
       <c r="R25" t="n">
-        <v>6787384</v>
+        <v>6787330</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3108,7 +3109,6 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3127,7 +3127,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129795207</v>
+        <v>129795198</v>
       </c>
       <c r="B26" t="n">
         <v>8450</v>
@@ -3171,10 +3171,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>444221</v>
+        <v>444434</v>
       </c>
       <c r="R26" t="n">
-        <v>6787340</v>
+        <v>6787384</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3234,7 +3234,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129795200</v>
+        <v>129795207</v>
       </c>
       <c r="B27" t="n">
         <v>8450</v>
@@ -3278,10 +3278,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>444429</v>
+        <v>444221</v>
       </c>
       <c r="R27" t="n">
-        <v>6787341</v>
+        <v>6787340</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3341,7 +3341,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129795206</v>
+        <v>129795200</v>
       </c>
       <c r="B28" t="n">
         <v>8450</v>
@@ -3385,10 +3385,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>444247</v>
+        <v>444429</v>
       </c>
       <c r="R28" t="n">
-        <v>6787328</v>
+        <v>6787341</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3553,45 +3553,54 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129795268</v>
+        <v>129795187</v>
       </c>
       <c r="B30" t="n">
-        <v>79081</v>
+        <v>8450</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>444383</v>
+        <v>444487</v>
       </c>
       <c r="R30" t="n">
-        <v>6787218</v>
+        <v>6787321</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3632,6 +3641,7 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
+      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -3650,45 +3660,54 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129795256</v>
+        <v>129795189</v>
       </c>
       <c r="B31" t="n">
-        <v>79081</v>
+        <v>8450</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>444226</v>
+        <v>444500</v>
       </c>
       <c r="R31" t="n">
-        <v>6787196</v>
+        <v>6787274</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3729,6 +3748,7 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
+      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
@@ -3747,7 +3767,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129795187</v>
+        <v>129795176</v>
       </c>
       <c r="B32" t="n">
         <v>8450</v>
@@ -3781,7 +3801,7 @@
       <c r="L32" t="inlineStr"/>
       <c r="M32" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="N32" t="inlineStr"/>
@@ -3791,10 +3811,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>444487</v>
+        <v>444215</v>
       </c>
       <c r="R32" t="n">
-        <v>6787321</v>
+        <v>6787151</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3854,54 +3874,45 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129795189</v>
+        <v>129795268</v>
       </c>
       <c r="B33" t="n">
-        <v>8450</v>
+        <v>79081</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>444500</v>
+        <v>444383</v>
       </c>
       <c r="R33" t="n">
-        <v>6787274</v>
+        <v>6787218</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3942,7 +3953,6 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
-      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -3961,54 +3971,45 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129795176</v>
+        <v>129795256</v>
       </c>
       <c r="B34" t="n">
-        <v>8450</v>
+        <v>79081</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>444215</v>
+        <v>444226</v>
       </c>
       <c r="R34" t="n">
-        <v>6787151</v>
+        <v>6787196</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4049,7 +4050,6 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
-      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
@@ -4068,10 +4068,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129795165</v>
+        <v>129795269</v>
       </c>
       <c r="B35" t="n">
-        <v>57733</v>
+        <v>79081</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4079,42 +4079,34 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>444251</v>
+        <v>444429</v>
       </c>
       <c r="R35" t="n">
-        <v>6787376</v>
+        <v>6787240</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4173,7 +4165,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129795269</v>
+        <v>129795249</v>
       </c>
       <c r="B36" t="n">
         <v>79081</v>
@@ -4208,10 +4200,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>444429</v>
+        <v>444267</v>
       </c>
       <c r="R36" t="n">
-        <v>6787240</v>
+        <v>6787295</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4270,7 +4262,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129795249</v>
+        <v>129795296</v>
       </c>
       <c r="B37" t="n">
         <v>79081</v>
@@ -4299,16 +4291,19 @@
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>444267</v>
+        <v>444299</v>
       </c>
       <c r="R37" t="n">
-        <v>6787295</v>
+        <v>6787304</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4343,12 +4338,18 @@
           <t>2025-11-22</t>
         </is>
       </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 50 m.</t>
+        </is>
+      </c>
       <c r="AD37" t="b">
         <v>0</v>
       </c>
       <c r="AE37" t="b">
         <v>0</v>
       </c>
+      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -4367,7 +4368,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129795296</v>
+        <v>129795270</v>
       </c>
       <c r="B38" t="n">
         <v>79081</v>
@@ -4396,19 +4397,16 @@
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
-      <c r="K38" t="inlineStr"/>
-      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>444299</v>
+        <v>444416</v>
       </c>
       <c r="R38" t="n">
-        <v>6787304</v>
+        <v>6787260</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4443,18 +4441,12 @@
           <t>2025-11-22</t>
         </is>
       </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 50 m.</t>
-        </is>
-      </c>
       <c r="AD38" t="b">
         <v>0</v>
       </c>
       <c r="AE38" t="b">
         <v>0</v>
       </c>
-      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -4473,45 +4465,54 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129795270</v>
+        <v>129795193</v>
       </c>
       <c r="B39" t="n">
-        <v>79081</v>
+        <v>8450</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>444416</v>
+        <v>444508</v>
       </c>
       <c r="R39" t="n">
-        <v>6787260</v>
+        <v>6787352</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4552,6 +4553,7 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
+      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -4570,40 +4572,41 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129795133</v>
+        <v>129795202</v>
       </c>
       <c r="B40" t="n">
-        <v>57896</v>
+        <v>8450</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>103021</v>
+        <v>106545</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr"/>
       <c r="L40" t="inlineStr"/>
       <c r="M40" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N40" t="inlineStr"/>
@@ -4613,10 +4616,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>444226</v>
+        <v>444413</v>
       </c>
       <c r="R40" t="n">
-        <v>6787236</v>
+        <v>6787314</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4657,6 +4660,7 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
+      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
@@ -4675,41 +4679,40 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129795193</v>
+        <v>129795165</v>
       </c>
       <c r="B41" t="n">
-        <v>8450</v>
+        <v>57733</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr"/>
       <c r="K41" t="inlineStr"/>
       <c r="L41" t="inlineStr"/>
       <c r="M41" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N41" t="inlineStr"/>
@@ -4719,10 +4722,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>444508</v>
+        <v>444251</v>
       </c>
       <c r="R41" t="n">
-        <v>6787352</v>
+        <v>6787376</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4763,7 +4766,6 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
-      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
@@ -4782,41 +4784,40 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129795202</v>
+        <v>129795133</v>
       </c>
       <c r="B42" t="n">
-        <v>8450</v>
+        <v>57896</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>106545</v>
+        <v>103021</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="J42" t="inlineStr"/>
       <c r="K42" t="inlineStr"/>
       <c r="L42" t="inlineStr"/>
       <c r="M42" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N42" t="inlineStr"/>
@@ -4826,10 +4827,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>444413</v>
+        <v>444226</v>
       </c>
       <c r="R42" t="n">
-        <v>6787314</v>
+        <v>6787236</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4870,7 +4871,6 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
-      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
@@ -4889,40 +4889,41 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129795158</v>
+        <v>129795170</v>
       </c>
       <c r="B43" t="n">
-        <v>57733</v>
+        <v>8450</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr"/>
       <c r="K43" t="inlineStr"/>
       <c r="L43" t="inlineStr"/>
       <c r="M43" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N43" t="inlineStr"/>
@@ -4932,10 +4933,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>444501</v>
+        <v>444172</v>
       </c>
       <c r="R43" t="n">
-        <v>6787402</v>
+        <v>6787202</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4976,6 +4977,7 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
+      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
@@ -4994,10 +4996,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129795293</v>
+        <v>129795158</v>
       </c>
       <c r="B44" t="n">
-        <v>79081</v>
+        <v>57733</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5005,34 +5007,42 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>444365</v>
+        <v>444501</v>
       </c>
       <c r="R44" t="n">
-        <v>6787285</v>
+        <v>6787402</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5065,11 +5075,6 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-11-22</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 50m.</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5096,10 +5101,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129795282</v>
+        <v>129795136</v>
       </c>
       <c r="B45" t="n">
-        <v>79081</v>
+        <v>91620</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5107,21 +5112,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5134,10 +5139,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>444374</v>
+        <v>444235</v>
       </c>
       <c r="R45" t="n">
-        <v>6787384</v>
+        <v>6787149</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5170,11 +5175,6 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-11-22</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 50 m.</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5202,54 +5202,45 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129795170</v>
+        <v>129795293</v>
       </c>
       <c r="B46" t="n">
-        <v>8450</v>
+        <v>79081</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="J46" t="inlineStr"/>
-      <c r="K46" t="inlineStr"/>
-      <c r="L46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>444172</v>
+        <v>444365</v>
       </c>
       <c r="R46" t="n">
-        <v>6787202</v>
+        <v>6787285</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5284,13 +5275,17 @@
           <t>2025-11-22</t>
         </is>
       </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 50m.</t>
+        </is>
+      </c>
       <c r="AD46" t="b">
         <v>0</v>
       </c>
       <c r="AE46" t="b">
         <v>0</v>
       </c>
-      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
@@ -5309,10 +5304,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129795136</v>
+        <v>129795282</v>
       </c>
       <c r="B47" t="n">
-        <v>91618</v>
+        <v>79081</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5320,21 +5315,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5347,10 +5342,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>444235</v>
+        <v>444374</v>
       </c>
       <c r="R47" t="n">
-        <v>6787149</v>
+        <v>6787384</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5383,6 +5378,11 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-11-22</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 50 m.</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5413,7 +5413,7 @@
         <v>129795138</v>
       </c>
       <c r="B48" t="n">
-        <v>91618</v>
+        <v>91620</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5909,7 +5909,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129795147</v>
+        <v>129795161</v>
       </c>
       <c r="B53" t="n">
         <v>57733</v>
@@ -5952,10 +5952,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>444220</v>
+        <v>444433</v>
       </c>
       <c r="R53" t="n">
-        <v>6787221</v>
+        <v>6787338</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6014,32 +6014,32 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129795131</v>
+        <v>129795147</v>
       </c>
       <c r="B54" t="n">
-        <v>56926</v>
+        <v>57733</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6047,7 +6047,7 @@
       <c r="L54" t="inlineStr"/>
       <c r="M54" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N54" t="inlineStr"/>
@@ -6057,10 +6057,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>444250</v>
+        <v>444220</v>
       </c>
       <c r="R54" t="n">
-        <v>6787212</v>
+        <v>6787221</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6119,32 +6119,32 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129795161</v>
+        <v>129795131</v>
       </c>
       <c r="B55" t="n">
-        <v>57733</v>
+        <v>56926</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6152,7 +6152,7 @@
       <c r="L55" t="inlineStr"/>
       <c r="M55" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="N55" t="inlineStr"/>
@@ -6162,10 +6162,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>444433</v>
+        <v>444250</v>
       </c>
       <c r="R55" t="n">
-        <v>6787338</v>
+        <v>6787212</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6224,45 +6224,54 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129795279</v>
+        <v>129795184</v>
       </c>
       <c r="B56" t="n">
-        <v>79081</v>
+        <v>8450</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
+      <c r="J56" t="inlineStr"/>
+      <c r="K56" t="inlineStr"/>
+      <c r="L56" t="inlineStr"/>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>444463</v>
+        <v>444452</v>
       </c>
       <c r="R56" t="n">
-        <v>6787459</v>
+        <v>6787305</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6303,6 +6312,7 @@
       <c r="AE56" t="b">
         <v>0</v>
       </c>
+      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
       </c>
@@ -6321,45 +6331,54 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129795277</v>
+        <v>129795172</v>
       </c>
       <c r="B57" t="n">
-        <v>79081</v>
+        <v>8450</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
+      <c r="J57" t="inlineStr"/>
+      <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>444491</v>
+        <v>444225</v>
       </c>
       <c r="R57" t="n">
-        <v>6787412</v>
+        <v>6787223</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6400,6 +6419,7 @@
       <c r="AE57" t="b">
         <v>0</v>
       </c>
+      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
@@ -6418,7 +6438,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129795184</v>
+        <v>129795199</v>
       </c>
       <c r="B58" t="n">
         <v>8450</v>
@@ -6462,10 +6482,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>444452</v>
+        <v>444431</v>
       </c>
       <c r="R58" t="n">
-        <v>6787305</v>
+        <v>6787350</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6525,54 +6545,45 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129795172</v>
+        <v>129795279</v>
       </c>
       <c r="B59" t="n">
-        <v>8450</v>
+        <v>79081</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
-      <c r="J59" t="inlineStr"/>
-      <c r="K59" t="inlineStr"/>
-      <c r="L59" t="inlineStr"/>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>444225</v>
+        <v>444463</v>
       </c>
       <c r="R59" t="n">
-        <v>6787223</v>
+        <v>6787459</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6613,7 +6624,6 @@
       <c r="AE59" t="b">
         <v>0</v>
       </c>
-      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
       </c>
@@ -6632,54 +6642,45 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129795199</v>
+        <v>129795277</v>
       </c>
       <c r="B60" t="n">
-        <v>8450</v>
+        <v>79081</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
-      <c r="J60" t="inlineStr"/>
-      <c r="K60" t="inlineStr"/>
-      <c r="L60" t="inlineStr"/>
-      <c r="M60" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>444431</v>
+        <v>444491</v>
       </c>
       <c r="R60" t="n">
-        <v>6787350</v>
+        <v>6787412</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6720,7 +6721,6 @@
       <c r="AE60" t="b">
         <v>0</v>
       </c>
-      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
       </c>
@@ -6941,40 +6941,41 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129795162</v>
+        <v>129795191</v>
       </c>
       <c r="B63" t="n">
-        <v>57733</v>
+        <v>8450</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
+      <c r="J63" t="inlineStr"/>
       <c r="K63" t="inlineStr"/>
       <c r="L63" t="inlineStr"/>
       <c r="M63" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N63" t="inlineStr"/>
@@ -6984,10 +6985,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>444428</v>
+        <v>444520</v>
       </c>
       <c r="R63" t="n">
-        <v>6787329</v>
+        <v>6787287</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7028,6 +7029,7 @@
       <c r="AE63" t="b">
         <v>0</v>
       </c>
+      <c r="AF63" t="inlineStr"/>
       <c r="AG63" t="b">
         <v>0</v>
       </c>
@@ -7046,7 +7048,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129795191</v>
+        <v>129795195</v>
       </c>
       <c r="B64" t="n">
         <v>8450</v>
@@ -7090,10 +7092,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>444520</v>
+        <v>444487</v>
       </c>
       <c r="R64" t="n">
-        <v>6787287</v>
+        <v>6787441</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7153,7 +7155,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129795195</v>
+        <v>129795177</v>
       </c>
       <c r="B65" t="n">
         <v>8450</v>
@@ -7187,7 +7189,7 @@
       <c r="L65" t="inlineStr"/>
       <c r="M65" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="N65" t="inlineStr"/>
@@ -7197,10 +7199,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>444487</v>
+        <v>444342</v>
       </c>
       <c r="R65" t="n">
-        <v>6787441</v>
+        <v>6787223</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7260,41 +7262,40 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129795177</v>
+        <v>129795162</v>
       </c>
       <c r="B66" t="n">
-        <v>8450</v>
+        <v>57733</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
-      <c r="J66" t="inlineStr"/>
       <c r="K66" t="inlineStr"/>
       <c r="L66" t="inlineStr"/>
       <c r="M66" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N66" t="inlineStr"/>
@@ -7304,10 +7305,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>444342</v>
+        <v>444428</v>
       </c>
       <c r="R66" t="n">
-        <v>6787223</v>
+        <v>6787329</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7348,7 +7349,6 @@
       <c r="AE66" t="b">
         <v>0</v>
       </c>
-      <c r="AF66" t="inlineStr"/>
       <c r="AG66" t="b">
         <v>0</v>
       </c>
@@ -7569,43 +7569,37 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129795182</v>
+        <v>129795135</v>
       </c>
       <c r="B69" t="n">
-        <v>8450</v>
+        <v>91620</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>106545</v>
+        <v>5442</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
       <c r="J69" t="inlineStr"/>
       <c r="K69" t="inlineStr"/>
-      <c r="L69" t="inlineStr"/>
-      <c r="M69" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
@@ -7613,10 +7607,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>444417</v>
+        <v>444158</v>
       </c>
       <c r="R69" t="n">
-        <v>6787266</v>
+        <v>6787148</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7676,53 +7670,45 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129795208</v>
+        <v>129795243</v>
       </c>
       <c r="B70" t="n">
-        <v>58106</v>
+        <v>79081</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>103015</v>
+        <v>6425</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
-      <c r="K70" t="inlineStr"/>
-      <c r="L70" t="inlineStr"/>
-      <c r="M70" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>444434</v>
+        <v>444159</v>
       </c>
       <c r="R70" t="n">
-        <v>6787357</v>
+        <v>6787297</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7781,10 +7767,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129795135</v>
+        <v>129795287</v>
       </c>
       <c r="B71" t="n">
-        <v>91618</v>
+        <v>79081</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7792,37 +7778,34 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
-      <c r="J71" t="inlineStr"/>
-      <c r="K71" t="inlineStr"/>
-      <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>444158</v>
+        <v>444430</v>
       </c>
       <c r="R71" t="n">
-        <v>6787148</v>
+        <v>6787384</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7863,7 +7846,6 @@
       <c r="AE71" t="b">
         <v>0</v>
       </c>
-      <c r="AF71" t="inlineStr"/>
       <c r="AG71" t="b">
         <v>0</v>
       </c>
@@ -7882,10 +7864,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129795166</v>
+        <v>129795272</v>
       </c>
       <c r="B72" t="n">
-        <v>57733</v>
+        <v>79081</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7893,42 +7875,34 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
-      <c r="K72" t="inlineStr"/>
-      <c r="L72" t="inlineStr"/>
-      <c r="M72" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>444254</v>
+        <v>444553</v>
       </c>
       <c r="R72" t="n">
-        <v>6787333</v>
+        <v>6787299</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7987,10 +7961,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129795243</v>
+        <v>129795166</v>
       </c>
       <c r="B73" t="n">
-        <v>79081</v>
+        <v>57733</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7998,34 +7972,42 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
+      <c r="K73" t="inlineStr"/>
+      <c r="L73" t="inlineStr"/>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>444159</v>
+        <v>444254</v>
       </c>
       <c r="R73" t="n">
-        <v>6787297</v>
+        <v>6787333</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8084,7 +8066,7 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129795287</v>
+        <v>129795280</v>
       </c>
       <c r="B74" t="n">
         <v>79081</v>
@@ -8119,10 +8101,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>444430</v>
+        <v>444451</v>
       </c>
       <c r="R74" t="n">
-        <v>6787384</v>
+        <v>6787467</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8181,7 +8163,7 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129795272</v>
+        <v>129795284</v>
       </c>
       <c r="B75" t="n">
         <v>79081</v>
@@ -8216,10 +8198,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>444553</v>
+        <v>444363</v>
       </c>
       <c r="R75" t="n">
-        <v>6787299</v>
+        <v>6787411</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8278,45 +8260,53 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129795280</v>
+        <v>129795208</v>
       </c>
       <c r="B76" t="n">
-        <v>79081</v>
+        <v>58106</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6425</v>
+        <v>103015</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
+      <c r="K76" t="inlineStr"/>
+      <c r="L76" t="inlineStr"/>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>444451</v>
+        <v>444434</v>
       </c>
       <c r="R76" t="n">
-        <v>6787467</v>
+        <v>6787357</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8375,45 +8365,54 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129795284</v>
+        <v>129795182</v>
       </c>
       <c r="B77" t="n">
-        <v>79081</v>
+        <v>8450</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
+      <c r="J77" t="inlineStr"/>
+      <c r="K77" t="inlineStr"/>
+      <c r="L77" t="inlineStr"/>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>444363</v>
+        <v>444417</v>
       </c>
       <c r="R77" t="n">
-        <v>6787411</v>
+        <v>6787266</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8454,6 +8453,7 @@
       <c r="AE77" t="b">
         <v>0</v>
       </c>
+      <c r="AF77" t="inlineStr"/>
       <c r="AG77" t="b">
         <v>0</v>
       </c>
@@ -8472,10 +8472,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129795126</v>
+        <v>129795307</v>
       </c>
       <c r="B78" t="n">
-        <v>79700</v>
+        <v>79081</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8483,21 +8483,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8507,10 +8507,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>444358</v>
+        <v>444134</v>
       </c>
       <c r="R78" t="n">
-        <v>6787400</v>
+        <v>6787304</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8569,10 +8569,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129795127</v>
+        <v>129795286</v>
       </c>
       <c r="B79" t="n">
-        <v>79700</v>
+        <v>79081</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8580,31 +8580,34 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
+      <c r="J79" t="inlineStr"/>
+      <c r="K79" t="inlineStr"/>
+      <c r="N79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>444432</v>
+        <v>444440</v>
       </c>
       <c r="R79" t="n">
         <v>6787388</v>
@@ -8642,12 +8645,18 @@
           <t>2025-11-22</t>
         </is>
       </c>
+      <c r="AC79" t="inlineStr">
+        <is>
+          <t>Gott om garnlav inom en radie av 50 m.</t>
+        </is>
+      </c>
       <c r="AD79" t="b">
         <v>0</v>
       </c>
       <c r="AE79" t="b">
         <v>0</v>
       </c>
+      <c r="AF79" t="inlineStr"/>
       <c r="AG79" t="b">
         <v>0</v>
       </c>
@@ -8666,7 +8675,7 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129795307</v>
+        <v>129795300</v>
       </c>
       <c r="B80" t="n">
         <v>79081</v>
@@ -8695,16 +8704,19 @@
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
+      <c r="J80" t="inlineStr"/>
+      <c r="K80" t="inlineStr"/>
+      <c r="N80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>444134</v>
+        <v>444264</v>
       </c>
       <c r="R80" t="n">
-        <v>6787304</v>
+        <v>6787349</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8739,12 +8751,18 @@
           <t>2025-11-22</t>
         </is>
       </c>
+      <c r="AC80" t="inlineStr">
+        <is>
+          <t>Garnlav i de flesta träd inom en radie av 50 m.</t>
+        </is>
+      </c>
       <c r="AD80" t="b">
         <v>0</v>
       </c>
       <c r="AE80" t="b">
         <v>0</v>
       </c>
+      <c r="AF80" t="inlineStr"/>
       <c r="AG80" t="b">
         <v>0</v>
       </c>
@@ -8763,10 +8781,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129795286</v>
+        <v>129795126</v>
       </c>
       <c r="B81" t="n">
-        <v>79081</v>
+        <v>79700</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8774,37 +8792,34 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
-      <c r="J81" t="inlineStr"/>
-      <c r="K81" t="inlineStr"/>
-      <c r="N81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>444440</v>
+        <v>444358</v>
       </c>
       <c r="R81" t="n">
-        <v>6787388</v>
+        <v>6787400</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8839,18 +8854,12 @@
           <t>2025-11-22</t>
         </is>
       </c>
-      <c r="AC81" t="inlineStr">
-        <is>
-          <t>Gott om garnlav inom en radie av 50 m.</t>
-        </is>
-      </c>
       <c r="AD81" t="b">
         <v>0</v>
       </c>
       <c r="AE81" t="b">
         <v>0</v>
       </c>
-      <c r="AF81" t="inlineStr"/>
       <c r="AG81" t="b">
         <v>0</v>
       </c>
@@ -8869,7 +8878,7 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129795300</v>
+        <v>129795241</v>
       </c>
       <c r="B82" t="n">
         <v>79081</v>
@@ -8898,19 +8907,16 @@
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
-      <c r="J82" t="inlineStr"/>
-      <c r="K82" t="inlineStr"/>
-      <c r="N82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>444264</v>
+        <v>444117</v>
       </c>
       <c r="R82" t="n">
-        <v>6787349</v>
+        <v>6787277</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8945,18 +8951,12 @@
           <t>2025-11-22</t>
         </is>
       </c>
-      <c r="AC82" t="inlineStr">
-        <is>
-          <t>Garnlav i de flesta träd inom en radie av 50 m.</t>
-        </is>
-      </c>
       <c r="AD82" t="b">
         <v>0</v>
       </c>
       <c r="AE82" t="b">
         <v>0</v>
       </c>
-      <c r="AF82" t="inlineStr"/>
       <c r="AG82" t="b">
         <v>0</v>
       </c>
@@ -8975,10 +8975,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129795241</v>
+        <v>129795127</v>
       </c>
       <c r="B83" t="n">
-        <v>79081</v>
+        <v>79700</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8986,21 +8986,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9010,10 +9010,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>444117</v>
+        <v>444432</v>
       </c>
       <c r="R83" t="n">
-        <v>6787277</v>
+        <v>6787388</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9694,10 +9694,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>129795121</v>
+        <v>129795152</v>
       </c>
       <c r="B90" t="n">
-        <v>79700</v>
+        <v>57733</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9705,34 +9705,42 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
+      <c r="K90" t="inlineStr"/>
+      <c r="L90" t="inlineStr"/>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>444254</v>
+        <v>444434</v>
       </c>
       <c r="R90" t="n">
-        <v>6787204</v>
+        <v>6787304</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9791,7 +9799,7 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>129795124</v>
+        <v>129795121</v>
       </c>
       <c r="B91" t="n">
         <v>79700</v>
@@ -9826,10 +9834,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>444393</v>
+        <v>444254</v>
       </c>
       <c r="R91" t="n">
-        <v>6787395</v>
+        <v>6787204</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9888,10 +9896,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>129795123</v>
+        <v>129795297</v>
       </c>
       <c r="B92" t="n">
-        <v>79700</v>
+        <v>79081</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9899,21 +9907,21 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -9923,10 +9931,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>444530</v>
+        <v>444297</v>
       </c>
       <c r="R92" t="n">
-        <v>6787326</v>
+        <v>6787333</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9985,10 +9993,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>129795152</v>
+        <v>129795252</v>
       </c>
       <c r="B93" t="n">
-        <v>57733</v>
+        <v>79081</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9996,42 +10004,34 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
-      <c r="K93" t="inlineStr"/>
-      <c r="L93" t="inlineStr"/>
-      <c r="M93" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>444434</v>
+        <v>444249</v>
       </c>
       <c r="R93" t="n">
-        <v>6787304</v>
+        <v>6787249</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10064,6 +10064,11 @@
       <c r="AA93" t="inlineStr">
         <is>
           <t>2025-11-22</t>
+        </is>
+      </c>
+      <c r="AC93" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 40m.</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10090,7 +10095,7 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>129795297</v>
+        <v>129795245</v>
       </c>
       <c r="B94" t="n">
         <v>79081</v>
@@ -10125,10 +10130,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>444297</v>
+        <v>444113</v>
       </c>
       <c r="R94" t="n">
-        <v>6787333</v>
+        <v>6787239</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10187,10 +10192,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>129795252</v>
+        <v>129795123</v>
       </c>
       <c r="B95" t="n">
-        <v>79081</v>
+        <v>79700</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10198,21 +10203,21 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10222,10 +10227,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>444249</v>
+        <v>444530</v>
       </c>
       <c r="R95" t="n">
-        <v>6787249</v>
+        <v>6787326</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10258,11 +10263,6 @@
       <c r="AA95" t="inlineStr">
         <is>
           <t>2025-11-22</t>
-        </is>
-      </c>
-      <c r="AC95" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 40m.</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10289,7 +10289,7 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>129795245</v>
+        <v>129795288</v>
       </c>
       <c r="B96" t="n">
         <v>79081</v>
@@ -10324,10 +10324,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>444113</v>
+        <v>444420</v>
       </c>
       <c r="R96" t="n">
-        <v>6787239</v>
+        <v>6787366</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10386,7 +10386,7 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>129795288</v>
+        <v>129795305</v>
       </c>
       <c r="B97" t="n">
         <v>79081</v>
@@ -10421,10 +10421,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>444420</v>
+        <v>444169</v>
       </c>
       <c r="R97" t="n">
-        <v>6787366</v>
+        <v>6787323</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10483,10 +10483,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>129795305</v>
+        <v>129795124</v>
       </c>
       <c r="B98" t="n">
-        <v>79081</v>
+        <v>79700</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10494,21 +10494,21 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10518,10 +10518,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>444169</v>
+        <v>444393</v>
       </c>
       <c r="R98" t="n">
-        <v>6787323</v>
+        <v>6787395</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10784,7 +10784,7 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>129795185</v>
+        <v>129795186</v>
       </c>
       <c r="B101" t="n">
         <v>8450</v>
@@ -10828,10 +10828,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>444458</v>
+        <v>444473</v>
       </c>
       <c r="R101" t="n">
-        <v>6787304</v>
+        <v>6787334</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10891,7 +10891,7 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>129795180</v>
+        <v>129795185</v>
       </c>
       <c r="B102" t="n">
         <v>8450</v>
@@ -10935,10 +10935,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>444409</v>
+        <v>444458</v>
       </c>
       <c r="R102" t="n">
-        <v>6787219</v>
+        <v>6787304</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -10998,7 +10998,7 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>129795178</v>
+        <v>129795180</v>
       </c>
       <c r="B103" t="n">
         <v>8450</v>
@@ -11042,10 +11042,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>444375</v>
+        <v>444409</v>
       </c>
       <c r="R103" t="n">
-        <v>6787207</v>
+        <v>6787219</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11105,7 +11105,7 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>129795186</v>
+        <v>129795178</v>
       </c>
       <c r="B104" t="n">
         <v>8450</v>
@@ -11149,10 +11149,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>444473</v>
+        <v>444375</v>
       </c>
       <c r="R104" t="n">
-        <v>6787334</v>
+        <v>6787207</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11707,40 +11707,41 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>129795145</v>
+        <v>129795203</v>
       </c>
       <c r="B110" t="n">
-        <v>57733</v>
+        <v>8450</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
+      <c r="J110" t="inlineStr"/>
       <c r="K110" t="inlineStr"/>
       <c r="L110" t="inlineStr"/>
       <c r="M110" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N110" t="inlineStr"/>
@@ -11750,10 +11751,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>444228</v>
+        <v>444401</v>
       </c>
       <c r="R110" t="n">
-        <v>6787226</v>
+        <v>6787298</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11794,6 +11795,7 @@
       <c r="AE110" t="b">
         <v>0</v>
       </c>
+      <c r="AF110" t="inlineStr"/>
       <c r="AG110" t="b">
         <v>0</v>
       </c>
@@ -11812,7 +11814,7 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>129795149</v>
+        <v>129795151</v>
       </c>
       <c r="B111" t="n">
         <v>57733</v>
@@ -11845,7 +11847,7 @@
       <c r="L111" t="inlineStr"/>
       <c r="M111" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N111" t="inlineStr"/>
@@ -11855,10 +11857,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>444223</v>
+        <v>444425</v>
       </c>
       <c r="R111" t="n">
-        <v>6787221</v>
+        <v>6787278</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -11917,10 +11919,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>129795151</v>
+        <v>129795259</v>
       </c>
       <c r="B112" t="n">
-        <v>57733</v>
+        <v>79081</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -11928,42 +11930,34 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
-      <c r="K112" t="inlineStr"/>
-      <c r="L112" t="inlineStr"/>
-      <c r="M112" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N112" t="inlineStr"/>
       <c r="P112" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>444425</v>
+        <v>444164</v>
       </c>
       <c r="R112" t="n">
-        <v>6787278</v>
+        <v>6787121</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12022,45 +12016,54 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>129795259</v>
+        <v>129795201</v>
       </c>
       <c r="B113" t="n">
-        <v>79081</v>
+        <v>8450</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
+      <c r="J113" t="inlineStr"/>
+      <c r="K113" t="inlineStr"/>
+      <c r="L113" t="inlineStr"/>
+      <c r="M113" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N113" t="inlineStr"/>
       <c r="P113" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>444164</v>
+        <v>444430</v>
       </c>
       <c r="R113" t="n">
-        <v>6787121</v>
+        <v>6787332</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12101,6 +12104,7 @@
       <c r="AE113" t="b">
         <v>0</v>
       </c>
+      <c r="AF113" t="inlineStr"/>
       <c r="AG113" t="b">
         <v>0</v>
       </c>
@@ -12119,41 +12123,40 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>129795203</v>
+        <v>129795149</v>
       </c>
       <c r="B114" t="n">
-        <v>8450</v>
+        <v>57733</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
-      <c r="J114" t="inlineStr"/>
       <c r="K114" t="inlineStr"/>
       <c r="L114" t="inlineStr"/>
       <c r="M114" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N114" t="inlineStr"/>
@@ -12163,10 +12166,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>444401</v>
+        <v>444223</v>
       </c>
       <c r="R114" t="n">
-        <v>6787298</v>
+        <v>6787221</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12207,7 +12210,6 @@
       <c r="AE114" t="b">
         <v>0</v>
       </c>
-      <c r="AF114" t="inlineStr"/>
       <c r="AG114" t="b">
         <v>0</v>
       </c>
@@ -12226,41 +12228,40 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>129795201</v>
+        <v>129795145</v>
       </c>
       <c r="B115" t="n">
-        <v>8450</v>
+        <v>57733</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
-      <c r="J115" t="inlineStr"/>
       <c r="K115" t="inlineStr"/>
       <c r="L115" t="inlineStr"/>
       <c r="M115" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N115" t="inlineStr"/>
@@ -12270,10 +12271,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>444430</v>
+        <v>444228</v>
       </c>
       <c r="R115" t="n">
-        <v>6787332</v>
+        <v>6787226</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12314,7 +12315,6 @@
       <c r="AE115" t="b">
         <v>0</v>
       </c>
-      <c r="AF115" t="inlineStr"/>
       <c r="AG115" t="b">
         <v>0</v>
       </c>
@@ -12333,10 +12333,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>129795157</v>
+        <v>129795289</v>
       </c>
       <c r="B116" t="n">
-        <v>57733</v>
+        <v>79081</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -12344,42 +12344,34 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
-      <c r="K116" t="inlineStr"/>
-      <c r="L116" t="inlineStr"/>
-      <c r="M116" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N116" t="inlineStr"/>
       <c r="P116" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>444525</v>
+        <v>444435</v>
       </c>
       <c r="R116" t="n">
-        <v>6787344</v>
+        <v>6787341</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12860,10 +12852,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>129795289</v>
+        <v>129795157</v>
       </c>
       <c r="B121" t="n">
-        <v>79081</v>
+        <v>57733</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -12871,34 +12863,42 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
+      <c r="K121" t="inlineStr"/>
+      <c r="L121" t="inlineStr"/>
+      <c r="M121" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N121" t="inlineStr"/>
       <c r="P121" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>444435</v>
+        <v>444525</v>
       </c>
       <c r="R121" t="n">
-        <v>6787341</v>
+        <v>6787344</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -13062,54 +13062,45 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>129795188</v>
+        <v>129795294</v>
       </c>
       <c r="B123" t="n">
-        <v>8450</v>
+        <v>79081</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
-      <c r="J123" t="inlineStr"/>
-      <c r="K123" t="inlineStr"/>
-      <c r="L123" t="inlineStr"/>
-      <c r="M123" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N123" t="inlineStr"/>
       <c r="P123" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>444498</v>
+        <v>444323</v>
       </c>
       <c r="R123" t="n">
-        <v>6787280</v>
+        <v>6787297</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13150,7 +13141,6 @@
       <c r="AE123" t="b">
         <v>0</v>
       </c>
-      <c r="AF123" t="inlineStr"/>
       <c r="AG123" t="b">
         <v>0</v>
       </c>
@@ -13169,54 +13159,45 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>129795179</v>
+        <v>129795301</v>
       </c>
       <c r="B124" t="n">
-        <v>8450</v>
+        <v>79081</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
-      <c r="J124" t="inlineStr"/>
-      <c r="K124" t="inlineStr"/>
-      <c r="L124" t="inlineStr"/>
-      <c r="M124" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N124" t="inlineStr"/>
       <c r="P124" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>444378</v>
+        <v>444250</v>
       </c>
       <c r="R124" t="n">
-        <v>6787236</v>
+        <v>6787342</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13257,7 +13238,6 @@
       <c r="AE124" t="b">
         <v>0</v>
       </c>
-      <c r="AF124" t="inlineStr"/>
       <c r="AG124" t="b">
         <v>0</v>
       </c>
@@ -13276,45 +13256,54 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>129795301</v>
+        <v>129795188</v>
       </c>
       <c r="B125" t="n">
-        <v>79081</v>
+        <v>8450</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
+      <c r="J125" t="inlineStr"/>
+      <c r="K125" t="inlineStr"/>
+      <c r="L125" t="inlineStr"/>
+      <c r="M125" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N125" t="inlineStr"/>
       <c r="P125" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>444250</v>
+        <v>444498</v>
       </c>
       <c r="R125" t="n">
-        <v>6787342</v>
+        <v>6787280</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13355,6 +13344,7 @@
       <c r="AE125" t="b">
         <v>0</v>
       </c>
+      <c r="AF125" t="inlineStr"/>
       <c r="AG125" t="b">
         <v>0</v>
       </c>
@@ -13373,45 +13363,54 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>129795294</v>
+        <v>129795179</v>
       </c>
       <c r="B126" t="n">
-        <v>79081</v>
+        <v>8450</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
+      <c r="J126" t="inlineStr"/>
+      <c r="K126" t="inlineStr"/>
+      <c r="L126" t="inlineStr"/>
+      <c r="M126" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N126" t="inlineStr"/>
       <c r="P126" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>444323</v>
+        <v>444378</v>
       </c>
       <c r="R126" t="n">
-        <v>6787297</v>
+        <v>6787236</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -13452,6 +13451,7 @@
       <c r="AE126" t="b">
         <v>0</v>
       </c>
+      <c r="AF126" t="inlineStr"/>
       <c r="AG126" t="b">
         <v>0</v>
       </c>
@@ -13470,10 +13470,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>129795275</v>
+        <v>129795159</v>
       </c>
       <c r="B127" t="n">
-        <v>79081</v>
+        <v>57733</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -13481,34 +13481,42 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
+      <c r="K127" t="inlineStr"/>
+      <c r="L127" t="inlineStr"/>
+      <c r="M127" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N127" t="inlineStr"/>
       <c r="P127" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>444495</v>
+        <v>444436</v>
       </c>
       <c r="R127" t="n">
-        <v>6787340</v>
+        <v>6787463</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -13567,45 +13575,54 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>129795263</v>
+        <v>129795175</v>
       </c>
       <c r="B128" t="n">
-        <v>79081</v>
+        <v>8450</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
+      <c r="J128" t="inlineStr"/>
+      <c r="K128" t="inlineStr"/>
+      <c r="L128" t="inlineStr"/>
+      <c r="M128" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N128" t="inlineStr"/>
       <c r="P128" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>444241</v>
+        <v>444182</v>
       </c>
       <c r="R128" t="n">
-        <v>6787149</v>
+        <v>6787101</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -13646,6 +13663,7 @@
       <c r="AE128" t="b">
         <v>0</v>
       </c>
+      <c r="AF128" t="inlineStr"/>
       <c r="AG128" t="b">
         <v>0</v>
       </c>
@@ -13664,45 +13682,54 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>129795267</v>
+        <v>129795168</v>
       </c>
       <c r="B129" t="n">
-        <v>79081</v>
+        <v>8450</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
+      <c r="J129" t="inlineStr"/>
+      <c r="K129" t="inlineStr"/>
+      <c r="L129" t="inlineStr"/>
+      <c r="M129" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N129" t="inlineStr"/>
       <c r="P129" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>444353</v>
+        <v>444272</v>
       </c>
       <c r="R129" t="n">
-        <v>6787215</v>
+        <v>6787286</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -13737,17 +13764,13 @@
           <t>2025-11-22</t>
         </is>
       </c>
-      <c r="AC129" t="inlineStr">
-        <is>
-          <t>Gott om garnlav inom en radie av 40m.</t>
-        </is>
-      </c>
       <c r="AD129" t="b">
         <v>0</v>
       </c>
       <c r="AE129" t="b">
         <v>0</v>
       </c>
+      <c r="AF129" t="inlineStr"/>
       <c r="AG129" t="b">
         <v>0</v>
       </c>
@@ -13766,10 +13789,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>129795258</v>
+        <v>129795137</v>
       </c>
       <c r="B130" t="n">
-        <v>79081</v>
+        <v>91620</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -13777,34 +13800,37 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
+      <c r="J130" t="inlineStr"/>
+      <c r="K130" t="inlineStr"/>
+      <c r="N130" t="inlineStr"/>
       <c r="P130" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>444174</v>
+        <v>444203</v>
       </c>
       <c r="R130" t="n">
-        <v>6787136</v>
+        <v>6787221</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -13845,6 +13871,7 @@
       <c r="AE130" t="b">
         <v>0</v>
       </c>
+      <c r="AF130" t="inlineStr"/>
       <c r="AG130" t="b">
         <v>0</v>
       </c>
@@ -13863,10 +13890,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>129795159</v>
+        <v>129795275</v>
       </c>
       <c r="B131" t="n">
-        <v>57733</v>
+        <v>79081</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -13874,42 +13901,34 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
-      <c r="K131" t="inlineStr"/>
-      <c r="L131" t="inlineStr"/>
-      <c r="M131" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N131" t="inlineStr"/>
       <c r="P131" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>444436</v>
+        <v>444495</v>
       </c>
       <c r="R131" t="n">
-        <v>6787463</v>
+        <v>6787340</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -13968,54 +13987,45 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>129795175</v>
+        <v>129795263</v>
       </c>
       <c r="B132" t="n">
-        <v>8450</v>
+        <v>79081</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
-      <c r="J132" t="inlineStr"/>
-      <c r="K132" t="inlineStr"/>
-      <c r="L132" t="inlineStr"/>
-      <c r="M132" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N132" t="inlineStr"/>
       <c r="P132" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>444182</v>
+        <v>444241</v>
       </c>
       <c r="R132" t="n">
-        <v>6787101</v>
+        <v>6787149</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -14056,7 +14066,6 @@
       <c r="AE132" t="b">
         <v>0</v>
       </c>
-      <c r="AF132" t="inlineStr"/>
       <c r="AG132" t="b">
         <v>0</v>
       </c>
@@ -14075,54 +14084,45 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>129795168</v>
+        <v>129795267</v>
       </c>
       <c r="B133" t="n">
-        <v>8450</v>
+        <v>79081</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
-      <c r="J133" t="inlineStr"/>
-      <c r="K133" t="inlineStr"/>
-      <c r="L133" t="inlineStr"/>
-      <c r="M133" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N133" t="inlineStr"/>
       <c r="P133" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>444272</v>
+        <v>444353</v>
       </c>
       <c r="R133" t="n">
-        <v>6787286</v>
+        <v>6787215</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -14157,13 +14157,17 @@
           <t>2025-11-22</t>
         </is>
       </c>
+      <c r="AC133" t="inlineStr">
+        <is>
+          <t>Gott om garnlav inom en radie av 40m.</t>
+        </is>
+      </c>
       <c r="AD133" t="b">
         <v>0</v>
       </c>
       <c r="AE133" t="b">
         <v>0</v>
       </c>
-      <c r="AF133" t="inlineStr"/>
       <c r="AG133" t="b">
         <v>0</v>
       </c>
@@ -14182,10 +14186,10 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>129795137</v>
+        <v>129795258</v>
       </c>
       <c r="B134" t="n">
-        <v>91618</v>
+        <v>79081</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -14193,37 +14197,34 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
-      <c r="J134" t="inlineStr"/>
-      <c r="K134" t="inlineStr"/>
-      <c r="N134" t="inlineStr"/>
       <c r="P134" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>444203</v>
+        <v>444174</v>
       </c>
       <c r="R134" t="n">
-        <v>6787221</v>
+        <v>6787136</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -14264,7 +14265,6 @@
       <c r="AE134" t="b">
         <v>0</v>
       </c>
-      <c r="AF134" t="inlineStr"/>
       <c r="AG134" t="b">
         <v>0</v>
       </c>
@@ -14283,37 +14283,43 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>129795254</v>
+        <v>129795204</v>
       </c>
       <c r="B135" t="n">
-        <v>79081</v>
+        <v>8450</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
       <c r="J135" t="inlineStr"/>
       <c r="K135" t="inlineStr"/>
+      <c r="L135" t="inlineStr"/>
+      <c r="M135" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N135" t="inlineStr"/>
       <c r="P135" t="inlineStr">
         <is>
@@ -14321,10 +14327,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>444199</v>
+        <v>444380</v>
       </c>
       <c r="R135" t="n">
-        <v>6787221</v>
+        <v>6787306</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -14384,10 +14390,10 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>129795266</v>
+        <v>129795139</v>
       </c>
       <c r="B136" t="n">
-        <v>79081</v>
+        <v>91620</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -14395,34 +14401,37 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
+      <c r="J136" t="inlineStr"/>
+      <c r="K136" t="inlineStr"/>
+      <c r="N136" t="inlineStr"/>
       <c r="P136" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>444314</v>
+        <v>444342</v>
       </c>
       <c r="R136" t="n">
-        <v>6787212</v>
+        <v>6787240</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -14457,17 +14466,13 @@
           <t>2025-11-22</t>
         </is>
       </c>
-      <c r="AC136" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 40m</t>
-        </is>
-      </c>
       <c r="AD136" t="b">
         <v>0</v>
       </c>
       <c r="AE136" t="b">
         <v>0</v>
       </c>
+      <c r="AF136" t="inlineStr"/>
       <c r="AG136" t="b">
         <v>0</v>
       </c>
@@ -14486,7 +14491,7 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>129795302</v>
+        <v>129795247</v>
       </c>
       <c r="B137" t="n">
         <v>79081</v>
@@ -14521,10 +14526,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>444222</v>
+        <v>444225</v>
       </c>
       <c r="R137" t="n">
-        <v>6787345</v>
+        <v>6787275</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -14583,54 +14588,45 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>129795204</v>
+        <v>129795304</v>
       </c>
       <c r="B138" t="n">
-        <v>8450</v>
+        <v>79081</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E138" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
-      <c r="J138" t="inlineStr"/>
-      <c r="K138" t="inlineStr"/>
-      <c r="L138" t="inlineStr"/>
-      <c r="M138" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N138" t="inlineStr"/>
       <c r="P138" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>444380</v>
+        <v>444172</v>
       </c>
       <c r="R138" t="n">
-        <v>6787306</v>
+        <v>6787339</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -14671,7 +14667,6 @@
       <c r="AE138" t="b">
         <v>0</v>
       </c>
-      <c r="AF138" t="inlineStr"/>
       <c r="AG138" t="b">
         <v>0</v>
       </c>
@@ -14690,10 +14685,10 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>129795139</v>
+        <v>129795251</v>
       </c>
       <c r="B139" t="n">
-        <v>91618</v>
+        <v>79081</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -14701,21 +14696,21 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
@@ -14728,10 +14723,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>444342</v>
+        <v>444309</v>
       </c>
       <c r="R139" t="n">
-        <v>6787240</v>
+        <v>6787272</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -14888,7 +14883,7 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>129795247</v>
+        <v>129795254</v>
       </c>
       <c r="B141" t="n">
         <v>79081</v>
@@ -14917,16 +14912,19 @@
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
+      <c r="J141" t="inlineStr"/>
+      <c r="K141" t="inlineStr"/>
+      <c r="N141" t="inlineStr"/>
       <c r="P141" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>444225</v>
+        <v>444199</v>
       </c>
       <c r="R141" t="n">
-        <v>6787275</v>
+        <v>6787221</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -14967,6 +14965,7 @@
       <c r="AE141" t="b">
         <v>0</v>
       </c>
+      <c r="AF141" t="inlineStr"/>
       <c r="AG141" t="b">
         <v>0</v>
       </c>
@@ -14985,7 +14984,7 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>129795304</v>
+        <v>129795266</v>
       </c>
       <c r="B142" t="n">
         <v>79081</v>
@@ -15020,10 +15019,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>444172</v>
+        <v>444314</v>
       </c>
       <c r="R142" t="n">
-        <v>6787339</v>
+        <v>6787212</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -15056,6 +15055,11 @@
       <c r="AA142" t="inlineStr">
         <is>
           <t>2025-11-22</t>
+        </is>
+      </c>
+      <c r="AC142" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 40m</t>
         </is>
       </c>
       <c r="AD142" t="b">
@@ -15082,7 +15086,7 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>129795251</v>
+        <v>129795302</v>
       </c>
       <c r="B143" t="n">
         <v>79081</v>
@@ -15111,19 +15115,16 @@
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
-      <c r="J143" t="inlineStr"/>
-      <c r="K143" t="inlineStr"/>
-      <c r="N143" t="inlineStr"/>
       <c r="P143" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>444309</v>
+        <v>444222</v>
       </c>
       <c r="R143" t="n">
-        <v>6787272</v>
+        <v>6787345</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -15164,7 +15165,6 @@
       <c r="AE143" t="b">
         <v>0</v>
       </c>
-      <c r="AF143" t="inlineStr"/>
       <c r="AG143" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 51041-2025 artfynd.xlsx
+++ b/artfynd/A 51041-2025 artfynd.xlsx
@@ -675,43 +675,37 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129795169</v>
+        <v>129795283</v>
       </c>
       <c r="B2" t="n">
-        <v>8450</v>
+        <v>79081</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -719,10 +713,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>444272</v>
+        <v>444337</v>
       </c>
       <c r="R2" t="n">
-        <v>6787239</v>
+        <v>6787374</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -782,54 +776,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129795190</v>
+        <v>129795261</v>
       </c>
       <c r="B3" t="n">
-        <v>8450</v>
+        <v>79081</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>444510</v>
+        <v>444193</v>
       </c>
       <c r="R3" t="n">
-        <v>6787276</v>
+        <v>6787130</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -870,7 +855,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -889,54 +873,45 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129795197</v>
+        <v>129795253</v>
       </c>
       <c r="B4" t="n">
-        <v>8450</v>
+        <v>79081</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>444406</v>
+        <v>444185</v>
       </c>
       <c r="R4" t="n">
-        <v>6787392</v>
+        <v>6787247</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -971,13 +946,17 @@
           <t>2025-11-22</t>
         </is>
       </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Gott om garnlav inom en radie av 50 m.</t>
+        </is>
+      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -996,7 +975,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129795283</v>
+        <v>129795285</v>
       </c>
       <c r="B5" t="n">
         <v>79081</v>
@@ -1025,19 +1004,16 @@
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>444337</v>
+        <v>444405</v>
       </c>
       <c r="R5" t="n">
-        <v>6787374</v>
+        <v>6787405</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1078,7 +1054,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1097,7 +1072,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129795261</v>
+        <v>129795244</v>
       </c>
       <c r="B6" t="n">
         <v>79081</v>
@@ -1132,10 +1107,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>444193</v>
+        <v>444105</v>
       </c>
       <c r="R6" t="n">
-        <v>6787130</v>
+        <v>6787246</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1194,7 +1169,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129795253</v>
+        <v>129795291</v>
       </c>
       <c r="B7" t="n">
         <v>79081</v>
@@ -1229,10 +1204,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>444185</v>
+        <v>444412</v>
       </c>
       <c r="R7" t="n">
-        <v>6787247</v>
+        <v>6787307</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1265,11 +1240,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-11-22</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Gott om garnlav inom en radie av 50 m.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1296,7 +1266,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129795285</v>
+        <v>129795298</v>
       </c>
       <c r="B8" t="n">
         <v>79081</v>
@@ -1331,10 +1301,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>444405</v>
+        <v>444305</v>
       </c>
       <c r="R8" t="n">
-        <v>6787405</v>
+        <v>6787353</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1393,45 +1363,54 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129795244</v>
+        <v>129795169</v>
       </c>
       <c r="B9" t="n">
-        <v>79081</v>
+        <v>8450</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>444105</v>
+        <v>444272</v>
       </c>
       <c r="R9" t="n">
-        <v>6787246</v>
+        <v>6787239</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1472,6 +1451,7 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1490,45 +1470,54 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129795291</v>
+        <v>129795190</v>
       </c>
       <c r="B10" t="n">
-        <v>79081</v>
+        <v>8450</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>444412</v>
+        <v>444510</v>
       </c>
       <c r="R10" t="n">
-        <v>6787307</v>
+        <v>6787276</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1569,6 +1558,7 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1587,45 +1577,54 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129795298</v>
+        <v>129795197</v>
       </c>
       <c r="B11" t="n">
-        <v>79081</v>
+        <v>8450</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>444305</v>
+        <v>444406</v>
       </c>
       <c r="R11" t="n">
-        <v>6787353</v>
+        <v>6787392</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1666,6 +1665,7 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -2623,54 +2623,45 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129795206</v>
+        <v>129795265</v>
       </c>
       <c r="B21" t="n">
-        <v>8450</v>
+        <v>79081</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>444247</v>
+        <v>444278</v>
       </c>
       <c r="R21" t="n">
-        <v>6787328</v>
+        <v>6787163</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2711,7 +2702,6 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -2730,7 +2720,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129795265</v>
+        <v>129795278</v>
       </c>
       <c r="B22" t="n">
         <v>79081</v>
@@ -2765,10 +2755,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>444278</v>
+        <v>444465</v>
       </c>
       <c r="R22" t="n">
-        <v>6787163</v>
+        <v>6787451</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2827,7 +2817,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129795278</v>
+        <v>129795310</v>
       </c>
       <c r="B23" t="n">
         <v>79081</v>
@@ -2856,16 +2846,19 @@
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>444465</v>
+        <v>444488</v>
       </c>
       <c r="R23" t="n">
-        <v>6787451</v>
+        <v>6787445</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2900,12 +2893,18 @@
           <t>2025-11-22</t>
         </is>
       </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Gott om garnlav inom en radie av 40m</t>
+        </is>
+      </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -2924,7 +2923,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129795310</v>
+        <v>129795273</v>
       </c>
       <c r="B24" t="n">
         <v>79081</v>
@@ -2953,19 +2952,16 @@
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>444488</v>
+        <v>444548</v>
       </c>
       <c r="R24" t="n">
-        <v>6787445</v>
+        <v>6787330</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3000,18 +2996,12 @@
           <t>2025-11-22</t>
         </is>
       </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Gott om garnlav inom en radie av 40m</t>
-        </is>
-      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3030,45 +3020,54 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129795273</v>
+        <v>129795198</v>
       </c>
       <c r="B25" t="n">
-        <v>79081</v>
+        <v>8450</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>444548</v>
+        <v>444434</v>
       </c>
       <c r="R25" t="n">
-        <v>6787330</v>
+        <v>6787384</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3109,6 +3108,7 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3127,7 +3127,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129795198</v>
+        <v>129795207</v>
       </c>
       <c r="B26" t="n">
         <v>8450</v>
@@ -3171,10 +3171,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>444434</v>
+        <v>444221</v>
       </c>
       <c r="R26" t="n">
-        <v>6787384</v>
+        <v>6787340</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3234,7 +3234,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129795207</v>
+        <v>129795200</v>
       </c>
       <c r="B27" t="n">
         <v>8450</v>
@@ -3278,10 +3278,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>444221</v>
+        <v>444429</v>
       </c>
       <c r="R27" t="n">
-        <v>6787340</v>
+        <v>6787341</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3341,7 +3341,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129795200</v>
+        <v>129795206</v>
       </c>
       <c r="B28" t="n">
         <v>8450</v>
@@ -3385,10 +3385,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>444429</v>
+        <v>444247</v>
       </c>
       <c r="R28" t="n">
-        <v>6787341</v>
+        <v>6787328</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -6224,41 +6224,40 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129795184</v>
+        <v>129795134</v>
       </c>
       <c r="B56" t="n">
-        <v>8450</v>
+        <v>57896</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>106545</v>
+        <v>103021</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
-      <c r="J56" t="inlineStr"/>
       <c r="K56" t="inlineStr"/>
       <c r="L56" t="inlineStr"/>
       <c r="M56" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N56" t="inlineStr"/>
@@ -6268,10 +6267,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>444452</v>
+        <v>444289</v>
       </c>
       <c r="R56" t="n">
-        <v>6787305</v>
+        <v>6787357</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6312,7 +6311,6 @@
       <c r="AE56" t="b">
         <v>0</v>
       </c>
-      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
       </c>
@@ -6331,7 +6329,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129795172</v>
+        <v>129795184</v>
       </c>
       <c r="B57" t="n">
         <v>8450</v>
@@ -6375,10 +6373,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>444225</v>
+        <v>444452</v>
       </c>
       <c r="R57" t="n">
-        <v>6787223</v>
+        <v>6787305</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6438,7 +6436,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129795199</v>
+        <v>129795172</v>
       </c>
       <c r="B58" t="n">
         <v>8450</v>
@@ -6482,10 +6480,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>444431</v>
+        <v>444225</v>
       </c>
       <c r="R58" t="n">
-        <v>6787350</v>
+        <v>6787223</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6545,45 +6543,54 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129795279</v>
+        <v>129795199</v>
       </c>
       <c r="B59" t="n">
-        <v>79081</v>
+        <v>8450</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
+      <c r="J59" t="inlineStr"/>
+      <c r="K59" t="inlineStr"/>
+      <c r="L59" t="inlineStr"/>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>444463</v>
+        <v>444431</v>
       </c>
       <c r="R59" t="n">
-        <v>6787459</v>
+        <v>6787350</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6624,6 +6631,7 @@
       <c r="AE59" t="b">
         <v>0</v>
       </c>
+      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
       </c>
@@ -6642,7 +6650,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129795277</v>
+        <v>129795279</v>
       </c>
       <c r="B60" t="n">
         <v>79081</v>
@@ -6677,10 +6685,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>444491</v>
+        <v>444463</v>
       </c>
       <c r="R60" t="n">
-        <v>6787412</v>
+        <v>6787459</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6739,10 +6747,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129795134</v>
+        <v>129795277</v>
       </c>
       <c r="B61" t="n">
-        <v>57896</v>
+        <v>79081</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6750,42 +6758,34 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
-      <c r="K61" t="inlineStr"/>
-      <c r="L61" t="inlineStr"/>
-      <c r="M61" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>444289</v>
+        <v>444491</v>
       </c>
       <c r="R61" t="n">
-        <v>6787357</v>
+        <v>6787412</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6844,45 +6844,54 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129795125</v>
+        <v>129795191</v>
       </c>
       <c r="B62" t="n">
-        <v>79700</v>
+        <v>8450</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
+      <c r="J62" t="inlineStr"/>
+      <c r="K62" t="inlineStr"/>
+      <c r="L62" t="inlineStr"/>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>444329</v>
+        <v>444520</v>
       </c>
       <c r="R62" t="n">
-        <v>6787371</v>
+        <v>6787287</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6923,6 +6932,7 @@
       <c r="AE62" t="b">
         <v>0</v>
       </c>
+      <c r="AF62" t="inlineStr"/>
       <c r="AG62" t="b">
         <v>0</v>
       </c>
@@ -6941,7 +6951,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129795191</v>
+        <v>129795195</v>
       </c>
       <c r="B63" t="n">
         <v>8450</v>
@@ -6985,10 +6995,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>444520</v>
+        <v>444487</v>
       </c>
       <c r="R63" t="n">
-        <v>6787287</v>
+        <v>6787441</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7048,7 +7058,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129795195</v>
+        <v>129795177</v>
       </c>
       <c r="B64" t="n">
         <v>8450</v>
@@ -7082,7 +7092,7 @@
       <c r="L64" t="inlineStr"/>
       <c r="M64" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="N64" t="inlineStr"/>
@@ -7092,10 +7102,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>444487</v>
+        <v>444342</v>
       </c>
       <c r="R64" t="n">
-        <v>6787441</v>
+        <v>6787223</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7155,41 +7165,40 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129795177</v>
+        <v>129795162</v>
       </c>
       <c r="B65" t="n">
-        <v>8450</v>
+        <v>57733</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
-      <c r="J65" t="inlineStr"/>
       <c r="K65" t="inlineStr"/>
       <c r="L65" t="inlineStr"/>
       <c r="M65" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N65" t="inlineStr"/>
@@ -7199,10 +7208,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>444342</v>
+        <v>444428</v>
       </c>
       <c r="R65" t="n">
-        <v>6787223</v>
+        <v>6787329</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7243,7 +7252,6 @@
       <c r="AE65" t="b">
         <v>0</v>
       </c>
-      <c r="AF65" t="inlineStr"/>
       <c r="AG65" t="b">
         <v>0</v>
       </c>
@@ -7262,10 +7270,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129795162</v>
+        <v>129795125</v>
       </c>
       <c r="B66" t="n">
-        <v>57733</v>
+        <v>79700</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7273,42 +7281,34 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
-      <c r="K66" t="inlineStr"/>
-      <c r="L66" t="inlineStr"/>
-      <c r="M66" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>444428</v>
+        <v>444329</v>
       </c>
       <c r="R66" t="n">
-        <v>6787329</v>
+        <v>6787371</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7367,10 +7367,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129795150</v>
+        <v>129795257</v>
       </c>
       <c r="B67" t="n">
-        <v>57733</v>
+        <v>79081</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7378,42 +7378,34 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
-      <c r="K67" t="inlineStr"/>
-      <c r="L67" t="inlineStr"/>
-      <c r="M67" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>444413</v>
+        <v>444168</v>
       </c>
       <c r="R67" t="n">
-        <v>6787222</v>
+        <v>6787171</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7472,10 +7464,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129795257</v>
+        <v>129795150</v>
       </c>
       <c r="B68" t="n">
-        <v>79081</v>
+        <v>57733</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7483,34 +7475,42 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
+      <c r="K68" t="inlineStr"/>
+      <c r="L68" t="inlineStr"/>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>444168</v>
+        <v>444413</v>
       </c>
       <c r="R68" t="n">
-        <v>6787171</v>
+        <v>6787222</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7569,10 +7569,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129795135</v>
+        <v>129795280</v>
       </c>
       <c r="B69" t="n">
-        <v>91620</v>
+        <v>79081</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7580,37 +7580,34 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
-      <c r="J69" t="inlineStr"/>
-      <c r="K69" t="inlineStr"/>
-      <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>444158</v>
+        <v>444451</v>
       </c>
       <c r="R69" t="n">
-        <v>6787148</v>
+        <v>6787467</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7651,7 +7648,6 @@
       <c r="AE69" t="b">
         <v>0</v>
       </c>
-      <c r="AF69" t="inlineStr"/>
       <c r="AG69" t="b">
         <v>0</v>
       </c>
@@ -7670,7 +7666,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129795243</v>
+        <v>129795284</v>
       </c>
       <c r="B70" t="n">
         <v>79081</v>
@@ -7705,10 +7701,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>444159</v>
+        <v>444363</v>
       </c>
       <c r="R70" t="n">
-        <v>6787297</v>
+        <v>6787411</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7767,10 +7763,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129795287</v>
+        <v>129795166</v>
       </c>
       <c r="B71" t="n">
-        <v>79081</v>
+        <v>57733</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7778,34 +7774,42 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
+      <c r="K71" t="inlineStr"/>
+      <c r="L71" t="inlineStr"/>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>444430</v>
+        <v>444254</v>
       </c>
       <c r="R71" t="n">
-        <v>6787384</v>
+        <v>6787333</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7864,10 +7868,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129795272</v>
+        <v>129795135</v>
       </c>
       <c r="B72" t="n">
-        <v>79081</v>
+        <v>91620</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7875,34 +7879,37 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
+      <c r="J72" t="inlineStr"/>
+      <c r="K72" t="inlineStr"/>
+      <c r="N72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>444553</v>
+        <v>444158</v>
       </c>
       <c r="R72" t="n">
-        <v>6787299</v>
+        <v>6787148</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7943,6 +7950,7 @@
       <c r="AE72" t="b">
         <v>0</v>
       </c>
+      <c r="AF72" t="inlineStr"/>
       <c r="AG72" t="b">
         <v>0</v>
       </c>
@@ -7961,10 +7969,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129795166</v>
+        <v>129795243</v>
       </c>
       <c r="B73" t="n">
-        <v>57733</v>
+        <v>79081</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7972,42 +7980,34 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
-      <c r="K73" t="inlineStr"/>
-      <c r="L73" t="inlineStr"/>
-      <c r="M73" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>444254</v>
+        <v>444159</v>
       </c>
       <c r="R73" t="n">
-        <v>6787333</v>
+        <v>6787297</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8066,7 +8066,7 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129795280</v>
+        <v>129795287</v>
       </c>
       <c r="B74" t="n">
         <v>79081</v>
@@ -8101,10 +8101,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>444451</v>
+        <v>444430</v>
       </c>
       <c r="R74" t="n">
-        <v>6787467</v>
+        <v>6787384</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8163,7 +8163,7 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129795284</v>
+        <v>129795272</v>
       </c>
       <c r="B75" t="n">
         <v>79081</v>
@@ -8198,10 +8198,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>444363</v>
+        <v>444553</v>
       </c>
       <c r="R75" t="n">
-        <v>6787411</v>
+        <v>6787299</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8472,10 +8472,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129795307</v>
+        <v>129795126</v>
       </c>
       <c r="B78" t="n">
-        <v>79081</v>
+        <v>79700</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8483,21 +8483,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8507,10 +8507,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>444134</v>
+        <v>444358</v>
       </c>
       <c r="R78" t="n">
-        <v>6787304</v>
+        <v>6787400</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8569,7 +8569,7 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129795286</v>
+        <v>129795307</v>
       </c>
       <c r="B79" t="n">
         <v>79081</v>
@@ -8598,19 +8598,16 @@
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
-      <c r="J79" t="inlineStr"/>
-      <c r="K79" t="inlineStr"/>
-      <c r="N79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>444440</v>
+        <v>444134</v>
       </c>
       <c r="R79" t="n">
-        <v>6787388</v>
+        <v>6787304</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8645,18 +8642,12 @@
           <t>2025-11-22</t>
         </is>
       </c>
-      <c r="AC79" t="inlineStr">
-        <is>
-          <t>Gott om garnlav inom en radie av 50 m.</t>
-        </is>
-      </c>
       <c r="AD79" t="b">
         <v>0</v>
       </c>
       <c r="AE79" t="b">
         <v>0</v>
       </c>
-      <c r="AF79" t="inlineStr"/>
       <c r="AG79" t="b">
         <v>0</v>
       </c>
@@ -8675,7 +8666,7 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129795300</v>
+        <v>129795286</v>
       </c>
       <c r="B80" t="n">
         <v>79081</v>
@@ -8713,10 +8704,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>444264</v>
+        <v>444440</v>
       </c>
       <c r="R80" t="n">
-        <v>6787349</v>
+        <v>6787388</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8753,7 +8744,7 @@
       </c>
       <c r="AC80" t="inlineStr">
         <is>
-          <t>Garnlav i de flesta träd inom en radie av 50 m.</t>
+          <t>Gott om garnlav inom en radie av 50 m.</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -8781,10 +8772,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129795126</v>
+        <v>129795300</v>
       </c>
       <c r="B81" t="n">
-        <v>79700</v>
+        <v>79081</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8792,34 +8783,37 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
+      <c r="J81" t="inlineStr"/>
+      <c r="K81" t="inlineStr"/>
+      <c r="N81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>444358</v>
+        <v>444264</v>
       </c>
       <c r="R81" t="n">
-        <v>6787400</v>
+        <v>6787349</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8854,12 +8848,18 @@
           <t>2025-11-22</t>
         </is>
       </c>
+      <c r="AC81" t="inlineStr">
+        <is>
+          <t>Garnlav i de flesta träd inom en radie av 50 m.</t>
+        </is>
+      </c>
       <c r="AD81" t="b">
         <v>0</v>
       </c>
       <c r="AE81" t="b">
         <v>0</v>
       </c>
+      <c r="AF81" t="inlineStr"/>
       <c r="AG81" t="b">
         <v>0</v>
       </c>
@@ -11707,41 +11707,40 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>129795203</v>
+        <v>129795149</v>
       </c>
       <c r="B110" t="n">
-        <v>8450</v>
+        <v>57733</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
-      <c r="J110" t="inlineStr"/>
       <c r="K110" t="inlineStr"/>
       <c r="L110" t="inlineStr"/>
       <c r="M110" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N110" t="inlineStr"/>
@@ -11751,10 +11750,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>444401</v>
+        <v>444223</v>
       </c>
       <c r="R110" t="n">
-        <v>6787298</v>
+        <v>6787221</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11795,7 +11794,6 @@
       <c r="AE110" t="b">
         <v>0</v>
       </c>
-      <c r="AF110" t="inlineStr"/>
       <c r="AG110" t="b">
         <v>0</v>
       </c>
@@ -11814,7 +11812,7 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>129795151</v>
+        <v>129795145</v>
       </c>
       <c r="B111" t="n">
         <v>57733</v>
@@ -11857,10 +11855,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>444425</v>
+        <v>444228</v>
       </c>
       <c r="R111" t="n">
-        <v>6787278</v>
+        <v>6787226</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -11919,10 +11917,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>129795259</v>
+        <v>129795151</v>
       </c>
       <c r="B112" t="n">
-        <v>79081</v>
+        <v>57733</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -11930,34 +11928,42 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
+      <c r="K112" t="inlineStr"/>
+      <c r="L112" t="inlineStr"/>
+      <c r="M112" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N112" t="inlineStr"/>
       <c r="P112" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>444164</v>
+        <v>444425</v>
       </c>
       <c r="R112" t="n">
-        <v>6787121</v>
+        <v>6787278</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12016,54 +12022,45 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>129795201</v>
+        <v>129795259</v>
       </c>
       <c r="B113" t="n">
-        <v>8450</v>
+        <v>79081</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
-      <c r="J113" t="inlineStr"/>
-      <c r="K113" t="inlineStr"/>
-      <c r="L113" t="inlineStr"/>
-      <c r="M113" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N113" t="inlineStr"/>
       <c r="P113" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>444430</v>
+        <v>444164</v>
       </c>
       <c r="R113" t="n">
-        <v>6787332</v>
+        <v>6787121</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12104,7 +12101,6 @@
       <c r="AE113" t="b">
         <v>0</v>
       </c>
-      <c r="AF113" t="inlineStr"/>
       <c r="AG113" t="b">
         <v>0</v>
       </c>
@@ -12123,40 +12119,41 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>129795149</v>
+        <v>129795201</v>
       </c>
       <c r="B114" t="n">
-        <v>57733</v>
+        <v>8450</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
+      <c r="J114" t="inlineStr"/>
       <c r="K114" t="inlineStr"/>
       <c r="L114" t="inlineStr"/>
       <c r="M114" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N114" t="inlineStr"/>
@@ -12166,10 +12163,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>444223</v>
+        <v>444430</v>
       </c>
       <c r="R114" t="n">
-        <v>6787221</v>
+        <v>6787332</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12210,6 +12207,7 @@
       <c r="AE114" t="b">
         <v>0</v>
       </c>
+      <c r="AF114" t="inlineStr"/>
       <c r="AG114" t="b">
         <v>0</v>
       </c>
@@ -12228,40 +12226,41 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>129795145</v>
+        <v>129795203</v>
       </c>
       <c r="B115" t="n">
-        <v>57733</v>
+        <v>8450</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
+      <c r="J115" t="inlineStr"/>
       <c r="K115" t="inlineStr"/>
       <c r="L115" t="inlineStr"/>
       <c r="M115" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N115" t="inlineStr"/>
@@ -12271,10 +12270,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>444228</v>
+        <v>444401</v>
       </c>
       <c r="R115" t="n">
-        <v>6787226</v>
+        <v>6787298</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12315,6 +12314,7 @@
       <c r="AE115" t="b">
         <v>0</v>
       </c>
+      <c r="AF115" t="inlineStr"/>
       <c r="AG115" t="b">
         <v>0</v>
       </c>
@@ -12957,10 +12957,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>129795144</v>
+        <v>129795301</v>
       </c>
       <c r="B122" t="n">
-        <v>57733</v>
+        <v>79081</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -12968,42 +12968,34 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
-      <c r="K122" t="inlineStr"/>
-      <c r="L122" t="inlineStr"/>
-      <c r="M122" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N122" t="inlineStr"/>
       <c r="P122" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>444186</v>
+        <v>444250</v>
       </c>
       <c r="R122" t="n">
-        <v>6787223</v>
+        <v>6787342</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -13159,10 +13151,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>129795301</v>
+        <v>129795144</v>
       </c>
       <c r="B124" t="n">
-        <v>79081</v>
+        <v>57733</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -13170,34 +13162,42 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
+      <c r="K124" t="inlineStr"/>
+      <c r="L124" t="inlineStr"/>
+      <c r="M124" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N124" t="inlineStr"/>
       <c r="P124" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>444250</v>
+        <v>444186</v>
       </c>
       <c r="R124" t="n">
-        <v>6787342</v>
+        <v>6787223</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>

--- a/artfynd/A 51041-2025 artfynd.xlsx
+++ b/artfynd/A 51041-2025 artfynd.xlsx
@@ -3448,10 +3448,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129795142</v>
+        <v>129795256</v>
       </c>
       <c r="B29" t="n">
-        <v>57733</v>
+        <v>79081</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3459,42 +3459,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>444276</v>
+        <v>444226</v>
       </c>
       <c r="R29" t="n">
-        <v>6787287</v>
+        <v>6787196</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3874,10 +3866,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129795268</v>
+        <v>129795142</v>
       </c>
       <c r="B33" t="n">
-        <v>79081</v>
+        <v>57733</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3885,34 +3877,42 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>444383</v>
+        <v>444276</v>
       </c>
       <c r="R33" t="n">
-        <v>6787218</v>
+        <v>6787287</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3971,7 +3971,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129795256</v>
+        <v>129795268</v>
       </c>
       <c r="B34" t="n">
         <v>79081</v>
@@ -4006,10 +4006,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>444226</v>
+        <v>444383</v>
       </c>
       <c r="R34" t="n">
-        <v>6787196</v>
+        <v>6787218</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4068,10 +4068,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129795269</v>
+        <v>129795165</v>
       </c>
       <c r="B35" t="n">
-        <v>79081</v>
+        <v>57733</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4079,34 +4079,42 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>444429</v>
+        <v>444251</v>
       </c>
       <c r="R35" t="n">
-        <v>6787240</v>
+        <v>6787376</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4165,10 +4173,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129795249</v>
+        <v>129795133</v>
       </c>
       <c r="B36" t="n">
-        <v>79081</v>
+        <v>57896</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4176,34 +4184,42 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>444267</v>
+        <v>444226</v>
       </c>
       <c r="R36" t="n">
-        <v>6787295</v>
+        <v>6787236</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4262,37 +4278,43 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129795296</v>
+        <v>129795193</v>
       </c>
       <c r="B37" t="n">
-        <v>79081</v>
+        <v>8450</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
@@ -4300,10 +4322,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>444299</v>
+        <v>444508</v>
       </c>
       <c r="R37" t="n">
-        <v>6787304</v>
+        <v>6787352</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4336,11 +4358,6 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-11-22</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 50 m.</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4368,45 +4385,54 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129795270</v>
+        <v>129795202</v>
       </c>
       <c r="B38" t="n">
-        <v>79081</v>
+        <v>8450</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>444416</v>
+        <v>444413</v>
       </c>
       <c r="R38" t="n">
-        <v>6787260</v>
+        <v>6787314</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4447,6 +4473,7 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
+      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -4465,54 +4492,45 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129795193</v>
+        <v>129795269</v>
       </c>
       <c r="B39" t="n">
-        <v>8450</v>
+        <v>79081</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>444508</v>
+        <v>444429</v>
       </c>
       <c r="R39" t="n">
-        <v>6787352</v>
+        <v>6787240</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4553,7 +4571,6 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
-      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -4572,54 +4589,45 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129795202</v>
+        <v>129795249</v>
       </c>
       <c r="B40" t="n">
-        <v>8450</v>
+        <v>79081</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr"/>
-      <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>444413</v>
+        <v>444267</v>
       </c>
       <c r="R40" t="n">
-        <v>6787314</v>
+        <v>6787295</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4660,7 +4668,6 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
-      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
@@ -4679,10 +4686,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129795165</v>
+        <v>129795296</v>
       </c>
       <c r="B41" t="n">
-        <v>57733</v>
+        <v>79081</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4690,31 +4697,26 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
       <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
@@ -4722,10 +4724,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>444251</v>
+        <v>444299</v>
       </c>
       <c r="R41" t="n">
-        <v>6787376</v>
+        <v>6787304</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4760,12 +4762,18 @@
           <t>2025-11-22</t>
         </is>
       </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 50 m.</t>
+        </is>
+      </c>
       <c r="AD41" t="b">
         <v>0</v>
       </c>
       <c r="AE41" t="b">
         <v>0</v>
       </c>
+      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
@@ -4784,10 +4792,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129795133</v>
+        <v>129795270</v>
       </c>
       <c r="B42" t="n">
-        <v>57896</v>
+        <v>79081</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4795,42 +4803,34 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="K42" t="inlineStr"/>
-      <c r="L42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>444226</v>
+        <v>444416</v>
       </c>
       <c r="R42" t="n">
-        <v>6787236</v>
+        <v>6787260</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4889,43 +4889,37 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129795170</v>
+        <v>129795136</v>
       </c>
       <c r="B43" t="n">
-        <v>8450</v>
+        <v>91620</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>106545</v>
+        <v>5442</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="J43" t="inlineStr"/>
       <c r="K43" t="inlineStr"/>
-      <c r="L43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
@@ -4933,10 +4927,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>444172</v>
+        <v>444235</v>
       </c>
       <c r="R43" t="n">
-        <v>6787202</v>
+        <v>6787149</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4996,10 +4990,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129795158</v>
+        <v>129795293</v>
       </c>
       <c r="B44" t="n">
-        <v>57733</v>
+        <v>79081</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5007,42 +5001,34 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="K44" t="inlineStr"/>
-      <c r="L44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>444501</v>
+        <v>444365</v>
       </c>
       <c r="R44" t="n">
-        <v>6787402</v>
+        <v>6787285</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5075,6 +5061,11 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-11-22</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 50m.</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5101,10 +5092,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129795136</v>
+        <v>129795282</v>
       </c>
       <c r="B45" t="n">
-        <v>91620</v>
+        <v>79081</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5112,21 +5103,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5139,10 +5130,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>444235</v>
+        <v>444374</v>
       </c>
       <c r="R45" t="n">
-        <v>6787149</v>
+        <v>6787384</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5175,6 +5166,11 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-11-22</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 50 m.</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5202,45 +5198,54 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129795293</v>
+        <v>129795170</v>
       </c>
       <c r="B46" t="n">
-        <v>79081</v>
+        <v>8450</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="J46" t="inlineStr"/>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>444365</v>
+        <v>444172</v>
       </c>
       <c r="R46" t="n">
-        <v>6787285</v>
+        <v>6787202</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5275,17 +5280,13 @@
           <t>2025-11-22</t>
         </is>
       </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 50m.</t>
-        </is>
-      </c>
       <c r="AD46" t="b">
         <v>0</v>
       </c>
       <c r="AE46" t="b">
         <v>0</v>
       </c>
+      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
@@ -5304,10 +5305,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129795282</v>
+        <v>129795158</v>
       </c>
       <c r="B47" t="n">
-        <v>79081</v>
+        <v>57733</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5315,26 +5316,31 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="J47" t="inlineStr"/>
       <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
@@ -5342,10 +5348,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>444374</v>
+        <v>444501</v>
       </c>
       <c r="R47" t="n">
-        <v>6787384</v>
+        <v>6787402</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5380,18 +5386,12 @@
           <t>2025-11-22</t>
         </is>
       </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 50 m.</t>
-        </is>
-      </c>
       <c r="AD47" t="b">
         <v>0</v>
       </c>
       <c r="AE47" t="b">
         <v>0</v>
       </c>
-      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
@@ -6224,40 +6224,41 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129795134</v>
+        <v>129795184</v>
       </c>
       <c r="B56" t="n">
-        <v>57896</v>
+        <v>8450</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>103021</v>
+        <v>106545</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
+      <c r="J56" t="inlineStr"/>
       <c r="K56" t="inlineStr"/>
       <c r="L56" t="inlineStr"/>
       <c r="M56" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N56" t="inlineStr"/>
@@ -6267,10 +6268,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>444289</v>
+        <v>444452</v>
       </c>
       <c r="R56" t="n">
-        <v>6787357</v>
+        <v>6787305</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6311,6 +6312,7 @@
       <c r="AE56" t="b">
         <v>0</v>
       </c>
+      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
       </c>
@@ -6329,7 +6331,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129795184</v>
+        <v>129795172</v>
       </c>
       <c r="B57" t="n">
         <v>8450</v>
@@ -6373,10 +6375,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>444452</v>
+        <v>444225</v>
       </c>
       <c r="R57" t="n">
-        <v>6787305</v>
+        <v>6787223</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6436,7 +6438,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129795172</v>
+        <v>129795199</v>
       </c>
       <c r="B58" t="n">
         <v>8450</v>
@@ -6480,10 +6482,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>444225</v>
+        <v>444431</v>
       </c>
       <c r="R58" t="n">
-        <v>6787223</v>
+        <v>6787350</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6543,54 +6545,45 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129795199</v>
+        <v>129795279</v>
       </c>
       <c r="B59" t="n">
-        <v>8450</v>
+        <v>79081</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
-      <c r="J59" t="inlineStr"/>
-      <c r="K59" t="inlineStr"/>
-      <c r="L59" t="inlineStr"/>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>444431</v>
+        <v>444463</v>
       </c>
       <c r="R59" t="n">
-        <v>6787350</v>
+        <v>6787459</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6631,7 +6624,6 @@
       <c r="AE59" t="b">
         <v>0</v>
       </c>
-      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
       </c>
@@ -6650,7 +6642,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129795279</v>
+        <v>129795277</v>
       </c>
       <c r="B60" t="n">
         <v>79081</v>
@@ -6685,10 +6677,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>444463</v>
+        <v>444491</v>
       </c>
       <c r="R60" t="n">
-        <v>6787459</v>
+        <v>6787412</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6747,10 +6739,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129795277</v>
+        <v>129795134</v>
       </c>
       <c r="B61" t="n">
-        <v>79081</v>
+        <v>57896</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6758,34 +6750,42 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
+      <c r="K61" t="inlineStr"/>
+      <c r="L61" t="inlineStr"/>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>444491</v>
+        <v>444289</v>
       </c>
       <c r="R61" t="n">
-        <v>6787412</v>
+        <v>6787357</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6844,54 +6844,45 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129795191</v>
+        <v>129795125</v>
       </c>
       <c r="B62" t="n">
-        <v>8450</v>
+        <v>79700</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
-      <c r="J62" t="inlineStr"/>
-      <c r="K62" t="inlineStr"/>
-      <c r="L62" t="inlineStr"/>
-      <c r="M62" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>444520</v>
+        <v>444329</v>
       </c>
       <c r="R62" t="n">
-        <v>6787287</v>
+        <v>6787371</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6932,7 +6923,6 @@
       <c r="AE62" t="b">
         <v>0</v>
       </c>
-      <c r="AF62" t="inlineStr"/>
       <c r="AG62" t="b">
         <v>0</v>
       </c>
@@ -6951,7 +6941,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129795195</v>
+        <v>129795191</v>
       </c>
       <c r="B63" t="n">
         <v>8450</v>
@@ -6995,10 +6985,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>444487</v>
+        <v>444520</v>
       </c>
       <c r="R63" t="n">
-        <v>6787441</v>
+        <v>6787287</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7058,7 +7048,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129795177</v>
+        <v>129795195</v>
       </c>
       <c r="B64" t="n">
         <v>8450</v>
@@ -7092,7 +7082,7 @@
       <c r="L64" t="inlineStr"/>
       <c r="M64" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N64" t="inlineStr"/>
@@ -7102,10 +7092,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>444342</v>
+        <v>444487</v>
       </c>
       <c r="R64" t="n">
-        <v>6787223</v>
+        <v>6787441</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7165,40 +7155,41 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129795162</v>
+        <v>129795177</v>
       </c>
       <c r="B65" t="n">
-        <v>57733</v>
+        <v>8450</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
+      <c r="J65" t="inlineStr"/>
       <c r="K65" t="inlineStr"/>
       <c r="L65" t="inlineStr"/>
       <c r="M65" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="N65" t="inlineStr"/>
@@ -7208,10 +7199,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>444428</v>
+        <v>444342</v>
       </c>
       <c r="R65" t="n">
-        <v>6787329</v>
+        <v>6787223</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7252,6 +7243,7 @@
       <c r="AE65" t="b">
         <v>0</v>
       </c>
+      <c r="AF65" t="inlineStr"/>
       <c r="AG65" t="b">
         <v>0</v>
       </c>
@@ -7270,10 +7262,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129795125</v>
+        <v>129795162</v>
       </c>
       <c r="B66" t="n">
-        <v>79700</v>
+        <v>57733</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7281,34 +7273,42 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
+      <c r="K66" t="inlineStr"/>
+      <c r="L66" t="inlineStr"/>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>444329</v>
+        <v>444428</v>
       </c>
       <c r="R66" t="n">
-        <v>6787371</v>
+        <v>6787329</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7569,10 +7569,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129795280</v>
+        <v>129795135</v>
       </c>
       <c r="B69" t="n">
-        <v>79081</v>
+        <v>91620</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7580,34 +7580,37 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
+      <c r="J69" t="inlineStr"/>
+      <c r="K69" t="inlineStr"/>
+      <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>444451</v>
+        <v>444158</v>
       </c>
       <c r="R69" t="n">
-        <v>6787467</v>
+        <v>6787148</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7648,6 +7651,7 @@
       <c r="AE69" t="b">
         <v>0</v>
       </c>
+      <c r="AF69" t="inlineStr"/>
       <c r="AG69" t="b">
         <v>0</v>
       </c>
@@ -7666,7 +7670,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129795284</v>
+        <v>129795243</v>
       </c>
       <c r="B70" t="n">
         <v>79081</v>
@@ -7701,10 +7705,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>444363</v>
+        <v>444159</v>
       </c>
       <c r="R70" t="n">
-        <v>6787411</v>
+        <v>6787297</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7763,10 +7767,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129795166</v>
+        <v>129795287</v>
       </c>
       <c r="B71" t="n">
-        <v>57733</v>
+        <v>79081</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7774,42 +7778,34 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
-      <c r="K71" t="inlineStr"/>
-      <c r="L71" t="inlineStr"/>
-      <c r="M71" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>444254</v>
+        <v>444430</v>
       </c>
       <c r="R71" t="n">
-        <v>6787333</v>
+        <v>6787384</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7868,10 +7864,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129795135</v>
+        <v>129795272</v>
       </c>
       <c r="B72" t="n">
-        <v>91620</v>
+        <v>79081</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7879,37 +7875,34 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
-      <c r="J72" t="inlineStr"/>
-      <c r="K72" t="inlineStr"/>
-      <c r="N72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>444158</v>
+        <v>444553</v>
       </c>
       <c r="R72" t="n">
-        <v>6787148</v>
+        <v>6787299</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7950,7 +7943,6 @@
       <c r="AE72" t="b">
         <v>0</v>
       </c>
-      <c r="AF72" t="inlineStr"/>
       <c r="AG72" t="b">
         <v>0</v>
       </c>
@@ -7969,10 +7961,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129795243</v>
+        <v>129795166</v>
       </c>
       <c r="B73" t="n">
-        <v>79081</v>
+        <v>57733</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7980,34 +7972,42 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
+      <c r="K73" t="inlineStr"/>
+      <c r="L73" t="inlineStr"/>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>444159</v>
+        <v>444254</v>
       </c>
       <c r="R73" t="n">
-        <v>6787297</v>
+        <v>6787333</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8066,7 +8066,7 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129795287</v>
+        <v>129795280</v>
       </c>
       <c r="B74" t="n">
         <v>79081</v>
@@ -8101,10 +8101,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>444430</v>
+        <v>444451</v>
       </c>
       <c r="R74" t="n">
-        <v>6787384</v>
+        <v>6787467</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8163,7 +8163,7 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129795272</v>
+        <v>129795284</v>
       </c>
       <c r="B75" t="n">
         <v>79081</v>
@@ -8198,10 +8198,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>444553</v>
+        <v>444363</v>
       </c>
       <c r="R75" t="n">
-        <v>6787299</v>
+        <v>6787411</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -10891,54 +10891,45 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>129795185</v>
+        <v>129795303</v>
       </c>
       <c r="B102" t="n">
-        <v>8450</v>
+        <v>79081</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
-      <c r="J102" t="inlineStr"/>
-      <c r="K102" t="inlineStr"/>
-      <c r="L102" t="inlineStr"/>
-      <c r="M102" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>444458</v>
+        <v>444200</v>
       </c>
       <c r="R102" t="n">
-        <v>6787304</v>
+        <v>6787331</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -10979,7 +10970,6 @@
       <c r="AE102" t="b">
         <v>0</v>
       </c>
-      <c r="AF102" t="inlineStr"/>
       <c r="AG102" t="b">
         <v>0</v>
       </c>
@@ -10998,54 +10988,45 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>129795180</v>
+        <v>129795264</v>
       </c>
       <c r="B103" t="n">
-        <v>8450</v>
+        <v>79081</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
-      <c r="J103" t="inlineStr"/>
-      <c r="K103" t="inlineStr"/>
-      <c r="L103" t="inlineStr"/>
-      <c r="M103" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N103" t="inlineStr"/>
       <c r="P103" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>444409</v>
+        <v>444252</v>
       </c>
       <c r="R103" t="n">
-        <v>6787219</v>
+        <v>6787160</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11086,7 +11067,6 @@
       <c r="AE103" t="b">
         <v>0</v>
       </c>
-      <c r="AF103" t="inlineStr"/>
       <c r="AG103" t="b">
         <v>0</v>
       </c>
@@ -11105,54 +11085,45 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>129795178</v>
+        <v>129795248</v>
       </c>
       <c r="B104" t="n">
-        <v>8450</v>
+        <v>79081</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
-      <c r="J104" t="inlineStr"/>
-      <c r="K104" t="inlineStr"/>
-      <c r="L104" t="inlineStr"/>
-      <c r="M104" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>444375</v>
+        <v>444238</v>
       </c>
       <c r="R104" t="n">
-        <v>6787207</v>
+        <v>6787281</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11193,7 +11164,6 @@
       <c r="AE104" t="b">
         <v>0</v>
       </c>
-      <c r="AF104" t="inlineStr"/>
       <c r="AG104" t="b">
         <v>0</v>
       </c>
@@ -11212,54 +11182,45 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>129795196</v>
+        <v>129795306</v>
       </c>
       <c r="B105" t="n">
-        <v>8450</v>
+        <v>79081</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
-      <c r="J105" t="inlineStr"/>
-      <c r="K105" t="inlineStr"/>
-      <c r="L105" t="inlineStr"/>
-      <c r="M105" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>444346</v>
+        <v>444152</v>
       </c>
       <c r="R105" t="n">
-        <v>6787369</v>
+        <v>6787313</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11300,7 +11261,6 @@
       <c r="AE105" t="b">
         <v>0</v>
       </c>
-      <c r="AF105" t="inlineStr"/>
       <c r="AG105" t="b">
         <v>0</v>
       </c>
@@ -11319,45 +11279,54 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>129795303</v>
+        <v>129795185</v>
       </c>
       <c r="B106" t="n">
-        <v>79081</v>
+        <v>8450</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
+      <c r="J106" t="inlineStr"/>
+      <c r="K106" t="inlineStr"/>
+      <c r="L106" t="inlineStr"/>
+      <c r="M106" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>444200</v>
+        <v>444458</v>
       </c>
       <c r="R106" t="n">
-        <v>6787331</v>
+        <v>6787304</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11398,6 +11367,7 @@
       <c r="AE106" t="b">
         <v>0</v>
       </c>
+      <c r="AF106" t="inlineStr"/>
       <c r="AG106" t="b">
         <v>0</v>
       </c>
@@ -11416,45 +11386,54 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>129795264</v>
+        <v>129795180</v>
       </c>
       <c r="B107" t="n">
-        <v>79081</v>
+        <v>8450</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
+      <c r="J107" t="inlineStr"/>
+      <c r="K107" t="inlineStr"/>
+      <c r="L107" t="inlineStr"/>
+      <c r="M107" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>444252</v>
+        <v>444409</v>
       </c>
       <c r="R107" t="n">
-        <v>6787160</v>
+        <v>6787219</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11495,6 +11474,7 @@
       <c r="AE107" t="b">
         <v>0</v>
       </c>
+      <c r="AF107" t="inlineStr"/>
       <c r="AG107" t="b">
         <v>0</v>
       </c>
@@ -11513,45 +11493,54 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>129795248</v>
+        <v>129795178</v>
       </c>
       <c r="B108" t="n">
-        <v>79081</v>
+        <v>8450</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
+      <c r="J108" t="inlineStr"/>
+      <c r="K108" t="inlineStr"/>
+      <c r="L108" t="inlineStr"/>
+      <c r="M108" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>444238</v>
+        <v>444375</v>
       </c>
       <c r="R108" t="n">
-        <v>6787281</v>
+        <v>6787207</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11592,6 +11581,7 @@
       <c r="AE108" t="b">
         <v>0</v>
       </c>
+      <c r="AF108" t="inlineStr"/>
       <c r="AG108" t="b">
         <v>0</v>
       </c>
@@ -11610,45 +11600,54 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>129795306</v>
+        <v>129795196</v>
       </c>
       <c r="B109" t="n">
-        <v>79081</v>
+        <v>8450</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
+      <c r="J109" t="inlineStr"/>
+      <c r="K109" t="inlineStr"/>
+      <c r="L109" t="inlineStr"/>
+      <c r="M109" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>444152</v>
+        <v>444346</v>
       </c>
       <c r="R109" t="n">
-        <v>6787313</v>
+        <v>6787369</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11689,6 +11688,7 @@
       <c r="AE109" t="b">
         <v>0</v>
       </c>
+      <c r="AF109" t="inlineStr"/>
       <c r="AG109" t="b">
         <v>0</v>
       </c>
@@ -12957,10 +12957,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>129795301</v>
+        <v>129795144</v>
       </c>
       <c r="B122" t="n">
-        <v>79081</v>
+        <v>57733</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -12968,34 +12968,42 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
+      <c r="K122" t="inlineStr"/>
+      <c r="L122" t="inlineStr"/>
+      <c r="M122" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N122" t="inlineStr"/>
       <c r="P122" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>444250</v>
+        <v>444186</v>
       </c>
       <c r="R122" t="n">
-        <v>6787342</v>
+        <v>6787223</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -13054,45 +13062,54 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>129795294</v>
+        <v>129795188</v>
       </c>
       <c r="B123" t="n">
-        <v>79081</v>
+        <v>8450</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
+      <c r="J123" t="inlineStr"/>
+      <c r="K123" t="inlineStr"/>
+      <c r="L123" t="inlineStr"/>
+      <c r="M123" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N123" t="inlineStr"/>
       <c r="P123" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>444323</v>
+        <v>444498</v>
       </c>
       <c r="R123" t="n">
-        <v>6787297</v>
+        <v>6787280</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13133,6 +13150,7 @@
       <c r="AE123" t="b">
         <v>0</v>
       </c>
+      <c r="AF123" t="inlineStr"/>
       <c r="AG123" t="b">
         <v>0</v>
       </c>
@@ -13151,40 +13169,41 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>129795144</v>
+        <v>129795179</v>
       </c>
       <c r="B124" t="n">
-        <v>57733</v>
+        <v>8450</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
+      <c r="J124" t="inlineStr"/>
       <c r="K124" t="inlineStr"/>
       <c r="L124" t="inlineStr"/>
       <c r="M124" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N124" t="inlineStr"/>
@@ -13194,10 +13213,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>444186</v>
+        <v>444378</v>
       </c>
       <c r="R124" t="n">
-        <v>6787223</v>
+        <v>6787236</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13238,6 +13257,7 @@
       <c r="AE124" t="b">
         <v>0</v>
       </c>
+      <c r="AF124" t="inlineStr"/>
       <c r="AG124" t="b">
         <v>0</v>
       </c>
@@ -13256,54 +13276,45 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>129795188</v>
+        <v>129795301</v>
       </c>
       <c r="B125" t="n">
-        <v>8450</v>
+        <v>79081</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
-      <c r="J125" t="inlineStr"/>
-      <c r="K125" t="inlineStr"/>
-      <c r="L125" t="inlineStr"/>
-      <c r="M125" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N125" t="inlineStr"/>
       <c r="P125" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>444498</v>
+        <v>444250</v>
       </c>
       <c r="R125" t="n">
-        <v>6787280</v>
+        <v>6787342</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13344,7 +13355,6 @@
       <c r="AE125" t="b">
         <v>0</v>
       </c>
-      <c r="AF125" t="inlineStr"/>
       <c r="AG125" t="b">
         <v>0</v>
       </c>
@@ -13363,54 +13373,45 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>129795179</v>
+        <v>129795294</v>
       </c>
       <c r="B126" t="n">
-        <v>8450</v>
+        <v>79081</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
-      <c r="J126" t="inlineStr"/>
-      <c r="K126" t="inlineStr"/>
-      <c r="L126" t="inlineStr"/>
-      <c r="M126" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N126" t="inlineStr"/>
       <c r="P126" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>444378</v>
+        <v>444323</v>
       </c>
       <c r="R126" t="n">
-        <v>6787236</v>
+        <v>6787297</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -13451,7 +13452,6 @@
       <c r="AE126" t="b">
         <v>0</v>
       </c>
-      <c r="AF126" t="inlineStr"/>
       <c r="AG126" t="b">
         <v>0</v>
       </c>
@@ -14283,43 +14283,37 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>129795204</v>
+        <v>129795139</v>
       </c>
       <c r="B135" t="n">
-        <v>8450</v>
+        <v>91620</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>106545</v>
+        <v>5442</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
       <c r="J135" t="inlineStr"/>
       <c r="K135" t="inlineStr"/>
-      <c r="L135" t="inlineStr"/>
-      <c r="M135" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N135" t="inlineStr"/>
       <c r="P135" t="inlineStr">
         <is>
@@ -14327,10 +14321,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>444380</v>
+        <v>444342</v>
       </c>
       <c r="R135" t="n">
-        <v>6787306</v>
+        <v>6787240</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -14390,10 +14384,10 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>129795139</v>
+        <v>129795247</v>
       </c>
       <c r="B136" t="n">
-        <v>91620</v>
+        <v>79081</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -14401,37 +14395,34 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
-      <c r="J136" t="inlineStr"/>
-      <c r="K136" t="inlineStr"/>
-      <c r="N136" t="inlineStr"/>
       <c r="P136" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>444342</v>
+        <v>444225</v>
       </c>
       <c r="R136" t="n">
-        <v>6787240</v>
+        <v>6787275</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -14472,7 +14463,6 @@
       <c r="AE136" t="b">
         <v>0</v>
       </c>
-      <c r="AF136" t="inlineStr"/>
       <c r="AG136" t="b">
         <v>0</v>
       </c>
@@ -14491,7 +14481,7 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>129795247</v>
+        <v>129795304</v>
       </c>
       <c r="B137" t="n">
         <v>79081</v>
@@ -14526,10 +14516,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>444225</v>
+        <v>444172</v>
       </c>
       <c r="R137" t="n">
-        <v>6787275</v>
+        <v>6787339</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -14588,7 +14578,7 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>129795304</v>
+        <v>129795251</v>
       </c>
       <c r="B138" t="n">
         <v>79081</v>
@@ -14617,16 +14607,19 @@
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
+      <c r="J138" t="inlineStr"/>
+      <c r="K138" t="inlineStr"/>
+      <c r="N138" t="inlineStr"/>
       <c r="P138" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>444172</v>
+        <v>444309</v>
       </c>
       <c r="R138" t="n">
-        <v>6787339</v>
+        <v>6787272</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -14667,6 +14660,7 @@
       <c r="AE138" t="b">
         <v>0</v>
       </c>
+      <c r="AF138" t="inlineStr"/>
       <c r="AG138" t="b">
         <v>0</v>
       </c>
@@ -14685,7 +14679,7 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>129795251</v>
+        <v>129795274</v>
       </c>
       <c r="B139" t="n">
         <v>79081</v>
@@ -14714,19 +14708,16 @@
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
-      <c r="J139" t="inlineStr"/>
-      <c r="K139" t="inlineStr"/>
-      <c r="N139" t="inlineStr"/>
       <c r="P139" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>444309</v>
+        <v>444538</v>
       </c>
       <c r="R139" t="n">
-        <v>6787272</v>
+        <v>6787325</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -14767,7 +14758,6 @@
       <c r="AE139" t="b">
         <v>0</v>
       </c>
-      <c r="AF139" t="inlineStr"/>
       <c r="AG139" t="b">
         <v>0</v>
       </c>
@@ -14786,7 +14776,7 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>129795274</v>
+        <v>129795254</v>
       </c>
       <c r="B140" t="n">
         <v>79081</v>
@@ -14815,16 +14805,19 @@
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
+      <c r="J140" t="inlineStr"/>
+      <c r="K140" t="inlineStr"/>
+      <c r="N140" t="inlineStr"/>
       <c r="P140" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>444538</v>
+        <v>444199</v>
       </c>
       <c r="R140" t="n">
-        <v>6787325</v>
+        <v>6787221</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -14865,6 +14858,7 @@
       <c r="AE140" t="b">
         <v>0</v>
       </c>
+      <c r="AF140" t="inlineStr"/>
       <c r="AG140" t="b">
         <v>0</v>
       </c>
@@ -14883,7 +14877,7 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>129795254</v>
+        <v>129795266</v>
       </c>
       <c r="B141" t="n">
         <v>79081</v>
@@ -14912,19 +14906,16 @@
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
-      <c r="J141" t="inlineStr"/>
-      <c r="K141" t="inlineStr"/>
-      <c r="N141" t="inlineStr"/>
       <c r="P141" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>444199</v>
+        <v>444314</v>
       </c>
       <c r="R141" t="n">
-        <v>6787221</v>
+        <v>6787212</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -14959,13 +14950,17 @@
           <t>2025-11-22</t>
         </is>
       </c>
+      <c r="AC141" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 40m</t>
+        </is>
+      </c>
       <c r="AD141" t="b">
         <v>0</v>
       </c>
       <c r="AE141" t="b">
         <v>0</v>
       </c>
-      <c r="AF141" t="inlineStr"/>
       <c r="AG141" t="b">
         <v>0</v>
       </c>
@@ -14984,7 +14979,7 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>129795266</v>
+        <v>129795302</v>
       </c>
       <c r="B142" t="n">
         <v>79081</v>
@@ -15019,10 +15014,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>444314</v>
+        <v>444222</v>
       </c>
       <c r="R142" t="n">
-        <v>6787212</v>
+        <v>6787345</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -15055,11 +15050,6 @@
       <c r="AA142" t="inlineStr">
         <is>
           <t>2025-11-22</t>
-        </is>
-      </c>
-      <c r="AC142" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 40m</t>
         </is>
       </c>
       <c r="AD142" t="b">
@@ -15086,45 +15076,54 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>129795302</v>
+        <v>129795204</v>
       </c>
       <c r="B143" t="n">
-        <v>79081</v>
+        <v>8450</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E143" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
+      <c r="J143" t="inlineStr"/>
+      <c r="K143" t="inlineStr"/>
+      <c r="L143" t="inlineStr"/>
+      <c r="M143" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N143" t="inlineStr"/>
       <c r="P143" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>444222</v>
+        <v>444380</v>
       </c>
       <c r="R143" t="n">
-        <v>6787345</v>
+        <v>6787306</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -15165,6 +15164,7 @@
       <c r="AE143" t="b">
         <v>0</v>
       </c>
+      <c r="AF143" t="inlineStr"/>
       <c r="AG143" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 51041-2025 artfynd.xlsx
+++ b/artfynd/A 51041-2025 artfynd.xlsx
@@ -4068,10 +4068,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129795165</v>
+        <v>129795269</v>
       </c>
       <c r="B35" t="n">
-        <v>57733</v>
+        <v>79081</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4079,42 +4079,34 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>444251</v>
+        <v>444429</v>
       </c>
       <c r="R35" t="n">
-        <v>6787376</v>
+        <v>6787240</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4173,10 +4165,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129795133</v>
+        <v>129795249</v>
       </c>
       <c r="B36" t="n">
-        <v>57896</v>
+        <v>79081</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4184,42 +4176,34 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>444226</v>
+        <v>444267</v>
       </c>
       <c r="R36" t="n">
-        <v>6787236</v>
+        <v>6787295</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4278,43 +4262,37 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129795193</v>
+        <v>129795296</v>
       </c>
       <c r="B37" t="n">
-        <v>8450</v>
+        <v>79081</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
@@ -4322,10 +4300,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>444508</v>
+        <v>444299</v>
       </c>
       <c r="R37" t="n">
-        <v>6787352</v>
+        <v>6787304</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4358,6 +4336,11 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-11-22</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 50 m.</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4385,54 +4368,45 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129795202</v>
+        <v>129795270</v>
       </c>
       <c r="B38" t="n">
-        <v>8450</v>
+        <v>79081</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
-      <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>444413</v>
+        <v>444416</v>
       </c>
       <c r="R38" t="n">
-        <v>6787314</v>
+        <v>6787260</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4473,7 +4447,6 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
-      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -4492,45 +4465,54 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129795269</v>
+        <v>129795193</v>
       </c>
       <c r="B39" t="n">
-        <v>79081</v>
+        <v>8450</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>444429</v>
+        <v>444508</v>
       </c>
       <c r="R39" t="n">
-        <v>6787240</v>
+        <v>6787352</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4571,6 +4553,7 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
+      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -4589,45 +4572,54 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129795249</v>
+        <v>129795202</v>
       </c>
       <c r="B40" t="n">
-        <v>79081</v>
+        <v>8450</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>444267</v>
+        <v>444413</v>
       </c>
       <c r="R40" t="n">
-        <v>6787295</v>
+        <v>6787314</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4668,6 +4660,7 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
+      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
@@ -4686,10 +4679,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129795296</v>
+        <v>129795165</v>
       </c>
       <c r="B41" t="n">
-        <v>79081</v>
+        <v>57733</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4697,26 +4690,31 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr"/>
       <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
@@ -4724,10 +4722,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>444299</v>
+        <v>444251</v>
       </c>
       <c r="R41" t="n">
-        <v>6787304</v>
+        <v>6787376</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4762,18 +4760,12 @@
           <t>2025-11-22</t>
         </is>
       </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 50 m.</t>
-        </is>
-      </c>
       <c r="AD41" t="b">
         <v>0</v>
       </c>
       <c r="AE41" t="b">
         <v>0</v>
       </c>
-      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
@@ -4792,10 +4784,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129795270</v>
+        <v>129795133</v>
       </c>
       <c r="B42" t="n">
-        <v>79081</v>
+        <v>57896</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4803,34 +4795,42 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>444416</v>
+        <v>444226</v>
       </c>
       <c r="R42" t="n">
-        <v>6787260</v>
+        <v>6787236</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -6844,45 +6844,54 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129795125</v>
+        <v>129795191</v>
       </c>
       <c r="B62" t="n">
-        <v>79700</v>
+        <v>8450</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
+      <c r="J62" t="inlineStr"/>
+      <c r="K62" t="inlineStr"/>
+      <c r="L62" t="inlineStr"/>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>444329</v>
+        <v>444520</v>
       </c>
       <c r="R62" t="n">
-        <v>6787371</v>
+        <v>6787287</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6923,6 +6932,7 @@
       <c r="AE62" t="b">
         <v>0</v>
       </c>
+      <c r="AF62" t="inlineStr"/>
       <c r="AG62" t="b">
         <v>0</v>
       </c>
@@ -6941,7 +6951,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129795191</v>
+        <v>129795195</v>
       </c>
       <c r="B63" t="n">
         <v>8450</v>
@@ -6985,10 +6995,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>444520</v>
+        <v>444487</v>
       </c>
       <c r="R63" t="n">
-        <v>6787287</v>
+        <v>6787441</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7048,7 +7058,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129795195</v>
+        <v>129795177</v>
       </c>
       <c r="B64" t="n">
         <v>8450</v>
@@ -7082,7 +7092,7 @@
       <c r="L64" t="inlineStr"/>
       <c r="M64" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="N64" t="inlineStr"/>
@@ -7092,10 +7102,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>444487</v>
+        <v>444342</v>
       </c>
       <c r="R64" t="n">
-        <v>6787441</v>
+        <v>6787223</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7155,41 +7165,40 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129795177</v>
+        <v>129795162</v>
       </c>
       <c r="B65" t="n">
-        <v>8450</v>
+        <v>57733</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
-      <c r="J65" t="inlineStr"/>
       <c r="K65" t="inlineStr"/>
       <c r="L65" t="inlineStr"/>
       <c r="M65" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N65" t="inlineStr"/>
@@ -7199,10 +7208,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>444342</v>
+        <v>444428</v>
       </c>
       <c r="R65" t="n">
-        <v>6787223</v>
+        <v>6787329</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7243,7 +7252,6 @@
       <c r="AE65" t="b">
         <v>0</v>
       </c>
-      <c r="AF65" t="inlineStr"/>
       <c r="AG65" t="b">
         <v>0</v>
       </c>
@@ -7262,10 +7270,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129795162</v>
+        <v>129795125</v>
       </c>
       <c r="B66" t="n">
-        <v>57733</v>
+        <v>79700</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7273,42 +7281,34 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
-      <c r="K66" t="inlineStr"/>
-      <c r="L66" t="inlineStr"/>
-      <c r="M66" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>444428</v>
+        <v>444329</v>
       </c>
       <c r="R66" t="n">
-        <v>6787329</v>
+        <v>6787371</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -10891,45 +10891,54 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>129795303</v>
+        <v>129795185</v>
       </c>
       <c r="B102" t="n">
-        <v>79081</v>
+        <v>8450</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
+      <c r="J102" t="inlineStr"/>
+      <c r="K102" t="inlineStr"/>
+      <c r="L102" t="inlineStr"/>
+      <c r="M102" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>444200</v>
+        <v>444458</v>
       </c>
       <c r="R102" t="n">
-        <v>6787331</v>
+        <v>6787304</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -10970,6 +10979,7 @@
       <c r="AE102" t="b">
         <v>0</v>
       </c>
+      <c r="AF102" t="inlineStr"/>
       <c r="AG102" t="b">
         <v>0</v>
       </c>
@@ -10988,45 +10998,54 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>129795264</v>
+        <v>129795180</v>
       </c>
       <c r="B103" t="n">
-        <v>79081</v>
+        <v>8450</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
+      <c r="J103" t="inlineStr"/>
+      <c r="K103" t="inlineStr"/>
+      <c r="L103" t="inlineStr"/>
+      <c r="M103" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N103" t="inlineStr"/>
       <c r="P103" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>444252</v>
+        <v>444409</v>
       </c>
       <c r="R103" t="n">
-        <v>6787160</v>
+        <v>6787219</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11067,6 +11086,7 @@
       <c r="AE103" t="b">
         <v>0</v>
       </c>
+      <c r="AF103" t="inlineStr"/>
       <c r="AG103" t="b">
         <v>0</v>
       </c>
@@ -11085,45 +11105,54 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>129795248</v>
+        <v>129795178</v>
       </c>
       <c r="B104" t="n">
-        <v>79081</v>
+        <v>8450</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
+      <c r="J104" t="inlineStr"/>
+      <c r="K104" t="inlineStr"/>
+      <c r="L104" t="inlineStr"/>
+      <c r="M104" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>444238</v>
+        <v>444375</v>
       </c>
       <c r="R104" t="n">
-        <v>6787281</v>
+        <v>6787207</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11164,6 +11193,7 @@
       <c r="AE104" t="b">
         <v>0</v>
       </c>
+      <c r="AF104" t="inlineStr"/>
       <c r="AG104" t="b">
         <v>0</v>
       </c>
@@ -11182,45 +11212,54 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>129795306</v>
+        <v>129795196</v>
       </c>
       <c r="B105" t="n">
-        <v>79081</v>
+        <v>8450</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
+      <c r="J105" t="inlineStr"/>
+      <c r="K105" t="inlineStr"/>
+      <c r="L105" t="inlineStr"/>
+      <c r="M105" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>444152</v>
+        <v>444346</v>
       </c>
       <c r="R105" t="n">
-        <v>6787313</v>
+        <v>6787369</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11261,6 +11300,7 @@
       <c r="AE105" t="b">
         <v>0</v>
       </c>
+      <c r="AF105" t="inlineStr"/>
       <c r="AG105" t="b">
         <v>0</v>
       </c>
@@ -11279,54 +11319,45 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>129795185</v>
+        <v>129795303</v>
       </c>
       <c r="B106" t="n">
-        <v>8450</v>
+        <v>79081</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
-      <c r="J106" t="inlineStr"/>
-      <c r="K106" t="inlineStr"/>
-      <c r="L106" t="inlineStr"/>
-      <c r="M106" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>444458</v>
+        <v>444200</v>
       </c>
       <c r="R106" t="n">
-        <v>6787304</v>
+        <v>6787331</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11367,7 +11398,6 @@
       <c r="AE106" t="b">
         <v>0</v>
       </c>
-      <c r="AF106" t="inlineStr"/>
       <c r="AG106" t="b">
         <v>0</v>
       </c>
@@ -11386,54 +11416,45 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>129795180</v>
+        <v>129795264</v>
       </c>
       <c r="B107" t="n">
-        <v>8450</v>
+        <v>79081</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
-      <c r="J107" t="inlineStr"/>
-      <c r="K107" t="inlineStr"/>
-      <c r="L107" t="inlineStr"/>
-      <c r="M107" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>444409</v>
+        <v>444252</v>
       </c>
       <c r="R107" t="n">
-        <v>6787219</v>
+        <v>6787160</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11474,7 +11495,6 @@
       <c r="AE107" t="b">
         <v>0</v>
       </c>
-      <c r="AF107" t="inlineStr"/>
       <c r="AG107" t="b">
         <v>0</v>
       </c>
@@ -11493,54 +11513,45 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>129795178</v>
+        <v>129795248</v>
       </c>
       <c r="B108" t="n">
-        <v>8450</v>
+        <v>79081</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
-      <c r="J108" t="inlineStr"/>
-      <c r="K108" t="inlineStr"/>
-      <c r="L108" t="inlineStr"/>
-      <c r="M108" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>444375</v>
+        <v>444238</v>
       </c>
       <c r="R108" t="n">
-        <v>6787207</v>
+        <v>6787281</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11581,7 +11592,6 @@
       <c r="AE108" t="b">
         <v>0</v>
       </c>
-      <c r="AF108" t="inlineStr"/>
       <c r="AG108" t="b">
         <v>0</v>
       </c>
@@ -11600,54 +11610,45 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>129795196</v>
+        <v>129795306</v>
       </c>
       <c r="B109" t="n">
-        <v>8450</v>
+        <v>79081</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
-      <c r="J109" t="inlineStr"/>
-      <c r="K109" t="inlineStr"/>
-      <c r="L109" t="inlineStr"/>
-      <c r="M109" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>444346</v>
+        <v>444152</v>
       </c>
       <c r="R109" t="n">
-        <v>6787369</v>
+        <v>6787313</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11688,7 +11689,6 @@
       <c r="AE109" t="b">
         <v>0</v>
       </c>
-      <c r="AF109" t="inlineStr"/>
       <c r="AG109" t="b">
         <v>0</v>
       </c>
@@ -14283,37 +14283,43 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>129795139</v>
+        <v>129795204</v>
       </c>
       <c r="B135" t="n">
-        <v>91620</v>
+        <v>8450</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>5442</v>
+        <v>106545</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
       <c r="J135" t="inlineStr"/>
       <c r="K135" t="inlineStr"/>
+      <c r="L135" t="inlineStr"/>
+      <c r="M135" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N135" t="inlineStr"/>
       <c r="P135" t="inlineStr">
         <is>
@@ -14321,10 +14327,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>444342</v>
+        <v>444380</v>
       </c>
       <c r="R135" t="n">
-        <v>6787240</v>
+        <v>6787306</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -14384,10 +14390,10 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>129795247</v>
+        <v>129795139</v>
       </c>
       <c r="B136" t="n">
-        <v>79081</v>
+        <v>91620</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -14395,34 +14401,37 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
+      <c r="J136" t="inlineStr"/>
+      <c r="K136" t="inlineStr"/>
+      <c r="N136" t="inlineStr"/>
       <c r="P136" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>444225</v>
+        <v>444342</v>
       </c>
       <c r="R136" t="n">
-        <v>6787275</v>
+        <v>6787240</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -14463,6 +14472,7 @@
       <c r="AE136" t="b">
         <v>0</v>
       </c>
+      <c r="AF136" t="inlineStr"/>
       <c r="AG136" t="b">
         <v>0</v>
       </c>
@@ -14481,7 +14491,7 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>129795304</v>
+        <v>129795247</v>
       </c>
       <c r="B137" t="n">
         <v>79081</v>
@@ -14516,10 +14526,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>444172</v>
+        <v>444225</v>
       </c>
       <c r="R137" t="n">
-        <v>6787339</v>
+        <v>6787275</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -14578,7 +14588,7 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>129795251</v>
+        <v>129795304</v>
       </c>
       <c r="B138" t="n">
         <v>79081</v>
@@ -14607,19 +14617,16 @@
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
-      <c r="J138" t="inlineStr"/>
-      <c r="K138" t="inlineStr"/>
-      <c r="N138" t="inlineStr"/>
       <c r="P138" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>444309</v>
+        <v>444172</v>
       </c>
       <c r="R138" t="n">
-        <v>6787272</v>
+        <v>6787339</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -14660,7 +14667,6 @@
       <c r="AE138" t="b">
         <v>0</v>
       </c>
-      <c r="AF138" t="inlineStr"/>
       <c r="AG138" t="b">
         <v>0</v>
       </c>
@@ -14679,7 +14685,7 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>129795274</v>
+        <v>129795251</v>
       </c>
       <c r="B139" t="n">
         <v>79081</v>
@@ -14708,16 +14714,19 @@
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
+      <c r="J139" t="inlineStr"/>
+      <c r="K139" t="inlineStr"/>
+      <c r="N139" t="inlineStr"/>
       <c r="P139" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>444538</v>
+        <v>444309</v>
       </c>
       <c r="R139" t="n">
-        <v>6787325</v>
+        <v>6787272</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -14758,6 +14767,7 @@
       <c r="AE139" t="b">
         <v>0</v>
       </c>
+      <c r="AF139" t="inlineStr"/>
       <c r="AG139" t="b">
         <v>0</v>
       </c>
@@ -14776,7 +14786,7 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>129795254</v>
+        <v>129795274</v>
       </c>
       <c r="B140" t="n">
         <v>79081</v>
@@ -14805,19 +14815,16 @@
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
-      <c r="J140" t="inlineStr"/>
-      <c r="K140" t="inlineStr"/>
-      <c r="N140" t="inlineStr"/>
       <c r="P140" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>444199</v>
+        <v>444538</v>
       </c>
       <c r="R140" t="n">
-        <v>6787221</v>
+        <v>6787325</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -14858,7 +14865,6 @@
       <c r="AE140" t="b">
         <v>0</v>
       </c>
-      <c r="AF140" t="inlineStr"/>
       <c r="AG140" t="b">
         <v>0</v>
       </c>
@@ -14877,7 +14883,7 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>129795266</v>
+        <v>129795254</v>
       </c>
       <c r="B141" t="n">
         <v>79081</v>
@@ -14906,16 +14912,19 @@
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
+      <c r="J141" t="inlineStr"/>
+      <c r="K141" t="inlineStr"/>
+      <c r="N141" t="inlineStr"/>
       <c r="P141" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>444314</v>
+        <v>444199</v>
       </c>
       <c r="R141" t="n">
-        <v>6787212</v>
+        <v>6787221</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -14950,17 +14959,13 @@
           <t>2025-11-22</t>
         </is>
       </c>
-      <c r="AC141" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 40m</t>
-        </is>
-      </c>
       <c r="AD141" t="b">
         <v>0</v>
       </c>
       <c r="AE141" t="b">
         <v>0</v>
       </c>
+      <c r="AF141" t="inlineStr"/>
       <c r="AG141" t="b">
         <v>0</v>
       </c>
@@ -14979,7 +14984,7 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>129795302</v>
+        <v>129795266</v>
       </c>
       <c r="B142" t="n">
         <v>79081</v>
@@ -15014,10 +15019,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>444222</v>
+        <v>444314</v>
       </c>
       <c r="R142" t="n">
-        <v>6787345</v>
+        <v>6787212</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -15050,6 +15055,11 @@
       <c r="AA142" t="inlineStr">
         <is>
           <t>2025-11-22</t>
+        </is>
+      </c>
+      <c r="AC142" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 40m</t>
         </is>
       </c>
       <c r="AD142" t="b">
@@ -15076,54 +15086,45 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>129795204</v>
+        <v>129795302</v>
       </c>
       <c r="B143" t="n">
-        <v>8450</v>
+        <v>79081</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E143" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
-      <c r="J143" t="inlineStr"/>
-      <c r="K143" t="inlineStr"/>
-      <c r="L143" t="inlineStr"/>
-      <c r="M143" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N143" t="inlineStr"/>
       <c r="P143" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>444380</v>
+        <v>444222</v>
       </c>
       <c r="R143" t="n">
-        <v>6787306</v>
+        <v>6787345</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -15164,7 +15165,6 @@
       <c r="AE143" t="b">
         <v>0</v>
       </c>
-      <c r="AF143" t="inlineStr"/>
       <c r="AG143" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 51041-2025 artfynd.xlsx
+++ b/artfynd/A 51041-2025 artfynd.xlsx
@@ -675,37 +675,43 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129795283</v>
+        <v>129795169</v>
       </c>
       <c r="B2" t="n">
-        <v>79081</v>
+        <v>8450</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -713,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>444337</v>
+        <v>444272</v>
       </c>
       <c r="R2" t="n">
-        <v>6787374</v>
+        <v>6787239</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -776,45 +782,54 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129795261</v>
+        <v>129795190</v>
       </c>
       <c r="B3" t="n">
-        <v>79081</v>
+        <v>8450</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>444193</v>
+        <v>444510</v>
       </c>
       <c r="R3" t="n">
-        <v>6787130</v>
+        <v>6787276</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -855,6 +870,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -873,45 +889,54 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129795253</v>
+        <v>129795197</v>
       </c>
       <c r="B4" t="n">
-        <v>79081</v>
+        <v>8450</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>444185</v>
+        <v>444406</v>
       </c>
       <c r="R4" t="n">
-        <v>6787247</v>
+        <v>6787392</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -946,17 +971,13 @@
           <t>2025-11-22</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Gott om garnlav inom en radie av 50 m.</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -975,7 +996,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129795285</v>
+        <v>129795283</v>
       </c>
       <c r="B5" t="n">
         <v>79081</v>
@@ -1004,16 +1025,19 @@
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>444405</v>
+        <v>444337</v>
       </c>
       <c r="R5" t="n">
-        <v>6787405</v>
+        <v>6787374</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1054,6 +1078,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1072,7 +1097,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129795244</v>
+        <v>129795285</v>
       </c>
       <c r="B6" t="n">
         <v>79081</v>
@@ -1107,10 +1132,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>444105</v>
+        <v>444405</v>
       </c>
       <c r="R6" t="n">
-        <v>6787246</v>
+        <v>6787405</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1169,7 +1194,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129795291</v>
+        <v>129795244</v>
       </c>
       <c r="B7" t="n">
         <v>79081</v>
@@ -1204,10 +1229,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>444412</v>
+        <v>444105</v>
       </c>
       <c r="R7" t="n">
-        <v>6787307</v>
+        <v>6787246</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1266,7 +1291,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129795298</v>
+        <v>129795291</v>
       </c>
       <c r="B8" t="n">
         <v>79081</v>
@@ -1301,10 +1326,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>444305</v>
+        <v>444412</v>
       </c>
       <c r="R8" t="n">
-        <v>6787353</v>
+        <v>6787307</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1363,54 +1388,45 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129795169</v>
+        <v>129795298</v>
       </c>
       <c r="B9" t="n">
-        <v>8450</v>
+        <v>79081</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>444272</v>
+        <v>444305</v>
       </c>
       <c r="R9" t="n">
-        <v>6787239</v>
+        <v>6787353</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1451,7 +1467,6 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1470,54 +1485,45 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129795190</v>
+        <v>129795253</v>
       </c>
       <c r="B10" t="n">
-        <v>8450</v>
+        <v>79081</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>444510</v>
+        <v>444185</v>
       </c>
       <c r="R10" t="n">
-        <v>6787276</v>
+        <v>6787247</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1552,13 +1558,17 @@
           <t>2025-11-22</t>
         </is>
       </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Gott om garnlav inom en radie av 50 m.</t>
+        </is>
+      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1577,54 +1587,45 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129795197</v>
+        <v>129795261</v>
       </c>
       <c r="B11" t="n">
-        <v>8450</v>
+        <v>79081</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>444406</v>
+        <v>444193</v>
       </c>
       <c r="R11" t="n">
-        <v>6787392</v>
+        <v>6787130</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1665,7 +1666,6 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1684,40 +1684,41 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129795155</v>
+        <v>129795174</v>
       </c>
       <c r="B12" t="n">
-        <v>57733</v>
+        <v>8450</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N12" t="inlineStr"/>
@@ -1727,10 +1728,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>444498</v>
+        <v>444166</v>
       </c>
       <c r="R12" t="n">
-        <v>6787306</v>
+        <v>6787161</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1771,6 +1772,7 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1789,40 +1791,41 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129795163</v>
+        <v>129795205</v>
       </c>
       <c r="B13" t="n">
-        <v>57733</v>
+        <v>8450</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N13" t="inlineStr"/>
@@ -1832,10 +1835,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>444415</v>
+        <v>444343</v>
       </c>
       <c r="R13" t="n">
-        <v>6787316</v>
+        <v>6787310</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1876,6 +1879,7 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -1894,10 +1898,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129795153</v>
+        <v>129795281</v>
       </c>
       <c r="B14" t="n">
-        <v>57733</v>
+        <v>79081</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1905,31 +1909,26 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -1937,10 +1936,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>444452</v>
+        <v>444408</v>
       </c>
       <c r="R14" t="n">
-        <v>6787294</v>
+        <v>6787452</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1981,6 +1980,7 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -1999,7 +1999,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129795276</v>
+        <v>129795271</v>
       </c>
       <c r="B15" t="n">
         <v>79081</v>
@@ -2037,10 +2037,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>444499</v>
+        <v>444466</v>
       </c>
       <c r="R15" t="n">
-        <v>6787367</v>
+        <v>6787306</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2105,7 +2105,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129795271</v>
+        <v>129795276</v>
       </c>
       <c r="B16" t="n">
         <v>79081</v>
@@ -2143,10 +2143,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>444466</v>
+        <v>444499</v>
       </c>
       <c r="R16" t="n">
-        <v>6787306</v>
+        <v>6787367</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2211,7 +2211,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129795281</v>
+        <v>129795299</v>
       </c>
       <c r="B17" t="n">
         <v>79081</v>
@@ -2240,19 +2240,16 @@
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>444408</v>
+        <v>444265</v>
       </c>
       <c r="R17" t="n">
-        <v>6787452</v>
+        <v>6787372</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2293,7 +2290,6 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2312,10 +2308,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129795299</v>
+        <v>129795155</v>
       </c>
       <c r="B18" t="n">
-        <v>79081</v>
+        <v>57733</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2323,34 +2319,42 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>444265</v>
+        <v>444498</v>
       </c>
       <c r="R18" t="n">
-        <v>6787372</v>
+        <v>6787306</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2409,41 +2413,40 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129795174</v>
+        <v>129795163</v>
       </c>
       <c r="B19" t="n">
-        <v>8450</v>
+        <v>57733</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
       <c r="M19" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N19" t="inlineStr"/>
@@ -2453,10 +2456,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>444166</v>
+        <v>444415</v>
       </c>
       <c r="R19" t="n">
-        <v>6787161</v>
+        <v>6787316</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2497,7 +2500,6 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2516,41 +2518,40 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129795205</v>
+        <v>129795153</v>
       </c>
       <c r="B20" t="n">
-        <v>8450</v>
+        <v>57733</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N20" t="inlineStr"/>
@@ -2560,10 +2561,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>444343</v>
+        <v>444452</v>
       </c>
       <c r="R20" t="n">
-        <v>6787310</v>
+        <v>6787294</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2604,7 +2605,6 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2623,45 +2623,54 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129795265</v>
+        <v>129795198</v>
       </c>
       <c r="B21" t="n">
-        <v>79081</v>
+        <v>8450</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>444278</v>
+        <v>444434</v>
       </c>
       <c r="R21" t="n">
-        <v>6787163</v>
+        <v>6787384</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2702,6 +2711,7 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -2720,45 +2730,54 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129795278</v>
+        <v>129795207</v>
       </c>
       <c r="B22" t="n">
-        <v>79081</v>
+        <v>8450</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>444465</v>
+        <v>444221</v>
       </c>
       <c r="R22" t="n">
-        <v>6787451</v>
+        <v>6787340</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2799,6 +2818,7 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -2817,37 +2837,43 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129795310</v>
+        <v>129795200</v>
       </c>
       <c r="B23" t="n">
-        <v>79081</v>
+        <v>8450</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -2855,10 +2881,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>444488</v>
+        <v>444429</v>
       </c>
       <c r="R23" t="n">
-        <v>6787445</v>
+        <v>6787341</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2891,11 +2917,6 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-11-22</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Gott om garnlav inom en radie av 40m</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2923,45 +2944,54 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129795273</v>
+        <v>129795206</v>
       </c>
       <c r="B24" t="n">
-        <v>79081</v>
+        <v>8450</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>444548</v>
+        <v>444247</v>
       </c>
       <c r="R24" t="n">
-        <v>6787330</v>
+        <v>6787328</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3002,6 +3032,7 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3020,54 +3051,45 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129795198</v>
+        <v>129795265</v>
       </c>
       <c r="B25" t="n">
-        <v>8450</v>
+        <v>79081</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>444434</v>
+        <v>444278</v>
       </c>
       <c r="R25" t="n">
-        <v>6787384</v>
+        <v>6787163</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3108,7 +3130,6 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3127,43 +3148,37 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129795207</v>
+        <v>129795310</v>
       </c>
       <c r="B26" t="n">
-        <v>8450</v>
+        <v>79081</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3171,10 +3186,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>444221</v>
+        <v>444488</v>
       </c>
       <c r="R26" t="n">
-        <v>6787340</v>
+        <v>6787445</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3207,6 +3222,11 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-11-22</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Gott om garnlav inom en radie av 40m</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3234,54 +3254,45 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129795200</v>
+        <v>129795278</v>
       </c>
       <c r="B27" t="n">
-        <v>8450</v>
+        <v>79081</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>444429</v>
+        <v>444465</v>
       </c>
       <c r="R27" t="n">
-        <v>6787341</v>
+        <v>6787451</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3322,7 +3333,6 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
-      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3341,54 +3351,45 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129795206</v>
+        <v>129795273</v>
       </c>
       <c r="B28" t="n">
-        <v>8450</v>
+        <v>79081</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>444247</v>
+        <v>444548</v>
       </c>
       <c r="R28" t="n">
-        <v>6787328</v>
+        <v>6787330</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3429,7 +3430,6 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
-      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -3448,10 +3448,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129795256</v>
+        <v>129795142</v>
       </c>
       <c r="B29" t="n">
-        <v>79081</v>
+        <v>57733</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3459,34 +3459,42 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>444226</v>
+        <v>444276</v>
       </c>
       <c r="R29" t="n">
-        <v>6787196</v>
+        <v>6787287</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3545,54 +3553,45 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129795187</v>
+        <v>129795268</v>
       </c>
       <c r="B30" t="n">
-        <v>8450</v>
+        <v>79081</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>444487</v>
+        <v>444383</v>
       </c>
       <c r="R30" t="n">
-        <v>6787321</v>
+        <v>6787218</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3633,7 +3632,6 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
-      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -3652,54 +3650,45 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129795189</v>
+        <v>129795256</v>
       </c>
       <c r="B31" t="n">
-        <v>8450</v>
+        <v>79081</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>444500</v>
+        <v>444226</v>
       </c>
       <c r="R31" t="n">
-        <v>6787274</v>
+        <v>6787196</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3740,7 +3729,6 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
-      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
@@ -3759,7 +3747,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129795176</v>
+        <v>129795187</v>
       </c>
       <c r="B32" t="n">
         <v>8450</v>
@@ -3793,7 +3781,7 @@
       <c r="L32" t="inlineStr"/>
       <c r="M32" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N32" t="inlineStr"/>
@@ -3803,10 +3791,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>444215</v>
+        <v>444487</v>
       </c>
       <c r="R32" t="n">
-        <v>6787151</v>
+        <v>6787321</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3866,40 +3854,41 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129795142</v>
+        <v>129795189</v>
       </c>
       <c r="B33" t="n">
-        <v>57733</v>
+        <v>8450</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr"/>
       <c r="L33" t="inlineStr"/>
       <c r="M33" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N33" t="inlineStr"/>
@@ -3909,10 +3898,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>444276</v>
+        <v>444500</v>
       </c>
       <c r="R33" t="n">
-        <v>6787287</v>
+        <v>6787274</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3953,6 +3942,7 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
+      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -3971,45 +3961,54 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129795268</v>
+        <v>129795176</v>
       </c>
       <c r="B34" t="n">
-        <v>79081</v>
+        <v>8450</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>444383</v>
+        <v>444215</v>
       </c>
       <c r="R34" t="n">
-        <v>6787218</v>
+        <v>6787151</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4050,6 +4049,7 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
+      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
@@ -4068,7 +4068,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129795269</v>
+        <v>129795296</v>
       </c>
       <c r="B35" t="n">
         <v>79081</v>
@@ -4097,16 +4097,19 @@
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>444429</v>
+        <v>444299</v>
       </c>
       <c r="R35" t="n">
-        <v>6787240</v>
+        <v>6787304</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4141,12 +4144,18 @@
           <t>2025-11-22</t>
         </is>
       </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 50 m.</t>
+        </is>
+      </c>
       <c r="AD35" t="b">
         <v>0</v>
       </c>
       <c r="AE35" t="b">
         <v>0</v>
       </c>
+      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
@@ -4165,7 +4174,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129795249</v>
+        <v>129795269</v>
       </c>
       <c r="B36" t="n">
         <v>79081</v>
@@ -4200,10 +4209,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>444267</v>
+        <v>444429</v>
       </c>
       <c r="R36" t="n">
-        <v>6787295</v>
+        <v>6787240</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4262,7 +4271,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129795296</v>
+        <v>129795249</v>
       </c>
       <c r="B37" t="n">
         <v>79081</v>
@@ -4291,19 +4300,16 @@
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
-      <c r="K37" t="inlineStr"/>
-      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>444299</v>
+        <v>444267</v>
       </c>
       <c r="R37" t="n">
-        <v>6787304</v>
+        <v>6787295</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4338,18 +4344,12 @@
           <t>2025-11-22</t>
         </is>
       </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 50 m.</t>
-        </is>
-      </c>
       <c r="AD37" t="b">
         <v>0</v>
       </c>
       <c r="AE37" t="b">
         <v>0</v>
       </c>
-      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -4465,41 +4465,40 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129795193</v>
+        <v>129795165</v>
       </c>
       <c r="B39" t="n">
-        <v>8450</v>
+        <v>57733</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr"/>
       <c r="L39" t="inlineStr"/>
       <c r="M39" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N39" t="inlineStr"/>
@@ -4509,10 +4508,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>444508</v>
+        <v>444251</v>
       </c>
       <c r="R39" t="n">
-        <v>6787352</v>
+        <v>6787376</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4553,7 +4552,6 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
-      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -4572,7 +4570,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129795202</v>
+        <v>129795193</v>
       </c>
       <c r="B40" t="n">
         <v>8450</v>
@@ -4616,10 +4614,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>444413</v>
+        <v>444508</v>
       </c>
       <c r="R40" t="n">
-        <v>6787314</v>
+        <v>6787352</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4679,40 +4677,41 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129795165</v>
+        <v>129795202</v>
       </c>
       <c r="B41" t="n">
-        <v>57733</v>
+        <v>8450</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
       <c r="K41" t="inlineStr"/>
       <c r="L41" t="inlineStr"/>
       <c r="M41" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N41" t="inlineStr"/>
@@ -4722,10 +4721,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>444251</v>
+        <v>444413</v>
       </c>
       <c r="R41" t="n">
-        <v>6787376</v>
+        <v>6787314</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4766,6 +4765,7 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
+      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
@@ -4990,7 +4990,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129795293</v>
+        <v>129795282</v>
       </c>
       <c r="B44" t="n">
         <v>79081</v>
@@ -5019,16 +5019,19 @@
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
+      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>444365</v>
+        <v>444374</v>
       </c>
       <c r="R44" t="n">
-        <v>6787285</v>
+        <v>6787384</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5065,7 +5068,7 @@
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>Rikligt med garnlav inom en radie av 50m.</t>
+          <t>Rikligt med garnlav inom en radie av 50 m.</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5074,6 +5077,7 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
+      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
@@ -5092,7 +5096,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129795282</v>
+        <v>129795293</v>
       </c>
       <c r="B45" t="n">
         <v>79081</v>
@@ -5121,19 +5125,16 @@
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="J45" t="inlineStr"/>
-      <c r="K45" t="inlineStr"/>
-      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>444374</v>
+        <v>444365</v>
       </c>
       <c r="R45" t="n">
-        <v>6787384</v>
+        <v>6787285</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5170,7 +5171,7 @@
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>Rikligt med garnlav inom en radie av 50 m.</t>
+          <t>Rikligt med garnlav inom en radie av 50m.</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5179,7 +5180,6 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
-      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
@@ -5198,41 +5198,40 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129795170</v>
+        <v>129795158</v>
       </c>
       <c r="B46" t="n">
-        <v>8450</v>
+        <v>57733</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="J46" t="inlineStr"/>
       <c r="K46" t="inlineStr"/>
       <c r="L46" t="inlineStr"/>
       <c r="M46" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N46" t="inlineStr"/>
@@ -5242,10 +5241,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>444172</v>
+        <v>444501</v>
       </c>
       <c r="R46" t="n">
-        <v>6787202</v>
+        <v>6787402</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5286,7 +5285,6 @@
       <c r="AE46" t="b">
         <v>0</v>
       </c>
-      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
@@ -5305,40 +5303,41 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129795158</v>
+        <v>129795170</v>
       </c>
       <c r="B47" t="n">
-        <v>57733</v>
+        <v>8450</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr"/>
       <c r="K47" t="inlineStr"/>
       <c r="L47" t="inlineStr"/>
       <c r="M47" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N47" t="inlineStr"/>
@@ -5348,10 +5347,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>444501</v>
+        <v>444172</v>
       </c>
       <c r="R47" t="n">
-        <v>6787402</v>
+        <v>6787202</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5392,6 +5391,7 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
+      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
@@ -5511,7 +5511,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129795246</v>
+        <v>129795309</v>
       </c>
       <c r="B49" t="n">
         <v>79081</v>
@@ -5546,10 +5546,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>444145</v>
+        <v>444095</v>
       </c>
       <c r="R49" t="n">
-        <v>6787239</v>
+        <v>6787293</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5586,7 +5586,7 @@
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>Rikligt med garnlav inom en radie av 40m.</t>
+          <t>8.32</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5613,7 +5613,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129795260</v>
+        <v>129795246</v>
       </c>
       <c r="B50" t="n">
         <v>79081</v>
@@ -5648,10 +5648,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>444197</v>
+        <v>444145</v>
       </c>
       <c r="R50" t="n">
-        <v>6787111</v>
+        <v>6787239</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5684,6 +5684,11 @@
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-11-22</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 40m.</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5710,7 +5715,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129795309</v>
+        <v>129795260</v>
       </c>
       <c r="B51" t="n">
         <v>79081</v>
@@ -5745,10 +5750,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>444095</v>
+        <v>444197</v>
       </c>
       <c r="R51" t="n">
-        <v>6787293</v>
+        <v>6787111</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5781,11 +5786,6 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-11-22</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>8.32</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5909,10 +5909,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129795161</v>
+        <v>129795279</v>
       </c>
       <c r="B53" t="n">
-        <v>57733</v>
+        <v>79081</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5920,42 +5920,34 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="K53" t="inlineStr"/>
-      <c r="L53" t="inlineStr"/>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>444433</v>
+        <v>444463</v>
       </c>
       <c r="R53" t="n">
-        <v>6787338</v>
+        <v>6787459</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6014,40 +6006,41 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129795147</v>
+        <v>129795184</v>
       </c>
       <c r="B54" t="n">
-        <v>57733</v>
+        <v>8450</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
+      <c r="J54" t="inlineStr"/>
       <c r="K54" t="inlineStr"/>
       <c r="L54" t="inlineStr"/>
       <c r="M54" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N54" t="inlineStr"/>
@@ -6057,10 +6050,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>444220</v>
+        <v>444452</v>
       </c>
       <c r="R54" t="n">
-        <v>6787221</v>
+        <v>6787305</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6101,6 +6094,7 @@
       <c r="AE54" t="b">
         <v>0</v>
       </c>
+      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
@@ -6119,10 +6113,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129795131</v>
+        <v>129795172</v>
       </c>
       <c r="B55" t="n">
-        <v>56926</v>
+        <v>8450</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6130,29 +6124,30 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>100138</v>
+        <v>106545</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
+      <c r="J55" t="inlineStr"/>
       <c r="K55" t="inlineStr"/>
       <c r="L55" t="inlineStr"/>
       <c r="M55" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N55" t="inlineStr"/>
@@ -6162,10 +6157,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>444250</v>
+        <v>444225</v>
       </c>
       <c r="R55" t="n">
-        <v>6787212</v>
+        <v>6787223</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6206,6 +6201,7 @@
       <c r="AE55" t="b">
         <v>0</v>
       </c>
+      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
@@ -6224,7 +6220,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129795184</v>
+        <v>129795199</v>
       </c>
       <c r="B56" t="n">
         <v>8450</v>
@@ -6268,10 +6264,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>444452</v>
+        <v>444431</v>
       </c>
       <c r="R56" t="n">
-        <v>6787305</v>
+        <v>6787350</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6331,54 +6327,45 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129795172</v>
+        <v>129795277</v>
       </c>
       <c r="B57" t="n">
-        <v>8450</v>
+        <v>79081</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
-      <c r="J57" t="inlineStr"/>
-      <c r="K57" t="inlineStr"/>
-      <c r="L57" t="inlineStr"/>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>444225</v>
+        <v>444491</v>
       </c>
       <c r="R57" t="n">
-        <v>6787223</v>
+        <v>6787412</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6419,7 +6406,6 @@
       <c r="AE57" t="b">
         <v>0</v>
       </c>
-      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
@@ -6438,41 +6424,40 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129795199</v>
+        <v>129795161</v>
       </c>
       <c r="B58" t="n">
-        <v>8450</v>
+        <v>57733</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
-      <c r="J58" t="inlineStr"/>
       <c r="K58" t="inlineStr"/>
       <c r="L58" t="inlineStr"/>
       <c r="M58" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N58" t="inlineStr"/>
@@ -6482,10 +6467,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>444431</v>
+        <v>444433</v>
       </c>
       <c r="R58" t="n">
-        <v>6787350</v>
+        <v>6787338</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6526,7 +6511,6 @@
       <c r="AE58" t="b">
         <v>0</v>
       </c>
-      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
       </c>
@@ -6545,10 +6529,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129795279</v>
+        <v>129795147</v>
       </c>
       <c r="B59" t="n">
-        <v>79081</v>
+        <v>57733</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6556,34 +6540,42 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
+      <c r="K59" t="inlineStr"/>
+      <c r="L59" t="inlineStr"/>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>444463</v>
+        <v>444220</v>
       </c>
       <c r="R59" t="n">
-        <v>6787459</v>
+        <v>6787221</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6642,45 +6634,53 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129795277</v>
+        <v>129795131</v>
       </c>
       <c r="B60" t="n">
-        <v>79081</v>
+        <v>56926</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
+      <c r="K60" t="inlineStr"/>
+      <c r="L60" t="inlineStr"/>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>444491</v>
+        <v>444250</v>
       </c>
       <c r="R60" t="n">
-        <v>6787412</v>
+        <v>6787212</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6844,41 +6844,40 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129795191</v>
+        <v>129795162</v>
       </c>
       <c r="B62" t="n">
-        <v>8450</v>
+        <v>57733</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
-      <c r="J62" t="inlineStr"/>
       <c r="K62" t="inlineStr"/>
       <c r="L62" t="inlineStr"/>
       <c r="M62" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N62" t="inlineStr"/>
@@ -6888,10 +6887,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>444520</v>
+        <v>444428</v>
       </c>
       <c r="R62" t="n">
-        <v>6787287</v>
+        <v>6787329</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6932,7 +6931,6 @@
       <c r="AE62" t="b">
         <v>0</v>
       </c>
-      <c r="AF62" t="inlineStr"/>
       <c r="AG62" t="b">
         <v>0</v>
       </c>
@@ -6951,54 +6949,45 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129795195</v>
+        <v>129795125</v>
       </c>
       <c r="B63" t="n">
-        <v>8450</v>
+        <v>79700</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
-      <c r="J63" t="inlineStr"/>
-      <c r="K63" t="inlineStr"/>
-      <c r="L63" t="inlineStr"/>
-      <c r="M63" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>444487</v>
+        <v>444329</v>
       </c>
       <c r="R63" t="n">
-        <v>6787441</v>
+        <v>6787371</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7039,7 +7028,6 @@
       <c r="AE63" t="b">
         <v>0</v>
       </c>
-      <c r="AF63" t="inlineStr"/>
       <c r="AG63" t="b">
         <v>0</v>
       </c>
@@ -7058,7 +7046,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129795177</v>
+        <v>129795191</v>
       </c>
       <c r="B64" t="n">
         <v>8450</v>
@@ -7092,7 +7080,7 @@
       <c r="L64" t="inlineStr"/>
       <c r="M64" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N64" t="inlineStr"/>
@@ -7102,10 +7090,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>444342</v>
+        <v>444520</v>
       </c>
       <c r="R64" t="n">
-        <v>6787223</v>
+        <v>6787287</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7165,40 +7153,41 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129795162</v>
+        <v>129795195</v>
       </c>
       <c r="B65" t="n">
-        <v>57733</v>
+        <v>8450</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
+      <c r="J65" t="inlineStr"/>
       <c r="K65" t="inlineStr"/>
       <c r="L65" t="inlineStr"/>
       <c r="M65" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N65" t="inlineStr"/>
@@ -7208,10 +7197,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>444428</v>
+        <v>444487</v>
       </c>
       <c r="R65" t="n">
-        <v>6787329</v>
+        <v>6787441</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7252,6 +7241,7 @@
       <c r="AE65" t="b">
         <v>0</v>
       </c>
+      <c r="AF65" t="inlineStr"/>
       <c r="AG65" t="b">
         <v>0</v>
       </c>
@@ -7270,45 +7260,54 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129795125</v>
+        <v>129795177</v>
       </c>
       <c r="B66" t="n">
-        <v>79700</v>
+        <v>8450</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
+      <c r="J66" t="inlineStr"/>
+      <c r="K66" t="inlineStr"/>
+      <c r="L66" t="inlineStr"/>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>444329</v>
+        <v>444342</v>
       </c>
       <c r="R66" t="n">
-        <v>6787371</v>
+        <v>6787223</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7349,6 +7348,7 @@
       <c r="AE66" t="b">
         <v>0</v>
       </c>
+      <c r="AF66" t="inlineStr"/>
       <c r="AG66" t="b">
         <v>0</v>
       </c>
@@ -7670,7 +7670,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129795243</v>
+        <v>129795272</v>
       </c>
       <c r="B70" t="n">
         <v>79081</v>
@@ -7705,10 +7705,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>444159</v>
+        <v>444553</v>
       </c>
       <c r="R70" t="n">
-        <v>6787297</v>
+        <v>6787299</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7767,7 +7767,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129795287</v>
+        <v>129795243</v>
       </c>
       <c r="B71" t="n">
         <v>79081</v>
@@ -7802,10 +7802,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>444430</v>
+        <v>444159</v>
       </c>
       <c r="R71" t="n">
-        <v>6787384</v>
+        <v>6787297</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7864,7 +7864,7 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129795272</v>
+        <v>129795287</v>
       </c>
       <c r="B72" t="n">
         <v>79081</v>
@@ -7899,10 +7899,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>444553</v>
+        <v>444430</v>
       </c>
       <c r="R72" t="n">
-        <v>6787299</v>
+        <v>6787384</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7961,10 +7961,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129795166</v>
+        <v>129795280</v>
       </c>
       <c r="B73" t="n">
-        <v>57733</v>
+        <v>79081</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7972,42 +7972,34 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
-      <c r="K73" t="inlineStr"/>
-      <c r="L73" t="inlineStr"/>
-      <c r="M73" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>444254</v>
+        <v>444451</v>
       </c>
       <c r="R73" t="n">
-        <v>6787333</v>
+        <v>6787467</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8066,7 +8058,7 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129795280</v>
+        <v>129795284</v>
       </c>
       <c r="B74" t="n">
         <v>79081</v>
@@ -8101,10 +8093,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>444451</v>
+        <v>444363</v>
       </c>
       <c r="R74" t="n">
-        <v>6787467</v>
+        <v>6787411</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8163,45 +8155,53 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129795284</v>
+        <v>129795208</v>
       </c>
       <c r="B75" t="n">
-        <v>79081</v>
+        <v>58106</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6425</v>
+        <v>103015</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
+      <c r="K75" t="inlineStr"/>
+      <c r="L75" t="inlineStr"/>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>444363</v>
+        <v>444434</v>
       </c>
       <c r="R75" t="n">
-        <v>6787411</v>
+        <v>6787357</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8260,27 +8260,27 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129795208</v>
+        <v>129795166</v>
       </c>
       <c r="B76" t="n">
-        <v>58106</v>
+        <v>57733</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>103015</v>
+        <v>100049</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -8293,7 +8293,7 @@
       <c r="L76" t="inlineStr"/>
       <c r="M76" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N76" t="inlineStr"/>
@@ -8303,10 +8303,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>444434</v>
+        <v>444254</v>
       </c>
       <c r="R76" t="n">
-        <v>6787357</v>
+        <v>6787333</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8472,10 +8472,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129795126</v>
+        <v>129795300</v>
       </c>
       <c r="B78" t="n">
-        <v>79700</v>
+        <v>79081</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8483,34 +8483,37 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
+      <c r="J78" t="inlineStr"/>
+      <c r="K78" t="inlineStr"/>
+      <c r="N78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>444358</v>
+        <v>444264</v>
       </c>
       <c r="R78" t="n">
-        <v>6787400</v>
+        <v>6787349</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8545,12 +8548,18 @@
           <t>2025-11-22</t>
         </is>
       </c>
+      <c r="AC78" t="inlineStr">
+        <is>
+          <t>Garnlav i de flesta träd inom en radie av 50 m.</t>
+        </is>
+      </c>
       <c r="AD78" t="b">
         <v>0</v>
       </c>
       <c r="AE78" t="b">
         <v>0</v>
       </c>
+      <c r="AF78" t="inlineStr"/>
       <c r="AG78" t="b">
         <v>0</v>
       </c>
@@ -8772,10 +8781,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129795300</v>
+        <v>129795126</v>
       </c>
       <c r="B81" t="n">
-        <v>79081</v>
+        <v>79700</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8783,37 +8792,34 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
-      <c r="J81" t="inlineStr"/>
-      <c r="K81" t="inlineStr"/>
-      <c r="N81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>444264</v>
+        <v>444358</v>
       </c>
       <c r="R81" t="n">
-        <v>6787349</v>
+        <v>6787400</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8848,18 +8854,12 @@
           <t>2025-11-22</t>
         </is>
       </c>
-      <c r="AC81" t="inlineStr">
-        <is>
-          <t>Garnlav i de flesta träd inom en radie av 50 m.</t>
-        </is>
-      </c>
       <c r="AD81" t="b">
         <v>0</v>
       </c>
       <c r="AE81" t="b">
         <v>0</v>
       </c>
-      <c r="AF81" t="inlineStr"/>
       <c r="AG81" t="b">
         <v>0</v>
       </c>
@@ -9694,40 +9694,41 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>129795152</v>
+        <v>129795167</v>
       </c>
       <c r="B90" t="n">
-        <v>57733</v>
+        <v>8450</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
+      <c r="J90" t="inlineStr"/>
       <c r="K90" t="inlineStr"/>
       <c r="L90" t="inlineStr"/>
       <c r="M90" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N90" t="inlineStr"/>
@@ -9737,10 +9738,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>444434</v>
+        <v>444132</v>
       </c>
       <c r="R90" t="n">
-        <v>6787304</v>
+        <v>6787237</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9781,6 +9782,7 @@
       <c r="AE90" t="b">
         <v>0</v>
       </c>
+      <c r="AF90" t="inlineStr"/>
       <c r="AG90" t="b">
         <v>0</v>
       </c>
@@ -9799,10 +9801,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>129795121</v>
+        <v>129795245</v>
       </c>
       <c r="B91" t="n">
-        <v>79700</v>
+        <v>79081</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9810,21 +9812,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -9834,10 +9836,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>444254</v>
+        <v>444113</v>
       </c>
       <c r="R91" t="n">
-        <v>6787204</v>
+        <v>6787239</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9993,7 +9995,7 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>129795252</v>
+        <v>129795262</v>
       </c>
       <c r="B93" t="n">
         <v>79081</v>
@@ -10028,10 +10030,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>444249</v>
+        <v>444219</v>
       </c>
       <c r="R93" t="n">
-        <v>6787249</v>
+        <v>6787163</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10064,11 +10066,6 @@
       <c r="AA93" t="inlineStr">
         <is>
           <t>2025-11-22</t>
-        </is>
-      </c>
-      <c r="AC93" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 40m.</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10095,7 +10092,7 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>129795245</v>
+        <v>129795252</v>
       </c>
       <c r="B94" t="n">
         <v>79081</v>
@@ -10130,10 +10127,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>444113</v>
+        <v>444249</v>
       </c>
       <c r="R94" t="n">
-        <v>6787239</v>
+        <v>6787249</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10166,6 +10163,11 @@
       <c r="AA94" t="inlineStr">
         <is>
           <t>2025-11-22</t>
+        </is>
+      </c>
+      <c r="AC94" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 40m.</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10192,7 +10194,7 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>129795123</v>
+        <v>129795121</v>
       </c>
       <c r="B95" t="n">
         <v>79700</v>
@@ -10227,10 +10229,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>444530</v>
+        <v>444254</v>
       </c>
       <c r="R95" t="n">
-        <v>6787326</v>
+        <v>6787204</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10289,10 +10291,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>129795288</v>
+        <v>129795123</v>
       </c>
       <c r="B96" t="n">
-        <v>79081</v>
+        <v>79700</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10300,21 +10302,21 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10324,10 +10326,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>444420</v>
+        <v>444530</v>
       </c>
       <c r="R96" t="n">
-        <v>6787366</v>
+        <v>6787326</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10386,7 +10388,7 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>129795305</v>
+        <v>129795288</v>
       </c>
       <c r="B97" t="n">
         <v>79081</v>
@@ -10421,10 +10423,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>444169</v>
+        <v>444420</v>
       </c>
       <c r="R97" t="n">
-        <v>6787323</v>
+        <v>6787366</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10483,10 +10485,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>129795124</v>
+        <v>129795305</v>
       </c>
       <c r="B98" t="n">
-        <v>79700</v>
+        <v>79081</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10494,21 +10496,21 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10518,10 +10520,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>444393</v>
+        <v>444169</v>
       </c>
       <c r="R98" t="n">
-        <v>6787395</v>
+        <v>6787323</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10580,10 +10582,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>129795262</v>
+        <v>129795124</v>
       </c>
       <c r="B99" t="n">
-        <v>79081</v>
+        <v>79700</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10591,21 +10593,21 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -10615,10 +10617,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>444219</v>
+        <v>444393</v>
       </c>
       <c r="R99" t="n">
-        <v>6787163</v>
+        <v>6787395</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10677,41 +10679,40 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>129795167</v>
+        <v>129795152</v>
       </c>
       <c r="B100" t="n">
-        <v>8450</v>
+        <v>57733</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
-      <c r="J100" t="inlineStr"/>
       <c r="K100" t="inlineStr"/>
       <c r="L100" t="inlineStr"/>
       <c r="M100" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N100" t="inlineStr"/>
@@ -10721,10 +10722,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>444132</v>
+        <v>444434</v>
       </c>
       <c r="R100" t="n">
-        <v>6787237</v>
+        <v>6787304</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10765,7 +10766,6 @@
       <c r="AE100" t="b">
         <v>0</v>
       </c>
-      <c r="AF100" t="inlineStr"/>
       <c r="AG100" t="b">
         <v>0</v>
       </c>
@@ -10784,7 +10784,7 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>129795186</v>
+        <v>129795185</v>
       </c>
       <c r="B101" t="n">
         <v>8450</v>
@@ -10828,10 +10828,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>444473</v>
+        <v>444458</v>
       </c>
       <c r="R101" t="n">
-        <v>6787334</v>
+        <v>6787304</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10891,7 +10891,7 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>129795185</v>
+        <v>129795180</v>
       </c>
       <c r="B102" t="n">
         <v>8450</v>
@@ -10935,10 +10935,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>444458</v>
+        <v>444409</v>
       </c>
       <c r="R102" t="n">
-        <v>6787304</v>
+        <v>6787219</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -10998,7 +10998,7 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>129795180</v>
+        <v>129795178</v>
       </c>
       <c r="B103" t="n">
         <v>8450</v>
@@ -11042,10 +11042,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>444409</v>
+        <v>444375</v>
       </c>
       <c r="R103" t="n">
-        <v>6787219</v>
+        <v>6787207</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11105,7 +11105,7 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>129795178</v>
+        <v>129795186</v>
       </c>
       <c r="B104" t="n">
         <v>8450</v>
@@ -11149,10 +11149,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>444375</v>
+        <v>444473</v>
       </c>
       <c r="R104" t="n">
-        <v>6787207</v>
+        <v>6787334</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11319,7 +11319,7 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>129795303</v>
+        <v>129795264</v>
       </c>
       <c r="B106" t="n">
         <v>79081</v>
@@ -11354,10 +11354,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>444200</v>
+        <v>444252</v>
       </c>
       <c r="R106" t="n">
-        <v>6787331</v>
+        <v>6787160</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11416,7 +11416,7 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>129795264</v>
+        <v>129795248</v>
       </c>
       <c r="B107" t="n">
         <v>79081</v>
@@ -11451,10 +11451,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>444252</v>
+        <v>444238</v>
       </c>
       <c r="R107" t="n">
-        <v>6787160</v>
+        <v>6787281</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11513,7 +11513,7 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>129795248</v>
+        <v>129795303</v>
       </c>
       <c r="B108" t="n">
         <v>79081</v>
@@ -11548,10 +11548,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>444238</v>
+        <v>444200</v>
       </c>
       <c r="R108" t="n">
-        <v>6787281</v>
+        <v>6787331</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -12119,7 +12119,7 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>129795201</v>
+        <v>129795203</v>
       </c>
       <c r="B114" t="n">
         <v>8450</v>
@@ -12163,10 +12163,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>444430</v>
+        <v>444401</v>
       </c>
       <c r="R114" t="n">
-        <v>6787332</v>
+        <v>6787298</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12226,7 +12226,7 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>129795203</v>
+        <v>129795201</v>
       </c>
       <c r="B115" t="n">
         <v>8450</v>
@@ -12270,10 +12270,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>444401</v>
+        <v>444430</v>
       </c>
       <c r="R115" t="n">
-        <v>6787298</v>
+        <v>6787332</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12333,10 +12333,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>129795289</v>
+        <v>129795164</v>
       </c>
       <c r="B116" t="n">
-        <v>79081</v>
+        <v>57733</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -12344,34 +12344,42 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
+      <c r="K116" t="inlineStr"/>
+      <c r="L116" t="inlineStr"/>
+      <c r="M116" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N116" t="inlineStr"/>
       <c r="P116" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>444435</v>
+        <v>444397</v>
       </c>
       <c r="R116" t="n">
-        <v>6787341</v>
+        <v>6787300</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12430,32 +12438,32 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>129795132</v>
+        <v>129795154</v>
       </c>
       <c r="B117" t="n">
-        <v>56926</v>
+        <v>57733</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -12463,7 +12471,7 @@
       <c r="L117" t="inlineStr"/>
       <c r="M117" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N117" t="inlineStr"/>
@@ -12473,10 +12481,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>444315</v>
+        <v>444457</v>
       </c>
       <c r="R117" t="n">
-        <v>6787291</v>
+        <v>6787303</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12535,41 +12543,40 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>129795171</v>
+        <v>129795157</v>
       </c>
       <c r="B118" t="n">
-        <v>8450</v>
+        <v>57733</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
-      <c r="J118" t="inlineStr"/>
       <c r="K118" t="inlineStr"/>
       <c r="L118" t="inlineStr"/>
       <c r="M118" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N118" t="inlineStr"/>
@@ -12579,10 +12586,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>444185</v>
+        <v>444525</v>
       </c>
       <c r="R118" t="n">
-        <v>6787226</v>
+        <v>6787344</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12623,7 +12630,6 @@
       <c r="AE118" t="b">
         <v>0</v>
       </c>
-      <c r="AF118" t="inlineStr"/>
       <c r="AG118" t="b">
         <v>0</v>
       </c>
@@ -12642,10 +12648,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>129795164</v>
+        <v>129795289</v>
       </c>
       <c r="B119" t="n">
-        <v>57733</v>
+        <v>79081</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -12653,42 +12659,34 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
-      <c r="K119" t="inlineStr"/>
-      <c r="L119" t="inlineStr"/>
-      <c r="M119" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N119" t="inlineStr"/>
       <c r="P119" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>444397</v>
+        <v>444435</v>
       </c>
       <c r="R119" t="n">
-        <v>6787300</v>
+        <v>6787341</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -12747,32 +12745,32 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>129795154</v>
+        <v>129795132</v>
       </c>
       <c r="B120" t="n">
-        <v>57733</v>
+        <v>56926</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -12780,7 +12778,7 @@
       <c r="L120" t="inlineStr"/>
       <c r="M120" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="N120" t="inlineStr"/>
@@ -12790,10 +12788,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>444457</v>
+        <v>444315</v>
       </c>
       <c r="R120" t="n">
-        <v>6787303</v>
+        <v>6787291</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -12852,40 +12850,41 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>129795157</v>
+        <v>129795171</v>
       </c>
       <c r="B121" t="n">
-        <v>57733</v>
+        <v>8450</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
+      <c r="J121" t="inlineStr"/>
       <c r="K121" t="inlineStr"/>
       <c r="L121" t="inlineStr"/>
       <c r="M121" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N121" t="inlineStr"/>
@@ -12895,10 +12894,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>444525</v>
+        <v>444185</v>
       </c>
       <c r="R121" t="n">
-        <v>6787344</v>
+        <v>6787226</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -12939,6 +12938,7 @@
       <c r="AE121" t="b">
         <v>0</v>
       </c>
+      <c r="AF121" t="inlineStr"/>
       <c r="AG121" t="b">
         <v>0</v>
       </c>
@@ -12957,10 +12957,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>129795144</v>
+        <v>129795294</v>
       </c>
       <c r="B122" t="n">
-        <v>57733</v>
+        <v>79081</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -12968,42 +12968,34 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
-      <c r="K122" t="inlineStr"/>
-      <c r="L122" t="inlineStr"/>
-      <c r="M122" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N122" t="inlineStr"/>
       <c r="P122" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>444186</v>
+        <v>444323</v>
       </c>
       <c r="R122" t="n">
-        <v>6787223</v>
+        <v>6787297</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -13062,41 +13054,40 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>129795188</v>
+        <v>129795144</v>
       </c>
       <c r="B123" t="n">
-        <v>8450</v>
+        <v>57733</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
-      <c r="J123" t="inlineStr"/>
       <c r="K123" t="inlineStr"/>
       <c r="L123" t="inlineStr"/>
       <c r="M123" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N123" t="inlineStr"/>
@@ -13106,10 +13097,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>444498</v>
+        <v>444186</v>
       </c>
       <c r="R123" t="n">
-        <v>6787280</v>
+        <v>6787223</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13150,7 +13141,6 @@
       <c r="AE123" t="b">
         <v>0</v>
       </c>
-      <c r="AF123" t="inlineStr"/>
       <c r="AG123" t="b">
         <v>0</v>
       </c>
@@ -13169,54 +13159,45 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>129795179</v>
+        <v>129795301</v>
       </c>
       <c r="B124" t="n">
-        <v>8450</v>
+        <v>79081</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
-      <c r="J124" t="inlineStr"/>
-      <c r="K124" t="inlineStr"/>
-      <c r="L124" t="inlineStr"/>
-      <c r="M124" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N124" t="inlineStr"/>
       <c r="P124" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>444378</v>
+        <v>444250</v>
       </c>
       <c r="R124" t="n">
-        <v>6787236</v>
+        <v>6787342</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13257,7 +13238,6 @@
       <c r="AE124" t="b">
         <v>0</v>
       </c>
-      <c r="AF124" t="inlineStr"/>
       <c r="AG124" t="b">
         <v>0</v>
       </c>
@@ -13276,45 +13256,54 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>129795301</v>
+        <v>129795188</v>
       </c>
       <c r="B125" t="n">
-        <v>79081</v>
+        <v>8450</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
+      <c r="J125" t="inlineStr"/>
+      <c r="K125" t="inlineStr"/>
+      <c r="L125" t="inlineStr"/>
+      <c r="M125" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N125" t="inlineStr"/>
       <c r="P125" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>444250</v>
+        <v>444498</v>
       </c>
       <c r="R125" t="n">
-        <v>6787342</v>
+        <v>6787280</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13355,6 +13344,7 @@
       <c r="AE125" t="b">
         <v>0</v>
       </c>
+      <c r="AF125" t="inlineStr"/>
       <c r="AG125" t="b">
         <v>0</v>
       </c>
@@ -13373,45 +13363,54 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>129795294</v>
+        <v>129795179</v>
       </c>
       <c r="B126" t="n">
-        <v>79081</v>
+        <v>8450</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
+      <c r="J126" t="inlineStr"/>
+      <c r="K126" t="inlineStr"/>
+      <c r="L126" t="inlineStr"/>
+      <c r="M126" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N126" t="inlineStr"/>
       <c r="P126" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>444323</v>
+        <v>444378</v>
       </c>
       <c r="R126" t="n">
-        <v>6787297</v>
+        <v>6787236</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -13452,6 +13451,7 @@
       <c r="AE126" t="b">
         <v>0</v>
       </c>
+      <c r="AF126" t="inlineStr"/>
       <c r="AG126" t="b">
         <v>0</v>
       </c>
@@ -13575,54 +13575,45 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>129795175</v>
+        <v>129795275</v>
       </c>
       <c r="B128" t="n">
-        <v>8450</v>
+        <v>79081</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
-      <c r="J128" t="inlineStr"/>
-      <c r="K128" t="inlineStr"/>
-      <c r="L128" t="inlineStr"/>
-      <c r="M128" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N128" t="inlineStr"/>
       <c r="P128" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>444182</v>
+        <v>444495</v>
       </c>
       <c r="R128" t="n">
-        <v>6787101</v>
+        <v>6787340</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -13663,7 +13654,6 @@
       <c r="AE128" t="b">
         <v>0</v>
       </c>
-      <c r="AF128" t="inlineStr"/>
       <c r="AG128" t="b">
         <v>0</v>
       </c>
@@ -13682,54 +13672,45 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>129795168</v>
+        <v>129795267</v>
       </c>
       <c r="B129" t="n">
-        <v>8450</v>
+        <v>79081</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
-      <c r="J129" t="inlineStr"/>
-      <c r="K129" t="inlineStr"/>
-      <c r="L129" t="inlineStr"/>
-      <c r="M129" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N129" t="inlineStr"/>
       <c r="P129" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>444272</v>
+        <v>444353</v>
       </c>
       <c r="R129" t="n">
-        <v>6787286</v>
+        <v>6787215</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -13764,13 +13745,17 @@
           <t>2025-11-22</t>
         </is>
       </c>
+      <c r="AC129" t="inlineStr">
+        <is>
+          <t>Gott om garnlav inom en radie av 40m.</t>
+        </is>
+      </c>
       <c r="AD129" t="b">
         <v>0</v>
       </c>
       <c r="AE129" t="b">
         <v>0</v>
       </c>
-      <c r="AF129" t="inlineStr"/>
       <c r="AG129" t="b">
         <v>0</v>
       </c>
@@ -13789,10 +13774,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>129795137</v>
+        <v>129795263</v>
       </c>
       <c r="B130" t="n">
-        <v>91620</v>
+        <v>79081</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -13800,37 +13785,34 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
-      <c r="J130" t="inlineStr"/>
-      <c r="K130" t="inlineStr"/>
-      <c r="N130" t="inlineStr"/>
       <c r="P130" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>444203</v>
+        <v>444241</v>
       </c>
       <c r="R130" t="n">
-        <v>6787221</v>
+        <v>6787149</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -13871,7 +13853,6 @@
       <c r="AE130" t="b">
         <v>0</v>
       </c>
-      <c r="AF130" t="inlineStr"/>
       <c r="AG130" t="b">
         <v>0</v>
       </c>
@@ -13890,10 +13871,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>129795275</v>
+        <v>129795137</v>
       </c>
       <c r="B131" t="n">
-        <v>79081</v>
+        <v>91620</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -13901,34 +13882,37 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
+      <c r="J131" t="inlineStr"/>
+      <c r="K131" t="inlineStr"/>
+      <c r="N131" t="inlineStr"/>
       <c r="P131" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>444495</v>
+        <v>444203</v>
       </c>
       <c r="R131" t="n">
-        <v>6787340</v>
+        <v>6787221</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -13969,6 +13953,7 @@
       <c r="AE131" t="b">
         <v>0</v>
       </c>
+      <c r="AF131" t="inlineStr"/>
       <c r="AG131" t="b">
         <v>0</v>
       </c>
@@ -13987,7 +13972,7 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>129795263</v>
+        <v>129795258</v>
       </c>
       <c r="B132" t="n">
         <v>79081</v>
@@ -14022,10 +14007,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>444241</v>
+        <v>444174</v>
       </c>
       <c r="R132" t="n">
-        <v>6787149</v>
+        <v>6787136</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -14084,45 +14069,54 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>129795267</v>
+        <v>129795175</v>
       </c>
       <c r="B133" t="n">
-        <v>79081</v>
+        <v>8450</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
+      <c r="J133" t="inlineStr"/>
+      <c r="K133" t="inlineStr"/>
+      <c r="L133" t="inlineStr"/>
+      <c r="M133" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N133" t="inlineStr"/>
       <c r="P133" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>444353</v>
+        <v>444182</v>
       </c>
       <c r="R133" t="n">
-        <v>6787215</v>
+        <v>6787101</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -14157,17 +14151,13 @@
           <t>2025-11-22</t>
         </is>
       </c>
-      <c r="AC133" t="inlineStr">
-        <is>
-          <t>Gott om garnlav inom en radie av 40m.</t>
-        </is>
-      </c>
       <c r="AD133" t="b">
         <v>0</v>
       </c>
       <c r="AE133" t="b">
         <v>0</v>
       </c>
+      <c r="AF133" t="inlineStr"/>
       <c r="AG133" t="b">
         <v>0</v>
       </c>
@@ -14186,45 +14176,54 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>129795258</v>
+        <v>129795168</v>
       </c>
       <c r="B134" t="n">
-        <v>79081</v>
+        <v>8450</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
+      <c r="J134" t="inlineStr"/>
+      <c r="K134" t="inlineStr"/>
+      <c r="L134" t="inlineStr"/>
+      <c r="M134" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N134" t="inlineStr"/>
       <c r="P134" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>444174</v>
+        <v>444272</v>
       </c>
       <c r="R134" t="n">
-        <v>6787136</v>
+        <v>6787286</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -14265,6 +14264,7 @@
       <c r="AE134" t="b">
         <v>0</v>
       </c>
+      <c r="AF134" t="inlineStr"/>
       <c r="AG134" t="b">
         <v>0</v>
       </c>
@@ -14283,54 +14283,45 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>129795204</v>
+        <v>129795304</v>
       </c>
       <c r="B135" t="n">
-        <v>8450</v>
+        <v>79081</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
-      <c r="J135" t="inlineStr"/>
-      <c r="K135" t="inlineStr"/>
-      <c r="L135" t="inlineStr"/>
-      <c r="M135" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N135" t="inlineStr"/>
       <c r="P135" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>444380</v>
+        <v>444172</v>
       </c>
       <c r="R135" t="n">
-        <v>6787306</v>
+        <v>6787339</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -14371,7 +14362,6 @@
       <c r="AE135" t="b">
         <v>0</v>
       </c>
-      <c r="AF135" t="inlineStr"/>
       <c r="AG135" t="b">
         <v>0</v>
       </c>
@@ -14390,10 +14380,10 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>129795139</v>
+        <v>129795251</v>
       </c>
       <c r="B136" t="n">
-        <v>91620</v>
+        <v>79081</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -14401,21 +14391,21 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
@@ -14428,10 +14418,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>444342</v>
+        <v>444309</v>
       </c>
       <c r="R136" t="n">
-        <v>6787240</v>
+        <v>6787272</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -14491,7 +14481,7 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>129795247</v>
+        <v>129795266</v>
       </c>
       <c r="B137" t="n">
         <v>79081</v>
@@ -14526,10 +14516,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>444225</v>
+        <v>444314</v>
       </c>
       <c r="R137" t="n">
-        <v>6787275</v>
+        <v>6787212</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -14562,6 +14552,11 @@
       <c r="AA137" t="inlineStr">
         <is>
           <t>2025-11-22</t>
+        </is>
+      </c>
+      <c r="AC137" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 40m</t>
         </is>
       </c>
       <c r="AD137" t="b">
@@ -14588,7 +14583,7 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>129795304</v>
+        <v>129795247</v>
       </c>
       <c r="B138" t="n">
         <v>79081</v>
@@ -14623,10 +14618,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>444172</v>
+        <v>444225</v>
       </c>
       <c r="R138" t="n">
-        <v>6787339</v>
+        <v>6787275</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -14685,10 +14680,10 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>129795251</v>
+        <v>129795139</v>
       </c>
       <c r="B139" t="n">
-        <v>79081</v>
+        <v>91620</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -14696,21 +14691,21 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
@@ -14723,10 +14718,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>444309</v>
+        <v>444342</v>
       </c>
       <c r="R139" t="n">
-        <v>6787272</v>
+        <v>6787240</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -14984,7 +14979,7 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>129795266</v>
+        <v>129795302</v>
       </c>
       <c r="B142" t="n">
         <v>79081</v>
@@ -15019,10 +15014,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>444314</v>
+        <v>444222</v>
       </c>
       <c r="R142" t="n">
-        <v>6787212</v>
+        <v>6787345</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -15055,11 +15050,6 @@
       <c r="AA142" t="inlineStr">
         <is>
           <t>2025-11-22</t>
-        </is>
-      </c>
-      <c r="AC142" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 40m</t>
         </is>
       </c>
       <c r="AD142" t="b">
@@ -15086,45 +15076,54 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>129795302</v>
+        <v>129795204</v>
       </c>
       <c r="B143" t="n">
-        <v>79081</v>
+        <v>8450</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E143" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
+      <c r="J143" t="inlineStr"/>
+      <c r="K143" t="inlineStr"/>
+      <c r="L143" t="inlineStr"/>
+      <c r="M143" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N143" t="inlineStr"/>
       <c r="P143" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>444222</v>
+        <v>444380</v>
       </c>
       <c r="R143" t="n">
-        <v>6787345</v>
+        <v>6787306</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -15165,6 +15164,7 @@
       <c r="AE143" t="b">
         <v>0</v>
       </c>
+      <c r="AF143" t="inlineStr"/>
       <c r="AG143" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 51041-2025 artfynd.xlsx
+++ b/artfynd/A 51041-2025 artfynd.xlsx
@@ -675,43 +675,37 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129795169</v>
+        <v>129795283</v>
       </c>
       <c r="B2" t="n">
-        <v>8450</v>
+        <v>79081</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -719,10 +713,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>444272</v>
+        <v>444337</v>
       </c>
       <c r="R2" t="n">
-        <v>6787239</v>
+        <v>6787374</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -782,54 +776,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129795190</v>
+        <v>129795285</v>
       </c>
       <c r="B3" t="n">
-        <v>8450</v>
+        <v>79081</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>444510</v>
+        <v>444405</v>
       </c>
       <c r="R3" t="n">
-        <v>6787276</v>
+        <v>6787405</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -870,7 +855,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -889,54 +873,45 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129795197</v>
+        <v>129795244</v>
       </c>
       <c r="B4" t="n">
-        <v>8450</v>
+        <v>79081</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>444406</v>
+        <v>444105</v>
       </c>
       <c r="R4" t="n">
-        <v>6787392</v>
+        <v>6787246</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -977,7 +952,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -996,7 +970,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129795283</v>
+        <v>129795291</v>
       </c>
       <c r="B5" t="n">
         <v>79081</v>
@@ -1025,19 +999,16 @@
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>444337</v>
+        <v>444412</v>
       </c>
       <c r="R5" t="n">
-        <v>6787374</v>
+        <v>6787307</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1078,7 +1049,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1097,7 +1067,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129795285</v>
+        <v>129795298</v>
       </c>
       <c r="B6" t="n">
         <v>79081</v>
@@ -1132,10 +1102,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>444405</v>
+        <v>444305</v>
       </c>
       <c r="R6" t="n">
-        <v>6787405</v>
+        <v>6787353</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1194,45 +1164,54 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129795244</v>
+        <v>129795169</v>
       </c>
       <c r="B7" t="n">
-        <v>79081</v>
+        <v>8450</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>444105</v>
+        <v>444272</v>
       </c>
       <c r="R7" t="n">
-        <v>6787246</v>
+        <v>6787239</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1273,6 +1252,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1291,45 +1271,54 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129795291</v>
+        <v>129795190</v>
       </c>
       <c r="B8" t="n">
-        <v>79081</v>
+        <v>8450</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>444412</v>
+        <v>444510</v>
       </c>
       <c r="R8" t="n">
-        <v>6787307</v>
+        <v>6787276</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1370,6 +1359,7 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1388,45 +1378,54 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129795298</v>
+        <v>129795197</v>
       </c>
       <c r="B9" t="n">
-        <v>79081</v>
+        <v>8450</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>444305</v>
+        <v>444406</v>
       </c>
       <c r="R9" t="n">
-        <v>6787353</v>
+        <v>6787392</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1467,6 +1466,7 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -2623,54 +2623,45 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129795198</v>
+        <v>129795265</v>
       </c>
       <c r="B21" t="n">
-        <v>8450</v>
+        <v>79081</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>444434</v>
+        <v>444278</v>
       </c>
       <c r="R21" t="n">
-        <v>6787384</v>
+        <v>6787163</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2711,7 +2702,6 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -2730,43 +2720,37 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129795207</v>
+        <v>129795310</v>
       </c>
       <c r="B22" t="n">
-        <v>8450</v>
+        <v>79081</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -2774,10 +2758,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>444221</v>
+        <v>444488</v>
       </c>
       <c r="R22" t="n">
-        <v>6787340</v>
+        <v>6787445</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2810,6 +2794,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-11-22</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Gott om garnlav inom en radie av 40m</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2837,54 +2826,45 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129795200</v>
+        <v>129795278</v>
       </c>
       <c r="B23" t="n">
-        <v>8450</v>
+        <v>79081</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>444429</v>
+        <v>444465</v>
       </c>
       <c r="R23" t="n">
-        <v>6787341</v>
+        <v>6787451</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2925,7 +2905,6 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -2944,54 +2923,45 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129795206</v>
+        <v>129795273</v>
       </c>
       <c r="B24" t="n">
-        <v>8450</v>
+        <v>79081</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>444247</v>
+        <v>444548</v>
       </c>
       <c r="R24" t="n">
-        <v>6787328</v>
+        <v>6787330</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3032,7 +3002,6 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3051,45 +3020,54 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129795265</v>
+        <v>129795198</v>
       </c>
       <c r="B25" t="n">
-        <v>79081</v>
+        <v>8450</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>444278</v>
+        <v>444434</v>
       </c>
       <c r="R25" t="n">
-        <v>6787163</v>
+        <v>6787384</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3130,6 +3108,7 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3148,37 +3127,43 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129795310</v>
+        <v>129795207</v>
       </c>
       <c r="B26" t="n">
-        <v>79081</v>
+        <v>8450</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3186,10 +3171,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>444488</v>
+        <v>444221</v>
       </c>
       <c r="R26" t="n">
-        <v>6787445</v>
+        <v>6787340</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3222,11 +3207,6 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-11-22</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Gott om garnlav inom en radie av 40m</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3254,45 +3234,54 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129795278</v>
+        <v>129795200</v>
       </c>
       <c r="B27" t="n">
-        <v>79081</v>
+        <v>8450</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>444465</v>
+        <v>444429</v>
       </c>
       <c r="R27" t="n">
-        <v>6787451</v>
+        <v>6787341</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3333,6 +3322,7 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
+      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3351,45 +3341,54 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129795273</v>
+        <v>129795206</v>
       </c>
       <c r="B28" t="n">
-        <v>79081</v>
+        <v>8450</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>444548</v>
+        <v>444247</v>
       </c>
       <c r="R28" t="n">
-        <v>6787330</v>
+        <v>6787328</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3430,6 +3429,7 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
+      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -6006,41 +6006,40 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129795184</v>
+        <v>129795161</v>
       </c>
       <c r="B54" t="n">
-        <v>8450</v>
+        <v>57733</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
-      <c r="J54" t="inlineStr"/>
       <c r="K54" t="inlineStr"/>
       <c r="L54" t="inlineStr"/>
       <c r="M54" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N54" t="inlineStr"/>
@@ -6050,10 +6049,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>444452</v>
+        <v>444433</v>
       </c>
       <c r="R54" t="n">
-        <v>6787305</v>
+        <v>6787338</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6094,7 +6093,6 @@
       <c r="AE54" t="b">
         <v>0</v>
       </c>
-      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
@@ -6113,41 +6111,40 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129795172</v>
+        <v>129795147</v>
       </c>
       <c r="B55" t="n">
-        <v>8450</v>
+        <v>57733</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
-      <c r="J55" t="inlineStr"/>
       <c r="K55" t="inlineStr"/>
       <c r="L55" t="inlineStr"/>
       <c r="M55" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N55" t="inlineStr"/>
@@ -6157,10 +6154,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>444225</v>
+        <v>444220</v>
       </c>
       <c r="R55" t="n">
-        <v>6787223</v>
+        <v>6787221</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6201,7 +6198,6 @@
       <c r="AE55" t="b">
         <v>0</v>
       </c>
-      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
@@ -6220,10 +6216,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129795199</v>
+        <v>129795131</v>
       </c>
       <c r="B56" t="n">
-        <v>8450</v>
+        <v>56926</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6231,30 +6227,29 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>106545</v>
+        <v>100138</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
-      <c r="J56" t="inlineStr"/>
       <c r="K56" t="inlineStr"/>
       <c r="L56" t="inlineStr"/>
       <c r="M56" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="N56" t="inlineStr"/>
@@ -6264,10 +6259,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>444431</v>
+        <v>444250</v>
       </c>
       <c r="R56" t="n">
-        <v>6787350</v>
+        <v>6787212</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6308,7 +6303,6 @@
       <c r="AE56" t="b">
         <v>0</v>
       </c>
-      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
       </c>
@@ -6327,10 +6321,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129795277</v>
+        <v>129795134</v>
       </c>
       <c r="B57" t="n">
-        <v>79081</v>
+        <v>57896</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6338,34 +6332,42 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
+      <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>444491</v>
+        <v>444289</v>
       </c>
       <c r="R57" t="n">
-        <v>6787412</v>
+        <v>6787357</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6424,40 +6426,41 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129795161</v>
+        <v>129795199</v>
       </c>
       <c r="B58" t="n">
-        <v>57733</v>
+        <v>8450</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
+      <c r="J58" t="inlineStr"/>
       <c r="K58" t="inlineStr"/>
       <c r="L58" t="inlineStr"/>
       <c r="M58" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N58" t="inlineStr"/>
@@ -6467,10 +6470,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>444433</v>
+        <v>444431</v>
       </c>
       <c r="R58" t="n">
-        <v>6787338</v>
+        <v>6787350</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6511,6 +6514,7 @@
       <c r="AE58" t="b">
         <v>0</v>
       </c>
+      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
       </c>
@@ -6529,10 +6533,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129795147</v>
+        <v>129795277</v>
       </c>
       <c r="B59" t="n">
-        <v>57733</v>
+        <v>79081</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6540,42 +6544,34 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
-      <c r="K59" t="inlineStr"/>
-      <c r="L59" t="inlineStr"/>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>444220</v>
+        <v>444491</v>
       </c>
       <c r="R59" t="n">
-        <v>6787221</v>
+        <v>6787412</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6634,10 +6630,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129795131</v>
+        <v>129795184</v>
       </c>
       <c r="B60" t="n">
-        <v>56926</v>
+        <v>8450</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6645,29 +6641,30 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>100138</v>
+        <v>106545</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
+      <c r="J60" t="inlineStr"/>
       <c r="K60" t="inlineStr"/>
       <c r="L60" t="inlineStr"/>
       <c r="M60" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N60" t="inlineStr"/>
@@ -6677,10 +6674,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>444250</v>
+        <v>444452</v>
       </c>
       <c r="R60" t="n">
-        <v>6787212</v>
+        <v>6787305</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6721,6 +6718,7 @@
       <c r="AE60" t="b">
         <v>0</v>
       </c>
+      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
       </c>
@@ -6739,40 +6737,41 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129795134</v>
+        <v>129795172</v>
       </c>
       <c r="B61" t="n">
-        <v>57896</v>
+        <v>8450</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>103021</v>
+        <v>106545</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
+      <c r="J61" t="inlineStr"/>
       <c r="K61" t="inlineStr"/>
       <c r="L61" t="inlineStr"/>
       <c r="M61" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N61" t="inlineStr"/>
@@ -6782,10 +6781,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>444289</v>
+        <v>444225</v>
       </c>
       <c r="R61" t="n">
-        <v>6787357</v>
+        <v>6787223</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6826,6 +6825,7 @@
       <c r="AE61" t="b">
         <v>0</v>
       </c>
+      <c r="AF61" t="inlineStr"/>
       <c r="AG61" t="b">
         <v>0</v>
       </c>
@@ -10784,54 +10784,45 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>129795185</v>
+        <v>129795264</v>
       </c>
       <c r="B101" t="n">
-        <v>8450</v>
+        <v>79081</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
-      <c r="J101" t="inlineStr"/>
-      <c r="K101" t="inlineStr"/>
-      <c r="L101" t="inlineStr"/>
-      <c r="M101" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>444458</v>
+        <v>444252</v>
       </c>
       <c r="R101" t="n">
-        <v>6787304</v>
+        <v>6787160</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10872,7 +10863,6 @@
       <c r="AE101" t="b">
         <v>0</v>
       </c>
-      <c r="AF101" t="inlineStr"/>
       <c r="AG101" t="b">
         <v>0</v>
       </c>
@@ -10891,54 +10881,45 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>129795180</v>
+        <v>129795248</v>
       </c>
       <c r="B102" t="n">
-        <v>8450</v>
+        <v>79081</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
-      <c r="J102" t="inlineStr"/>
-      <c r="K102" t="inlineStr"/>
-      <c r="L102" t="inlineStr"/>
-      <c r="M102" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>444409</v>
+        <v>444238</v>
       </c>
       <c r="R102" t="n">
-        <v>6787219</v>
+        <v>6787281</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -10979,7 +10960,6 @@
       <c r="AE102" t="b">
         <v>0</v>
       </c>
-      <c r="AF102" t="inlineStr"/>
       <c r="AG102" t="b">
         <v>0</v>
       </c>
@@ -10998,54 +10978,45 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>129795178</v>
+        <v>129795303</v>
       </c>
       <c r="B103" t="n">
-        <v>8450</v>
+        <v>79081</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
-      <c r="J103" t="inlineStr"/>
-      <c r="K103" t="inlineStr"/>
-      <c r="L103" t="inlineStr"/>
-      <c r="M103" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N103" t="inlineStr"/>
       <c r="P103" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>444375</v>
+        <v>444200</v>
       </c>
       <c r="R103" t="n">
-        <v>6787207</v>
+        <v>6787331</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11086,7 +11057,6 @@
       <c r="AE103" t="b">
         <v>0</v>
       </c>
-      <c r="AF103" t="inlineStr"/>
       <c r="AG103" t="b">
         <v>0</v>
       </c>
@@ -11105,54 +11075,45 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>129795186</v>
+        <v>129795306</v>
       </c>
       <c r="B104" t="n">
-        <v>8450</v>
+        <v>79081</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
-      <c r="J104" t="inlineStr"/>
-      <c r="K104" t="inlineStr"/>
-      <c r="L104" t="inlineStr"/>
-      <c r="M104" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>444473</v>
+        <v>444152</v>
       </c>
       <c r="R104" t="n">
-        <v>6787334</v>
+        <v>6787313</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11193,7 +11154,6 @@
       <c r="AE104" t="b">
         <v>0</v>
       </c>
-      <c r="AF104" t="inlineStr"/>
       <c r="AG104" t="b">
         <v>0</v>
       </c>
@@ -11212,7 +11172,7 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>129795196</v>
+        <v>129795185</v>
       </c>
       <c r="B105" t="n">
         <v>8450</v>
@@ -11256,10 +11216,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>444346</v>
+        <v>444458</v>
       </c>
       <c r="R105" t="n">
-        <v>6787369</v>
+        <v>6787304</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11319,45 +11279,54 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>129795264</v>
+        <v>129795180</v>
       </c>
       <c r="B106" t="n">
-        <v>79081</v>
+        <v>8450</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
+      <c r="J106" t="inlineStr"/>
+      <c r="K106" t="inlineStr"/>
+      <c r="L106" t="inlineStr"/>
+      <c r="M106" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>444252</v>
+        <v>444409</v>
       </c>
       <c r="R106" t="n">
-        <v>6787160</v>
+        <v>6787219</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11398,6 +11367,7 @@
       <c r="AE106" t="b">
         <v>0</v>
       </c>
+      <c r="AF106" t="inlineStr"/>
       <c r="AG106" t="b">
         <v>0</v>
       </c>
@@ -11416,45 +11386,54 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>129795248</v>
+        <v>129795178</v>
       </c>
       <c r="B107" t="n">
-        <v>79081</v>
+        <v>8450</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
+      <c r="J107" t="inlineStr"/>
+      <c r="K107" t="inlineStr"/>
+      <c r="L107" t="inlineStr"/>
+      <c r="M107" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>444238</v>
+        <v>444375</v>
       </c>
       <c r="R107" t="n">
-        <v>6787281</v>
+        <v>6787207</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11495,6 +11474,7 @@
       <c r="AE107" t="b">
         <v>0</v>
       </c>
+      <c r="AF107" t="inlineStr"/>
       <c r="AG107" t="b">
         <v>0</v>
       </c>
@@ -11513,45 +11493,54 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>129795303</v>
+        <v>129795186</v>
       </c>
       <c r="B108" t="n">
-        <v>79081</v>
+        <v>8450</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
+      <c r="J108" t="inlineStr"/>
+      <c r="K108" t="inlineStr"/>
+      <c r="L108" t="inlineStr"/>
+      <c r="M108" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>444200</v>
+        <v>444473</v>
       </c>
       <c r="R108" t="n">
-        <v>6787331</v>
+        <v>6787334</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11592,6 +11581,7 @@
       <c r="AE108" t="b">
         <v>0</v>
       </c>
+      <c r="AF108" t="inlineStr"/>
       <c r="AG108" t="b">
         <v>0</v>
       </c>
@@ -11610,45 +11600,54 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>129795306</v>
+        <v>129795196</v>
       </c>
       <c r="B109" t="n">
-        <v>79081</v>
+        <v>8450</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
+      <c r="J109" t="inlineStr"/>
+      <c r="K109" t="inlineStr"/>
+      <c r="L109" t="inlineStr"/>
+      <c r="M109" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>444152</v>
+        <v>444346</v>
       </c>
       <c r="R109" t="n">
-        <v>6787313</v>
+        <v>6787369</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11689,6 +11688,7 @@
       <c r="AE109" t="b">
         <v>0</v>
       </c>
+      <c r="AF109" t="inlineStr"/>
       <c r="AG109" t="b">
         <v>0</v>
       </c>
@@ -13470,40 +13470,41 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>129795159</v>
+        <v>129795175</v>
       </c>
       <c r="B127" t="n">
-        <v>57733</v>
+        <v>8450</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
+      <c r="J127" t="inlineStr"/>
       <c r="K127" t="inlineStr"/>
       <c r="L127" t="inlineStr"/>
       <c r="M127" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N127" t="inlineStr"/>
@@ -13513,10 +13514,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>444436</v>
+        <v>444182</v>
       </c>
       <c r="R127" t="n">
-        <v>6787463</v>
+        <v>6787101</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -13557,6 +13558,7 @@
       <c r="AE127" t="b">
         <v>0</v>
       </c>
+      <c r="AF127" t="inlineStr"/>
       <c r="AG127" t="b">
         <v>0</v>
       </c>
@@ -13575,45 +13577,54 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>129795275</v>
+        <v>129795168</v>
       </c>
       <c r="B128" t="n">
-        <v>79081</v>
+        <v>8450</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
+      <c r="J128" t="inlineStr"/>
+      <c r="K128" t="inlineStr"/>
+      <c r="L128" t="inlineStr"/>
+      <c r="M128" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N128" t="inlineStr"/>
       <c r="P128" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>444495</v>
+        <v>444272</v>
       </c>
       <c r="R128" t="n">
-        <v>6787340</v>
+        <v>6787286</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -13654,6 +13665,7 @@
       <c r="AE128" t="b">
         <v>0</v>
       </c>
+      <c r="AF128" t="inlineStr"/>
       <c r="AG128" t="b">
         <v>0</v>
       </c>
@@ -13672,7 +13684,7 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>129795267</v>
+        <v>129795275</v>
       </c>
       <c r="B129" t="n">
         <v>79081</v>
@@ -13707,10 +13719,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>444353</v>
+        <v>444495</v>
       </c>
       <c r="R129" t="n">
-        <v>6787215</v>
+        <v>6787340</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -13743,11 +13755,6 @@
       <c r="AA129" t="inlineStr">
         <is>
           <t>2025-11-22</t>
-        </is>
-      </c>
-      <c r="AC129" t="inlineStr">
-        <is>
-          <t>Gott om garnlav inom en radie av 40m.</t>
         </is>
       </c>
       <c r="AD129" t="b">
@@ -13774,7 +13781,7 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>129795263</v>
+        <v>129795267</v>
       </c>
       <c r="B130" t="n">
         <v>79081</v>
@@ -13809,10 +13816,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>444241</v>
+        <v>444353</v>
       </c>
       <c r="R130" t="n">
-        <v>6787149</v>
+        <v>6787215</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -13845,6 +13852,11 @@
       <c r="AA130" t="inlineStr">
         <is>
           <t>2025-11-22</t>
+        </is>
+      </c>
+      <c r="AC130" t="inlineStr">
+        <is>
+          <t>Gott om garnlav inom en radie av 40m.</t>
         </is>
       </c>
       <c r="AD130" t="b">
@@ -13871,10 +13883,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>129795137</v>
+        <v>129795263</v>
       </c>
       <c r="B131" t="n">
-        <v>91620</v>
+        <v>79081</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -13882,37 +13894,34 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
-      <c r="J131" t="inlineStr"/>
-      <c r="K131" t="inlineStr"/>
-      <c r="N131" t="inlineStr"/>
       <c r="P131" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>444203</v>
+        <v>444241</v>
       </c>
       <c r="R131" t="n">
-        <v>6787221</v>
+        <v>6787149</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -13953,7 +13962,6 @@
       <c r="AE131" t="b">
         <v>0</v>
       </c>
-      <c r="AF131" t="inlineStr"/>
       <c r="AG131" t="b">
         <v>0</v>
       </c>
@@ -13972,10 +13980,10 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>129795258</v>
+        <v>129795137</v>
       </c>
       <c r="B132" t="n">
-        <v>79081</v>
+        <v>91620</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -13983,34 +13991,37 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
+      <c r="J132" t="inlineStr"/>
+      <c r="K132" t="inlineStr"/>
+      <c r="N132" t="inlineStr"/>
       <c r="P132" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>444174</v>
+        <v>444203</v>
       </c>
       <c r="R132" t="n">
-        <v>6787136</v>
+        <v>6787221</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -14051,6 +14062,7 @@
       <c r="AE132" t="b">
         <v>0</v>
       </c>
+      <c r="AF132" t="inlineStr"/>
       <c r="AG132" t="b">
         <v>0</v>
       </c>
@@ -14069,54 +14081,45 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>129795175</v>
+        <v>129795258</v>
       </c>
       <c r="B133" t="n">
-        <v>8450</v>
+        <v>79081</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
-      <c r="J133" t="inlineStr"/>
-      <c r="K133" t="inlineStr"/>
-      <c r="L133" t="inlineStr"/>
-      <c r="M133" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N133" t="inlineStr"/>
       <c r="P133" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>444182</v>
+        <v>444174</v>
       </c>
       <c r="R133" t="n">
-        <v>6787101</v>
+        <v>6787136</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -14157,7 +14160,6 @@
       <c r="AE133" t="b">
         <v>0</v>
       </c>
-      <c r="AF133" t="inlineStr"/>
       <c r="AG133" t="b">
         <v>0</v>
       </c>
@@ -14176,41 +14178,40 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>129795168</v>
+        <v>129795159</v>
       </c>
       <c r="B134" t="n">
-        <v>8450</v>
+        <v>57733</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
-      <c r="J134" t="inlineStr"/>
       <c r="K134" t="inlineStr"/>
       <c r="L134" t="inlineStr"/>
       <c r="M134" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N134" t="inlineStr"/>
@@ -14220,10 +14221,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>444272</v>
+        <v>444436</v>
       </c>
       <c r="R134" t="n">
-        <v>6787286</v>
+        <v>6787463</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -14264,7 +14265,6 @@
       <c r="AE134" t="b">
         <v>0</v>
       </c>
-      <c r="AF134" t="inlineStr"/>
       <c r="AG134" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 51041-2025 artfynd.xlsx
+++ b/artfynd/A 51041-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129795283</v>
+        <v>129795253</v>
       </c>
       <c r="B2" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -704,19 +704,16 @@
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>444337</v>
+        <v>444185</v>
       </c>
       <c r="R2" t="n">
-        <v>6787374</v>
+        <v>6787247</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,13 +748,17 @@
           <t>2025-11-22</t>
         </is>
       </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Gott om garnlav inom en radie av 50 m.</t>
+        </is>
+      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -776,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129795285</v>
+        <v>129795291</v>
       </c>
       <c r="B3" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -811,10 +812,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>444405</v>
+        <v>444412</v>
       </c>
       <c r="R3" t="n">
-        <v>6787405</v>
+        <v>6787307</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -873,10 +874,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129795244</v>
+        <v>129795298</v>
       </c>
       <c r="B4" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -908,10 +909,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>444105</v>
+        <v>444305</v>
       </c>
       <c r="R4" t="n">
-        <v>6787246</v>
+        <v>6787353</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -970,10 +971,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129795291</v>
+        <v>129795285</v>
       </c>
       <c r="B5" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1005,10 +1006,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>444412</v>
+        <v>444405</v>
       </c>
       <c r="R5" t="n">
-        <v>6787307</v>
+        <v>6787405</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1067,10 +1068,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129795298</v>
+        <v>129795244</v>
       </c>
       <c r="B6" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1102,10 +1103,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>444305</v>
+        <v>444105</v>
       </c>
       <c r="R6" t="n">
-        <v>6787353</v>
+        <v>6787246</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1164,54 +1165,45 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129795169</v>
+        <v>129795261</v>
       </c>
       <c r="B7" t="n">
-        <v>8450</v>
+        <v>79084</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>444272</v>
+        <v>444193</v>
       </c>
       <c r="R7" t="n">
-        <v>6787239</v>
+        <v>6787130</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1252,7 +1244,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1271,43 +1262,37 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129795190</v>
+        <v>129795283</v>
       </c>
       <c r="B8" t="n">
-        <v>8450</v>
+        <v>79084</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1315,10 +1300,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>444510</v>
+        <v>444337</v>
       </c>
       <c r="R8" t="n">
-        <v>6787276</v>
+        <v>6787374</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1378,7 +1363,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129795197</v>
+        <v>129795169</v>
       </c>
       <c r="B9" t="n">
         <v>8450</v>
@@ -1422,10 +1407,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>444406</v>
+        <v>444272</v>
       </c>
       <c r="R9" t="n">
-        <v>6787392</v>
+        <v>6787239</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1485,45 +1470,54 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129795253</v>
+        <v>129795190</v>
       </c>
       <c r="B10" t="n">
-        <v>79081</v>
+        <v>8450</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>444185</v>
+        <v>444510</v>
       </c>
       <c r="R10" t="n">
-        <v>6787247</v>
+        <v>6787276</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1558,17 +1552,13 @@
           <t>2025-11-22</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Gott om garnlav inom en radie av 50 m.</t>
-        </is>
-      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1587,45 +1577,54 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129795261</v>
+        <v>129795197</v>
       </c>
       <c r="B11" t="n">
-        <v>79081</v>
+        <v>8450</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>444193</v>
+        <v>444406</v>
       </c>
       <c r="R11" t="n">
-        <v>6787130</v>
+        <v>6787392</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1666,6 +1665,7 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1684,43 +1684,37 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129795174</v>
+        <v>129795281</v>
       </c>
       <c r="B12" t="n">
-        <v>8450</v>
+        <v>79084</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1728,10 +1722,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>444166</v>
+        <v>444408</v>
       </c>
       <c r="R12" t="n">
-        <v>6787161</v>
+        <v>6787452</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1791,43 +1785,37 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129795205</v>
+        <v>129795271</v>
       </c>
       <c r="B13" t="n">
-        <v>8450</v>
+        <v>79084</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1835,10 +1823,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>444343</v>
+        <v>444466</v>
       </c>
       <c r="R13" t="n">
-        <v>6787310</v>
+        <v>6787306</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1871,6 +1859,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-11-22</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 50m.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1898,10 +1891,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129795281</v>
+        <v>129795276</v>
       </c>
       <c r="B14" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1936,10 +1929,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>444408</v>
+        <v>444499</v>
       </c>
       <c r="R14" t="n">
-        <v>6787452</v>
+        <v>6787367</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1972,6 +1965,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-11-22</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 50m.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -1999,10 +1997,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129795271</v>
+        <v>129795299</v>
       </c>
       <c r="B15" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2028,19 +2026,16 @@
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>444466</v>
+        <v>444265</v>
       </c>
       <c r="R15" t="n">
-        <v>6787306</v>
+        <v>6787372</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2075,18 +2070,12 @@
           <t>2025-11-22</t>
         </is>
       </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 50m.</t>
-        </is>
-      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2105,10 +2094,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129795276</v>
+        <v>129795155</v>
       </c>
       <c r="B16" t="n">
-        <v>79081</v>
+        <v>57734</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2116,26 +2105,31 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2143,10 +2137,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>444499</v>
+        <v>444498</v>
       </c>
       <c r="R16" t="n">
-        <v>6787367</v>
+        <v>6787306</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2181,18 +2175,12 @@
           <t>2025-11-22</t>
         </is>
       </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 50m.</t>
-        </is>
-      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2211,10 +2199,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129795299</v>
+        <v>129795163</v>
       </c>
       <c r="B17" t="n">
-        <v>79081</v>
+        <v>57734</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2222,34 +2210,42 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>444265</v>
+        <v>444415</v>
       </c>
       <c r="R17" t="n">
-        <v>6787372</v>
+        <v>6787316</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2308,10 +2304,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129795155</v>
+        <v>129795153</v>
       </c>
       <c r="B18" t="n">
-        <v>57733</v>
+        <v>57734</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2341,7 +2337,7 @@
       <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N18" t="inlineStr"/>
@@ -2351,10 +2347,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>444498</v>
+        <v>444452</v>
       </c>
       <c r="R18" t="n">
-        <v>6787306</v>
+        <v>6787294</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2413,40 +2409,41 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129795163</v>
+        <v>129795174</v>
       </c>
       <c r="B19" t="n">
-        <v>57733</v>
+        <v>8450</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
       <c r="M19" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N19" t="inlineStr"/>
@@ -2456,10 +2453,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>444415</v>
+        <v>444166</v>
       </c>
       <c r="R19" t="n">
-        <v>6787316</v>
+        <v>6787161</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2500,6 +2497,7 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2518,40 +2516,41 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129795153</v>
+        <v>129795205</v>
       </c>
       <c r="B20" t="n">
-        <v>57733</v>
+        <v>8450</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N20" t="inlineStr"/>
@@ -2561,10 +2560,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>444452</v>
+        <v>444343</v>
       </c>
       <c r="R20" t="n">
-        <v>6787294</v>
+        <v>6787310</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2605,6 +2604,7 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2626,7 +2626,7 @@
         <v>129795265</v>
       </c>
       <c r="B21" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2720,10 +2720,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129795310</v>
+        <v>129795273</v>
       </c>
       <c r="B22" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2749,19 +2749,16 @@
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>444488</v>
+        <v>444548</v>
       </c>
       <c r="R22" t="n">
-        <v>6787445</v>
+        <v>6787330</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2796,18 +2793,12 @@
           <t>2025-11-22</t>
         </is>
       </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Gott om garnlav inom en radie av 40m</t>
-        </is>
-      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -2826,10 +2817,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129795278</v>
+        <v>129795310</v>
       </c>
       <c r="B23" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2855,16 +2846,19 @@
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>444465</v>
+        <v>444488</v>
       </c>
       <c r="R23" t="n">
-        <v>6787451</v>
+        <v>6787445</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2899,12 +2893,18 @@
           <t>2025-11-22</t>
         </is>
       </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Gott om garnlav inom en radie av 40m</t>
+        </is>
+      </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -2923,10 +2923,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129795273</v>
+        <v>129795278</v>
       </c>
       <c r="B24" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2958,10 +2958,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>444548</v>
+        <v>444465</v>
       </c>
       <c r="R24" t="n">
-        <v>6787330</v>
+        <v>6787451</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3448,10 +3448,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129795142</v>
+        <v>129795268</v>
       </c>
       <c r="B29" t="n">
-        <v>57733</v>
+        <v>79084</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3459,42 +3459,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>444276</v>
+        <v>444383</v>
       </c>
       <c r="R29" t="n">
-        <v>6787287</v>
+        <v>6787218</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3553,10 +3545,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129795268</v>
+        <v>129795256</v>
       </c>
       <c r="B30" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3588,10 +3580,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>444383</v>
+        <v>444226</v>
       </c>
       <c r="R30" t="n">
-        <v>6787218</v>
+        <v>6787196</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3650,10 +3642,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129795256</v>
+        <v>129795142</v>
       </c>
       <c r="B31" t="n">
-        <v>79081</v>
+        <v>57734</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3661,34 +3653,42 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>444226</v>
+        <v>444276</v>
       </c>
       <c r="R31" t="n">
-        <v>6787196</v>
+        <v>6787287</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4068,10 +4068,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129795296</v>
+        <v>129795165</v>
       </c>
       <c r="B35" t="n">
-        <v>79081</v>
+        <v>57734</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4079,26 +4079,31 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
@@ -4106,10 +4111,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>444299</v>
+        <v>444251</v>
       </c>
       <c r="R35" t="n">
-        <v>6787304</v>
+        <v>6787376</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4144,18 +4149,12 @@
           <t>2025-11-22</t>
         </is>
       </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 50 m.</t>
-        </is>
-      </c>
       <c r="AD35" t="b">
         <v>0</v>
       </c>
       <c r="AE35" t="b">
         <v>0</v>
       </c>
-      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
@@ -4174,45 +4173,54 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129795269</v>
+        <v>129795193</v>
       </c>
       <c r="B36" t="n">
-        <v>79081</v>
+        <v>8450</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>444429</v>
+        <v>444508</v>
       </c>
       <c r="R36" t="n">
-        <v>6787240</v>
+        <v>6787352</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4253,6 +4261,7 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
+      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
@@ -4271,45 +4280,54 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129795249</v>
+        <v>129795202</v>
       </c>
       <c r="B37" t="n">
-        <v>79081</v>
+        <v>8450</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>444267</v>
+        <v>444413</v>
       </c>
       <c r="R37" t="n">
-        <v>6787295</v>
+        <v>6787314</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4350,6 +4368,7 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
+      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -4371,7 +4390,7 @@
         <v>129795270</v>
       </c>
       <c r="B38" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4465,10 +4484,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129795165</v>
+        <v>129795296</v>
       </c>
       <c r="B39" t="n">
-        <v>57733</v>
+        <v>79084</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4476,31 +4495,26 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
@@ -4508,10 +4522,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>444251</v>
+        <v>444299</v>
       </c>
       <c r="R39" t="n">
-        <v>6787376</v>
+        <v>6787304</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4546,12 +4560,18 @@
           <t>2025-11-22</t>
         </is>
       </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 50 m.</t>
+        </is>
+      </c>
       <c r="AD39" t="b">
         <v>0</v>
       </c>
       <c r="AE39" t="b">
         <v>0</v>
       </c>
+      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -4570,54 +4590,45 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129795193</v>
+        <v>129795269</v>
       </c>
       <c r="B40" t="n">
-        <v>8450</v>
+        <v>79084</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr"/>
-      <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>444508</v>
+        <v>444429</v>
       </c>
       <c r="R40" t="n">
-        <v>6787352</v>
+        <v>6787240</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4658,7 +4669,6 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
-      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
@@ -4677,54 +4687,45 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129795202</v>
+        <v>129795249</v>
       </c>
       <c r="B41" t="n">
-        <v>8450</v>
+        <v>79084</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr"/>
-      <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>444413</v>
+        <v>444267</v>
       </c>
       <c r="R41" t="n">
-        <v>6787314</v>
+        <v>6787295</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4765,7 +4766,6 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
-      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
@@ -4787,7 +4787,7 @@
         <v>129795133</v>
       </c>
       <c r="B42" t="n">
-        <v>57896</v>
+        <v>57895</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4892,7 +4892,7 @@
         <v>129795136</v>
       </c>
       <c r="B43" t="n">
-        <v>91620</v>
+        <v>91623</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4993,7 +4993,7 @@
         <v>129795282</v>
       </c>
       <c r="B44" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5099,7 +5099,7 @@
         <v>129795293</v>
       </c>
       <c r="B45" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5201,7 +5201,7 @@
         <v>129795158</v>
       </c>
       <c r="B46" t="n">
-        <v>57733</v>
+        <v>57734</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5413,7 +5413,7 @@
         <v>129795138</v>
       </c>
       <c r="B48" t="n">
-        <v>91620</v>
+        <v>91623</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5514,7 +5514,7 @@
         <v>129795309</v>
       </c>
       <c r="B49" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5613,10 +5613,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129795246</v>
+        <v>129795260</v>
       </c>
       <c r="B50" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5648,10 +5648,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>444145</v>
+        <v>444197</v>
       </c>
       <c r="R50" t="n">
-        <v>6787239</v>
+        <v>6787111</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5684,11 +5684,6 @@
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-11-22</t>
-        </is>
-      </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 40m.</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5715,10 +5710,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129795260</v>
+        <v>129795250</v>
       </c>
       <c r="B51" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5750,10 +5745,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>444197</v>
+        <v>444295</v>
       </c>
       <c r="R51" t="n">
-        <v>6787111</v>
+        <v>6787287</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5812,10 +5807,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129795250</v>
+        <v>129795246</v>
       </c>
       <c r="B52" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5847,10 +5842,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>444295</v>
+        <v>444145</v>
       </c>
       <c r="R52" t="n">
-        <v>6787287</v>
+        <v>6787239</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5883,6 +5878,11 @@
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-11-22</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 40m.</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -5909,10 +5909,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129795279</v>
+        <v>129795161</v>
       </c>
       <c r="B53" t="n">
-        <v>79081</v>
+        <v>57734</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5920,34 +5920,42 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
+      <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>444463</v>
+        <v>444433</v>
       </c>
       <c r="R53" t="n">
-        <v>6787459</v>
+        <v>6787338</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6006,10 +6014,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129795161</v>
+        <v>129795147</v>
       </c>
       <c r="B54" t="n">
-        <v>57733</v>
+        <v>57734</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6049,10 +6057,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>444433</v>
+        <v>444220</v>
       </c>
       <c r="R54" t="n">
-        <v>6787338</v>
+        <v>6787221</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6111,32 +6119,32 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129795147</v>
+        <v>129795131</v>
       </c>
       <c r="B55" t="n">
-        <v>57733</v>
+        <v>56927</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6144,7 +6152,7 @@
       <c r="L55" t="inlineStr"/>
       <c r="M55" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="N55" t="inlineStr"/>
@@ -6154,10 +6162,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>444220</v>
+        <v>444250</v>
       </c>
       <c r="R55" t="n">
-        <v>6787221</v>
+        <v>6787212</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6216,32 +6224,32 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129795131</v>
+        <v>129795134</v>
       </c>
       <c r="B56" t="n">
-        <v>56926</v>
+        <v>57895</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>100138</v>
+        <v>103021</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6249,7 +6257,7 @@
       <c r="L56" t="inlineStr"/>
       <c r="M56" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N56" t="inlineStr"/>
@@ -6259,10 +6267,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>444250</v>
+        <v>444289</v>
       </c>
       <c r="R56" t="n">
-        <v>6787212</v>
+        <v>6787357</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6321,10 +6329,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129795134</v>
+        <v>129795277</v>
       </c>
       <c r="B57" t="n">
-        <v>57896</v>
+        <v>79084</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6332,42 +6340,34 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
-      <c r="K57" t="inlineStr"/>
-      <c r="L57" t="inlineStr"/>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>444289</v>
+        <v>444491</v>
       </c>
       <c r="R57" t="n">
-        <v>6787357</v>
+        <v>6787412</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6426,54 +6426,45 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129795199</v>
+        <v>129795279</v>
       </c>
       <c r="B58" t="n">
-        <v>8450</v>
+        <v>79084</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
-      <c r="J58" t="inlineStr"/>
-      <c r="K58" t="inlineStr"/>
-      <c r="L58" t="inlineStr"/>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>444431</v>
+        <v>444463</v>
       </c>
       <c r="R58" t="n">
-        <v>6787350</v>
+        <v>6787459</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6514,7 +6505,6 @@
       <c r="AE58" t="b">
         <v>0</v>
       </c>
-      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
       </c>
@@ -6533,45 +6523,54 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129795277</v>
+        <v>129795184</v>
       </c>
       <c r="B59" t="n">
-        <v>79081</v>
+        <v>8450</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
+      <c r="J59" t="inlineStr"/>
+      <c r="K59" t="inlineStr"/>
+      <c r="L59" t="inlineStr"/>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>444491</v>
+        <v>444452</v>
       </c>
       <c r="R59" t="n">
-        <v>6787412</v>
+        <v>6787305</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6612,6 +6611,7 @@
       <c r="AE59" t="b">
         <v>0</v>
       </c>
+      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
       </c>
@@ -6630,7 +6630,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129795184</v>
+        <v>129795172</v>
       </c>
       <c r="B60" t="n">
         <v>8450</v>
@@ -6674,10 +6674,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>444452</v>
+        <v>444225</v>
       </c>
       <c r="R60" t="n">
-        <v>6787305</v>
+        <v>6787223</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6737,7 +6737,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129795172</v>
+        <v>129795199</v>
       </c>
       <c r="B61" t="n">
         <v>8450</v>
@@ -6781,10 +6781,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>444225</v>
+        <v>444431</v>
       </c>
       <c r="R61" t="n">
-        <v>6787223</v>
+        <v>6787350</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6844,40 +6844,41 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129795162</v>
+        <v>129795191</v>
       </c>
       <c r="B62" t="n">
-        <v>57733</v>
+        <v>8450</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
+      <c r="J62" t="inlineStr"/>
       <c r="K62" t="inlineStr"/>
       <c r="L62" t="inlineStr"/>
       <c r="M62" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N62" t="inlineStr"/>
@@ -6887,10 +6888,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>444428</v>
+        <v>444520</v>
       </c>
       <c r="R62" t="n">
-        <v>6787329</v>
+        <v>6787287</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6931,6 +6932,7 @@
       <c r="AE62" t="b">
         <v>0</v>
       </c>
+      <c r="AF62" t="inlineStr"/>
       <c r="AG62" t="b">
         <v>0</v>
       </c>
@@ -6952,7 +6954,7 @@
         <v>129795125</v>
       </c>
       <c r="B63" t="n">
-        <v>79700</v>
+        <v>79703</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7046,41 +7048,40 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129795191</v>
+        <v>129795162</v>
       </c>
       <c r="B64" t="n">
-        <v>8450</v>
+        <v>57734</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
-      <c r="J64" t="inlineStr"/>
       <c r="K64" t="inlineStr"/>
       <c r="L64" t="inlineStr"/>
       <c r="M64" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N64" t="inlineStr"/>
@@ -7090,10 +7091,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>444520</v>
+        <v>444428</v>
       </c>
       <c r="R64" t="n">
-        <v>6787287</v>
+        <v>6787329</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7134,7 +7135,6 @@
       <c r="AE64" t="b">
         <v>0</v>
       </c>
-      <c r="AF64" t="inlineStr"/>
       <c r="AG64" t="b">
         <v>0</v>
       </c>
@@ -7370,7 +7370,7 @@
         <v>129795257</v>
       </c>
       <c r="B67" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7467,7 +7467,7 @@
         <v>129795150</v>
       </c>
       <c r="B68" t="n">
-        <v>57733</v>
+        <v>57734</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7569,37 +7569,43 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129795135</v>
+        <v>129795182</v>
       </c>
       <c r="B69" t="n">
-        <v>91620</v>
+        <v>8450</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>5442</v>
+        <v>106545</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
       <c r="J69" t="inlineStr"/>
       <c r="K69" t="inlineStr"/>
+      <c r="L69" t="inlineStr"/>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
@@ -7607,10 +7613,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>444158</v>
+        <v>444417</v>
       </c>
       <c r="R69" t="n">
-        <v>6787148</v>
+        <v>6787266</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7670,10 +7676,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129795272</v>
+        <v>129795280</v>
       </c>
       <c r="B70" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7705,10 +7711,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>444553</v>
+        <v>444451</v>
       </c>
       <c r="R70" t="n">
-        <v>6787299</v>
+        <v>6787467</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7767,10 +7773,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129795243</v>
+        <v>129795135</v>
       </c>
       <c r="B71" t="n">
-        <v>79081</v>
+        <v>91623</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7778,34 +7784,37 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
+      <c r="J71" t="inlineStr"/>
+      <c r="K71" t="inlineStr"/>
+      <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>444159</v>
+        <v>444158</v>
       </c>
       <c r="R71" t="n">
-        <v>6787297</v>
+        <v>6787148</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7846,6 +7855,7 @@
       <c r="AE71" t="b">
         <v>0</v>
       </c>
+      <c r="AF71" t="inlineStr"/>
       <c r="AG71" t="b">
         <v>0</v>
       </c>
@@ -7864,10 +7874,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129795287</v>
+        <v>129795272</v>
       </c>
       <c r="B72" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7899,10 +7909,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>444430</v>
+        <v>444553</v>
       </c>
       <c r="R72" t="n">
-        <v>6787384</v>
+        <v>6787299</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7961,10 +7971,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129795280</v>
+        <v>129795287</v>
       </c>
       <c r="B73" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7996,10 +8006,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>444451</v>
+        <v>444430</v>
       </c>
       <c r="R73" t="n">
-        <v>6787467</v>
+        <v>6787384</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8061,7 +8071,7 @@
         <v>129795284</v>
       </c>
       <c r="B74" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8155,53 +8165,45 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129795208</v>
+        <v>129795243</v>
       </c>
       <c r="B75" t="n">
-        <v>58106</v>
+        <v>79084</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>103015</v>
+        <v>6425</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
-      <c r="K75" t="inlineStr"/>
-      <c r="L75" t="inlineStr"/>
-      <c r="M75" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>444434</v>
+        <v>444159</v>
       </c>
       <c r="R75" t="n">
-        <v>6787357</v>
+        <v>6787297</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8263,7 +8265,7 @@
         <v>129795166</v>
       </c>
       <c r="B76" t="n">
-        <v>57733</v>
+        <v>57734</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8365,10 +8367,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129795182</v>
+        <v>129795208</v>
       </c>
       <c r="B77" t="n">
-        <v>8450</v>
+        <v>58108</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8376,30 +8378,29 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>106545</v>
+        <v>103015</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
-      <c r="J77" t="inlineStr"/>
       <c r="K77" t="inlineStr"/>
       <c r="L77" t="inlineStr"/>
       <c r="M77" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N77" t="inlineStr"/>
@@ -8409,10 +8410,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>444417</v>
+        <v>444434</v>
       </c>
       <c r="R77" t="n">
-        <v>6787266</v>
+        <v>6787357</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8453,7 +8454,6 @@
       <c r="AE77" t="b">
         <v>0</v>
       </c>
-      <c r="AF77" t="inlineStr"/>
       <c r="AG77" t="b">
         <v>0</v>
       </c>
@@ -8472,10 +8472,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129795300</v>
+        <v>129795126</v>
       </c>
       <c r="B78" t="n">
-        <v>79081</v>
+        <v>79703</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8483,37 +8483,34 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
-      <c r="J78" t="inlineStr"/>
-      <c r="K78" t="inlineStr"/>
-      <c r="N78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>444264</v>
+        <v>444358</v>
       </c>
       <c r="R78" t="n">
-        <v>6787349</v>
+        <v>6787400</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8548,18 +8545,12 @@
           <t>2025-11-22</t>
         </is>
       </c>
-      <c r="AC78" t="inlineStr">
-        <is>
-          <t>Garnlav i de flesta träd inom en radie av 50 m.</t>
-        </is>
-      </c>
       <c r="AD78" t="b">
         <v>0</v>
       </c>
       <c r="AE78" t="b">
         <v>0</v>
       </c>
-      <c r="AF78" t="inlineStr"/>
       <c r="AG78" t="b">
         <v>0</v>
       </c>
@@ -8578,10 +8569,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129795307</v>
+        <v>129795127</v>
       </c>
       <c r="B79" t="n">
-        <v>79081</v>
+        <v>79703</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8589,21 +8580,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8613,10 +8604,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>444134</v>
+        <v>444432</v>
       </c>
       <c r="R79" t="n">
-        <v>6787304</v>
+        <v>6787388</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8675,10 +8666,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129795286</v>
+        <v>129795300</v>
       </c>
       <c r="B80" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8713,10 +8704,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>444440</v>
+        <v>444264</v>
       </c>
       <c r="R80" t="n">
-        <v>6787388</v>
+        <v>6787349</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8753,7 +8744,7 @@
       </c>
       <c r="AC80" t="inlineStr">
         <is>
-          <t>Gott om garnlav inom en radie av 50 m.</t>
+          <t>Garnlav i de flesta träd inom en radie av 50 m.</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -8781,10 +8772,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129795126</v>
+        <v>129795307</v>
       </c>
       <c r="B81" t="n">
-        <v>79700</v>
+        <v>79084</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8792,21 +8783,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8816,10 +8807,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>444358</v>
+        <v>444134</v>
       </c>
       <c r="R81" t="n">
-        <v>6787400</v>
+        <v>6787304</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8878,10 +8869,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129795241</v>
+        <v>129795286</v>
       </c>
       <c r="B82" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8907,16 +8898,19 @@
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
+      <c r="J82" t="inlineStr"/>
+      <c r="K82" t="inlineStr"/>
+      <c r="N82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>444117</v>
+        <v>444440</v>
       </c>
       <c r="R82" t="n">
-        <v>6787277</v>
+        <v>6787388</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8951,12 +8945,18 @@
           <t>2025-11-22</t>
         </is>
       </c>
+      <c r="AC82" t="inlineStr">
+        <is>
+          <t>Gott om garnlav inom en radie av 50 m.</t>
+        </is>
+      </c>
       <c r="AD82" t="b">
         <v>0</v>
       </c>
       <c r="AE82" t="b">
         <v>0</v>
       </c>
+      <c r="AF82" t="inlineStr"/>
       <c r="AG82" t="b">
         <v>0</v>
       </c>
@@ -8975,10 +8975,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129795127</v>
+        <v>129795241</v>
       </c>
       <c r="B83" t="n">
-        <v>79700</v>
+        <v>79084</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8986,21 +8986,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9010,10 +9010,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>444432</v>
+        <v>444117</v>
       </c>
       <c r="R83" t="n">
-        <v>6787388</v>
+        <v>6787277</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9286,10 +9286,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129795242</v>
+        <v>129795308</v>
       </c>
       <c r="B86" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9321,7 +9321,7 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>444125</v>
+        <v>444098</v>
       </c>
       <c r="R86" t="n">
         <v>6787297</v>
@@ -9383,10 +9383,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129795308</v>
+        <v>129795242</v>
       </c>
       <c r="B87" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9418,7 +9418,7 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>444098</v>
+        <v>444125</v>
       </c>
       <c r="R87" t="n">
         <v>6787297</v>
@@ -9694,41 +9694,40 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>129795167</v>
+        <v>129795152</v>
       </c>
       <c r="B90" t="n">
-        <v>8450</v>
+        <v>57734</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
-      <c r="J90" t="inlineStr"/>
       <c r="K90" t="inlineStr"/>
       <c r="L90" t="inlineStr"/>
       <c r="M90" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N90" t="inlineStr"/>
@@ -9738,10 +9737,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>444132</v>
+        <v>444434</v>
       </c>
       <c r="R90" t="n">
-        <v>6787237</v>
+        <v>6787304</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9782,7 +9781,6 @@
       <c r="AE90" t="b">
         <v>0</v>
       </c>
-      <c r="AF90" t="inlineStr"/>
       <c r="AG90" t="b">
         <v>0</v>
       </c>
@@ -9801,10 +9799,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>129795245</v>
+        <v>129795305</v>
       </c>
       <c r="B91" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9836,10 +9834,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>444113</v>
+        <v>444169</v>
       </c>
       <c r="R91" t="n">
-        <v>6787239</v>
+        <v>6787323</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9898,10 +9896,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>129795297</v>
+        <v>129795288</v>
       </c>
       <c r="B92" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9933,10 +9931,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>444297</v>
+        <v>444420</v>
       </c>
       <c r="R92" t="n">
-        <v>6787333</v>
+        <v>6787366</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9995,10 +9993,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>129795262</v>
+        <v>129795245</v>
       </c>
       <c r="B93" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10030,10 +10028,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>444219</v>
+        <v>444113</v>
       </c>
       <c r="R93" t="n">
-        <v>6787163</v>
+        <v>6787239</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10092,10 +10090,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>129795252</v>
+        <v>129795297</v>
       </c>
       <c r="B94" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10127,10 +10125,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>444249</v>
+        <v>444297</v>
       </c>
       <c r="R94" t="n">
-        <v>6787249</v>
+        <v>6787333</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10163,11 +10161,6 @@
       <c r="AA94" t="inlineStr">
         <is>
           <t>2025-11-22</t>
-        </is>
-      </c>
-      <c r="AC94" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 40m.</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10194,10 +10187,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>129795121</v>
+        <v>129795262</v>
       </c>
       <c r="B95" t="n">
-        <v>79700</v>
+        <v>79084</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10205,21 +10198,21 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10229,10 +10222,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>444254</v>
+        <v>444219</v>
       </c>
       <c r="R95" t="n">
-        <v>6787204</v>
+        <v>6787163</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10291,10 +10284,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>129795123</v>
+        <v>129795252</v>
       </c>
       <c r="B96" t="n">
-        <v>79700</v>
+        <v>79084</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10302,21 +10295,21 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10326,10 +10319,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>444530</v>
+        <v>444249</v>
       </c>
       <c r="R96" t="n">
-        <v>6787326</v>
+        <v>6787249</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10362,6 +10355,11 @@
       <c r="AA96" t="inlineStr">
         <is>
           <t>2025-11-22</t>
+        </is>
+      </c>
+      <c r="AC96" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 40m.</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10388,10 +10386,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>129795288</v>
+        <v>129795121</v>
       </c>
       <c r="B97" t="n">
-        <v>79081</v>
+        <v>79703</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10399,21 +10397,21 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -10423,10 +10421,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>444420</v>
+        <v>444254</v>
       </c>
       <c r="R97" t="n">
-        <v>6787366</v>
+        <v>6787204</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10485,10 +10483,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>129795305</v>
+        <v>129795124</v>
       </c>
       <c r="B98" t="n">
-        <v>79081</v>
+        <v>79703</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10496,21 +10494,21 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10520,10 +10518,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>444169</v>
+        <v>444393</v>
       </c>
       <c r="R98" t="n">
-        <v>6787323</v>
+        <v>6787395</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10582,10 +10580,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>129795124</v>
+        <v>129795123</v>
       </c>
       <c r="B99" t="n">
-        <v>79700</v>
+        <v>79703</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10617,10 +10615,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>444393</v>
+        <v>444530</v>
       </c>
       <c r="R99" t="n">
-        <v>6787395</v>
+        <v>6787326</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10679,40 +10677,41 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>129795152</v>
+        <v>129795167</v>
       </c>
       <c r="B100" t="n">
-        <v>57733</v>
+        <v>8450</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
+      <c r="J100" t="inlineStr"/>
       <c r="K100" t="inlineStr"/>
       <c r="L100" t="inlineStr"/>
       <c r="M100" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N100" t="inlineStr"/>
@@ -10722,10 +10721,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>444434</v>
+        <v>444132</v>
       </c>
       <c r="R100" t="n">
-        <v>6787304</v>
+        <v>6787237</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10766,6 +10765,7 @@
       <c r="AE100" t="b">
         <v>0</v>
       </c>
+      <c r="AF100" t="inlineStr"/>
       <c r="AG100" t="b">
         <v>0</v>
       </c>
@@ -10787,7 +10787,7 @@
         <v>129795264</v>
       </c>
       <c r="B101" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -10881,10 +10881,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>129795248</v>
+        <v>129795303</v>
       </c>
       <c r="B102" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -10916,10 +10916,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>444238</v>
+        <v>444200</v>
       </c>
       <c r="R102" t="n">
-        <v>6787281</v>
+        <v>6787331</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -10978,10 +10978,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>129795303</v>
+        <v>129795248</v>
       </c>
       <c r="B103" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11013,10 +11013,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>444200</v>
+        <v>444238</v>
       </c>
       <c r="R103" t="n">
-        <v>6787331</v>
+        <v>6787281</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11078,7 +11078,7 @@
         <v>129795306</v>
       </c>
       <c r="B104" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11710,7 +11710,7 @@
         <v>129795149</v>
       </c>
       <c r="B110" t="n">
-        <v>57733</v>
+        <v>57734</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -11815,7 +11815,7 @@
         <v>129795145</v>
       </c>
       <c r="B111" t="n">
-        <v>57733</v>
+        <v>57734</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -11920,7 +11920,7 @@
         <v>129795151</v>
       </c>
       <c r="B112" t="n">
-        <v>57733</v>
+        <v>57734</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -12022,45 +12022,54 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>129795259</v>
+        <v>129795203</v>
       </c>
       <c r="B113" t="n">
-        <v>79081</v>
+        <v>8450</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
+      <c r="J113" t="inlineStr"/>
+      <c r="K113" t="inlineStr"/>
+      <c r="L113" t="inlineStr"/>
+      <c r="M113" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N113" t="inlineStr"/>
       <c r="P113" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>444164</v>
+        <v>444401</v>
       </c>
       <c r="R113" t="n">
-        <v>6787121</v>
+        <v>6787298</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12101,6 +12110,7 @@
       <c r="AE113" t="b">
         <v>0</v>
       </c>
+      <c r="AF113" t="inlineStr"/>
       <c r="AG113" t="b">
         <v>0</v>
       </c>
@@ -12119,7 +12129,7 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>129795203</v>
+        <v>129795201</v>
       </c>
       <c r="B114" t="n">
         <v>8450</v>
@@ -12163,10 +12173,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>444401</v>
+        <v>444430</v>
       </c>
       <c r="R114" t="n">
-        <v>6787298</v>
+        <v>6787332</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12226,54 +12236,45 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>129795201</v>
+        <v>129795259</v>
       </c>
       <c r="B115" t="n">
-        <v>8450</v>
+        <v>79084</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
-      <c r="J115" t="inlineStr"/>
-      <c r="K115" t="inlineStr"/>
-      <c r="L115" t="inlineStr"/>
-      <c r="M115" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N115" t="inlineStr"/>
       <c r="P115" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>444430</v>
+        <v>444164</v>
       </c>
       <c r="R115" t="n">
-        <v>6787332</v>
+        <v>6787121</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12314,7 +12315,6 @@
       <c r="AE115" t="b">
         <v>0</v>
       </c>
-      <c r="AF115" t="inlineStr"/>
       <c r="AG115" t="b">
         <v>0</v>
       </c>
@@ -12333,10 +12333,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>129795164</v>
+        <v>129795289</v>
       </c>
       <c r="B116" t="n">
-        <v>57733</v>
+        <v>79084</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -12344,42 +12344,34 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
-      <c r="K116" t="inlineStr"/>
-      <c r="L116" t="inlineStr"/>
-      <c r="M116" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N116" t="inlineStr"/>
       <c r="P116" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>444397</v>
+        <v>444435</v>
       </c>
       <c r="R116" t="n">
-        <v>6787300</v>
+        <v>6787341</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12438,40 +12430,41 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>129795154</v>
+        <v>129795171</v>
       </c>
       <c r="B117" t="n">
-        <v>57733</v>
+        <v>8450</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
+      <c r="J117" t="inlineStr"/>
       <c r="K117" t="inlineStr"/>
       <c r="L117" t="inlineStr"/>
       <c r="M117" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N117" t="inlineStr"/>
@@ -12481,10 +12474,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>444457</v>
+        <v>444185</v>
       </c>
       <c r="R117" t="n">
-        <v>6787303</v>
+        <v>6787226</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12525,6 +12518,7 @@
       <c r="AE117" t="b">
         <v>0</v>
       </c>
+      <c r="AF117" t="inlineStr"/>
       <c r="AG117" t="b">
         <v>0</v>
       </c>
@@ -12543,10 +12537,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>129795157</v>
+        <v>129795164</v>
       </c>
       <c r="B118" t="n">
-        <v>57733</v>
+        <v>57734</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12586,10 +12580,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>444525</v>
+        <v>444397</v>
       </c>
       <c r="R118" t="n">
-        <v>6787344</v>
+        <v>6787300</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12648,10 +12642,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>129795289</v>
+        <v>129795154</v>
       </c>
       <c r="B119" t="n">
-        <v>79081</v>
+        <v>57734</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -12659,34 +12653,42 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
+      <c r="K119" t="inlineStr"/>
+      <c r="L119" t="inlineStr"/>
+      <c r="M119" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N119" t="inlineStr"/>
       <c r="P119" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>444435</v>
+        <v>444457</v>
       </c>
       <c r="R119" t="n">
-        <v>6787341</v>
+        <v>6787303</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -12745,32 +12747,32 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>129795132</v>
+        <v>129795157</v>
       </c>
       <c r="B120" t="n">
-        <v>56926</v>
+        <v>57734</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -12778,7 +12780,7 @@
       <c r="L120" t="inlineStr"/>
       <c r="M120" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N120" t="inlineStr"/>
@@ -12788,10 +12790,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>444315</v>
+        <v>444525</v>
       </c>
       <c r="R120" t="n">
-        <v>6787291</v>
+        <v>6787344</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -12850,10 +12852,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>129795171</v>
+        <v>129795132</v>
       </c>
       <c r="B121" t="n">
-        <v>8450</v>
+        <v>56927</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -12861,30 +12863,29 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>106545</v>
+        <v>100138</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
-      <c r="J121" t="inlineStr"/>
       <c r="K121" t="inlineStr"/>
       <c r="L121" t="inlineStr"/>
       <c r="M121" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="N121" t="inlineStr"/>
@@ -12894,10 +12895,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>444185</v>
+        <v>444315</v>
       </c>
       <c r="R121" t="n">
-        <v>6787226</v>
+        <v>6787291</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -12938,7 +12939,6 @@
       <c r="AE121" t="b">
         <v>0</v>
       </c>
-      <c r="AF121" t="inlineStr"/>
       <c r="AG121" t="b">
         <v>0</v>
       </c>
@@ -12957,45 +12957,54 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>129795294</v>
+        <v>129795188</v>
       </c>
       <c r="B122" t="n">
-        <v>79081</v>
+        <v>8450</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
+      <c r="J122" t="inlineStr"/>
+      <c r="K122" t="inlineStr"/>
+      <c r="L122" t="inlineStr"/>
+      <c r="M122" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N122" t="inlineStr"/>
       <c r="P122" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>444323</v>
+        <v>444498</v>
       </c>
       <c r="R122" t="n">
-        <v>6787297</v>
+        <v>6787280</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -13036,6 +13045,7 @@
       <c r="AE122" t="b">
         <v>0</v>
       </c>
+      <c r="AF122" t="inlineStr"/>
       <c r="AG122" t="b">
         <v>0</v>
       </c>
@@ -13054,40 +13064,41 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>129795144</v>
+        <v>129795179</v>
       </c>
       <c r="B123" t="n">
-        <v>57733</v>
+        <v>8450</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
+      <c r="J123" t="inlineStr"/>
       <c r="K123" t="inlineStr"/>
       <c r="L123" t="inlineStr"/>
       <c r="M123" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N123" t="inlineStr"/>
@@ -13097,10 +13108,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>444186</v>
+        <v>444378</v>
       </c>
       <c r="R123" t="n">
-        <v>6787223</v>
+        <v>6787236</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13141,6 +13152,7 @@
       <c r="AE123" t="b">
         <v>0</v>
       </c>
+      <c r="AF123" t="inlineStr"/>
       <c r="AG123" t="b">
         <v>0</v>
       </c>
@@ -13162,7 +13174,7 @@
         <v>129795301</v>
       </c>
       <c r="B124" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -13256,54 +13268,45 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>129795188</v>
+        <v>129795294</v>
       </c>
       <c r="B125" t="n">
-        <v>8450</v>
+        <v>79084</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
-      <c r="J125" t="inlineStr"/>
-      <c r="K125" t="inlineStr"/>
-      <c r="L125" t="inlineStr"/>
-      <c r="M125" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N125" t="inlineStr"/>
       <c r="P125" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>444498</v>
+        <v>444323</v>
       </c>
       <c r="R125" t="n">
-        <v>6787280</v>
+        <v>6787297</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13344,7 +13347,6 @@
       <c r="AE125" t="b">
         <v>0</v>
       </c>
-      <c r="AF125" t="inlineStr"/>
       <c r="AG125" t="b">
         <v>0</v>
       </c>
@@ -13363,41 +13365,40 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>129795179</v>
+        <v>129795144</v>
       </c>
       <c r="B126" t="n">
-        <v>8450</v>
+        <v>57734</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
-      <c r="J126" t="inlineStr"/>
       <c r="K126" t="inlineStr"/>
       <c r="L126" t="inlineStr"/>
       <c r="M126" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N126" t="inlineStr"/>
@@ -13407,10 +13408,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>444378</v>
+        <v>444186</v>
       </c>
       <c r="R126" t="n">
-        <v>6787236</v>
+        <v>6787223</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -13451,7 +13452,6 @@
       <c r="AE126" t="b">
         <v>0</v>
       </c>
-      <c r="AF126" t="inlineStr"/>
       <c r="AG126" t="b">
         <v>0</v>
       </c>
@@ -13470,54 +13470,45 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>129795175</v>
+        <v>129795258</v>
       </c>
       <c r="B127" t="n">
-        <v>8450</v>
+        <v>79084</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
-      <c r="J127" t="inlineStr"/>
-      <c r="K127" t="inlineStr"/>
-      <c r="L127" t="inlineStr"/>
-      <c r="M127" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N127" t="inlineStr"/>
       <c r="P127" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>444182</v>
+        <v>444174</v>
       </c>
       <c r="R127" t="n">
-        <v>6787101</v>
+        <v>6787136</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -13558,7 +13549,6 @@
       <c r="AE127" t="b">
         <v>0</v>
       </c>
-      <c r="AF127" t="inlineStr"/>
       <c r="AG127" t="b">
         <v>0</v>
       </c>
@@ -13577,54 +13567,45 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>129795168</v>
+        <v>129795275</v>
       </c>
       <c r="B128" t="n">
-        <v>8450</v>
+        <v>79084</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
-      <c r="J128" t="inlineStr"/>
-      <c r="K128" t="inlineStr"/>
-      <c r="L128" t="inlineStr"/>
-      <c r="M128" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N128" t="inlineStr"/>
       <c r="P128" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>444272</v>
+        <v>444495</v>
       </c>
       <c r="R128" t="n">
-        <v>6787286</v>
+        <v>6787340</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -13665,7 +13646,6 @@
       <c r="AE128" t="b">
         <v>0</v>
       </c>
-      <c r="AF128" t="inlineStr"/>
       <c r="AG128" t="b">
         <v>0</v>
       </c>
@@ -13684,10 +13664,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>129795275</v>
+        <v>129795267</v>
       </c>
       <c r="B129" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -13719,10 +13699,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>444495</v>
+        <v>444353</v>
       </c>
       <c r="R129" t="n">
-        <v>6787340</v>
+        <v>6787215</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -13755,6 +13735,11 @@
       <c r="AA129" t="inlineStr">
         <is>
           <t>2025-11-22</t>
+        </is>
+      </c>
+      <c r="AC129" t="inlineStr">
+        <is>
+          <t>Gott om garnlav inom en radie av 40m.</t>
         </is>
       </c>
       <c r="AD129" t="b">
@@ -13781,10 +13766,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>129795267</v>
+        <v>129795263</v>
       </c>
       <c r="B130" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -13816,10 +13801,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>444353</v>
+        <v>444241</v>
       </c>
       <c r="R130" t="n">
-        <v>6787215</v>
+        <v>6787149</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -13852,11 +13837,6 @@
       <c r="AA130" t="inlineStr">
         <is>
           <t>2025-11-22</t>
-        </is>
-      </c>
-      <c r="AC130" t="inlineStr">
-        <is>
-          <t>Gott om garnlav inom en radie av 40m.</t>
         </is>
       </c>
       <c r="AD130" t="b">
@@ -13883,10 +13863,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>129795263</v>
+        <v>129795137</v>
       </c>
       <c r="B131" t="n">
-        <v>79081</v>
+        <v>91623</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -13894,34 +13874,37 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
+      <c r="J131" t="inlineStr"/>
+      <c r="K131" t="inlineStr"/>
+      <c r="N131" t="inlineStr"/>
       <c r="P131" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>444241</v>
+        <v>444203</v>
       </c>
       <c r="R131" t="n">
-        <v>6787149</v>
+        <v>6787221</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -13962,6 +13945,7 @@
       <c r="AE131" t="b">
         <v>0</v>
       </c>
+      <c r="AF131" t="inlineStr"/>
       <c r="AG131" t="b">
         <v>0</v>
       </c>
@@ -13980,10 +13964,10 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>129795137</v>
+        <v>129795159</v>
       </c>
       <c r="B132" t="n">
-        <v>91620</v>
+        <v>57734</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -13991,26 +13975,31 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>5442</v>
+        <v>100049</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
-      <c r="J132" t="inlineStr"/>
       <c r="K132" t="inlineStr"/>
+      <c r="L132" t="inlineStr"/>
+      <c r="M132" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N132" t="inlineStr"/>
       <c r="P132" t="inlineStr">
         <is>
@@ -14018,10 +14007,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>444203</v>
+        <v>444436</v>
       </c>
       <c r="R132" t="n">
-        <v>6787221</v>
+        <v>6787463</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -14062,7 +14051,6 @@
       <c r="AE132" t="b">
         <v>0</v>
       </c>
-      <c r="AF132" t="inlineStr"/>
       <c r="AG132" t="b">
         <v>0</v>
       </c>
@@ -14081,45 +14069,54 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>129795258</v>
+        <v>129795175</v>
       </c>
       <c r="B133" t="n">
-        <v>79081</v>
+        <v>8450</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
+      <c r="J133" t="inlineStr"/>
+      <c r="K133" t="inlineStr"/>
+      <c r="L133" t="inlineStr"/>
+      <c r="M133" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N133" t="inlineStr"/>
       <c r="P133" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>444174</v>
+        <v>444182</v>
       </c>
       <c r="R133" t="n">
-        <v>6787136</v>
+        <v>6787101</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -14160,6 +14157,7 @@
       <c r="AE133" t="b">
         <v>0</v>
       </c>
+      <c r="AF133" t="inlineStr"/>
       <c r="AG133" t="b">
         <v>0</v>
       </c>
@@ -14178,40 +14176,41 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>129795159</v>
+        <v>129795168</v>
       </c>
       <c r="B134" t="n">
-        <v>57733</v>
+        <v>8450</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
+      <c r="J134" t="inlineStr"/>
       <c r="K134" t="inlineStr"/>
       <c r="L134" t="inlineStr"/>
       <c r="M134" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N134" t="inlineStr"/>
@@ -14221,10 +14220,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>444436</v>
+        <v>444272</v>
       </c>
       <c r="R134" t="n">
-        <v>6787463</v>
+        <v>6787286</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -14265,6 +14264,7 @@
       <c r="AE134" t="b">
         <v>0</v>
       </c>
+      <c r="AF134" t="inlineStr"/>
       <c r="AG134" t="b">
         <v>0</v>
       </c>
@@ -14286,7 +14286,7 @@
         <v>129795304</v>
       </c>
       <c r="B135" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -14380,37 +14380,43 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>129795251</v>
+        <v>129795204</v>
       </c>
       <c r="B136" t="n">
-        <v>79081</v>
+        <v>8450</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
       <c r="J136" t="inlineStr"/>
       <c r="K136" t="inlineStr"/>
+      <c r="L136" t="inlineStr"/>
+      <c r="M136" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N136" t="inlineStr"/>
       <c r="P136" t="inlineStr">
         <is>
@@ -14418,10 +14424,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>444309</v>
+        <v>444380</v>
       </c>
       <c r="R136" t="n">
-        <v>6787272</v>
+        <v>6787306</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -14481,10 +14487,10 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>129795266</v>
+        <v>129795274</v>
       </c>
       <c r="B137" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -14516,10 +14522,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>444314</v>
+        <v>444538</v>
       </c>
       <c r="R137" t="n">
-        <v>6787212</v>
+        <v>6787325</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -14552,11 +14558,6 @@
       <c r="AA137" t="inlineStr">
         <is>
           <t>2025-11-22</t>
-        </is>
-      </c>
-      <c r="AC137" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 40m</t>
         </is>
       </c>
       <c r="AD137" t="b">
@@ -14583,10 +14584,10 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>129795247</v>
+        <v>129795254</v>
       </c>
       <c r="B138" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -14612,16 +14613,19 @@
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
+      <c r="J138" t="inlineStr"/>
+      <c r="K138" t="inlineStr"/>
+      <c r="N138" t="inlineStr"/>
       <c r="P138" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>444225</v>
+        <v>444199</v>
       </c>
       <c r="R138" t="n">
-        <v>6787275</v>
+        <v>6787221</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -14662,6 +14666,7 @@
       <c r="AE138" t="b">
         <v>0</v>
       </c>
+      <c r="AF138" t="inlineStr"/>
       <c r="AG138" t="b">
         <v>0</v>
       </c>
@@ -14680,10 +14685,10 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>129795139</v>
+        <v>129795302</v>
       </c>
       <c r="B139" t="n">
-        <v>91620</v>
+        <v>79084</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -14691,37 +14696,34 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
-      <c r="J139" t="inlineStr"/>
-      <c r="K139" t="inlineStr"/>
-      <c r="N139" t="inlineStr"/>
       <c r="P139" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>444342</v>
+        <v>444222</v>
       </c>
       <c r="R139" t="n">
-        <v>6787240</v>
+        <v>6787345</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -14762,7 +14764,6 @@
       <c r="AE139" t="b">
         <v>0</v>
       </c>
-      <c r="AF139" t="inlineStr"/>
       <c r="AG139" t="b">
         <v>0</v>
       </c>
@@ -14781,10 +14782,10 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>129795274</v>
+        <v>129795251</v>
       </c>
       <c r="B140" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -14810,16 +14811,19 @@
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
+      <c r="J140" t="inlineStr"/>
+      <c r="K140" t="inlineStr"/>
+      <c r="N140" t="inlineStr"/>
       <c r="P140" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>444538</v>
+        <v>444309</v>
       </c>
       <c r="R140" t="n">
-        <v>6787325</v>
+        <v>6787272</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -14860,6 +14864,7 @@
       <c r="AE140" t="b">
         <v>0</v>
       </c>
+      <c r="AF140" t="inlineStr"/>
       <c r="AG140" t="b">
         <v>0</v>
       </c>
@@ -14878,10 +14883,10 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>129795254</v>
+        <v>129795266</v>
       </c>
       <c r="B141" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -14907,19 +14912,16 @@
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
-      <c r="J141" t="inlineStr"/>
-      <c r="K141" t="inlineStr"/>
-      <c r="N141" t="inlineStr"/>
       <c r="P141" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>444199</v>
+        <v>444314</v>
       </c>
       <c r="R141" t="n">
-        <v>6787221</v>
+        <v>6787212</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -14954,13 +14956,17 @@
           <t>2025-11-22</t>
         </is>
       </c>
+      <c r="AC141" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 40m</t>
+        </is>
+      </c>
       <c r="AD141" t="b">
         <v>0</v>
       </c>
       <c r="AE141" t="b">
         <v>0</v>
       </c>
-      <c r="AF141" t="inlineStr"/>
       <c r="AG141" t="b">
         <v>0</v>
       </c>
@@ -14979,10 +14985,10 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>129795302</v>
+        <v>129795247</v>
       </c>
       <c r="B142" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -15014,10 +15020,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>444222</v>
+        <v>444225</v>
       </c>
       <c r="R142" t="n">
-        <v>6787345</v>
+        <v>6787275</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -15076,43 +15082,37 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>129795204</v>
+        <v>129795139</v>
       </c>
       <c r="B143" t="n">
-        <v>8450</v>
+        <v>91623</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E143" t="n">
-        <v>106545</v>
+        <v>5442</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
       <c r="J143" t="inlineStr"/>
       <c r="K143" t="inlineStr"/>
-      <c r="L143" t="inlineStr"/>
-      <c r="M143" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N143" t="inlineStr"/>
       <c r="P143" t="inlineStr">
         <is>
@@ -15120,10 +15120,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>444380</v>
+        <v>444342</v>
       </c>
       <c r="R143" t="n">
-        <v>6787306</v>
+        <v>6787240</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>

--- a/artfynd/A 51041-2025 artfynd.xlsx
+++ b/artfynd/A 51041-2025 artfynd.xlsx
@@ -874,7 +874,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129795298</v>
+        <v>129795285</v>
       </c>
       <c r="B4" t="n">
         <v>79084</v>
@@ -909,10 +909,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>444305</v>
+        <v>444405</v>
       </c>
       <c r="R4" t="n">
-        <v>6787353</v>
+        <v>6787405</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -971,7 +971,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129795285</v>
+        <v>129795261</v>
       </c>
       <c r="B5" t="n">
         <v>79084</v>
@@ -1006,10 +1006,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>444405</v>
+        <v>444193</v>
       </c>
       <c r="R5" t="n">
-        <v>6787405</v>
+        <v>6787130</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1068,7 +1068,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129795244</v>
+        <v>129795283</v>
       </c>
       <c r="B6" t="n">
         <v>79084</v>
@@ -1097,16 +1097,19 @@
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>444105</v>
+        <v>444337</v>
       </c>
       <c r="R6" t="n">
-        <v>6787246</v>
+        <v>6787374</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1147,6 +1150,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1165,7 +1169,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129795261</v>
+        <v>129795244</v>
       </c>
       <c r="B7" t="n">
         <v>79084</v>
@@ -1200,10 +1204,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>444193</v>
+        <v>444105</v>
       </c>
       <c r="R7" t="n">
-        <v>6787130</v>
+        <v>6787246</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1262,7 +1266,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129795283</v>
+        <v>129795298</v>
       </c>
       <c r="B8" t="n">
         <v>79084</v>
@@ -1291,19 +1295,16 @@
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>444337</v>
+        <v>444305</v>
       </c>
       <c r="R8" t="n">
-        <v>6787374</v>
+        <v>6787353</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1344,7 +1345,6 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1363,7 +1363,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129795169</v>
+        <v>129795197</v>
       </c>
       <c r="B9" t="n">
         <v>8450</v>
@@ -1407,10 +1407,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>444272</v>
+        <v>444406</v>
       </c>
       <c r="R9" t="n">
-        <v>6787239</v>
+        <v>6787392</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1470,7 +1470,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129795190</v>
+        <v>129795169</v>
       </c>
       <c r="B10" t="n">
         <v>8450</v>
@@ -1514,10 +1514,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>444510</v>
+        <v>444272</v>
       </c>
       <c r="R10" t="n">
-        <v>6787276</v>
+        <v>6787239</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1577,7 +1577,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129795197</v>
+        <v>129795190</v>
       </c>
       <c r="B11" t="n">
         <v>8450</v>
@@ -1621,10 +1621,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>444406</v>
+        <v>444510</v>
       </c>
       <c r="R11" t="n">
-        <v>6787392</v>
+        <v>6787276</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1684,10 +1684,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129795281</v>
+        <v>129795163</v>
       </c>
       <c r="B12" t="n">
-        <v>79084</v>
+        <v>57734</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1695,26 +1695,31 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1722,10 +1727,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>444408</v>
+        <v>444415</v>
       </c>
       <c r="R12" t="n">
-        <v>6787452</v>
+        <v>6787316</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1766,7 +1771,6 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1785,10 +1789,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129795271</v>
+        <v>129795153</v>
       </c>
       <c r="B13" t="n">
-        <v>79084</v>
+        <v>57734</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1796,26 +1800,31 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1823,10 +1832,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>444466</v>
+        <v>444452</v>
       </c>
       <c r="R13" t="n">
-        <v>6787306</v>
+        <v>6787294</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1861,18 +1870,12 @@
           <t>2025-11-22</t>
         </is>
       </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 50m.</t>
-        </is>
-      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -1891,7 +1894,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129795276</v>
+        <v>129795281</v>
       </c>
       <c r="B14" t="n">
         <v>79084</v>
@@ -1929,10 +1932,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>444499</v>
+        <v>444408</v>
       </c>
       <c r="R14" t="n">
-        <v>6787367</v>
+        <v>6787452</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1965,11 +1968,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-11-22</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 50m.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -1997,45 +1995,54 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129795299</v>
+        <v>129795174</v>
       </c>
       <c r="B15" t="n">
-        <v>79084</v>
+        <v>8450</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>444265</v>
+        <v>444166</v>
       </c>
       <c r="R15" t="n">
-        <v>6787372</v>
+        <v>6787161</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2076,6 +2083,7 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2094,40 +2102,41 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129795155</v>
+        <v>129795205</v>
       </c>
       <c r="B16" t="n">
-        <v>57734</v>
+        <v>8450</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N16" t="inlineStr"/>
@@ -2137,10 +2146,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>444498</v>
+        <v>444343</v>
       </c>
       <c r="R16" t="n">
-        <v>6787306</v>
+        <v>6787310</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2181,6 +2190,7 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2199,10 +2209,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129795163</v>
+        <v>129795271</v>
       </c>
       <c r="B17" t="n">
-        <v>57734</v>
+        <v>79084</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2210,31 +2220,26 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2242,10 +2247,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>444415</v>
+        <v>444466</v>
       </c>
       <c r="R17" t="n">
-        <v>6787316</v>
+        <v>6787306</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2280,12 +2285,18 @@
           <t>2025-11-22</t>
         </is>
       </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 50m.</t>
+        </is>
+      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2304,10 +2315,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129795153</v>
+        <v>129795276</v>
       </c>
       <c r="B18" t="n">
-        <v>57734</v>
+        <v>79084</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2315,31 +2326,26 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2347,10 +2353,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>444452</v>
+        <v>444499</v>
       </c>
       <c r="R18" t="n">
-        <v>6787294</v>
+        <v>6787367</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2385,12 +2391,18 @@
           <t>2025-11-22</t>
         </is>
       </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 50m.</t>
+        </is>
+      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2409,54 +2421,45 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129795174</v>
+        <v>129795299</v>
       </c>
       <c r="B19" t="n">
-        <v>8450</v>
+        <v>79084</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>444166</v>
+        <v>444265</v>
       </c>
       <c r="R19" t="n">
-        <v>6787161</v>
+        <v>6787372</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2497,7 +2500,6 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2516,41 +2518,40 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129795205</v>
+        <v>129795155</v>
       </c>
       <c r="B20" t="n">
-        <v>8450</v>
+        <v>57734</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N20" t="inlineStr"/>
@@ -2560,10 +2561,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>444343</v>
+        <v>444498</v>
       </c>
       <c r="R20" t="n">
-        <v>6787310</v>
+        <v>6787306</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2604,7 +2605,6 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2623,7 +2623,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129795265</v>
+        <v>129795310</v>
       </c>
       <c r="B21" t="n">
         <v>79084</v>
@@ -2652,16 +2652,19 @@
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>444278</v>
+        <v>444488</v>
       </c>
       <c r="R21" t="n">
-        <v>6787163</v>
+        <v>6787445</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2696,12 +2699,18 @@
           <t>2025-11-22</t>
         </is>
       </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Gott om garnlav inom en radie av 40m</t>
+        </is>
+      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -2720,7 +2729,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129795273</v>
+        <v>129795265</v>
       </c>
       <c r="B22" t="n">
         <v>79084</v>
@@ -2755,10 +2764,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>444548</v>
+        <v>444278</v>
       </c>
       <c r="R22" t="n">
-        <v>6787330</v>
+        <v>6787163</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2817,7 +2826,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129795310</v>
+        <v>129795278</v>
       </c>
       <c r="B23" t="n">
         <v>79084</v>
@@ -2846,19 +2855,16 @@
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>444488</v>
+        <v>444465</v>
       </c>
       <c r="R23" t="n">
-        <v>6787445</v>
+        <v>6787451</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2893,18 +2899,12 @@
           <t>2025-11-22</t>
         </is>
       </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Gott om garnlav inom en radie av 40m</t>
-        </is>
-      </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -2923,7 +2923,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129795278</v>
+        <v>129795273</v>
       </c>
       <c r="B24" t="n">
         <v>79084</v>
@@ -2958,10 +2958,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>444465</v>
+        <v>444548</v>
       </c>
       <c r="R24" t="n">
-        <v>6787451</v>
+        <v>6787330</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3020,7 +3020,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129795198</v>
+        <v>129795200</v>
       </c>
       <c r="B25" t="n">
         <v>8450</v>
@@ -3064,10 +3064,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>444434</v>
+        <v>444429</v>
       </c>
       <c r="R25" t="n">
-        <v>6787384</v>
+        <v>6787341</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3127,7 +3127,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129795207</v>
+        <v>129795198</v>
       </c>
       <c r="B26" t="n">
         <v>8450</v>
@@ -3171,10 +3171,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>444221</v>
+        <v>444434</v>
       </c>
       <c r="R26" t="n">
-        <v>6787340</v>
+        <v>6787384</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3234,7 +3234,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129795200</v>
+        <v>129795207</v>
       </c>
       <c r="B27" t="n">
         <v>8450</v>
@@ -3278,10 +3278,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>444429</v>
+        <v>444221</v>
       </c>
       <c r="R27" t="n">
-        <v>6787341</v>
+        <v>6787340</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3448,10 +3448,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129795268</v>
+        <v>129795142</v>
       </c>
       <c r="B29" t="n">
-        <v>79084</v>
+        <v>57734</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3459,34 +3459,42 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>444383</v>
+        <v>444276</v>
       </c>
       <c r="R29" t="n">
-        <v>6787218</v>
+        <v>6787287</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3545,7 +3553,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129795256</v>
+        <v>129795268</v>
       </c>
       <c r="B30" t="n">
         <v>79084</v>
@@ -3580,10 +3588,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>444226</v>
+        <v>444383</v>
       </c>
       <c r="R30" t="n">
-        <v>6787196</v>
+        <v>6787218</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3642,10 +3650,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129795142</v>
+        <v>129795256</v>
       </c>
       <c r="B31" t="n">
-        <v>57734</v>
+        <v>79084</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3653,42 +3661,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>444276</v>
+        <v>444226</v>
       </c>
       <c r="R31" t="n">
-        <v>6787287</v>
+        <v>6787196</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3747,7 +3747,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129795187</v>
+        <v>129795176</v>
       </c>
       <c r="B32" t="n">
         <v>8450</v>
@@ -3781,7 +3781,7 @@
       <c r="L32" t="inlineStr"/>
       <c r="M32" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="N32" t="inlineStr"/>
@@ -3791,10 +3791,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>444487</v>
+        <v>444215</v>
       </c>
       <c r="R32" t="n">
-        <v>6787321</v>
+        <v>6787151</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3961,7 +3961,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129795176</v>
+        <v>129795187</v>
       </c>
       <c r="B34" t="n">
         <v>8450</v>
@@ -3995,7 +3995,7 @@
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N34" t="inlineStr"/>
@@ -4005,10 +4005,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>444215</v>
+        <v>444487</v>
       </c>
       <c r="R34" t="n">
-        <v>6787151</v>
+        <v>6787321</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4173,54 +4173,45 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129795193</v>
+        <v>129795269</v>
       </c>
       <c r="B36" t="n">
-        <v>8450</v>
+        <v>79084</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>444508</v>
+        <v>444429</v>
       </c>
       <c r="R36" t="n">
-        <v>6787352</v>
+        <v>6787240</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4261,7 +4252,6 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
-      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
@@ -4280,54 +4270,45 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129795202</v>
+        <v>129795249</v>
       </c>
       <c r="B37" t="n">
-        <v>8450</v>
+        <v>79084</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
-      <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>444413</v>
+        <v>444267</v>
       </c>
       <c r="R37" t="n">
-        <v>6787314</v>
+        <v>6787295</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4368,7 +4349,6 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
-      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -4387,7 +4367,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129795270</v>
+        <v>129795296</v>
       </c>
       <c r="B38" t="n">
         <v>79084</v>
@@ -4416,16 +4396,19 @@
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>444416</v>
+        <v>444299</v>
       </c>
       <c r="R38" t="n">
-        <v>6787260</v>
+        <v>6787304</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4460,12 +4443,18 @@
           <t>2025-11-22</t>
         </is>
       </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 50 m.</t>
+        </is>
+      </c>
       <c r="AD38" t="b">
         <v>0</v>
       </c>
       <c r="AE38" t="b">
         <v>0</v>
       </c>
+      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -4484,10 +4473,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129795296</v>
+        <v>129795133</v>
       </c>
       <c r="B39" t="n">
-        <v>79084</v>
+        <v>57895</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4495,26 +4484,31 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
@@ -4522,10 +4516,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>444299</v>
+        <v>444226</v>
       </c>
       <c r="R39" t="n">
-        <v>6787304</v>
+        <v>6787236</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4560,18 +4554,12 @@
           <t>2025-11-22</t>
         </is>
       </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 50 m.</t>
-        </is>
-      </c>
       <c r="AD39" t="b">
         <v>0</v>
       </c>
       <c r="AE39" t="b">
         <v>0</v>
       </c>
-      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -4590,45 +4578,54 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129795269</v>
+        <v>129795202</v>
       </c>
       <c r="B40" t="n">
-        <v>79084</v>
+        <v>8450</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>444429</v>
+        <v>444413</v>
       </c>
       <c r="R40" t="n">
-        <v>6787240</v>
+        <v>6787314</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4669,6 +4666,7 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
+      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
@@ -4687,45 +4685,54 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129795249</v>
+        <v>129795193</v>
       </c>
       <c r="B41" t="n">
-        <v>79084</v>
+        <v>8450</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>444267</v>
+        <v>444508</v>
       </c>
       <c r="R41" t="n">
-        <v>6787295</v>
+        <v>6787352</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4766,6 +4773,7 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
+      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
@@ -4784,10 +4792,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129795133</v>
+        <v>129795270</v>
       </c>
       <c r="B42" t="n">
-        <v>57895</v>
+        <v>79084</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4795,42 +4803,34 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="K42" t="inlineStr"/>
-      <c r="L42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>444226</v>
+        <v>444416</v>
       </c>
       <c r="R42" t="n">
-        <v>6787236</v>
+        <v>6787260</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5410,10 +5410,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129795138</v>
+        <v>129795246</v>
       </c>
       <c r="B48" t="n">
-        <v>91623</v>
+        <v>79084</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5421,37 +5421,34 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="J48" t="inlineStr"/>
-      <c r="K48" t="inlineStr"/>
-      <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>444250</v>
+        <v>444145</v>
       </c>
       <c r="R48" t="n">
-        <v>6787196</v>
+        <v>6787239</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5486,13 +5483,17 @@
           <t>2025-11-22</t>
         </is>
       </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 40m.</t>
+        </is>
+      </c>
       <c r="AD48" t="b">
         <v>0</v>
       </c>
       <c r="AE48" t="b">
         <v>0</v>
       </c>
-      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
@@ -5511,7 +5512,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129795309</v>
+        <v>129795250</v>
       </c>
       <c r="B49" t="n">
         <v>79084</v>
@@ -5546,10 +5547,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>444095</v>
+        <v>444295</v>
       </c>
       <c r="R49" t="n">
-        <v>6787293</v>
+        <v>6787287</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5582,11 +5583,6 @@
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-11-22</t>
-        </is>
-      </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>8.32</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5613,10 +5609,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129795260</v>
+        <v>129795138</v>
       </c>
       <c r="B50" t="n">
-        <v>79084</v>
+        <v>91623</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5624,34 +5620,37 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
+      <c r="J50" t="inlineStr"/>
+      <c r="K50" t="inlineStr"/>
+      <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>444197</v>
+        <v>444250</v>
       </c>
       <c r="R50" t="n">
-        <v>6787111</v>
+        <v>6787196</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5692,6 +5691,7 @@
       <c r="AE50" t="b">
         <v>0</v>
       </c>
+      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>
@@ -5710,7 +5710,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129795250</v>
+        <v>129795309</v>
       </c>
       <c r="B51" t="n">
         <v>79084</v>
@@ -5745,10 +5745,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>444295</v>
+        <v>444095</v>
       </c>
       <c r="R51" t="n">
-        <v>6787287</v>
+        <v>6787293</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5781,6 +5781,11 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-11-22</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>8.32</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5807,7 +5812,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129795246</v>
+        <v>129795260</v>
       </c>
       <c r="B52" t="n">
         <v>79084</v>
@@ -5842,10 +5847,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>444145</v>
+        <v>444197</v>
       </c>
       <c r="R52" t="n">
-        <v>6787239</v>
+        <v>6787111</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5878,11 +5883,6 @@
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-11-22</t>
-        </is>
-      </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 40m.</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6014,10 +6014,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129795147</v>
+        <v>129795134</v>
       </c>
       <c r="B54" t="n">
-        <v>57734</v>
+        <v>57895</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6025,21 +6025,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6047,7 +6047,7 @@
       <c r="L54" t="inlineStr"/>
       <c r="M54" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N54" t="inlineStr"/>
@@ -6057,10 +6057,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>444220</v>
+        <v>444289</v>
       </c>
       <c r="R54" t="n">
-        <v>6787221</v>
+        <v>6787357</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6119,10 +6119,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129795131</v>
+        <v>129795172</v>
       </c>
       <c r="B55" t="n">
-        <v>56927</v>
+        <v>8450</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6130,29 +6130,30 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>100138</v>
+        <v>106545</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
+      <c r="J55" t="inlineStr"/>
       <c r="K55" t="inlineStr"/>
       <c r="L55" t="inlineStr"/>
       <c r="M55" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N55" t="inlineStr"/>
@@ -6162,10 +6163,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>444250</v>
+        <v>444225</v>
       </c>
       <c r="R55" t="n">
-        <v>6787212</v>
+        <v>6787223</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6206,6 +6207,7 @@
       <c r="AE55" t="b">
         <v>0</v>
       </c>
+      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
@@ -6224,40 +6226,41 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129795134</v>
+        <v>129795199</v>
       </c>
       <c r="B56" t="n">
-        <v>57895</v>
+        <v>8450</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>103021</v>
+        <v>106545</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
+      <c r="J56" t="inlineStr"/>
       <c r="K56" t="inlineStr"/>
       <c r="L56" t="inlineStr"/>
       <c r="M56" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N56" t="inlineStr"/>
@@ -6267,10 +6270,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>444289</v>
+        <v>444431</v>
       </c>
       <c r="R56" t="n">
-        <v>6787357</v>
+        <v>6787350</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6311,6 +6314,7 @@
       <c r="AE56" t="b">
         <v>0</v>
       </c>
+      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
       </c>
@@ -6329,45 +6333,53 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129795277</v>
+        <v>129795131</v>
       </c>
       <c r="B57" t="n">
-        <v>79084</v>
+        <v>56927</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
+      <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>444491</v>
+        <v>444250</v>
       </c>
       <c r="R57" t="n">
-        <v>6787412</v>
+        <v>6787212</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6426,7 +6438,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129795279</v>
+        <v>129795277</v>
       </c>
       <c r="B58" t="n">
         <v>79084</v>
@@ -6461,10 +6473,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>444463</v>
+        <v>444491</v>
       </c>
       <c r="R58" t="n">
-        <v>6787459</v>
+        <v>6787412</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6523,54 +6535,45 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129795184</v>
+        <v>129795279</v>
       </c>
       <c r="B59" t="n">
-        <v>8450</v>
+        <v>79084</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
-      <c r="J59" t="inlineStr"/>
-      <c r="K59" t="inlineStr"/>
-      <c r="L59" t="inlineStr"/>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>444452</v>
+        <v>444463</v>
       </c>
       <c r="R59" t="n">
-        <v>6787305</v>
+        <v>6787459</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6611,7 +6614,6 @@
       <c r="AE59" t="b">
         <v>0</v>
       </c>
-      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
       </c>
@@ -6630,41 +6632,40 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129795172</v>
+        <v>129795147</v>
       </c>
       <c r="B60" t="n">
-        <v>8450</v>
+        <v>57734</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
-      <c r="J60" t="inlineStr"/>
       <c r="K60" t="inlineStr"/>
       <c r="L60" t="inlineStr"/>
       <c r="M60" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N60" t="inlineStr"/>
@@ -6674,10 +6675,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>444225</v>
+        <v>444220</v>
       </c>
       <c r="R60" t="n">
-        <v>6787223</v>
+        <v>6787221</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6718,7 +6719,6 @@
       <c r="AE60" t="b">
         <v>0</v>
       </c>
-      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
       </c>
@@ -6737,7 +6737,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129795199</v>
+        <v>129795184</v>
       </c>
       <c r="B61" t="n">
         <v>8450</v>
@@ -6781,10 +6781,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>444431</v>
+        <v>444452</v>
       </c>
       <c r="R61" t="n">
-        <v>6787350</v>
+        <v>6787305</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6844,7 +6844,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129795191</v>
+        <v>129795195</v>
       </c>
       <c r="B62" t="n">
         <v>8450</v>
@@ -6888,10 +6888,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>444520</v>
+        <v>444487</v>
       </c>
       <c r="R62" t="n">
-        <v>6787287</v>
+        <v>6787441</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6951,45 +6951,54 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129795125</v>
+        <v>129795191</v>
       </c>
       <c r="B63" t="n">
-        <v>79703</v>
+        <v>8450</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
+      <c r="J63" t="inlineStr"/>
+      <c r="K63" t="inlineStr"/>
+      <c r="L63" t="inlineStr"/>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>444329</v>
+        <v>444520</v>
       </c>
       <c r="R63" t="n">
-        <v>6787371</v>
+        <v>6787287</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7030,6 +7039,7 @@
       <c r="AE63" t="b">
         <v>0</v>
       </c>
+      <c r="AF63" t="inlineStr"/>
       <c r="AG63" t="b">
         <v>0</v>
       </c>
@@ -7048,40 +7058,41 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129795162</v>
+        <v>129795177</v>
       </c>
       <c r="B64" t="n">
-        <v>57734</v>
+        <v>8450</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
+      <c r="J64" t="inlineStr"/>
       <c r="K64" t="inlineStr"/>
       <c r="L64" t="inlineStr"/>
       <c r="M64" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="N64" t="inlineStr"/>
@@ -7091,10 +7102,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>444428</v>
+        <v>444342</v>
       </c>
       <c r="R64" t="n">
-        <v>6787329</v>
+        <v>6787223</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7135,6 +7146,7 @@
       <c r="AE64" t="b">
         <v>0</v>
       </c>
+      <c r="AF64" t="inlineStr"/>
       <c r="AG64" t="b">
         <v>0</v>
       </c>
@@ -7153,41 +7165,40 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129795195</v>
+        <v>129795162</v>
       </c>
       <c r="B65" t="n">
-        <v>8450</v>
+        <v>57734</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
-      <c r="J65" t="inlineStr"/>
       <c r="K65" t="inlineStr"/>
       <c r="L65" t="inlineStr"/>
       <c r="M65" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N65" t="inlineStr"/>
@@ -7197,10 +7208,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>444487</v>
+        <v>444428</v>
       </c>
       <c r="R65" t="n">
-        <v>6787441</v>
+        <v>6787329</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7241,7 +7252,6 @@
       <c r="AE65" t="b">
         <v>0</v>
       </c>
-      <c r="AF65" t="inlineStr"/>
       <c r="AG65" t="b">
         <v>0</v>
       </c>
@@ -7260,54 +7270,45 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129795177</v>
+        <v>129795125</v>
       </c>
       <c r="B66" t="n">
-        <v>8450</v>
+        <v>79703</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
-      <c r="J66" t="inlineStr"/>
-      <c r="K66" t="inlineStr"/>
-      <c r="L66" t="inlineStr"/>
-      <c r="M66" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>444342</v>
+        <v>444329</v>
       </c>
       <c r="R66" t="n">
-        <v>6787223</v>
+        <v>6787371</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7348,7 +7349,6 @@
       <c r="AE66" t="b">
         <v>0</v>
       </c>
-      <c r="AF66" t="inlineStr"/>
       <c r="AG66" t="b">
         <v>0</v>
       </c>
@@ -7367,10 +7367,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129795257</v>
+        <v>129795150</v>
       </c>
       <c r="B67" t="n">
-        <v>79084</v>
+        <v>57734</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7378,34 +7378,42 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
+      <c r="K67" t="inlineStr"/>
+      <c r="L67" t="inlineStr"/>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>444168</v>
+        <v>444413</v>
       </c>
       <c r="R67" t="n">
-        <v>6787171</v>
+        <v>6787222</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7464,10 +7472,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129795150</v>
+        <v>129795257</v>
       </c>
       <c r="B68" t="n">
-        <v>57734</v>
+        <v>79084</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7475,42 +7483,34 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
-      <c r="K68" t="inlineStr"/>
-      <c r="L68" t="inlineStr"/>
-      <c r="M68" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>444413</v>
+        <v>444168</v>
       </c>
       <c r="R68" t="n">
-        <v>6787222</v>
+        <v>6787171</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7569,54 +7569,45 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129795182</v>
+        <v>129795243</v>
       </c>
       <c r="B69" t="n">
-        <v>8450</v>
+        <v>79084</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
-      <c r="J69" t="inlineStr"/>
-      <c r="K69" t="inlineStr"/>
-      <c r="L69" t="inlineStr"/>
-      <c r="M69" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>444417</v>
+        <v>444159</v>
       </c>
       <c r="R69" t="n">
-        <v>6787266</v>
+        <v>6787297</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7657,7 +7648,6 @@
       <c r="AE69" t="b">
         <v>0</v>
       </c>
-      <c r="AF69" t="inlineStr"/>
       <c r="AG69" t="b">
         <v>0</v>
       </c>
@@ -7773,10 +7763,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129795135</v>
+        <v>129795284</v>
       </c>
       <c r="B71" t="n">
-        <v>91623</v>
+        <v>79084</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7784,37 +7774,34 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
-      <c r="J71" t="inlineStr"/>
-      <c r="K71" t="inlineStr"/>
-      <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>444158</v>
+        <v>444363</v>
       </c>
       <c r="R71" t="n">
-        <v>6787148</v>
+        <v>6787411</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7855,7 +7842,6 @@
       <c r="AE71" t="b">
         <v>0</v>
       </c>
-      <c r="AF71" t="inlineStr"/>
       <c r="AG71" t="b">
         <v>0</v>
       </c>
@@ -7874,45 +7860,53 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129795272</v>
+        <v>129795208</v>
       </c>
       <c r="B72" t="n">
-        <v>79084</v>
+        <v>58108</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6425</v>
+        <v>103015</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
+      <c r="K72" t="inlineStr"/>
+      <c r="L72" t="inlineStr"/>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>444553</v>
+        <v>444434</v>
       </c>
       <c r="R72" t="n">
-        <v>6787299</v>
+        <v>6787357</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7971,45 +7965,54 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129795287</v>
+        <v>129795182</v>
       </c>
       <c r="B73" t="n">
-        <v>79084</v>
+        <v>8450</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
+      <c r="J73" t="inlineStr"/>
+      <c r="K73" t="inlineStr"/>
+      <c r="L73" t="inlineStr"/>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>444430</v>
+        <v>444417</v>
       </c>
       <c r="R73" t="n">
-        <v>6787384</v>
+        <v>6787266</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8050,6 +8053,7 @@
       <c r="AE73" t="b">
         <v>0</v>
       </c>
+      <c r="AF73" t="inlineStr"/>
       <c r="AG73" t="b">
         <v>0</v>
       </c>
@@ -8068,10 +8072,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129795284</v>
+        <v>129795166</v>
       </c>
       <c r="B74" t="n">
-        <v>79084</v>
+        <v>57734</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8079,34 +8083,42 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
+      <c r="K74" t="inlineStr"/>
+      <c r="L74" t="inlineStr"/>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>444363</v>
+        <v>444254</v>
       </c>
       <c r="R74" t="n">
-        <v>6787411</v>
+        <v>6787333</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8165,10 +8177,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129795243</v>
+        <v>129795135</v>
       </c>
       <c r="B75" t="n">
-        <v>79084</v>
+        <v>91623</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8176,34 +8188,37 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
+      <c r="J75" t="inlineStr"/>
+      <c r="K75" t="inlineStr"/>
+      <c r="N75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>444159</v>
+        <v>444158</v>
       </c>
       <c r="R75" t="n">
-        <v>6787297</v>
+        <v>6787148</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8244,6 +8259,7 @@
       <c r="AE75" t="b">
         <v>0</v>
       </c>
+      <c r="AF75" t="inlineStr"/>
       <c r="AG75" t="b">
         <v>0</v>
       </c>
@@ -8262,10 +8278,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129795166</v>
+        <v>129795272</v>
       </c>
       <c r="B76" t="n">
-        <v>57734</v>
+        <v>79084</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8273,42 +8289,34 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
-      <c r="K76" t="inlineStr"/>
-      <c r="L76" t="inlineStr"/>
-      <c r="M76" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>444254</v>
+        <v>444553</v>
       </c>
       <c r="R76" t="n">
-        <v>6787333</v>
+        <v>6787299</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8367,53 +8375,45 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129795208</v>
+        <v>129795287</v>
       </c>
       <c r="B77" t="n">
-        <v>58108</v>
+        <v>79084</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>103015</v>
+        <v>6425</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
-      <c r="K77" t="inlineStr"/>
-      <c r="L77" t="inlineStr"/>
-      <c r="M77" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>444434</v>
+        <v>444430</v>
       </c>
       <c r="R77" t="n">
-        <v>6787357</v>
+        <v>6787384</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8569,10 +8569,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129795127</v>
+        <v>129795300</v>
       </c>
       <c r="B79" t="n">
-        <v>79703</v>
+        <v>79084</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8580,34 +8580,37 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
+      <c r="J79" t="inlineStr"/>
+      <c r="K79" t="inlineStr"/>
+      <c r="N79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>444432</v>
+        <v>444264</v>
       </c>
       <c r="R79" t="n">
-        <v>6787388</v>
+        <v>6787349</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8642,12 +8645,18 @@
           <t>2025-11-22</t>
         </is>
       </c>
+      <c r="AC79" t="inlineStr">
+        <is>
+          <t>Garnlav i de flesta träd inom en radie av 50 m.</t>
+        </is>
+      </c>
       <c r="AD79" t="b">
         <v>0</v>
       </c>
       <c r="AE79" t="b">
         <v>0</v>
       </c>
+      <c r="AF79" t="inlineStr"/>
       <c r="AG79" t="b">
         <v>0</v>
       </c>
@@ -8666,7 +8675,7 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129795300</v>
+        <v>129795241</v>
       </c>
       <c r="B80" t="n">
         <v>79084</v>
@@ -8695,19 +8704,16 @@
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
-      <c r="J80" t="inlineStr"/>
-      <c r="K80" t="inlineStr"/>
-      <c r="N80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>444264</v>
+        <v>444117</v>
       </c>
       <c r="R80" t="n">
-        <v>6787349</v>
+        <v>6787277</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8742,18 +8748,12 @@
           <t>2025-11-22</t>
         </is>
       </c>
-      <c r="AC80" t="inlineStr">
-        <is>
-          <t>Garnlav i de flesta träd inom en radie av 50 m.</t>
-        </is>
-      </c>
       <c r="AD80" t="b">
         <v>0</v>
       </c>
       <c r="AE80" t="b">
         <v>0</v>
       </c>
-      <c r="AF80" t="inlineStr"/>
       <c r="AG80" t="b">
         <v>0</v>
       </c>
@@ -8772,10 +8772,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129795307</v>
+        <v>129795127</v>
       </c>
       <c r="B81" t="n">
-        <v>79084</v>
+        <v>79703</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8783,21 +8783,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8807,10 +8807,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>444134</v>
+        <v>444432</v>
       </c>
       <c r="R81" t="n">
-        <v>6787304</v>
+        <v>6787388</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8869,37 +8869,43 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129795286</v>
+        <v>129795173</v>
       </c>
       <c r="B82" t="n">
-        <v>79084</v>
+        <v>8450</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
       <c r="J82" t="inlineStr"/>
       <c r="K82" t="inlineStr"/>
+      <c r="L82" t="inlineStr"/>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
@@ -8907,10 +8913,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>444440</v>
+        <v>444220</v>
       </c>
       <c r="R82" t="n">
-        <v>6787388</v>
+        <v>6787210</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8943,11 +8949,6 @@
       <c r="AA82" t="inlineStr">
         <is>
           <t>2025-11-22</t>
-        </is>
-      </c>
-      <c r="AC82" t="inlineStr">
-        <is>
-          <t>Gott om garnlav inom en radie av 50 m.</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -8975,45 +8976,54 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129795241</v>
+        <v>129795194</v>
       </c>
       <c r="B83" t="n">
-        <v>79084</v>
+        <v>8450</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
+      <c r="J83" t="inlineStr"/>
+      <c r="K83" t="inlineStr"/>
+      <c r="L83" t="inlineStr"/>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>444117</v>
+        <v>444501</v>
       </c>
       <c r="R83" t="n">
-        <v>6787277</v>
+        <v>6787363</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9054,6 +9064,7 @@
       <c r="AE83" t="b">
         <v>0</v>
       </c>
+      <c r="AF83" t="inlineStr"/>
       <c r="AG83" t="b">
         <v>0</v>
       </c>
@@ -9072,54 +9083,45 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129795194</v>
+        <v>129795307</v>
       </c>
       <c r="B84" t="n">
-        <v>8450</v>
+        <v>79084</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
-      <c r="J84" t="inlineStr"/>
-      <c r="K84" t="inlineStr"/>
-      <c r="L84" t="inlineStr"/>
-      <c r="M84" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>444501</v>
+        <v>444134</v>
       </c>
       <c r="R84" t="n">
-        <v>6787363</v>
+        <v>6787304</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9160,7 +9162,6 @@
       <c r="AE84" t="b">
         <v>0</v>
       </c>
-      <c r="AF84" t="inlineStr"/>
       <c r="AG84" t="b">
         <v>0</v>
       </c>
@@ -9179,43 +9180,37 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129795173</v>
+        <v>129795286</v>
       </c>
       <c r="B85" t="n">
-        <v>8450</v>
+        <v>79084</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
       <c r="J85" t="inlineStr"/>
       <c r="K85" t="inlineStr"/>
-      <c r="L85" t="inlineStr"/>
-      <c r="M85" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
@@ -9223,10 +9218,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>444220</v>
+        <v>444440</v>
       </c>
       <c r="R85" t="n">
-        <v>6787210</v>
+        <v>6787388</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9259,6 +9254,11 @@
       <c r="AA85" t="inlineStr">
         <is>
           <t>2025-11-22</t>
+        </is>
+      </c>
+      <c r="AC85" t="inlineStr">
+        <is>
+          <t>Gott om garnlav inom en radie av 50 m.</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9286,7 +9286,7 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129795308</v>
+        <v>129795242</v>
       </c>
       <c r="B86" t="n">
         <v>79084</v>
@@ -9321,7 +9321,7 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>444098</v>
+        <v>444125</v>
       </c>
       <c r="R86" t="n">
         <v>6787297</v>
@@ -9383,7 +9383,7 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129795242</v>
+        <v>129795308</v>
       </c>
       <c r="B87" t="n">
         <v>79084</v>
@@ -9418,7 +9418,7 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>444125</v>
+        <v>444098</v>
       </c>
       <c r="R87" t="n">
         <v>6787297</v>
@@ -9799,10 +9799,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>129795305</v>
+        <v>129795121</v>
       </c>
       <c r="B91" t="n">
-        <v>79084</v>
+        <v>79703</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9810,21 +9810,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -9834,10 +9834,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>444169</v>
+        <v>444254</v>
       </c>
       <c r="R91" t="n">
-        <v>6787323</v>
+        <v>6787204</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9896,7 +9896,7 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>129795288</v>
+        <v>129795252</v>
       </c>
       <c r="B92" t="n">
         <v>79084</v>
@@ -9931,10 +9931,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>444420</v>
+        <v>444249</v>
       </c>
       <c r="R92" t="n">
-        <v>6787366</v>
+        <v>6787249</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9967,6 +9967,11 @@
       <c r="AA92" t="inlineStr">
         <is>
           <t>2025-11-22</t>
+        </is>
+      </c>
+      <c r="AC92" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 40m.</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10090,10 +10095,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>129795297</v>
+        <v>129795123</v>
       </c>
       <c r="B94" t="n">
-        <v>79084</v>
+        <v>79703</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10101,21 +10106,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -10125,10 +10130,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>444297</v>
+        <v>444530</v>
       </c>
       <c r="R94" t="n">
-        <v>6787333</v>
+        <v>6787326</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10187,7 +10192,7 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>129795262</v>
+        <v>129795288</v>
       </c>
       <c r="B95" t="n">
         <v>79084</v>
@@ -10222,10 +10227,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>444219</v>
+        <v>444420</v>
       </c>
       <c r="R95" t="n">
-        <v>6787163</v>
+        <v>6787366</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10284,7 +10289,7 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>129795252</v>
+        <v>129795305</v>
       </c>
       <c r="B96" t="n">
         <v>79084</v>
@@ -10319,10 +10324,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>444249</v>
+        <v>444169</v>
       </c>
       <c r="R96" t="n">
-        <v>6787249</v>
+        <v>6787323</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10355,11 +10360,6 @@
       <c r="AA96" t="inlineStr">
         <is>
           <t>2025-11-22</t>
-        </is>
-      </c>
-      <c r="AC96" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 40m.</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10386,7 +10386,7 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>129795121</v>
+        <v>129795124</v>
       </c>
       <c r="B97" t="n">
         <v>79703</v>
@@ -10421,10 +10421,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>444254</v>
+        <v>444393</v>
       </c>
       <c r="R97" t="n">
-        <v>6787204</v>
+        <v>6787395</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10483,45 +10483,54 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>129795124</v>
+        <v>129795167</v>
       </c>
       <c r="B98" t="n">
-        <v>79703</v>
+        <v>8450</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
+      <c r="J98" t="inlineStr"/>
+      <c r="K98" t="inlineStr"/>
+      <c r="L98" t="inlineStr"/>
+      <c r="M98" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>444393</v>
+        <v>444132</v>
       </c>
       <c r="R98" t="n">
-        <v>6787395</v>
+        <v>6787237</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10562,6 +10571,7 @@
       <c r="AE98" t="b">
         <v>0</v>
       </c>
+      <c r="AF98" t="inlineStr"/>
       <c r="AG98" t="b">
         <v>0</v>
       </c>
@@ -10580,10 +10590,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>129795123</v>
+        <v>129795297</v>
       </c>
       <c r="B99" t="n">
-        <v>79703</v>
+        <v>79084</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10591,21 +10601,21 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -10615,10 +10625,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>444530</v>
+        <v>444297</v>
       </c>
       <c r="R99" t="n">
-        <v>6787326</v>
+        <v>6787333</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10677,54 +10687,45 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>129795167</v>
+        <v>129795262</v>
       </c>
       <c r="B100" t="n">
-        <v>8450</v>
+        <v>79084</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
-      <c r="J100" t="inlineStr"/>
-      <c r="K100" t="inlineStr"/>
-      <c r="L100" t="inlineStr"/>
-      <c r="M100" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>444132</v>
+        <v>444219</v>
       </c>
       <c r="R100" t="n">
-        <v>6787237</v>
+        <v>6787163</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10765,7 +10766,6 @@
       <c r="AE100" t="b">
         <v>0</v>
       </c>
-      <c r="AF100" t="inlineStr"/>
       <c r="AG100" t="b">
         <v>0</v>
       </c>
@@ -10784,7 +10784,7 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>129795264</v>
+        <v>129795303</v>
       </c>
       <c r="B101" t="n">
         <v>79084</v>
@@ -10819,10 +10819,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>444252</v>
+        <v>444200</v>
       </c>
       <c r="R101" t="n">
-        <v>6787160</v>
+        <v>6787331</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10881,7 +10881,7 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>129795303</v>
+        <v>129795264</v>
       </c>
       <c r="B102" t="n">
         <v>79084</v>
@@ -10916,10 +10916,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>444200</v>
+        <v>444252</v>
       </c>
       <c r="R102" t="n">
-        <v>6787331</v>
+        <v>6787160</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11279,7 +11279,7 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>129795180</v>
+        <v>129795186</v>
       </c>
       <c r="B106" t="n">
         <v>8450</v>
@@ -11323,10 +11323,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>444409</v>
+        <v>444473</v>
       </c>
       <c r="R106" t="n">
-        <v>6787219</v>
+        <v>6787334</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11386,7 +11386,7 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>129795178</v>
+        <v>129795196</v>
       </c>
       <c r="B107" t="n">
         <v>8450</v>
@@ -11430,10 +11430,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>444375</v>
+        <v>444346</v>
       </c>
       <c r="R107" t="n">
-        <v>6787207</v>
+        <v>6787369</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11493,7 +11493,7 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>129795186</v>
+        <v>129795178</v>
       </c>
       <c r="B108" t="n">
         <v>8450</v>
@@ -11537,10 +11537,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>444473</v>
+        <v>444375</v>
       </c>
       <c r="R108" t="n">
-        <v>6787334</v>
+        <v>6787207</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11600,7 +11600,7 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>129795196</v>
+        <v>129795180</v>
       </c>
       <c r="B109" t="n">
         <v>8450</v>
@@ -11644,10 +11644,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>444346</v>
+        <v>444409</v>
       </c>
       <c r="R109" t="n">
-        <v>6787369</v>
+        <v>6787219</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11707,40 +11707,41 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>129795149</v>
+        <v>129795203</v>
       </c>
       <c r="B110" t="n">
-        <v>57734</v>
+        <v>8450</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
+      <c r="J110" t="inlineStr"/>
       <c r="K110" t="inlineStr"/>
       <c r="L110" t="inlineStr"/>
       <c r="M110" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N110" t="inlineStr"/>
@@ -11750,10 +11751,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>444223</v>
+        <v>444401</v>
       </c>
       <c r="R110" t="n">
-        <v>6787221</v>
+        <v>6787298</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11794,6 +11795,7 @@
       <c r="AE110" t="b">
         <v>0</v>
       </c>
+      <c r="AF110" t="inlineStr"/>
       <c r="AG110" t="b">
         <v>0</v>
       </c>
@@ -11812,40 +11814,41 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>129795145</v>
+        <v>129795201</v>
       </c>
       <c r="B111" t="n">
-        <v>57734</v>
+        <v>8450</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
+      <c r="J111" t="inlineStr"/>
       <c r="K111" t="inlineStr"/>
       <c r="L111" t="inlineStr"/>
       <c r="M111" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N111" t="inlineStr"/>
@@ -11855,10 +11858,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>444228</v>
+        <v>444430</v>
       </c>
       <c r="R111" t="n">
-        <v>6787226</v>
+        <v>6787332</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -11899,6 +11902,7 @@
       <c r="AE111" t="b">
         <v>0</v>
       </c>
+      <c r="AF111" t="inlineStr"/>
       <c r="AG111" t="b">
         <v>0</v>
       </c>
@@ -11917,7 +11921,7 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>129795151</v>
+        <v>129795149</v>
       </c>
       <c r="B112" t="n">
         <v>57734</v>
@@ -11950,7 +11954,7 @@
       <c r="L112" t="inlineStr"/>
       <c r="M112" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N112" t="inlineStr"/>
@@ -11960,10 +11964,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>444425</v>
+        <v>444223</v>
       </c>
       <c r="R112" t="n">
-        <v>6787278</v>
+        <v>6787221</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12022,41 +12026,40 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>129795203</v>
+        <v>129795145</v>
       </c>
       <c r="B113" t="n">
-        <v>8450</v>
+        <v>57734</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
-      <c r="J113" t="inlineStr"/>
       <c r="K113" t="inlineStr"/>
       <c r="L113" t="inlineStr"/>
       <c r="M113" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N113" t="inlineStr"/>
@@ -12066,10 +12069,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>444401</v>
+        <v>444228</v>
       </c>
       <c r="R113" t="n">
-        <v>6787298</v>
+        <v>6787226</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12110,7 +12113,6 @@
       <c r="AE113" t="b">
         <v>0</v>
       </c>
-      <c r="AF113" t="inlineStr"/>
       <c r="AG113" t="b">
         <v>0</v>
       </c>
@@ -12129,41 +12131,40 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>129795201</v>
+        <v>129795151</v>
       </c>
       <c r="B114" t="n">
-        <v>8450</v>
+        <v>57734</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
-      <c r="J114" t="inlineStr"/>
       <c r="K114" t="inlineStr"/>
       <c r="L114" t="inlineStr"/>
       <c r="M114" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N114" t="inlineStr"/>
@@ -12173,10 +12174,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>444430</v>
+        <v>444425</v>
       </c>
       <c r="R114" t="n">
-        <v>6787332</v>
+        <v>6787278</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12217,7 +12218,6 @@
       <c r="AE114" t="b">
         <v>0</v>
       </c>
-      <c r="AF114" t="inlineStr"/>
       <c r="AG114" t="b">
         <v>0</v>
       </c>
@@ -12333,45 +12333,54 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>129795289</v>
+        <v>129795171</v>
       </c>
       <c r="B116" t="n">
-        <v>79084</v>
+        <v>8450</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
+      <c r="J116" t="inlineStr"/>
+      <c r="K116" t="inlineStr"/>
+      <c r="L116" t="inlineStr"/>
+      <c r="M116" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N116" t="inlineStr"/>
       <c r="P116" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>444435</v>
+        <v>444185</v>
       </c>
       <c r="R116" t="n">
-        <v>6787341</v>
+        <v>6787226</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12412,6 +12421,7 @@
       <c r="AE116" t="b">
         <v>0</v>
       </c>
+      <c r="AF116" t="inlineStr"/>
       <c r="AG116" t="b">
         <v>0</v>
       </c>
@@ -12430,10 +12440,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>129795171</v>
+        <v>129795132</v>
       </c>
       <c r="B117" t="n">
-        <v>8450</v>
+        <v>56927</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -12441,30 +12451,29 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>106545</v>
+        <v>100138</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
-      <c r="J117" t="inlineStr"/>
       <c r="K117" t="inlineStr"/>
       <c r="L117" t="inlineStr"/>
       <c r="M117" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="N117" t="inlineStr"/>
@@ -12474,10 +12483,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>444185</v>
+        <v>444315</v>
       </c>
       <c r="R117" t="n">
-        <v>6787226</v>
+        <v>6787291</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12518,7 +12527,6 @@
       <c r="AE117" t="b">
         <v>0</v>
       </c>
-      <c r="AF117" t="inlineStr"/>
       <c r="AG117" t="b">
         <v>0</v>
       </c>
@@ -12537,7 +12545,7 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>129795164</v>
+        <v>129795154</v>
       </c>
       <c r="B118" t="n">
         <v>57734</v>
@@ -12580,10 +12588,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>444397</v>
+        <v>444457</v>
       </c>
       <c r="R118" t="n">
-        <v>6787300</v>
+        <v>6787303</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12642,7 +12650,7 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>129795154</v>
+        <v>129795157</v>
       </c>
       <c r="B119" t="n">
         <v>57734</v>
@@ -12685,10 +12693,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>444457</v>
+        <v>444525</v>
       </c>
       <c r="R119" t="n">
-        <v>6787303</v>
+        <v>6787344</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -12747,7 +12755,7 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>129795157</v>
+        <v>129795164</v>
       </c>
       <c r="B120" t="n">
         <v>57734</v>
@@ -12790,10 +12798,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>444525</v>
+        <v>444397</v>
       </c>
       <c r="R120" t="n">
-        <v>6787344</v>
+        <v>6787300</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -12852,53 +12860,45 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>129795132</v>
+        <v>129795289</v>
       </c>
       <c r="B121" t="n">
-        <v>56927</v>
+        <v>79084</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
-      <c r="K121" t="inlineStr"/>
-      <c r="L121" t="inlineStr"/>
-      <c r="M121" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N121" t="inlineStr"/>
       <c r="P121" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>444315</v>
+        <v>444435</v>
       </c>
       <c r="R121" t="n">
-        <v>6787291</v>
+        <v>6787341</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -12957,41 +12957,40 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>129795188</v>
+        <v>129795144</v>
       </c>
       <c r="B122" t="n">
-        <v>8450</v>
+        <v>57734</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
-      <c r="J122" t="inlineStr"/>
       <c r="K122" t="inlineStr"/>
       <c r="L122" t="inlineStr"/>
       <c r="M122" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N122" t="inlineStr"/>
@@ -13001,10 +13000,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>444498</v>
+        <v>444186</v>
       </c>
       <c r="R122" t="n">
-        <v>6787280</v>
+        <v>6787223</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -13045,7 +13044,6 @@
       <c r="AE122" t="b">
         <v>0</v>
       </c>
-      <c r="AF122" t="inlineStr"/>
       <c r="AG122" t="b">
         <v>0</v>
       </c>
@@ -13064,54 +13062,45 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>129795179</v>
+        <v>129795301</v>
       </c>
       <c r="B123" t="n">
-        <v>8450</v>
+        <v>79084</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
-      <c r="J123" t="inlineStr"/>
-      <c r="K123" t="inlineStr"/>
-      <c r="L123" t="inlineStr"/>
-      <c r="M123" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N123" t="inlineStr"/>
       <c r="P123" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>444378</v>
+        <v>444250</v>
       </c>
       <c r="R123" t="n">
-        <v>6787236</v>
+        <v>6787342</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13152,7 +13141,6 @@
       <c r="AE123" t="b">
         <v>0</v>
       </c>
-      <c r="AF123" t="inlineStr"/>
       <c r="AG123" t="b">
         <v>0</v>
       </c>
@@ -13171,7 +13159,7 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>129795301</v>
+        <v>129795294</v>
       </c>
       <c r="B124" t="n">
         <v>79084</v>
@@ -13206,10 +13194,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>444250</v>
+        <v>444323</v>
       </c>
       <c r="R124" t="n">
-        <v>6787342</v>
+        <v>6787297</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13268,45 +13256,54 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>129795294</v>
+        <v>129795179</v>
       </c>
       <c r="B125" t="n">
-        <v>79084</v>
+        <v>8450</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
+      <c r="J125" t="inlineStr"/>
+      <c r="K125" t="inlineStr"/>
+      <c r="L125" t="inlineStr"/>
+      <c r="M125" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N125" t="inlineStr"/>
       <c r="P125" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>444323</v>
+        <v>444378</v>
       </c>
       <c r="R125" t="n">
-        <v>6787297</v>
+        <v>6787236</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13347,6 +13344,7 @@
       <c r="AE125" t="b">
         <v>0</v>
       </c>
+      <c r="AF125" t="inlineStr"/>
       <c r="AG125" t="b">
         <v>0</v>
       </c>
@@ -13365,40 +13363,41 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>129795144</v>
+        <v>129795188</v>
       </c>
       <c r="B126" t="n">
-        <v>57734</v>
+        <v>8450</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
+      <c r="J126" t="inlineStr"/>
       <c r="K126" t="inlineStr"/>
       <c r="L126" t="inlineStr"/>
       <c r="M126" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N126" t="inlineStr"/>
@@ -13408,10 +13407,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>444186</v>
+        <v>444498</v>
       </c>
       <c r="R126" t="n">
-        <v>6787223</v>
+        <v>6787280</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -13452,6 +13451,7 @@
       <c r="AE126" t="b">
         <v>0</v>
       </c>
+      <c r="AF126" t="inlineStr"/>
       <c r="AG126" t="b">
         <v>0</v>
       </c>
@@ -13470,10 +13470,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>129795258</v>
+        <v>129795159</v>
       </c>
       <c r="B127" t="n">
-        <v>79084</v>
+        <v>57734</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -13481,34 +13481,42 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
+      <c r="K127" t="inlineStr"/>
+      <c r="L127" t="inlineStr"/>
+      <c r="M127" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N127" t="inlineStr"/>
       <c r="P127" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>444174</v>
+        <v>444436</v>
       </c>
       <c r="R127" t="n">
-        <v>6787136</v>
+        <v>6787463</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -13567,45 +13575,54 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>129795275</v>
+        <v>129795168</v>
       </c>
       <c r="B128" t="n">
-        <v>79084</v>
+        <v>8450</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
+      <c r="J128" t="inlineStr"/>
+      <c r="K128" t="inlineStr"/>
+      <c r="L128" t="inlineStr"/>
+      <c r="M128" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N128" t="inlineStr"/>
       <c r="P128" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>444495</v>
+        <v>444272</v>
       </c>
       <c r="R128" t="n">
-        <v>6787340</v>
+        <v>6787286</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -13646,6 +13663,7 @@
       <c r="AE128" t="b">
         <v>0</v>
       </c>
+      <c r="AF128" t="inlineStr"/>
       <c r="AG128" t="b">
         <v>0</v>
       </c>
@@ -13664,45 +13682,54 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>129795267</v>
+        <v>129795175</v>
       </c>
       <c r="B129" t="n">
-        <v>79084</v>
+        <v>8450</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
+      <c r="J129" t="inlineStr"/>
+      <c r="K129" t="inlineStr"/>
+      <c r="L129" t="inlineStr"/>
+      <c r="M129" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N129" t="inlineStr"/>
       <c r="P129" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>444353</v>
+        <v>444182</v>
       </c>
       <c r="R129" t="n">
-        <v>6787215</v>
+        <v>6787101</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -13737,17 +13764,13 @@
           <t>2025-11-22</t>
         </is>
       </c>
-      <c r="AC129" t="inlineStr">
-        <is>
-          <t>Gott om garnlav inom en radie av 40m.</t>
-        </is>
-      </c>
       <c r="AD129" t="b">
         <v>0</v>
       </c>
       <c r="AE129" t="b">
         <v>0</v>
       </c>
+      <c r="AF129" t="inlineStr"/>
       <c r="AG129" t="b">
         <v>0</v>
       </c>
@@ -13766,7 +13789,7 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>129795263</v>
+        <v>129795258</v>
       </c>
       <c r="B130" t="n">
         <v>79084</v>
@@ -13801,10 +13824,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>444241</v>
+        <v>444174</v>
       </c>
       <c r="R130" t="n">
-        <v>6787149</v>
+        <v>6787136</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -13863,10 +13886,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>129795137</v>
+        <v>129795267</v>
       </c>
       <c r="B131" t="n">
-        <v>91623</v>
+        <v>79084</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -13874,37 +13897,34 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
-      <c r="J131" t="inlineStr"/>
-      <c r="K131" t="inlineStr"/>
-      <c r="N131" t="inlineStr"/>
       <c r="P131" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>444203</v>
+        <v>444353</v>
       </c>
       <c r="R131" t="n">
-        <v>6787221</v>
+        <v>6787215</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -13939,13 +13959,17 @@
           <t>2025-11-22</t>
         </is>
       </c>
+      <c r="AC131" t="inlineStr">
+        <is>
+          <t>Gott om garnlav inom en radie av 40m.</t>
+        </is>
+      </c>
       <c r="AD131" t="b">
         <v>0</v>
       </c>
       <c r="AE131" t="b">
         <v>0</v>
       </c>
-      <c r="AF131" t="inlineStr"/>
       <c r="AG131" t="b">
         <v>0</v>
       </c>
@@ -13964,10 +13988,10 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>129795159</v>
+        <v>129795137</v>
       </c>
       <c r="B132" t="n">
-        <v>57734</v>
+        <v>91623</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -13975,31 +13999,26 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>100049</v>
+        <v>5442</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
+      <c r="J132" t="inlineStr"/>
       <c r="K132" t="inlineStr"/>
-      <c r="L132" t="inlineStr"/>
-      <c r="M132" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N132" t="inlineStr"/>
       <c r="P132" t="inlineStr">
         <is>
@@ -14007,10 +14026,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>444436</v>
+        <v>444203</v>
       </c>
       <c r="R132" t="n">
-        <v>6787463</v>
+        <v>6787221</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -14051,6 +14070,7 @@
       <c r="AE132" t="b">
         <v>0</v>
       </c>
+      <c r="AF132" t="inlineStr"/>
       <c r="AG132" t="b">
         <v>0</v>
       </c>
@@ -14069,54 +14089,45 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>129795175</v>
+        <v>129795275</v>
       </c>
       <c r="B133" t="n">
-        <v>8450</v>
+        <v>79084</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
-      <c r="J133" t="inlineStr"/>
-      <c r="K133" t="inlineStr"/>
-      <c r="L133" t="inlineStr"/>
-      <c r="M133" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N133" t="inlineStr"/>
       <c r="P133" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>444182</v>
+        <v>444495</v>
       </c>
       <c r="R133" t="n">
-        <v>6787101</v>
+        <v>6787340</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -14157,7 +14168,6 @@
       <c r="AE133" t="b">
         <v>0</v>
       </c>
-      <c r="AF133" t="inlineStr"/>
       <c r="AG133" t="b">
         <v>0</v>
       </c>
@@ -14176,54 +14186,45 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>129795168</v>
+        <v>129795263</v>
       </c>
       <c r="B134" t="n">
-        <v>8450</v>
+        <v>79084</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
-      <c r="J134" t="inlineStr"/>
-      <c r="K134" t="inlineStr"/>
-      <c r="L134" t="inlineStr"/>
-      <c r="M134" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N134" t="inlineStr"/>
       <c r="P134" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>444272</v>
+        <v>444241</v>
       </c>
       <c r="R134" t="n">
-        <v>6787286</v>
+        <v>6787149</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -14264,7 +14265,6 @@
       <c r="AE134" t="b">
         <v>0</v>
       </c>
-      <c r="AF134" t="inlineStr"/>
       <c r="AG134" t="b">
         <v>0</v>
       </c>
@@ -14283,7 +14283,7 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>129795304</v>
+        <v>129795254</v>
       </c>
       <c r="B135" t="n">
         <v>79084</v>
@@ -14312,16 +14312,19 @@
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
+      <c r="J135" t="inlineStr"/>
+      <c r="K135" t="inlineStr"/>
+      <c r="N135" t="inlineStr"/>
       <c r="P135" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>444172</v>
+        <v>444199</v>
       </c>
       <c r="R135" t="n">
-        <v>6787339</v>
+        <v>6787221</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -14362,6 +14365,7 @@
       <c r="AE135" t="b">
         <v>0</v>
       </c>
+      <c r="AF135" t="inlineStr"/>
       <c r="AG135" t="b">
         <v>0</v>
       </c>
@@ -14380,54 +14384,45 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>129795204</v>
+        <v>129795266</v>
       </c>
       <c r="B136" t="n">
-        <v>8450</v>
+        <v>79084</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
-      <c r="J136" t="inlineStr"/>
-      <c r="K136" t="inlineStr"/>
-      <c r="L136" t="inlineStr"/>
-      <c r="M136" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N136" t="inlineStr"/>
       <c r="P136" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>444380</v>
+        <v>444314</v>
       </c>
       <c r="R136" t="n">
-        <v>6787306</v>
+        <v>6787212</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -14462,13 +14457,17 @@
           <t>2025-11-22</t>
         </is>
       </c>
+      <c r="AC136" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 40m</t>
+        </is>
+      </c>
       <c r="AD136" t="b">
         <v>0</v>
       </c>
       <c r="AE136" t="b">
         <v>0</v>
       </c>
-      <c r="AF136" t="inlineStr"/>
       <c r="AG136" t="b">
         <v>0</v>
       </c>
@@ -14487,7 +14486,7 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>129795274</v>
+        <v>129795247</v>
       </c>
       <c r="B137" t="n">
         <v>79084</v>
@@ -14522,10 +14521,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>444538</v>
+        <v>444225</v>
       </c>
       <c r="R137" t="n">
-        <v>6787325</v>
+        <v>6787275</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -14584,10 +14583,10 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>129795254</v>
+        <v>129795139</v>
       </c>
       <c r="B138" t="n">
-        <v>79084</v>
+        <v>91623</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -14595,21 +14594,21 @@
         </is>
       </c>
       <c r="E138" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
@@ -14622,10 +14621,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>444199</v>
+        <v>444342</v>
       </c>
       <c r="R138" t="n">
-        <v>6787221</v>
+        <v>6787240</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -14685,7 +14684,7 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>129795302</v>
+        <v>129795304</v>
       </c>
       <c r="B139" t="n">
         <v>79084</v>
@@ -14720,10 +14719,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>444222</v>
+        <v>444172</v>
       </c>
       <c r="R139" t="n">
-        <v>6787345</v>
+        <v>6787339</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -14883,7 +14882,7 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>129795266</v>
+        <v>129795274</v>
       </c>
       <c r="B141" t="n">
         <v>79084</v>
@@ -14918,10 +14917,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>444314</v>
+        <v>444538</v>
       </c>
       <c r="R141" t="n">
-        <v>6787212</v>
+        <v>6787325</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -14954,11 +14953,6 @@
       <c r="AA141" t="inlineStr">
         <is>
           <t>2025-11-22</t>
-        </is>
-      </c>
-      <c r="AC141" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 40m</t>
         </is>
       </c>
       <c r="AD141" t="b">
@@ -14985,7 +14979,7 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>129795247</v>
+        <v>129795302</v>
       </c>
       <c r="B142" t="n">
         <v>79084</v>
@@ -15020,10 +15014,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>444225</v>
+        <v>444222</v>
       </c>
       <c r="R142" t="n">
-        <v>6787275</v>
+        <v>6787345</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -15082,37 +15076,43 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>129795139</v>
+        <v>129795204</v>
       </c>
       <c r="B143" t="n">
-        <v>91623</v>
+        <v>8450</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E143" t="n">
-        <v>5442</v>
+        <v>106545</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
       <c r="J143" t="inlineStr"/>
       <c r="K143" t="inlineStr"/>
+      <c r="L143" t="inlineStr"/>
+      <c r="M143" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N143" t="inlineStr"/>
       <c r="P143" t="inlineStr">
         <is>
@@ -15120,10 +15120,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>444342</v>
+        <v>444380</v>
       </c>
       <c r="R143" t="n">
-        <v>6787240</v>
+        <v>6787306</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>

--- a/artfynd/A 51041-2025 artfynd.xlsx
+++ b/artfynd/A 51041-2025 artfynd.xlsx
@@ -1068,37 +1068,43 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129795283</v>
+        <v>129795197</v>
       </c>
       <c r="B6" t="n">
-        <v>79084</v>
+        <v>8450</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1106,10 +1112,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>444337</v>
+        <v>444406</v>
       </c>
       <c r="R6" t="n">
-        <v>6787374</v>
+        <v>6787392</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1169,45 +1175,54 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129795244</v>
+        <v>129795169</v>
       </c>
       <c r="B7" t="n">
-        <v>79084</v>
+        <v>8450</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>444105</v>
+        <v>444272</v>
       </c>
       <c r="R7" t="n">
-        <v>6787246</v>
+        <v>6787239</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1248,6 +1263,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1266,45 +1282,54 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129795298</v>
+        <v>129795190</v>
       </c>
       <c r="B8" t="n">
-        <v>79084</v>
+        <v>8450</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>444305</v>
+        <v>444510</v>
       </c>
       <c r="R8" t="n">
-        <v>6787353</v>
+        <v>6787276</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1345,6 +1370,7 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1363,43 +1389,37 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129795197</v>
+        <v>129795283</v>
       </c>
       <c r="B9" t="n">
-        <v>8450</v>
+        <v>79084</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1407,10 +1427,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>444406</v>
+        <v>444337</v>
       </c>
       <c r="R9" t="n">
-        <v>6787392</v>
+        <v>6787374</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1470,54 +1490,45 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129795169</v>
+        <v>129795244</v>
       </c>
       <c r="B10" t="n">
-        <v>8450</v>
+        <v>79084</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>444272</v>
+        <v>444105</v>
       </c>
       <c r="R10" t="n">
-        <v>6787239</v>
+        <v>6787246</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1558,7 +1569,6 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1577,54 +1587,45 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129795190</v>
+        <v>129795298</v>
       </c>
       <c r="B11" t="n">
-        <v>8450</v>
+        <v>79084</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>444510</v>
+        <v>444305</v>
       </c>
       <c r="R11" t="n">
-        <v>6787276</v>
+        <v>6787353</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1665,7 +1666,6 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1684,10 +1684,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129795163</v>
+        <v>129795271</v>
       </c>
       <c r="B12" t="n">
-        <v>57734</v>
+        <v>79084</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1695,31 +1695,26 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1727,10 +1722,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>444415</v>
+        <v>444466</v>
       </c>
       <c r="R12" t="n">
-        <v>6787316</v>
+        <v>6787306</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1765,12 +1760,18 @@
           <t>2025-11-22</t>
         </is>
       </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 50m.</t>
+        </is>
+      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1789,10 +1790,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129795153</v>
+        <v>129795276</v>
       </c>
       <c r="B13" t="n">
-        <v>57734</v>
+        <v>79084</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1800,31 +1801,26 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1832,10 +1828,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>444452</v>
+        <v>444499</v>
       </c>
       <c r="R13" t="n">
-        <v>6787294</v>
+        <v>6787367</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1870,12 +1866,18 @@
           <t>2025-11-22</t>
         </is>
       </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 50m.</t>
+        </is>
+      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -1894,7 +1896,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129795281</v>
+        <v>129795299</v>
       </c>
       <c r="B14" t="n">
         <v>79084</v>
@@ -1923,19 +1925,16 @@
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>444408</v>
+        <v>444265</v>
       </c>
       <c r="R14" t="n">
-        <v>6787452</v>
+        <v>6787372</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1976,7 +1975,6 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -1995,41 +1993,40 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129795174</v>
+        <v>129795155</v>
       </c>
       <c r="B15" t="n">
-        <v>8450</v>
+        <v>57734</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N15" t="inlineStr"/>
@@ -2039,10 +2036,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>444166</v>
+        <v>444498</v>
       </c>
       <c r="R15" t="n">
-        <v>6787161</v>
+        <v>6787306</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2083,7 +2080,6 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2102,41 +2098,40 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129795205</v>
+        <v>129795163</v>
       </c>
       <c r="B16" t="n">
-        <v>8450</v>
+        <v>57734</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N16" t="inlineStr"/>
@@ -2146,10 +2141,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>444343</v>
+        <v>444415</v>
       </c>
       <c r="R16" t="n">
-        <v>6787310</v>
+        <v>6787316</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2190,7 +2185,6 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2209,10 +2203,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129795271</v>
+        <v>129795153</v>
       </c>
       <c r="B17" t="n">
-        <v>79084</v>
+        <v>57734</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2220,26 +2214,31 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2247,10 +2246,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>444466</v>
+        <v>444452</v>
       </c>
       <c r="R17" t="n">
-        <v>6787306</v>
+        <v>6787294</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2285,18 +2284,12 @@
           <t>2025-11-22</t>
         </is>
       </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 50m.</t>
-        </is>
-      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2315,7 +2308,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129795276</v>
+        <v>129795281</v>
       </c>
       <c r="B18" t="n">
         <v>79084</v>
@@ -2353,10 +2346,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>444499</v>
+        <v>444408</v>
       </c>
       <c r="R18" t="n">
-        <v>6787367</v>
+        <v>6787452</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2389,11 +2382,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-11-22</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 50m.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2421,45 +2409,54 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129795299</v>
+        <v>129795174</v>
       </c>
       <c r="B19" t="n">
-        <v>79084</v>
+        <v>8450</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>444265</v>
+        <v>444166</v>
       </c>
       <c r="R19" t="n">
-        <v>6787372</v>
+        <v>6787161</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2500,6 +2497,7 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2518,40 +2516,41 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129795155</v>
+        <v>129795205</v>
       </c>
       <c r="B20" t="n">
-        <v>57734</v>
+        <v>8450</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N20" t="inlineStr"/>
@@ -2561,10 +2560,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>444498</v>
+        <v>444343</v>
       </c>
       <c r="R20" t="n">
-        <v>6787306</v>
+        <v>6787310</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2605,6 +2604,7 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -4068,10 +4068,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129795165</v>
+        <v>129795270</v>
       </c>
       <c r="B35" t="n">
-        <v>57734</v>
+        <v>79084</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4079,42 +4079,34 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>444251</v>
+        <v>444416</v>
       </c>
       <c r="R35" t="n">
-        <v>6787376</v>
+        <v>6787260</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4173,10 +4165,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129795269</v>
+        <v>129795165</v>
       </c>
       <c r="B36" t="n">
-        <v>79084</v>
+        <v>57734</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4184,34 +4176,42 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>444429</v>
+        <v>444251</v>
       </c>
       <c r="R36" t="n">
-        <v>6787240</v>
+        <v>6787376</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4270,7 +4270,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129795249</v>
+        <v>129795269</v>
       </c>
       <c r="B37" t="n">
         <v>79084</v>
@@ -4305,10 +4305,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>444267</v>
+        <v>444429</v>
       </c>
       <c r="R37" t="n">
-        <v>6787295</v>
+        <v>6787240</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4367,7 +4367,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129795296</v>
+        <v>129795249</v>
       </c>
       <c r="B38" t="n">
         <v>79084</v>
@@ -4396,19 +4396,16 @@
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
-      <c r="K38" t="inlineStr"/>
-      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>444299</v>
+        <v>444267</v>
       </c>
       <c r="R38" t="n">
-        <v>6787304</v>
+        <v>6787295</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4443,18 +4440,12 @@
           <t>2025-11-22</t>
         </is>
       </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 50 m.</t>
-        </is>
-      </c>
       <c r="AD38" t="b">
         <v>0</v>
       </c>
       <c r="AE38" t="b">
         <v>0</v>
       </c>
-      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -4473,10 +4464,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129795133</v>
+        <v>129795296</v>
       </c>
       <c r="B39" t="n">
-        <v>57895</v>
+        <v>79084</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4484,31 +4475,26 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
@@ -4516,10 +4502,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>444226</v>
+        <v>444299</v>
       </c>
       <c r="R39" t="n">
-        <v>6787236</v>
+        <v>6787304</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4554,12 +4540,18 @@
           <t>2025-11-22</t>
         </is>
       </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 50 m.</t>
+        </is>
+      </c>
       <c r="AD39" t="b">
         <v>0</v>
       </c>
       <c r="AE39" t="b">
         <v>0</v>
       </c>
+      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -4578,41 +4570,40 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129795202</v>
+        <v>129795133</v>
       </c>
       <c r="B40" t="n">
-        <v>8450</v>
+        <v>57895</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>106545</v>
+        <v>103021</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr"/>
       <c r="L40" t="inlineStr"/>
       <c r="M40" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N40" t="inlineStr"/>
@@ -4622,10 +4613,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>444413</v>
+        <v>444226</v>
       </c>
       <c r="R40" t="n">
-        <v>6787314</v>
+        <v>6787236</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4666,7 +4657,6 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
-      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
@@ -4685,7 +4675,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129795193</v>
+        <v>129795202</v>
       </c>
       <c r="B41" t="n">
         <v>8450</v>
@@ -4729,10 +4719,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>444508</v>
+        <v>444413</v>
       </c>
       <c r="R41" t="n">
-        <v>6787352</v>
+        <v>6787314</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4792,45 +4782,54 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129795270</v>
+        <v>129795193</v>
       </c>
       <c r="B42" t="n">
-        <v>79084</v>
+        <v>8450</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>444416</v>
+        <v>444508</v>
       </c>
       <c r="R42" t="n">
-        <v>6787260</v>
+        <v>6787352</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4871,6 +4870,7 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
+      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
@@ -6844,54 +6844,45 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129795195</v>
+        <v>129795125</v>
       </c>
       <c r="B62" t="n">
-        <v>8450</v>
+        <v>79703</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
-      <c r="J62" t="inlineStr"/>
-      <c r="K62" t="inlineStr"/>
-      <c r="L62" t="inlineStr"/>
-      <c r="M62" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>444487</v>
+        <v>444329</v>
       </c>
       <c r="R62" t="n">
-        <v>6787441</v>
+        <v>6787371</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6932,7 +6923,6 @@
       <c r="AE62" t="b">
         <v>0</v>
       </c>
-      <c r="AF62" t="inlineStr"/>
       <c r="AG62" t="b">
         <v>0</v>
       </c>
@@ -6951,7 +6941,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129795191</v>
+        <v>129795195</v>
       </c>
       <c r="B63" t="n">
         <v>8450</v>
@@ -6995,10 +6985,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>444520</v>
+        <v>444487</v>
       </c>
       <c r="R63" t="n">
-        <v>6787287</v>
+        <v>6787441</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7058,7 +7048,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129795177</v>
+        <v>129795191</v>
       </c>
       <c r="B64" t="n">
         <v>8450</v>
@@ -7092,7 +7082,7 @@
       <c r="L64" t="inlineStr"/>
       <c r="M64" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N64" t="inlineStr"/>
@@ -7102,10 +7092,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>444342</v>
+        <v>444520</v>
       </c>
       <c r="R64" t="n">
-        <v>6787223</v>
+        <v>6787287</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7165,40 +7155,41 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129795162</v>
+        <v>129795177</v>
       </c>
       <c r="B65" t="n">
-        <v>57734</v>
+        <v>8450</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
+      <c r="J65" t="inlineStr"/>
       <c r="K65" t="inlineStr"/>
       <c r="L65" t="inlineStr"/>
       <c r="M65" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="N65" t="inlineStr"/>
@@ -7208,10 +7199,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>444428</v>
+        <v>444342</v>
       </c>
       <c r="R65" t="n">
-        <v>6787329</v>
+        <v>6787223</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7252,6 +7243,7 @@
       <c r="AE65" t="b">
         <v>0</v>
       </c>
+      <c r="AF65" t="inlineStr"/>
       <c r="AG65" t="b">
         <v>0</v>
       </c>
@@ -7270,10 +7262,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129795125</v>
+        <v>129795162</v>
       </c>
       <c r="B66" t="n">
-        <v>79703</v>
+        <v>57734</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7281,34 +7273,42 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
+      <c r="K66" t="inlineStr"/>
+      <c r="L66" t="inlineStr"/>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>444329</v>
+        <v>444428</v>
       </c>
       <c r="R66" t="n">
-        <v>6787371</v>
+        <v>6787329</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -8472,10 +8472,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129795126</v>
+        <v>129795307</v>
       </c>
       <c r="B78" t="n">
-        <v>79703</v>
+        <v>79084</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8483,21 +8483,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8507,10 +8507,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>444358</v>
+        <v>444134</v>
       </c>
       <c r="R78" t="n">
-        <v>6787400</v>
+        <v>6787304</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8569,7 +8569,7 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129795300</v>
+        <v>129795286</v>
       </c>
       <c r="B79" t="n">
         <v>79084</v>
@@ -8607,10 +8607,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>444264</v>
+        <v>444440</v>
       </c>
       <c r="R79" t="n">
-        <v>6787349</v>
+        <v>6787388</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8647,7 +8647,7 @@
       </c>
       <c r="AC79" t="inlineStr">
         <is>
-          <t>Garnlav i de flesta träd inom en radie av 50 m.</t>
+          <t>Gott om garnlav inom en radie av 50 m.</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -8675,10 +8675,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129795241</v>
+        <v>129795126</v>
       </c>
       <c r="B80" t="n">
-        <v>79084</v>
+        <v>79703</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8686,21 +8686,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8710,10 +8710,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>444117</v>
+        <v>444358</v>
       </c>
       <c r="R80" t="n">
-        <v>6787277</v>
+        <v>6787400</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8772,10 +8772,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129795127</v>
+        <v>129795300</v>
       </c>
       <c r="B81" t="n">
-        <v>79703</v>
+        <v>79084</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8783,34 +8783,37 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
+      <c r="J81" t="inlineStr"/>
+      <c r="K81" t="inlineStr"/>
+      <c r="N81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>444432</v>
+        <v>444264</v>
       </c>
       <c r="R81" t="n">
-        <v>6787388</v>
+        <v>6787349</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8845,12 +8848,18 @@
           <t>2025-11-22</t>
         </is>
       </c>
+      <c r="AC81" t="inlineStr">
+        <is>
+          <t>Garnlav i de flesta träd inom en radie av 50 m.</t>
+        </is>
+      </c>
       <c r="AD81" t="b">
         <v>0</v>
       </c>
       <c r="AE81" t="b">
         <v>0</v>
       </c>
+      <c r="AF81" t="inlineStr"/>
       <c r="AG81" t="b">
         <v>0</v>
       </c>
@@ -8869,54 +8878,45 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129795173</v>
+        <v>129795241</v>
       </c>
       <c r="B82" t="n">
-        <v>8450</v>
+        <v>79084</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
-      <c r="J82" t="inlineStr"/>
-      <c r="K82" t="inlineStr"/>
-      <c r="L82" t="inlineStr"/>
-      <c r="M82" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>444220</v>
+        <v>444117</v>
       </c>
       <c r="R82" t="n">
-        <v>6787210</v>
+        <v>6787277</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8957,7 +8957,6 @@
       <c r="AE82" t="b">
         <v>0</v>
       </c>
-      <c r="AF82" t="inlineStr"/>
       <c r="AG82" t="b">
         <v>0</v>
       </c>
@@ -8976,54 +8975,45 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129795194</v>
+        <v>129795127</v>
       </c>
       <c r="B83" t="n">
-        <v>8450</v>
+        <v>79703</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
-      <c r="J83" t="inlineStr"/>
-      <c r="K83" t="inlineStr"/>
-      <c r="L83" t="inlineStr"/>
-      <c r="M83" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>444501</v>
+        <v>444432</v>
       </c>
       <c r="R83" t="n">
-        <v>6787363</v>
+        <v>6787388</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9064,7 +9054,6 @@
       <c r="AE83" t="b">
         <v>0</v>
       </c>
-      <c r="AF83" t="inlineStr"/>
       <c r="AG83" t="b">
         <v>0</v>
       </c>
@@ -9083,45 +9072,54 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129795307</v>
+        <v>129795173</v>
       </c>
       <c r="B84" t="n">
-        <v>79084</v>
+        <v>8450</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
+      <c r="J84" t="inlineStr"/>
+      <c r="K84" t="inlineStr"/>
+      <c r="L84" t="inlineStr"/>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>444134</v>
+        <v>444220</v>
       </c>
       <c r="R84" t="n">
-        <v>6787304</v>
+        <v>6787210</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9162,6 +9160,7 @@
       <c r="AE84" t="b">
         <v>0</v>
       </c>
+      <c r="AF84" t="inlineStr"/>
       <c r="AG84" t="b">
         <v>0</v>
       </c>
@@ -9180,37 +9179,43 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129795286</v>
+        <v>129795194</v>
       </c>
       <c r="B85" t="n">
-        <v>79084</v>
+        <v>8450</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
       <c r="J85" t="inlineStr"/>
       <c r="K85" t="inlineStr"/>
+      <c r="L85" t="inlineStr"/>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
@@ -9218,10 +9223,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>444440</v>
+        <v>444501</v>
       </c>
       <c r="R85" t="n">
-        <v>6787388</v>
+        <v>6787363</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9254,11 +9259,6 @@
       <c r="AA85" t="inlineStr">
         <is>
           <t>2025-11-22</t>
-        </is>
-      </c>
-      <c r="AC85" t="inlineStr">
-        <is>
-          <t>Gott om garnlav inom en radie av 50 m.</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9694,10 +9694,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>129795152</v>
+        <v>129795297</v>
       </c>
       <c r="B90" t="n">
-        <v>57734</v>
+        <v>79084</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9705,42 +9705,34 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
-      <c r="K90" t="inlineStr"/>
-      <c r="L90" t="inlineStr"/>
-      <c r="M90" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>444434</v>
+        <v>444297</v>
       </c>
       <c r="R90" t="n">
-        <v>6787304</v>
+        <v>6787333</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9799,10 +9791,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>129795121</v>
+        <v>129795262</v>
       </c>
       <c r="B91" t="n">
-        <v>79703</v>
+        <v>79084</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9810,21 +9802,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -9834,10 +9826,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>444254</v>
+        <v>444219</v>
       </c>
       <c r="R91" t="n">
-        <v>6787204</v>
+        <v>6787163</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9896,10 +9888,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>129795252</v>
+        <v>129795152</v>
       </c>
       <c r="B92" t="n">
-        <v>79084</v>
+        <v>57734</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9907,34 +9899,42 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
+      <c r="K92" t="inlineStr"/>
+      <c r="L92" t="inlineStr"/>
+      <c r="M92" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>444249</v>
+        <v>444434</v>
       </c>
       <c r="R92" t="n">
-        <v>6787249</v>
+        <v>6787304</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9967,11 +9967,6 @@
       <c r="AA92" t="inlineStr">
         <is>
           <t>2025-11-22</t>
-        </is>
-      </c>
-      <c r="AC92" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 40m.</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -9998,10 +9993,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>129795245</v>
+        <v>129795121</v>
       </c>
       <c r="B93" t="n">
-        <v>79084</v>
+        <v>79703</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10009,21 +10004,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -10033,10 +10028,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>444113</v>
+        <v>444254</v>
       </c>
       <c r="R93" t="n">
-        <v>6787239</v>
+        <v>6787204</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10095,10 +10090,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>129795123</v>
+        <v>129795252</v>
       </c>
       <c r="B94" t="n">
-        <v>79703</v>
+        <v>79084</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10106,21 +10101,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -10130,10 +10125,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>444530</v>
+        <v>444249</v>
       </c>
       <c r="R94" t="n">
-        <v>6787326</v>
+        <v>6787249</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10166,6 +10161,11 @@
       <c r="AA94" t="inlineStr">
         <is>
           <t>2025-11-22</t>
+        </is>
+      </c>
+      <c r="AC94" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 40m.</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10192,7 +10192,7 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>129795288</v>
+        <v>129795245</v>
       </c>
       <c r="B95" t="n">
         <v>79084</v>
@@ -10227,10 +10227,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>444420</v>
+        <v>444113</v>
       </c>
       <c r="R95" t="n">
-        <v>6787366</v>
+        <v>6787239</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10289,10 +10289,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>129795305</v>
+        <v>129795123</v>
       </c>
       <c r="B96" t="n">
-        <v>79084</v>
+        <v>79703</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10300,21 +10300,21 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10324,10 +10324,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>444169</v>
+        <v>444530</v>
       </c>
       <c r="R96" t="n">
-        <v>6787323</v>
+        <v>6787326</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10386,10 +10386,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>129795124</v>
+        <v>129795288</v>
       </c>
       <c r="B97" t="n">
-        <v>79703</v>
+        <v>79084</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10397,21 +10397,21 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -10421,10 +10421,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>444393</v>
+        <v>444420</v>
       </c>
       <c r="R97" t="n">
-        <v>6787395</v>
+        <v>6787366</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10483,54 +10483,45 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>129795167</v>
+        <v>129795305</v>
       </c>
       <c r="B98" t="n">
-        <v>8450</v>
+        <v>79084</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
-      <c r="J98" t="inlineStr"/>
-      <c r="K98" t="inlineStr"/>
-      <c r="L98" t="inlineStr"/>
-      <c r="M98" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>444132</v>
+        <v>444169</v>
       </c>
       <c r="R98" t="n">
-        <v>6787237</v>
+        <v>6787323</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10571,7 +10562,6 @@
       <c r="AE98" t="b">
         <v>0</v>
       </c>
-      <c r="AF98" t="inlineStr"/>
       <c r="AG98" t="b">
         <v>0</v>
       </c>
@@ -10590,10 +10580,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>129795297</v>
+        <v>129795124</v>
       </c>
       <c r="B99" t="n">
-        <v>79084</v>
+        <v>79703</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10601,21 +10591,21 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -10625,10 +10615,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>444297</v>
+        <v>444393</v>
       </c>
       <c r="R99" t="n">
-        <v>6787333</v>
+        <v>6787395</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10687,45 +10677,54 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>129795262</v>
+        <v>129795167</v>
       </c>
       <c r="B100" t="n">
-        <v>79084</v>
+        <v>8450</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
+      <c r="J100" t="inlineStr"/>
+      <c r="K100" t="inlineStr"/>
+      <c r="L100" t="inlineStr"/>
+      <c r="M100" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>444219</v>
+        <v>444132</v>
       </c>
       <c r="R100" t="n">
-        <v>6787163</v>
+        <v>6787237</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10766,6 +10765,7 @@
       <c r="AE100" t="b">
         <v>0</v>
       </c>
+      <c r="AF100" t="inlineStr"/>
       <c r="AG100" t="b">
         <v>0</v>
       </c>
@@ -12333,10 +12333,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>129795171</v>
+        <v>129795132</v>
       </c>
       <c r="B116" t="n">
-        <v>8450</v>
+        <v>56927</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -12344,30 +12344,29 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>106545</v>
+        <v>100138</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
-      <c r="J116" t="inlineStr"/>
       <c r="K116" t="inlineStr"/>
       <c r="L116" t="inlineStr"/>
       <c r="M116" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="N116" t="inlineStr"/>
@@ -12377,10 +12376,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>444185</v>
+        <v>444315</v>
       </c>
       <c r="R116" t="n">
-        <v>6787226</v>
+        <v>6787291</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12421,7 +12420,6 @@
       <c r="AE116" t="b">
         <v>0</v>
       </c>
-      <c r="AF116" t="inlineStr"/>
       <c r="AG116" t="b">
         <v>0</v>
       </c>
@@ -12440,32 +12438,32 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>129795132</v>
+        <v>129795154</v>
       </c>
       <c r="B117" t="n">
-        <v>56927</v>
+        <v>57734</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -12473,7 +12471,7 @@
       <c r="L117" t="inlineStr"/>
       <c r="M117" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N117" t="inlineStr"/>
@@ -12483,10 +12481,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>444315</v>
+        <v>444457</v>
       </c>
       <c r="R117" t="n">
-        <v>6787291</v>
+        <v>6787303</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12545,7 +12543,7 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>129795154</v>
+        <v>129795157</v>
       </c>
       <c r="B118" t="n">
         <v>57734</v>
@@ -12588,10 +12586,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>444457</v>
+        <v>444525</v>
       </c>
       <c r="R118" t="n">
-        <v>6787303</v>
+        <v>6787344</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12650,7 +12648,7 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>129795157</v>
+        <v>129795164</v>
       </c>
       <c r="B119" t="n">
         <v>57734</v>
@@ -12693,10 +12691,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>444525</v>
+        <v>444397</v>
       </c>
       <c r="R119" t="n">
-        <v>6787344</v>
+        <v>6787300</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -12755,10 +12753,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>129795164</v>
+        <v>129795289</v>
       </c>
       <c r="B120" t="n">
-        <v>57734</v>
+        <v>79084</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -12766,42 +12764,34 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
-      <c r="K120" t="inlineStr"/>
-      <c r="L120" t="inlineStr"/>
-      <c r="M120" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N120" t="inlineStr"/>
       <c r="P120" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>444397</v>
+        <v>444435</v>
       </c>
       <c r="R120" t="n">
-        <v>6787300</v>
+        <v>6787341</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -12860,45 +12850,54 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>129795289</v>
+        <v>129795171</v>
       </c>
       <c r="B121" t="n">
-        <v>79084</v>
+        <v>8450</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
+      <c r="J121" t="inlineStr"/>
+      <c r="K121" t="inlineStr"/>
+      <c r="L121" t="inlineStr"/>
+      <c r="M121" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N121" t="inlineStr"/>
       <c r="P121" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>444435</v>
+        <v>444185</v>
       </c>
       <c r="R121" t="n">
-        <v>6787341</v>
+        <v>6787226</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -12939,6 +12938,7 @@
       <c r="AE121" t="b">
         <v>0</v>
       </c>
+      <c r="AF121" t="inlineStr"/>
       <c r="AG121" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 51041-2025 artfynd.xlsx
+++ b/artfynd/A 51041-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129795253</v>
       </c>
       <c r="B2" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>129795291</v>
       </c>
       <c r="B3" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -874,10 +874,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129795285</v>
+        <v>129795298</v>
       </c>
       <c r="B4" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -909,10 +909,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>444405</v>
+        <v>444305</v>
       </c>
       <c r="R4" t="n">
-        <v>6787405</v>
+        <v>6787353</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -971,10 +971,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129795261</v>
+        <v>129795285</v>
       </c>
       <c r="B5" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1006,10 +1006,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>444193</v>
+        <v>444405</v>
       </c>
       <c r="R5" t="n">
-        <v>6787130</v>
+        <v>6787405</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1068,54 +1068,45 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129795197</v>
+        <v>129795244</v>
       </c>
       <c r="B6" t="n">
-        <v>8450</v>
+        <v>79087</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>444406</v>
+        <v>444105</v>
       </c>
       <c r="R6" t="n">
-        <v>6787392</v>
+        <v>6787246</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1156,7 +1147,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1175,54 +1165,45 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129795169</v>
+        <v>129795261</v>
       </c>
       <c r="B7" t="n">
-        <v>8450</v>
+        <v>79087</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>444272</v>
+        <v>444193</v>
       </c>
       <c r="R7" t="n">
-        <v>6787239</v>
+        <v>6787130</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1263,7 +1244,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1282,43 +1262,37 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129795190</v>
+        <v>129795283</v>
       </c>
       <c r="B8" t="n">
-        <v>8450</v>
+        <v>79087</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1326,10 +1300,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>444510</v>
+        <v>444337</v>
       </c>
       <c r="R8" t="n">
-        <v>6787276</v>
+        <v>6787374</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1389,37 +1363,43 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129795283</v>
+        <v>129795169</v>
       </c>
       <c r="B9" t="n">
-        <v>79084</v>
+        <v>8451</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1427,10 +1407,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>444337</v>
+        <v>444272</v>
       </c>
       <c r="R9" t="n">
-        <v>6787374</v>
+        <v>6787239</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1490,45 +1470,54 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129795244</v>
+        <v>129795190</v>
       </c>
       <c r="B10" t="n">
-        <v>79084</v>
+        <v>8451</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>444105</v>
+        <v>444510</v>
       </c>
       <c r="R10" t="n">
-        <v>6787246</v>
+        <v>6787276</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1569,6 +1558,7 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1587,45 +1577,54 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129795298</v>
+        <v>129795197</v>
       </c>
       <c r="B11" t="n">
-        <v>79084</v>
+        <v>8451</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>444305</v>
+        <v>444406</v>
       </c>
       <c r="R11" t="n">
-        <v>6787353</v>
+        <v>6787392</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1666,6 +1665,7 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1684,37 +1684,43 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129795271</v>
+        <v>129795174</v>
       </c>
       <c r="B12" t="n">
-        <v>79084</v>
+        <v>8451</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1722,10 +1728,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>444466</v>
+        <v>444166</v>
       </c>
       <c r="R12" t="n">
-        <v>6787306</v>
+        <v>6787161</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1758,11 +1764,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-11-22</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 50m.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1790,37 +1791,43 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129795276</v>
+        <v>129795205</v>
       </c>
       <c r="B13" t="n">
-        <v>79084</v>
+        <v>8451</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1828,10 +1835,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>444499</v>
+        <v>444343</v>
       </c>
       <c r="R13" t="n">
-        <v>6787367</v>
+        <v>6787310</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1864,11 +1871,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-11-22</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 50m.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1896,10 +1898,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129795299</v>
+        <v>129795155</v>
       </c>
       <c r="B14" t="n">
-        <v>79084</v>
+        <v>57737</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1907,34 +1909,42 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>444265</v>
+        <v>444498</v>
       </c>
       <c r="R14" t="n">
-        <v>6787372</v>
+        <v>6787306</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1993,10 +2003,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129795155</v>
+        <v>129795163</v>
       </c>
       <c r="B15" t="n">
-        <v>57734</v>
+        <v>57737</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2036,10 +2046,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>444498</v>
+        <v>444415</v>
       </c>
       <c r="R15" t="n">
-        <v>6787306</v>
+        <v>6787316</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2098,10 +2108,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129795163</v>
+        <v>129795153</v>
       </c>
       <c r="B16" t="n">
-        <v>57734</v>
+        <v>57737</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2131,7 +2141,7 @@
       <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N16" t="inlineStr"/>
@@ -2141,10 +2151,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>444415</v>
+        <v>444452</v>
       </c>
       <c r="R16" t="n">
-        <v>6787316</v>
+        <v>6787294</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2203,10 +2213,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129795153</v>
+        <v>129795281</v>
       </c>
       <c r="B17" t="n">
-        <v>57734</v>
+        <v>79087</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2214,31 +2224,26 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2246,10 +2251,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>444452</v>
+        <v>444408</v>
       </c>
       <c r="R17" t="n">
-        <v>6787294</v>
+        <v>6787452</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2290,6 +2295,7 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2308,10 +2314,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129795281</v>
+        <v>129795271</v>
       </c>
       <c r="B18" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2346,10 +2352,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>444408</v>
+        <v>444466</v>
       </c>
       <c r="R18" t="n">
-        <v>6787452</v>
+        <v>6787306</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2382,6 +2388,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-11-22</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 50m.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2409,43 +2420,37 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129795174</v>
+        <v>129795276</v>
       </c>
       <c r="B19" t="n">
-        <v>8450</v>
+        <v>79087</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2453,10 +2458,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>444166</v>
+        <v>444499</v>
       </c>
       <c r="R19" t="n">
-        <v>6787161</v>
+        <v>6787367</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2489,6 +2494,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-11-22</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 50m.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2516,54 +2526,45 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129795205</v>
+        <v>129795299</v>
       </c>
       <c r="B20" t="n">
-        <v>8450</v>
+        <v>79087</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>444343</v>
+        <v>444265</v>
       </c>
       <c r="R20" t="n">
-        <v>6787310</v>
+        <v>6787372</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2604,7 +2605,6 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2623,10 +2623,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129795310</v>
+        <v>129795273</v>
       </c>
       <c r="B21" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2652,19 +2652,16 @@
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>444488</v>
+        <v>444548</v>
       </c>
       <c r="R21" t="n">
-        <v>6787445</v>
+        <v>6787330</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2699,18 +2696,12 @@
           <t>2025-11-22</t>
         </is>
       </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Gott om garnlav inom en radie av 40m</t>
-        </is>
-      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -2732,7 +2723,7 @@
         <v>129795265</v>
       </c>
       <c r="B22" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2826,10 +2817,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129795278</v>
+        <v>129795310</v>
       </c>
       <c r="B23" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2855,16 +2846,19 @@
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>444465</v>
+        <v>444488</v>
       </c>
       <c r="R23" t="n">
-        <v>6787451</v>
+        <v>6787445</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2899,12 +2893,18 @@
           <t>2025-11-22</t>
         </is>
       </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Gott om garnlav inom en radie av 40m</t>
+        </is>
+      </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -2923,10 +2923,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129795273</v>
+        <v>129795278</v>
       </c>
       <c r="B24" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2958,10 +2958,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>444548</v>
+        <v>444465</v>
       </c>
       <c r="R24" t="n">
-        <v>6787330</v>
+        <v>6787451</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3020,10 +3020,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129795200</v>
+        <v>129795198</v>
       </c>
       <c r="B25" t="n">
-        <v>8450</v>
+        <v>8451</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3064,10 +3064,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>444429</v>
+        <v>444434</v>
       </c>
       <c r="R25" t="n">
-        <v>6787341</v>
+        <v>6787384</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3127,10 +3127,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129795198</v>
+        <v>129795207</v>
       </c>
       <c r="B26" t="n">
-        <v>8450</v>
+        <v>8451</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3171,10 +3171,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>444434</v>
+        <v>444221</v>
       </c>
       <c r="R26" t="n">
-        <v>6787384</v>
+        <v>6787340</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3234,10 +3234,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129795207</v>
+        <v>129795200</v>
       </c>
       <c r="B27" t="n">
-        <v>8450</v>
+        <v>8451</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3278,10 +3278,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>444221</v>
+        <v>444429</v>
       </c>
       <c r="R27" t="n">
-        <v>6787340</v>
+        <v>6787341</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3344,7 +3344,7 @@
         <v>129795206</v>
       </c>
       <c r="B28" t="n">
-        <v>8450</v>
+        <v>8451</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3448,10 +3448,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129795142</v>
+        <v>129795268</v>
       </c>
       <c r="B29" t="n">
-        <v>57734</v>
+        <v>79087</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3459,42 +3459,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>444276</v>
+        <v>444383</v>
       </c>
       <c r="R29" t="n">
-        <v>6787287</v>
+        <v>6787218</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3553,10 +3545,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129795268</v>
+        <v>129795256</v>
       </c>
       <c r="B30" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3588,10 +3580,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>444383</v>
+        <v>444226</v>
       </c>
       <c r="R30" t="n">
-        <v>6787218</v>
+        <v>6787196</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3650,45 +3642,54 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129795256</v>
+        <v>129795187</v>
       </c>
       <c r="B31" t="n">
-        <v>79084</v>
+        <v>8451</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>444226</v>
+        <v>444487</v>
       </c>
       <c r="R31" t="n">
-        <v>6787196</v>
+        <v>6787321</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3729,6 +3730,7 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
+      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
@@ -3747,10 +3749,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129795176</v>
+        <v>129795189</v>
       </c>
       <c r="B32" t="n">
-        <v>8450</v>
+        <v>8451</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3781,7 +3783,7 @@
       <c r="L32" t="inlineStr"/>
       <c r="M32" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N32" t="inlineStr"/>
@@ -3791,10 +3793,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>444215</v>
+        <v>444500</v>
       </c>
       <c r="R32" t="n">
-        <v>6787151</v>
+        <v>6787274</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3854,10 +3856,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129795189</v>
+        <v>129795176</v>
       </c>
       <c r="B33" t="n">
-        <v>8450</v>
+        <v>8451</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3888,7 +3890,7 @@
       <c r="L33" t="inlineStr"/>
       <c r="M33" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="N33" t="inlineStr"/>
@@ -3898,10 +3900,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>444500</v>
+        <v>444215</v>
       </c>
       <c r="R33" t="n">
-        <v>6787274</v>
+        <v>6787151</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3961,41 +3963,40 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129795187</v>
+        <v>129795142</v>
       </c>
       <c r="B34" t="n">
-        <v>8450</v>
+        <v>57737</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N34" t="inlineStr"/>
@@ -4005,10 +4006,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>444487</v>
+        <v>444276</v>
       </c>
       <c r="R34" t="n">
-        <v>6787321</v>
+        <v>6787287</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4049,7 +4050,6 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
-      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
@@ -4068,10 +4068,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129795270</v>
+        <v>129795133</v>
       </c>
       <c r="B35" t="n">
-        <v>79084</v>
+        <v>57898</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4079,34 +4079,42 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>444416</v>
+        <v>444226</v>
       </c>
       <c r="R35" t="n">
-        <v>6787260</v>
+        <v>6787236</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4165,40 +4173,41 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129795165</v>
+        <v>129795193</v>
       </c>
       <c r="B36" t="n">
-        <v>57734</v>
+        <v>8451</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr"/>
       <c r="L36" t="inlineStr"/>
       <c r="M36" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N36" t="inlineStr"/>
@@ -4208,10 +4217,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>444251</v>
+        <v>444508</v>
       </c>
       <c r="R36" t="n">
-        <v>6787376</v>
+        <v>6787352</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4252,6 +4261,7 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
+      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
@@ -4270,45 +4280,54 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129795269</v>
+        <v>129795202</v>
       </c>
       <c r="B37" t="n">
-        <v>79084</v>
+        <v>8451</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>444429</v>
+        <v>444413</v>
       </c>
       <c r="R37" t="n">
-        <v>6787240</v>
+        <v>6787314</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4349,6 +4368,7 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
+      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -4367,10 +4387,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129795249</v>
+        <v>129795165</v>
       </c>
       <c r="B38" t="n">
-        <v>79084</v>
+        <v>57737</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4378,34 +4398,42 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>444267</v>
+        <v>444251</v>
       </c>
       <c r="R38" t="n">
-        <v>6787295</v>
+        <v>6787376</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4464,10 +4492,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129795296</v>
+        <v>129795270</v>
       </c>
       <c r="B39" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4493,19 +4521,16 @@
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
-      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>444299</v>
+        <v>444416</v>
       </c>
       <c r="R39" t="n">
-        <v>6787304</v>
+        <v>6787260</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4540,18 +4565,12 @@
           <t>2025-11-22</t>
         </is>
       </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 50 m.</t>
-        </is>
-      </c>
       <c r="AD39" t="b">
         <v>0</v>
       </c>
       <c r="AE39" t="b">
         <v>0</v>
       </c>
-      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -4570,10 +4589,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129795133</v>
+        <v>129795296</v>
       </c>
       <c r="B40" t="n">
-        <v>57895</v>
+        <v>79087</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4581,31 +4600,26 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
@@ -4613,10 +4627,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>444226</v>
+        <v>444299</v>
       </c>
       <c r="R40" t="n">
-        <v>6787236</v>
+        <v>6787304</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4651,12 +4665,18 @@
           <t>2025-11-22</t>
         </is>
       </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 50 m.</t>
+        </is>
+      </c>
       <c r="AD40" t="b">
         <v>0</v>
       </c>
       <c r="AE40" t="b">
         <v>0</v>
       </c>
+      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
@@ -4675,54 +4695,45 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129795202</v>
+        <v>129795269</v>
       </c>
       <c r="B41" t="n">
-        <v>8450</v>
+        <v>79087</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr"/>
-      <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>444413</v>
+        <v>444429</v>
       </c>
       <c r="R41" t="n">
-        <v>6787314</v>
+        <v>6787240</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4763,7 +4774,6 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
-      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
@@ -4782,54 +4792,45 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129795193</v>
+        <v>129795249</v>
       </c>
       <c r="B42" t="n">
-        <v>8450</v>
+        <v>79087</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="J42" t="inlineStr"/>
-      <c r="K42" t="inlineStr"/>
-      <c r="L42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>444508</v>
+        <v>444267</v>
       </c>
       <c r="R42" t="n">
-        <v>6787352</v>
+        <v>6787295</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4870,7 +4871,6 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
-      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
@@ -4889,10 +4889,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129795136</v>
+        <v>129795158</v>
       </c>
       <c r="B43" t="n">
-        <v>91623</v>
+        <v>57737</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4900,26 +4900,31 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>5442</v>
+        <v>100049</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="J43" t="inlineStr"/>
       <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
@@ -4927,10 +4932,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>444235</v>
+        <v>444501</v>
       </c>
       <c r="R43" t="n">
-        <v>6787149</v>
+        <v>6787402</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4971,7 +4976,6 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
-      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
@@ -4990,10 +4994,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129795282</v>
+        <v>129795136</v>
       </c>
       <c r="B44" t="n">
-        <v>79084</v>
+        <v>91626</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5001,21 +5005,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5028,10 +5032,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>444374</v>
+        <v>444235</v>
       </c>
       <c r="R44" t="n">
-        <v>6787384</v>
+        <v>6787149</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5064,11 +5068,6 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-11-22</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 50 m.</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5096,10 +5095,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129795293</v>
+        <v>129795282</v>
       </c>
       <c r="B45" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5125,16 +5124,19 @@
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="J45" t="inlineStr"/>
+      <c r="K45" t="inlineStr"/>
+      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>444365</v>
+        <v>444374</v>
       </c>
       <c r="R45" t="n">
-        <v>6787285</v>
+        <v>6787384</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5171,7 +5173,7 @@
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>Rikligt med garnlav inom en radie av 50m.</t>
+          <t>Rikligt med garnlav inom en radie av 50 m.</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5180,6 +5182,7 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
+      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
@@ -5198,10 +5201,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129795158</v>
+        <v>129795293</v>
       </c>
       <c r="B46" t="n">
-        <v>57734</v>
+        <v>79087</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5209,42 +5212,34 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="K46" t="inlineStr"/>
-      <c r="L46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>444501</v>
+        <v>444365</v>
       </c>
       <c r="R46" t="n">
-        <v>6787402</v>
+        <v>6787285</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5277,6 +5272,11 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-11-22</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 50m.</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5306,7 +5306,7 @@
         <v>129795170</v>
       </c>
       <c r="B47" t="n">
-        <v>8450</v>
+        <v>8451</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5410,10 +5410,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129795246</v>
+        <v>129795138</v>
       </c>
       <c r="B48" t="n">
-        <v>79084</v>
+        <v>91626</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5421,34 +5421,37 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="J48" t="inlineStr"/>
+      <c r="K48" t="inlineStr"/>
+      <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>444145</v>
+        <v>444250</v>
       </c>
       <c r="R48" t="n">
-        <v>6787239</v>
+        <v>6787196</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5483,17 +5486,13 @@
           <t>2025-11-22</t>
         </is>
       </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 40m.</t>
-        </is>
-      </c>
       <c r="AD48" t="b">
         <v>0</v>
       </c>
       <c r="AE48" t="b">
         <v>0</v>
       </c>
+      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
@@ -5512,10 +5511,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129795250</v>
+        <v>129795309</v>
       </c>
       <c r="B49" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5547,10 +5546,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>444295</v>
+        <v>444095</v>
       </c>
       <c r="R49" t="n">
-        <v>6787287</v>
+        <v>6787293</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5583,6 +5582,11 @@
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-11-22</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>8.32</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5609,10 +5613,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129795138</v>
+        <v>129795260</v>
       </c>
       <c r="B50" t="n">
-        <v>91623</v>
+        <v>79087</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5620,37 +5624,34 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="J50" t="inlineStr"/>
-      <c r="K50" t="inlineStr"/>
-      <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>444250</v>
+        <v>444197</v>
       </c>
       <c r="R50" t="n">
-        <v>6787196</v>
+        <v>6787111</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5691,7 +5692,6 @@
       <c r="AE50" t="b">
         <v>0</v>
       </c>
-      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>
@@ -5710,10 +5710,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129795309</v>
+        <v>129795250</v>
       </c>
       <c r="B51" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5745,10 +5745,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>444095</v>
+        <v>444295</v>
       </c>
       <c r="R51" t="n">
-        <v>6787293</v>
+        <v>6787287</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5781,11 +5781,6 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-11-22</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>8.32</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5812,10 +5807,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129795260</v>
+        <v>129795246</v>
       </c>
       <c r="B52" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5847,10 +5842,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>444197</v>
+        <v>444145</v>
       </c>
       <c r="R52" t="n">
-        <v>6787111</v>
+        <v>6787239</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5883,6 +5878,11 @@
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-11-22</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 40m.</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -5909,10 +5909,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129795161</v>
+        <v>129795277</v>
       </c>
       <c r="B53" t="n">
-        <v>57734</v>
+        <v>79087</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5920,42 +5920,34 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="K53" t="inlineStr"/>
-      <c r="L53" t="inlineStr"/>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>444433</v>
+        <v>444491</v>
       </c>
       <c r="R53" t="n">
-        <v>6787338</v>
+        <v>6787412</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6014,10 +6006,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129795134</v>
+        <v>129795279</v>
       </c>
       <c r="B54" t="n">
-        <v>57895</v>
+        <v>79087</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6025,42 +6017,34 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
-      <c r="K54" t="inlineStr"/>
-      <c r="L54" t="inlineStr"/>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>444289</v>
+        <v>444463</v>
       </c>
       <c r="R54" t="n">
-        <v>6787357</v>
+        <v>6787459</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6119,10 +6103,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129795172</v>
+        <v>129795131</v>
       </c>
       <c r="B55" t="n">
-        <v>8450</v>
+        <v>56930</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6130,30 +6114,29 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>106545</v>
+        <v>100138</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
-      <c r="J55" t="inlineStr"/>
       <c r="K55" t="inlineStr"/>
       <c r="L55" t="inlineStr"/>
       <c r="M55" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="N55" t="inlineStr"/>
@@ -6163,10 +6146,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>444225</v>
+        <v>444250</v>
       </c>
       <c r="R55" t="n">
-        <v>6787223</v>
+        <v>6787212</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6207,7 +6190,6 @@
       <c r="AE55" t="b">
         <v>0</v>
       </c>
-      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
@@ -6226,41 +6208,40 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129795199</v>
+        <v>129795161</v>
       </c>
       <c r="B56" t="n">
-        <v>8450</v>
+        <v>57737</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
-      <c r="J56" t="inlineStr"/>
       <c r="K56" t="inlineStr"/>
       <c r="L56" t="inlineStr"/>
       <c r="M56" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N56" t="inlineStr"/>
@@ -6270,10 +6251,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>444431</v>
+        <v>444433</v>
       </c>
       <c r="R56" t="n">
-        <v>6787350</v>
+        <v>6787338</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6314,7 +6295,6 @@
       <c r="AE56" t="b">
         <v>0</v>
       </c>
-      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
       </c>
@@ -6333,32 +6313,32 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129795131</v>
+        <v>129795147</v>
       </c>
       <c r="B57" t="n">
-        <v>56927</v>
+        <v>57737</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6366,7 +6346,7 @@
       <c r="L57" t="inlineStr"/>
       <c r="M57" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N57" t="inlineStr"/>
@@ -6376,10 +6356,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>444250</v>
+        <v>444220</v>
       </c>
       <c r="R57" t="n">
-        <v>6787212</v>
+        <v>6787221</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6438,10 +6418,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129795277</v>
+        <v>129795134</v>
       </c>
       <c r="B58" t="n">
-        <v>79084</v>
+        <v>57898</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6449,34 +6429,42 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
+      <c r="K58" t="inlineStr"/>
+      <c r="L58" t="inlineStr"/>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>444491</v>
+        <v>444289</v>
       </c>
       <c r="R58" t="n">
-        <v>6787412</v>
+        <v>6787357</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6535,45 +6523,54 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129795279</v>
+        <v>129795184</v>
       </c>
       <c r="B59" t="n">
-        <v>79084</v>
+        <v>8451</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
+      <c r="J59" t="inlineStr"/>
+      <c r="K59" t="inlineStr"/>
+      <c r="L59" t="inlineStr"/>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>444463</v>
+        <v>444452</v>
       </c>
       <c r="R59" t="n">
-        <v>6787459</v>
+        <v>6787305</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6614,6 +6611,7 @@
       <c r="AE59" t="b">
         <v>0</v>
       </c>
+      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
       </c>
@@ -6632,40 +6630,41 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129795147</v>
+        <v>129795172</v>
       </c>
       <c r="B60" t="n">
-        <v>57734</v>
+        <v>8451</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
+      <c r="J60" t="inlineStr"/>
       <c r="K60" t="inlineStr"/>
       <c r="L60" t="inlineStr"/>
       <c r="M60" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N60" t="inlineStr"/>
@@ -6675,10 +6674,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>444220</v>
+        <v>444225</v>
       </c>
       <c r="R60" t="n">
-        <v>6787221</v>
+        <v>6787223</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6719,6 +6718,7 @@
       <c r="AE60" t="b">
         <v>0</v>
       </c>
+      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
       </c>
@@ -6737,10 +6737,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129795184</v>
+        <v>129795199</v>
       </c>
       <c r="B61" t="n">
-        <v>8450</v>
+        <v>8451</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6781,10 +6781,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>444452</v>
+        <v>444431</v>
       </c>
       <c r="R61" t="n">
-        <v>6787305</v>
+        <v>6787350</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6847,7 +6847,7 @@
         <v>129795125</v>
       </c>
       <c r="B62" t="n">
-        <v>79703</v>
+        <v>79706</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6941,41 +6941,40 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129795195</v>
+        <v>129795162</v>
       </c>
       <c r="B63" t="n">
-        <v>8450</v>
+        <v>57737</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
-      <c r="J63" t="inlineStr"/>
       <c r="K63" t="inlineStr"/>
       <c r="L63" t="inlineStr"/>
       <c r="M63" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N63" t="inlineStr"/>
@@ -6985,10 +6984,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>444487</v>
+        <v>444428</v>
       </c>
       <c r="R63" t="n">
-        <v>6787441</v>
+        <v>6787329</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7029,7 +7028,6 @@
       <c r="AE63" t="b">
         <v>0</v>
       </c>
-      <c r="AF63" t="inlineStr"/>
       <c r="AG63" t="b">
         <v>0</v>
       </c>
@@ -7051,7 +7049,7 @@
         <v>129795191</v>
       </c>
       <c r="B64" t="n">
-        <v>8450</v>
+        <v>8451</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7155,10 +7153,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129795177</v>
+        <v>129795195</v>
       </c>
       <c r="B65" t="n">
-        <v>8450</v>
+        <v>8451</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7189,7 +7187,7 @@
       <c r="L65" t="inlineStr"/>
       <c r="M65" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N65" t="inlineStr"/>
@@ -7199,10 +7197,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>444342</v>
+        <v>444487</v>
       </c>
       <c r="R65" t="n">
-        <v>6787223</v>
+        <v>6787441</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7262,40 +7260,41 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129795162</v>
+        <v>129795177</v>
       </c>
       <c r="B66" t="n">
-        <v>57734</v>
+        <v>8451</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
+      <c r="J66" t="inlineStr"/>
       <c r="K66" t="inlineStr"/>
       <c r="L66" t="inlineStr"/>
       <c r="M66" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="N66" t="inlineStr"/>
@@ -7305,10 +7304,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>444428</v>
+        <v>444342</v>
       </c>
       <c r="R66" t="n">
-        <v>6787329</v>
+        <v>6787223</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7349,6 +7348,7 @@
       <c r="AE66" t="b">
         <v>0</v>
       </c>
+      <c r="AF66" t="inlineStr"/>
       <c r="AG66" t="b">
         <v>0</v>
       </c>
@@ -7370,7 +7370,7 @@
         <v>129795150</v>
       </c>
       <c r="B67" t="n">
-        <v>57734</v>
+        <v>57737</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7475,7 +7475,7 @@
         <v>129795257</v>
       </c>
       <c r="B68" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7569,45 +7569,53 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129795243</v>
+        <v>129795208</v>
       </c>
       <c r="B69" t="n">
-        <v>79084</v>
+        <v>58111</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6425</v>
+        <v>103015</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
+      <c r="K69" t="inlineStr"/>
+      <c r="L69" t="inlineStr"/>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>444159</v>
+        <v>444434</v>
       </c>
       <c r="R69" t="n">
-        <v>6787297</v>
+        <v>6787357</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7666,45 +7674,54 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129795280</v>
+        <v>129795182</v>
       </c>
       <c r="B70" t="n">
-        <v>79084</v>
+        <v>8451</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
+      <c r="J70" t="inlineStr"/>
+      <c r="K70" t="inlineStr"/>
+      <c r="L70" t="inlineStr"/>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>444451</v>
+        <v>444417</v>
       </c>
       <c r="R70" t="n">
-        <v>6787467</v>
+        <v>6787266</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7745,6 +7762,7 @@
       <c r="AE70" t="b">
         <v>0</v>
       </c>
+      <c r="AF70" t="inlineStr"/>
       <c r="AG70" t="b">
         <v>0</v>
       </c>
@@ -7763,10 +7781,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129795284</v>
+        <v>129795280</v>
       </c>
       <c r="B71" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7798,10 +7816,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>444363</v>
+        <v>444451</v>
       </c>
       <c r="R71" t="n">
-        <v>6787411</v>
+        <v>6787467</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7860,42 +7878,37 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129795208</v>
+        <v>129795135</v>
       </c>
       <c r="B72" t="n">
-        <v>58108</v>
+        <v>91626</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>103015</v>
+        <v>5442</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
+      <c r="J72" t="inlineStr"/>
       <c r="K72" t="inlineStr"/>
-      <c r="L72" t="inlineStr"/>
-      <c r="M72" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
@@ -7903,10 +7916,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>444434</v>
+        <v>444158</v>
       </c>
       <c r="R72" t="n">
-        <v>6787357</v>
+        <v>6787148</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7947,6 +7960,7 @@
       <c r="AE72" t="b">
         <v>0</v>
       </c>
+      <c r="AF72" t="inlineStr"/>
       <c r="AG72" t="b">
         <v>0</v>
       </c>
@@ -7965,54 +7979,45 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129795182</v>
+        <v>129795272</v>
       </c>
       <c r="B73" t="n">
-        <v>8450</v>
+        <v>79087</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
-      <c r="J73" t="inlineStr"/>
-      <c r="K73" t="inlineStr"/>
-      <c r="L73" t="inlineStr"/>
-      <c r="M73" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>444417</v>
+        <v>444553</v>
       </c>
       <c r="R73" t="n">
-        <v>6787266</v>
+        <v>6787299</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8053,7 +8058,6 @@
       <c r="AE73" t="b">
         <v>0</v>
       </c>
-      <c r="AF73" t="inlineStr"/>
       <c r="AG73" t="b">
         <v>0</v>
       </c>
@@ -8072,10 +8076,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129795166</v>
+        <v>129795287</v>
       </c>
       <c r="B74" t="n">
-        <v>57734</v>
+        <v>79087</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8083,42 +8087,34 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
-      <c r="K74" t="inlineStr"/>
-      <c r="L74" t="inlineStr"/>
-      <c r="M74" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>444254</v>
+        <v>444430</v>
       </c>
       <c r="R74" t="n">
-        <v>6787333</v>
+        <v>6787384</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8177,10 +8173,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129795135</v>
+        <v>129795284</v>
       </c>
       <c r="B75" t="n">
-        <v>91623</v>
+        <v>79087</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8188,37 +8184,34 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
-      <c r="J75" t="inlineStr"/>
-      <c r="K75" t="inlineStr"/>
-      <c r="N75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>444158</v>
+        <v>444363</v>
       </c>
       <c r="R75" t="n">
-        <v>6787148</v>
+        <v>6787411</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8259,7 +8252,6 @@
       <c r="AE75" t="b">
         <v>0</v>
       </c>
-      <c r="AF75" t="inlineStr"/>
       <c r="AG75" t="b">
         <v>0</v>
       </c>
@@ -8278,10 +8270,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129795272</v>
+        <v>129795243</v>
       </c>
       <c r="B76" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8313,10 +8305,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>444553</v>
+        <v>444159</v>
       </c>
       <c r="R76" t="n">
-        <v>6787299</v>
+        <v>6787297</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8375,10 +8367,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129795287</v>
+        <v>129795166</v>
       </c>
       <c r="B77" t="n">
-        <v>79084</v>
+        <v>57737</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8386,34 +8378,42 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
+      <c r="K77" t="inlineStr"/>
+      <c r="L77" t="inlineStr"/>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>444430</v>
+        <v>444254</v>
       </c>
       <c r="R77" t="n">
-        <v>6787384</v>
+        <v>6787333</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8472,10 +8472,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129795307</v>
+        <v>129795126</v>
       </c>
       <c r="B78" t="n">
-        <v>79084</v>
+        <v>79706</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8483,21 +8483,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8507,10 +8507,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>444134</v>
+        <v>444358</v>
       </c>
       <c r="R78" t="n">
-        <v>6787304</v>
+        <v>6787400</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8569,10 +8569,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129795286</v>
+        <v>129795300</v>
       </c>
       <c r="B79" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8607,10 +8607,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>444440</v>
+        <v>444264</v>
       </c>
       <c r="R79" t="n">
-        <v>6787388</v>
+        <v>6787349</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8647,7 +8647,7 @@
       </c>
       <c r="AC79" t="inlineStr">
         <is>
-          <t>Gott om garnlav inom en radie av 50 m.</t>
+          <t>Garnlav i de flesta träd inom en radie av 50 m.</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -8675,10 +8675,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129795126</v>
+        <v>129795307</v>
       </c>
       <c r="B80" t="n">
-        <v>79703</v>
+        <v>79087</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8686,21 +8686,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8710,10 +8710,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>444358</v>
+        <v>444134</v>
       </c>
       <c r="R80" t="n">
-        <v>6787400</v>
+        <v>6787304</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8772,10 +8772,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129795300</v>
+        <v>129795241</v>
       </c>
       <c r="B81" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8801,19 +8801,16 @@
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
-      <c r="J81" t="inlineStr"/>
-      <c r="K81" t="inlineStr"/>
-      <c r="N81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>444264</v>
+        <v>444117</v>
       </c>
       <c r="R81" t="n">
-        <v>6787349</v>
+        <v>6787277</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8848,18 +8845,12 @@
           <t>2025-11-22</t>
         </is>
       </c>
-      <c r="AC81" t="inlineStr">
-        <is>
-          <t>Garnlav i de flesta träd inom en radie av 50 m.</t>
-        </is>
-      </c>
       <c r="AD81" t="b">
         <v>0</v>
       </c>
       <c r="AE81" t="b">
         <v>0</v>
       </c>
-      <c r="AF81" t="inlineStr"/>
       <c r="AG81" t="b">
         <v>0</v>
       </c>
@@ -8878,10 +8869,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129795241</v>
+        <v>129795127</v>
       </c>
       <c r="B82" t="n">
-        <v>79084</v>
+        <v>79706</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8889,21 +8880,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8913,10 +8904,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>444117</v>
+        <v>444432</v>
       </c>
       <c r="R82" t="n">
-        <v>6787277</v>
+        <v>6787388</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8975,10 +8966,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129795127</v>
+        <v>129795286</v>
       </c>
       <c r="B83" t="n">
-        <v>79703</v>
+        <v>79087</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8986,31 +8977,34 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
+      <c r="J83" t="inlineStr"/>
+      <c r="K83" t="inlineStr"/>
+      <c r="N83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>444432</v>
+        <v>444440</v>
       </c>
       <c r="R83" t="n">
         <v>6787388</v>
@@ -9048,12 +9042,18 @@
           <t>2025-11-22</t>
         </is>
       </c>
+      <c r="AC83" t="inlineStr">
+        <is>
+          <t>Gott om garnlav inom en radie av 50 m.</t>
+        </is>
+      </c>
       <c r="AD83" t="b">
         <v>0</v>
       </c>
       <c r="AE83" t="b">
         <v>0</v>
       </c>
+      <c r="AF83" t="inlineStr"/>
       <c r="AG83" t="b">
         <v>0</v>
       </c>
@@ -9072,10 +9072,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129795173</v>
+        <v>129795194</v>
       </c>
       <c r="B84" t="n">
-        <v>8450</v>
+        <v>8451</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9116,10 +9116,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>444220</v>
+        <v>444501</v>
       </c>
       <c r="R84" t="n">
-        <v>6787210</v>
+        <v>6787363</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9179,10 +9179,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129795194</v>
+        <v>129795173</v>
       </c>
       <c r="B85" t="n">
-        <v>8450</v>
+        <v>8451</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9223,10 +9223,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>444501</v>
+        <v>444220</v>
       </c>
       <c r="R85" t="n">
-        <v>6787363</v>
+        <v>6787210</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9286,45 +9286,54 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129795242</v>
+        <v>129795192</v>
       </c>
       <c r="B86" t="n">
-        <v>79084</v>
+        <v>8451</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
+      <c r="J86" t="inlineStr"/>
+      <c r="K86" t="inlineStr"/>
+      <c r="L86" t="inlineStr"/>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>444125</v>
+        <v>444549</v>
       </c>
       <c r="R86" t="n">
-        <v>6787297</v>
+        <v>6787335</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9365,6 +9374,7 @@
       <c r="AE86" t="b">
         <v>0</v>
       </c>
+      <c r="AF86" t="inlineStr"/>
       <c r="AG86" t="b">
         <v>0</v>
       </c>
@@ -9383,45 +9393,54 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129795308</v>
+        <v>129795181</v>
       </c>
       <c r="B87" t="n">
-        <v>79084</v>
+        <v>8451</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
+      <c r="J87" t="inlineStr"/>
+      <c r="K87" t="inlineStr"/>
+      <c r="L87" t="inlineStr"/>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>444098</v>
+        <v>444408</v>
       </c>
       <c r="R87" t="n">
-        <v>6787297</v>
+        <v>6787250</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9462,6 +9481,7 @@
       <c r="AE87" t="b">
         <v>0</v>
       </c>
+      <c r="AF87" t="inlineStr"/>
       <c r="AG87" t="b">
         <v>0</v>
       </c>
@@ -9480,54 +9500,45 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129795181</v>
+        <v>129795308</v>
       </c>
       <c r="B88" t="n">
-        <v>8450</v>
+        <v>79087</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
-      <c r="J88" t="inlineStr"/>
-      <c r="K88" t="inlineStr"/>
-      <c r="L88" t="inlineStr"/>
-      <c r="M88" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>444408</v>
+        <v>444098</v>
       </c>
       <c r="R88" t="n">
-        <v>6787250</v>
+        <v>6787297</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9568,7 +9579,6 @@
       <c r="AE88" t="b">
         <v>0</v>
       </c>
-      <c r="AF88" t="inlineStr"/>
       <c r="AG88" t="b">
         <v>0</v>
       </c>
@@ -9587,54 +9597,45 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>129795192</v>
+        <v>129795242</v>
       </c>
       <c r="B89" t="n">
-        <v>8450</v>
+        <v>79087</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
-      <c r="J89" t="inlineStr"/>
-      <c r="K89" t="inlineStr"/>
-      <c r="L89" t="inlineStr"/>
-      <c r="M89" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>444549</v>
+        <v>444125</v>
       </c>
       <c r="R89" t="n">
-        <v>6787335</v>
+        <v>6787297</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9675,7 +9676,6 @@
       <c r="AE89" t="b">
         <v>0</v>
       </c>
-      <c r="AF89" t="inlineStr"/>
       <c r="AG89" t="b">
         <v>0</v>
       </c>
@@ -9694,10 +9694,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>129795297</v>
+        <v>129795121</v>
       </c>
       <c r="B90" t="n">
-        <v>79084</v>
+        <v>79706</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9705,21 +9705,21 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9729,10 +9729,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>444297</v>
+        <v>444254</v>
       </c>
       <c r="R90" t="n">
-        <v>6787333</v>
+        <v>6787204</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9791,10 +9791,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>129795262</v>
+        <v>129795124</v>
       </c>
       <c r="B91" t="n">
-        <v>79084</v>
+        <v>79706</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9802,21 +9802,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -9826,10 +9826,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>444219</v>
+        <v>444393</v>
       </c>
       <c r="R91" t="n">
-        <v>6787163</v>
+        <v>6787395</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9891,7 +9891,7 @@
         <v>129795152</v>
       </c>
       <c r="B92" t="n">
-        <v>57734</v>
+        <v>57737</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9993,10 +9993,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>129795121</v>
+        <v>129795305</v>
       </c>
       <c r="B93" t="n">
-        <v>79703</v>
+        <v>79087</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10004,21 +10004,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -10028,10 +10028,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>444254</v>
+        <v>444169</v>
       </c>
       <c r="R93" t="n">
-        <v>6787204</v>
+        <v>6787323</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10090,10 +10090,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>129795252</v>
+        <v>129795288</v>
       </c>
       <c r="B94" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10125,10 +10125,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>444249</v>
+        <v>444420</v>
       </c>
       <c r="R94" t="n">
-        <v>6787249</v>
+        <v>6787366</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10161,11 +10161,6 @@
       <c r="AA94" t="inlineStr">
         <is>
           <t>2025-11-22</t>
-        </is>
-      </c>
-      <c r="AC94" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 40m.</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10195,7 +10190,7 @@
         <v>129795245</v>
       </c>
       <c r="B95" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10292,7 +10287,7 @@
         <v>129795123</v>
       </c>
       <c r="B96" t="n">
-        <v>79703</v>
+        <v>79706</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10386,10 +10381,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>129795288</v>
+        <v>129795297</v>
       </c>
       <c r="B97" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10421,10 +10416,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>444420</v>
+        <v>444297</v>
       </c>
       <c r="R97" t="n">
-        <v>6787366</v>
+        <v>6787333</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10483,10 +10478,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>129795305</v>
+        <v>129795262</v>
       </c>
       <c r="B98" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10518,10 +10513,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>444169</v>
+        <v>444219</v>
       </c>
       <c r="R98" t="n">
-        <v>6787323</v>
+        <v>6787163</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10580,10 +10575,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>129795124</v>
+        <v>129795252</v>
       </c>
       <c r="B99" t="n">
-        <v>79703</v>
+        <v>79087</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10591,21 +10586,21 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -10615,10 +10610,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>444393</v>
+        <v>444249</v>
       </c>
       <c r="R99" t="n">
-        <v>6787395</v>
+        <v>6787249</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10651,6 +10646,11 @@
       <c r="AA99" t="inlineStr">
         <is>
           <t>2025-11-22</t>
+        </is>
+      </c>
+      <c r="AC99" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 40m.</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -10680,7 +10680,7 @@
         <v>129795167</v>
       </c>
       <c r="B100" t="n">
-        <v>8450</v>
+        <v>8451</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10784,45 +10784,54 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>129795303</v>
+        <v>129795185</v>
       </c>
       <c r="B101" t="n">
-        <v>79084</v>
+        <v>8451</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
+      <c r="J101" t="inlineStr"/>
+      <c r="K101" t="inlineStr"/>
+      <c r="L101" t="inlineStr"/>
+      <c r="M101" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>444200</v>
+        <v>444458</v>
       </c>
       <c r="R101" t="n">
-        <v>6787331</v>
+        <v>6787304</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10863,6 +10872,7 @@
       <c r="AE101" t="b">
         <v>0</v>
       </c>
+      <c r="AF101" t="inlineStr"/>
       <c r="AG101" t="b">
         <v>0</v>
       </c>
@@ -10881,45 +10891,54 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>129795264</v>
+        <v>129795180</v>
       </c>
       <c r="B102" t="n">
-        <v>79084</v>
+        <v>8451</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
+      <c r="J102" t="inlineStr"/>
+      <c r="K102" t="inlineStr"/>
+      <c r="L102" t="inlineStr"/>
+      <c r="M102" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>444252</v>
+        <v>444409</v>
       </c>
       <c r="R102" t="n">
-        <v>6787160</v>
+        <v>6787219</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -10960,6 +10979,7 @@
       <c r="AE102" t="b">
         <v>0</v>
       </c>
+      <c r="AF102" t="inlineStr"/>
       <c r="AG102" t="b">
         <v>0</v>
       </c>
@@ -10978,45 +10998,54 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>129795248</v>
+        <v>129795178</v>
       </c>
       <c r="B103" t="n">
-        <v>79084</v>
+        <v>8451</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
+      <c r="J103" t="inlineStr"/>
+      <c r="K103" t="inlineStr"/>
+      <c r="L103" t="inlineStr"/>
+      <c r="M103" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N103" t="inlineStr"/>
       <c r="P103" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>444238</v>
+        <v>444375</v>
       </c>
       <c r="R103" t="n">
-        <v>6787281</v>
+        <v>6787207</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11057,6 +11086,7 @@
       <c r="AE103" t="b">
         <v>0</v>
       </c>
+      <c r="AF103" t="inlineStr"/>
       <c r="AG103" t="b">
         <v>0</v>
       </c>
@@ -11075,45 +11105,54 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>129795306</v>
+        <v>129795186</v>
       </c>
       <c r="B104" t="n">
-        <v>79084</v>
+        <v>8451</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
+      <c r="J104" t="inlineStr"/>
+      <c r="K104" t="inlineStr"/>
+      <c r="L104" t="inlineStr"/>
+      <c r="M104" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>444152</v>
+        <v>444473</v>
       </c>
       <c r="R104" t="n">
-        <v>6787313</v>
+        <v>6787334</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11154,6 +11193,7 @@
       <c r="AE104" t="b">
         <v>0</v>
       </c>
+      <c r="AF104" t="inlineStr"/>
       <c r="AG104" t="b">
         <v>0</v>
       </c>
@@ -11172,10 +11212,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>129795185</v>
+        <v>129795196</v>
       </c>
       <c r="B105" t="n">
-        <v>8450</v>
+        <v>8451</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11216,10 +11256,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>444458</v>
+        <v>444346</v>
       </c>
       <c r="R105" t="n">
-        <v>6787304</v>
+        <v>6787369</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11279,54 +11319,45 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>129795186</v>
+        <v>129795264</v>
       </c>
       <c r="B106" t="n">
-        <v>8450</v>
+        <v>79087</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
-      <c r="J106" t="inlineStr"/>
-      <c r="K106" t="inlineStr"/>
-      <c r="L106" t="inlineStr"/>
-      <c r="M106" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>444473</v>
+        <v>444252</v>
       </c>
       <c r="R106" t="n">
-        <v>6787334</v>
+        <v>6787160</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11367,7 +11398,6 @@
       <c r="AE106" t="b">
         <v>0</v>
       </c>
-      <c r="AF106" t="inlineStr"/>
       <c r="AG106" t="b">
         <v>0</v>
       </c>
@@ -11386,54 +11416,45 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>129795196</v>
+        <v>129795248</v>
       </c>
       <c r="B107" t="n">
-        <v>8450</v>
+        <v>79087</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
-      <c r="J107" t="inlineStr"/>
-      <c r="K107" t="inlineStr"/>
-      <c r="L107" t="inlineStr"/>
-      <c r="M107" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>444346</v>
+        <v>444238</v>
       </c>
       <c r="R107" t="n">
-        <v>6787369</v>
+        <v>6787281</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11474,7 +11495,6 @@
       <c r="AE107" t="b">
         <v>0</v>
       </c>
-      <c r="AF107" t="inlineStr"/>
       <c r="AG107" t="b">
         <v>0</v>
       </c>
@@ -11493,54 +11513,45 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>129795178</v>
+        <v>129795303</v>
       </c>
       <c r="B108" t="n">
-        <v>8450</v>
+        <v>79087</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
-      <c r="J108" t="inlineStr"/>
-      <c r="K108" t="inlineStr"/>
-      <c r="L108" t="inlineStr"/>
-      <c r="M108" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>444375</v>
+        <v>444200</v>
       </c>
       <c r="R108" t="n">
-        <v>6787207</v>
+        <v>6787331</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11581,7 +11592,6 @@
       <c r="AE108" t="b">
         <v>0</v>
       </c>
-      <c r="AF108" t="inlineStr"/>
       <c r="AG108" t="b">
         <v>0</v>
       </c>
@@ -11600,54 +11610,45 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>129795180</v>
+        <v>129795306</v>
       </c>
       <c r="B109" t="n">
-        <v>8450</v>
+        <v>79087</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
-      <c r="J109" t="inlineStr"/>
-      <c r="K109" t="inlineStr"/>
-      <c r="L109" t="inlineStr"/>
-      <c r="M109" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>444409</v>
+        <v>444152</v>
       </c>
       <c r="R109" t="n">
-        <v>6787219</v>
+        <v>6787313</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11688,7 +11689,6 @@
       <c r="AE109" t="b">
         <v>0</v>
       </c>
-      <c r="AF109" t="inlineStr"/>
       <c r="AG109" t="b">
         <v>0</v>
       </c>
@@ -11707,41 +11707,40 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>129795203</v>
+        <v>129795149</v>
       </c>
       <c r="B110" t="n">
-        <v>8450</v>
+        <v>57737</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
-      <c r="J110" t="inlineStr"/>
       <c r="K110" t="inlineStr"/>
       <c r="L110" t="inlineStr"/>
       <c r="M110" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N110" t="inlineStr"/>
@@ -11751,10 +11750,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>444401</v>
+        <v>444223</v>
       </c>
       <c r="R110" t="n">
-        <v>6787298</v>
+        <v>6787221</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11795,7 +11794,6 @@
       <c r="AE110" t="b">
         <v>0</v>
       </c>
-      <c r="AF110" t="inlineStr"/>
       <c r="AG110" t="b">
         <v>0</v>
       </c>
@@ -11814,41 +11812,40 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>129795201</v>
+        <v>129795145</v>
       </c>
       <c r="B111" t="n">
-        <v>8450</v>
+        <v>57737</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
-      <c r="J111" t="inlineStr"/>
       <c r="K111" t="inlineStr"/>
       <c r="L111" t="inlineStr"/>
       <c r="M111" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N111" t="inlineStr"/>
@@ -11858,10 +11855,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>444430</v>
+        <v>444228</v>
       </c>
       <c r="R111" t="n">
-        <v>6787332</v>
+        <v>6787226</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -11902,7 +11899,6 @@
       <c r="AE111" t="b">
         <v>0</v>
       </c>
-      <c r="AF111" t="inlineStr"/>
       <c r="AG111" t="b">
         <v>0</v>
       </c>
@@ -11921,10 +11917,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>129795149</v>
+        <v>129795151</v>
       </c>
       <c r="B112" t="n">
-        <v>57734</v>
+        <v>57737</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -11954,7 +11950,7 @@
       <c r="L112" t="inlineStr"/>
       <c r="M112" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N112" t="inlineStr"/>
@@ -11964,10 +11960,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>444223</v>
+        <v>444425</v>
       </c>
       <c r="R112" t="n">
-        <v>6787221</v>
+        <v>6787278</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12026,10 +12022,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>129795145</v>
+        <v>129795259</v>
       </c>
       <c r="B113" t="n">
-        <v>57734</v>
+        <v>79087</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -12037,42 +12033,34 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
-      <c r="K113" t="inlineStr"/>
-      <c r="L113" t="inlineStr"/>
-      <c r="M113" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N113" t="inlineStr"/>
       <c r="P113" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>444228</v>
+        <v>444164</v>
       </c>
       <c r="R113" t="n">
-        <v>6787226</v>
+        <v>6787121</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12131,40 +12119,41 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>129795151</v>
+        <v>129795203</v>
       </c>
       <c r="B114" t="n">
-        <v>57734</v>
+        <v>8451</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
+      <c r="J114" t="inlineStr"/>
       <c r="K114" t="inlineStr"/>
       <c r="L114" t="inlineStr"/>
       <c r="M114" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N114" t="inlineStr"/>
@@ -12174,10 +12163,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>444425</v>
+        <v>444401</v>
       </c>
       <c r="R114" t="n">
-        <v>6787278</v>
+        <v>6787298</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12218,6 +12207,7 @@
       <c r="AE114" t="b">
         <v>0</v>
       </c>
+      <c r="AF114" t="inlineStr"/>
       <c r="AG114" t="b">
         <v>0</v>
       </c>
@@ -12236,45 +12226,54 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>129795259</v>
+        <v>129795201</v>
       </c>
       <c r="B115" t="n">
-        <v>79084</v>
+        <v>8451</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
+      <c r="J115" t="inlineStr"/>
+      <c r="K115" t="inlineStr"/>
+      <c r="L115" t="inlineStr"/>
+      <c r="M115" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N115" t="inlineStr"/>
       <c r="P115" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>444164</v>
+        <v>444430</v>
       </c>
       <c r="R115" t="n">
-        <v>6787121</v>
+        <v>6787332</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12315,6 +12314,7 @@
       <c r="AE115" t="b">
         <v>0</v>
       </c>
+      <c r="AF115" t="inlineStr"/>
       <c r="AG115" t="b">
         <v>0</v>
       </c>
@@ -12333,10 +12333,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>129795132</v>
+        <v>129795171</v>
       </c>
       <c r="B116" t="n">
-        <v>56927</v>
+        <v>8451</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -12344,29 +12344,30 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>100138</v>
+        <v>106545</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
+      <c r="J116" t="inlineStr"/>
       <c r="K116" t="inlineStr"/>
       <c r="L116" t="inlineStr"/>
       <c r="M116" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N116" t="inlineStr"/>
@@ -12376,10 +12377,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>444315</v>
+        <v>444185</v>
       </c>
       <c r="R116" t="n">
-        <v>6787291</v>
+        <v>6787226</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12420,6 +12421,7 @@
       <c r="AE116" t="b">
         <v>0</v>
       </c>
+      <c r="AF116" t="inlineStr"/>
       <c r="AG116" t="b">
         <v>0</v>
       </c>
@@ -12438,10 +12440,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>129795154</v>
+        <v>129795164</v>
       </c>
       <c r="B117" t="n">
-        <v>57734</v>
+        <v>57737</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -12481,10 +12483,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>444457</v>
+        <v>444397</v>
       </c>
       <c r="R117" t="n">
-        <v>6787303</v>
+        <v>6787300</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12543,10 +12545,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>129795157</v>
+        <v>129795154</v>
       </c>
       <c r="B118" t="n">
-        <v>57734</v>
+        <v>57737</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12586,10 +12588,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>444525</v>
+        <v>444457</v>
       </c>
       <c r="R118" t="n">
-        <v>6787344</v>
+        <v>6787303</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12648,10 +12650,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>129795164</v>
+        <v>129795157</v>
       </c>
       <c r="B119" t="n">
-        <v>57734</v>
+        <v>57737</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -12691,10 +12693,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>444397</v>
+        <v>444525</v>
       </c>
       <c r="R119" t="n">
-        <v>6787300</v>
+        <v>6787344</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -12753,45 +12755,53 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>129795289</v>
+        <v>129795132</v>
       </c>
       <c r="B120" t="n">
-        <v>79084</v>
+        <v>56930</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
+      <c r="K120" t="inlineStr"/>
+      <c r="L120" t="inlineStr"/>
+      <c r="M120" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N120" t="inlineStr"/>
       <c r="P120" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>444435</v>
+        <v>444315</v>
       </c>
       <c r="R120" t="n">
-        <v>6787341</v>
+        <v>6787291</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -12850,54 +12860,45 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>129795171</v>
+        <v>129795289</v>
       </c>
       <c r="B121" t="n">
-        <v>8450</v>
+        <v>79087</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
-      <c r="J121" t="inlineStr"/>
-      <c r="K121" t="inlineStr"/>
-      <c r="L121" t="inlineStr"/>
-      <c r="M121" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N121" t="inlineStr"/>
       <c r="P121" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>444185</v>
+        <v>444435</v>
       </c>
       <c r="R121" t="n">
-        <v>6787226</v>
+        <v>6787341</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -12938,7 +12939,6 @@
       <c r="AE121" t="b">
         <v>0</v>
       </c>
-      <c r="AF121" t="inlineStr"/>
       <c r="AG121" t="b">
         <v>0</v>
       </c>
@@ -12960,7 +12960,7 @@
         <v>129795144</v>
       </c>
       <c r="B122" t="n">
-        <v>57734</v>
+        <v>57737</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -13065,7 +13065,7 @@
         <v>129795301</v>
       </c>
       <c r="B123" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -13162,7 +13162,7 @@
         <v>129795294</v>
       </c>
       <c r="B124" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -13256,10 +13256,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>129795179</v>
+        <v>129795188</v>
       </c>
       <c r="B125" t="n">
-        <v>8450</v>
+        <v>8451</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -13300,10 +13300,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>444378</v>
+        <v>444498</v>
       </c>
       <c r="R125" t="n">
-        <v>6787236</v>
+        <v>6787280</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13363,10 +13363,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>129795188</v>
+        <v>129795179</v>
       </c>
       <c r="B126" t="n">
-        <v>8450</v>
+        <v>8451</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -13407,10 +13407,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>444498</v>
+        <v>444378</v>
       </c>
       <c r="R126" t="n">
-        <v>6787280</v>
+        <v>6787236</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -13470,10 +13470,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>129795159</v>
+        <v>129795258</v>
       </c>
       <c r="B127" t="n">
-        <v>57734</v>
+        <v>79087</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -13481,42 +13481,34 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
-      <c r="K127" t="inlineStr"/>
-      <c r="L127" t="inlineStr"/>
-      <c r="M127" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N127" t="inlineStr"/>
       <c r="P127" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>444436</v>
+        <v>444174</v>
       </c>
       <c r="R127" t="n">
-        <v>6787463</v>
+        <v>6787136</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -13575,54 +13567,45 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>129795168</v>
+        <v>129795275</v>
       </c>
       <c r="B128" t="n">
-        <v>8450</v>
+        <v>79087</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
-      <c r="J128" t="inlineStr"/>
-      <c r="K128" t="inlineStr"/>
-      <c r="L128" t="inlineStr"/>
-      <c r="M128" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N128" t="inlineStr"/>
       <c r="P128" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>444272</v>
+        <v>444495</v>
       </c>
       <c r="R128" t="n">
-        <v>6787286</v>
+        <v>6787340</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -13663,7 +13646,6 @@
       <c r="AE128" t="b">
         <v>0</v>
       </c>
-      <c r="AF128" t="inlineStr"/>
       <c r="AG128" t="b">
         <v>0</v>
       </c>
@@ -13682,54 +13664,45 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>129795175</v>
+        <v>129795267</v>
       </c>
       <c r="B129" t="n">
-        <v>8450</v>
+        <v>79087</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
-      <c r="J129" t="inlineStr"/>
-      <c r="K129" t="inlineStr"/>
-      <c r="L129" t="inlineStr"/>
-      <c r="M129" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N129" t="inlineStr"/>
       <c r="P129" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>444182</v>
+        <v>444353</v>
       </c>
       <c r="R129" t="n">
-        <v>6787101</v>
+        <v>6787215</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -13764,13 +13737,17 @@
           <t>2025-11-22</t>
         </is>
       </c>
+      <c r="AC129" t="inlineStr">
+        <is>
+          <t>Gott om garnlav inom en radie av 40m.</t>
+        </is>
+      </c>
       <c r="AD129" t="b">
         <v>0</v>
       </c>
       <c r="AE129" t="b">
         <v>0</v>
       </c>
-      <c r="AF129" t="inlineStr"/>
       <c r="AG129" t="b">
         <v>0</v>
       </c>
@@ -13789,10 +13766,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>129795258</v>
+        <v>129795263</v>
       </c>
       <c r="B130" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -13824,10 +13801,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>444174</v>
+        <v>444241</v>
       </c>
       <c r="R130" t="n">
-        <v>6787136</v>
+        <v>6787149</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -13886,10 +13863,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>129795267</v>
+        <v>129795137</v>
       </c>
       <c r="B131" t="n">
-        <v>79084</v>
+        <v>91626</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -13897,34 +13874,37 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
+      <c r="J131" t="inlineStr"/>
+      <c r="K131" t="inlineStr"/>
+      <c r="N131" t="inlineStr"/>
       <c r="P131" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>444353</v>
+        <v>444203</v>
       </c>
       <c r="R131" t="n">
-        <v>6787215</v>
+        <v>6787221</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -13959,17 +13939,13 @@
           <t>2025-11-22</t>
         </is>
       </c>
-      <c r="AC131" t="inlineStr">
-        <is>
-          <t>Gott om garnlav inom en radie av 40m.</t>
-        </is>
-      </c>
       <c r="AD131" t="b">
         <v>0</v>
       </c>
       <c r="AE131" t="b">
         <v>0</v>
       </c>
+      <c r="AF131" t="inlineStr"/>
       <c r="AG131" t="b">
         <v>0</v>
       </c>
@@ -13988,10 +13964,10 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>129795137</v>
+        <v>129795159</v>
       </c>
       <c r="B132" t="n">
-        <v>91623</v>
+        <v>57737</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -13999,26 +13975,31 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>5442</v>
+        <v>100049</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
-      <c r="J132" t="inlineStr"/>
       <c r="K132" t="inlineStr"/>
+      <c r="L132" t="inlineStr"/>
+      <c r="M132" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N132" t="inlineStr"/>
       <c r="P132" t="inlineStr">
         <is>
@@ -14026,10 +14007,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>444203</v>
+        <v>444436</v>
       </c>
       <c r="R132" t="n">
-        <v>6787221</v>
+        <v>6787463</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -14070,7 +14051,6 @@
       <c r="AE132" t="b">
         <v>0</v>
       </c>
-      <c r="AF132" t="inlineStr"/>
       <c r="AG132" t="b">
         <v>0</v>
       </c>
@@ -14089,45 +14069,54 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>129795275</v>
+        <v>129795175</v>
       </c>
       <c r="B133" t="n">
-        <v>79084</v>
+        <v>8451</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
+      <c r="J133" t="inlineStr"/>
+      <c r="K133" t="inlineStr"/>
+      <c r="L133" t="inlineStr"/>
+      <c r="M133" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N133" t="inlineStr"/>
       <c r="P133" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>444495</v>
+        <v>444182</v>
       </c>
       <c r="R133" t="n">
-        <v>6787340</v>
+        <v>6787101</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -14168,6 +14157,7 @@
       <c r="AE133" t="b">
         <v>0</v>
       </c>
+      <c r="AF133" t="inlineStr"/>
       <c r="AG133" t="b">
         <v>0</v>
       </c>
@@ -14186,45 +14176,54 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>129795263</v>
+        <v>129795168</v>
       </c>
       <c r="B134" t="n">
-        <v>79084</v>
+        <v>8451</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
+      <c r="J134" t="inlineStr"/>
+      <c r="K134" t="inlineStr"/>
+      <c r="L134" t="inlineStr"/>
+      <c r="M134" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N134" t="inlineStr"/>
       <c r="P134" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>444241</v>
+        <v>444272</v>
       </c>
       <c r="R134" t="n">
-        <v>6787149</v>
+        <v>6787286</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -14265,6 +14264,7 @@
       <c r="AE134" t="b">
         <v>0</v>
       </c>
+      <c r="AF134" t="inlineStr"/>
       <c r="AG134" t="b">
         <v>0</v>
       </c>
@@ -14283,10 +14283,10 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>129795254</v>
+        <v>129795274</v>
       </c>
       <c r="B135" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -14312,19 +14312,16 @@
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
-      <c r="J135" t="inlineStr"/>
-      <c r="K135" t="inlineStr"/>
-      <c r="N135" t="inlineStr"/>
       <c r="P135" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>444199</v>
+        <v>444538</v>
       </c>
       <c r="R135" t="n">
-        <v>6787221</v>
+        <v>6787325</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -14365,7 +14362,6 @@
       <c r="AE135" t="b">
         <v>0</v>
       </c>
-      <c r="AF135" t="inlineStr"/>
       <c r="AG135" t="b">
         <v>0</v>
       </c>
@@ -14384,10 +14380,10 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>129795266</v>
+        <v>129795304</v>
       </c>
       <c r="B136" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -14419,10 +14415,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>444314</v>
+        <v>444172</v>
       </c>
       <c r="R136" t="n">
-        <v>6787212</v>
+        <v>6787339</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -14455,11 +14451,6 @@
       <c r="AA136" t="inlineStr">
         <is>
           <t>2025-11-22</t>
-        </is>
-      </c>
-      <c r="AC136" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 40m</t>
         </is>
       </c>
       <c r="AD136" t="b">
@@ -14486,10 +14477,10 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>129795247</v>
+        <v>129795254</v>
       </c>
       <c r="B137" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -14515,16 +14506,19 @@
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
+      <c r="J137" t="inlineStr"/>
+      <c r="K137" t="inlineStr"/>
+      <c r="N137" t="inlineStr"/>
       <c r="P137" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>444225</v>
+        <v>444199</v>
       </c>
       <c r="R137" t="n">
-        <v>6787275</v>
+        <v>6787221</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -14565,6 +14559,7 @@
       <c r="AE137" t="b">
         <v>0</v>
       </c>
+      <c r="AF137" t="inlineStr"/>
       <c r="AG137" t="b">
         <v>0</v>
       </c>
@@ -14583,10 +14578,10 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>129795139</v>
+        <v>129795302</v>
       </c>
       <c r="B138" t="n">
-        <v>91623</v>
+        <v>79087</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -14594,37 +14589,34 @@
         </is>
       </c>
       <c r="E138" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
-      <c r="J138" t="inlineStr"/>
-      <c r="K138" t="inlineStr"/>
-      <c r="N138" t="inlineStr"/>
       <c r="P138" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>444342</v>
+        <v>444222</v>
       </c>
       <c r="R138" t="n">
-        <v>6787240</v>
+        <v>6787345</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -14665,7 +14657,6 @@
       <c r="AE138" t="b">
         <v>0</v>
       </c>
-      <c r="AF138" t="inlineStr"/>
       <c r="AG138" t="b">
         <v>0</v>
       </c>
@@ -14684,10 +14675,10 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>129795304</v>
+        <v>129795251</v>
       </c>
       <c r="B139" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -14713,16 +14704,19 @@
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
+      <c r="J139" t="inlineStr"/>
+      <c r="K139" t="inlineStr"/>
+      <c r="N139" t="inlineStr"/>
       <c r="P139" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>444172</v>
+        <v>444309</v>
       </c>
       <c r="R139" t="n">
-        <v>6787339</v>
+        <v>6787272</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -14763,6 +14757,7 @@
       <c r="AE139" t="b">
         <v>0</v>
       </c>
+      <c r="AF139" t="inlineStr"/>
       <c r="AG139" t="b">
         <v>0</v>
       </c>
@@ -14781,10 +14776,10 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>129795251</v>
+        <v>129795266</v>
       </c>
       <c r="B140" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -14810,19 +14805,16 @@
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
-      <c r="J140" t="inlineStr"/>
-      <c r="K140" t="inlineStr"/>
-      <c r="N140" t="inlineStr"/>
       <c r="P140" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>444309</v>
+        <v>444314</v>
       </c>
       <c r="R140" t="n">
-        <v>6787272</v>
+        <v>6787212</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -14857,13 +14849,17 @@
           <t>2025-11-22</t>
         </is>
       </c>
+      <c r="AC140" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 40m</t>
+        </is>
+      </c>
       <c r="AD140" t="b">
         <v>0</v>
       </c>
       <c r="AE140" t="b">
         <v>0</v>
       </c>
-      <c r="AF140" t="inlineStr"/>
       <c r="AG140" t="b">
         <v>0</v>
       </c>
@@ -14882,10 +14878,10 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>129795274</v>
+        <v>129795247</v>
       </c>
       <c r="B141" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -14917,10 +14913,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>444538</v>
+        <v>444225</v>
       </c>
       <c r="R141" t="n">
-        <v>6787325</v>
+        <v>6787275</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -14979,10 +14975,10 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>129795302</v>
+        <v>129795139</v>
       </c>
       <c r="B142" t="n">
-        <v>79084</v>
+        <v>91626</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -14990,34 +14986,37 @@
         </is>
       </c>
       <c r="E142" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
+      <c r="J142" t="inlineStr"/>
+      <c r="K142" t="inlineStr"/>
+      <c r="N142" t="inlineStr"/>
       <c r="P142" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>444222</v>
+        <v>444342</v>
       </c>
       <c r="R142" t="n">
-        <v>6787345</v>
+        <v>6787240</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -15058,6 +15057,7 @@
       <c r="AE142" t="b">
         <v>0</v>
       </c>
+      <c r="AF142" t="inlineStr"/>
       <c r="AG142" t="b">
         <v>0</v>
       </c>
@@ -15079,7 +15079,7 @@
         <v>129795204</v>
       </c>
       <c r="B143" t="n">
-        <v>8450</v>
+        <v>8451</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>

--- a/artfynd/A 51041-2025 artfynd.xlsx
+++ b/artfynd/A 51041-2025 artfynd.xlsx
@@ -675,45 +675,54 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129795253</v>
+        <v>129795169</v>
       </c>
       <c r="B2" t="n">
-        <v>79087</v>
+        <v>8451</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>444185</v>
+        <v>444272</v>
       </c>
       <c r="R2" t="n">
-        <v>6787247</v>
+        <v>6787239</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,17 +757,13 @@
           <t>2025-11-22</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Gott om garnlav inom en radie av 50 m.</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -777,45 +782,54 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129795291</v>
+        <v>129795190</v>
       </c>
       <c r="B3" t="n">
-        <v>79087</v>
+        <v>8451</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>444412</v>
+        <v>444510</v>
       </c>
       <c r="R3" t="n">
-        <v>6787307</v>
+        <v>6787276</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -856,6 +870,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -874,45 +889,54 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129795298</v>
+        <v>129795197</v>
       </c>
       <c r="B4" t="n">
-        <v>79087</v>
+        <v>8451</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>444305</v>
+        <v>444406</v>
       </c>
       <c r="R4" t="n">
-        <v>6787353</v>
+        <v>6787392</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -953,6 +977,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -971,7 +996,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129795285</v>
+        <v>129795253</v>
       </c>
       <c r="B5" t="n">
         <v>79087</v>
@@ -1006,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>444405</v>
+        <v>444185</v>
       </c>
       <c r="R5" t="n">
-        <v>6787405</v>
+        <v>6787247</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1042,6 +1067,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-11-22</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Gott om garnlav inom en radie av 50 m.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1068,7 +1098,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129795244</v>
+        <v>129795291</v>
       </c>
       <c r="B6" t="n">
         <v>79087</v>
@@ -1103,10 +1133,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>444105</v>
+        <v>444412</v>
       </c>
       <c r="R6" t="n">
-        <v>6787246</v>
+        <v>6787307</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1165,7 +1195,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129795261</v>
+        <v>129795298</v>
       </c>
       <c r="B7" t="n">
         <v>79087</v>
@@ -1200,10 +1230,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>444193</v>
+        <v>444305</v>
       </c>
       <c r="R7" t="n">
-        <v>6787130</v>
+        <v>6787353</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1262,7 +1292,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129795283</v>
+        <v>129795285</v>
       </c>
       <c r="B8" t="n">
         <v>79087</v>
@@ -1291,19 +1321,16 @@
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>444337</v>
+        <v>444405</v>
       </c>
       <c r="R8" t="n">
-        <v>6787374</v>
+        <v>6787405</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1344,7 +1371,6 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1363,54 +1389,45 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129795169</v>
+        <v>129795244</v>
       </c>
       <c r="B9" t="n">
-        <v>8451</v>
+        <v>79087</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>444272</v>
+        <v>444105</v>
       </c>
       <c r="R9" t="n">
-        <v>6787239</v>
+        <v>6787246</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1451,7 +1468,6 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1470,54 +1486,45 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129795190</v>
+        <v>129795261</v>
       </c>
       <c r="B10" t="n">
-        <v>8451</v>
+        <v>79087</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>444510</v>
+        <v>444193</v>
       </c>
       <c r="R10" t="n">
-        <v>6787276</v>
+        <v>6787130</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1558,7 +1565,6 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1577,43 +1583,37 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129795197</v>
+        <v>129795283</v>
       </c>
       <c r="B11" t="n">
-        <v>8451</v>
+        <v>79087</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1621,10 +1621,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>444406</v>
+        <v>444337</v>
       </c>
       <c r="R11" t="n">
-        <v>6787392</v>
+        <v>6787374</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -5909,10 +5909,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129795277</v>
+        <v>129795161</v>
       </c>
       <c r="B53" t="n">
-        <v>79087</v>
+        <v>57737</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5920,34 +5920,42 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
+      <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>444491</v>
+        <v>444433</v>
       </c>
       <c r="R53" t="n">
-        <v>6787412</v>
+        <v>6787338</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6006,10 +6014,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129795279</v>
+        <v>129795147</v>
       </c>
       <c r="B54" t="n">
-        <v>79087</v>
+        <v>57737</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6017,34 +6025,42 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
+      <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr"/>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>444463</v>
+        <v>444220</v>
       </c>
       <c r="R54" t="n">
-        <v>6787459</v>
+        <v>6787221</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6103,32 +6119,32 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129795131</v>
+        <v>129795134</v>
       </c>
       <c r="B55" t="n">
-        <v>56930</v>
+        <v>57898</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>100138</v>
+        <v>103021</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6136,7 +6152,7 @@
       <c r="L55" t="inlineStr"/>
       <c r="M55" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N55" t="inlineStr"/>
@@ -6146,10 +6162,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>444250</v>
+        <v>444289</v>
       </c>
       <c r="R55" t="n">
-        <v>6787212</v>
+        <v>6787357</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6208,40 +6224,41 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129795161</v>
+        <v>129795184</v>
       </c>
       <c r="B56" t="n">
-        <v>57737</v>
+        <v>8451</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
+      <c r="J56" t="inlineStr"/>
       <c r="K56" t="inlineStr"/>
       <c r="L56" t="inlineStr"/>
       <c r="M56" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N56" t="inlineStr"/>
@@ -6251,10 +6268,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>444433</v>
+        <v>444452</v>
       </c>
       <c r="R56" t="n">
-        <v>6787338</v>
+        <v>6787305</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6295,6 +6312,7 @@
       <c r="AE56" t="b">
         <v>0</v>
       </c>
+      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
       </c>
@@ -6313,40 +6331,41 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129795147</v>
+        <v>129795172</v>
       </c>
       <c r="B57" t="n">
-        <v>57737</v>
+        <v>8451</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
+      <c r="J57" t="inlineStr"/>
       <c r="K57" t="inlineStr"/>
       <c r="L57" t="inlineStr"/>
       <c r="M57" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N57" t="inlineStr"/>
@@ -6356,10 +6375,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>444220</v>
+        <v>444225</v>
       </c>
       <c r="R57" t="n">
-        <v>6787221</v>
+        <v>6787223</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6400,6 +6419,7 @@
       <c r="AE57" t="b">
         <v>0</v>
       </c>
+      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
@@ -6418,40 +6438,41 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129795134</v>
+        <v>129795199</v>
       </c>
       <c r="B58" t="n">
-        <v>57898</v>
+        <v>8451</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>103021</v>
+        <v>106545</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
+      <c r="J58" t="inlineStr"/>
       <c r="K58" t="inlineStr"/>
       <c r="L58" t="inlineStr"/>
       <c r="M58" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N58" t="inlineStr"/>
@@ -6461,10 +6482,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>444289</v>
+        <v>444431</v>
       </c>
       <c r="R58" t="n">
-        <v>6787357</v>
+        <v>6787350</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6505,6 +6526,7 @@
       <c r="AE58" t="b">
         <v>0</v>
       </c>
+      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
       </c>
@@ -6523,54 +6545,45 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129795184</v>
+        <v>129795277</v>
       </c>
       <c r="B59" t="n">
-        <v>8451</v>
+        <v>79087</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
-      <c r="J59" t="inlineStr"/>
-      <c r="K59" t="inlineStr"/>
-      <c r="L59" t="inlineStr"/>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>444452</v>
+        <v>444491</v>
       </c>
       <c r="R59" t="n">
-        <v>6787305</v>
+        <v>6787412</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6611,7 +6624,6 @@
       <c r="AE59" t="b">
         <v>0</v>
       </c>
-      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
       </c>
@@ -6630,54 +6642,45 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129795172</v>
+        <v>129795279</v>
       </c>
       <c r="B60" t="n">
-        <v>8451</v>
+        <v>79087</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
-      <c r="J60" t="inlineStr"/>
-      <c r="K60" t="inlineStr"/>
-      <c r="L60" t="inlineStr"/>
-      <c r="M60" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>444225</v>
+        <v>444463</v>
       </c>
       <c r="R60" t="n">
-        <v>6787223</v>
+        <v>6787459</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6718,7 +6721,6 @@
       <c r="AE60" t="b">
         <v>0</v>
       </c>
-      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
       </c>
@@ -6737,10 +6739,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129795199</v>
+        <v>129795131</v>
       </c>
       <c r="B61" t="n">
-        <v>8451</v>
+        <v>56930</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6748,30 +6750,29 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>106545</v>
+        <v>100138</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
-      <c r="J61" t="inlineStr"/>
       <c r="K61" t="inlineStr"/>
       <c r="L61" t="inlineStr"/>
       <c r="M61" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="N61" t="inlineStr"/>
@@ -6781,10 +6782,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>444431</v>
+        <v>444250</v>
       </c>
       <c r="R61" t="n">
-        <v>6787350</v>
+        <v>6787212</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6825,7 +6826,6 @@
       <c r="AE61" t="b">
         <v>0</v>
       </c>
-      <c r="AF61" t="inlineStr"/>
       <c r="AG61" t="b">
         <v>0</v>
       </c>
@@ -10784,54 +10784,45 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>129795185</v>
+        <v>129795264</v>
       </c>
       <c r="B101" t="n">
-        <v>8451</v>
+        <v>79087</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
-      <c r="J101" t="inlineStr"/>
-      <c r="K101" t="inlineStr"/>
-      <c r="L101" t="inlineStr"/>
-      <c r="M101" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>444458</v>
+        <v>444252</v>
       </c>
       <c r="R101" t="n">
-        <v>6787304</v>
+        <v>6787160</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10872,7 +10863,6 @@
       <c r="AE101" t="b">
         <v>0</v>
       </c>
-      <c r="AF101" t="inlineStr"/>
       <c r="AG101" t="b">
         <v>0</v>
       </c>
@@ -10891,54 +10881,45 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>129795180</v>
+        <v>129795248</v>
       </c>
       <c r="B102" t="n">
-        <v>8451</v>
+        <v>79087</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
-      <c r="J102" t="inlineStr"/>
-      <c r="K102" t="inlineStr"/>
-      <c r="L102" t="inlineStr"/>
-      <c r="M102" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>444409</v>
+        <v>444238</v>
       </c>
       <c r="R102" t="n">
-        <v>6787219</v>
+        <v>6787281</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -10979,7 +10960,6 @@
       <c r="AE102" t="b">
         <v>0</v>
       </c>
-      <c r="AF102" t="inlineStr"/>
       <c r="AG102" t="b">
         <v>0</v>
       </c>
@@ -10998,54 +10978,45 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>129795178</v>
+        <v>129795303</v>
       </c>
       <c r="B103" t="n">
-        <v>8451</v>
+        <v>79087</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
-      <c r="J103" t="inlineStr"/>
-      <c r="K103" t="inlineStr"/>
-      <c r="L103" t="inlineStr"/>
-      <c r="M103" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N103" t="inlineStr"/>
       <c r="P103" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>444375</v>
+        <v>444200</v>
       </c>
       <c r="R103" t="n">
-        <v>6787207</v>
+        <v>6787331</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11086,7 +11057,6 @@
       <c r="AE103" t="b">
         <v>0</v>
       </c>
-      <c r="AF103" t="inlineStr"/>
       <c r="AG103" t="b">
         <v>0</v>
       </c>
@@ -11105,54 +11075,45 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>129795186</v>
+        <v>129795306</v>
       </c>
       <c r="B104" t="n">
-        <v>8451</v>
+        <v>79087</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
-      <c r="J104" t="inlineStr"/>
-      <c r="K104" t="inlineStr"/>
-      <c r="L104" t="inlineStr"/>
-      <c r="M104" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>444473</v>
+        <v>444152</v>
       </c>
       <c r="R104" t="n">
-        <v>6787334</v>
+        <v>6787313</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11193,7 +11154,6 @@
       <c r="AE104" t="b">
         <v>0</v>
       </c>
-      <c r="AF104" t="inlineStr"/>
       <c r="AG104" t="b">
         <v>0</v>
       </c>
@@ -11212,7 +11172,7 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>129795196</v>
+        <v>129795185</v>
       </c>
       <c r="B105" t="n">
         <v>8451</v>
@@ -11256,10 +11216,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>444346</v>
+        <v>444458</v>
       </c>
       <c r="R105" t="n">
-        <v>6787369</v>
+        <v>6787304</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11319,45 +11279,54 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>129795264</v>
+        <v>129795180</v>
       </c>
       <c r="B106" t="n">
-        <v>79087</v>
+        <v>8451</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
+      <c r="J106" t="inlineStr"/>
+      <c r="K106" t="inlineStr"/>
+      <c r="L106" t="inlineStr"/>
+      <c r="M106" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>444252</v>
+        <v>444409</v>
       </c>
       <c r="R106" t="n">
-        <v>6787160</v>
+        <v>6787219</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11398,6 +11367,7 @@
       <c r="AE106" t="b">
         <v>0</v>
       </c>
+      <c r="AF106" t="inlineStr"/>
       <c r="AG106" t="b">
         <v>0</v>
       </c>
@@ -11416,45 +11386,54 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>129795248</v>
+        <v>129795178</v>
       </c>
       <c r="B107" t="n">
-        <v>79087</v>
+        <v>8451</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
+      <c r="J107" t="inlineStr"/>
+      <c r="K107" t="inlineStr"/>
+      <c r="L107" t="inlineStr"/>
+      <c r="M107" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>444238</v>
+        <v>444375</v>
       </c>
       <c r="R107" t="n">
-        <v>6787281</v>
+        <v>6787207</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11495,6 +11474,7 @@
       <c r="AE107" t="b">
         <v>0</v>
       </c>
+      <c r="AF107" t="inlineStr"/>
       <c r="AG107" t="b">
         <v>0</v>
       </c>
@@ -11513,45 +11493,54 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>129795303</v>
+        <v>129795186</v>
       </c>
       <c r="B108" t="n">
-        <v>79087</v>
+        <v>8451</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
+      <c r="J108" t="inlineStr"/>
+      <c r="K108" t="inlineStr"/>
+      <c r="L108" t="inlineStr"/>
+      <c r="M108" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>444200</v>
+        <v>444473</v>
       </c>
       <c r="R108" t="n">
-        <v>6787331</v>
+        <v>6787334</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11592,6 +11581,7 @@
       <c r="AE108" t="b">
         <v>0</v>
       </c>
+      <c r="AF108" t="inlineStr"/>
       <c r="AG108" t="b">
         <v>0</v>
       </c>
@@ -11610,45 +11600,54 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>129795306</v>
+        <v>129795196</v>
       </c>
       <c r="B109" t="n">
-        <v>79087</v>
+        <v>8451</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
+      <c r="J109" t="inlineStr"/>
+      <c r="K109" t="inlineStr"/>
+      <c r="L109" t="inlineStr"/>
+      <c r="M109" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>444152</v>
+        <v>444346</v>
       </c>
       <c r="R109" t="n">
-        <v>6787313</v>
+        <v>6787369</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11689,6 +11688,7 @@
       <c r="AE109" t="b">
         <v>0</v>
       </c>
+      <c r="AF109" t="inlineStr"/>
       <c r="AG109" t="b">
         <v>0</v>
       </c>
@@ -12333,41 +12333,40 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>129795171</v>
+        <v>129795164</v>
       </c>
       <c r="B116" t="n">
-        <v>8451</v>
+        <v>57737</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
-      <c r="J116" t="inlineStr"/>
       <c r="K116" t="inlineStr"/>
       <c r="L116" t="inlineStr"/>
       <c r="M116" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N116" t="inlineStr"/>
@@ -12377,10 +12376,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>444185</v>
+        <v>444397</v>
       </c>
       <c r="R116" t="n">
-        <v>6787226</v>
+        <v>6787300</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12421,7 +12420,6 @@
       <c r="AE116" t="b">
         <v>0</v>
       </c>
-      <c r="AF116" t="inlineStr"/>
       <c r="AG116" t="b">
         <v>0</v>
       </c>
@@ -12440,7 +12438,7 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>129795164</v>
+        <v>129795154</v>
       </c>
       <c r="B117" t="n">
         <v>57737</v>
@@ -12483,10 +12481,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>444397</v>
+        <v>444457</v>
       </c>
       <c r="R117" t="n">
-        <v>6787300</v>
+        <v>6787303</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12545,7 +12543,7 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>129795154</v>
+        <v>129795157</v>
       </c>
       <c r="B118" t="n">
         <v>57737</v>
@@ -12588,10 +12586,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>444457</v>
+        <v>444525</v>
       </c>
       <c r="R118" t="n">
-        <v>6787303</v>
+        <v>6787344</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12650,32 +12648,32 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>129795157</v>
+        <v>129795132</v>
       </c>
       <c r="B119" t="n">
-        <v>57737</v>
+        <v>56930</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -12683,7 +12681,7 @@
       <c r="L119" t="inlineStr"/>
       <c r="M119" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="N119" t="inlineStr"/>
@@ -12693,10 +12691,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>444525</v>
+        <v>444315</v>
       </c>
       <c r="R119" t="n">
-        <v>6787344</v>
+        <v>6787291</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -12755,10 +12753,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>129795132</v>
+        <v>129795171</v>
       </c>
       <c r="B120" t="n">
-        <v>56930</v>
+        <v>8451</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -12766,29 +12764,30 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>100138</v>
+        <v>106545</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
+      <c r="J120" t="inlineStr"/>
       <c r="K120" t="inlineStr"/>
       <c r="L120" t="inlineStr"/>
       <c r="M120" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N120" t="inlineStr"/>
@@ -12798,10 +12797,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>444315</v>
+        <v>444185</v>
       </c>
       <c r="R120" t="n">
-        <v>6787291</v>
+        <v>6787226</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -12842,6 +12841,7 @@
       <c r="AE120" t="b">
         <v>0</v>
       </c>
+      <c r="AF120" t="inlineStr"/>
       <c r="AG120" t="b">
         <v>0</v>
       </c>
@@ -14283,7 +14283,7 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>129795274</v>
+        <v>129795254</v>
       </c>
       <c r="B135" t="n">
         <v>79087</v>
@@ -14312,16 +14312,19 @@
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
+      <c r="J135" t="inlineStr"/>
+      <c r="K135" t="inlineStr"/>
+      <c r="N135" t="inlineStr"/>
       <c r="P135" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>444538</v>
+        <v>444199</v>
       </c>
       <c r="R135" t="n">
-        <v>6787325</v>
+        <v>6787221</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -14362,6 +14365,7 @@
       <c r="AE135" t="b">
         <v>0</v>
       </c>
+      <c r="AF135" t="inlineStr"/>
       <c r="AG135" t="b">
         <v>0</v>
       </c>
@@ -14380,7 +14384,7 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>129795304</v>
+        <v>129795251</v>
       </c>
       <c r="B136" t="n">
         <v>79087</v>
@@ -14409,16 +14413,19 @@
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
+      <c r="J136" t="inlineStr"/>
+      <c r="K136" t="inlineStr"/>
+      <c r="N136" t="inlineStr"/>
       <c r="P136" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>444172</v>
+        <v>444309</v>
       </c>
       <c r="R136" t="n">
-        <v>6787339</v>
+        <v>6787272</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -14459,6 +14466,7 @@
       <c r="AE136" t="b">
         <v>0</v>
       </c>
+      <c r="AF136" t="inlineStr"/>
       <c r="AG136" t="b">
         <v>0</v>
       </c>
@@ -14477,7 +14485,7 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>129795254</v>
+        <v>129795266</v>
       </c>
       <c r="B137" t="n">
         <v>79087</v>
@@ -14506,19 +14514,16 @@
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
-      <c r="J137" t="inlineStr"/>
-      <c r="K137" t="inlineStr"/>
-      <c r="N137" t="inlineStr"/>
       <c r="P137" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>444199</v>
+        <v>444314</v>
       </c>
       <c r="R137" t="n">
-        <v>6787221</v>
+        <v>6787212</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -14553,13 +14558,17 @@
           <t>2025-11-22</t>
         </is>
       </c>
+      <c r="AC137" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 40m</t>
+        </is>
+      </c>
       <c r="AD137" t="b">
         <v>0</v>
       </c>
       <c r="AE137" t="b">
         <v>0</v>
       </c>
-      <c r="AF137" t="inlineStr"/>
       <c r="AG137" t="b">
         <v>0</v>
       </c>
@@ -14578,7 +14587,7 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>129795302</v>
+        <v>129795274</v>
       </c>
       <c r="B138" t="n">
         <v>79087</v>
@@ -14613,10 +14622,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>444222</v>
+        <v>444538</v>
       </c>
       <c r="R138" t="n">
-        <v>6787345</v>
+        <v>6787325</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -14675,7 +14684,7 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>129795251</v>
+        <v>129795304</v>
       </c>
       <c r="B139" t="n">
         <v>79087</v>
@@ -14704,19 +14713,16 @@
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
-      <c r="J139" t="inlineStr"/>
-      <c r="K139" t="inlineStr"/>
-      <c r="N139" t="inlineStr"/>
       <c r="P139" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>444309</v>
+        <v>444172</v>
       </c>
       <c r="R139" t="n">
-        <v>6787272</v>
+        <v>6787339</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -14757,7 +14763,6 @@
       <c r="AE139" t="b">
         <v>0</v>
       </c>
-      <c r="AF139" t="inlineStr"/>
       <c r="AG139" t="b">
         <v>0</v>
       </c>
@@ -14776,7 +14781,7 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>129795266</v>
+        <v>129795302</v>
       </c>
       <c r="B140" t="n">
         <v>79087</v>
@@ -14811,10 +14816,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>444314</v>
+        <v>444222</v>
       </c>
       <c r="R140" t="n">
-        <v>6787212</v>
+        <v>6787345</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -14847,11 +14852,6 @@
       <c r="AA140" t="inlineStr">
         <is>
           <t>2025-11-22</t>
-        </is>
-      </c>
-      <c r="AC140" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 40m</t>
         </is>
       </c>
       <c r="AD140" t="b">

--- a/artfynd/A 51041-2025 artfynd.xlsx
+++ b/artfynd/A 51041-2025 artfynd.xlsx
@@ -4889,40 +4889,41 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129795158</v>
+        <v>129795170</v>
       </c>
       <c r="B43" t="n">
-        <v>57737</v>
+        <v>8451</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr"/>
       <c r="K43" t="inlineStr"/>
       <c r="L43" t="inlineStr"/>
       <c r="M43" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N43" t="inlineStr"/>
@@ -4932,10 +4933,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>444501</v>
+        <v>444172</v>
       </c>
       <c r="R43" t="n">
-        <v>6787402</v>
+        <v>6787202</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4976,6 +4977,7 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
+      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
@@ -4994,10 +4996,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129795136</v>
+        <v>129795158</v>
       </c>
       <c r="B44" t="n">
-        <v>91626</v>
+        <v>57737</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5005,26 +5007,31 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>5442</v>
+        <v>100049</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="J44" t="inlineStr"/>
       <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
@@ -5032,10 +5039,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>444235</v>
+        <v>444501</v>
       </c>
       <c r="R44" t="n">
-        <v>6787149</v>
+        <v>6787402</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5076,7 +5083,6 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
-      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
@@ -5095,10 +5101,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129795282</v>
+        <v>129795136</v>
       </c>
       <c r="B45" t="n">
-        <v>79087</v>
+        <v>91626</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5106,21 +5112,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5133,10 +5139,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>444374</v>
+        <v>444235</v>
       </c>
       <c r="R45" t="n">
-        <v>6787384</v>
+        <v>6787149</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5169,11 +5175,6 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-11-22</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 50 m.</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5201,7 +5202,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129795293</v>
+        <v>129795282</v>
       </c>
       <c r="B46" t="n">
         <v>79087</v>
@@ -5230,16 +5231,19 @@
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="J46" t="inlineStr"/>
+      <c r="K46" t="inlineStr"/>
+      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>444365</v>
+        <v>444374</v>
       </c>
       <c r="R46" t="n">
-        <v>6787285</v>
+        <v>6787384</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5276,7 +5280,7 @@
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>Rikligt med garnlav inom en radie av 50m.</t>
+          <t>Rikligt med garnlav inom en radie av 50 m.</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5285,6 +5289,7 @@
       <c r="AE46" t="b">
         <v>0</v>
       </c>
+      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
@@ -5303,54 +5308,45 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129795170</v>
+        <v>129795293</v>
       </c>
       <c r="B47" t="n">
-        <v>8451</v>
+        <v>79087</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="J47" t="inlineStr"/>
-      <c r="K47" t="inlineStr"/>
-      <c r="L47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>444172</v>
+        <v>444365</v>
       </c>
       <c r="R47" t="n">
-        <v>6787202</v>
+        <v>6787285</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5385,13 +5381,17 @@
           <t>2025-11-22</t>
         </is>
       </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 50m.</t>
+        </is>
+      </c>
       <c r="AD47" t="b">
         <v>0</v>
       </c>
       <c r="AE47" t="b">
         <v>0</v>
       </c>
-      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
@@ -9286,54 +9286,45 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129795192</v>
+        <v>129795308</v>
       </c>
       <c r="B86" t="n">
-        <v>8451</v>
+        <v>79087</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
-      <c r="J86" t="inlineStr"/>
-      <c r="K86" t="inlineStr"/>
-      <c r="L86" t="inlineStr"/>
-      <c r="M86" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>444549</v>
+        <v>444098</v>
       </c>
       <c r="R86" t="n">
-        <v>6787335</v>
+        <v>6787297</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9374,7 +9365,6 @@
       <c r="AE86" t="b">
         <v>0</v>
       </c>
-      <c r="AF86" t="inlineStr"/>
       <c r="AG86" t="b">
         <v>0</v>
       </c>
@@ -9393,54 +9383,45 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129795181</v>
+        <v>129795242</v>
       </c>
       <c r="B87" t="n">
-        <v>8451</v>
+        <v>79087</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
-      <c r="J87" t="inlineStr"/>
-      <c r="K87" t="inlineStr"/>
-      <c r="L87" t="inlineStr"/>
-      <c r="M87" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>444408</v>
+        <v>444125</v>
       </c>
       <c r="R87" t="n">
-        <v>6787250</v>
+        <v>6787297</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9481,7 +9462,6 @@
       <c r="AE87" t="b">
         <v>0</v>
       </c>
-      <c r="AF87" t="inlineStr"/>
       <c r="AG87" t="b">
         <v>0</v>
       </c>
@@ -9500,45 +9480,54 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129795308</v>
+        <v>129795192</v>
       </c>
       <c r="B88" t="n">
-        <v>79087</v>
+        <v>8451</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
+      <c r="J88" t="inlineStr"/>
+      <c r="K88" t="inlineStr"/>
+      <c r="L88" t="inlineStr"/>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>444098</v>
+        <v>444549</v>
       </c>
       <c r="R88" t="n">
-        <v>6787297</v>
+        <v>6787335</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9579,6 +9568,7 @@
       <c r="AE88" t="b">
         <v>0</v>
       </c>
+      <c r="AF88" t="inlineStr"/>
       <c r="AG88" t="b">
         <v>0</v>
       </c>
@@ -9597,45 +9587,54 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>129795242</v>
+        <v>129795181</v>
       </c>
       <c r="B89" t="n">
-        <v>79087</v>
+        <v>8451</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
+      <c r="J89" t="inlineStr"/>
+      <c r="K89" t="inlineStr"/>
+      <c r="L89" t="inlineStr"/>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>444125</v>
+        <v>444408</v>
       </c>
       <c r="R89" t="n">
-        <v>6787297</v>
+        <v>6787250</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9676,6 +9675,7 @@
       <c r="AE89" t="b">
         <v>0</v>
       </c>
+      <c r="AF89" t="inlineStr"/>
       <c r="AG89" t="b">
         <v>0</v>
       </c>
@@ -9694,10 +9694,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>129795121</v>
+        <v>129795152</v>
       </c>
       <c r="B90" t="n">
-        <v>79706</v>
+        <v>57737</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9705,34 +9705,42 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
+      <c r="K90" t="inlineStr"/>
+      <c r="L90" t="inlineStr"/>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>444254</v>
+        <v>444434</v>
       </c>
       <c r="R90" t="n">
-        <v>6787204</v>
+        <v>6787304</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9791,10 +9799,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>129795124</v>
+        <v>129795305</v>
       </c>
       <c r="B91" t="n">
-        <v>79706</v>
+        <v>79087</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9802,21 +9810,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -9826,10 +9834,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>444393</v>
+        <v>444169</v>
       </c>
       <c r="R91" t="n">
-        <v>6787395</v>
+        <v>6787323</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9888,10 +9896,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>129795152</v>
+        <v>129795288</v>
       </c>
       <c r="B92" t="n">
-        <v>57737</v>
+        <v>79087</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9899,42 +9907,34 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
-      <c r="K92" t="inlineStr"/>
-      <c r="L92" t="inlineStr"/>
-      <c r="M92" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>444434</v>
+        <v>444420</v>
       </c>
       <c r="R92" t="n">
-        <v>6787304</v>
+        <v>6787366</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9993,7 +9993,7 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>129795305</v>
+        <v>129795245</v>
       </c>
       <c r="B93" t="n">
         <v>79087</v>
@@ -10028,10 +10028,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>444169</v>
+        <v>444113</v>
       </c>
       <c r="R93" t="n">
-        <v>6787323</v>
+        <v>6787239</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10090,10 +10090,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>129795288</v>
+        <v>129795123</v>
       </c>
       <c r="B94" t="n">
-        <v>79087</v>
+        <v>79706</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10101,21 +10101,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -10125,10 +10125,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>444420</v>
+        <v>444530</v>
       </c>
       <c r="R94" t="n">
-        <v>6787366</v>
+        <v>6787326</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10187,7 +10187,7 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>129795245</v>
+        <v>129795297</v>
       </c>
       <c r="B95" t="n">
         <v>79087</v>
@@ -10222,10 +10222,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>444113</v>
+        <v>444297</v>
       </c>
       <c r="R95" t="n">
-        <v>6787239</v>
+        <v>6787333</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10284,10 +10284,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>129795123</v>
+        <v>129795262</v>
       </c>
       <c r="B96" t="n">
-        <v>79706</v>
+        <v>79087</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10295,21 +10295,21 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10319,10 +10319,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>444530</v>
+        <v>444219</v>
       </c>
       <c r="R96" t="n">
-        <v>6787326</v>
+        <v>6787163</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10381,7 +10381,7 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>129795297</v>
+        <v>129795252</v>
       </c>
       <c r="B97" t="n">
         <v>79087</v>
@@ -10416,10 +10416,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>444297</v>
+        <v>444249</v>
       </c>
       <c r="R97" t="n">
-        <v>6787333</v>
+        <v>6787249</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10452,6 +10452,11 @@
       <c r="AA97" t="inlineStr">
         <is>
           <t>2025-11-22</t>
+        </is>
+      </c>
+      <c r="AC97" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 40m.</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -10478,45 +10483,54 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>129795262</v>
+        <v>129795167</v>
       </c>
       <c r="B98" t="n">
-        <v>79087</v>
+        <v>8451</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
+      <c r="J98" t="inlineStr"/>
+      <c r="K98" t="inlineStr"/>
+      <c r="L98" t="inlineStr"/>
+      <c r="M98" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>444219</v>
+        <v>444132</v>
       </c>
       <c r="R98" t="n">
-        <v>6787163</v>
+        <v>6787237</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10557,6 +10571,7 @@
       <c r="AE98" t="b">
         <v>0</v>
       </c>
+      <c r="AF98" t="inlineStr"/>
       <c r="AG98" t="b">
         <v>0</v>
       </c>
@@ -10575,10 +10590,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>129795252</v>
+        <v>129795121</v>
       </c>
       <c r="B99" t="n">
-        <v>79087</v>
+        <v>79706</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10586,21 +10601,21 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -10610,10 +10625,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>444249</v>
+        <v>444254</v>
       </c>
       <c r="R99" t="n">
-        <v>6787249</v>
+        <v>6787204</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10646,11 +10661,6 @@
       <c r="AA99" t="inlineStr">
         <is>
           <t>2025-11-22</t>
-        </is>
-      </c>
-      <c r="AC99" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 40m.</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -10677,54 +10687,45 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>129795167</v>
+        <v>129795124</v>
       </c>
       <c r="B100" t="n">
-        <v>8451</v>
+        <v>79706</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
-      <c r="J100" t="inlineStr"/>
-      <c r="K100" t="inlineStr"/>
-      <c r="L100" t="inlineStr"/>
-      <c r="M100" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>444132</v>
+        <v>444393</v>
       </c>
       <c r="R100" t="n">
-        <v>6787237</v>
+        <v>6787395</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10765,7 +10766,6 @@
       <c r="AE100" t="b">
         <v>0</v>
       </c>
-      <c r="AF100" t="inlineStr"/>
       <c r="AG100" t="b">
         <v>0</v>
       </c>
@@ -12333,40 +12333,41 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>129795164</v>
+        <v>129795171</v>
       </c>
       <c r="B116" t="n">
-        <v>57737</v>
+        <v>8451</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
+      <c r="J116" t="inlineStr"/>
       <c r="K116" t="inlineStr"/>
       <c r="L116" t="inlineStr"/>
       <c r="M116" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N116" t="inlineStr"/>
@@ -12376,10 +12377,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>444397</v>
+        <v>444185</v>
       </c>
       <c r="R116" t="n">
-        <v>6787300</v>
+        <v>6787226</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12420,6 +12421,7 @@
       <c r="AE116" t="b">
         <v>0</v>
       </c>
+      <c r="AF116" t="inlineStr"/>
       <c r="AG116" t="b">
         <v>0</v>
       </c>
@@ -12438,7 +12440,7 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>129795154</v>
+        <v>129795164</v>
       </c>
       <c r="B117" t="n">
         <v>57737</v>
@@ -12481,10 +12483,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>444457</v>
+        <v>444397</v>
       </c>
       <c r="R117" t="n">
-        <v>6787303</v>
+        <v>6787300</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12543,7 +12545,7 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>129795157</v>
+        <v>129795154</v>
       </c>
       <c r="B118" t="n">
         <v>57737</v>
@@ -12586,10 +12588,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>444525</v>
+        <v>444457</v>
       </c>
       <c r="R118" t="n">
-        <v>6787344</v>
+        <v>6787303</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12648,32 +12650,32 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>129795132</v>
+        <v>129795157</v>
       </c>
       <c r="B119" t="n">
-        <v>56930</v>
+        <v>57737</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -12681,7 +12683,7 @@
       <c r="L119" t="inlineStr"/>
       <c r="M119" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N119" t="inlineStr"/>
@@ -12691,10 +12693,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>444315</v>
+        <v>444525</v>
       </c>
       <c r="R119" t="n">
-        <v>6787291</v>
+        <v>6787344</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -12753,10 +12755,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>129795171</v>
+        <v>129795132</v>
       </c>
       <c r="B120" t="n">
-        <v>8451</v>
+        <v>56930</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -12764,30 +12766,29 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>106545</v>
+        <v>100138</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
-      <c r="J120" t="inlineStr"/>
       <c r="K120" t="inlineStr"/>
       <c r="L120" t="inlineStr"/>
       <c r="M120" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="N120" t="inlineStr"/>
@@ -12797,10 +12798,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>444185</v>
+        <v>444315</v>
       </c>
       <c r="R120" t="n">
-        <v>6787226</v>
+        <v>6787291</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -12841,7 +12842,6 @@
       <c r="AE120" t="b">
         <v>0</v>
       </c>
-      <c r="AF120" t="inlineStr"/>
       <c r="AG120" t="b">
         <v>0</v>
       </c>
@@ -14283,7 +14283,7 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>129795254</v>
+        <v>129795274</v>
       </c>
       <c r="B135" t="n">
         <v>79087</v>
@@ -14312,19 +14312,16 @@
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
-      <c r="J135" t="inlineStr"/>
-      <c r="K135" t="inlineStr"/>
-      <c r="N135" t="inlineStr"/>
       <c r="P135" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>444199</v>
+        <v>444538</v>
       </c>
       <c r="R135" t="n">
-        <v>6787221</v>
+        <v>6787325</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -14365,7 +14362,6 @@
       <c r="AE135" t="b">
         <v>0</v>
       </c>
-      <c r="AF135" t="inlineStr"/>
       <c r="AG135" t="b">
         <v>0</v>
       </c>
@@ -14384,7 +14380,7 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>129795251</v>
+        <v>129795304</v>
       </c>
       <c r="B136" t="n">
         <v>79087</v>
@@ -14413,19 +14409,16 @@
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
-      <c r="J136" t="inlineStr"/>
-      <c r="K136" t="inlineStr"/>
-      <c r="N136" t="inlineStr"/>
       <c r="P136" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>444309</v>
+        <v>444172</v>
       </c>
       <c r="R136" t="n">
-        <v>6787272</v>
+        <v>6787339</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -14466,7 +14459,6 @@
       <c r="AE136" t="b">
         <v>0</v>
       </c>
-      <c r="AF136" t="inlineStr"/>
       <c r="AG136" t="b">
         <v>0</v>
       </c>
@@ -14485,7 +14477,7 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>129795266</v>
+        <v>129795254</v>
       </c>
       <c r="B137" t="n">
         <v>79087</v>
@@ -14514,16 +14506,19 @@
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
+      <c r="J137" t="inlineStr"/>
+      <c r="K137" t="inlineStr"/>
+      <c r="N137" t="inlineStr"/>
       <c r="P137" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>444314</v>
+        <v>444199</v>
       </c>
       <c r="R137" t="n">
-        <v>6787212</v>
+        <v>6787221</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -14558,17 +14553,13 @@
           <t>2025-11-22</t>
         </is>
       </c>
-      <c r="AC137" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 40m</t>
-        </is>
-      </c>
       <c r="AD137" t="b">
         <v>0</v>
       </c>
       <c r="AE137" t="b">
         <v>0</v>
       </c>
+      <c r="AF137" t="inlineStr"/>
       <c r="AG137" t="b">
         <v>0</v>
       </c>
@@ -14587,7 +14578,7 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>129795274</v>
+        <v>129795302</v>
       </c>
       <c r="B138" t="n">
         <v>79087</v>
@@ -14622,10 +14613,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>444538</v>
+        <v>444222</v>
       </c>
       <c r="R138" t="n">
-        <v>6787325</v>
+        <v>6787345</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -14684,7 +14675,7 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>129795304</v>
+        <v>129795251</v>
       </c>
       <c r="B139" t="n">
         <v>79087</v>
@@ -14713,16 +14704,19 @@
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
+      <c r="J139" t="inlineStr"/>
+      <c r="K139" t="inlineStr"/>
+      <c r="N139" t="inlineStr"/>
       <c r="P139" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>444172</v>
+        <v>444309</v>
       </c>
       <c r="R139" t="n">
-        <v>6787339</v>
+        <v>6787272</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -14763,6 +14757,7 @@
       <c r="AE139" t="b">
         <v>0</v>
       </c>
+      <c r="AF139" t="inlineStr"/>
       <c r="AG139" t="b">
         <v>0</v>
       </c>
@@ -14781,7 +14776,7 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>129795302</v>
+        <v>129795266</v>
       </c>
       <c r="B140" t="n">
         <v>79087</v>
@@ -14816,10 +14811,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>444222</v>
+        <v>444314</v>
       </c>
       <c r="R140" t="n">
-        <v>6787345</v>
+        <v>6787212</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -14852,6 +14847,11 @@
       <c r="AA140" t="inlineStr">
         <is>
           <t>2025-11-22</t>
+        </is>
+      </c>
+      <c r="AC140" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 40m</t>
         </is>
       </c>
       <c r="AD140" t="b">

--- a/artfynd/A 51041-2025 artfynd.xlsx
+++ b/artfynd/A 51041-2025 artfynd.xlsx
@@ -999,7 +999,7 @@
         <v>129795253</v>
       </c>
       <c r="B5" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1098,10 +1098,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129795291</v>
+        <v>129795261</v>
       </c>
       <c r="B6" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1133,10 +1133,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>444412</v>
+        <v>444193</v>
       </c>
       <c r="R6" t="n">
-        <v>6787307</v>
+        <v>6787130</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1195,10 +1195,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129795298</v>
+        <v>129795283</v>
       </c>
       <c r="B7" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1224,16 +1224,19 @@
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>444305</v>
+        <v>444337</v>
       </c>
       <c r="R7" t="n">
-        <v>6787353</v>
+        <v>6787374</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1274,6 +1277,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1292,10 +1296,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129795285</v>
+        <v>129795291</v>
       </c>
       <c r="B8" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1327,10 +1331,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>444405</v>
+        <v>444412</v>
       </c>
       <c r="R8" t="n">
-        <v>6787405</v>
+        <v>6787307</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1389,10 +1393,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129795244</v>
+        <v>129795298</v>
       </c>
       <c r="B9" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1424,10 +1428,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>444105</v>
+        <v>444305</v>
       </c>
       <c r="R9" t="n">
-        <v>6787246</v>
+        <v>6787353</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1486,10 +1490,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129795261</v>
+        <v>129795285</v>
       </c>
       <c r="B10" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1521,10 +1525,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>444193</v>
+        <v>444405</v>
       </c>
       <c r="R10" t="n">
-        <v>6787130</v>
+        <v>6787405</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1583,10 +1587,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129795283</v>
+        <v>129795244</v>
       </c>
       <c r="B11" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1612,19 +1616,16 @@
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>444337</v>
+        <v>444105</v>
       </c>
       <c r="R11" t="n">
-        <v>6787374</v>
+        <v>6787246</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1665,7 +1666,6 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1684,43 +1684,37 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129795174</v>
+        <v>129795276</v>
       </c>
       <c r="B12" t="n">
-        <v>8451</v>
+        <v>79088</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1728,10 +1722,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>444166</v>
+        <v>444499</v>
       </c>
       <c r="R12" t="n">
-        <v>6787161</v>
+        <v>6787367</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1764,6 +1758,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-11-22</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 50m.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1791,54 +1790,45 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129795205</v>
+        <v>129795299</v>
       </c>
       <c r="B13" t="n">
-        <v>8451</v>
+        <v>79088</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>444343</v>
+        <v>444265</v>
       </c>
       <c r="R13" t="n">
-        <v>6787310</v>
+        <v>6787372</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1879,7 +1869,6 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -1898,10 +1887,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129795155</v>
+        <v>129795281</v>
       </c>
       <c r="B14" t="n">
-        <v>57737</v>
+        <v>79088</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1909,31 +1898,26 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -1941,10 +1925,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>444498</v>
+        <v>444408</v>
       </c>
       <c r="R14" t="n">
-        <v>6787306</v>
+        <v>6787452</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1985,6 +1969,7 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2003,10 +1988,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129795163</v>
+        <v>129795271</v>
       </c>
       <c r="B15" t="n">
-        <v>57737</v>
+        <v>79088</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2014,31 +1999,26 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2046,10 +2026,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>444415</v>
+        <v>444466</v>
       </c>
       <c r="R15" t="n">
-        <v>6787316</v>
+        <v>6787306</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2084,12 +2064,18 @@
           <t>2025-11-22</t>
         </is>
       </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 50m.</t>
+        </is>
+      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2108,7 +2094,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129795153</v>
+        <v>129795155</v>
       </c>
       <c r="B16" t="n">
         <v>57737</v>
@@ -2141,7 +2127,7 @@
       <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N16" t="inlineStr"/>
@@ -2151,10 +2137,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>444452</v>
+        <v>444498</v>
       </c>
       <c r="R16" t="n">
-        <v>6787294</v>
+        <v>6787306</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2213,10 +2199,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129795281</v>
+        <v>129795163</v>
       </c>
       <c r="B17" t="n">
-        <v>79087</v>
+        <v>57737</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2224,26 +2210,31 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2251,10 +2242,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>444408</v>
+        <v>444415</v>
       </c>
       <c r="R17" t="n">
-        <v>6787452</v>
+        <v>6787316</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2295,7 +2286,6 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2314,10 +2304,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129795271</v>
+        <v>129795153</v>
       </c>
       <c r="B18" t="n">
-        <v>79087</v>
+        <v>57737</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2325,26 +2315,31 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2352,10 +2347,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>444466</v>
+        <v>444452</v>
       </c>
       <c r="R18" t="n">
-        <v>6787306</v>
+        <v>6787294</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2390,18 +2385,12 @@
           <t>2025-11-22</t>
         </is>
       </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 50m.</t>
-        </is>
-      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2420,37 +2409,43 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129795276</v>
+        <v>129795174</v>
       </c>
       <c r="B19" t="n">
-        <v>79087</v>
+        <v>8451</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2458,10 +2453,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>444499</v>
+        <v>444166</v>
       </c>
       <c r="R19" t="n">
-        <v>6787367</v>
+        <v>6787161</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2494,11 +2489,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-11-22</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 50m.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2526,45 +2516,54 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129795299</v>
+        <v>129795205</v>
       </c>
       <c r="B20" t="n">
-        <v>79087</v>
+        <v>8451</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>444265</v>
+        <v>444343</v>
       </c>
       <c r="R20" t="n">
-        <v>6787372</v>
+        <v>6787310</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2605,6 +2604,7 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2626,7 +2626,7 @@
         <v>129795273</v>
       </c>
       <c r="B21" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2723,7 +2723,7 @@
         <v>129795265</v>
       </c>
       <c r="B22" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2817,10 +2817,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129795310</v>
+        <v>129795278</v>
       </c>
       <c r="B23" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2846,19 +2846,16 @@
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>444488</v>
+        <v>444465</v>
       </c>
       <c r="R23" t="n">
-        <v>6787445</v>
+        <v>6787451</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2893,18 +2890,12 @@
           <t>2025-11-22</t>
         </is>
       </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Gott om garnlav inom en radie av 40m</t>
-        </is>
-      </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -2923,10 +2914,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129795278</v>
+        <v>129795310</v>
       </c>
       <c r="B24" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2952,16 +2943,19 @@
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>444465</v>
+        <v>444488</v>
       </c>
       <c r="R24" t="n">
-        <v>6787451</v>
+        <v>6787445</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2996,12 +2990,18 @@
           <t>2025-11-22</t>
         </is>
       </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Gott om garnlav inom en radie av 40m</t>
+        </is>
+      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3448,10 +3448,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129795268</v>
+        <v>129795142</v>
       </c>
       <c r="B29" t="n">
-        <v>79087</v>
+        <v>57737</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3459,34 +3459,42 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>444383</v>
+        <v>444276</v>
       </c>
       <c r="R29" t="n">
-        <v>6787218</v>
+        <v>6787287</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3545,10 +3553,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129795256</v>
+        <v>129795268</v>
       </c>
       <c r="B30" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3580,10 +3588,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>444226</v>
+        <v>444383</v>
       </c>
       <c r="R30" t="n">
-        <v>6787196</v>
+        <v>6787218</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3642,54 +3650,45 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129795187</v>
+        <v>129795256</v>
       </c>
       <c r="B31" t="n">
-        <v>8451</v>
+        <v>79088</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>444487</v>
+        <v>444226</v>
       </c>
       <c r="R31" t="n">
-        <v>6787321</v>
+        <v>6787196</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3730,7 +3729,6 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
-      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
@@ -3749,7 +3747,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129795189</v>
+        <v>129795187</v>
       </c>
       <c r="B32" t="n">
         <v>8451</v>
@@ -3793,10 +3791,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>444500</v>
+        <v>444487</v>
       </c>
       <c r="R32" t="n">
-        <v>6787274</v>
+        <v>6787321</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3856,7 +3854,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129795176</v>
+        <v>129795189</v>
       </c>
       <c r="B33" t="n">
         <v>8451</v>
@@ -3890,7 +3888,7 @@
       <c r="L33" t="inlineStr"/>
       <c r="M33" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N33" t="inlineStr"/>
@@ -3900,10 +3898,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>444215</v>
+        <v>444500</v>
       </c>
       <c r="R33" t="n">
-        <v>6787151</v>
+        <v>6787274</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3963,40 +3961,41 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129795142</v>
+        <v>129795176</v>
       </c>
       <c r="B34" t="n">
-        <v>57737</v>
+        <v>8451</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="N34" t="inlineStr"/>
@@ -4006,10 +4005,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>444276</v>
+        <v>444215</v>
       </c>
       <c r="R34" t="n">
-        <v>6787287</v>
+        <v>6787151</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4050,6 +4049,7 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
+      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
@@ -4068,10 +4068,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129795133</v>
+        <v>129795270</v>
       </c>
       <c r="B35" t="n">
-        <v>57898</v>
+        <v>79088</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4079,42 +4079,34 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>444226</v>
+        <v>444416</v>
       </c>
       <c r="R35" t="n">
-        <v>6787236</v>
+        <v>6787260</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4173,43 +4165,37 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129795193</v>
+        <v>129795296</v>
       </c>
       <c r="B36" t="n">
-        <v>8451</v>
+        <v>79088</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
@@ -4217,10 +4203,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>444508</v>
+        <v>444299</v>
       </c>
       <c r="R36" t="n">
-        <v>6787352</v>
+        <v>6787304</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4253,6 +4239,11 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-11-22</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 50 m.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4280,54 +4271,45 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129795202</v>
+        <v>129795269</v>
       </c>
       <c r="B37" t="n">
-        <v>8451</v>
+        <v>79088</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
-      <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>444413</v>
+        <v>444429</v>
       </c>
       <c r="R37" t="n">
-        <v>6787314</v>
+        <v>6787240</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4368,7 +4350,6 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
-      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -4387,10 +4368,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129795165</v>
+        <v>129795249</v>
       </c>
       <c r="B38" t="n">
-        <v>57737</v>
+        <v>79088</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4398,42 +4379,34 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>444251</v>
+        <v>444267</v>
       </c>
       <c r="R38" t="n">
-        <v>6787376</v>
+        <v>6787295</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4492,10 +4465,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129795270</v>
+        <v>129795165</v>
       </c>
       <c r="B39" t="n">
-        <v>79087</v>
+        <v>57737</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4503,34 +4476,42 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>444416</v>
+        <v>444251</v>
       </c>
       <c r="R39" t="n">
-        <v>6787260</v>
+        <v>6787376</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4589,37 +4570,43 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129795296</v>
+        <v>129795193</v>
       </c>
       <c r="B40" t="n">
-        <v>79087</v>
+        <v>8451</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
@@ -4627,10 +4614,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>444299</v>
+        <v>444508</v>
       </c>
       <c r="R40" t="n">
-        <v>6787304</v>
+        <v>6787352</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4663,11 +4650,6 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-11-22</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 50 m.</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4695,45 +4677,54 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129795269</v>
+        <v>129795202</v>
       </c>
       <c r="B41" t="n">
-        <v>79087</v>
+        <v>8451</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>444429</v>
+        <v>444413</v>
       </c>
       <c r="R41" t="n">
-        <v>6787240</v>
+        <v>6787314</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4774,6 +4765,7 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
+      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
@@ -4792,10 +4784,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129795249</v>
+        <v>129795133</v>
       </c>
       <c r="B42" t="n">
-        <v>79087</v>
+        <v>57898</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4803,34 +4795,42 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>444267</v>
+        <v>444226</v>
       </c>
       <c r="R42" t="n">
-        <v>6787295</v>
+        <v>6787236</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4889,54 +4889,45 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129795170</v>
+        <v>129795293</v>
       </c>
       <c r="B43" t="n">
-        <v>8451</v>
+        <v>79088</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="J43" t="inlineStr"/>
-      <c r="K43" t="inlineStr"/>
-      <c r="L43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>444172</v>
+        <v>444365</v>
       </c>
       <c r="R43" t="n">
-        <v>6787202</v>
+        <v>6787285</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4971,13 +4962,17 @@
           <t>2025-11-22</t>
         </is>
       </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 50m.</t>
+        </is>
+      </c>
       <c r="AD43" t="b">
         <v>0</v>
       </c>
       <c r="AE43" t="b">
         <v>0</v>
       </c>
-      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
@@ -4996,10 +4991,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129795158</v>
+        <v>129795136</v>
       </c>
       <c r="B44" t="n">
-        <v>57737</v>
+        <v>91627</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5007,31 +5002,26 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100049</v>
+        <v>5442</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr"/>
       <c r="K44" t="inlineStr"/>
-      <c r="L44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
@@ -5039,10 +5029,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>444501</v>
+        <v>444235</v>
       </c>
       <c r="R44" t="n">
-        <v>6787402</v>
+        <v>6787149</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5083,6 +5073,7 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
+      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
@@ -5101,10 +5092,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129795136</v>
+        <v>129795282</v>
       </c>
       <c r="B45" t="n">
-        <v>91626</v>
+        <v>79088</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5112,21 +5103,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5139,10 +5130,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>444235</v>
+        <v>444374</v>
       </c>
       <c r="R45" t="n">
-        <v>6787149</v>
+        <v>6787384</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5175,6 +5166,11 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-11-22</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 50 m.</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5202,10 +5198,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129795282</v>
+        <v>129795158</v>
       </c>
       <c r="B46" t="n">
-        <v>79087</v>
+        <v>57737</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5213,26 +5209,31 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="J46" t="inlineStr"/>
       <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
@@ -5240,10 +5241,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>444374</v>
+        <v>444501</v>
       </c>
       <c r="R46" t="n">
-        <v>6787384</v>
+        <v>6787402</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5278,18 +5279,12 @@
           <t>2025-11-22</t>
         </is>
       </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 50 m.</t>
-        </is>
-      </c>
       <c r="AD46" t="b">
         <v>0</v>
       </c>
       <c r="AE46" t="b">
         <v>0</v>
       </c>
-      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
@@ -5308,45 +5303,54 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129795293</v>
+        <v>129795170</v>
       </c>
       <c r="B47" t="n">
-        <v>79087</v>
+        <v>8451</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr"/>
+      <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>444365</v>
+        <v>444172</v>
       </c>
       <c r="R47" t="n">
-        <v>6787285</v>
+        <v>6787202</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5381,17 +5385,13 @@
           <t>2025-11-22</t>
         </is>
       </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 50m.</t>
-        </is>
-      </c>
       <c r="AD47" t="b">
         <v>0</v>
       </c>
       <c r="AE47" t="b">
         <v>0</v>
       </c>
+      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
@@ -5413,7 +5413,7 @@
         <v>129795138</v>
       </c>
       <c r="B48" t="n">
-        <v>91626</v>
+        <v>91627</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5514,7 +5514,7 @@
         <v>129795309</v>
       </c>
       <c r="B49" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5613,10 +5613,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129795260</v>
+        <v>129795246</v>
       </c>
       <c r="B50" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5648,10 +5648,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>444197</v>
+        <v>444145</v>
       </c>
       <c r="R50" t="n">
-        <v>6787111</v>
+        <v>6787239</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5684,6 +5684,11 @@
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-11-22</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 40m.</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5710,10 +5715,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129795250</v>
+        <v>129795260</v>
       </c>
       <c r="B51" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5745,10 +5750,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>444295</v>
+        <v>444197</v>
       </c>
       <c r="R51" t="n">
-        <v>6787287</v>
+        <v>6787111</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5807,10 +5812,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129795246</v>
+        <v>129795250</v>
       </c>
       <c r="B52" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5842,10 +5847,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>444145</v>
+        <v>444295</v>
       </c>
       <c r="R52" t="n">
-        <v>6787239</v>
+        <v>6787287</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5878,11 +5883,6 @@
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-11-22</t>
-        </is>
-      </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 40m.</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -5909,10 +5909,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129795161</v>
+        <v>129795277</v>
       </c>
       <c r="B53" t="n">
-        <v>57737</v>
+        <v>79088</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5920,42 +5920,34 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="K53" t="inlineStr"/>
-      <c r="L53" t="inlineStr"/>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>444433</v>
+        <v>444491</v>
       </c>
       <c r="R53" t="n">
-        <v>6787338</v>
+        <v>6787412</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6014,10 +6006,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129795147</v>
+        <v>129795279</v>
       </c>
       <c r="B54" t="n">
-        <v>57737</v>
+        <v>79088</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6025,42 +6017,34 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
-      <c r="K54" t="inlineStr"/>
-      <c r="L54" t="inlineStr"/>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>444220</v>
+        <v>444463</v>
       </c>
       <c r="R54" t="n">
-        <v>6787221</v>
+        <v>6787459</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6119,10 +6103,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129795134</v>
+        <v>129795161</v>
       </c>
       <c r="B55" t="n">
-        <v>57898</v>
+        <v>57737</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6130,21 +6114,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6152,7 +6136,7 @@
       <c r="L55" t="inlineStr"/>
       <c r="M55" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N55" t="inlineStr"/>
@@ -6162,10 +6146,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>444289</v>
+        <v>444433</v>
       </c>
       <c r="R55" t="n">
-        <v>6787357</v>
+        <v>6787338</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6224,41 +6208,40 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129795184</v>
+        <v>129795147</v>
       </c>
       <c r="B56" t="n">
-        <v>8451</v>
+        <v>57737</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
-      <c r="J56" t="inlineStr"/>
       <c r="K56" t="inlineStr"/>
       <c r="L56" t="inlineStr"/>
       <c r="M56" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N56" t="inlineStr"/>
@@ -6268,10 +6251,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>444452</v>
+        <v>444220</v>
       </c>
       <c r="R56" t="n">
-        <v>6787305</v>
+        <v>6787221</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6312,7 +6295,6 @@
       <c r="AE56" t="b">
         <v>0</v>
       </c>
-      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
       </c>
@@ -6331,10 +6313,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129795172</v>
+        <v>129795131</v>
       </c>
       <c r="B57" t="n">
-        <v>8451</v>
+        <v>56930</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6342,30 +6324,29 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>106545</v>
+        <v>100138</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
-      <c r="J57" t="inlineStr"/>
       <c r="K57" t="inlineStr"/>
       <c r="L57" t="inlineStr"/>
       <c r="M57" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="N57" t="inlineStr"/>
@@ -6375,10 +6356,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>444225</v>
+        <v>444250</v>
       </c>
       <c r="R57" t="n">
-        <v>6787223</v>
+        <v>6787212</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6419,7 +6400,6 @@
       <c r="AE57" t="b">
         <v>0</v>
       </c>
-      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
@@ -6438,41 +6418,40 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129795199</v>
+        <v>129795134</v>
       </c>
       <c r="B58" t="n">
-        <v>8451</v>
+        <v>57898</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>106545</v>
+        <v>103021</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
-      <c r="J58" t="inlineStr"/>
       <c r="K58" t="inlineStr"/>
       <c r="L58" t="inlineStr"/>
       <c r="M58" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N58" t="inlineStr"/>
@@ -6482,10 +6461,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>444431</v>
+        <v>444289</v>
       </c>
       <c r="R58" t="n">
-        <v>6787350</v>
+        <v>6787357</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6526,7 +6505,6 @@
       <c r="AE58" t="b">
         <v>0</v>
       </c>
-      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
       </c>
@@ -6545,45 +6523,54 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129795277</v>
+        <v>129795184</v>
       </c>
       <c r="B59" t="n">
-        <v>79087</v>
+        <v>8451</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
+      <c r="J59" t="inlineStr"/>
+      <c r="K59" t="inlineStr"/>
+      <c r="L59" t="inlineStr"/>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>444491</v>
+        <v>444452</v>
       </c>
       <c r="R59" t="n">
-        <v>6787412</v>
+        <v>6787305</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6624,6 +6611,7 @@
       <c r="AE59" t="b">
         <v>0</v>
       </c>
+      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
       </c>
@@ -6642,45 +6630,54 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129795279</v>
+        <v>129795172</v>
       </c>
       <c r="B60" t="n">
-        <v>79087</v>
+        <v>8451</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
+      <c r="J60" t="inlineStr"/>
+      <c r="K60" t="inlineStr"/>
+      <c r="L60" t="inlineStr"/>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>444463</v>
+        <v>444225</v>
       </c>
       <c r="R60" t="n">
-        <v>6787459</v>
+        <v>6787223</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6721,6 +6718,7 @@
       <c r="AE60" t="b">
         <v>0</v>
       </c>
+      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
       </c>
@@ -6739,10 +6737,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129795131</v>
+        <v>129795199</v>
       </c>
       <c r="B61" t="n">
-        <v>56930</v>
+        <v>8451</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6750,29 +6748,30 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>100138</v>
+        <v>106545</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
+      <c r="J61" t="inlineStr"/>
       <c r="K61" t="inlineStr"/>
       <c r="L61" t="inlineStr"/>
       <c r="M61" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N61" t="inlineStr"/>
@@ -6782,10 +6781,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>444250</v>
+        <v>444431</v>
       </c>
       <c r="R61" t="n">
-        <v>6787212</v>
+        <v>6787350</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6826,6 +6825,7 @@
       <c r="AE61" t="b">
         <v>0</v>
       </c>
+      <c r="AF61" t="inlineStr"/>
       <c r="AG61" t="b">
         <v>0</v>
       </c>
@@ -6844,45 +6844,54 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129795125</v>
+        <v>129795191</v>
       </c>
       <c r="B62" t="n">
-        <v>79706</v>
+        <v>8451</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
+      <c r="J62" t="inlineStr"/>
+      <c r="K62" t="inlineStr"/>
+      <c r="L62" t="inlineStr"/>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>444329</v>
+        <v>444520</v>
       </c>
       <c r="R62" t="n">
-        <v>6787371</v>
+        <v>6787287</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6923,6 +6932,7 @@
       <c r="AE62" t="b">
         <v>0</v>
       </c>
+      <c r="AF62" t="inlineStr"/>
       <c r="AG62" t="b">
         <v>0</v>
       </c>
@@ -6941,40 +6951,41 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129795162</v>
+        <v>129795195</v>
       </c>
       <c r="B63" t="n">
-        <v>57737</v>
+        <v>8451</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
+      <c r="J63" t="inlineStr"/>
       <c r="K63" t="inlineStr"/>
       <c r="L63" t="inlineStr"/>
       <c r="M63" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N63" t="inlineStr"/>
@@ -6984,10 +6995,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>444428</v>
+        <v>444487</v>
       </c>
       <c r="R63" t="n">
-        <v>6787329</v>
+        <v>6787441</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7028,6 +7039,7 @@
       <c r="AE63" t="b">
         <v>0</v>
       </c>
+      <c r="AF63" t="inlineStr"/>
       <c r="AG63" t="b">
         <v>0</v>
       </c>
@@ -7046,7 +7058,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129795191</v>
+        <v>129795177</v>
       </c>
       <c r="B64" t="n">
         <v>8451</v>
@@ -7080,7 +7092,7 @@
       <c r="L64" t="inlineStr"/>
       <c r="M64" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="N64" t="inlineStr"/>
@@ -7090,10 +7102,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>444520</v>
+        <v>444342</v>
       </c>
       <c r="R64" t="n">
-        <v>6787287</v>
+        <v>6787223</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7153,41 +7165,40 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129795195</v>
+        <v>129795162</v>
       </c>
       <c r="B65" t="n">
-        <v>8451</v>
+        <v>57737</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
-      <c r="J65" t="inlineStr"/>
       <c r="K65" t="inlineStr"/>
       <c r="L65" t="inlineStr"/>
       <c r="M65" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N65" t="inlineStr"/>
@@ -7197,10 +7208,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>444487</v>
+        <v>444428</v>
       </c>
       <c r="R65" t="n">
-        <v>6787441</v>
+        <v>6787329</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7241,7 +7252,6 @@
       <c r="AE65" t="b">
         <v>0</v>
       </c>
-      <c r="AF65" t="inlineStr"/>
       <c r="AG65" t="b">
         <v>0</v>
       </c>
@@ -7260,54 +7270,45 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129795177</v>
+        <v>129795125</v>
       </c>
       <c r="B66" t="n">
-        <v>8451</v>
+        <v>79707</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
-      <c r="J66" t="inlineStr"/>
-      <c r="K66" t="inlineStr"/>
-      <c r="L66" t="inlineStr"/>
-      <c r="M66" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>444342</v>
+        <v>444329</v>
       </c>
       <c r="R66" t="n">
-        <v>6787223</v>
+        <v>6787371</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7348,7 +7349,6 @@
       <c r="AE66" t="b">
         <v>0</v>
       </c>
-      <c r="AF66" t="inlineStr"/>
       <c r="AG66" t="b">
         <v>0</v>
       </c>
@@ -7367,10 +7367,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129795150</v>
+        <v>129795257</v>
       </c>
       <c r="B67" t="n">
-        <v>57737</v>
+        <v>79088</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7378,42 +7378,34 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
-      <c r="K67" t="inlineStr"/>
-      <c r="L67" t="inlineStr"/>
-      <c r="M67" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>444413</v>
+        <v>444168</v>
       </c>
       <c r="R67" t="n">
-        <v>6787222</v>
+        <v>6787171</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7472,10 +7464,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129795257</v>
+        <v>129795150</v>
       </c>
       <c r="B68" t="n">
-        <v>79087</v>
+        <v>57737</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7483,34 +7475,42 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
+      <c r="K68" t="inlineStr"/>
+      <c r="L68" t="inlineStr"/>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>444168</v>
+        <v>444413</v>
       </c>
       <c r="R68" t="n">
-        <v>6787171</v>
+        <v>6787222</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7569,42 +7569,37 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129795208</v>
+        <v>129795135</v>
       </c>
       <c r="B69" t="n">
-        <v>58111</v>
+        <v>91627</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>103015</v>
+        <v>5442</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
+      <c r="J69" t="inlineStr"/>
       <c r="K69" t="inlineStr"/>
-      <c r="L69" t="inlineStr"/>
-      <c r="M69" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
@@ -7612,10 +7607,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>444434</v>
+        <v>444158</v>
       </c>
       <c r="R69" t="n">
-        <v>6787357</v>
+        <v>6787148</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7656,6 +7651,7 @@
       <c r="AE69" t="b">
         <v>0</v>
       </c>
+      <c r="AF69" t="inlineStr"/>
       <c r="AG69" t="b">
         <v>0</v>
       </c>
@@ -7674,54 +7670,45 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129795182</v>
+        <v>129795280</v>
       </c>
       <c r="B70" t="n">
-        <v>8451</v>
+        <v>79088</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
-      <c r="J70" t="inlineStr"/>
-      <c r="K70" t="inlineStr"/>
-      <c r="L70" t="inlineStr"/>
-      <c r="M70" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>444417</v>
+        <v>444451</v>
       </c>
       <c r="R70" t="n">
-        <v>6787266</v>
+        <v>6787467</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7762,7 +7749,6 @@
       <c r="AE70" t="b">
         <v>0</v>
       </c>
-      <c r="AF70" t="inlineStr"/>
       <c r="AG70" t="b">
         <v>0</v>
       </c>
@@ -7781,10 +7767,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129795280</v>
+        <v>129795272</v>
       </c>
       <c r="B71" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7816,10 +7802,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>444451</v>
+        <v>444553</v>
       </c>
       <c r="R71" t="n">
-        <v>6787467</v>
+        <v>6787299</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7878,10 +7864,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129795135</v>
+        <v>129795287</v>
       </c>
       <c r="B72" t="n">
-        <v>91626</v>
+        <v>79088</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7889,37 +7875,34 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
-      <c r="J72" t="inlineStr"/>
-      <c r="K72" t="inlineStr"/>
-      <c r="N72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>444158</v>
+        <v>444430</v>
       </c>
       <c r="R72" t="n">
-        <v>6787148</v>
+        <v>6787384</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7960,7 +7943,6 @@
       <c r="AE72" t="b">
         <v>0</v>
       </c>
-      <c r="AF72" t="inlineStr"/>
       <c r="AG72" t="b">
         <v>0</v>
       </c>
@@ -7979,10 +7961,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129795272</v>
+        <v>129795284</v>
       </c>
       <c r="B73" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8014,10 +7996,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>444553</v>
+        <v>444363</v>
       </c>
       <c r="R73" t="n">
-        <v>6787299</v>
+        <v>6787411</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8076,10 +8058,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129795287</v>
+        <v>129795243</v>
       </c>
       <c r="B74" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8111,10 +8093,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>444430</v>
+        <v>444159</v>
       </c>
       <c r="R74" t="n">
-        <v>6787384</v>
+        <v>6787297</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8173,10 +8155,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129795284</v>
+        <v>129795166</v>
       </c>
       <c r="B75" t="n">
-        <v>79087</v>
+        <v>57737</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8184,34 +8166,42 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
+      <c r="K75" t="inlineStr"/>
+      <c r="L75" t="inlineStr"/>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>444363</v>
+        <v>444254</v>
       </c>
       <c r="R75" t="n">
-        <v>6787411</v>
+        <v>6787333</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8270,45 +8260,53 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129795243</v>
+        <v>129795208</v>
       </c>
       <c r="B76" t="n">
-        <v>79087</v>
+        <v>58111</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6425</v>
+        <v>103015</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
+      <c r="K76" t="inlineStr"/>
+      <c r="L76" t="inlineStr"/>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>444159</v>
+        <v>444434</v>
       </c>
       <c r="R76" t="n">
-        <v>6787297</v>
+        <v>6787357</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8367,40 +8365,41 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129795166</v>
+        <v>129795182</v>
       </c>
       <c r="B77" t="n">
-        <v>57737</v>
+        <v>8451</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
+      <c r="J77" t="inlineStr"/>
       <c r="K77" t="inlineStr"/>
       <c r="L77" t="inlineStr"/>
       <c r="M77" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N77" t="inlineStr"/>
@@ -8410,10 +8409,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>444254</v>
+        <v>444417</v>
       </c>
       <c r="R77" t="n">
-        <v>6787333</v>
+        <v>6787266</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8454,6 +8453,7 @@
       <c r="AE77" t="b">
         <v>0</v>
       </c>
+      <c r="AF77" t="inlineStr"/>
       <c r="AG77" t="b">
         <v>0</v>
       </c>
@@ -8475,7 +8475,7 @@
         <v>129795126</v>
       </c>
       <c r="B78" t="n">
-        <v>79706</v>
+        <v>79707</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8572,7 +8572,7 @@
         <v>129795300</v>
       </c>
       <c r="B79" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8675,10 +8675,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129795307</v>
+        <v>129795127</v>
       </c>
       <c r="B80" t="n">
-        <v>79087</v>
+        <v>79707</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8686,21 +8686,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8710,10 +8710,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>444134</v>
+        <v>444432</v>
       </c>
       <c r="R80" t="n">
-        <v>6787304</v>
+        <v>6787388</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8772,10 +8772,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129795241</v>
+        <v>129795307</v>
       </c>
       <c r="B81" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8807,10 +8807,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>444117</v>
+        <v>444134</v>
       </c>
       <c r="R81" t="n">
-        <v>6787277</v>
+        <v>6787304</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8869,10 +8869,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129795127</v>
+        <v>129795286</v>
       </c>
       <c r="B82" t="n">
-        <v>79706</v>
+        <v>79088</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8880,31 +8880,34 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
+      <c r="J82" t="inlineStr"/>
+      <c r="K82" t="inlineStr"/>
+      <c r="N82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>444432</v>
+        <v>444440</v>
       </c>
       <c r="R82" t="n">
         <v>6787388</v>
@@ -8942,12 +8945,18 @@
           <t>2025-11-22</t>
         </is>
       </c>
+      <c r="AC82" t="inlineStr">
+        <is>
+          <t>Gott om garnlav inom en radie av 50 m.</t>
+        </is>
+      </c>
       <c r="AD82" t="b">
         <v>0</v>
       </c>
       <c r="AE82" t="b">
         <v>0</v>
       </c>
+      <c r="AF82" t="inlineStr"/>
       <c r="AG82" t="b">
         <v>0</v>
       </c>
@@ -8966,10 +8975,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129795286</v>
+        <v>129795241</v>
       </c>
       <c r="B83" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8995,19 +9004,16 @@
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
-      <c r="J83" t="inlineStr"/>
-      <c r="K83" t="inlineStr"/>
-      <c r="N83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>444440</v>
+        <v>444117</v>
       </c>
       <c r="R83" t="n">
-        <v>6787388</v>
+        <v>6787277</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9042,18 +9048,12 @@
           <t>2025-11-22</t>
         </is>
       </c>
-      <c r="AC83" t="inlineStr">
-        <is>
-          <t>Gott om garnlav inom en radie av 50 m.</t>
-        </is>
-      </c>
       <c r="AD83" t="b">
         <v>0</v>
       </c>
       <c r="AE83" t="b">
         <v>0</v>
       </c>
-      <c r="AF83" t="inlineStr"/>
       <c r="AG83" t="b">
         <v>0</v>
       </c>
@@ -9289,7 +9289,7 @@
         <v>129795308</v>
       </c>
       <c r="B86" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9386,7 +9386,7 @@
         <v>129795242</v>
       </c>
       <c r="B87" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9480,7 +9480,7 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129795192</v>
+        <v>129795181</v>
       </c>
       <c r="B88" t="n">
         <v>8451</v>
@@ -9524,10 +9524,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>444549</v>
+        <v>444408</v>
       </c>
       <c r="R88" t="n">
-        <v>6787335</v>
+        <v>6787250</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9587,7 +9587,7 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>129795181</v>
+        <v>129795192</v>
       </c>
       <c r="B89" t="n">
         <v>8451</v>
@@ -9631,10 +9631,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>444408</v>
+        <v>444549</v>
       </c>
       <c r="R89" t="n">
-        <v>6787250</v>
+        <v>6787335</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9694,10 +9694,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>129795152</v>
+        <v>129795305</v>
       </c>
       <c r="B90" t="n">
-        <v>57737</v>
+        <v>79088</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9705,42 +9705,34 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
-      <c r="K90" t="inlineStr"/>
-      <c r="L90" t="inlineStr"/>
-      <c r="M90" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>444434</v>
+        <v>444169</v>
       </c>
       <c r="R90" t="n">
-        <v>6787304</v>
+        <v>6787323</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9799,10 +9791,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>129795305</v>
+        <v>129795245</v>
       </c>
       <c r="B91" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9834,10 +9826,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>444169</v>
+        <v>444113</v>
       </c>
       <c r="R91" t="n">
-        <v>6787323</v>
+        <v>6787239</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9896,10 +9888,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>129795288</v>
+        <v>129795297</v>
       </c>
       <c r="B92" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9931,10 +9923,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>444420</v>
+        <v>444297</v>
       </c>
       <c r="R92" t="n">
-        <v>6787366</v>
+        <v>6787333</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9993,10 +9985,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>129795245</v>
+        <v>129795262</v>
       </c>
       <c r="B93" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10028,10 +10020,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>444113</v>
+        <v>444219</v>
       </c>
       <c r="R93" t="n">
-        <v>6787239</v>
+        <v>6787163</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10090,10 +10082,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>129795123</v>
+        <v>129795252</v>
       </c>
       <c r="B94" t="n">
-        <v>79706</v>
+        <v>79088</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10101,21 +10093,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -10125,10 +10117,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>444530</v>
+        <v>444249</v>
       </c>
       <c r="R94" t="n">
-        <v>6787326</v>
+        <v>6787249</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10161,6 +10153,11 @@
       <c r="AA94" t="inlineStr">
         <is>
           <t>2025-11-22</t>
+        </is>
+      </c>
+      <c r="AC94" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 40m.</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10187,10 +10184,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>129795297</v>
+        <v>129795152</v>
       </c>
       <c r="B95" t="n">
-        <v>79087</v>
+        <v>57737</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10198,34 +10195,42 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
+      <c r="K95" t="inlineStr"/>
+      <c r="L95" t="inlineStr"/>
+      <c r="M95" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>444297</v>
+        <v>444434</v>
       </c>
       <c r="R95" t="n">
-        <v>6787333</v>
+        <v>6787304</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10284,10 +10289,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>129795262</v>
+        <v>129795121</v>
       </c>
       <c r="B96" t="n">
-        <v>79087</v>
+        <v>79707</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10295,21 +10300,21 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10319,10 +10324,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>444219</v>
+        <v>444254</v>
       </c>
       <c r="R96" t="n">
-        <v>6787163</v>
+        <v>6787204</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10381,10 +10386,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>129795252</v>
+        <v>129795124</v>
       </c>
       <c r="B97" t="n">
-        <v>79087</v>
+        <v>79707</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10392,21 +10397,21 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -10416,10 +10421,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>444249</v>
+        <v>444393</v>
       </c>
       <c r="R97" t="n">
-        <v>6787249</v>
+        <v>6787395</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10452,11 +10457,6 @@
       <c r="AA97" t="inlineStr">
         <is>
           <t>2025-11-22</t>
-        </is>
-      </c>
-      <c r="AC97" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 40m.</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -10483,54 +10483,45 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>129795167</v>
+        <v>129795123</v>
       </c>
       <c r="B98" t="n">
-        <v>8451</v>
+        <v>79707</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
-      <c r="J98" t="inlineStr"/>
-      <c r="K98" t="inlineStr"/>
-      <c r="L98" t="inlineStr"/>
-      <c r="M98" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>444132</v>
+        <v>444530</v>
       </c>
       <c r="R98" t="n">
-        <v>6787237</v>
+        <v>6787326</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10571,7 +10562,6 @@
       <c r="AE98" t="b">
         <v>0</v>
       </c>
-      <c r="AF98" t="inlineStr"/>
       <c r="AG98" t="b">
         <v>0</v>
       </c>
@@ -10590,45 +10580,54 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>129795121</v>
+        <v>129795167</v>
       </c>
       <c r="B99" t="n">
-        <v>79706</v>
+        <v>8451</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
+      <c r="J99" t="inlineStr"/>
+      <c r="K99" t="inlineStr"/>
+      <c r="L99" t="inlineStr"/>
+      <c r="M99" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>444254</v>
+        <v>444132</v>
       </c>
       <c r="R99" t="n">
-        <v>6787204</v>
+        <v>6787237</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10669,6 +10668,7 @@
       <c r="AE99" t="b">
         <v>0</v>
       </c>
+      <c r="AF99" t="inlineStr"/>
       <c r="AG99" t="b">
         <v>0</v>
       </c>
@@ -10687,10 +10687,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>129795124</v>
+        <v>129795288</v>
       </c>
       <c r="B100" t="n">
-        <v>79706</v>
+        <v>79088</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10698,21 +10698,21 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -10722,10 +10722,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>444393</v>
+        <v>444420</v>
       </c>
       <c r="R100" t="n">
-        <v>6787395</v>
+        <v>6787366</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10787,7 +10787,7 @@
         <v>129795264</v>
       </c>
       <c r="B101" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -10884,7 +10884,7 @@
         <v>129795248</v>
       </c>
       <c r="B102" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -10981,7 +10981,7 @@
         <v>129795303</v>
       </c>
       <c r="B103" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11078,7 +11078,7 @@
         <v>129795306</v>
       </c>
       <c r="B104" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11707,10 +11707,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>129795149</v>
+        <v>129795259</v>
       </c>
       <c r="B110" t="n">
-        <v>57737</v>
+        <v>79088</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -11718,42 +11718,34 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
-      <c r="K110" t="inlineStr"/>
-      <c r="L110" t="inlineStr"/>
-      <c r="M110" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N110" t="inlineStr"/>
       <c r="P110" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>444223</v>
+        <v>444164</v>
       </c>
       <c r="R110" t="n">
-        <v>6787221</v>
+        <v>6787121</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11812,7 +11804,7 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>129795145</v>
+        <v>129795149</v>
       </c>
       <c r="B111" t="n">
         <v>57737</v>
@@ -11845,7 +11837,7 @@
       <c r="L111" t="inlineStr"/>
       <c r="M111" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N111" t="inlineStr"/>
@@ -11855,10 +11847,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>444228</v>
+        <v>444223</v>
       </c>
       <c r="R111" t="n">
-        <v>6787226</v>
+        <v>6787221</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -11917,7 +11909,7 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>129795151</v>
+        <v>129795145</v>
       </c>
       <c r="B112" t="n">
         <v>57737</v>
@@ -11960,10 +11952,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>444425</v>
+        <v>444228</v>
       </c>
       <c r="R112" t="n">
-        <v>6787278</v>
+        <v>6787226</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12022,10 +12014,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>129795259</v>
+        <v>129795151</v>
       </c>
       <c r="B113" t="n">
-        <v>79087</v>
+        <v>57737</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -12033,34 +12025,42 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
+      <c r="K113" t="inlineStr"/>
+      <c r="L113" t="inlineStr"/>
+      <c r="M113" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N113" t="inlineStr"/>
       <c r="P113" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>444164</v>
+        <v>444425</v>
       </c>
       <c r="R113" t="n">
-        <v>6787121</v>
+        <v>6787278</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12333,41 +12333,40 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>129795171</v>
+        <v>129795164</v>
       </c>
       <c r="B116" t="n">
-        <v>8451</v>
+        <v>57737</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
-      <c r="J116" t="inlineStr"/>
       <c r="K116" t="inlineStr"/>
       <c r="L116" t="inlineStr"/>
       <c r="M116" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N116" t="inlineStr"/>
@@ -12377,10 +12376,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>444185</v>
+        <v>444397</v>
       </c>
       <c r="R116" t="n">
-        <v>6787226</v>
+        <v>6787300</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12421,7 +12420,6 @@
       <c r="AE116" t="b">
         <v>0</v>
       </c>
-      <c r="AF116" t="inlineStr"/>
       <c r="AG116" t="b">
         <v>0</v>
       </c>
@@ -12440,7 +12438,7 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>129795164</v>
+        <v>129795154</v>
       </c>
       <c r="B117" t="n">
         <v>57737</v>
@@ -12483,10 +12481,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>444397</v>
+        <v>444457</v>
       </c>
       <c r="R117" t="n">
-        <v>6787300</v>
+        <v>6787303</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12545,7 +12543,7 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>129795154</v>
+        <v>129795157</v>
       </c>
       <c r="B118" t="n">
         <v>57737</v>
@@ -12588,10 +12586,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>444457</v>
+        <v>444525</v>
       </c>
       <c r="R118" t="n">
-        <v>6787303</v>
+        <v>6787344</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12650,10 +12648,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>129795157</v>
+        <v>129795289</v>
       </c>
       <c r="B119" t="n">
-        <v>57737</v>
+        <v>79088</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -12661,42 +12659,34 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
-      <c r="K119" t="inlineStr"/>
-      <c r="L119" t="inlineStr"/>
-      <c r="M119" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N119" t="inlineStr"/>
       <c r="P119" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>444525</v>
+        <v>444435</v>
       </c>
       <c r="R119" t="n">
-        <v>6787344</v>
+        <v>6787341</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -12860,45 +12850,54 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>129795289</v>
+        <v>129795171</v>
       </c>
       <c r="B121" t="n">
-        <v>79087</v>
+        <v>8451</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
+      <c r="J121" t="inlineStr"/>
+      <c r="K121" t="inlineStr"/>
+      <c r="L121" t="inlineStr"/>
+      <c r="M121" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N121" t="inlineStr"/>
       <c r="P121" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>444435</v>
+        <v>444185</v>
       </c>
       <c r="R121" t="n">
-        <v>6787341</v>
+        <v>6787226</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -12939,6 +12938,7 @@
       <c r="AE121" t="b">
         <v>0</v>
       </c>
+      <c r="AF121" t="inlineStr"/>
       <c r="AG121" t="b">
         <v>0</v>
       </c>
@@ -12957,40 +12957,41 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>129795144</v>
+        <v>129795188</v>
       </c>
       <c r="B122" t="n">
-        <v>57737</v>
+        <v>8451</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
+      <c r="J122" t="inlineStr"/>
       <c r="K122" t="inlineStr"/>
       <c r="L122" t="inlineStr"/>
       <c r="M122" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N122" t="inlineStr"/>
@@ -13000,10 +13001,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>444186</v>
+        <v>444498</v>
       </c>
       <c r="R122" t="n">
-        <v>6787223</v>
+        <v>6787280</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -13044,6 +13045,7 @@
       <c r="AE122" t="b">
         <v>0</v>
       </c>
+      <c r="AF122" t="inlineStr"/>
       <c r="AG122" t="b">
         <v>0</v>
       </c>
@@ -13062,45 +13064,54 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>129795301</v>
+        <v>129795179</v>
       </c>
       <c r="B123" t="n">
-        <v>79087</v>
+        <v>8451</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
+      <c r="J123" t="inlineStr"/>
+      <c r="K123" t="inlineStr"/>
+      <c r="L123" t="inlineStr"/>
+      <c r="M123" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N123" t="inlineStr"/>
       <c r="P123" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>444250</v>
+        <v>444378</v>
       </c>
       <c r="R123" t="n">
-        <v>6787342</v>
+        <v>6787236</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13141,6 +13152,7 @@
       <c r="AE123" t="b">
         <v>0</v>
       </c>
+      <c r="AF123" t="inlineStr"/>
       <c r="AG123" t="b">
         <v>0</v>
       </c>
@@ -13159,10 +13171,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>129795294</v>
+        <v>129795301</v>
       </c>
       <c r="B124" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -13194,10 +13206,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>444323</v>
+        <v>444250</v>
       </c>
       <c r="R124" t="n">
-        <v>6787297</v>
+        <v>6787342</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13256,54 +13268,45 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>129795188</v>
+        <v>129795294</v>
       </c>
       <c r="B125" t="n">
-        <v>8451</v>
+        <v>79088</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
-      <c r="J125" t="inlineStr"/>
-      <c r="K125" t="inlineStr"/>
-      <c r="L125" t="inlineStr"/>
-      <c r="M125" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N125" t="inlineStr"/>
       <c r="P125" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>444498</v>
+        <v>444323</v>
       </c>
       <c r="R125" t="n">
-        <v>6787280</v>
+        <v>6787297</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13344,7 +13347,6 @@
       <c r="AE125" t="b">
         <v>0</v>
       </c>
-      <c r="AF125" t="inlineStr"/>
       <c r="AG125" t="b">
         <v>0</v>
       </c>
@@ -13363,41 +13365,40 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>129795179</v>
+        <v>129795144</v>
       </c>
       <c r="B126" t="n">
-        <v>8451</v>
+        <v>57737</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
-      <c r="J126" t="inlineStr"/>
       <c r="K126" t="inlineStr"/>
       <c r="L126" t="inlineStr"/>
       <c r="M126" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N126" t="inlineStr"/>
@@ -13407,10 +13408,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>444378</v>
+        <v>444186</v>
       </c>
       <c r="R126" t="n">
-        <v>6787236</v>
+        <v>6787223</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -13451,7 +13452,6 @@
       <c r="AE126" t="b">
         <v>0</v>
       </c>
-      <c r="AF126" t="inlineStr"/>
       <c r="AG126" t="b">
         <v>0</v>
       </c>
@@ -13470,10 +13470,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>129795258</v>
+        <v>129795267</v>
       </c>
       <c r="B127" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -13505,10 +13505,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>444174</v>
+        <v>444353</v>
       </c>
       <c r="R127" t="n">
-        <v>6787136</v>
+        <v>6787215</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -13541,6 +13541,11 @@
       <c r="AA127" t="inlineStr">
         <is>
           <t>2025-11-22</t>
+        </is>
+      </c>
+      <c r="AC127" t="inlineStr">
+        <is>
+          <t>Gott om garnlav inom en radie av 40m.</t>
         </is>
       </c>
       <c r="AD127" t="b">
@@ -13567,10 +13572,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>129795275</v>
+        <v>129795159</v>
       </c>
       <c r="B128" t="n">
-        <v>79087</v>
+        <v>57737</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -13578,34 +13583,42 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
+      <c r="K128" t="inlineStr"/>
+      <c r="L128" t="inlineStr"/>
+      <c r="M128" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N128" t="inlineStr"/>
       <c r="P128" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>444495</v>
+        <v>444436</v>
       </c>
       <c r="R128" t="n">
-        <v>6787340</v>
+        <v>6787463</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -13664,10 +13677,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>129795267</v>
+        <v>129795137</v>
       </c>
       <c r="B129" t="n">
-        <v>79087</v>
+        <v>91627</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -13675,34 +13688,37 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
+      <c r="J129" t="inlineStr"/>
+      <c r="K129" t="inlineStr"/>
+      <c r="N129" t="inlineStr"/>
       <c r="P129" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>444353</v>
+        <v>444203</v>
       </c>
       <c r="R129" t="n">
-        <v>6787215</v>
+        <v>6787221</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -13737,17 +13753,13 @@
           <t>2025-11-22</t>
         </is>
       </c>
-      <c r="AC129" t="inlineStr">
-        <is>
-          <t>Gott om garnlav inom en radie av 40m.</t>
-        </is>
-      </c>
       <c r="AD129" t="b">
         <v>0</v>
       </c>
       <c r="AE129" t="b">
         <v>0</v>
       </c>
+      <c r="AF129" t="inlineStr"/>
       <c r="AG129" t="b">
         <v>0</v>
       </c>
@@ -13766,10 +13778,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>129795263</v>
+        <v>129795258</v>
       </c>
       <c r="B130" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -13801,10 +13813,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>444241</v>
+        <v>444174</v>
       </c>
       <c r="R130" t="n">
-        <v>6787149</v>
+        <v>6787136</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -13863,10 +13875,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>129795137</v>
+        <v>129795275</v>
       </c>
       <c r="B131" t="n">
-        <v>91626</v>
+        <v>79088</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -13874,37 +13886,34 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
-      <c r="J131" t="inlineStr"/>
-      <c r="K131" t="inlineStr"/>
-      <c r="N131" t="inlineStr"/>
       <c r="P131" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>444203</v>
+        <v>444495</v>
       </c>
       <c r="R131" t="n">
-        <v>6787221</v>
+        <v>6787340</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -13945,7 +13954,6 @@
       <c r="AE131" t="b">
         <v>0</v>
       </c>
-      <c r="AF131" t="inlineStr"/>
       <c r="AG131" t="b">
         <v>0</v>
       </c>
@@ -13964,10 +13972,10 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>129795159</v>
+        <v>129795263</v>
       </c>
       <c r="B132" t="n">
-        <v>57737</v>
+        <v>79088</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -13975,42 +13983,34 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
-      <c r="K132" t="inlineStr"/>
-      <c r="L132" t="inlineStr"/>
-      <c r="M132" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N132" t="inlineStr"/>
       <c r="P132" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>444436</v>
+        <v>444241</v>
       </c>
       <c r="R132" t="n">
-        <v>6787463</v>
+        <v>6787149</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -14283,10 +14283,10 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>129795274</v>
+        <v>129795139</v>
       </c>
       <c r="B135" t="n">
-        <v>79087</v>
+        <v>91627</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -14294,34 +14294,37 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
+      <c r="J135" t="inlineStr"/>
+      <c r="K135" t="inlineStr"/>
+      <c r="N135" t="inlineStr"/>
       <c r="P135" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>444538</v>
+        <v>444342</v>
       </c>
       <c r="R135" t="n">
-        <v>6787325</v>
+        <v>6787240</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -14362,6 +14365,7 @@
       <c r="AE135" t="b">
         <v>0</v>
       </c>
+      <c r="AF135" t="inlineStr"/>
       <c r="AG135" t="b">
         <v>0</v>
       </c>
@@ -14380,10 +14384,10 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>129795304</v>
+        <v>129795254</v>
       </c>
       <c r="B136" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -14409,16 +14413,19 @@
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
+      <c r="J136" t="inlineStr"/>
+      <c r="K136" t="inlineStr"/>
+      <c r="N136" t="inlineStr"/>
       <c r="P136" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>444172</v>
+        <v>444199</v>
       </c>
       <c r="R136" t="n">
-        <v>6787339</v>
+        <v>6787221</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -14459,6 +14466,7 @@
       <c r="AE136" t="b">
         <v>0</v>
       </c>
+      <c r="AF136" t="inlineStr"/>
       <c r="AG136" t="b">
         <v>0</v>
       </c>
@@ -14477,10 +14485,10 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>129795254</v>
+        <v>129795266</v>
       </c>
       <c r="B137" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -14506,19 +14514,16 @@
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
-      <c r="J137" t="inlineStr"/>
-      <c r="K137" t="inlineStr"/>
-      <c r="N137" t="inlineStr"/>
       <c r="P137" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>444199</v>
+        <v>444314</v>
       </c>
       <c r="R137" t="n">
-        <v>6787221</v>
+        <v>6787212</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -14553,13 +14558,17 @@
           <t>2025-11-22</t>
         </is>
       </c>
+      <c r="AC137" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 40m</t>
+        </is>
+      </c>
       <c r="AD137" t="b">
         <v>0</v>
       </c>
       <c r="AE137" t="b">
         <v>0</v>
       </c>
-      <c r="AF137" t="inlineStr"/>
       <c r="AG137" t="b">
         <v>0</v>
       </c>
@@ -14578,10 +14587,10 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>129795302</v>
+        <v>129795247</v>
       </c>
       <c r="B138" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -14613,10 +14622,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>444222</v>
+        <v>444225</v>
       </c>
       <c r="R138" t="n">
-        <v>6787345</v>
+        <v>6787275</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -14675,10 +14684,10 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>129795251</v>
+        <v>129795274</v>
       </c>
       <c r="B139" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -14704,19 +14713,16 @@
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
-      <c r="J139" t="inlineStr"/>
-      <c r="K139" t="inlineStr"/>
-      <c r="N139" t="inlineStr"/>
       <c r="P139" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>444309</v>
+        <v>444538</v>
       </c>
       <c r="R139" t="n">
-        <v>6787272</v>
+        <v>6787325</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -14757,7 +14763,6 @@
       <c r="AE139" t="b">
         <v>0</v>
       </c>
-      <c r="AF139" t="inlineStr"/>
       <c r="AG139" t="b">
         <v>0</v>
       </c>
@@ -14776,10 +14781,10 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>129795266</v>
+        <v>129795304</v>
       </c>
       <c r="B140" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -14811,10 +14816,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>444314</v>
+        <v>444172</v>
       </c>
       <c r="R140" t="n">
-        <v>6787212</v>
+        <v>6787339</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -14847,11 +14852,6 @@
       <c r="AA140" t="inlineStr">
         <is>
           <t>2025-11-22</t>
-        </is>
-      </c>
-      <c r="AC140" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 40m</t>
         </is>
       </c>
       <c r="AD140" t="b">
@@ -14878,10 +14878,10 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>129795247</v>
+        <v>129795302</v>
       </c>
       <c r="B141" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -14913,10 +14913,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>444225</v>
+        <v>444222</v>
       </c>
       <c r="R141" t="n">
-        <v>6787275</v>
+        <v>6787345</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -14975,10 +14975,10 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>129795139</v>
+        <v>129795251</v>
       </c>
       <c r="B142" t="n">
-        <v>91626</v>
+        <v>79088</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -14986,21 +14986,21 @@
         </is>
       </c>
       <c r="E142" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
@@ -15013,10 +15013,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>444342</v>
+        <v>444309</v>
       </c>
       <c r="R142" t="n">
-        <v>6787240</v>
+        <v>6787272</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>

--- a/artfynd/A 51041-2025 artfynd.xlsx
+++ b/artfynd/A 51041-2025 artfynd.xlsx
@@ -1684,10 +1684,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129795276</v>
+        <v>129795153</v>
       </c>
       <c r="B12" t="n">
-        <v>79088</v>
+        <v>57737</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1695,26 +1695,31 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1722,10 +1727,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>444499</v>
+        <v>444452</v>
       </c>
       <c r="R12" t="n">
-        <v>6787367</v>
+        <v>6787294</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1760,18 +1765,12 @@
           <t>2025-11-22</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 50m.</t>
-        </is>
-      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1790,7 +1789,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129795299</v>
+        <v>129795276</v>
       </c>
       <c r="B13" t="n">
         <v>79088</v>
@@ -1819,16 +1818,19 @@
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>444265</v>
+        <v>444499</v>
       </c>
       <c r="R13" t="n">
-        <v>6787372</v>
+        <v>6787367</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1863,12 +1865,18 @@
           <t>2025-11-22</t>
         </is>
       </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 50m.</t>
+        </is>
+      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -1887,7 +1895,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129795281</v>
+        <v>129795299</v>
       </c>
       <c r="B14" t="n">
         <v>79088</v>
@@ -1916,19 +1924,16 @@
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>444408</v>
+        <v>444265</v>
       </c>
       <c r="R14" t="n">
-        <v>6787452</v>
+        <v>6787372</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1969,7 +1974,6 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -1988,7 +1992,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129795271</v>
+        <v>129795281</v>
       </c>
       <c r="B15" t="n">
         <v>79088</v>
@@ -2026,10 +2030,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>444466</v>
+        <v>444408</v>
       </c>
       <c r="R15" t="n">
-        <v>6787306</v>
+        <v>6787452</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2062,11 +2066,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-11-22</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 50m.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2094,10 +2093,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129795155</v>
+        <v>129795271</v>
       </c>
       <c r="B16" t="n">
-        <v>57737</v>
+        <v>79088</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2105,31 +2104,26 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2137,7 +2131,7 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>444498</v>
+        <v>444466</v>
       </c>
       <c r="R16" t="n">
         <v>6787306</v>
@@ -2175,12 +2169,18 @@
           <t>2025-11-22</t>
         </is>
       </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 50m.</t>
+        </is>
+      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2199,7 +2199,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129795163</v>
+        <v>129795155</v>
       </c>
       <c r="B17" t="n">
         <v>57737</v>
@@ -2242,10 +2242,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>444415</v>
+        <v>444498</v>
       </c>
       <c r="R17" t="n">
-        <v>6787316</v>
+        <v>6787306</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2304,7 +2304,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129795153</v>
+        <v>129795163</v>
       </c>
       <c r="B18" t="n">
         <v>57737</v>
@@ -2337,7 +2337,7 @@
       <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N18" t="inlineStr"/>
@@ -2347,10 +2347,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>444452</v>
+        <v>444415</v>
       </c>
       <c r="R18" t="n">
-        <v>6787294</v>
+        <v>6787316</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2623,7 +2623,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129795273</v>
+        <v>129795310</v>
       </c>
       <c r="B21" t="n">
         <v>79088</v>
@@ -2652,16 +2652,19 @@
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>444548</v>
+        <v>444488</v>
       </c>
       <c r="R21" t="n">
-        <v>6787330</v>
+        <v>6787445</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2696,12 +2699,18 @@
           <t>2025-11-22</t>
         </is>
       </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Gott om garnlav inom en radie av 40m</t>
+        </is>
+      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -2720,45 +2729,54 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129795265</v>
+        <v>129795198</v>
       </c>
       <c r="B22" t="n">
-        <v>79088</v>
+        <v>8451</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>444278</v>
+        <v>444434</v>
       </c>
       <c r="R22" t="n">
-        <v>6787163</v>
+        <v>6787384</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2799,6 +2817,7 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -2817,45 +2836,54 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129795278</v>
+        <v>129795207</v>
       </c>
       <c r="B23" t="n">
-        <v>79088</v>
+        <v>8451</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>444465</v>
+        <v>444221</v>
       </c>
       <c r="R23" t="n">
-        <v>6787451</v>
+        <v>6787340</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2896,6 +2924,7 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -2914,37 +2943,43 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129795310</v>
+        <v>129795200</v>
       </c>
       <c r="B24" t="n">
-        <v>79088</v>
+        <v>8451</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -2952,10 +2987,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>444488</v>
+        <v>444429</v>
       </c>
       <c r="R24" t="n">
-        <v>6787445</v>
+        <v>6787341</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2988,11 +3023,6 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-11-22</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Gott om garnlav inom en radie av 40m</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3020,7 +3050,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129795198</v>
+        <v>129795206</v>
       </c>
       <c r="B25" t="n">
         <v>8451</v>
@@ -3064,10 +3094,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>444434</v>
+        <v>444247</v>
       </c>
       <c r="R25" t="n">
-        <v>6787384</v>
+        <v>6787328</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3127,54 +3157,45 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129795207</v>
+        <v>129795273</v>
       </c>
       <c r="B26" t="n">
-        <v>8451</v>
+        <v>79088</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>444221</v>
+        <v>444548</v>
       </c>
       <c r="R26" t="n">
-        <v>6787340</v>
+        <v>6787330</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3215,7 +3236,6 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
-      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3234,54 +3254,45 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129795200</v>
+        <v>129795265</v>
       </c>
       <c r="B27" t="n">
-        <v>8451</v>
+        <v>79088</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>444429</v>
+        <v>444278</v>
       </c>
       <c r="R27" t="n">
-        <v>6787341</v>
+        <v>6787163</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3322,7 +3333,6 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
-      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3341,54 +3351,45 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129795206</v>
+        <v>129795278</v>
       </c>
       <c r="B28" t="n">
-        <v>8451</v>
+        <v>79088</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>444247</v>
+        <v>444465</v>
       </c>
       <c r="R28" t="n">
-        <v>6787328</v>
+        <v>6787451</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3429,7 +3430,6 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
-      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -4068,7 +4068,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129795270</v>
+        <v>129795269</v>
       </c>
       <c r="B35" t="n">
         <v>79088</v>
@@ -4103,10 +4103,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>444416</v>
+        <v>444429</v>
       </c>
       <c r="R35" t="n">
-        <v>6787260</v>
+        <v>6787240</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4165,7 +4165,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129795296</v>
+        <v>129795249</v>
       </c>
       <c r="B36" t="n">
         <v>79088</v>
@@ -4194,19 +4194,16 @@
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
-      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>444299</v>
+        <v>444267</v>
       </c>
       <c r="R36" t="n">
-        <v>6787304</v>
+        <v>6787295</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4241,18 +4238,12 @@
           <t>2025-11-22</t>
         </is>
       </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 50 m.</t>
-        </is>
-      </c>
       <c r="AD36" t="b">
         <v>0</v>
       </c>
       <c r="AE36" t="b">
         <v>0</v>
       </c>
-      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
@@ -4271,10 +4262,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129795269</v>
+        <v>129795165</v>
       </c>
       <c r="B37" t="n">
-        <v>79088</v>
+        <v>57737</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4282,34 +4273,42 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>444429</v>
+        <v>444251</v>
       </c>
       <c r="R37" t="n">
-        <v>6787240</v>
+        <v>6787376</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4368,7 +4367,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129795249</v>
+        <v>129795296</v>
       </c>
       <c r="B38" t="n">
         <v>79088</v>
@@ -4397,16 +4396,19 @@
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>444267</v>
+        <v>444299</v>
       </c>
       <c r="R38" t="n">
-        <v>6787295</v>
+        <v>6787304</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4441,12 +4443,18 @@
           <t>2025-11-22</t>
         </is>
       </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 50 m.</t>
+        </is>
+      </c>
       <c r="AD38" t="b">
         <v>0</v>
       </c>
       <c r="AE38" t="b">
         <v>0</v>
       </c>
+      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -4465,10 +4473,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129795165</v>
+        <v>129795270</v>
       </c>
       <c r="B39" t="n">
-        <v>57737</v>
+        <v>79088</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4476,42 +4484,34 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>444251</v>
+        <v>444416</v>
       </c>
       <c r="R39" t="n">
-        <v>6787376</v>
+        <v>6787260</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4570,41 +4570,40 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129795193</v>
+        <v>129795133</v>
       </c>
       <c r="B40" t="n">
-        <v>8451</v>
+        <v>57898</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>106545</v>
+        <v>103021</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr"/>
       <c r="L40" t="inlineStr"/>
       <c r="M40" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N40" t="inlineStr"/>
@@ -4614,10 +4613,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>444508</v>
+        <v>444226</v>
       </c>
       <c r="R40" t="n">
-        <v>6787352</v>
+        <v>6787236</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4658,7 +4657,6 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
-      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
@@ -4677,7 +4675,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129795202</v>
+        <v>129795193</v>
       </c>
       <c r="B41" t="n">
         <v>8451</v>
@@ -4721,10 +4719,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>444413</v>
+        <v>444508</v>
       </c>
       <c r="R41" t="n">
-        <v>6787314</v>
+        <v>6787352</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4784,40 +4782,41 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129795133</v>
+        <v>129795202</v>
       </c>
       <c r="B42" t="n">
-        <v>57898</v>
+        <v>8451</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>103021</v>
+        <v>106545</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr"/>
       <c r="K42" t="inlineStr"/>
       <c r="L42" t="inlineStr"/>
       <c r="M42" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N42" t="inlineStr"/>
@@ -4827,10 +4826,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>444226</v>
+        <v>444413</v>
       </c>
       <c r="R42" t="n">
-        <v>6787236</v>
+        <v>6787314</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4871,6 +4870,7 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
+      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
@@ -6313,32 +6313,32 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129795131</v>
+        <v>129795134</v>
       </c>
       <c r="B57" t="n">
-        <v>56930</v>
+        <v>57898</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>100138</v>
+        <v>103021</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6346,7 +6346,7 @@
       <c r="L57" t="inlineStr"/>
       <c r="M57" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N57" t="inlineStr"/>
@@ -6356,10 +6356,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>444250</v>
+        <v>444289</v>
       </c>
       <c r="R57" t="n">
-        <v>6787212</v>
+        <v>6787357</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6418,40 +6418,41 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129795134</v>
+        <v>129795184</v>
       </c>
       <c r="B58" t="n">
-        <v>57898</v>
+        <v>8451</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>103021</v>
+        <v>106545</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
+      <c r="J58" t="inlineStr"/>
       <c r="K58" t="inlineStr"/>
       <c r="L58" t="inlineStr"/>
       <c r="M58" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N58" t="inlineStr"/>
@@ -6461,10 +6462,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>444289</v>
+        <v>444452</v>
       </c>
       <c r="R58" t="n">
-        <v>6787357</v>
+        <v>6787305</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6505,6 +6506,7 @@
       <c r="AE58" t="b">
         <v>0</v>
       </c>
+      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
       </c>
@@ -6523,7 +6525,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129795184</v>
+        <v>129795172</v>
       </c>
       <c r="B59" t="n">
         <v>8451</v>
@@ -6567,10 +6569,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>444452</v>
+        <v>444225</v>
       </c>
       <c r="R59" t="n">
-        <v>6787305</v>
+        <v>6787223</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6630,7 +6632,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129795172</v>
+        <v>129795199</v>
       </c>
       <c r="B60" t="n">
         <v>8451</v>
@@ -6674,10 +6676,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>444225</v>
+        <v>444431</v>
       </c>
       <c r="R60" t="n">
-        <v>6787223</v>
+        <v>6787350</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6737,10 +6739,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129795199</v>
+        <v>129795131</v>
       </c>
       <c r="B61" t="n">
-        <v>8451</v>
+        <v>56930</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6748,30 +6750,29 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>106545</v>
+        <v>100138</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
-      <c r="J61" t="inlineStr"/>
       <c r="K61" t="inlineStr"/>
       <c r="L61" t="inlineStr"/>
       <c r="M61" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="N61" t="inlineStr"/>
@@ -6781,10 +6782,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>444431</v>
+        <v>444250</v>
       </c>
       <c r="R61" t="n">
-        <v>6787350</v>
+        <v>6787212</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6825,7 +6826,6 @@
       <c r="AE61" t="b">
         <v>0</v>
       </c>
-      <c r="AF61" t="inlineStr"/>
       <c r="AG61" t="b">
         <v>0</v>
       </c>
@@ -6844,41 +6844,40 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129795191</v>
+        <v>129795162</v>
       </c>
       <c r="B62" t="n">
-        <v>8451</v>
+        <v>57737</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
-      <c r="J62" t="inlineStr"/>
       <c r="K62" t="inlineStr"/>
       <c r="L62" t="inlineStr"/>
       <c r="M62" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N62" t="inlineStr"/>
@@ -6888,10 +6887,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>444520</v>
+        <v>444428</v>
       </c>
       <c r="R62" t="n">
-        <v>6787287</v>
+        <v>6787329</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6932,7 +6931,6 @@
       <c r="AE62" t="b">
         <v>0</v>
       </c>
-      <c r="AF62" t="inlineStr"/>
       <c r="AG62" t="b">
         <v>0</v>
       </c>
@@ -6951,7 +6949,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129795195</v>
+        <v>129795191</v>
       </c>
       <c r="B63" t="n">
         <v>8451</v>
@@ -6995,10 +6993,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>444487</v>
+        <v>444520</v>
       </c>
       <c r="R63" t="n">
-        <v>6787441</v>
+        <v>6787287</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7058,7 +7056,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129795177</v>
+        <v>129795195</v>
       </c>
       <c r="B64" t="n">
         <v>8451</v>
@@ -7092,7 +7090,7 @@
       <c r="L64" t="inlineStr"/>
       <c r="M64" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N64" t="inlineStr"/>
@@ -7102,10 +7100,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>444342</v>
+        <v>444487</v>
       </c>
       <c r="R64" t="n">
-        <v>6787223</v>
+        <v>6787441</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7165,40 +7163,41 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129795162</v>
+        <v>129795177</v>
       </c>
       <c r="B65" t="n">
-        <v>57737</v>
+        <v>8451</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
+      <c r="J65" t="inlineStr"/>
       <c r="K65" t="inlineStr"/>
       <c r="L65" t="inlineStr"/>
       <c r="M65" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="N65" t="inlineStr"/>
@@ -7208,10 +7207,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>444428</v>
+        <v>444342</v>
       </c>
       <c r="R65" t="n">
-        <v>6787329</v>
+        <v>6787223</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7252,6 +7251,7 @@
       <c r="AE65" t="b">
         <v>0</v>
       </c>
+      <c r="AF65" t="inlineStr"/>
       <c r="AG65" t="b">
         <v>0</v>
       </c>
@@ -7569,37 +7569,43 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129795135</v>
+        <v>129795182</v>
       </c>
       <c r="B69" t="n">
-        <v>91627</v>
+        <v>8451</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>5442</v>
+        <v>106545</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
       <c r="J69" t="inlineStr"/>
       <c r="K69" t="inlineStr"/>
+      <c r="L69" t="inlineStr"/>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
@@ -7607,10 +7613,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>444158</v>
+        <v>444417</v>
       </c>
       <c r="R69" t="n">
-        <v>6787148</v>
+        <v>6787266</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8155,10 +8161,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129795166</v>
+        <v>129795135</v>
       </c>
       <c r="B75" t="n">
-        <v>57737</v>
+        <v>91627</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8166,31 +8172,26 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>100049</v>
+        <v>5442</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
+      <c r="J75" t="inlineStr"/>
       <c r="K75" t="inlineStr"/>
-      <c r="L75" t="inlineStr"/>
-      <c r="M75" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
@@ -8198,10 +8199,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>444254</v>
+        <v>444158</v>
       </c>
       <c r="R75" t="n">
-        <v>6787333</v>
+        <v>6787148</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8242,6 +8243,7 @@
       <c r="AE75" t="b">
         <v>0</v>
       </c>
+      <c r="AF75" t="inlineStr"/>
       <c r="AG75" t="b">
         <v>0</v>
       </c>
@@ -8260,27 +8262,27 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129795208</v>
+        <v>129795166</v>
       </c>
       <c r="B76" t="n">
-        <v>58111</v>
+        <v>57737</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>103015</v>
+        <v>100049</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -8293,7 +8295,7 @@
       <c r="L76" t="inlineStr"/>
       <c r="M76" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N76" t="inlineStr"/>
@@ -8303,10 +8305,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>444434</v>
+        <v>444254</v>
       </c>
       <c r="R76" t="n">
-        <v>6787357</v>
+        <v>6787333</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8365,10 +8367,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129795182</v>
+        <v>129795208</v>
       </c>
       <c r="B77" t="n">
-        <v>8451</v>
+        <v>58111</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8376,30 +8378,29 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>106545</v>
+        <v>103015</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
-      <c r="J77" t="inlineStr"/>
       <c r="K77" t="inlineStr"/>
       <c r="L77" t="inlineStr"/>
       <c r="M77" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N77" t="inlineStr"/>
@@ -8409,10 +8410,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>444417</v>
+        <v>444434</v>
       </c>
       <c r="R77" t="n">
-        <v>6787266</v>
+        <v>6787357</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8453,7 +8454,6 @@
       <c r="AE77" t="b">
         <v>0</v>
       </c>
-      <c r="AF77" t="inlineStr"/>
       <c r="AG77" t="b">
         <v>0</v>
       </c>
@@ -8472,10 +8472,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129795126</v>
+        <v>129795300</v>
       </c>
       <c r="B78" t="n">
-        <v>79707</v>
+        <v>79088</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8483,34 +8483,37 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
+      <c r="J78" t="inlineStr"/>
+      <c r="K78" t="inlineStr"/>
+      <c r="N78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>444358</v>
+        <v>444264</v>
       </c>
       <c r="R78" t="n">
-        <v>6787400</v>
+        <v>6787349</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8545,12 +8548,18 @@
           <t>2025-11-22</t>
         </is>
       </c>
+      <c r="AC78" t="inlineStr">
+        <is>
+          <t>Garnlav i de flesta träd inom en radie av 50 m.</t>
+        </is>
+      </c>
       <c r="AD78" t="b">
         <v>0</v>
       </c>
       <c r="AE78" t="b">
         <v>0</v>
       </c>
+      <c r="AF78" t="inlineStr"/>
       <c r="AG78" t="b">
         <v>0</v>
       </c>
@@ -8569,10 +8578,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129795300</v>
+        <v>129795127</v>
       </c>
       <c r="B79" t="n">
-        <v>79088</v>
+        <v>79707</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8580,37 +8589,34 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
-      <c r="J79" t="inlineStr"/>
-      <c r="K79" t="inlineStr"/>
-      <c r="N79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>444264</v>
+        <v>444432</v>
       </c>
       <c r="R79" t="n">
-        <v>6787349</v>
+        <v>6787388</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8645,18 +8651,12 @@
           <t>2025-11-22</t>
         </is>
       </c>
-      <c r="AC79" t="inlineStr">
-        <is>
-          <t>Garnlav i de flesta träd inom en radie av 50 m.</t>
-        </is>
-      </c>
       <c r="AD79" t="b">
         <v>0</v>
       </c>
       <c r="AE79" t="b">
         <v>0</v>
       </c>
-      <c r="AF79" t="inlineStr"/>
       <c r="AG79" t="b">
         <v>0</v>
       </c>
@@ -8675,10 +8675,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129795127</v>
+        <v>129795307</v>
       </c>
       <c r="B80" t="n">
-        <v>79707</v>
+        <v>79088</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8686,21 +8686,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8710,10 +8710,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>444432</v>
+        <v>444134</v>
       </c>
       <c r="R80" t="n">
-        <v>6787388</v>
+        <v>6787304</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8772,7 +8772,7 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129795307</v>
+        <v>129795286</v>
       </c>
       <c r="B81" t="n">
         <v>79088</v>
@@ -8801,16 +8801,19 @@
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
+      <c r="J81" t="inlineStr"/>
+      <c r="K81" t="inlineStr"/>
+      <c r="N81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>444134</v>
+        <v>444440</v>
       </c>
       <c r="R81" t="n">
-        <v>6787304</v>
+        <v>6787388</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8845,12 +8848,18 @@
           <t>2025-11-22</t>
         </is>
       </c>
+      <c r="AC81" t="inlineStr">
+        <is>
+          <t>Gott om garnlav inom en radie av 50 m.</t>
+        </is>
+      </c>
       <c r="AD81" t="b">
         <v>0</v>
       </c>
       <c r="AE81" t="b">
         <v>0</v>
       </c>
+      <c r="AF81" t="inlineStr"/>
       <c r="AG81" t="b">
         <v>0</v>
       </c>
@@ -8869,7 +8878,7 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129795286</v>
+        <v>129795241</v>
       </c>
       <c r="B82" t="n">
         <v>79088</v>
@@ -8898,19 +8907,16 @@
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
-      <c r="J82" t="inlineStr"/>
-      <c r="K82" t="inlineStr"/>
-      <c r="N82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>444440</v>
+        <v>444117</v>
       </c>
       <c r="R82" t="n">
-        <v>6787388</v>
+        <v>6787277</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8945,18 +8951,12 @@
           <t>2025-11-22</t>
         </is>
       </c>
-      <c r="AC82" t="inlineStr">
-        <is>
-          <t>Gott om garnlav inom en radie av 50 m.</t>
-        </is>
-      </c>
       <c r="AD82" t="b">
         <v>0</v>
       </c>
       <c r="AE82" t="b">
         <v>0</v>
       </c>
-      <c r="AF82" t="inlineStr"/>
       <c r="AG82" t="b">
         <v>0</v>
       </c>
@@ -8975,10 +8975,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129795241</v>
+        <v>129795126</v>
       </c>
       <c r="B83" t="n">
-        <v>79088</v>
+        <v>79707</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8986,21 +8986,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9010,10 +9010,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>444117</v>
+        <v>444358</v>
       </c>
       <c r="R83" t="n">
-        <v>6787277</v>
+        <v>6787400</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -12957,54 +12957,45 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>129795188</v>
+        <v>129795301</v>
       </c>
       <c r="B122" t="n">
-        <v>8451</v>
+        <v>79088</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
-      <c r="J122" t="inlineStr"/>
-      <c r="K122" t="inlineStr"/>
-      <c r="L122" t="inlineStr"/>
-      <c r="M122" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N122" t="inlineStr"/>
       <c r="P122" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>444498</v>
+        <v>444250</v>
       </c>
       <c r="R122" t="n">
-        <v>6787280</v>
+        <v>6787342</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -13045,7 +13036,6 @@
       <c r="AE122" t="b">
         <v>0</v>
       </c>
-      <c r="AF122" t="inlineStr"/>
       <c r="AG122" t="b">
         <v>0</v>
       </c>
@@ -13064,54 +13054,45 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>129795179</v>
+        <v>129795294</v>
       </c>
       <c r="B123" t="n">
-        <v>8451</v>
+        <v>79088</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
-      <c r="J123" t="inlineStr"/>
-      <c r="K123" t="inlineStr"/>
-      <c r="L123" t="inlineStr"/>
-      <c r="M123" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N123" t="inlineStr"/>
       <c r="P123" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>444378</v>
+        <v>444323</v>
       </c>
       <c r="R123" t="n">
-        <v>6787236</v>
+        <v>6787297</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13152,7 +13133,6 @@
       <c r="AE123" t="b">
         <v>0</v>
       </c>
-      <c r="AF123" t="inlineStr"/>
       <c r="AG123" t="b">
         <v>0</v>
       </c>
@@ -13171,10 +13151,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>129795301</v>
+        <v>129795144</v>
       </c>
       <c r="B124" t="n">
-        <v>79088</v>
+        <v>57737</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -13182,34 +13162,42 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
+      <c r="K124" t="inlineStr"/>
+      <c r="L124" t="inlineStr"/>
+      <c r="M124" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N124" t="inlineStr"/>
       <c r="P124" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>444250</v>
+        <v>444186</v>
       </c>
       <c r="R124" t="n">
-        <v>6787342</v>
+        <v>6787223</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13268,45 +13256,54 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>129795294</v>
+        <v>129795188</v>
       </c>
       <c r="B125" t="n">
-        <v>79088</v>
+        <v>8451</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
+      <c r="J125" t="inlineStr"/>
+      <c r="K125" t="inlineStr"/>
+      <c r="L125" t="inlineStr"/>
+      <c r="M125" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N125" t="inlineStr"/>
       <c r="P125" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>444323</v>
+        <v>444498</v>
       </c>
       <c r="R125" t="n">
-        <v>6787297</v>
+        <v>6787280</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13347,6 +13344,7 @@
       <c r="AE125" t="b">
         <v>0</v>
       </c>
+      <c r="AF125" t="inlineStr"/>
       <c r="AG125" t="b">
         <v>0</v>
       </c>
@@ -13365,40 +13363,41 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>129795144</v>
+        <v>129795179</v>
       </c>
       <c r="B126" t="n">
-        <v>57737</v>
+        <v>8451</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
+      <c r="J126" t="inlineStr"/>
       <c r="K126" t="inlineStr"/>
       <c r="L126" t="inlineStr"/>
       <c r="M126" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N126" t="inlineStr"/>
@@ -13408,10 +13407,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>444186</v>
+        <v>444378</v>
       </c>
       <c r="R126" t="n">
-        <v>6787223</v>
+        <v>6787236</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -13452,6 +13451,7 @@
       <c r="AE126" t="b">
         <v>0</v>
       </c>
+      <c r="AF126" t="inlineStr"/>
       <c r="AG126" t="b">
         <v>0</v>
       </c>
@@ -14684,45 +14684,54 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>129795274</v>
+        <v>129795204</v>
       </c>
       <c r="B139" t="n">
-        <v>79088</v>
+        <v>8451</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E139" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
+      <c r="J139" t="inlineStr"/>
+      <c r="K139" t="inlineStr"/>
+      <c r="L139" t="inlineStr"/>
+      <c r="M139" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N139" t="inlineStr"/>
       <c r="P139" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>444538</v>
+        <v>444380</v>
       </c>
       <c r="R139" t="n">
-        <v>6787325</v>
+        <v>6787306</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -14763,6 +14772,7 @@
       <c r="AE139" t="b">
         <v>0</v>
       </c>
+      <c r="AF139" t="inlineStr"/>
       <c r="AG139" t="b">
         <v>0</v>
       </c>
@@ -14781,7 +14791,7 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>129795304</v>
+        <v>129795274</v>
       </c>
       <c r="B140" t="n">
         <v>79088</v>
@@ -14816,10 +14826,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>444172</v>
+        <v>444538</v>
       </c>
       <c r="R140" t="n">
-        <v>6787339</v>
+        <v>6787325</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -14878,7 +14888,7 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>129795302</v>
+        <v>129795304</v>
       </c>
       <c r="B141" t="n">
         <v>79088</v>
@@ -14913,10 +14923,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>444222</v>
+        <v>444172</v>
       </c>
       <c r="R141" t="n">
-        <v>6787345</v>
+        <v>6787339</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -14975,7 +14985,7 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>129795251</v>
+        <v>129795302</v>
       </c>
       <c r="B142" t="n">
         <v>79088</v>
@@ -15004,19 +15014,16 @@
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
-      <c r="J142" t="inlineStr"/>
-      <c r="K142" t="inlineStr"/>
-      <c r="N142" t="inlineStr"/>
       <c r="P142" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>444309</v>
+        <v>444222</v>
       </c>
       <c r="R142" t="n">
-        <v>6787272</v>
+        <v>6787345</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -15057,7 +15064,6 @@
       <c r="AE142" t="b">
         <v>0</v>
       </c>
-      <c r="AF142" t="inlineStr"/>
       <c r="AG142" t="b">
         <v>0</v>
       </c>
@@ -15076,43 +15082,37 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>129795204</v>
+        <v>129795251</v>
       </c>
       <c r="B143" t="n">
-        <v>8451</v>
+        <v>79088</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E143" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
       <c r="J143" t="inlineStr"/>
       <c r="K143" t="inlineStr"/>
-      <c r="L143" t="inlineStr"/>
-      <c r="M143" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N143" t="inlineStr"/>
       <c r="P143" t="inlineStr">
         <is>
@@ -15120,10 +15120,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>444380</v>
+        <v>444309</v>
       </c>
       <c r="R143" t="n">
-        <v>6787306</v>
+        <v>6787272</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>

--- a/artfynd/A 51041-2025 artfynd.xlsx
+++ b/artfynd/A 51041-2025 artfynd.xlsx
@@ -675,54 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129795169</v>
+        <v>129795253</v>
       </c>
       <c r="B2" t="n">
-        <v>8451</v>
+        <v>79088</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>444272</v>
+        <v>444185</v>
       </c>
       <c r="R2" t="n">
-        <v>6787239</v>
+        <v>6787247</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -757,13 +748,17 @@
           <t>2025-11-22</t>
         </is>
       </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Gott om garnlav inom en radie av 50 m.</t>
+        </is>
+      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -782,54 +777,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129795190</v>
+        <v>129795261</v>
       </c>
       <c r="B3" t="n">
-        <v>8451</v>
+        <v>79088</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>444510</v>
+        <v>444193</v>
       </c>
       <c r="R3" t="n">
-        <v>6787276</v>
+        <v>6787130</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -870,7 +856,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -889,43 +874,37 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129795197</v>
+        <v>129795283</v>
       </c>
       <c r="B4" t="n">
-        <v>8451</v>
+        <v>79088</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -933,10 +912,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>444406</v>
+        <v>444337</v>
       </c>
       <c r="R4" t="n">
-        <v>6787392</v>
+        <v>6787374</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -996,7 +975,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129795253</v>
+        <v>129795291</v>
       </c>
       <c r="B5" t="n">
         <v>79088</v>
@@ -1031,10 +1010,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>444185</v>
+        <v>444412</v>
       </c>
       <c r="R5" t="n">
-        <v>6787247</v>
+        <v>6787307</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1067,11 +1046,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-11-22</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Gott om garnlav inom en radie av 50 m.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1098,7 +1072,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129795261</v>
+        <v>129795298</v>
       </c>
       <c r="B6" t="n">
         <v>79088</v>
@@ -1133,10 +1107,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>444193</v>
+        <v>444305</v>
       </c>
       <c r="R6" t="n">
-        <v>6787130</v>
+        <v>6787353</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1195,7 +1169,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129795283</v>
+        <v>129795285</v>
       </c>
       <c r="B7" t="n">
         <v>79088</v>
@@ -1224,19 +1198,16 @@
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>444337</v>
+        <v>444405</v>
       </c>
       <c r="R7" t="n">
-        <v>6787374</v>
+        <v>6787405</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1277,7 +1248,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1296,7 +1266,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129795291</v>
+        <v>129795244</v>
       </c>
       <c r="B8" t="n">
         <v>79088</v>
@@ -1331,10 +1301,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>444412</v>
+        <v>444105</v>
       </c>
       <c r="R8" t="n">
-        <v>6787307</v>
+        <v>6787246</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1393,45 +1363,54 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129795298</v>
+        <v>129795169</v>
       </c>
       <c r="B9" t="n">
-        <v>79088</v>
+        <v>8451</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>444305</v>
+        <v>444272</v>
       </c>
       <c r="R9" t="n">
-        <v>6787353</v>
+        <v>6787239</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1472,6 +1451,7 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1490,45 +1470,54 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129795285</v>
+        <v>129795190</v>
       </c>
       <c r="B10" t="n">
-        <v>79088</v>
+        <v>8451</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>444405</v>
+        <v>444510</v>
       </c>
       <c r="R10" t="n">
-        <v>6787405</v>
+        <v>6787276</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1569,6 +1558,7 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1587,45 +1577,54 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129795244</v>
+        <v>129795197</v>
       </c>
       <c r="B11" t="n">
-        <v>79088</v>
+        <v>8451</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>444105</v>
+        <v>444406</v>
       </c>
       <c r="R11" t="n">
-        <v>6787246</v>
+        <v>6787392</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1666,6 +1665,7 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -3448,10 +3448,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129795142</v>
+        <v>129795256</v>
       </c>
       <c r="B29" t="n">
-        <v>57737</v>
+        <v>79088</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3459,42 +3459,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>444276</v>
+        <v>444226</v>
       </c>
       <c r="R29" t="n">
-        <v>6787287</v>
+        <v>6787196</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3553,10 +3545,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129795268</v>
+        <v>129795142</v>
       </c>
       <c r="B30" t="n">
-        <v>79088</v>
+        <v>57737</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3564,34 +3556,42 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>444383</v>
+        <v>444276</v>
       </c>
       <c r="R30" t="n">
-        <v>6787218</v>
+        <v>6787287</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3650,7 +3650,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129795256</v>
+        <v>129795268</v>
       </c>
       <c r="B31" t="n">
         <v>79088</v>
@@ -3685,10 +3685,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>444226</v>
+        <v>444383</v>
       </c>
       <c r="R31" t="n">
-        <v>6787196</v>
+        <v>6787218</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4068,7 +4068,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129795269</v>
+        <v>129795270</v>
       </c>
       <c r="B35" t="n">
         <v>79088</v>
@@ -4103,10 +4103,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>444429</v>
+        <v>444416</v>
       </c>
       <c r="R35" t="n">
-        <v>6787240</v>
+        <v>6787260</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4165,7 +4165,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129795249</v>
+        <v>129795296</v>
       </c>
       <c r="B36" t="n">
         <v>79088</v>
@@ -4194,16 +4194,19 @@
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>444267</v>
+        <v>444299</v>
       </c>
       <c r="R36" t="n">
-        <v>6787295</v>
+        <v>6787304</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4238,12 +4241,18 @@
           <t>2025-11-22</t>
         </is>
       </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 50 m.</t>
+        </is>
+      </c>
       <c r="AD36" t="b">
         <v>0</v>
       </c>
       <c r="AE36" t="b">
         <v>0</v>
       </c>
+      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
@@ -4262,10 +4271,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129795165</v>
+        <v>129795269</v>
       </c>
       <c r="B37" t="n">
-        <v>57737</v>
+        <v>79088</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4273,42 +4282,34 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>444251</v>
+        <v>444429</v>
       </c>
       <c r="R37" t="n">
-        <v>6787376</v>
+        <v>6787240</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4367,7 +4368,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129795296</v>
+        <v>129795249</v>
       </c>
       <c r="B38" t="n">
         <v>79088</v>
@@ -4396,19 +4397,16 @@
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
-      <c r="K38" t="inlineStr"/>
-      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>444299</v>
+        <v>444267</v>
       </c>
       <c r="R38" t="n">
-        <v>6787304</v>
+        <v>6787295</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4443,18 +4441,12 @@
           <t>2025-11-22</t>
         </is>
       </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 50 m.</t>
-        </is>
-      </c>
       <c r="AD38" t="b">
         <v>0</v>
       </c>
       <c r="AE38" t="b">
         <v>0</v>
       </c>
-      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -4473,10 +4465,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129795270</v>
+        <v>129795165</v>
       </c>
       <c r="B39" t="n">
-        <v>79088</v>
+        <v>57737</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4484,34 +4476,42 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>444416</v>
+        <v>444251</v>
       </c>
       <c r="R39" t="n">
-        <v>6787260</v>
+        <v>6787376</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4570,40 +4570,41 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129795133</v>
+        <v>129795193</v>
       </c>
       <c r="B40" t="n">
-        <v>57898</v>
+        <v>8451</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>103021</v>
+        <v>106545</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr"/>
       <c r="L40" t="inlineStr"/>
       <c r="M40" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N40" t="inlineStr"/>
@@ -4613,10 +4614,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>444226</v>
+        <v>444508</v>
       </c>
       <c r="R40" t="n">
-        <v>6787236</v>
+        <v>6787352</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4657,6 +4658,7 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
+      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
@@ -4675,7 +4677,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129795193</v>
+        <v>129795202</v>
       </c>
       <c r="B41" t="n">
         <v>8451</v>
@@ -4719,10 +4721,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>444508</v>
+        <v>444413</v>
       </c>
       <c r="R41" t="n">
-        <v>6787352</v>
+        <v>6787314</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4782,41 +4784,40 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129795202</v>
+        <v>129795133</v>
       </c>
       <c r="B42" t="n">
-        <v>8451</v>
+        <v>57898</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>106545</v>
+        <v>103021</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="J42" t="inlineStr"/>
       <c r="K42" t="inlineStr"/>
       <c r="L42" t="inlineStr"/>
       <c r="M42" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N42" t="inlineStr"/>
@@ -4826,10 +4827,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>444413</v>
+        <v>444226</v>
       </c>
       <c r="R42" t="n">
-        <v>6787314</v>
+        <v>6787236</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4870,7 +4871,6 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
-      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
@@ -6844,40 +6844,41 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129795162</v>
+        <v>129795191</v>
       </c>
       <c r="B62" t="n">
-        <v>57737</v>
+        <v>8451</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
+      <c r="J62" t="inlineStr"/>
       <c r="K62" t="inlineStr"/>
       <c r="L62" t="inlineStr"/>
       <c r="M62" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N62" t="inlineStr"/>
@@ -6887,10 +6888,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>444428</v>
+        <v>444520</v>
       </c>
       <c r="R62" t="n">
-        <v>6787329</v>
+        <v>6787287</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6931,6 +6932,7 @@
       <c r="AE62" t="b">
         <v>0</v>
       </c>
+      <c r="AF62" t="inlineStr"/>
       <c r="AG62" t="b">
         <v>0</v>
       </c>
@@ -6949,7 +6951,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129795191</v>
+        <v>129795195</v>
       </c>
       <c r="B63" t="n">
         <v>8451</v>
@@ -6993,10 +6995,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>444520</v>
+        <v>444487</v>
       </c>
       <c r="R63" t="n">
-        <v>6787287</v>
+        <v>6787441</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7056,7 +7058,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129795195</v>
+        <v>129795177</v>
       </c>
       <c r="B64" t="n">
         <v>8451</v>
@@ -7090,7 +7092,7 @@
       <c r="L64" t="inlineStr"/>
       <c r="M64" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="N64" t="inlineStr"/>
@@ -7100,10 +7102,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>444487</v>
+        <v>444342</v>
       </c>
       <c r="R64" t="n">
-        <v>6787441</v>
+        <v>6787223</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7163,41 +7165,40 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129795177</v>
+        <v>129795162</v>
       </c>
       <c r="B65" t="n">
-        <v>8451</v>
+        <v>57737</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
-      <c r="J65" t="inlineStr"/>
       <c r="K65" t="inlineStr"/>
       <c r="L65" t="inlineStr"/>
       <c r="M65" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N65" t="inlineStr"/>
@@ -7207,10 +7208,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>444342</v>
+        <v>444428</v>
       </c>
       <c r="R65" t="n">
-        <v>6787223</v>
+        <v>6787329</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7251,7 +7252,6 @@
       <c r="AE65" t="b">
         <v>0</v>
       </c>
-      <c r="AF65" t="inlineStr"/>
       <c r="AG65" t="b">
         <v>0</v>
       </c>
@@ -7569,43 +7569,37 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129795182</v>
+        <v>129795135</v>
       </c>
       <c r="B69" t="n">
-        <v>8451</v>
+        <v>91627</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>106545</v>
+        <v>5442</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
       <c r="J69" t="inlineStr"/>
       <c r="K69" t="inlineStr"/>
-      <c r="L69" t="inlineStr"/>
-      <c r="M69" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
@@ -7613,10 +7607,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>444417</v>
+        <v>444158</v>
       </c>
       <c r="R69" t="n">
-        <v>6787266</v>
+        <v>6787148</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8161,10 +8155,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129795135</v>
+        <v>129795166</v>
       </c>
       <c r="B75" t="n">
-        <v>91627</v>
+        <v>57737</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8172,26 +8166,31 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>5442</v>
+        <v>100049</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
-      <c r="J75" t="inlineStr"/>
       <c r="K75" t="inlineStr"/>
+      <c r="L75" t="inlineStr"/>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
@@ -8199,10 +8198,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>444158</v>
+        <v>444254</v>
       </c>
       <c r="R75" t="n">
-        <v>6787148</v>
+        <v>6787333</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8243,7 +8242,6 @@
       <c r="AE75" t="b">
         <v>0</v>
       </c>
-      <c r="AF75" t="inlineStr"/>
       <c r="AG75" t="b">
         <v>0</v>
       </c>
@@ -8262,27 +8260,27 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129795166</v>
+        <v>129795208</v>
       </c>
       <c r="B76" t="n">
-        <v>57737</v>
+        <v>58111</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>100049</v>
+        <v>103015</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -8295,7 +8293,7 @@
       <c r="L76" t="inlineStr"/>
       <c r="M76" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N76" t="inlineStr"/>
@@ -8305,10 +8303,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>444254</v>
+        <v>444434</v>
       </c>
       <c r="R76" t="n">
-        <v>6787333</v>
+        <v>6787357</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8367,10 +8365,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129795208</v>
+        <v>129795182</v>
       </c>
       <c r="B77" t="n">
-        <v>58111</v>
+        <v>8451</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8378,29 +8376,30 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>103015</v>
+        <v>106545</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
+      <c r="J77" t="inlineStr"/>
       <c r="K77" t="inlineStr"/>
       <c r="L77" t="inlineStr"/>
       <c r="M77" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N77" t="inlineStr"/>
@@ -8410,10 +8409,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>444434</v>
+        <v>444417</v>
       </c>
       <c r="R77" t="n">
-        <v>6787357</v>
+        <v>6787266</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8454,6 +8453,7 @@
       <c r="AE77" t="b">
         <v>0</v>
       </c>
+      <c r="AF77" t="inlineStr"/>
       <c r="AG77" t="b">
         <v>0</v>
       </c>
@@ -12333,32 +12333,32 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>129795164</v>
+        <v>129795132</v>
       </c>
       <c r="B116" t="n">
-        <v>57737</v>
+        <v>56930</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -12366,7 +12366,7 @@
       <c r="L116" t="inlineStr"/>
       <c r="M116" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="N116" t="inlineStr"/>
@@ -12376,10 +12376,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>444397</v>
+        <v>444315</v>
       </c>
       <c r="R116" t="n">
-        <v>6787300</v>
+        <v>6787291</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12438,10 +12438,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>129795154</v>
+        <v>129795289</v>
       </c>
       <c r="B117" t="n">
-        <v>57737</v>
+        <v>79088</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -12449,42 +12449,34 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
-      <c r="K117" t="inlineStr"/>
-      <c r="L117" t="inlineStr"/>
-      <c r="M117" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N117" t="inlineStr"/>
       <c r="P117" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>444457</v>
+        <v>444435</v>
       </c>
       <c r="R117" t="n">
-        <v>6787303</v>
+        <v>6787341</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12543,7 +12535,7 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>129795157</v>
+        <v>129795164</v>
       </c>
       <c r="B118" t="n">
         <v>57737</v>
@@ -12586,10 +12578,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>444525</v>
+        <v>444397</v>
       </c>
       <c r="R118" t="n">
-        <v>6787344</v>
+        <v>6787300</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12648,10 +12640,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>129795289</v>
+        <v>129795154</v>
       </c>
       <c r="B119" t="n">
-        <v>79088</v>
+        <v>57737</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -12659,34 +12651,42 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
+      <c r="K119" t="inlineStr"/>
+      <c r="L119" t="inlineStr"/>
+      <c r="M119" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N119" t="inlineStr"/>
       <c r="P119" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>444435</v>
+        <v>444457</v>
       </c>
       <c r="R119" t="n">
-        <v>6787341</v>
+        <v>6787303</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -12745,32 +12745,32 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>129795132</v>
+        <v>129795157</v>
       </c>
       <c r="B120" t="n">
-        <v>56930</v>
+        <v>57737</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -12778,7 +12778,7 @@
       <c r="L120" t="inlineStr"/>
       <c r="M120" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N120" t="inlineStr"/>
@@ -12788,10 +12788,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>444315</v>
+        <v>444525</v>
       </c>
       <c r="R120" t="n">
-        <v>6787291</v>
+        <v>6787344</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -14684,54 +14684,45 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>129795204</v>
+        <v>129795274</v>
       </c>
       <c r="B139" t="n">
-        <v>8451</v>
+        <v>79088</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E139" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
-      <c r="J139" t="inlineStr"/>
-      <c r="K139" t="inlineStr"/>
-      <c r="L139" t="inlineStr"/>
-      <c r="M139" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N139" t="inlineStr"/>
       <c r="P139" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>444380</v>
+        <v>444538</v>
       </c>
       <c r="R139" t="n">
-        <v>6787306</v>
+        <v>6787325</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -14772,7 +14763,6 @@
       <c r="AE139" t="b">
         <v>0</v>
       </c>
-      <c r="AF139" t="inlineStr"/>
       <c r="AG139" t="b">
         <v>0</v>
       </c>
@@ -14791,7 +14781,7 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>129795274</v>
+        <v>129795304</v>
       </c>
       <c r="B140" t="n">
         <v>79088</v>
@@ -14826,10 +14816,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>444538</v>
+        <v>444172</v>
       </c>
       <c r="R140" t="n">
-        <v>6787325</v>
+        <v>6787339</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -14888,7 +14878,7 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>129795304</v>
+        <v>129795302</v>
       </c>
       <c r="B141" t="n">
         <v>79088</v>
@@ -14923,10 +14913,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>444172</v>
+        <v>444222</v>
       </c>
       <c r="R141" t="n">
-        <v>6787339</v>
+        <v>6787345</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -14985,7 +14975,7 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>129795302</v>
+        <v>129795251</v>
       </c>
       <c r="B142" t="n">
         <v>79088</v>
@@ -15014,16 +15004,19 @@
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
+      <c r="J142" t="inlineStr"/>
+      <c r="K142" t="inlineStr"/>
+      <c r="N142" t="inlineStr"/>
       <c r="P142" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>444222</v>
+        <v>444309</v>
       </c>
       <c r="R142" t="n">
-        <v>6787345</v>
+        <v>6787272</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -15064,6 +15057,7 @@
       <c r="AE142" t="b">
         <v>0</v>
       </c>
+      <c r="AF142" t="inlineStr"/>
       <c r="AG142" t="b">
         <v>0</v>
       </c>
@@ -15082,37 +15076,43 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>129795251</v>
+        <v>129795204</v>
       </c>
       <c r="B143" t="n">
-        <v>79088</v>
+        <v>8451</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E143" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
       <c r="J143" t="inlineStr"/>
       <c r="K143" t="inlineStr"/>
+      <c r="L143" t="inlineStr"/>
+      <c r="M143" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N143" t="inlineStr"/>
       <c r="P143" t="inlineStr">
         <is>
@@ -15120,10 +15120,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>444309</v>
+        <v>444380</v>
       </c>
       <c r="R143" t="n">
-        <v>6787272</v>
+        <v>6787306</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>

--- a/artfynd/A 51041-2025 artfynd.xlsx
+++ b/artfynd/A 51041-2025 artfynd.xlsx
@@ -675,45 +675,54 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129795253</v>
+        <v>129795169</v>
       </c>
       <c r="B2" t="n">
-        <v>79088</v>
+        <v>8451</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>444185</v>
+        <v>444272</v>
       </c>
       <c r="R2" t="n">
-        <v>6787247</v>
+        <v>6787239</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,17 +757,13 @@
           <t>2025-11-22</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Gott om garnlav inom en radie av 50 m.</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -777,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129795261</v>
+        <v>129795253</v>
       </c>
       <c r="B3" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -812,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>444193</v>
+        <v>444185</v>
       </c>
       <c r="R3" t="n">
-        <v>6787130</v>
+        <v>6787247</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -848,6 +853,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-11-22</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Gott om garnlav inom en radie av 50 m.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -874,10 +884,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129795283</v>
+        <v>129795291</v>
       </c>
       <c r="B4" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -903,19 +913,16 @@
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>444337</v>
+        <v>444412</v>
       </c>
       <c r="R4" t="n">
-        <v>6787374</v>
+        <v>6787307</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -956,7 +963,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -975,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129795291</v>
+        <v>129795298</v>
       </c>
       <c r="B5" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1010,10 +1016,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>444412</v>
+        <v>444305</v>
       </c>
       <c r="R5" t="n">
-        <v>6787307</v>
+        <v>6787353</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1072,10 +1078,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129795298</v>
+        <v>129795285</v>
       </c>
       <c r="B6" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1107,10 +1113,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>444305</v>
+        <v>444405</v>
       </c>
       <c r="R6" t="n">
-        <v>6787353</v>
+        <v>6787405</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1169,10 +1175,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129795285</v>
+        <v>129795244</v>
       </c>
       <c r="B7" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1204,10 +1210,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>444405</v>
+        <v>444105</v>
       </c>
       <c r="R7" t="n">
-        <v>6787405</v>
+        <v>6787246</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1266,10 +1272,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129795244</v>
+        <v>129795261</v>
       </c>
       <c r="B8" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1301,10 +1307,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>444105</v>
+        <v>444193</v>
       </c>
       <c r="R8" t="n">
-        <v>6787246</v>
+        <v>6787130</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1363,43 +1369,37 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129795169</v>
+        <v>129795283</v>
       </c>
       <c r="B9" t="n">
-        <v>8451</v>
+        <v>79089</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1407,10 +1407,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>444272</v>
+        <v>444337</v>
       </c>
       <c r="R9" t="n">
-        <v>6787239</v>
+        <v>6787374</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1684,10 +1684,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129795153</v>
+        <v>129795281</v>
       </c>
       <c r="B12" t="n">
-        <v>57737</v>
+        <v>79089</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1695,31 +1695,26 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1727,10 +1722,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>444452</v>
+        <v>444408</v>
       </c>
       <c r="R12" t="n">
-        <v>6787294</v>
+        <v>6787452</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1771,6 +1766,7 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1789,10 +1785,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129795276</v>
+        <v>129795271</v>
       </c>
       <c r="B13" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1827,10 +1823,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>444499</v>
+        <v>444466</v>
       </c>
       <c r="R13" t="n">
-        <v>6787367</v>
+        <v>6787306</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1895,10 +1891,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129795299</v>
+        <v>129795276</v>
       </c>
       <c r="B14" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1924,16 +1920,19 @@
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>444265</v>
+        <v>444499</v>
       </c>
       <c r="R14" t="n">
-        <v>6787372</v>
+        <v>6787367</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1968,12 +1967,18 @@
           <t>2025-11-22</t>
         </is>
       </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 50m.</t>
+        </is>
+      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -1992,10 +1997,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129795281</v>
+        <v>129795299</v>
       </c>
       <c r="B15" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2021,19 +2026,16 @@
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>444408</v>
+        <v>444265</v>
       </c>
       <c r="R15" t="n">
-        <v>6787452</v>
+        <v>6787372</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2074,7 +2076,6 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2093,10 +2094,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129795271</v>
+        <v>129795155</v>
       </c>
       <c r="B16" t="n">
-        <v>79088</v>
+        <v>57737</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2104,26 +2105,31 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2131,7 +2137,7 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>444466</v>
+        <v>444498</v>
       </c>
       <c r="R16" t="n">
         <v>6787306</v>
@@ -2169,18 +2175,12 @@
           <t>2025-11-22</t>
         </is>
       </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 50m.</t>
-        </is>
-      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2199,7 +2199,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129795155</v>
+        <v>129795163</v>
       </c>
       <c r="B17" t="n">
         <v>57737</v>
@@ -2242,10 +2242,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>444498</v>
+        <v>444415</v>
       </c>
       <c r="R17" t="n">
-        <v>6787306</v>
+        <v>6787316</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2304,7 +2304,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129795163</v>
+        <v>129795153</v>
       </c>
       <c r="B18" t="n">
         <v>57737</v>
@@ -2337,7 +2337,7 @@
       <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N18" t="inlineStr"/>
@@ -2347,10 +2347,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>444415</v>
+        <v>444452</v>
       </c>
       <c r="R18" t="n">
-        <v>6787316</v>
+        <v>6787294</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2409,7 +2409,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129795174</v>
+        <v>129795205</v>
       </c>
       <c r="B19" t="n">
         <v>8451</v>
@@ -2453,10 +2453,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>444166</v>
+        <v>444343</v>
       </c>
       <c r="R19" t="n">
-        <v>6787161</v>
+        <v>6787310</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2516,7 +2516,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129795205</v>
+        <v>129795174</v>
       </c>
       <c r="B20" t="n">
         <v>8451</v>
@@ -2560,10 +2560,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>444343</v>
+        <v>444166</v>
       </c>
       <c r="R20" t="n">
-        <v>6787310</v>
+        <v>6787161</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2623,37 +2623,43 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129795310</v>
+        <v>129795207</v>
       </c>
       <c r="B21" t="n">
-        <v>79088</v>
+        <v>8451</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2661,10 +2667,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>444488</v>
+        <v>444221</v>
       </c>
       <c r="R21" t="n">
-        <v>6787445</v>
+        <v>6787340</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2697,11 +2703,6 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-11-22</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Gott om garnlav inom en radie av 40m</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2836,7 +2837,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129795207</v>
+        <v>129795200</v>
       </c>
       <c r="B23" t="n">
         <v>8451</v>
@@ -2880,10 +2881,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>444221</v>
+        <v>444429</v>
       </c>
       <c r="R23" t="n">
-        <v>6787340</v>
+        <v>6787341</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2943,7 +2944,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129795200</v>
+        <v>129795206</v>
       </c>
       <c r="B24" t="n">
         <v>8451</v>
@@ -2987,10 +2988,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>444429</v>
+        <v>444247</v>
       </c>
       <c r="R24" t="n">
-        <v>6787341</v>
+        <v>6787328</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3050,54 +3051,45 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129795206</v>
+        <v>129795273</v>
       </c>
       <c r="B25" t="n">
-        <v>8451</v>
+        <v>79089</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>444247</v>
+        <v>444548</v>
       </c>
       <c r="R25" t="n">
-        <v>6787328</v>
+        <v>6787330</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3138,7 +3130,6 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3157,10 +3148,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129795273</v>
+        <v>129795265</v>
       </c>
       <c r="B26" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3192,10 +3183,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>444548</v>
+        <v>444278</v>
       </c>
       <c r="R26" t="n">
-        <v>6787330</v>
+        <v>6787163</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3254,10 +3245,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129795265</v>
+        <v>129795310</v>
       </c>
       <c r="B27" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3283,16 +3274,19 @@
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>444278</v>
+        <v>444488</v>
       </c>
       <c r="R27" t="n">
-        <v>6787163</v>
+        <v>6787445</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3327,12 +3321,18 @@
           <t>2025-11-22</t>
         </is>
       </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Gott om garnlav inom en radie av 40m</t>
+        </is>
+      </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
       <c r="AE27" t="b">
         <v>0</v>
       </c>
+      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3354,7 +3354,7 @@
         <v>129795278</v>
       </c>
       <c r="B28" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3448,45 +3448,54 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129795256</v>
+        <v>129795187</v>
       </c>
       <c r="B29" t="n">
-        <v>79088</v>
+        <v>8451</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>444226</v>
+        <v>444487</v>
       </c>
       <c r="R29" t="n">
-        <v>6787196</v>
+        <v>6787321</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3527,6 +3536,7 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -3545,10 +3555,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129795142</v>
+        <v>129795268</v>
       </c>
       <c r="B30" t="n">
-        <v>57737</v>
+        <v>79089</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3556,42 +3566,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>444276</v>
+        <v>444383</v>
       </c>
       <c r="R30" t="n">
-        <v>6787287</v>
+        <v>6787218</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3650,10 +3652,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129795268</v>
+        <v>129795256</v>
       </c>
       <c r="B31" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3685,10 +3687,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>444383</v>
+        <v>444226</v>
       </c>
       <c r="R31" t="n">
-        <v>6787218</v>
+        <v>6787196</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3747,41 +3749,40 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129795187</v>
+        <v>129795142</v>
       </c>
       <c r="B32" t="n">
-        <v>8451</v>
+        <v>57737</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr"/>
       <c r="M32" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N32" t="inlineStr"/>
@@ -3791,10 +3792,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>444487</v>
+        <v>444276</v>
       </c>
       <c r="R32" t="n">
-        <v>6787321</v>
+        <v>6787287</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3835,7 +3836,6 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
-      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
@@ -4071,7 +4071,7 @@
         <v>129795270</v>
       </c>
       <c r="B35" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4168,7 +4168,7 @@
         <v>129795296</v>
       </c>
       <c r="B36" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4274,7 +4274,7 @@
         <v>129795269</v>
       </c>
       <c r="B37" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4371,7 +4371,7 @@
         <v>129795249</v>
       </c>
       <c r="B38" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4465,10 +4465,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129795165</v>
+        <v>129795133</v>
       </c>
       <c r="B39" t="n">
-        <v>57737</v>
+        <v>57899</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4476,21 +4476,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4498,7 +4498,7 @@
       <c r="L39" t="inlineStr"/>
       <c r="M39" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N39" t="inlineStr"/>
@@ -4508,10 +4508,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>444251</v>
+        <v>444226</v>
       </c>
       <c r="R39" t="n">
-        <v>6787376</v>
+        <v>6787236</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4570,41 +4570,40 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129795193</v>
+        <v>129795165</v>
       </c>
       <c r="B40" t="n">
-        <v>8451</v>
+        <v>57737</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr"/>
       <c r="L40" t="inlineStr"/>
       <c r="M40" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N40" t="inlineStr"/>
@@ -4614,10 +4613,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>444508</v>
+        <v>444251</v>
       </c>
       <c r="R40" t="n">
-        <v>6787352</v>
+        <v>6787376</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4658,7 +4657,6 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
-      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
@@ -4784,40 +4782,41 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129795133</v>
+        <v>129795193</v>
       </c>
       <c r="B42" t="n">
-        <v>57898</v>
+        <v>8451</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>103021</v>
+        <v>106545</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr"/>
       <c r="K42" t="inlineStr"/>
       <c r="L42" t="inlineStr"/>
       <c r="M42" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N42" t="inlineStr"/>
@@ -4827,10 +4826,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>444226</v>
+        <v>444508</v>
       </c>
       <c r="R42" t="n">
-        <v>6787236</v>
+        <v>6787352</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4871,6 +4870,7 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
+      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
@@ -4889,10 +4889,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129795293</v>
+        <v>129795136</v>
       </c>
       <c r="B43" t="n">
-        <v>79088</v>
+        <v>91644</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4900,34 +4900,37 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr"/>
+      <c r="K43" t="inlineStr"/>
+      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>444365</v>
+        <v>444235</v>
       </c>
       <c r="R43" t="n">
-        <v>6787285</v>
+        <v>6787149</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4962,17 +4965,13 @@
           <t>2025-11-22</t>
         </is>
       </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 50m.</t>
-        </is>
-      </c>
       <c r="AD43" t="b">
         <v>0</v>
       </c>
       <c r="AE43" t="b">
         <v>0</v>
       </c>
+      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
@@ -4991,10 +4990,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129795136</v>
+        <v>129795282</v>
       </c>
       <c r="B44" t="n">
-        <v>91627</v>
+        <v>79089</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5002,21 +5001,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5029,10 +5028,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>444235</v>
+        <v>444374</v>
       </c>
       <c r="R44" t="n">
-        <v>6787149</v>
+        <v>6787384</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5065,6 +5064,11 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-11-22</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 50 m.</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5092,10 +5096,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129795282</v>
+        <v>129795293</v>
       </c>
       <c r="B45" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5121,19 +5125,16 @@
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="J45" t="inlineStr"/>
-      <c r="K45" t="inlineStr"/>
-      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>444374</v>
+        <v>444365</v>
       </c>
       <c r="R45" t="n">
-        <v>6787384</v>
+        <v>6787285</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5170,7 +5171,7 @@
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>Rikligt med garnlav inom en radie av 50 m.</t>
+          <t>Rikligt med garnlav inom en radie av 50m.</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5179,7 +5180,6 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
-      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
@@ -5413,7 +5413,7 @@
         <v>129795138</v>
       </c>
       <c r="B48" t="n">
-        <v>91627</v>
+        <v>91644</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5514,7 +5514,7 @@
         <v>129795309</v>
       </c>
       <c r="B49" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5613,10 +5613,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129795246</v>
+        <v>129795260</v>
       </c>
       <c r="B50" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5648,10 +5648,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>444145</v>
+        <v>444197</v>
       </c>
       <c r="R50" t="n">
-        <v>6787239</v>
+        <v>6787111</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5684,11 +5684,6 @@
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-11-22</t>
-        </is>
-      </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 40m.</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5715,10 +5710,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129795260</v>
+        <v>129795250</v>
       </c>
       <c r="B51" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5750,10 +5745,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>444197</v>
+        <v>444295</v>
       </c>
       <c r="R51" t="n">
-        <v>6787111</v>
+        <v>6787287</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5812,10 +5807,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129795250</v>
+        <v>129795246</v>
       </c>
       <c r="B52" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5847,10 +5842,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>444295</v>
+        <v>444145</v>
       </c>
       <c r="R52" t="n">
-        <v>6787287</v>
+        <v>6787239</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5883,6 +5878,11 @@
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-11-22</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 40m.</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -5909,45 +5909,53 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129795277</v>
+        <v>129795131</v>
       </c>
       <c r="B53" t="n">
-        <v>79088</v>
+        <v>56930</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
+      <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>444491</v>
+        <v>444250</v>
       </c>
       <c r="R53" t="n">
-        <v>6787412</v>
+        <v>6787212</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6006,45 +6014,54 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129795279</v>
+        <v>129795172</v>
       </c>
       <c r="B54" t="n">
-        <v>79088</v>
+        <v>8451</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
+      <c r="J54" t="inlineStr"/>
+      <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr"/>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>444463</v>
+        <v>444225</v>
       </c>
       <c r="R54" t="n">
-        <v>6787459</v>
+        <v>6787223</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6085,6 +6102,7 @@
       <c r="AE54" t="b">
         <v>0</v>
       </c>
+      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
@@ -6103,40 +6121,41 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129795161</v>
+        <v>129795184</v>
       </c>
       <c r="B55" t="n">
-        <v>57737</v>
+        <v>8451</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
+      <c r="J55" t="inlineStr"/>
       <c r="K55" t="inlineStr"/>
       <c r="L55" t="inlineStr"/>
       <c r="M55" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N55" t="inlineStr"/>
@@ -6146,10 +6165,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>444433</v>
+        <v>444452</v>
       </c>
       <c r="R55" t="n">
-        <v>6787338</v>
+        <v>6787305</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6190,6 +6209,7 @@
       <c r="AE55" t="b">
         <v>0</v>
       </c>
+      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
@@ -6208,40 +6228,41 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129795147</v>
+        <v>129795199</v>
       </c>
       <c r="B56" t="n">
-        <v>57737</v>
+        <v>8451</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
+      <c r="J56" t="inlineStr"/>
       <c r="K56" t="inlineStr"/>
       <c r="L56" t="inlineStr"/>
       <c r="M56" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N56" t="inlineStr"/>
@@ -6251,10 +6272,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>444220</v>
+        <v>444431</v>
       </c>
       <c r="R56" t="n">
-        <v>6787221</v>
+        <v>6787350</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6295,6 +6316,7 @@
       <c r="AE56" t="b">
         <v>0</v>
       </c>
+      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
       </c>
@@ -6313,10 +6335,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129795134</v>
+        <v>129795277</v>
       </c>
       <c r="B57" t="n">
-        <v>57898</v>
+        <v>79089</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6324,42 +6346,34 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
-      <c r="K57" t="inlineStr"/>
-      <c r="L57" t="inlineStr"/>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>444289</v>
+        <v>444491</v>
       </c>
       <c r="R57" t="n">
-        <v>6787357</v>
+        <v>6787412</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6418,54 +6432,45 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129795184</v>
+        <v>129795279</v>
       </c>
       <c r="B58" t="n">
-        <v>8451</v>
+        <v>79089</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
-      <c r="J58" t="inlineStr"/>
-      <c r="K58" t="inlineStr"/>
-      <c r="L58" t="inlineStr"/>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>444452</v>
+        <v>444463</v>
       </c>
       <c r="R58" t="n">
-        <v>6787305</v>
+        <v>6787459</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6506,7 +6511,6 @@
       <c r="AE58" t="b">
         <v>0</v>
       </c>
-      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
       </c>
@@ -6525,41 +6529,40 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129795172</v>
+        <v>129795161</v>
       </c>
       <c r="B59" t="n">
-        <v>8451</v>
+        <v>57737</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
-      <c r="J59" t="inlineStr"/>
       <c r="K59" t="inlineStr"/>
       <c r="L59" t="inlineStr"/>
       <c r="M59" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N59" t="inlineStr"/>
@@ -6569,10 +6572,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>444225</v>
+        <v>444433</v>
       </c>
       <c r="R59" t="n">
-        <v>6787223</v>
+        <v>6787338</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6613,7 +6616,6 @@
       <c r="AE59" t="b">
         <v>0</v>
       </c>
-      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
       </c>
@@ -6632,41 +6634,40 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129795199</v>
+        <v>129795147</v>
       </c>
       <c r="B60" t="n">
-        <v>8451</v>
+        <v>57737</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
-      <c r="J60" t="inlineStr"/>
       <c r="K60" t="inlineStr"/>
       <c r="L60" t="inlineStr"/>
       <c r="M60" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N60" t="inlineStr"/>
@@ -6676,10 +6677,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>444431</v>
+        <v>444220</v>
       </c>
       <c r="R60" t="n">
-        <v>6787350</v>
+        <v>6787221</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6720,7 +6721,6 @@
       <c r="AE60" t="b">
         <v>0</v>
       </c>
-      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
       </c>
@@ -6739,32 +6739,32 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129795131</v>
+        <v>129795134</v>
       </c>
       <c r="B61" t="n">
-        <v>56930</v>
+        <v>57899</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>100138</v>
+        <v>103021</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6772,7 +6772,7 @@
       <c r="L61" t="inlineStr"/>
       <c r="M61" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N61" t="inlineStr"/>
@@ -6782,10 +6782,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>444250</v>
+        <v>444289</v>
       </c>
       <c r="R61" t="n">
-        <v>6787212</v>
+        <v>6787357</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6844,41 +6844,40 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129795191</v>
+        <v>129795162</v>
       </c>
       <c r="B62" t="n">
-        <v>8451</v>
+        <v>57737</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
-      <c r="J62" t="inlineStr"/>
       <c r="K62" t="inlineStr"/>
       <c r="L62" t="inlineStr"/>
       <c r="M62" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N62" t="inlineStr"/>
@@ -6888,10 +6887,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>444520</v>
+        <v>444428</v>
       </c>
       <c r="R62" t="n">
-        <v>6787287</v>
+        <v>6787329</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6932,7 +6931,6 @@
       <c r="AE62" t="b">
         <v>0</v>
       </c>
-      <c r="AF62" t="inlineStr"/>
       <c r="AG62" t="b">
         <v>0</v>
       </c>
@@ -6951,54 +6949,45 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129795195</v>
+        <v>129795125</v>
       </c>
       <c r="B63" t="n">
-        <v>8451</v>
+        <v>79708</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
-      <c r="J63" t="inlineStr"/>
-      <c r="K63" t="inlineStr"/>
-      <c r="L63" t="inlineStr"/>
-      <c r="M63" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>444487</v>
+        <v>444329</v>
       </c>
       <c r="R63" t="n">
-        <v>6787441</v>
+        <v>6787371</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7039,7 +7028,6 @@
       <c r="AE63" t="b">
         <v>0</v>
       </c>
-      <c r="AF63" t="inlineStr"/>
       <c r="AG63" t="b">
         <v>0</v>
       </c>
@@ -7058,7 +7046,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129795177</v>
+        <v>129795191</v>
       </c>
       <c r="B64" t="n">
         <v>8451</v>
@@ -7092,7 +7080,7 @@
       <c r="L64" t="inlineStr"/>
       <c r="M64" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N64" t="inlineStr"/>
@@ -7102,10 +7090,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>444342</v>
+        <v>444520</v>
       </c>
       <c r="R64" t="n">
-        <v>6787223</v>
+        <v>6787287</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7165,40 +7153,41 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129795162</v>
+        <v>129795195</v>
       </c>
       <c r="B65" t="n">
-        <v>57737</v>
+        <v>8451</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
+      <c r="J65" t="inlineStr"/>
       <c r="K65" t="inlineStr"/>
       <c r="L65" t="inlineStr"/>
       <c r="M65" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N65" t="inlineStr"/>
@@ -7208,10 +7197,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>444428</v>
+        <v>444487</v>
       </c>
       <c r="R65" t="n">
-        <v>6787329</v>
+        <v>6787441</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7252,6 +7241,7 @@
       <c r="AE65" t="b">
         <v>0</v>
       </c>
+      <c r="AF65" t="inlineStr"/>
       <c r="AG65" t="b">
         <v>0</v>
       </c>
@@ -7270,45 +7260,54 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129795125</v>
+        <v>129795177</v>
       </c>
       <c r="B66" t="n">
-        <v>79707</v>
+        <v>8451</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
+      <c r="J66" t="inlineStr"/>
+      <c r="K66" t="inlineStr"/>
+      <c r="L66" t="inlineStr"/>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>444329</v>
+        <v>444342</v>
       </c>
       <c r="R66" t="n">
-        <v>6787371</v>
+        <v>6787223</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7349,6 +7348,7 @@
       <c r="AE66" t="b">
         <v>0</v>
       </c>
+      <c r="AF66" t="inlineStr"/>
       <c r="AG66" t="b">
         <v>0</v>
       </c>
@@ -7370,7 +7370,7 @@
         <v>129795257</v>
       </c>
       <c r="B67" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7569,10 +7569,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129795135</v>
+        <v>129795280</v>
       </c>
       <c r="B69" t="n">
-        <v>91627</v>
+        <v>79089</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7580,37 +7580,34 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
-      <c r="J69" t="inlineStr"/>
-      <c r="K69" t="inlineStr"/>
-      <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>444158</v>
+        <v>444451</v>
       </c>
       <c r="R69" t="n">
-        <v>6787148</v>
+        <v>6787467</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7651,7 +7648,6 @@
       <c r="AE69" t="b">
         <v>0</v>
       </c>
-      <c r="AF69" t="inlineStr"/>
       <c r="AG69" t="b">
         <v>0</v>
       </c>
@@ -7670,10 +7666,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129795280</v>
+        <v>129795135</v>
       </c>
       <c r="B70" t="n">
-        <v>79088</v>
+        <v>91644</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7681,34 +7677,37 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
+      <c r="J70" t="inlineStr"/>
+      <c r="K70" t="inlineStr"/>
+      <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>444451</v>
+        <v>444158</v>
       </c>
       <c r="R70" t="n">
-        <v>6787467</v>
+        <v>6787148</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7749,6 +7748,7 @@
       <c r="AE70" t="b">
         <v>0</v>
       </c>
+      <c r="AF70" t="inlineStr"/>
       <c r="AG70" t="b">
         <v>0</v>
       </c>
@@ -7770,7 +7770,7 @@
         <v>129795272</v>
       </c>
       <c r="B71" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7867,7 +7867,7 @@
         <v>129795287</v>
       </c>
       <c r="B72" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7964,7 +7964,7 @@
         <v>129795284</v>
       </c>
       <c r="B73" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8061,7 +8061,7 @@
         <v>129795243</v>
       </c>
       <c r="B74" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8260,10 +8260,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129795208</v>
+        <v>129795182</v>
       </c>
       <c r="B76" t="n">
-        <v>58111</v>
+        <v>8451</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8271,29 +8271,30 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>103015</v>
+        <v>106545</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
+      <c r="J76" t="inlineStr"/>
       <c r="K76" t="inlineStr"/>
       <c r="L76" t="inlineStr"/>
       <c r="M76" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N76" t="inlineStr"/>
@@ -8303,10 +8304,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>444434</v>
+        <v>444417</v>
       </c>
       <c r="R76" t="n">
-        <v>6787357</v>
+        <v>6787266</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8347,6 +8348,7 @@
       <c r="AE76" t="b">
         <v>0</v>
       </c>
+      <c r="AF76" t="inlineStr"/>
       <c r="AG76" t="b">
         <v>0</v>
       </c>
@@ -8365,10 +8367,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129795182</v>
+        <v>129795208</v>
       </c>
       <c r="B77" t="n">
-        <v>8451</v>
+        <v>58112</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8376,30 +8378,29 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>106545</v>
+        <v>103015</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
-      <c r="J77" t="inlineStr"/>
       <c r="K77" t="inlineStr"/>
       <c r="L77" t="inlineStr"/>
       <c r="M77" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N77" t="inlineStr"/>
@@ -8409,10 +8410,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>444417</v>
+        <v>444434</v>
       </c>
       <c r="R77" t="n">
-        <v>6787266</v>
+        <v>6787357</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8453,7 +8454,6 @@
       <c r="AE77" t="b">
         <v>0</v>
       </c>
-      <c r="AF77" t="inlineStr"/>
       <c r="AG77" t="b">
         <v>0</v>
       </c>
@@ -8472,37 +8472,43 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129795300</v>
+        <v>129795194</v>
       </c>
       <c r="B78" t="n">
-        <v>79088</v>
+        <v>8451</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
       <c r="J78" t="inlineStr"/>
       <c r="K78" t="inlineStr"/>
+      <c r="L78" t="inlineStr"/>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
@@ -8510,10 +8516,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>444264</v>
+        <v>444501</v>
       </c>
       <c r="R78" t="n">
-        <v>6787349</v>
+        <v>6787363</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8546,11 +8552,6 @@
       <c r="AA78" t="inlineStr">
         <is>
           <t>2025-11-22</t>
-        </is>
-      </c>
-      <c r="AC78" t="inlineStr">
-        <is>
-          <t>Garnlav i de flesta träd inom en radie av 50 m.</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8578,45 +8579,54 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129795127</v>
+        <v>129795173</v>
       </c>
       <c r="B79" t="n">
-        <v>79707</v>
+        <v>8451</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
+      <c r="J79" t="inlineStr"/>
+      <c r="K79" t="inlineStr"/>
+      <c r="L79" t="inlineStr"/>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>444432</v>
+        <v>444220</v>
       </c>
       <c r="R79" t="n">
-        <v>6787388</v>
+        <v>6787210</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8657,6 +8667,7 @@
       <c r="AE79" t="b">
         <v>0</v>
       </c>
+      <c r="AF79" t="inlineStr"/>
       <c r="AG79" t="b">
         <v>0</v>
       </c>
@@ -8675,10 +8686,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129795307</v>
+        <v>129795300</v>
       </c>
       <c r="B80" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8704,16 +8715,19 @@
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
+      <c r="J80" t="inlineStr"/>
+      <c r="K80" t="inlineStr"/>
+      <c r="N80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>444134</v>
+        <v>444264</v>
       </c>
       <c r="R80" t="n">
-        <v>6787304</v>
+        <v>6787349</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8748,12 +8762,18 @@
           <t>2025-11-22</t>
         </is>
       </c>
+      <c r="AC80" t="inlineStr">
+        <is>
+          <t>Garnlav i de flesta träd inom en radie av 50 m.</t>
+        </is>
+      </c>
       <c r="AD80" t="b">
         <v>0</v>
       </c>
       <c r="AE80" t="b">
         <v>0</v>
       </c>
+      <c r="AF80" t="inlineStr"/>
       <c r="AG80" t="b">
         <v>0</v>
       </c>
@@ -8772,10 +8792,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129795286</v>
+        <v>129795307</v>
       </c>
       <c r="B81" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8801,19 +8821,16 @@
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
-      <c r="J81" t="inlineStr"/>
-      <c r="K81" t="inlineStr"/>
-      <c r="N81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>444440</v>
+        <v>444134</v>
       </c>
       <c r="R81" t="n">
-        <v>6787388</v>
+        <v>6787304</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8848,18 +8865,12 @@
           <t>2025-11-22</t>
         </is>
       </c>
-      <c r="AC81" t="inlineStr">
-        <is>
-          <t>Gott om garnlav inom en radie av 50 m.</t>
-        </is>
-      </c>
       <c r="AD81" t="b">
         <v>0</v>
       </c>
       <c r="AE81" t="b">
         <v>0</v>
       </c>
-      <c r="AF81" t="inlineStr"/>
       <c r="AG81" t="b">
         <v>0</v>
       </c>
@@ -8878,10 +8889,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129795241</v>
+        <v>129795286</v>
       </c>
       <c r="B82" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8907,16 +8918,19 @@
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
+      <c r="J82" t="inlineStr"/>
+      <c r="K82" t="inlineStr"/>
+      <c r="N82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>444117</v>
+        <v>444440</v>
       </c>
       <c r="R82" t="n">
-        <v>6787277</v>
+        <v>6787388</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8951,12 +8965,18 @@
           <t>2025-11-22</t>
         </is>
       </c>
+      <c r="AC82" t="inlineStr">
+        <is>
+          <t>Gott om garnlav inom en radie av 50 m.</t>
+        </is>
+      </c>
       <c r="AD82" t="b">
         <v>0</v>
       </c>
       <c r="AE82" t="b">
         <v>0</v>
       </c>
+      <c r="AF82" t="inlineStr"/>
       <c r="AG82" t="b">
         <v>0</v>
       </c>
@@ -8975,10 +8995,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129795126</v>
+        <v>129795241</v>
       </c>
       <c r="B83" t="n">
-        <v>79707</v>
+        <v>79089</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8986,21 +9006,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9010,10 +9030,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>444358</v>
+        <v>444117</v>
       </c>
       <c r="R83" t="n">
-        <v>6787400</v>
+        <v>6787277</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9072,54 +9092,45 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129795194</v>
+        <v>129795126</v>
       </c>
       <c r="B84" t="n">
-        <v>8451</v>
+        <v>79708</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
-      <c r="J84" t="inlineStr"/>
-      <c r="K84" t="inlineStr"/>
-      <c r="L84" t="inlineStr"/>
-      <c r="M84" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>444501</v>
+        <v>444358</v>
       </c>
       <c r="R84" t="n">
-        <v>6787363</v>
+        <v>6787400</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9160,7 +9171,6 @@
       <c r="AE84" t="b">
         <v>0</v>
       </c>
-      <c r="AF84" t="inlineStr"/>
       <c r="AG84" t="b">
         <v>0</v>
       </c>
@@ -9179,54 +9189,45 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129795173</v>
+        <v>129795127</v>
       </c>
       <c r="B85" t="n">
-        <v>8451</v>
+        <v>79708</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
-      <c r="J85" t="inlineStr"/>
-      <c r="K85" t="inlineStr"/>
-      <c r="L85" t="inlineStr"/>
-      <c r="M85" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>444220</v>
+        <v>444432</v>
       </c>
       <c r="R85" t="n">
-        <v>6787210</v>
+        <v>6787388</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9267,7 +9268,6 @@
       <c r="AE85" t="b">
         <v>0</v>
       </c>
-      <c r="AF85" t="inlineStr"/>
       <c r="AG85" t="b">
         <v>0</v>
       </c>
@@ -9289,7 +9289,7 @@
         <v>129795308</v>
       </c>
       <c r="B86" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9386,7 +9386,7 @@
         <v>129795242</v>
       </c>
       <c r="B87" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9480,7 +9480,7 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129795181</v>
+        <v>129795192</v>
       </c>
       <c r="B88" t="n">
         <v>8451</v>
@@ -9524,10 +9524,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>444408</v>
+        <v>444549</v>
       </c>
       <c r="R88" t="n">
-        <v>6787250</v>
+        <v>6787335</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9587,7 +9587,7 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>129795192</v>
+        <v>129795181</v>
       </c>
       <c r="B89" t="n">
         <v>8451</v>
@@ -9631,10 +9631,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>444549</v>
+        <v>444408</v>
       </c>
       <c r="R89" t="n">
-        <v>6787335</v>
+        <v>6787250</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9697,7 +9697,7 @@
         <v>129795305</v>
       </c>
       <c r="B90" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9791,10 +9791,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>129795245</v>
+        <v>129795288</v>
       </c>
       <c r="B91" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9826,10 +9826,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>444113</v>
+        <v>444420</v>
       </c>
       <c r="R91" t="n">
-        <v>6787239</v>
+        <v>6787366</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9888,10 +9888,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>129795297</v>
+        <v>129795245</v>
       </c>
       <c r="B92" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9923,10 +9923,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>444297</v>
+        <v>444113</v>
       </c>
       <c r="R92" t="n">
-        <v>6787333</v>
+        <v>6787239</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9985,10 +9985,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>129795262</v>
+        <v>129795297</v>
       </c>
       <c r="B93" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10020,10 +10020,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>444219</v>
+        <v>444297</v>
       </c>
       <c r="R93" t="n">
-        <v>6787163</v>
+        <v>6787333</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10082,10 +10082,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>129795252</v>
+        <v>129795262</v>
       </c>
       <c r="B94" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10117,10 +10117,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>444249</v>
+        <v>444219</v>
       </c>
       <c r="R94" t="n">
-        <v>6787249</v>
+        <v>6787163</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10153,11 +10153,6 @@
       <c r="AA94" t="inlineStr">
         <is>
           <t>2025-11-22</t>
-        </is>
-      </c>
-      <c r="AC94" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 40m.</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10184,10 +10179,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>129795152</v>
+        <v>129795252</v>
       </c>
       <c r="B95" t="n">
-        <v>57737</v>
+        <v>79089</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10195,42 +10190,34 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
-      <c r="K95" t="inlineStr"/>
-      <c r="L95" t="inlineStr"/>
-      <c r="M95" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>444434</v>
+        <v>444249</v>
       </c>
       <c r="R95" t="n">
-        <v>6787304</v>
+        <v>6787249</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10263,6 +10250,11 @@
       <c r="AA95" t="inlineStr">
         <is>
           <t>2025-11-22</t>
+        </is>
+      </c>
+      <c r="AC95" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 40m.</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10292,7 +10284,7 @@
         <v>129795121</v>
       </c>
       <c r="B96" t="n">
-        <v>79707</v>
+        <v>79708</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10389,7 +10381,7 @@
         <v>129795124</v>
       </c>
       <c r="B97" t="n">
-        <v>79707</v>
+        <v>79708</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10486,7 +10478,7 @@
         <v>129795123</v>
       </c>
       <c r="B98" t="n">
-        <v>79707</v>
+        <v>79708</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10580,41 +10572,40 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>129795167</v>
+        <v>129795152</v>
       </c>
       <c r="B99" t="n">
-        <v>8451</v>
+        <v>57737</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
-      <c r="J99" t="inlineStr"/>
       <c r="K99" t="inlineStr"/>
       <c r="L99" t="inlineStr"/>
       <c r="M99" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N99" t="inlineStr"/>
@@ -10624,10 +10615,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>444132</v>
+        <v>444434</v>
       </c>
       <c r="R99" t="n">
-        <v>6787237</v>
+        <v>6787304</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10668,7 +10659,6 @@
       <c r="AE99" t="b">
         <v>0</v>
       </c>
-      <c r="AF99" t="inlineStr"/>
       <c r="AG99" t="b">
         <v>0</v>
       </c>
@@ -10687,45 +10677,54 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>129795288</v>
+        <v>129795167</v>
       </c>
       <c r="B100" t="n">
-        <v>79088</v>
+        <v>8451</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
+      <c r="J100" t="inlineStr"/>
+      <c r="K100" t="inlineStr"/>
+      <c r="L100" t="inlineStr"/>
+      <c r="M100" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>444420</v>
+        <v>444132</v>
       </c>
       <c r="R100" t="n">
-        <v>6787366</v>
+        <v>6787237</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10766,6 +10765,7 @@
       <c r="AE100" t="b">
         <v>0</v>
       </c>
+      <c r="AF100" t="inlineStr"/>
       <c r="AG100" t="b">
         <v>0</v>
       </c>
@@ -10787,7 +10787,7 @@
         <v>129795264</v>
       </c>
       <c r="B101" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -10884,7 +10884,7 @@
         <v>129795248</v>
       </c>
       <c r="B102" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -10981,7 +10981,7 @@
         <v>129795303</v>
       </c>
       <c r="B103" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11078,7 +11078,7 @@
         <v>129795306</v>
       </c>
       <c r="B104" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11386,7 +11386,7 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>129795178</v>
+        <v>129795186</v>
       </c>
       <c r="B107" t="n">
         <v>8451</v>
@@ -11430,10 +11430,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>444375</v>
+        <v>444473</v>
       </c>
       <c r="R107" t="n">
-        <v>6787207</v>
+        <v>6787334</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11493,7 +11493,7 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>129795186</v>
+        <v>129795178</v>
       </c>
       <c r="B108" t="n">
         <v>8451</v>
@@ -11537,10 +11537,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>444473</v>
+        <v>444375</v>
       </c>
       <c r="R108" t="n">
-        <v>6787334</v>
+        <v>6787207</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11707,10 +11707,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>129795259</v>
+        <v>129795149</v>
       </c>
       <c r="B110" t="n">
-        <v>79088</v>
+        <v>57737</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -11718,34 +11718,42 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
+      <c r="K110" t="inlineStr"/>
+      <c r="L110" t="inlineStr"/>
+      <c r="M110" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N110" t="inlineStr"/>
       <c r="P110" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>444164</v>
+        <v>444223</v>
       </c>
       <c r="R110" t="n">
-        <v>6787121</v>
+        <v>6787221</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11804,7 +11812,7 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>129795149</v>
+        <v>129795145</v>
       </c>
       <c r="B111" t="n">
         <v>57737</v>
@@ -11837,7 +11845,7 @@
       <c r="L111" t="inlineStr"/>
       <c r="M111" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N111" t="inlineStr"/>
@@ -11847,10 +11855,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>444223</v>
+        <v>444228</v>
       </c>
       <c r="R111" t="n">
-        <v>6787221</v>
+        <v>6787226</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -11909,7 +11917,7 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>129795145</v>
+        <v>129795151</v>
       </c>
       <c r="B112" t="n">
         <v>57737</v>
@@ -11952,10 +11960,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>444228</v>
+        <v>444425</v>
       </c>
       <c r="R112" t="n">
-        <v>6787226</v>
+        <v>6787278</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12014,10 +12022,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>129795151</v>
+        <v>129795259</v>
       </c>
       <c r="B113" t="n">
-        <v>57737</v>
+        <v>79089</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -12025,42 +12033,34 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
-      <c r="K113" t="inlineStr"/>
-      <c r="L113" t="inlineStr"/>
-      <c r="M113" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N113" t="inlineStr"/>
       <c r="P113" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>444425</v>
+        <v>444164</v>
       </c>
       <c r="R113" t="n">
-        <v>6787278</v>
+        <v>6787121</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12333,10 +12333,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>129795132</v>
+        <v>129795171</v>
       </c>
       <c r="B116" t="n">
-        <v>56930</v>
+        <v>8451</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -12344,29 +12344,30 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>100138</v>
+        <v>106545</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
+      <c r="J116" t="inlineStr"/>
       <c r="K116" t="inlineStr"/>
       <c r="L116" t="inlineStr"/>
       <c r="M116" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N116" t="inlineStr"/>
@@ -12376,10 +12377,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>444315</v>
+        <v>444185</v>
       </c>
       <c r="R116" t="n">
-        <v>6787291</v>
+        <v>6787226</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12420,6 +12421,7 @@
       <c r="AE116" t="b">
         <v>0</v>
       </c>
+      <c r="AF116" t="inlineStr"/>
       <c r="AG116" t="b">
         <v>0</v>
       </c>
@@ -12441,7 +12443,7 @@
         <v>129795289</v>
       </c>
       <c r="B117" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -12850,10 +12852,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>129795171</v>
+        <v>129795132</v>
       </c>
       <c r="B121" t="n">
-        <v>8451</v>
+        <v>56930</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -12861,30 +12863,29 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>106545</v>
+        <v>100138</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
-      <c r="J121" t="inlineStr"/>
       <c r="K121" t="inlineStr"/>
       <c r="L121" t="inlineStr"/>
       <c r="M121" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="N121" t="inlineStr"/>
@@ -12894,10 +12895,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>444185</v>
+        <v>444315</v>
       </c>
       <c r="R121" t="n">
-        <v>6787226</v>
+        <v>6787291</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -12938,7 +12939,6 @@
       <c r="AE121" t="b">
         <v>0</v>
       </c>
-      <c r="AF121" t="inlineStr"/>
       <c r="AG121" t="b">
         <v>0</v>
       </c>
@@ -12960,7 +12960,7 @@
         <v>129795301</v>
       </c>
       <c r="B122" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -13057,7 +13057,7 @@
         <v>129795294</v>
       </c>
       <c r="B123" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -13470,10 +13470,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>129795267</v>
+        <v>129795258</v>
       </c>
       <c r="B127" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -13505,10 +13505,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>444353</v>
+        <v>444174</v>
       </c>
       <c r="R127" t="n">
-        <v>6787215</v>
+        <v>6787136</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -13541,11 +13541,6 @@
       <c r="AA127" t="inlineStr">
         <is>
           <t>2025-11-22</t>
-        </is>
-      </c>
-      <c r="AC127" t="inlineStr">
-        <is>
-          <t>Gott om garnlav inom en radie av 40m.</t>
         </is>
       </c>
       <c r="AD127" t="b">
@@ -13572,10 +13567,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>129795159</v>
+        <v>129795275</v>
       </c>
       <c r="B128" t="n">
-        <v>57737</v>
+        <v>79089</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -13583,42 +13578,34 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
-      <c r="K128" t="inlineStr"/>
-      <c r="L128" t="inlineStr"/>
-      <c r="M128" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N128" t="inlineStr"/>
       <c r="P128" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>444436</v>
+        <v>444495</v>
       </c>
       <c r="R128" t="n">
-        <v>6787463</v>
+        <v>6787340</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -13677,10 +13664,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>129795137</v>
+        <v>129795267</v>
       </c>
       <c r="B129" t="n">
-        <v>91627</v>
+        <v>79089</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -13688,37 +13675,34 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
-      <c r="J129" t="inlineStr"/>
-      <c r="K129" t="inlineStr"/>
-      <c r="N129" t="inlineStr"/>
       <c r="P129" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>444203</v>
+        <v>444353</v>
       </c>
       <c r="R129" t="n">
-        <v>6787221</v>
+        <v>6787215</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -13753,13 +13737,17 @@
           <t>2025-11-22</t>
         </is>
       </c>
+      <c r="AC129" t="inlineStr">
+        <is>
+          <t>Gott om garnlav inom en radie av 40m.</t>
+        </is>
+      </c>
       <c r="AD129" t="b">
         <v>0</v>
       </c>
       <c r="AE129" t="b">
         <v>0</v>
       </c>
-      <c r="AF129" t="inlineStr"/>
       <c r="AG129" t="b">
         <v>0</v>
       </c>
@@ -13778,10 +13766,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>129795258</v>
+        <v>129795263</v>
       </c>
       <c r="B130" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -13813,10 +13801,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>444174</v>
+        <v>444241</v>
       </c>
       <c r="R130" t="n">
-        <v>6787136</v>
+        <v>6787149</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -13875,10 +13863,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>129795275</v>
+        <v>129795137</v>
       </c>
       <c r="B131" t="n">
-        <v>79088</v>
+        <v>91644</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -13886,34 +13874,37 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
+      <c r="J131" t="inlineStr"/>
+      <c r="K131" t="inlineStr"/>
+      <c r="N131" t="inlineStr"/>
       <c r="P131" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>444495</v>
+        <v>444203</v>
       </c>
       <c r="R131" t="n">
-        <v>6787340</v>
+        <v>6787221</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -13954,6 +13945,7 @@
       <c r="AE131" t="b">
         <v>0</v>
       </c>
+      <c r="AF131" t="inlineStr"/>
       <c r="AG131" t="b">
         <v>0</v>
       </c>
@@ -13972,10 +13964,10 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>129795263</v>
+        <v>129795159</v>
       </c>
       <c r="B132" t="n">
-        <v>79088</v>
+        <v>57737</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -13983,34 +13975,42 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
+      <c r="K132" t="inlineStr"/>
+      <c r="L132" t="inlineStr"/>
+      <c r="M132" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N132" t="inlineStr"/>
       <c r="P132" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>444241</v>
+        <v>444436</v>
       </c>
       <c r="R132" t="n">
-        <v>6787149</v>
+        <v>6787463</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -14283,10 +14283,10 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>129795139</v>
+        <v>129795274</v>
       </c>
       <c r="B135" t="n">
-        <v>91627</v>
+        <v>79089</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -14294,37 +14294,34 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
-      <c r="J135" t="inlineStr"/>
-      <c r="K135" t="inlineStr"/>
-      <c r="N135" t="inlineStr"/>
       <c r="P135" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>444342</v>
+        <v>444538</v>
       </c>
       <c r="R135" t="n">
-        <v>6787240</v>
+        <v>6787325</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -14365,7 +14362,6 @@
       <c r="AE135" t="b">
         <v>0</v>
       </c>
-      <c r="AF135" t="inlineStr"/>
       <c r="AG135" t="b">
         <v>0</v>
       </c>
@@ -14384,10 +14380,10 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>129795254</v>
+        <v>129795304</v>
       </c>
       <c r="B136" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -14413,19 +14409,16 @@
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
-      <c r="J136" t="inlineStr"/>
-      <c r="K136" t="inlineStr"/>
-      <c r="N136" t="inlineStr"/>
       <c r="P136" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>444199</v>
+        <v>444172</v>
       </c>
       <c r="R136" t="n">
-        <v>6787221</v>
+        <v>6787339</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -14466,7 +14459,6 @@
       <c r="AE136" t="b">
         <v>0</v>
       </c>
-      <c r="AF136" t="inlineStr"/>
       <c r="AG136" t="b">
         <v>0</v>
       </c>
@@ -14485,10 +14477,10 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>129795266</v>
+        <v>129795254</v>
       </c>
       <c r="B137" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -14514,16 +14506,19 @@
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
+      <c r="J137" t="inlineStr"/>
+      <c r="K137" t="inlineStr"/>
+      <c r="N137" t="inlineStr"/>
       <c r="P137" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>444314</v>
+        <v>444199</v>
       </c>
       <c r="R137" t="n">
-        <v>6787212</v>
+        <v>6787221</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -14558,17 +14553,13 @@
           <t>2025-11-22</t>
         </is>
       </c>
-      <c r="AC137" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 40m</t>
-        </is>
-      </c>
       <c r="AD137" t="b">
         <v>0</v>
       </c>
       <c r="AE137" t="b">
         <v>0</v>
       </c>
+      <c r="AF137" t="inlineStr"/>
       <c r="AG137" t="b">
         <v>0</v>
       </c>
@@ -14587,10 +14578,10 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>129795247</v>
+        <v>129795302</v>
       </c>
       <c r="B138" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -14622,10 +14613,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>444225</v>
+        <v>444222</v>
       </c>
       <c r="R138" t="n">
-        <v>6787275</v>
+        <v>6787345</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -14684,10 +14675,10 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>129795274</v>
+        <v>129795251</v>
       </c>
       <c r="B139" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -14713,16 +14704,19 @@
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
+      <c r="J139" t="inlineStr"/>
+      <c r="K139" t="inlineStr"/>
+      <c r="N139" t="inlineStr"/>
       <c r="P139" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>444538</v>
+        <v>444309</v>
       </c>
       <c r="R139" t="n">
-        <v>6787325</v>
+        <v>6787272</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -14763,6 +14757,7 @@
       <c r="AE139" t="b">
         <v>0</v>
       </c>
+      <c r="AF139" t="inlineStr"/>
       <c r="AG139" t="b">
         <v>0</v>
       </c>
@@ -14781,10 +14776,10 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>129795304</v>
+        <v>129795266</v>
       </c>
       <c r="B140" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -14816,10 +14811,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>444172</v>
+        <v>444314</v>
       </c>
       <c r="R140" t="n">
-        <v>6787339</v>
+        <v>6787212</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -14852,6 +14847,11 @@
       <c r="AA140" t="inlineStr">
         <is>
           <t>2025-11-22</t>
+        </is>
+      </c>
+      <c r="AC140" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 40m</t>
         </is>
       </c>
       <c r="AD140" t="b">
@@ -14878,10 +14878,10 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>129795302</v>
+        <v>129795247</v>
       </c>
       <c r="B141" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -14913,10 +14913,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>444222</v>
+        <v>444225</v>
       </c>
       <c r="R141" t="n">
-        <v>6787345</v>
+        <v>6787275</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -14975,10 +14975,10 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>129795251</v>
+        <v>129795139</v>
       </c>
       <c r="B142" t="n">
-        <v>79088</v>
+        <v>91644</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -14986,21 +14986,21 @@
         </is>
       </c>
       <c r="E142" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
@@ -15013,10 +15013,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>444309</v>
+        <v>444342</v>
       </c>
       <c r="R142" t="n">
-        <v>6787272</v>
+        <v>6787240</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>

--- a/artfynd/A 51041-2025 artfynd.xlsx
+++ b/artfynd/A 51041-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129795283</v>
+        <v>129795253</v>
       </c>
       <c r="B2" t="n">
         <v>79095</v>
@@ -704,19 +704,16 @@
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>444337</v>
+        <v>444185</v>
       </c>
       <c r="R2" t="n">
-        <v>6787374</v>
+        <v>6787247</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,13 +748,17 @@
           <t>2025-11-22</t>
         </is>
       </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Gott om garnlav inom en radie av 50 m.</t>
+        </is>
+      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -776,54 +777,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129795197</v>
+        <v>129795291</v>
       </c>
       <c r="B3" t="n">
-        <v>8451</v>
+        <v>79095</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>444406</v>
+        <v>444412</v>
       </c>
       <c r="R3" t="n">
-        <v>6787392</v>
+        <v>6787307</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -864,7 +856,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -883,7 +874,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129795253</v>
+        <v>129795298</v>
       </c>
       <c r="B4" t="n">
         <v>79095</v>
@@ -918,10 +909,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>444185</v>
+        <v>444305</v>
       </c>
       <c r="R4" t="n">
-        <v>6787247</v>
+        <v>6787353</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -954,11 +945,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-11-22</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Gott om garnlav inom en radie av 50 m.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -985,7 +971,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129795291</v>
+        <v>129795285</v>
       </c>
       <c r="B5" t="n">
         <v>79095</v>
@@ -1020,10 +1006,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>444412</v>
+        <v>444405</v>
       </c>
       <c r="R5" t="n">
-        <v>6787307</v>
+        <v>6787405</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1082,7 +1068,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129795298</v>
+        <v>129795244</v>
       </c>
       <c r="B6" t="n">
         <v>79095</v>
@@ -1117,10 +1103,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>444305</v>
+        <v>444105</v>
       </c>
       <c r="R6" t="n">
-        <v>6787353</v>
+        <v>6787246</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1179,7 +1165,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129795285</v>
+        <v>129795261</v>
       </c>
       <c r="B7" t="n">
         <v>79095</v>
@@ -1214,10 +1200,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>444405</v>
+        <v>444193</v>
       </c>
       <c r="R7" t="n">
-        <v>6787405</v>
+        <v>6787130</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1276,7 +1262,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129795244</v>
+        <v>129795283</v>
       </c>
       <c r="B8" t="n">
         <v>79095</v>
@@ -1305,16 +1291,19 @@
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>444105</v>
+        <v>444337</v>
       </c>
       <c r="R8" t="n">
-        <v>6787246</v>
+        <v>6787374</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1355,6 +1344,7 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1373,45 +1363,54 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129795261</v>
+        <v>129795169</v>
       </c>
       <c r="B9" t="n">
-        <v>79095</v>
+        <v>8451</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>444193</v>
+        <v>444272</v>
       </c>
       <c r="R9" t="n">
-        <v>6787130</v>
+        <v>6787239</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1452,6 +1451,7 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1470,7 +1470,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129795169</v>
+        <v>129795190</v>
       </c>
       <c r="B10" t="n">
         <v>8451</v>
@@ -1514,10 +1514,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>444272</v>
+        <v>444510</v>
       </c>
       <c r="R10" t="n">
-        <v>6787239</v>
+        <v>6787276</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1577,7 +1577,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129795190</v>
+        <v>129795197</v>
       </c>
       <c r="B11" t="n">
         <v>8451</v>
@@ -1621,10 +1621,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>444510</v>
+        <v>444406</v>
       </c>
       <c r="R11" t="n">
-        <v>6787276</v>
+        <v>6787392</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1684,37 +1684,43 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129795281</v>
+        <v>129795174</v>
       </c>
       <c r="B12" t="n">
-        <v>79095</v>
+        <v>8451</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1722,10 +1728,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>444408</v>
+        <v>444166</v>
       </c>
       <c r="R12" t="n">
-        <v>6787452</v>
+        <v>6787161</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1785,37 +1791,43 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129795271</v>
+        <v>129795205</v>
       </c>
       <c r="B13" t="n">
-        <v>79095</v>
+        <v>8451</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1823,10 +1835,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>444466</v>
+        <v>444343</v>
       </c>
       <c r="R13" t="n">
-        <v>6787306</v>
+        <v>6787310</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1859,11 +1871,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-11-22</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 50m.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1891,7 +1898,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129795276</v>
+        <v>129795281</v>
       </c>
       <c r="B14" t="n">
         <v>79095</v>
@@ -1929,10 +1936,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>444499</v>
+        <v>444408</v>
       </c>
       <c r="R14" t="n">
-        <v>6787367</v>
+        <v>6787452</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1965,11 +1972,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-11-22</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 50m.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -1997,7 +1999,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129795299</v>
+        <v>129795271</v>
       </c>
       <c r="B15" t="n">
         <v>79095</v>
@@ -2026,16 +2028,19 @@
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Storfljot, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>444265</v>
+        <v>444466</v>
       </c>
       <c r="R15" t="n">
-        <v>6787372</v>
+        <v>6787306</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2070,12 +2075,18 @@
           <t>2025-11-22</t>
         </is>
       </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 50m.</t>
+        </is>
+      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t=